--- a/data/DLG.MI.xlsx
+++ b/data/DLG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1940" uniqueCount="1940">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1942" uniqueCount="1942">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,109 +44,109 @@
     <t xml:space="preserve">DLG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5564212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6553955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1757488250732</t>
+    <t xml:space="preserve">20.5564231872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6553974151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1757469177246</t>
   </si>
   <si>
     <t xml:space="preserve">19.9777965545654</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7722320556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4905319213867</t>
+    <t xml:space="preserve">19.7722301483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4905300140381</t>
   </si>
   <si>
     <t xml:space="preserve">19.8864345550537</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5160064697266</t>
+    <t xml:space="preserve">18.5160083770752</t>
   </si>
   <si>
     <t xml:space="preserve">17.6328392028809</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4348907470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5262489318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0542163848877</t>
+    <t xml:space="preserve">17.4348926544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5262508392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0542125701904</t>
   </si>
   <si>
     <t xml:space="preserve">16.8943328857422</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0135173797607</t>
+    <t xml:space="preserve">18.0135154724121</t>
   </si>
   <si>
     <t xml:space="preserve">16.6354751586914</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4451370239258</t>
+    <t xml:space="preserve">16.4451389312744</t>
   </si>
   <si>
     <t xml:space="preserve">16.7116088867188</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8029727935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6735420227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1329879760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9654865264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6533346176147</t>
+    <t xml:space="preserve">16.8029708862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6735382080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.132984161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9654855728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6533336639404</t>
   </si>
   <si>
     <t xml:space="preserve">14.9909620285034</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7777805328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3335704803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4123363494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7397146224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4553804397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2574338912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4097023010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7523097991943</t>
+    <t xml:space="preserve">14.7777814865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3335666656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4123334884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7397165298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4553823471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2574300765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4097013473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7523107528687</t>
   </si>
   <si>
     <t xml:space="preserve">15.3868608474731</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9121923446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9578723907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.584813117981</t>
+    <t xml:space="preserve">15.9121932983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9578714370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5848150253296</t>
   </si>
   <si>
     <t xml:space="preserve">16.1253700256348</t>
@@ -161,115 +161,115 @@
     <t xml:space="preserve">16.7496757507324</t>
   </si>
   <si>
-    <t xml:space="preserve">15.881742477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2193651199341</t>
+    <t xml:space="preserve">15.8817358016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2193660736084</t>
   </si>
   <si>
     <t xml:space="preserve">15.3792486190796</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0872993469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7142419815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2878866195679</t>
+    <t xml:space="preserve">16.0873050689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7142391204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2878837585449</t>
   </si>
   <si>
     <t xml:space="preserve">15.8969631195068</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3183422088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6076545715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9274168014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9883298873901</t>
+    <t xml:space="preserve">15.3183393478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6076517105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9274158477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9883260726929</t>
   </si>
   <si>
     <t xml:space="preserve">15.8893527984619</t>
   </si>
   <si>
-    <t xml:space="preserve">15.615270614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.356406211853</t>
+    <t xml:space="preserve">15.6152677536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3564081192017</t>
   </si>
   <si>
     <t xml:space="preserve">15.1356163024902</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2269773483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3487958908081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0442562103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2345914840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0594844818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1432275772095</t>
+    <t xml:space="preserve">15.2269792556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3487949371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0442533493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2345924377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0594835281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1432304382324</t>
   </si>
   <si>
     <t xml:space="preserve">14.5493803024292</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7853956222534</t>
+    <t xml:space="preserve">14.7853965759277</t>
   </si>
   <si>
     <t xml:space="preserve">14.8234615325928</t>
   </si>
   <si>
-    <t xml:space="preserve">14.783166885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9779891967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1494340896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9624052047729</t>
+    <t xml:space="preserve">14.7831659317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9779872894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1572256088257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1494312286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9624032974243</t>
   </si>
   <si>
     <t xml:space="preserve">14.9857816696167</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9546117782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8533010482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4689416885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6715593338013</t>
+    <t xml:space="preserve">14.954610824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8533000946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4689426422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.671558380127</t>
   </si>
   <si>
     <t xml:space="preserve">16.21706199646</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7572803497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0300312042236</t>
+    <t xml:space="preserve">15.7572774887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0300331115723</t>
   </si>
   <si>
     <t xml:space="preserve">16.2404441833496</t>
@@ -278,25 +278,25 @@
     <t xml:space="preserve">16.1469268798828</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3495426177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5053997039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3105773925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7288932800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.793737411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0742797851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7625694274902</t>
+    <t xml:space="preserve">16.3495407104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5054016113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3105812072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7288913726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7937393188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0742835998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7625675201416</t>
   </si>
   <si>
     <t xml:space="preserve">16.7547740936279</t>
@@ -305,175 +305,175 @@
     <t xml:space="preserve">16.8482894897461</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1132488250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3002796173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7678565979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9081268310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.947093963623</t>
+    <t xml:space="preserve">17.1132469177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3002777099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7678508758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9081249237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9470901489258</t>
   </si>
   <si>
     <t xml:space="preserve">18.063985824585</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4847984313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.788724899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4614238739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3367385864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2743968963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0795707702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6484527587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8276901245117</t>
+    <t xml:space="preserve">18.4848022460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7887268066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4614219665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3367366790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.274393081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0795726776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6484546661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8276882171631</t>
   </si>
   <si>
     <t xml:space="preserve">18.4536304473877</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8379917144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3937950134277</t>
+    <t xml:space="preserve">17.8379898071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3937931060791</t>
   </si>
   <si>
     <t xml:space="preserve">17.2535190582275</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0820770263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4951038360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9237117767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8224029541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7834377288818</t>
+    <t xml:space="preserve">17.0820732116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4951000213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9237098693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8224048614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7834396362305</t>
   </si>
   <si>
     <t xml:space="preserve">17.9315052032471</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6768474578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.523494720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1157569885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3651275634766</t>
+    <t xml:space="preserve">16.6768436431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.523491859436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1157531738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3651294708252</t>
   </si>
   <si>
     <t xml:space="preserve">16.6612567901611</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6300888061523</t>
+    <t xml:space="preserve">16.6300849914551</t>
   </si>
   <si>
     <t xml:space="preserve">15.8975515365601</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7806587219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5468702316284</t>
+    <t xml:space="preserve">15.7806606292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5468721389771</t>
   </si>
   <si>
     <t xml:space="preserve">15.7884531021118</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3729190826416</t>
+    <t xml:space="preserve">16.3729228973389</t>
   </si>
   <si>
     <t xml:space="preserve">16.1858901977539</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1625137329102</t>
+    <t xml:space="preserve">16.1625118255615</t>
   </si>
   <si>
     <t xml:space="preserve">16.4196796417236</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5209846496582</t>
+    <t xml:space="preserve">16.5209884643555</t>
   </si>
   <si>
     <t xml:space="preserve">16.5287799835205</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8404960632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9184226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8716678619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8015289306641</t>
+    <t xml:space="preserve">16.8404941558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9184246063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8716640472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8015308380127</t>
   </si>
   <si>
     <t xml:space="preserve">17.6119956970215</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2223510742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5964088439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4171733856201</t>
+    <t xml:space="preserve">17.2223472595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5964069366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4171752929688</t>
   </si>
   <si>
     <t xml:space="preserve">17.6587524414062</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3158645629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.323657989502</t>
+    <t xml:space="preserve">17.3158626556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3236560821533</t>
   </si>
   <si>
     <t xml:space="preserve">17.5028915405273</t>
   </si>
   <si>
-    <t xml:space="preserve">18.056188583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5393524169922</t>
+    <t xml:space="preserve">18.0561923980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5393543243408</t>
   </si>
   <si>
     <t xml:space="preserve">18.7030029296875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6640357971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8121013641357</t>
+    <t xml:space="preserve">18.6640377044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8121032714844</t>
   </si>
   <si>
     <t xml:space="preserve">18.095157623291</t>
@@ -482,10 +482,10 @@
     <t xml:space="preserve">18.1497058868408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9003314971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1575012207031</t>
+    <t xml:space="preserve">17.900333404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1574993133545</t>
   </si>
   <si>
     <t xml:space="preserve">17.8769550323486</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">17.6665458679199</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9704666137695</t>
+    <t xml:space="preserve">17.9704685211182</t>
   </si>
   <si>
     <t xml:space="preserve">18.0328121185303</t>
@@ -509,13 +509,13 @@
     <t xml:space="preserve">17.362621307373</t>
   </si>
   <si>
-    <t xml:space="preserve">17.40159034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2379360198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4093780517578</t>
+    <t xml:space="preserve">17.4015884399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2379341125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4093799591064</t>
   </si>
   <si>
     <t xml:space="preserve">17.1444187164307</t>
@@ -524,40 +524,40 @@
     <t xml:space="preserve">16.8171157836914</t>
   </si>
   <si>
-    <t xml:space="preserve">16.614501953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6846370697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0197353363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1288356781006</t>
+    <t xml:space="preserve">16.6144981384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6846389770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0197334289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1288318634033</t>
   </si>
   <si>
     <t xml:space="preserve">17.2691059112549</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9963550567627</t>
+    <t xml:space="preserve">16.9963531494141</t>
   </si>
   <si>
     <t xml:space="preserve">17.4405498504639</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4639320373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8327045440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8249111175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9028415679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.785945892334</t>
+    <t xml:space="preserve">17.4639282226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8327026367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8249092102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9028396606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7859439849854</t>
   </si>
   <si>
     <t xml:space="preserve">16.7469825744629</t>
@@ -566,46 +566,46 @@
     <t xml:space="preserve">17.2768993377686</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2457256317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0509052276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0976619720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.957389831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2301406860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2067623138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4327621459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2846927642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0664901733398</t>
+    <t xml:space="preserve">17.2457294464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0509014129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0976638793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9573917388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2301425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.20676612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4327602386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2846908569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0664882659912</t>
   </si>
   <si>
     <t xml:space="preserve">15.9521045684814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9832782745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.256031036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3339557647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9988613128662</t>
+    <t xml:space="preserve">15.9832744598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2560272216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3339576721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9988622665405</t>
   </si>
   <si>
     <t xml:space="preserve">15.4065999984741</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">15.3130826950073</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1182622909546</t>
+    <t xml:space="preserve">15.1182613372803</t>
   </si>
   <si>
     <t xml:space="preserve">16.5131950378418</t>
@@ -623,67 +623,67 @@
     <t xml:space="preserve">16.0923767089844</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9131383895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1780986785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7158088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0586986541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4664344787598</t>
+    <t xml:space="preserve">15.9131374359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1780967712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7158107757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0586948394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.466438293457</t>
   </si>
   <si>
     <t xml:space="preserve">16.2248573303223</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9754819869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7080192565918</t>
+    <t xml:space="preserve">15.9754800796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7080154418945</t>
   </si>
   <si>
     <t xml:space="preserve">16.4976100921631</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6924324035645</t>
+    <t xml:space="preserve">16.6924304962158</t>
   </si>
   <si>
     <t xml:space="preserve">16.5599517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">16.770357131958</t>
+    <t xml:space="preserve">16.7703590393066</t>
   </si>
   <si>
     <t xml:space="preserve">16.8638744354248</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0275249481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4561386108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4483432769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8847484588623</t>
+    <t xml:space="preserve">17.0275287628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4561347961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4483451843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8847503662109</t>
   </si>
   <si>
     <t xml:space="preserve">18.1185321807861</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2354278564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0172290802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8457813262939</t>
+    <t xml:space="preserve">18.2354297637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0172271728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8457832336426</t>
   </si>
   <si>
     <t xml:space="preserve">17.9626750946045</t>
@@ -692,46 +692,46 @@
     <t xml:space="preserve">17.8691635131836</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6353740692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7912311553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5808238983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6509590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1107387542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9782619476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3133563995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2042579650879</t>
+    <t xml:space="preserve">17.6353759765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7912330627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5808200836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6509609222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1107425689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9782600402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3133583068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2042560577393</t>
   </si>
   <si>
     <t xml:space="preserve">18.4692153930664</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0848560333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3498134613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2952632904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4667110443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2485065460205</t>
+    <t xml:space="preserve">19.0848541259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.349817276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2952651977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4667091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2485103607178</t>
   </si>
   <si>
     <t xml:space="preserve">19.3186473846436</t>
@@ -740,61 +740,61 @@
     <t xml:space="preserve">19.0614776611328</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4199504852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2407150268555</t>
+    <t xml:space="preserve">19.4199523925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2407169342041</t>
   </si>
   <si>
     <t xml:space="preserve">19.0926494598389</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4511241912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8588638305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6406631469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9056224822998</t>
+    <t xml:space="preserve">19.4511222839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8588600158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6406574249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9056167602539</t>
   </si>
   <si>
     <t xml:space="preserve">19.2329216003418</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4978828430176</t>
+    <t xml:space="preserve">19.4978809356689</t>
   </si>
   <si>
     <t xml:space="preserve">20.1914501190186</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9888324737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1213130950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9732475280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9551544189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6278553009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2201156616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0408782958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7915058135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7447490692139</t>
+    <t xml:space="preserve">19.9888381958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1213092803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9732494354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9551582336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.627857208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2201137542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0408802032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7915077209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7447452545166</t>
   </si>
   <si>
     <t xml:space="preserve">20.8616428375244</t>
@@ -803,64 +803,64 @@
     <t xml:space="preserve">21.2434959411621</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9006061553955</t>
+    <t xml:space="preserve">20.9006080627441</t>
   </si>
   <si>
     <t xml:space="preserve">21.0330867767334</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9785385131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6721057891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4149398803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3136310577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1967391967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4227313995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5785884857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1884727478027</t>
+    <t xml:space="preserve">20.9785327911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6721038818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4149379730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3136348724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1967353820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4227333068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.578592300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1884746551514</t>
   </si>
   <si>
     <t xml:space="preserve">22.1002006530762</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9477310180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0279769897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9878540039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8273620605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3489685058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4693393707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8946552276611</t>
+    <t xml:space="preserve">21.947732925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0279788970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9878559112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.827356338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.348970413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4693374633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8946533203125</t>
   </si>
   <si>
     <t xml:space="preserve">23.3199672698975</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2878646850586</t>
+    <t xml:space="preserve">23.2878665924072</t>
   </si>
   <si>
     <t xml:space="preserve">22.878604888916</t>
@@ -869,10 +869,10 @@
     <t xml:space="preserve">23.0310726165771</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4483585357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0230503082275</t>
+    <t xml:space="preserve">23.4483604431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0230484008789</t>
   </si>
   <si>
     <t xml:space="preserve">22.9026775360107</t>
@@ -881,13 +881,13 @@
     <t xml:space="preserve">22.6218109130859</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5014400482178</t>
+    <t xml:space="preserve">22.5014419555664</t>
   </si>
   <si>
     <t xml:space="preserve">23.255765914917</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8434085845947</t>
+    <t xml:space="preserve">21.8434066772461</t>
   </si>
   <si>
     <t xml:space="preserve">22.0600776672363</t>
@@ -896,58 +896,58 @@
     <t xml:space="preserve">22.6298351287842</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7341575622559</t>
+    <t xml:space="preserve">22.7341594696045</t>
   </si>
   <si>
     <t xml:space="preserve">22.9267501831055</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2316932678223</t>
+    <t xml:space="preserve">23.2316951751709</t>
   </si>
   <si>
     <t xml:space="preserve">23.1434192657471</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1674938201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.65700340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7693519592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6730556488037</t>
+    <t xml:space="preserve">23.1674957275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6570053100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7693557739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6730537414551</t>
   </si>
   <si>
     <t xml:space="preserve">23.8495998382568</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7613296508789</t>
+    <t xml:space="preserve">23.7613277435303</t>
   </si>
   <si>
     <t xml:space="preserve">23.4002132415771</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2958908081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4323120117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7051563262939</t>
+    <t xml:space="preserve">23.2958927154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.432315826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7051544189453</t>
   </si>
   <si>
     <t xml:space="preserve">23.0069999694824</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8304538726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7903251647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0631713867188</t>
+    <t xml:space="preserve">22.8304557800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7903308868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0631732940674</t>
   </si>
   <si>
     <t xml:space="preserve">23.8255252838135</t>
@@ -956,16 +956,16 @@
     <t xml:space="preserve">23.3921890258789</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2637939453125</t>
+    <t xml:space="preserve">23.2637901306152</t>
   </si>
   <si>
     <t xml:space="preserve">23.2718162536621</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1915721893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9989738464355</t>
+    <t xml:space="preserve">23.1915664672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9989719390869</t>
   </si>
   <si>
     <t xml:space="preserve">21.9076042175293</t>
@@ -974,34 +974,34 @@
     <t xml:space="preserve">22.0199527740479</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0761222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5545177459717</t>
+    <t xml:space="preserve">22.0761260986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.554515838623</t>
   </si>
   <si>
     <t xml:space="preserve">21.4742698669434</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6267414093018</t>
+    <t xml:space="preserve">21.6267375946045</t>
   </si>
   <si>
     <t xml:space="preserve">21.7711868286133</t>
   </si>
   <si>
-    <t xml:space="preserve">21.739086151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8674831390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8594551086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5255107879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7421836853027</t>
+    <t xml:space="preserve">21.7390880584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8674850463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8594570159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5255126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7421798706055</t>
   </si>
   <si>
     <t xml:space="preserve">22.3730411529541</t>
@@ -1010,94 +1010,94 @@
     <t xml:space="preserve">22.7181072235107</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8625526428223</t>
+    <t xml:space="preserve">22.8625545501709</t>
   </si>
   <si>
     <t xml:space="preserve">22.7100830078125</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5335388183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6539096832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2927951812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7551364898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2415523529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9927806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9446353912354</t>
+    <t xml:space="preserve">22.5335350036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6539115905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2927932739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7551383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2415542602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9927845001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9446334838867</t>
   </si>
   <si>
     <t xml:space="preserve">21.0730323791504</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0489540100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6396942138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4310474395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4872245788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8804359436035</t>
+    <t xml:space="preserve">21.0489597320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6396903991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4310512542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4872226715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8804378509521</t>
   </si>
   <si>
     <t xml:space="preserve">20.8643856048584</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7119121551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.575496673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5995674133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6477165222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6156215667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5915451049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3508014678955</t>
+    <t xml:space="preserve">20.7119178771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5754947662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.599573135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6477184295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6156196594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5915470123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3508071899414</t>
   </si>
   <si>
     <t xml:space="preserve">20.3427772521973</t>
   </si>
   <si>
-    <t xml:space="preserve">20.286600112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7440185546875</t>
+    <t xml:space="preserve">20.2866039276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7440166473389</t>
   </si>
   <si>
     <t xml:space="preserve">20.6717929840088</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4952487945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7359924316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2174777984619</t>
+    <t xml:space="preserve">20.495246887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7359886169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2174758911133</t>
   </si>
   <si>
     <t xml:space="preserve">21.0168571472168</t>
@@ -1106,19 +1106,19 @@
     <t xml:space="preserve">21.3538970947266</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2335262298584</t>
+    <t xml:space="preserve">21.2335243225098</t>
   </si>
   <si>
     <t xml:space="preserve">20.9045104980469</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5594482421875</t>
+    <t xml:space="preserve">20.5594444274902</t>
   </si>
   <si>
     <t xml:space="preserve">20.5353736877441</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4711761474609</t>
+    <t xml:space="preserve">20.4711723327637</t>
   </si>
   <si>
     <t xml:space="preserve">20.7520408630371</t>
@@ -1127,13 +1127,13 @@
     <t xml:space="preserve">21.3779697418213</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0650043487549</t>
+    <t xml:space="preserve">21.0650100708008</t>
   </si>
   <si>
     <t xml:space="preserve">21.2255039215088</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3699474334717</t>
+    <t xml:space="preserve">21.3699436187744</t>
   </si>
   <si>
     <t xml:space="preserve">21.9156322479248</t>
@@ -1142,28 +1142,28 @@
     <t xml:space="preserve">21.4582195281982</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8032817840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7952556610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3088455200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.140323638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2285995483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2045211791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1483516693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.694034576416</t>
+    <t xml:space="preserve">21.8032855987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.795259475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3088436126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1403255462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2285957336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2045249938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1483497619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6940307617188</t>
   </si>
   <si>
     <t xml:space="preserve">22.0921764373779</t>
@@ -1172,64 +1172,64 @@
     <t xml:space="preserve">22.1082248687744</t>
   </si>
   <si>
-    <t xml:space="preserve">22.164400100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7742805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7662582397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5897102355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5415630340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4131679534912</t>
+    <t xml:space="preserve">22.1643981933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7742786407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7662563323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5897121429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.541561126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4131698608398</t>
   </si>
   <si>
     <t xml:space="preserve">22.5174865722656</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1563758850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8353843688965</t>
+    <t xml:space="preserve">22.1563739776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8353824615479</t>
   </si>
   <si>
     <t xml:space="preserve">22.5495853424072</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2526721954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2125492095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2594337463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9335155487061</t>
+    <t xml:space="preserve">22.2526741027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2125473022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2594356536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9335136413574</t>
   </si>
   <si>
     <t xml:space="preserve">19.861291885376</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6927738189697</t>
+    <t xml:space="preserve">19.6927719116211</t>
   </si>
   <si>
     <t xml:space="preserve">19.6205501556396</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5403003692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4921550750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4279556274414</t>
+    <t xml:space="preserve">19.5403022766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4921531677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4279537200928</t>
   </si>
   <si>
     <t xml:space="preserve">19.7409210205078</t>
@@ -1241,10 +1241,10 @@
     <t xml:space="preserve">19.805118560791</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4199314117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7569713592529</t>
+    <t xml:space="preserve">19.4199275970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7569694519043</t>
   </si>
   <si>
     <t xml:space="preserve">19.6606731414795</t>
@@ -1253,16 +1253,16 @@
     <t xml:space="preserve">20.1421585083008</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2304306030273</t>
+    <t xml:space="preserve">20.2304286956787</t>
   </si>
   <si>
     <t xml:space="preserve">20.4069766998291</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4792003631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2545070648193</t>
+    <t xml:space="preserve">20.4791965484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2545032501221</t>
   </si>
   <si>
     <t xml:space="preserve">19.9415397644043</t>
@@ -1271,76 +1271,76 @@
     <t xml:space="preserve">20.0619106292725</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9254875183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9366111755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0971031188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8162403106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3989505767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6878452301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4390735626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2464790344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4631519317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5433940887451</t>
+    <t xml:space="preserve">19.9254913330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9366092681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0971050262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8162384033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3989486694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6878433227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4390754699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2464809417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4631481170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5433959960938</t>
   </si>
   <si>
     <t xml:space="preserve">21.4100723266602</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0088310241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6508121490479</t>
+    <t xml:space="preserve">21.0088329315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6508140563965</t>
   </si>
   <si>
     <t xml:space="preserve">21.137228012085</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2816734313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.506368637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4421691894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9606857299805</t>
+    <t xml:space="preserve">21.2816753387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5063705444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4421710968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9606838226318</t>
   </si>
   <si>
     <t xml:space="preserve">21.3458728790283</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0890808105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6989650726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8113117218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7792072296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.394021987915</t>
+    <t xml:space="preserve">21.0890789031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6989631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8113079071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7792129516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3940200805664</t>
   </si>
   <si>
     <t xml:space="preserve">21.7471122741699</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">21.2495765686035</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5322742462158</t>
+    <t xml:space="preserve">19.5322780609131</t>
   </si>
   <si>
     <t xml:space="preserve">19.3236351013184</t>
@@ -1358,19 +1358,19 @@
     <t xml:space="preserve">19.5001754760742</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5162239074707</t>
+    <t xml:space="preserve">19.516227722168</t>
   </si>
   <si>
     <t xml:space="preserve">20.0458602905273</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0940113067627</t>
+    <t xml:space="preserve">20.0940093994141</t>
   </si>
   <si>
     <t xml:space="preserve">19.7248687744141</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7088222503662</t>
+    <t xml:space="preserve">19.7088184356689</t>
   </si>
   <si>
     <t xml:space="preserve">19.4038791656494</t>
@@ -1391,10 +1391,10 @@
     <t xml:space="preserve">18.0075702667236</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5853538513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7137508392334</t>
+    <t xml:space="preserve">18.5853519439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7137489318848</t>
   </si>
   <si>
     <t xml:space="preserve">19.9977111816406</t>
@@ -1403,10 +1403,10 @@
     <t xml:space="preserve">20.1261100769043</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7199401855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1903095245361</t>
+    <t xml:space="preserve">20.7199382781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1903076171875</t>
   </si>
   <si>
     <t xml:space="preserve">19.7730178833008</t>
@@ -1415,31 +1415,31 @@
     <t xml:space="preserve">19.837215423584</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8211669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4359817504883</t>
+    <t xml:space="preserve">19.8211688995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.435977935791</t>
   </si>
   <si>
     <t xml:space="preserve">19.1310386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3557300567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5483283996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9174652099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5804233551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0186901092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0026435852051</t>
+    <t xml:space="preserve">19.3557319641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5483245849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9174633026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5804214477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0186920166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0026416778564</t>
   </si>
   <si>
     <t xml:space="preserve">18.8421459197998</t>
@@ -1448,28 +1448,28 @@
     <t xml:space="preserve">19.0828895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8853664398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5112953186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1582069396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8936653137207</t>
+    <t xml:space="preserve">19.8853645324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5112991333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1582088470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8936672210693</t>
   </si>
   <si>
     <t xml:space="preserve">20.6596546173096</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5760822296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6763687133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7265148162842</t>
+    <t xml:space="preserve">20.5760803222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6763725280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7265167236328</t>
   </si>
   <si>
     <t xml:space="preserve">20.8435230255127</t>
@@ -1478,10 +1478,10 @@
     <t xml:space="preserve">20.8268051147461</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4954032897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1276702880859</t>
+    <t xml:space="preserve">21.4954013824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1276741027832</t>
   </si>
   <si>
     <t xml:space="preserve">21.2781066894531</t>
@@ -1490,28 +1490,28 @@
     <t xml:space="preserve">21.1778202056885</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0942459106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9772396087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7766628265381</t>
+    <t xml:space="preserve">21.0942440032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9772415161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7766609191895</t>
   </si>
   <si>
     <t xml:space="preserve">20.4757919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6429386138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5259380340576</t>
+    <t xml:space="preserve">20.6429443359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.525936126709</t>
   </si>
   <si>
     <t xml:space="preserve">20.2584972381592</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1247806549072</t>
+    <t xml:space="preserve">20.1247787475586</t>
   </si>
   <si>
     <t xml:space="preserve">20.1916370391846</t>
@@ -1523,34 +1523,34 @@
     <t xml:space="preserve">19.5063247680664</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2417850494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8769493103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7933731079102</t>
+    <t xml:space="preserve">20.2417812347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8769512176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7933750152588</t>
   </si>
   <si>
     <t xml:space="preserve">20.9939556121826</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8100891113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.592794418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6930847167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3420696258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4925079345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5593681335449</t>
+    <t xml:space="preserve">20.8100910186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5927982330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6930885314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3420734405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.492504119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5593662261963</t>
   </si>
   <si>
     <t xml:space="preserve">19.7570476531982</t>
@@ -1559,25 +1559,25 @@
     <t xml:space="preserve">19.8740558624268</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1414928436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2919273376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0244903564453</t>
+    <t xml:space="preserve">20.1414947509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2919254302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0244884490967</t>
   </si>
   <si>
     <t xml:space="preserve">19.9409160614014</t>
   </si>
   <si>
-    <t xml:space="preserve">20.108060836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2752151489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3922157287598</t>
+    <t xml:space="preserve">20.1080665588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2752113342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.392219543457</t>
   </si>
   <si>
     <t xml:space="preserve">20.0579166412354</t>
@@ -1595,10 +1595,10 @@
     <t xml:space="preserve">19.6901893615723</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0273857116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2475757598877</t>
+    <t xml:space="preserve">21.0273818969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2475738525391</t>
   </si>
   <si>
     <t xml:space="preserve">22.3144340515137</t>
@@ -1610,19 +1610,19 @@
     <t xml:space="preserve">23.200325012207</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2671852111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5847682952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5346260070801</t>
+    <t xml:space="preserve">23.2671871185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5847702026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5346240997314</t>
   </si>
   <si>
     <t xml:space="preserve">23.217041015625</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8660278320312</t>
+    <t xml:space="preserve">22.8660297393799</t>
   </si>
   <si>
     <t xml:space="preserve">22.799165725708</t>
@@ -1634,43 +1634,43 @@
     <t xml:space="preserve">22.5484428405762</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6153049468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9328880310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1167526245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.150182723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2504692077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4009037017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.618200302124</t>
+    <t xml:space="preserve">22.6153011322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9328861236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1167507171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1501808166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2504711151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4009056091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6182022094727</t>
   </si>
   <si>
     <t xml:space="preserve">23.5011959075928</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3841896057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2839012145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0833225250244</t>
+    <t xml:space="preserve">23.3841915130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.283899307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0833206176758</t>
   </si>
   <si>
     <t xml:space="preserve">22.8994579315186</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5651588439941</t>
+    <t xml:space="preserve">22.5651569366455</t>
   </si>
   <si>
     <t xml:space="preserve">22.5818748474121</t>
@@ -1679,7 +1679,7 @@
     <t xml:space="preserve">22.331148147583</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8158798217773</t>
+    <t xml:space="preserve">22.815881729126</t>
   </si>
   <si>
     <t xml:space="preserve">22.5317268371582</t>
@@ -1688,40 +1688,40 @@
     <t xml:space="preserve">23.1334686279297</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9663162231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6850605010986</t>
+    <t xml:space="preserve">22.9663143157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.68505859375</t>
   </si>
   <si>
     <t xml:space="preserve">23.3006134033203</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4343357086182</t>
+    <t xml:space="preserve">23.4343376159668</t>
   </si>
   <si>
     <t xml:space="preserve">22.9997463226318</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8493118286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9496002197266</t>
+    <t xml:space="preserve">22.8493137359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9496021270752</t>
   </si>
   <si>
     <t xml:space="preserve">21.7628402709961</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4619731903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0440998077393</t>
+    <t xml:space="preserve">21.461971282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0440979003906</t>
   </si>
   <si>
     <t xml:space="preserve">20.7098026275635</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9103813171387</t>
+    <t xml:space="preserve">20.91037940979</t>
   </si>
   <si>
     <t xml:space="preserve">21.6625518798828</t>
@@ -1733,133 +1733,133 @@
     <t xml:space="preserve">21.4285449981689</t>
   </si>
   <si>
-    <t xml:space="preserve">20.927095413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3616809844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5121173858643</t>
+    <t xml:space="preserve">20.9270973205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3616828918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5121154785156</t>
   </si>
   <si>
     <t xml:space="preserve">20.9605255126953</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8573379516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5397548675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9547348022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.556468963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.055025100708</t>
+    <t xml:space="preserve">19.8573398590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5397567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9547328948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5564708709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0550193786621</t>
   </si>
   <si>
     <t xml:space="preserve">19.4394683837891</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3893222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2556018829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3057498931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3726062774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8043003082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6037178039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6872940063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6705799102783</t>
+    <t xml:space="preserve">19.3893241882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2556037902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3057479858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3726100921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8042984008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6037197113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6872959136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6705780029297</t>
   </si>
   <si>
     <t xml:space="preserve">18.704008102417</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8878726959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2221717834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6734733581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.656759262085</t>
+    <t xml:space="preserve">18.8878765106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2221736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6734771728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6567611694336</t>
   </si>
   <si>
     <t xml:space="preserve">19.8907680511475</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0913486480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8406257629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.589900970459</t>
+    <t xml:space="preserve">20.0913467407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8406238555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5898990631104</t>
   </si>
   <si>
     <t xml:space="preserve">19.088451385498</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7737655639648</t>
+    <t xml:space="preserve">19.7737636566162</t>
   </si>
   <si>
     <t xml:space="preserve">19.6400451660156</t>
   </si>
   <si>
-    <t xml:space="preserve">19.456184387207</t>
+    <t xml:space="preserve">19.4561824798584</t>
   </si>
   <si>
     <t xml:space="preserve">18.9213008880615</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3391780853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5201454162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5506782531738</t>
+    <t xml:space="preserve">19.3391742706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5201473236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5506801605225</t>
   </si>
   <si>
     <t xml:space="preserve">18.0019836425781</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9016952514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4700031280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.235990524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4365692138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0412044525146</t>
+    <t xml:space="preserve">17.9016933441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4699993133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2359924316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4365711212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.041202545166</t>
   </si>
   <si>
     <t xml:space="preserve">20.3086414337158</t>
   </si>
   <si>
-    <t xml:space="preserve">19.991060256958</t>
+    <t xml:space="preserve">19.9910583496094</t>
   </si>
   <si>
     <t xml:space="preserve">20.3253555297852</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">18.2861347198486</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2694206237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.219274520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4198570251465</t>
+    <t xml:space="preserve">18.2694225311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2192764282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4198551177979</t>
   </si>
   <si>
     <t xml:space="preserve">18.6538639068604</t>
@@ -1889,136 +1889,136 @@
     <t xml:space="preserve">18.5368595123291</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7541522979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6371459960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1553115844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4060363769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2723140716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9714508056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3558921813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0215911865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3224620819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7403354644775</t>
+    <t xml:space="preserve">18.7541542053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.637149810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.155309677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4060344696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2723159790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9714488983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3558940887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0215930938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3224601745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7403373718262</t>
   </si>
   <si>
     <t xml:space="preserve">20.1749210357666</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7875823974609</t>
+    <t xml:space="preserve">18.7875804901123</t>
   </si>
   <si>
     <t xml:space="preserve">18.9380187988281</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0077743530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2250690460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5789775848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1443862915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2054576873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0354118347168</t>
+    <t xml:space="preserve">20.0077705383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2250709533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5789756774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1443901062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2054557800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0354137420654</t>
   </si>
   <si>
     <t xml:space="preserve">17.6509704589844</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4336776733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5841102600098</t>
+    <t xml:space="preserve">17.4336757659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5841083526611</t>
   </si>
   <si>
     <t xml:space="preserve">17.1328048706055</t>
   </si>
   <si>
-    <t xml:space="preserve">16.547779083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1716957092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9961881637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3221321105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.879186630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7939529418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7683820724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7769050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3081111907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4018745422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4359674453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5382471084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.163215637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.333685874939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0524101257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1717376708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3507308959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5552930831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.640528678894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6490526199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6320056915283</t>
+    <t xml:space="preserve">16.5477809906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1716976165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.996187210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3221302032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8791847229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7939491271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7683801651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7769041061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3081130981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4018726348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4359655380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5382461547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.16321849823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.333683013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0524091720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1717386245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.350733757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5552959442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6405296325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6490545272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.632004737854</t>
   </si>
   <si>
     <t xml:space="preserve">15.5808658599854</t>
@@ -2033,34 +2033,34 @@
     <t xml:space="preserve">14.8904628753662</t>
   </si>
   <si>
-    <t xml:space="preserve">14.984224319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0438861846924</t>
+    <t xml:space="preserve">14.9842233657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0438871383667</t>
   </si>
   <si>
     <t xml:space="preserve">15.3763017654419</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4274435043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.282546043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0865058898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1120738983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1546907424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3251600265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3592567443848</t>
+    <t xml:space="preserve">15.4274425506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2825441360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0865049362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1120767593384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1546936035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3251609802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3592576980591</t>
   </si>
   <si>
     <t xml:space="preserve">14.9671764373779</t>
@@ -2069,25 +2069,25 @@
     <t xml:space="preserve">14.745566368103</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6091899871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6518077850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5154333114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7114725112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6347627639771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5410022735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3534870147705</t>
+    <t xml:space="preserve">14.6091890335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6518087387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5154342651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7114744186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6347608566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5410041809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3534898757935</t>
   </si>
   <si>
     <t xml:space="preserve">14.3449640274048</t>
@@ -2096,73 +2096,73 @@
     <t xml:space="preserve">14.4472465515137</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4387226104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7540893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4642925262451</t>
+    <t xml:space="preserve">14.4387235641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7540903091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4642915725708</t>
   </si>
   <si>
     <t xml:space="preserve">14.4813394546509</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3620119094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2484483718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4956312179565</t>
+    <t xml:space="preserve">14.3620109558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2484502792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4956293106079</t>
   </si>
   <si>
     <t xml:space="preserve">15.0268392562866</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0012722015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6859035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5324783325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9784555435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4046277999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.035364151001</t>
+    <t xml:space="preserve">15.0012712478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.68590259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5324792861938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9784564971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4046287536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0353631973267</t>
   </si>
   <si>
     <t xml:space="preserve">15.1376447677612</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8308000564575</t>
+    <t xml:space="preserve">14.8308010101318</t>
   </si>
   <si>
     <t xml:space="preserve">14.9586515426636</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2399253845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8109979629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4843502044678</t>
+    <t xml:space="preserve">15.2399272918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8109970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4843521118164</t>
   </si>
   <si>
     <t xml:space="preserve">17.0468978881836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7911930084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5269660949707</t>
+    <t xml:space="preserve">16.7911949157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5269641876221</t>
   </si>
   <si>
     <t xml:space="preserve">17.0128040313721</t>
@@ -2171,52 +2171,52 @@
     <t xml:space="preserve">16.5781078338623</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3138809204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2371692657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9303274154663</t>
+    <t xml:space="preserve">16.3138828277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2371673583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.930326461792</t>
   </si>
   <si>
     <t xml:space="preserve">15.9218015670776</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3933477401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9416055679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5239591598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9330825805664</t>
+    <t xml:space="preserve">15.3933486938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9416065216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5239562988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9330806732178</t>
   </si>
   <si>
     <t xml:space="preserve">14.6603326797485</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2512054443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1318798065186</t>
+    <t xml:space="preserve">14.2512063980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1318778991699</t>
   </si>
   <si>
     <t xml:space="preserve">14.617714881897</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4557676315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5580501556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5750980377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7370452880859</t>
+    <t xml:space="preserve">14.4557695388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.558051109314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5750970840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.737042427063</t>
   </si>
   <si>
     <t xml:space="preserve">14.7796611785889</t>
@@ -2231,40 +2231,40 @@
     <t xml:space="preserve">14.6688547134399</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2341623306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1404008865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0636901855469</t>
+    <t xml:space="preserve">14.2341585159302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.14040184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0636920928955</t>
   </si>
   <si>
     <t xml:space="preserve">14.8222770690918</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6262397766113</t>
+    <t xml:space="preserve">14.626238822937</t>
   </si>
   <si>
     <t xml:space="preserve">15.0183191299438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1291217803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2058305740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5467691421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8195219039917</t>
+    <t xml:space="preserve">15.1291227340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2058334350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5467729568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8195199966431</t>
   </si>
   <si>
     <t xml:space="preserve">16.0326061248779</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4502563476562</t>
+    <t xml:space="preserve">16.4502544403076</t>
   </si>
   <si>
     <t xml:space="preserve">16.4928722381592</t>
@@ -2276,25 +2276,25 @@
     <t xml:space="preserve">16.1519355773926</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2030754089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0411281585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0752258300781</t>
+    <t xml:space="preserve">16.2030773162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.041130065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0752239227295</t>
   </si>
   <si>
     <t xml:space="preserve">15.8962326049805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2883110046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2627391815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1263675689697</t>
+    <t xml:space="preserve">16.2883129119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2627410888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1263656616211</t>
   </si>
   <si>
     <t xml:space="preserve">16.1178417205811</t>
@@ -2306,16 +2306,16 @@
     <t xml:space="preserve">16.2286472320557</t>
   </si>
   <si>
-    <t xml:space="preserve">16.168981552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0667037963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2797889709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1093196868896</t>
+    <t xml:space="preserve">16.1689834594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0667018890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2797870635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.109317779541</t>
   </si>
   <si>
     <t xml:space="preserve">15.7087163925171</t>
@@ -2330,43 +2330,43 @@
     <t xml:space="preserve">15.7428092956543</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3422079086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2910661697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1035528182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5665740966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2853012084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2426805496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5949020385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7057056427002</t>
+    <t xml:space="preserve">15.342209815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2910680770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.103551864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5665731430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2853002548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2426815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5949010848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7057046890259</t>
   </si>
   <si>
     <t xml:space="preserve">14.6944246292114</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5069103240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0694589614868</t>
+    <t xml:space="preserve">14.5069093704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0694608688354</t>
   </si>
   <si>
     <t xml:space="preserve">15.4615364074707</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4444894790649</t>
+    <t xml:space="preserve">15.4444913864136</t>
   </si>
   <si>
     <t xml:space="preserve">15.4700603485107</t>
@@ -2378,16 +2378,16 @@
     <t xml:space="preserve">15.2740201950073</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2995910644531</t>
+    <t xml:space="preserve">15.2995929718018</t>
   </si>
   <si>
     <t xml:space="preserve">13.7142286300659</t>
   </si>
   <si>
-    <t xml:space="preserve">13.381814956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.552282333374</t>
+    <t xml:space="preserve">13.3818130493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5522842407227</t>
   </si>
   <si>
     <t xml:space="preserve">13.1772518157959</t>
@@ -2396,94 +2396,94 @@
     <t xml:space="preserve">13.2965812683105</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2624864578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0323534011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7596035003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6232280731201</t>
+    <t xml:space="preserve">13.262487411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0323514938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7596025466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6232290267944</t>
   </si>
   <si>
     <t xml:space="preserve">12.3590002059937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6600790023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1912879943848</t>
+    <t xml:space="preserve">11.6600780487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1912889480591</t>
   </si>
   <si>
     <t xml:space="preserve">10.8333034515381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74230194091797</t>
+    <t xml:space="preserve">9.74230098724365</t>
   </si>
   <si>
     <t xml:space="preserve">10.6543102264404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.643030166626</t>
+    <t xml:space="preserve">11.6430320739746</t>
   </si>
   <si>
     <t xml:space="preserve">11.8220243453979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6686010360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0351104736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3306751251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.722752571106</t>
+    <t xml:space="preserve">11.6686029434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0351095199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3306732177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7227535247803</t>
   </si>
   <si>
     <t xml:space="preserve">14.2767763137817</t>
   </si>
   <si>
-    <t xml:space="preserve">13.074969291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5011425018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4500017166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9897365570068</t>
+    <t xml:space="preserve">13.0749702453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5011444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4500036239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9897356033325</t>
   </si>
   <si>
     <t xml:space="preserve">13.0834941864014</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1175889968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4953765869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0238304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3562440872192</t>
+    <t xml:space="preserve">13.1175880432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4953756332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.023829460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3562450408936</t>
   </si>
   <si>
     <t xml:space="preserve">13.4244318008423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6119480133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8192672729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6999387741089</t>
+    <t xml:space="preserve">13.6119470596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8192682266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6999397277832</t>
   </si>
   <si>
     <t xml:space="preserve">12.904501914978</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">13.3988628387451</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3136262893677</t>
+    <t xml:space="preserve">13.313627243042</t>
   </si>
   <si>
     <t xml:space="preserve">13.8079881668091</t>
@@ -2507,52 +2507,52 @@
     <t xml:space="preserve">13.8932209014893</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9358406066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0551671981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8847007751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4898614883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7029504776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2000646591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4983854293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4131536483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1205978393555</t>
+    <t xml:space="preserve">13.9358396530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0551681518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8846998214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4898624420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7029485702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2000665664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.498387336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4131526947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1205987930298</t>
   </si>
   <si>
     <t xml:space="preserve">14.7711372375488</t>
   </si>
   <si>
-    <t xml:space="preserve">14.856372833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4189186096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.938850402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.75133228302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6207237243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4161624908447</t>
+    <t xml:space="preserve">14.8563709259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4189205169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9388475418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7513341903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6207256317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4161643981934</t>
   </si>
   <si>
     <t xml:space="preserve">16.2456912994385</t>
@@ -2564,7 +2564,7 @@
     <t xml:space="preserve">16.7826709747314</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3707866668701</t>
+    <t xml:space="preserve">17.3707885742188</t>
   </si>
   <si>
     <t xml:space="preserve">18.4276962280273</t>
@@ -2573,28 +2573,28 @@
     <t xml:space="preserve">19.2629947662354</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0754776000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6493053436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.90500831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6039333343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6380271911621</t>
+    <t xml:space="preserve">19.0754795074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6493034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9050102233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.603931427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6380252838135</t>
   </si>
   <si>
     <t xml:space="preserve">20.0641975402832</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8766841888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7744026184082</t>
+    <t xml:space="preserve">19.8766822814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7744007110596</t>
   </si>
   <si>
     <t xml:space="preserve">20.1494312286377</t>
@@ -2603,31 +2603,31 @@
     <t xml:space="preserve">20.0471515655518</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4846038818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8425903320312</t>
+    <t xml:space="preserve">19.4846019744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8425884246826</t>
   </si>
   <si>
     <t xml:space="preserve">19.8084945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7119789123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9506359100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6778888702393</t>
+    <t xml:space="preserve">20.7119827270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9506378173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6778907775879</t>
   </si>
   <si>
     <t xml:space="preserve">20.8483543395996</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8824520111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0529174804688</t>
+    <t xml:space="preserve">20.8824501037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0529193878174</t>
   </si>
   <si>
     <t xml:space="preserve">20.9335918426514</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">21.0870113372803</t>
   </si>
   <si>
-    <t xml:space="preserve">21.155200958252</t>
+    <t xml:space="preserve">21.1551990509033</t>
   </si>
   <si>
     <t xml:space="preserve">21.2915744781494</t>
@@ -2645,34 +2645,34 @@
     <t xml:space="preserve">21.2574825286865</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2233867645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0699634552002</t>
+    <t xml:space="preserve">21.223388671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0699653625488</t>
   </si>
   <si>
     <t xml:space="preserve">21.3086204528809</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8994979858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9676837921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7631225585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9165458679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1609668731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6382789611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.013313293457</t>
+    <t xml:space="preserve">20.8994941711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9676856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7631244659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9165439605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1609649658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6382808685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0133113861084</t>
   </si>
   <si>
     <t xml:space="preserve">23.9167976379395</t>
@@ -2684,37 +2684,37 @@
     <t xml:space="preserve">23.9679393768311</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0020332336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5758609771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8656558990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7974700927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5247211456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5929088592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6610927581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8486080169678</t>
+    <t xml:space="preserve">24.0020313262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5758590698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8656578063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7974681854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5247192382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5929069519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6610946655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8486099243164</t>
   </si>
   <si>
     <t xml:space="preserve">23.6781425476074</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4394855499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7292804718018</t>
+    <t xml:space="preserve">23.4394874572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7292823791504</t>
   </si>
   <si>
     <t xml:space="preserve">23.7463302612305</t>
@@ -2723,22 +2723,22 @@
     <t xml:space="preserve">23.6951885223389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4906272888184</t>
+    <t xml:space="preserve">23.4906234741211</t>
   </si>
   <si>
     <t xml:space="preserve">23.7633743286133</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1496849060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9849834442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.899751663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4963932037354</t>
+    <t xml:space="preserve">23.1496906280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9849853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8997497558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.496395111084</t>
   </si>
   <si>
     <t xml:space="preserve">25.2123622894287</t>
@@ -2747,28 +2747,28 @@
     <t xml:space="preserve">24.5304870605469</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1100807189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0647068023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4680633544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5532989501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4851112365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1271266937256</t>
+    <t xml:space="preserve">25.1100788116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0647029876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4680671691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5533008575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4851131439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.127124786377</t>
   </si>
   <si>
     <t xml:space="preserve">25.0589389801025</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0759887695312</t>
+    <t xml:space="preserve">25.0759868621826</t>
   </si>
   <si>
     <t xml:space="preserve">24.8202819824219</t>
@@ -2777,55 +2777,55 @@
     <t xml:space="preserve">24.8884716033936</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1953144073486</t>
+    <t xml:space="preserve">25.1953163146973</t>
   </si>
   <si>
     <t xml:space="preserve">24.7180004119873</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3487358093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2294101715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4339714050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3657836914062</t>
+    <t xml:space="preserve">25.3487377166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2294082641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4339733123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3657875061035</t>
   </si>
   <si>
     <t xml:space="preserve">25.9453792572021</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8829574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7636299133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0306148529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9283332824707</t>
+    <t xml:space="preserve">26.8829612731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7636260986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0306129455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9283313751221</t>
   </si>
   <si>
     <t xml:space="preserve">26.0135669708252</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1441745758057</t>
+    <t xml:space="preserve">25.144172668457</t>
   </si>
   <si>
     <t xml:space="preserve">24.956657409668</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4224395751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2690143585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4053897857666</t>
+    <t xml:space="preserve">23.422435760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2690162658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.405387878418</t>
   </si>
   <si>
     <t xml:space="preserve">23.4565315246582</t>
@@ -2834,13 +2834,13 @@
     <t xml:space="preserve">24.8373279571533</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0930347442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5703468322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6385345458984</t>
+    <t xml:space="preserve">25.0930328369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.570348739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6385364532471</t>
   </si>
   <si>
     <t xml:space="preserve">24.3600158691406</t>
@@ -2849,10 +2849,10 @@
     <t xml:space="preserve">24.13840675354</t>
   </si>
   <si>
-    <t xml:space="preserve">25.911283493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5475330352783</t>
+    <t xml:space="preserve">25.9112854003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5475311279297</t>
   </si>
   <si>
     <t xml:space="preserve">23.8315620422363</t>
@@ -2861,46 +2861,46 @@
     <t xml:space="preserve">23.5588111877441</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1213626861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5417671203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0985488891602</t>
+    <t xml:space="preserve">24.1213607788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.54176902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0985469818115</t>
   </si>
   <si>
     <t xml:space="preserve">24.2747821807861</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9396114349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2918281555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0702209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5076694488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3372020721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.183780670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6894245147705</t>
+    <t xml:space="preserve">24.9396095275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2918300628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.070219039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5076713562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3372058868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1837844848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6894207000732</t>
   </si>
   <si>
     <t xml:space="preserve">23.1667366027832</t>
   </si>
   <si>
-    <t xml:space="preserve">23.286060333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2029075622559</t>
+    <t xml:space="preserve">23.2860641479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2029094696045</t>
   </si>
   <si>
     <t xml:space="preserve">23.3768405914307</t>
@@ -2909,76 +2909,76 @@
     <t xml:space="preserve">22.6984939575195</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5941352844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8202495574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.420202255249</t>
+    <t xml:space="preserve">22.5941333770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8202514648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4202003479004</t>
   </si>
   <si>
     <t xml:space="preserve">22.7854652404785</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2898769378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8028564453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8724308013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.750675201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7158889770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2462635040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3332347869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4723796844482</t>
+    <t xml:space="preserve">23.2898750305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8028583526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.872428894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7506771087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7158908843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.246265411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.33323097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4723815917969</t>
   </si>
   <si>
     <t xml:space="preserve">23.2550868988037</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5769920349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3596992492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5510292053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1945858001709</t>
+    <t xml:space="preserve">24.5769939422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3596973419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5510272979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1945877075195</t>
   </si>
   <si>
     <t xml:space="preserve">26.4207000732422</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7597522735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4033088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0294723510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1860160827637</t>
+    <t xml:space="preserve">25.7597503662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4033107757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0294742584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1860179901123</t>
   </si>
   <si>
     <t xml:space="preserve">27.1164417266846</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0120792388916</t>
+    <t xml:space="preserve">27.0120811462402</t>
   </si>
   <si>
     <t xml:space="preserve">28.1426563262939</t>
@@ -2987,40 +2987,40 @@
     <t xml:space="preserve">28.8036098480225</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0992984771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3775901794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5863132476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0385494232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2210502624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0819034576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7688217163086</t>
+    <t xml:space="preserve">29.0992965698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.377592086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5863170623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0385475158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2210521697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0819053649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7688236236572</t>
   </si>
   <si>
     <t xml:space="preserve">28.4035587310791</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6904277801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7859630584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5946369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.412130355835</t>
+    <t xml:space="preserve">27.6904239654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7859649658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.594633102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4121265411377</t>
   </si>
   <si>
     <t xml:space="preserve">26.6294250488281</t>
@@ -3035,31 +3035,31 @@
     <t xml:space="preserve">26.5250625610352</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2034091949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3077697753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7078189849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1081161499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1340827941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0471229553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2906265258789</t>
+    <t xml:space="preserve">27.2034072875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3077659606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.707820892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1081218719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1340847015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0471172332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2906303405762</t>
   </si>
   <si>
     <t xml:space="preserve">28.8905773162842</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3080215454102</t>
+    <t xml:space="preserve">29.3080177307129</t>
   </si>
   <si>
     <t xml:space="preserve">30.8560409545898</t>
@@ -3077,10 +3077,10 @@
     <t xml:space="preserve">30.4385986328125</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0559387207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2994441986084</t>
+    <t xml:space="preserve">30.0559425354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2994480133057</t>
   </si>
   <si>
     <t xml:space="preserve">29.9515781402588</t>
@@ -3092,31 +3092,31 @@
     <t xml:space="preserve">30.9951858520508</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6039562225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8300724029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5691757202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.864860534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7778968811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.499605178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0387992858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6909275054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3430595397949</t>
+    <t xml:space="preserve">31.6039619445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8300762176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5691738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8648643493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7778911590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4995956420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0387954711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6909236907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3430614471436</t>
   </si>
   <si>
     <t xml:space="preserve">31.447416305542</t>
@@ -3125,16 +3125,16 @@
     <t xml:space="preserve">31.2734832763672</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7605018615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7083225250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5865707397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7431049346924</t>
+    <t xml:space="preserve">31.7605037689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7083187103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5865669250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7431106567383</t>
   </si>
   <si>
     <t xml:space="preserve">31.6387462615967</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">31.6735305786133</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3866691589355</t>
+    <t xml:space="preserve">32.3866767883301</t>
   </si>
   <si>
     <t xml:space="preserve">32.5606002807617</t>
@@ -3152,58 +3152,58 @@
     <t xml:space="preserve">31.8474636077881</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5432052612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8996486663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5169906616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7952899932861</t>
+    <t xml:space="preserve">32.5432090759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8996448516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5169944763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7952880859375</t>
   </si>
   <si>
     <t xml:space="preserve">31.8126831054688</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6213531494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4822044372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3952350616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.155330657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9081172943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7845077514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1376724243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1729850769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2612800598145</t>
+    <t xml:space="preserve">31.6213512420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4822063446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3952388763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1553268432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9081153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7845115661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1376762390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.172981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2612762451172</t>
   </si>
   <si>
     <t xml:space="preserve">32.2789344787598</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7491931915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7668533325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8727970123291</t>
+    <t xml:space="preserve">31.7491912841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7668476104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8728008270264</t>
   </si>
   <si>
     <t xml:space="preserve">32.6674156188965</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">33.3031044006348</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3096122741699</t>
+    <t xml:space="preserve">34.3096160888672</t>
   </si>
   <si>
     <t xml:space="preserve">34.9982757568359</t>
@@ -3227,13 +3227,13 @@
     <t xml:space="preserve">34.9806175231934</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2808074951172</t>
+    <t xml:space="preserve">35.2808036804199</t>
   </si>
   <si>
     <t xml:space="preserve">34.7863807678223</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9564476013184</t>
+    <t xml:space="preserve">33.9564514160156</t>
   </si>
   <si>
     <t xml:space="preserve">33.7975311279297</t>
@@ -3242,52 +3242,52 @@
     <t xml:space="preserve">33.3384170532227</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9499397277832</t>
+    <t xml:space="preserve">32.9499435424805</t>
   </si>
   <si>
     <t xml:space="preserve">33.1794967651367</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2148132324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0912055969238</t>
+    <t xml:space="preserve">33.2148094177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0912094116211</t>
   </si>
   <si>
     <t xml:space="preserve">32.4378623962402</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0205764770508</t>
+    <t xml:space="preserve">33.0205726623535</t>
   </si>
   <si>
     <t xml:space="preserve">32.843994140625</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1441764831543</t>
+    <t xml:space="preserve">33.1441841125488</t>
   </si>
   <si>
     <t xml:space="preserve">32.0317230224609</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3319091796875</t>
+    <t xml:space="preserve">32.3319053649902</t>
   </si>
   <si>
     <t xml:space="preserve">32.7027282714844</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2677879333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4267120361328</t>
+    <t xml:space="preserve">33.2677917480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4267082214355</t>
   </si>
   <si>
     <t xml:space="preserve">32.8616523742676</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2083015441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2017955780029</t>
+    <t xml:space="preserve">32.2083053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2017936706543</t>
   </si>
   <si>
     <t xml:space="preserve">31.1135063171387</t>
@@ -3302,10 +3302,10 @@
     <t xml:space="preserve">32.9322814941406</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9257717132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5438041687012</t>
+    <t xml:space="preserve">31.9257698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5438079833984</t>
   </si>
   <si>
     <t xml:space="preserve">34.0270843505859</t>
@@ -3317,13 +3317,13 @@
     <t xml:space="preserve">34.0800552368164</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3449325561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3802375793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1330299377441</t>
+    <t xml:space="preserve">34.3449287414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.380241394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1330337524414</t>
   </si>
   <si>
     <t xml:space="preserve">34.5215072631836</t>
@@ -3332,31 +3332,31 @@
     <t xml:space="preserve">34.150691986084</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2036628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1153755187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.938793182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6209526062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.691577911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2919540405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.503849029541</t>
+    <t xml:space="preserve">34.2036666870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1153717041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9387893676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6209487915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6915817260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2919502258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5038528442383</t>
   </si>
   <si>
     <t xml:space="preserve">32.914623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1971549987793</t>
+    <t xml:space="preserve">33.197151184082</t>
   </si>
   <si>
     <t xml:space="preserve">33.5149955749512</t>
@@ -3365,19 +3365,19 @@
     <t xml:space="preserve">33.5503158569336</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8151893615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6451187133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1395378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8570137023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6804313659668</t>
+    <t xml:space="preserve">33.815185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6451148986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1395454406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8570098876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6804275512695</t>
   </si>
   <si>
     <t xml:space="preserve">35.0865669250488</t>
@@ -3386,25 +3386,25 @@
     <t xml:space="preserve">34.3272743225098</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2371101379395</t>
+    <t xml:space="preserve">31.2371082305908</t>
   </si>
   <si>
     <t xml:space="preserve">30.4248390197754</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1776275634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0716781616211</t>
+    <t xml:space="preserve">30.1776237487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0716800689697</t>
   </si>
   <si>
     <t xml:space="preserve">29.5595951080322</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6125679016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6478843688965</t>
+    <t xml:space="preserve">29.6125659942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6478862762451</t>
   </si>
   <si>
     <t xml:space="preserve">30.2306003570557</t>
@@ -3416,16 +3416,16 @@
     <t xml:space="preserve">29.0121955871582</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2882137298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8467617034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4406261444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5530834197998</t>
+    <t xml:space="preserve">28.2882118225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8467636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4406280517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5530815124512</t>
   </si>
   <si>
     <t xml:space="preserve">28.09397315979</t>
@@ -3437,70 +3437,70 @@
     <t xml:space="preserve">27.6348648071289</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0763149261475</t>
+    <t xml:space="preserve">28.0763168334961</t>
   </si>
   <si>
     <t xml:space="preserve">28.0410003662109</t>
   </si>
   <si>
-    <t xml:space="preserve">28.305871963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2240905761719</t>
+    <t xml:space="preserve">28.3058738708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2240886688232</t>
   </si>
   <si>
     <t xml:space="preserve">29.1004829406738</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4713039398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.135799407959</t>
+    <t xml:space="preserve">29.471305847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1358013153076</t>
   </si>
   <si>
     <t xml:space="preserve">29.3123817443848</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8244609832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9480667114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7891540527344</t>
+    <t xml:space="preserve">29.824462890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9480724334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7891483306885</t>
   </si>
   <si>
     <t xml:space="preserve">29.2417488098145</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8421211242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0010471343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9833850860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5661010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9545822143555</t>
+    <t xml:space="preserve">29.8421230316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0010452270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9833869934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5661029815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9545841217041</t>
   </si>
   <si>
     <t xml:space="preserve">30.1952838897705</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1246490478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3300399780273</t>
+    <t xml:space="preserve">30.1246509552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.330041885376</t>
   </si>
   <si>
     <t xml:space="preserve">27.2287292480469</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8402500152588</t>
+    <t xml:space="preserve">26.8402519226074</t>
   </si>
   <si>
     <t xml:space="preserve">26.9462013244629</t>
@@ -3509,10 +3509,10 @@
     <t xml:space="preserve">26.6106986999512</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2817039489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7231540679932</t>
+    <t xml:space="preserve">27.281702041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7231521606445</t>
   </si>
   <si>
     <t xml:space="preserve">27.3876533508301</t>
@@ -3527,10 +3527,10 @@
     <t xml:space="preserve">27.0698070526123</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7807712554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.434118270874</t>
+    <t xml:space="preserve">25.7807693481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4341163635254</t>
   </si>
   <si>
     <t xml:space="preserve">26.1162719726562</t>
@@ -3542,13 +3542,13 @@
     <t xml:space="preserve">26.3634834289551</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1339302062988</t>
+    <t xml:space="preserve">26.1339282989502</t>
   </si>
   <si>
     <t xml:space="preserve">26.3987998962402</t>
   </si>
   <si>
-    <t xml:space="preserve">27.140438079834</t>
+    <t xml:space="preserve">27.1404399871826</t>
   </si>
   <si>
     <t xml:space="preserve">26.5753803253174</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">26.7519607543945</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3105087280273</t>
+    <t xml:space="preserve">26.310510635376</t>
   </si>
   <si>
     <t xml:space="preserve">26.4694328308105</t>
@@ -3569,19 +3569,19 @@
     <t xml:space="preserve">27.2110710144043</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0521469116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3523349761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.981517791748</t>
+    <t xml:space="preserve">27.0521488189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3523368835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9815158843994</t>
   </si>
   <si>
     <t xml:space="preserve">27.9350509643555</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8291034698486</t>
+    <t xml:space="preserve">27.8291015625</t>
   </si>
   <si>
     <t xml:space="preserve">27.405309677124</t>
@@ -3593,58 +3593,58 @@
     <t xml:space="preserve">27.6525230407715</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3699951171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4164581298828</t>
+    <t xml:space="preserve">27.3699932098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4164600372314</t>
   </si>
   <si>
     <t xml:space="preserve">24.9155235290527</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0214710235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7212829589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8978652954102</t>
+    <t xml:space="preserve">25.0214729309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7212867736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8978672027588</t>
   </si>
   <si>
     <t xml:space="preserve">25.2686862945557</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5447025299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.10325050354</t>
+    <t xml:space="preserve">24.5447063446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1032524108887</t>
   </si>
   <si>
     <t xml:space="preserve">23.8383808135986</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6924781799316</t>
+    <t xml:space="preserve">25.692476272583</t>
   </si>
   <si>
     <t xml:space="preserve">26.4517726898193</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5112590789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9703674316406</t>
+    <t xml:space="preserve">27.5112571716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9703712463379</t>
   </si>
   <si>
     <t xml:space="preserve">27.2993621826172</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9285411834717</t>
+    <t xml:space="preserve">26.9285430908203</t>
   </si>
   <si>
     <t xml:space="preserve">27.5289173126221</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4759426116943</t>
+    <t xml:space="preserve">27.475944519043</t>
   </si>
   <si>
     <t xml:space="preserve">26.9638595581055</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">26.3811435699463</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8932247161865</t>
+    <t xml:space="preserve">26.8932228088379</t>
   </si>
   <si>
     <t xml:space="preserve">27.1757564544678</t>
@@ -3662,22 +3662,22 @@
     <t xml:space="preserve">26.7872772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">26.098611831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4629230499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8095741271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2333660125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.127420425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7389450073242</t>
+    <t xml:space="preserve">26.0986137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4629249572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8095779418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2333679199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1274185180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7389430999756</t>
   </si>
   <si>
     <t xml:space="preserve">24.173885345459</t>
@@ -3689,70 +3689,70 @@
     <t xml:space="preserve">21.4192295074463</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3662528991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6906070709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.066068649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9424591064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3551044464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.772388458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7789001464844</t>
+    <t xml:space="preserve">21.3662548065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6906089782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0660667419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9424610137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3551063537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7723903656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7788982391357</t>
   </si>
   <si>
     <t xml:space="preserve">22.4610538482666</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2844734191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2314968109131</t>
+    <t xml:space="preserve">22.2844715118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2314987182617</t>
   </si>
   <si>
     <t xml:space="preserve">21.8077049255371</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5251770019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4722003936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5604915618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9907932281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3374443054199</t>
+    <t xml:space="preserve">21.5251750946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4722023010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5604934692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.990795135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3374462127686</t>
   </si>
   <si>
     <t xml:space="preserve">21.8430194854736</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7547302246094</t>
+    <t xml:space="preserve">21.7547283172607</t>
   </si>
   <si>
     <t xml:space="preserve">21.7900485992432</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5958061218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3839130401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9601173400879</t>
+    <t xml:space="preserve">21.5958080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3839111328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9601192474365</t>
   </si>
   <si>
     <t xml:space="preserve">21.1896724700928</t>
@@ -3770,13 +3770,13 @@
     <t xml:space="preserve">20.8365116119385</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0595550537109</t>
+    <t xml:space="preserve">20.0595569610596</t>
   </si>
   <si>
     <t xml:space="preserve">19.9359512329102</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3774032592773</t>
+    <t xml:space="preserve">20.3774013519287</t>
   </si>
   <si>
     <t xml:space="preserve">20.5186653137207</t>
@@ -3797,22 +3797,22 @@
     <t xml:space="preserve">20.041898727417</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1943130493164</t>
+    <t xml:space="preserve">19.194314956665</t>
   </si>
   <si>
     <t xml:space="preserve">19.4238662719727</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7770290374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3420867919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3355770111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5474739074707</t>
+    <t xml:space="preserve">19.777027130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3420848846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3355751037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5474720001221</t>
   </si>
   <si>
     <t xml:space="preserve">19.6710815429688</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">19.911153793335</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0677719116211</t>
+    <t xml:space="preserve">19.0677738189697</t>
   </si>
   <si>
     <t xml:space="preserve">19.4711265563965</t>
@@ -3836,52 +3836,52 @@
     <t xml:space="preserve">20.9012126922607</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6995334625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3145122528076</t>
+    <t xml:space="preserve">20.6995315551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.314510345459</t>
   </si>
   <si>
     <t xml:space="preserve">20.64453125</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0944976806641</t>
+    <t xml:space="preserve">20.0944995880127</t>
   </si>
   <si>
     <t xml:space="preserve">20.4061832427979</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1678352355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5811347961426</t>
+    <t xml:space="preserve">20.1678371429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5811367034912</t>
   </si>
   <si>
     <t xml:space="preserve">19.3061180114746</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3710670471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7560882568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0127696990967</t>
+    <t xml:space="preserve">18.3710651397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7560863494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.012767791748</t>
   </si>
   <si>
     <t xml:space="preserve">18.0960502624512</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0861072540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.729362487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9493770599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2801704406738</t>
+    <t xml:space="preserve">19.0861053466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7293605804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9493751525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2801685333252</t>
   </si>
   <si>
     <t xml:space="preserve">17.261833190918</t>
@@ -3893,7 +3893,7 @@
     <t xml:space="preserve">17.2343330383301</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0968246459961</t>
+    <t xml:space="preserve">17.0968227386475</t>
   </si>
   <si>
     <t xml:space="preserve">16.7576389312744</t>
@@ -3902,28 +3902,28 @@
     <t xml:space="preserve">16.2626094818115</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1617698669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1709384918213</t>
+    <t xml:space="preserve">16.1617679595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1709365844727</t>
   </si>
   <si>
     <t xml:space="preserve">15.9875946044922</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3817844390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7851390838623</t>
+    <t xml:space="preserve">16.3817825317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7851409912109</t>
   </si>
   <si>
     <t xml:space="preserve">17.0601558685303</t>
   </si>
   <si>
-    <t xml:space="preserve">17.188497543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4635124206543</t>
+    <t xml:space="preserve">17.1884956359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4635105133057</t>
   </si>
   <si>
     <t xml:space="preserve">16.9501476287842</t>
@@ -3938,10 +3938,10 @@
     <t xml:space="preserve">16.9043140411377</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0693244934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9593181610107</t>
+    <t xml:space="preserve">17.0693225860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9593162536621</t>
   </si>
   <si>
     <t xml:space="preserve">17.1334934234619</t>
@@ -3950,10 +3950,10 @@
     <t xml:space="preserve">16.8676452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3359470367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8500881195068</t>
+    <t xml:space="preserve">16.3359489440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8500862121582</t>
   </si>
   <si>
     <t xml:space="preserve">16.8218078613281</t>
@@ -3965,25 +3965,25 @@
     <t xml:space="preserve">17.1151599884033</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8852043151855</t>
+    <t xml:space="preserve">17.8852062225342</t>
   </si>
   <si>
     <t xml:space="preserve">17.6560230255127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6376876831055</t>
+    <t xml:space="preserve">17.6376895904541</t>
   </si>
   <si>
     <t xml:space="preserve">16.8859786987305</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4726791381836</t>
+    <t xml:space="preserve">17.472677230835</t>
   </si>
   <si>
     <t xml:space="preserve">17.5643520355225</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6835250854492</t>
+    <t xml:space="preserve">17.6835269927979</t>
   </si>
   <si>
     <t xml:space="preserve">17.6651916503906</t>
@@ -3995,91 +3995,91 @@
     <t xml:space="preserve">17.3351707458496</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9868183135986</t>
+    <t xml:space="preserve">16.9868202209473</t>
   </si>
   <si>
     <t xml:space="preserve">17.0784893035889</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8584766387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4001159667969</t>
+    <t xml:space="preserve">16.8584785461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4001178741455</t>
   </si>
   <si>
     <t xml:space="preserve">15.9967613220215</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9417572021484</t>
+    <t xml:space="preserve">15.9417581558228</t>
   </si>
   <si>
     <t xml:space="preserve">16.0425968170166</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0150947570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6392383575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9142560958862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0525388717651</t>
+    <t xml:space="preserve">16.0150966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6392393112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9142570495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0525398254395</t>
   </si>
   <si>
     <t xml:space="preserve">15.2542181015015</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2175493240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1992158889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6117391586304</t>
+    <t xml:space="preserve">15.21755027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1992139816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6117401123047</t>
   </si>
   <si>
     <t xml:space="preserve">16.0059280395508</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6942434310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9883699417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5758438110352</t>
+    <t xml:space="preserve">15.6942443847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9883689880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5758447647095</t>
   </si>
   <si>
     <t xml:space="preserve">14.5850114822388</t>
   </si>
   <si>
-    <t xml:space="preserve">13.860803604126</t>
+    <t xml:space="preserve">13.8608026504517</t>
   </si>
   <si>
     <t xml:space="preserve">13.8058004379272</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6041231155396</t>
+    <t xml:space="preserve">13.6041212081909</t>
   </si>
   <si>
     <t xml:space="preserve">13.3841104507446</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5857877731323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7599658966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.924973487854</t>
+    <t xml:space="preserve">13.585786819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7599639892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9249725341797</t>
   </si>
   <si>
     <t xml:space="preserve">13.3107719421387</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8149681091309</t>
+    <t xml:space="preserve">13.8149671554565</t>
   </si>
   <si>
     <t xml:space="preserve">13.5032825469971</t>
@@ -4097,13 +4097,13 @@
     <t xml:space="preserve">13.3382730484009</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4482793807983</t>
+    <t xml:space="preserve">13.4482803344727</t>
   </si>
   <si>
     <t xml:space="preserve">13.8516359329224</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5307836532593</t>
+    <t xml:space="preserve">13.5307855606079</t>
   </si>
   <si>
     <t xml:space="preserve">13.8424692153931</t>
@@ -4112,13 +4112,13 @@
     <t xml:space="preserve">14.1908226013184</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3466653823853</t>
+    <t xml:space="preserve">14.3466644287109</t>
   </si>
   <si>
     <t xml:space="preserve">14.603346824646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1816549301147</t>
+    <t xml:space="preserve">14.1816558837891</t>
   </si>
   <si>
     <t xml:space="preserve">14.5483436584473</t>
@@ -4127,16 +4127,16 @@
     <t xml:space="preserve">14.8233594894409</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5659017562866</t>
+    <t xml:space="preserve">15.5659008026123</t>
   </si>
   <si>
     <t xml:space="preserve">15.7217445373535</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9050884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1526050567627</t>
+    <t xml:space="preserve">15.9050903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1526031494141</t>
   </si>
   <si>
     <t xml:space="preserve">16.7026348114014</t>
@@ -4154,22 +4154,22 @@
     <t xml:space="preserve">20.5528583526611</t>
   </si>
   <si>
-    <t xml:space="preserve">20.717866897583</t>
+    <t xml:space="preserve">20.7178688049316</t>
   </si>
   <si>
     <t xml:space="preserve">19.4161243438721</t>
   </si>
   <si>
-    <t xml:space="preserve">19.15944480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0494384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.617805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2595100402832</t>
+    <t xml:space="preserve">19.1594409942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0494403839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6178035736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2595081329346</t>
   </si>
   <si>
     <t xml:space="preserve">19.7094764709473</t>
@@ -4193,13 +4193,13 @@
     <t xml:space="preserve">19.4527931213379</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5261325836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7278079986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3695125579834</t>
+    <t xml:space="preserve">19.5261306762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7278099060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.369514465332</t>
   </si>
   <si>
     <t xml:space="preserve">19.8378162384033</t>
@@ -4208,25 +4208,25 @@
     <t xml:space="preserve">19.3244533538818</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9760990142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9577674865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2144470214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6728076934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2327823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0578289031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1128330230713</t>
+    <t xml:space="preserve">18.9761028289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9577655792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2144451141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6728038787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.232780456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0578269958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1128311157227</t>
   </si>
   <si>
     <t xml:space="preserve">20.2961769104004</t>
@@ -4235,52 +4235,52 @@
     <t xml:space="preserve">20.5161895751953</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8179321289062</t>
+    <t xml:space="preserve">21.8179302215576</t>
   </si>
   <si>
     <t xml:space="preserve">21.2495651245117</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9928817749023</t>
+    <t xml:space="preserve">20.992883682251</t>
   </si>
   <si>
     <t xml:space="preserve">20.7728710174561</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8828773498535</t>
+    <t xml:space="preserve">20.8828792572021</t>
   </si>
   <si>
     <t xml:space="preserve">21.047887802124</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8095397949219</t>
+    <t xml:space="preserve">20.8095417022705</t>
   </si>
   <si>
     <t xml:space="preserve">20.7362041473389</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7828121185303</t>
+    <t xml:space="preserve">19.7828140258789</t>
   </si>
   <si>
     <t xml:space="preserve">19.7644786834717</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2511177062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8660926818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3977928161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3427886962891</t>
+    <t xml:space="preserve">19.2511157989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8660945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3977890014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3427867889404</t>
   </si>
   <si>
     <t xml:space="preserve">19.4894638061523</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5994682312012</t>
+    <t xml:space="preserve">19.5994663238525</t>
   </si>
   <si>
     <t xml:space="preserve">20.3511810302734</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">19.8744869232178</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1495037078857</t>
+    <t xml:space="preserve">20.1495018005371</t>
   </si>
   <si>
     <t xml:space="preserve">20.0761642456055</t>
@@ -4298,10 +4298,10 @@
     <t xml:space="preserve">20.0394954681396</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9745483398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2128963470459</t>
+    <t xml:space="preserve">20.9745502471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2128944396973</t>
   </si>
   <si>
     <t xml:space="preserve">21.5795841217041</t>
@@ -4310,16 +4310,16 @@
     <t xml:space="preserve">21.6345882415771</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6529235839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6162509918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5429153442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6811981201172</t>
+    <t xml:space="preserve">21.6529216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6162528991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5429134368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6812000274658</t>
   </si>
   <si>
     <t xml:space="preserve">21.3045673370361</t>
@@ -4328,10 +4328,10 @@
     <t xml:space="preserve">20.6628665924072</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4245204925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5711936950684</t>
+    <t xml:space="preserve">20.4245185852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5711917877197</t>
   </si>
   <si>
     <t xml:space="preserve">19.966157913208</t>
@@ -4343,40 +4343,40 @@
     <t xml:space="preserve">19.3611240386963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5444660186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9294891357422</t>
+    <t xml:space="preserve">19.5444641113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9294872283936</t>
   </si>
   <si>
     <t xml:space="preserve">20.0211620330811</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6460819244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4444046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.481071472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.609411239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4077339172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3343963623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9210948944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2877864837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1961116790771</t>
+    <t xml:space="preserve">18.6460800170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4444026947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4810733795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6094131469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.407735824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3343982696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9210987091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.287784576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1961135864258</t>
   </si>
   <si>
     <t xml:space="preserve">19.1044406890869</t>
@@ -4388,19 +4388,19 @@
     <t xml:space="preserve">18.6169300079346</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8756313323975</t>
+    <t xml:space="preserve">17.8756294250488</t>
   </si>
   <si>
     <t xml:space="preserve">17.5378246307373</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7348785400391</t>
+    <t xml:space="preserve">17.7348766326904</t>
   </si>
   <si>
     <t xml:space="preserve">17.6410427093506</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2469329833984</t>
+    <t xml:space="preserve">17.2469348907471</t>
   </si>
   <si>
     <t xml:space="preserve">17.1437168121338</t>
@@ -4412,7 +4412,7 @@
     <t xml:space="preserve">17.0498809814453</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0029621124268</t>
+    <t xml:space="preserve">17.0029640197754</t>
   </si>
   <si>
     <t xml:space="preserve">17.0311126708984</t>
@@ -4421,40 +4421,40 @@
     <t xml:space="preserve">16.9560451507568</t>
   </si>
   <si>
-    <t xml:space="preserve">16.89035987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9091281890869</t>
+    <t xml:space="preserve">16.8903617858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9091262817383</t>
   </si>
   <si>
     <t xml:space="preserve">17.078031539917</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1852855682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2885055541992</t>
+    <t xml:space="preserve">18.1852874755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2885074615479</t>
   </si>
   <si>
     <t xml:space="preserve">17.565975189209</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0069999694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.922550201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8662490844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8005619049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5753593444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7536468505859</t>
+    <t xml:space="preserve">18.0070018768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9225482940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8662509918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8005599975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5753555297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7536449432373</t>
   </si>
   <si>
     <t xml:space="preserve">17.9319343566895</t>
@@ -4463,16 +4463,16 @@
     <t xml:space="preserve">17.9882335662842</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3354263305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5137119293213</t>
+    <t xml:space="preserve">18.3354244232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5137100219727</t>
   </si>
   <si>
     <t xml:space="preserve">18.7858333587646</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5230960845947</t>
+    <t xml:space="preserve">18.5230941772461</t>
   </si>
   <si>
     <t xml:space="preserve">18.7483005523682</t>
@@ -4487,10 +4487,10 @@
     <t xml:space="preserve">17.8474807739258</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4386425018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0056934356689</t>
+    <t xml:space="preserve">18.4386444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0056915283203</t>
   </si>
   <si>
     <t xml:space="preserve">20.1558284759521</t>
@@ -4505,7 +4505,7 @@
     <t xml:space="preserve">19.8555564880371</t>
   </si>
   <si>
-    <t xml:space="preserve">19.874324798584</t>
+    <t xml:space="preserve">19.8743228912354</t>
   </si>
   <si>
     <t xml:space="preserve">19.198709487915</t>
@@ -4514,7 +4514,7 @@
     <t xml:space="preserve">19.2925453186035</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6678848266602</t>
+    <t xml:space="preserve">19.6678867340088</t>
   </si>
   <si>
     <t xml:space="preserve">19.2737789154053</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">19.4989833831787</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3622665405273</t>
+    <t xml:space="preserve">20.362268447876</t>
   </si>
   <si>
     <t xml:space="preserve">20.7939109802246</t>
@@ -4547,16 +4547,16 @@
     <t xml:space="preserve">21.8073310852051</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1826705932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2389755249023</t>
+    <t xml:space="preserve">22.1826725006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2389736175537</t>
   </si>
   <si>
     <t xml:space="preserve">22.2952766418457</t>
   </si>
   <si>
-    <t xml:space="preserve">22.482946395874</t>
+    <t xml:space="preserve">22.4829444885254</t>
   </si>
   <si>
     <t xml:space="preserve">21.9574661254883</t>
@@ -4565,40 +4565,40 @@
     <t xml:space="preserve">21.8448677062988</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7697982788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7134971618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.995002746582</t>
+    <t xml:space="preserve">21.7698001861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7134952545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9950046539307</t>
   </si>
   <si>
     <t xml:space="preserve">22.5767803192139</t>
   </si>
   <si>
-    <t xml:space="preserve">22.670618057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9708881378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.914587020874</t>
+    <t xml:space="preserve">22.6706161499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.970890045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9145908355713</t>
   </si>
   <si>
     <t xml:space="preserve">23.158561706543</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2711639404297</t>
+    <t xml:space="preserve">23.2711620330811</t>
   </si>
   <si>
     <t xml:space="preserve">23.1397933959961</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4882926940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8824005126953</t>
+    <t xml:space="preserve">21.4882907867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8823986053467</t>
   </si>
   <si>
     <t xml:space="preserve">21.8636322021484</t>
@@ -4613,13 +4613,13 @@
     <t xml:space="preserve">21.1692504882812</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2443180084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8877468109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6813106536865</t>
+    <t xml:space="preserve">21.2443199157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8877449035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6813087463379</t>
   </si>
   <si>
     <t xml:space="preserve">20.1182975769043</t>
@@ -4643,7 +4643,7 @@
     <t xml:space="preserve">19.7054195404053</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0807628631592</t>
+    <t xml:space="preserve">20.0807609558105</t>
   </si>
   <si>
     <t xml:space="preserve">19.742956161499</t>
@@ -4652,13 +4652,13 @@
     <t xml:space="preserve">19.6115837097168</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4239139556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4426803588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3300800323486</t>
+    <t xml:space="preserve">19.4239158630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4426822662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.330078125</t>
   </si>
   <si>
     <t xml:space="preserve">18.9359703063965</t>
@@ -4667,40 +4667,40 @@
     <t xml:space="preserve">18.9172039031982</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2684326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.686653137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1236419677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9922695159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9118595123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4051475524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.818021774292</t>
+    <t xml:space="preserve">20.2684345245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6866512298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1236400604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9922714233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9118576049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4051456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8180255889893</t>
   </si>
   <si>
     <t xml:space="preserve">19.9681606292725</t>
   </si>
   <si>
-    <t xml:space="preserve">20.606237411499</t>
+    <t xml:space="preserve">20.6062393188477</t>
   </si>
   <si>
     <t xml:space="preserve">21.4695243835449</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7162265777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5848598480225</t>
+    <t xml:space="preserve">24.7162284851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5848579406738</t>
   </si>
   <si>
     <t xml:space="preserve">24.6974601745605</t>
@@ -4712,19 +4712,19 @@
     <t xml:space="preserve">24.922664642334</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8475971221924</t>
+    <t xml:space="preserve">24.8475952148438</t>
   </si>
   <si>
     <t xml:space="preserve">25.4293766021729</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0486869812012</t>
+    <t xml:space="preserve">26.0486888885498</t>
   </si>
   <si>
     <t xml:space="preserve">25.710880279541</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2363605499268</t>
+    <t xml:space="preserve">26.2363567352295</t>
   </si>
   <si>
     <t xml:space="preserve">25.8422527313232</t>
@@ -4739,7 +4739,7 @@
     <t xml:space="preserve">25.7484169006348</t>
   </si>
   <si>
-    <t xml:space="preserve">26.067455291748</t>
+    <t xml:space="preserve">26.0674571990967</t>
   </si>
   <si>
     <t xml:space="preserve">26.5741672515869</t>
@@ -4754,10 +4754,10 @@
     <t xml:space="preserve">26.7806053161621</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9119758605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0058116912842</t>
+    <t xml:space="preserve">26.9119739532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0058097839355</t>
   </si>
   <si>
     <t xml:space="preserve">27.231014251709</t>
@@ -4772,64 +4772,64 @@
     <t xml:space="preserve">26.8932075500488</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6814250946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7189598083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4749851226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7377262115479</t>
+    <t xml:space="preserve">27.6814231872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.718957901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4749870300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7377243041992</t>
   </si>
   <si>
     <t xml:space="preserve">28.1693687438965</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9629287719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6573123931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5071754455566</t>
+    <t xml:space="preserve">27.962926864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6573104858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.507173538208</t>
   </si>
   <si>
     <t xml:space="preserve">28.6385440826416</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9307422637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.775260925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8878612518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4321060180664</t>
+    <t xml:space="preserve">26.9307403564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7752590179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8878593444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4321041107178</t>
   </si>
   <si>
     <t xml:space="preserve">28.8074474334717</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2766265869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8449802398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7136135101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1881351470947</t>
+    <t xml:space="preserve">29.2766246795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8449821472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7136116027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1881332397461</t>
   </si>
   <si>
     <t xml:space="preserve">27.8315601348877</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7940292358398</t>
+    <t xml:space="preserve">27.7940273284912</t>
   </si>
   <si>
     <t xml:space="preserve">27.9253959655762</t>
@@ -4838,25 +4838,25 @@
     <t xml:space="preserve">28.2819690704346</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1640224456787</t>
+    <t xml:space="preserve">29.1640205383301</t>
   </si>
   <si>
     <t xml:space="preserve">27.944164276123</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2444343566895</t>
+    <t xml:space="preserve">28.2444362640381</t>
   </si>
   <si>
     <t xml:space="preserve">27.6063556671143</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1130657196045</t>
+    <t xml:space="preserve">28.1130638122559</t>
   </si>
   <si>
     <t xml:space="preserve">27.5500545501709</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1934795379639</t>
+    <t xml:space="preserve">27.1934814453125</t>
   </si>
   <si>
     <t xml:space="preserve">26.7243022918701</t>
@@ -4868,7 +4868,7 @@
     <t xml:space="preserve">26.874439239502</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4374504089355</t>
+    <t xml:space="preserve">27.4374523162842</t>
   </si>
   <si>
     <t xml:space="preserve">27.3060817718506</t>
@@ -4877,37 +4877,37 @@
     <t xml:space="preserve">26.7055339813232</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8181381225586</t>
+    <t xml:space="preserve">26.8181400299072</t>
   </si>
   <si>
     <t xml:space="preserve">27.0996437072754</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1318321228027</t>
+    <t xml:space="preserve">28.1318340301514</t>
   </si>
   <si>
     <t xml:space="preserve">28.206901550293</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9951171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.019229888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4884090423584</t>
+    <t xml:space="preserve">28.9951190948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0192317962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4884071350098</t>
   </si>
   <si>
     <t xml:space="preserve">30.2900447845459</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5527877807617</t>
+    <t xml:space="preserve">30.5527858734131</t>
   </si>
   <si>
     <t xml:space="preserve">31.1533317565918</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4777145385742</t>
+    <t xml:space="preserve">30.4777164459229</t>
   </si>
   <si>
     <t xml:space="preserve">30.515251159668</t>
@@ -4916,7 +4916,7 @@
     <t xml:space="preserve">30.383882522583</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0460758209229</t>
+    <t xml:space="preserve">30.0460739135742</t>
   </si>
   <si>
     <t xml:space="preserve">30.1211414337158</t>
@@ -4925,7 +4925,7 @@
     <t xml:space="preserve">29.6519660949707</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9897708892822</t>
+    <t xml:space="preserve">29.9897727966309</t>
   </si>
   <si>
     <t xml:space="preserve">30.083610534668</t>
@@ -4937,7 +4937,7 @@
     <t xml:space="preserve">29.7270336151123</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4026489257812</t>
+    <t xml:space="preserve">30.4026508331299</t>
   </si>
   <si>
     <t xml:space="preserve">30.2712783813477</t>
@@ -4949,7 +4949,7 @@
     <t xml:space="preserve">28.5259418487549</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3007354736328</t>
+    <t xml:space="preserve">28.3007373809814</t>
   </si>
   <si>
     <t xml:space="preserve">28.0942993164062</t>
@@ -4967,7 +4967,7 @@
     <t xml:space="preserve">29.5205955505371</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9763507843018</t>
+    <t xml:space="preserve">28.9763488769531</t>
   </si>
   <si>
     <t xml:space="preserve">29.4830627441406</t>
@@ -4979,13 +4979,13 @@
     <t xml:space="preserve">28.9575843811035</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1452541351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0031967163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9468936920166</t>
+    <t xml:space="preserve">29.1452560424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.00319480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.946891784668</t>
   </si>
   <si>
     <t xml:space="preserve">30.7779903411865</t>
@@ -4994,19 +4994,19 @@
     <t xml:space="preserve">31.3973007202148</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5581321716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7029209136963</t>
+    <t xml:space="preserve">29.5581302642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7029228210449</t>
   </si>
   <si>
     <t xml:space="preserve">30.3463478088379</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4455280303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2953910827637</t>
+    <t xml:space="preserve">29.4455261230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2953929901123</t>
   </si>
   <si>
     <t xml:space="preserve">29.4392318725586</t>
@@ -5021,31 +5021,31 @@
     <t xml:space="preserve">29.6310176849365</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5543022155762</t>
+    <t xml:space="preserve">29.5543041229248</t>
   </si>
   <si>
     <t xml:space="preserve">30.7242012023926</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6064167022705</t>
+    <t xml:space="preserve">31.6064205169678</t>
   </si>
   <si>
     <t xml:space="preserve">30.6091289520264</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3570995330811</t>
+    <t xml:space="preserve">31.3570957183838</t>
   </si>
   <si>
     <t xml:space="preserve">30.8968086242676</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8776321411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4940547943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2995586395264</t>
+    <t xml:space="preserve">30.8776302337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4940567016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.299560546875</t>
   </si>
   <si>
     <t xml:space="preserve">31.2803802490234</t>
@@ -5054,7 +5054,7 @@
     <t xml:space="preserve">30.9159889221191</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8392715454102</t>
+    <t xml:space="preserve">30.8392734527588</t>
   </si>
   <si>
     <t xml:space="preserve">30.7050228118896</t>
@@ -5066,7 +5066,7 @@
     <t xml:space="preserve">30.9543437957764</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7077312469482</t>
+    <t xml:space="preserve">29.7077331542969</t>
   </si>
   <si>
     <t xml:space="preserve">30.6858425140381</t>
@@ -5078,22 +5078,22 @@
     <t xml:space="preserve">30.4556999206543</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4913463592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7817344665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4721698760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0145893096924</t>
+    <t xml:space="preserve">31.4913482666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7817363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.47216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.014591217041</t>
   </si>
   <si>
     <t xml:space="preserve">28.4227619171143</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4419422149658</t>
+    <t xml:space="preserve">28.4419403076172</t>
   </si>
   <si>
     <t xml:space="preserve">28.0008335113525</t>
@@ -5102,13 +5102,13 @@
     <t xml:space="preserve">28.5761909484863</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8638706207275</t>
+    <t xml:space="preserve">28.8638725280762</t>
   </si>
   <si>
     <t xml:space="preserve">30.359806060791</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2063789367676</t>
+    <t xml:space="preserve">30.2063770294189</t>
   </si>
   <si>
     <t xml:space="preserve">30.4365196228027</t>
@@ -5120,7 +5120,7 @@
     <t xml:space="preserve">30.8009147644043</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2611999511719</t>
+    <t xml:space="preserve">31.2612018585205</t>
   </si>
   <si>
     <t xml:space="preserve">31.4146308898926</t>
@@ -5141,7 +5141,7 @@
     <t xml:space="preserve">29.3241596221924</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4584102630615</t>
+    <t xml:space="preserve">29.4584083557129</t>
   </si>
   <si>
     <t xml:space="preserve">28.7487983703613</t>
@@ -5153,10 +5153,10 @@
     <t xml:space="preserve">27.9432964324951</t>
   </si>
   <si>
-    <t xml:space="preserve">26.102144241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5459632873535</t>
+    <t xml:space="preserve">26.1021461486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5459651947021</t>
   </si>
   <si>
     <t xml:space="preserve">25.1432113647461</t>
@@ -5171,28 +5171,28 @@
     <t xml:space="preserve">26.0446090698242</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2172164916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0637893676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.929536819458</t>
+    <t xml:space="preserve">26.2172183990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0637874603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9295387268066</t>
   </si>
   <si>
     <t xml:space="preserve">26.5432548522949</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4281826019287</t>
+    <t xml:space="preserve">26.4281806945801</t>
   </si>
   <si>
     <t xml:space="preserve">26.8692932128906</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0419006347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1953296661377</t>
+    <t xml:space="preserve">27.041898727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1953277587891</t>
   </si>
   <si>
     <t xml:space="preserve">27.0610771179199</t>
@@ -5213,7 +5213,7 @@
     <t xml:space="preserve">26.524076461792</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5624332427979</t>
+    <t xml:space="preserve">26.5624351501465</t>
   </si>
   <si>
     <t xml:space="preserve">25.6802158355713</t>
@@ -5222,28 +5222,28 @@
     <t xml:space="preserve">25.3158206939697</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5843238830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3925342559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0281410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7952861785889</t>
+    <t xml:space="preserve">25.584321975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3925361633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0281429290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7952880859375</t>
   </si>
   <si>
     <t xml:space="preserve">26.2939319610596</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9487152099609</t>
+    <t xml:space="preserve">25.9487171173096</t>
   </si>
   <si>
     <t xml:space="preserve">26.4857196807861</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7733974456787</t>
+    <t xml:space="preserve">26.7733993530273</t>
   </si>
   <si>
     <t xml:space="preserve">25.6418590545654</t>
@@ -5252,34 +5252,34 @@
     <t xml:space="preserve">25.7761077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1213245391846</t>
+    <t xml:space="preserve">26.1213226318359</t>
   </si>
   <si>
     <t xml:space="preserve">25.7377510070801</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6583271026611</t>
+    <t xml:space="preserve">26.6583251953125</t>
   </si>
   <si>
     <t xml:space="preserve">26.0829677581787</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9678955078125</t>
+    <t xml:space="preserve">25.9678936004639</t>
   </si>
   <si>
     <t xml:space="preserve">26.1405029296875</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1596813201904</t>
+    <t xml:space="preserve">26.1596832275391</t>
   </si>
   <si>
     <t xml:space="preserve">25.8528232574463</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8144664764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9103603363037</t>
+    <t xml:space="preserve">25.8144645690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9103584289551</t>
   </si>
   <si>
     <t xml:space="preserve">25.9870738983154</t>
@@ -5288,13 +5288,13 @@
     <t xml:space="preserve">25.6993942260742</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4884281158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7569313049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2966423034668</t>
+    <t xml:space="preserve">25.4884300231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.756929397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2966403961182</t>
   </si>
   <si>
     <t xml:space="preserve">26.3514671325684</t>
@@ -5312,10 +5312,10 @@
     <t xml:space="preserve">27.5789012908936</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8309326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3541793823242</t>
+    <t xml:space="preserve">26.8309345245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3541774749756</t>
   </si>
   <si>
     <t xml:space="preserve">26.7542190551758</t>
@@ -5327,7 +5327,7 @@
     <t xml:space="preserve">26.6391487121582</t>
   </si>
   <si>
-    <t xml:space="preserve">28.307689666748</t>
+    <t xml:space="preserve">28.3076915740967</t>
   </si>
   <si>
     <t xml:space="preserve">28.557014465332</t>
@@ -5348,16 +5348,16 @@
     <t xml:space="preserve">26.7925777435303</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0227203369141</t>
+    <t xml:space="preserve">27.0227222442627</t>
   </si>
   <si>
     <t xml:space="preserve">26.8501129150391</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2145080566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3487586975098</t>
+    <t xml:space="preserve">27.214506149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3487567901611</t>
   </si>
   <si>
     <t xml:space="preserve">27.962474822998</t>
@@ -5366,16 +5366,16 @@
     <t xml:space="preserve">28.6337280273438</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1131954193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3049812316895</t>
+    <t xml:space="preserve">29.1131935119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3049793243408</t>
   </si>
   <si>
     <t xml:space="preserve">29.0556564331055</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9597663879395</t>
+    <t xml:space="preserve">28.9597644805908</t>
   </si>
   <si>
     <t xml:space="preserve">28.7296199798584</t>
@@ -5405,10 +5405,10 @@
     <t xml:space="preserve">27.809045791626</t>
   </si>
   <si>
-    <t xml:space="preserve">27.617259979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9049377441406</t>
+    <t xml:space="preserve">27.6172580718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9049396514893</t>
   </si>
   <si>
     <t xml:space="preserve">30.6666641235352</t>
@@ -5420,13 +5420,13 @@
     <t xml:space="preserve">31.1077728271484</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2228488922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6037063598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1050643920898</t>
+    <t xml:space="preserve">31.2228469848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6037101745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1050605773926</t>
   </si>
   <si>
     <t xml:space="preserve">32.6804275512695</t>
@@ -5438,7 +5438,7 @@
     <t xml:space="preserve">32.5269927978516</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2584953308105</t>
+    <t xml:space="preserve">32.2584915161133</t>
   </si>
   <si>
     <t xml:space="preserve">32.2776718139648</t>
@@ -5447,7 +5447,7 @@
     <t xml:space="preserve">31.8365631103516</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7598476409912</t>
+    <t xml:space="preserve">31.7598495483398</t>
   </si>
   <si>
     <t xml:space="preserve">32.2009582519531</t>
@@ -5468,7 +5468,7 @@
     <t xml:space="preserve">32.584529876709</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0475234985352</t>
+    <t xml:space="preserve">32.0475273132324</t>
   </si>
   <si>
     <t xml:space="preserve">32.6228866577148</t>
@@ -5480,22 +5480,22 @@
     <t xml:space="preserve">32.6420669555664</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2968482971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9708137512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4338111877441</t>
+    <t xml:space="preserve">32.2968521118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9708118438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4338092803955</t>
   </si>
   <si>
     <t xml:space="preserve">30.9735221862793</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9762344360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5324153900146</t>
+    <t xml:space="preserve">29.9762325286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.532413482666</t>
   </si>
   <si>
     <t xml:space="preserve">30.1104831695557</t>
@@ -5519,7 +5519,10 @@
     <t xml:space="preserve">29.2090854644775</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6856346130371</t>
+    <t xml:space="preserve">23.6856365203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.721284866333</t>
   </si>
   <si>
     <t xml:space="preserve">23.9157791137695</t>
@@ -5543,7 +5546,7 @@
     <t xml:space="preserve">25.2774639129639</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6829261779785</t>
+    <t xml:space="preserve">24.6829242706299</t>
   </si>
   <si>
     <t xml:space="preserve">25.1048564910889</t>
@@ -5555,13 +5558,13 @@
     <t xml:space="preserve">25.5267868041992</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5816116333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6199684143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4090042114258</t>
+    <t xml:space="preserve">26.5816097259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6199703216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4090061187744</t>
   </si>
   <si>
     <t xml:space="preserve">27.7131519317627</t>
@@ -5570,7 +5573,7 @@
     <t xml:space="preserve">29.611837387085</t>
   </si>
   <si>
-    <t xml:space="preserve">28.902229309082</t>
+    <t xml:space="preserve">28.9022274017334</t>
   </si>
   <si>
     <t xml:space="preserve">28.6145496368408</t>
@@ -5832,6 +5835,9 @@
   </si>
   <si>
     <t xml:space="preserve">29.1599998474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1399993896484</t>
   </si>
 </sst>
 </file>
@@ -67470,7 +67476,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G2358" t="s">
-        <v>1197</v>
+        <v>1836</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67496,7 +67502,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G2359" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67522,7 +67528,7 @@
         <v>26.0599994659424</v>
       </c>
       <c r="G2360" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67548,7 +67554,7 @@
         <v>26.2399997711182</v>
       </c>
       <c r="G2361" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67574,7 +67580,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G2362" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67600,7 +67606,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G2363" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -67626,7 +67632,7 @@
         <v>26.7199993133545</v>
       </c>
       <c r="G2364" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67652,7 +67658,7 @@
         <v>26.3600006103516</v>
       </c>
       <c r="G2365" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67678,7 +67684,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G2366" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67704,7 +67710,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G2367" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67756,7 +67762,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G2369" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67782,7 +67788,7 @@
         <v>26.6200008392334</v>
       </c>
       <c r="G2370" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -67860,7 +67866,7 @@
         <v>27.7199993133545</v>
       </c>
       <c r="G2373" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -67912,7 +67918,7 @@
         <v>27.7600002288818</v>
       </c>
       <c r="G2375" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -67964,7 +67970,7 @@
         <v>27.5400009155273</v>
       </c>
       <c r="G2377" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -68016,7 +68022,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G2379" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -68042,7 +68048,7 @@
         <v>30.8799991607666</v>
       </c>
       <c r="G2380" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -68068,7 +68074,7 @@
         <v>30.1399993896484</v>
       </c>
       <c r="G2381" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -68094,7 +68100,7 @@
         <v>29.8400001525879</v>
       </c>
       <c r="G2382" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -68146,7 +68152,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G2384" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -68172,7 +68178,7 @@
         <v>29.0200004577637</v>
       </c>
       <c r="G2385" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -68198,7 +68204,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G2386" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -68224,7 +68230,7 @@
         <v>28.3799991607666</v>
       </c>
       <c r="G2387" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -68250,7 +68256,7 @@
         <v>27.9799995422363</v>
       </c>
       <c r="G2388" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -68276,7 +68282,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -68302,7 +68308,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G2390" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -68328,7 +68334,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G2391" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -68354,7 +68360,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G2392" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -68380,7 +68386,7 @@
         <v>28.8199996948242</v>
       </c>
       <c r="G2393" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -68406,7 +68412,7 @@
         <v>28.4400005340576</v>
       </c>
       <c r="G2394" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68432,7 +68438,7 @@
         <v>28.3400001525879</v>
       </c>
       <c r="G2395" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68458,7 +68464,7 @@
         <v>28.2800006866455</v>
       </c>
       <c r="G2396" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68484,7 +68490,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G2397" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68510,7 +68516,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G2398" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68536,7 +68542,7 @@
         <v>28.4200000762939</v>
       </c>
       <c r="G2399" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68562,7 +68568,7 @@
         <v>28.5599994659424</v>
       </c>
       <c r="G2400" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68588,7 +68594,7 @@
         <v>28.5799999237061</v>
       </c>
       <c r="G2401" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68614,7 +68620,7 @@
         <v>28.0599994659424</v>
       </c>
       <c r="G2402" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68640,7 +68646,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G2403" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68666,7 +68672,7 @@
         <v>27.9400005340576</v>
       </c>
       <c r="G2404" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68692,7 +68698,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G2405" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68718,7 +68724,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G2406" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68744,7 +68750,7 @@
         <v>27.0400009155273</v>
       </c>
       <c r="G2407" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68770,7 +68776,7 @@
         <v>27.1599998474121</v>
       </c>
       <c r="G2408" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68796,7 +68802,7 @@
         <v>27.1200008392334</v>
       </c>
       <c r="G2409" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68822,7 +68828,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G2410" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68848,7 +68854,7 @@
         <v>27.5400009155273</v>
       </c>
       <c r="G2411" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -68874,7 +68880,7 @@
         <v>27.9799995422363</v>
       </c>
       <c r="G2412" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -68900,7 +68906,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G2413" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -68926,7 +68932,7 @@
         <v>28.5</v>
       </c>
       <c r="G2414" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -68952,7 +68958,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G2415" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -68978,7 +68984,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G2416" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -69004,7 +69010,7 @@
         <v>29.0400009155273</v>
       </c>
       <c r="G2417" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -69030,7 +69036,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G2418" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -69056,7 +69062,7 @@
         <v>29.2800006866455</v>
       </c>
       <c r="G2419" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -69082,7 +69088,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G2420" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -69108,7 +69114,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G2421" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -69134,7 +69140,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G2422" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -69160,7 +69166,7 @@
         <v>29.8199996948242</v>
       </c>
       <c r="G2423" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -69186,7 +69192,7 @@
         <v>29.3400001525879</v>
       </c>
       <c r="G2424" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -69212,7 +69218,7 @@
         <v>29.7800006866455</v>
       </c>
       <c r="G2425" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -69238,7 +69244,7 @@
         <v>29.5599994659424</v>
       </c>
       <c r="G2426" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -69264,7 +69270,7 @@
         <v>29.7199993133545</v>
       </c>
       <c r="G2427" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -69290,7 +69296,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G2428" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -69316,7 +69322,7 @@
         <v>29.2199993133545</v>
       </c>
       <c r="G2429" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -69342,7 +69348,7 @@
         <v>28.4799995422363</v>
       </c>
       <c r="G2430" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -69368,7 +69374,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G2431" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -69394,7 +69400,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G2432" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -69420,7 +69426,7 @@
         <v>28.6599998474121</v>
       </c>
       <c r="G2433" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -69446,7 +69452,7 @@
         <v>28.9599990844727</v>
       </c>
       <c r="G2434" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69472,7 +69478,7 @@
         <v>28.8400001525879</v>
       </c>
       <c r="G2435" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69498,7 +69504,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G2436" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69524,7 +69530,7 @@
         <v>28.8600006103516</v>
       </c>
       <c r="G2437" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69550,7 +69556,7 @@
         <v>28.3799991607666</v>
       </c>
       <c r="G2438" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69576,7 +69582,7 @@
         <v>29</v>
       </c>
       <c r="G2439" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69602,7 +69608,7 @@
         <v>29.2600002288818</v>
       </c>
       <c r="G2440" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69628,7 +69634,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G2441" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69654,7 +69660,7 @@
         <v>29.8400001525879</v>
       </c>
       <c r="G2442" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69680,7 +69686,7 @@
         <v>29.9200000762939</v>
       </c>
       <c r="G2443" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69706,7 +69712,7 @@
         <v>29.3600006103516</v>
       </c>
       <c r="G2444" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69732,7 +69738,7 @@
         <v>29.3600006103516</v>
       </c>
       <c r="G2445" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69758,7 +69764,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G2446" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -69784,7 +69790,7 @@
         <v>29.5</v>
       </c>
       <c r="G2447" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -69810,7 +69816,7 @@
         <v>29.7199993133545</v>
       </c>
       <c r="G2448" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -69836,7 +69842,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G2449" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -69862,7 +69868,7 @@
         <v>29.8600006103516</v>
       </c>
       <c r="G2450" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -69888,7 +69894,7 @@
         <v>30.2600002288818</v>
       </c>
       <c r="G2451" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -69914,7 +69920,7 @@
         <v>30.4799995422363</v>
       </c>
       <c r="G2452" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -69940,7 +69946,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G2453" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -69966,7 +69972,7 @@
         <v>30.4200000762939</v>
       </c>
       <c r="G2454" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -69992,7 +69998,7 @@
         <v>30.2600002288818</v>
       </c>
       <c r="G2455" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -70018,7 +70024,7 @@
         <v>30.4400005340576</v>
       </c>
       <c r="G2456" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -70044,7 +70050,7 @@
         <v>29.9400005340576</v>
       </c>
       <c r="G2457" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -70070,7 +70076,7 @@
         <v>30.2399997711182</v>
       </c>
       <c r="G2458" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -70096,7 +70102,7 @@
         <v>29.7800006866455</v>
       </c>
       <c r="G2459" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -70122,7 +70128,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G2460" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -70148,7 +70154,7 @@
         <v>29.2600002288818</v>
       </c>
       <c r="G2461" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -70174,7 +70180,7 @@
         <v>29.5400009155273</v>
       </c>
       <c r="G2462" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -70200,7 +70206,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G2463" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -70226,7 +70232,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G2464" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -70252,7 +70258,7 @@
         <v>29.3199996948242</v>
       </c>
       <c r="G2465" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -70278,7 +70284,7 @@
         <v>30.5400009155273</v>
       </c>
       <c r="G2466" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -70304,7 +70310,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G2467" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -70330,7 +70336,7 @@
         <v>30.6200008392334</v>
       </c>
       <c r="G2468" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -70356,7 +70362,7 @@
         <v>30.7600002288818</v>
       </c>
       <c r="G2469" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -70382,7 +70388,7 @@
         <v>30.2600002288818</v>
       </c>
       <c r="G2470" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -70408,7 +70414,7 @@
         <v>30.8199996948242</v>
       </c>
       <c r="G2471" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -70434,7 +70440,7 @@
         <v>30.9400005340576</v>
       </c>
       <c r="G2472" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70460,7 +70466,7 @@
         <v>30.2199993133545</v>
       </c>
       <c r="G2473" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -70486,7 +70492,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G2474" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -70512,7 +70518,7 @@
         <v>30.3199996948242</v>
       </c>
       <c r="G2475" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -70538,7 +70544,7 @@
         <v>29.7399997711182</v>
       </c>
       <c r="G2476" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -70564,7 +70570,7 @@
         <v>30.2199993133545</v>
       </c>
       <c r="G2477" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -70590,7 +70596,7 @@
         <v>30.5799999237061</v>
       </c>
       <c r="G2478" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -70616,7 +70622,7 @@
         <v>30.7800006866455</v>
       </c>
       <c r="G2479" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -70642,7 +70648,7 @@
         <v>31.3199996948242</v>
       </c>
       <c r="G2480" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -70668,7 +70674,7 @@
         <v>31.9400005340576</v>
       </c>
       <c r="G2481" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -70694,7 +70700,7 @@
         <v>32.4799995422363</v>
       </c>
       <c r="G2482" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -70720,7 +70726,7 @@
         <v>31.1599998474121</v>
       </c>
       <c r="G2483" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -70746,7 +70752,7 @@
         <v>31.0200004577637</v>
       </c>
       <c r="G2484" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -70772,7 +70778,7 @@
         <v>31.0599994659424</v>
       </c>
       <c r="G2485" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -70798,7 +70804,7 @@
         <v>30.4400005340576</v>
       </c>
       <c r="G2486" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -70824,7 +70830,7 @@
         <v>29</v>
       </c>
       <c r="G2487" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -70832,7 +70838,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6496412037</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>110717</v>
@@ -70850,9 +70856,35 @@
         <v>29.1599998474121</v>
       </c>
       <c r="G2488" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6493981481</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>166430</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>29.0599994659424</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>28.1399993896484</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>29.0599994659424</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>28.1399993896484</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1941</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DLG.MI.xlsx
+++ b/data/DLG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1944" uniqueCount="1944">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1945" uniqueCount="1945">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7391471862793</t>
+    <t xml:space="preserve">20.7391452789307</t>
   </si>
   <si>
     <t xml:space="preserve">DLG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5564193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6553955078125</t>
+    <t xml:space="preserve">20.5564212799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6553974151611</t>
   </si>
   <si>
     <t xml:space="preserve">20.1757488250732</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9777965545654</t>
+    <t xml:space="preserve">19.9777927398682</t>
   </si>
   <si>
     <t xml:space="preserve">19.7722339630127</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4905338287354</t>
+    <t xml:space="preserve">19.4905300140381</t>
   </si>
   <si>
     <t xml:space="preserve">19.8864364624023</t>
@@ -71,37 +71,37 @@
     <t xml:space="preserve">17.6328392028809</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4348888397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.526252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0542182922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8943347930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0135173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.63547706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4451389312744</t>
+    <t xml:space="preserve">17.4348907470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5262508392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0542163848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8943328857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0135154724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6354732513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4451351165771</t>
   </si>
   <si>
     <t xml:space="preserve">16.7116088867188</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8029689788818</t>
+    <t xml:space="preserve">16.8029708862305</t>
   </si>
   <si>
     <t xml:space="preserve">16.6735401153564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1329822540283</t>
+    <t xml:space="preserve">16.132984161377</t>
   </si>
   <si>
     <t xml:space="preserve">15.9654846191406</t>
@@ -110,13 +110,13 @@
     <t xml:space="preserve">15.6533355712891</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9909591674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7777805328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3335666656494</t>
+    <t xml:space="preserve">14.9909610748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7777814865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3335638046265</t>
   </si>
   <si>
     <t xml:space="preserve">14.412335395813</t>
@@ -125,106 +125,106 @@
     <t xml:space="preserve">14.7397165298462</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4553813934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2574338912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.409704208374</t>
+    <t xml:space="preserve">15.4553823471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2574319839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4097023010254</t>
   </si>
   <si>
     <t xml:space="preserve">15.7523097991943</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3868627548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9121904373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9578742980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5848083496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1253719329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1938896179199</t>
+    <t xml:space="preserve">15.3868608474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9121923446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9578723907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5848121643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1253700256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1938915252686</t>
   </si>
   <si>
     <t xml:space="preserve">16.5593376159668</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7496776580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.881742477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2193622589111</t>
+    <t xml:space="preserve">16.7496738433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.881739616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2193651199341</t>
   </si>
   <si>
     <t xml:space="preserve">15.3792486190796</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0873012542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7142419815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2878866195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8969659805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3183403015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6076574325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9274206161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9883270263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8893508911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6152658462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.356406211853</t>
+    <t xml:space="preserve">16.0872993469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.714241027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2878856658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8969650268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3183422088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6076498031616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9274196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9883279800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8893537521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6152677536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3564081192017</t>
   </si>
   <si>
     <t xml:space="preserve">15.1356163024902</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2269763946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3487939834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0442552566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2345924377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0594816207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1432294845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5493793487549</t>
+    <t xml:space="preserve">15.226978302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3487949371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0442543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2345933914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0594825744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1432275772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5493803024292</t>
   </si>
   <si>
     <t xml:space="preserve">14.7853946685791</t>
@@ -233,61 +233,61 @@
     <t xml:space="preserve">14.8234643936157</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7831649780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9779891967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1494312286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.96240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9857797622681</t>
+    <t xml:space="preserve">14.783164024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9779834747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1572275161743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1494331359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9624042510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9857816696167</t>
   </si>
   <si>
     <t xml:space="preserve">14.954607963562</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8533020019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4689407348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6715612411499</t>
+    <t xml:space="preserve">14.8533039093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4689388275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6715593338013</t>
   </si>
   <si>
     <t xml:space="preserve">16.2170639038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7572784423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0300350189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2404403686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1469249725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3495426177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5054016113281</t>
+    <t xml:space="preserve">15.7572793960571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0300312042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2404384613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1469230651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3495407104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5053997039795</t>
   </si>
   <si>
     <t xml:space="preserve">16.3105754852295</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7288856506348</t>
+    <t xml:space="preserve">17.7288875579834</t>
   </si>
   <si>
     <t xml:space="preserve">16.7937355041504</t>
@@ -296,43 +296,43 @@
     <t xml:space="preserve">17.0742835998535</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7625675201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7547702789307</t>
+    <t xml:space="preserve">16.762565612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7547760009766</t>
   </si>
   <si>
     <t xml:space="preserve">16.8482894897461</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1132469177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3002777099609</t>
+    <t xml:space="preserve">17.113245010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3002796173096</t>
   </si>
   <si>
     <t xml:space="preserve">17.7678527832031</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9081287384033</t>
+    <t xml:space="preserve">17.9081268310547</t>
   </si>
   <si>
     <t xml:space="preserve">17.9470901489258</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0639839172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4848003387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.788724899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.46142578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3367366790771</t>
+    <t xml:space="preserve">18.0639877319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4848022460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7887268066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4614238739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3367385864258</t>
   </si>
   <si>
     <t xml:space="preserve">18.2743911743164</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">18.0795726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6484508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8276882171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4536304473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8379898071289</t>
+    <t xml:space="preserve">18.6484546661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8276901245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4536323547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8379917144775</t>
   </si>
   <si>
     <t xml:space="preserve">17.3937931060791</t>
@@ -359,52 +359,52 @@
     <t xml:space="preserve">17.2535190582275</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0820789337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4951019287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9237079620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8224048614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7834396362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9315032958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6768417358398</t>
+    <t xml:space="preserve">17.0820751190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4951038360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.923713684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8224029541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7834377288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9315052032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6768455505371</t>
   </si>
   <si>
     <t xml:space="preserve">15.523491859436</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1157550811768</t>
+    <t xml:space="preserve">16.1157531738281</t>
   </si>
   <si>
     <t xml:space="preserve">16.3651275634766</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6612606048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6300849914551</t>
+    <t xml:space="preserve">16.6612567901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6300868988037</t>
   </si>
   <si>
     <t xml:space="preserve">15.8975534439087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7806615829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5468721389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7884531021118</t>
+    <t xml:space="preserve">15.7806587219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5468702316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7884511947632</t>
   </si>
   <si>
     <t xml:space="preserve">16.3729228973389</t>
@@ -422,43 +422,43 @@
     <t xml:space="preserve">16.5209865570068</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5287780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8404960632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9184246063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8716640472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8015327453613</t>
+    <t xml:space="preserve">16.5287799835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8404979705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9184226989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8716659545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8015308380127</t>
   </si>
   <si>
     <t xml:space="preserve">17.6119956970215</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2223491668701</t>
+    <t xml:space="preserve">17.2223472595215</t>
   </si>
   <si>
     <t xml:space="preserve">17.5964088439941</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4171695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6587543487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3158626556396</t>
+    <t xml:space="preserve">17.4171733856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6587524414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3158645629883</t>
   </si>
   <si>
     <t xml:space="preserve">17.323657989502</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5028953552246</t>
+    <t xml:space="preserve">17.5028915405273</t>
   </si>
   <si>
     <t xml:space="preserve">18.0561904907227</t>
@@ -467,37 +467,37 @@
     <t xml:space="preserve">18.5393524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7030048370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6640377044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.812105178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0951538085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1497077941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9003353118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1574974060059</t>
+    <t xml:space="preserve">18.7030029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6640396118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8121032714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0951519012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1497058868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9003314971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1575012207031</t>
   </si>
   <si>
     <t xml:space="preserve">17.8769550323486</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6665458679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9704704284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0328140258789</t>
+    <t xml:space="preserve">17.6665439605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9704685211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0328159332275</t>
   </si>
   <si>
     <t xml:space="preserve">17.5106887817383</t>
@@ -509,64 +509,64 @@
     <t xml:space="preserve">17.3626194000244</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4015846252441</t>
+    <t xml:space="preserve">17.4015865325928</t>
   </si>
   <si>
     <t xml:space="preserve">17.2379341125488</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4093818664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1444206237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8171195983887</t>
+    <t xml:space="preserve">17.4093780517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.144416809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8171157836914</t>
   </si>
   <si>
     <t xml:space="preserve">16.614501953125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6846389770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0197315216064</t>
+    <t xml:space="preserve">16.6846370697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0197334289551</t>
   </si>
   <si>
     <t xml:space="preserve">17.128833770752</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2691078186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9963550567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4405517578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4639301300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.832706451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8249130249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9028377532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7859477996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7469806671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2769012451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2457275390625</t>
+    <t xml:space="preserve">17.2691059112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9963531494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4405498504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4639263153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8327026367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8249092102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9028434753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.785945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7469825744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2768974304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2457294464111</t>
   </si>
   <si>
     <t xml:space="preserve">17.0509052276611</t>
@@ -575,100 +575,100 @@
     <t xml:space="preserve">17.0976638793945</t>
   </si>
   <si>
-    <t xml:space="preserve">16.957389831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2301445007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2067623138428</t>
+    <t xml:space="preserve">16.9573879241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2301464080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2067642211914</t>
   </si>
   <si>
     <t xml:space="preserve">17.4327583312988</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2846927642822</t>
+    <t xml:space="preserve">17.2846965789795</t>
   </si>
   <si>
     <t xml:space="preserve">17.0664901733398</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9520998001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9832744598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.256031036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3339576721191</t>
+    <t xml:space="preserve">15.9521026611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9832773208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2560272216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3339557647705</t>
   </si>
   <si>
     <t xml:space="preserve">15.9988603591919</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4066009521484</t>
+    <t xml:space="preserve">15.4065999984741</t>
   </si>
   <si>
     <t xml:space="preserve">15.313084602356</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1182613372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5131931304932</t>
+    <t xml:space="preserve">15.1182622909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5131950378418</t>
   </si>
   <si>
     <t xml:space="preserve">16.0923748016357</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9131393432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1780967712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7158126831055</t>
+    <t xml:space="preserve">15.9131383895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1780986785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7158107757568</t>
   </si>
   <si>
     <t xml:space="preserve">17.0586986541748</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4664344787598</t>
+    <t xml:space="preserve">16.4664325714111</t>
   </si>
   <si>
     <t xml:space="preserve">16.2248554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9754867553711</t>
+    <t xml:space="preserve">15.9754791259766</t>
   </si>
   <si>
     <t xml:space="preserve">16.7080173492432</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4976100921631</t>
+    <t xml:space="preserve">16.4976062774658</t>
   </si>
   <si>
     <t xml:space="preserve">16.6924304962158</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5599498748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7703590393066</t>
+    <t xml:space="preserve">16.5599517822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7703609466553</t>
   </si>
   <si>
     <t xml:space="preserve">16.8638744354248</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0275287628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4561386108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4483432769775</t>
+    <t xml:space="preserve">17.0275249481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4561367034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4483413696289</t>
   </si>
   <si>
     <t xml:space="preserve">17.8847484588623</t>
@@ -680,13 +680,13 @@
     <t xml:space="preserve">18.2354297637939</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0172290802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8457813262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9626750946045</t>
+    <t xml:space="preserve">18.0172271728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8457832336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9626789093018</t>
   </si>
   <si>
     <t xml:space="preserve">17.869161605835</t>
@@ -695,10 +695,10 @@
     <t xml:space="preserve">17.6353721618652</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7912349700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5808200836182</t>
+    <t xml:space="preserve">17.7912311553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5808277130127</t>
   </si>
   <si>
     <t xml:space="preserve">17.6509590148926</t>
@@ -707,16 +707,16 @@
     <t xml:space="preserve">18.1107406616211</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9782600402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3133544921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2042541503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.469217300415</t>
+    <t xml:space="preserve">17.9782638549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3133563995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2042579650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4692153930664</t>
   </si>
   <si>
     <t xml:space="preserve">19.0848579406738</t>
@@ -728,37 +728,37 @@
     <t xml:space="preserve">19.2952671051025</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4667053222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2485103607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3186454772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0614757537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4199504852295</t>
+    <t xml:space="preserve">19.4667091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2485084533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3186435699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0614776611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4199523925781</t>
   </si>
   <si>
     <t xml:space="preserve">19.2407169342041</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0926475524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4511241912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8588619232178</t>
+    <t xml:space="preserve">19.0926494598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4511222839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8588638305664</t>
   </si>
   <si>
     <t xml:space="preserve">18.640661239624</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9056205749512</t>
+    <t xml:space="preserve">18.9056224822998</t>
   </si>
   <si>
     <t xml:space="preserve">19.2329216003418</t>
@@ -770,16 +770,16 @@
     <t xml:space="preserve">20.1914501190186</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9888362884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.12131690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9732494354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9551544189453</t>
+    <t xml:space="preserve">19.9888343811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1213130950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9732513427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9551582336426</t>
   </si>
   <si>
     <t xml:space="preserve">20.6278514862061</t>
@@ -788,16 +788,16 @@
     <t xml:space="preserve">21.2201156616211</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0408782958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.79150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7447490692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.861644744873</t>
+    <t xml:space="preserve">21.0408802032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7915077209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7447452545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8616428375244</t>
   </si>
   <si>
     <t xml:space="preserve">21.2434940338135</t>
@@ -806,31 +806,31 @@
     <t xml:space="preserve">20.9006061553955</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0330867767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9785385131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6721076965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4149398803711</t>
+    <t xml:space="preserve">21.033088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9785346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6721038818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4149360656738</t>
   </si>
   <si>
     <t xml:space="preserve">21.3136329650879</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1967372894287</t>
+    <t xml:space="preserve">21.1967391967773</t>
   </si>
   <si>
     <t xml:space="preserve">21.4227333068848</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5785884857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1884746551514</t>
+    <t xml:space="preserve">21.578592300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1884708404541</t>
   </si>
   <si>
     <t xml:space="preserve">22.1002025604248</t>
@@ -839,13 +839,13 @@
     <t xml:space="preserve">21.947732925415</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0279769897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9878520965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8273582458496</t>
+    <t xml:space="preserve">22.0279788970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9878540039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8273601531982</t>
   </si>
   <si>
     <t xml:space="preserve">22.3489685058594</t>
@@ -860,34 +860,34 @@
     <t xml:space="preserve">23.3199653625488</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2878684997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8786029815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0310726165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4483623504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0230464935303</t>
+    <t xml:space="preserve">23.2878665924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8786067962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.031078338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4483585357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0230484008789</t>
   </si>
   <si>
     <t xml:space="preserve">22.9026775360107</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6218128204346</t>
+    <t xml:space="preserve">22.6218090057373</t>
   </si>
   <si>
     <t xml:space="preserve">22.5014400482178</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2557678222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8434085845947</t>
+    <t xml:space="preserve">23.255765914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8434066772461</t>
   </si>
   <si>
     <t xml:space="preserve">22.0600776672363</t>
@@ -899,19 +899,19 @@
     <t xml:space="preserve">22.7341556549072</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9267520904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2316913604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1434211730957</t>
+    <t xml:space="preserve">22.9267501831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2316951751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1434192657471</t>
   </si>
   <si>
     <t xml:space="preserve">23.1674957275391</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6570053100586</t>
+    <t xml:space="preserve">23.65700340271</t>
   </si>
   <si>
     <t xml:space="preserve">23.7693500518799</t>
@@ -920,28 +920,28 @@
     <t xml:space="preserve">23.6730556488037</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8495960235596</t>
+    <t xml:space="preserve">23.8495998382568</t>
   </si>
   <si>
     <t xml:space="preserve">23.7613296508789</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4002151489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2958927154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4323101043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.705150604248</t>
+    <t xml:space="preserve">23.4002113342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2958908081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4323139190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7051563262939</t>
   </si>
   <si>
     <t xml:space="preserve">23.0069980621338</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8304538726807</t>
+    <t xml:space="preserve">22.8304557800293</t>
   </si>
   <si>
     <t xml:space="preserve">22.7903308868408</t>
@@ -950,49 +950,49 @@
     <t xml:space="preserve">23.0631713867188</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8255271911621</t>
+    <t xml:space="preserve">23.8255252838135</t>
   </si>
   <si>
     <t xml:space="preserve">23.3921852111816</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2637920379639</t>
+    <t xml:space="preserve">23.2637939453125</t>
   </si>
   <si>
     <t xml:space="preserve">23.2718162536621</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1915664672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9989757537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9076061248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0199527740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0761280059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.554515838623</t>
+    <t xml:space="preserve">23.1915702819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9989738464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9076042175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0199546813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0761260986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5545139312744</t>
   </si>
   <si>
     <t xml:space="preserve">21.4742679595947</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6267414093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.771183013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.739086151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8674812316895</t>
+    <t xml:space="preserve">21.6267433166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7711868286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7390880584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8674831390381</t>
   </si>
   <si>
     <t xml:space="preserve">21.8594589233398</t>
@@ -1001,22 +1001,22 @@
     <t xml:space="preserve">22.5255146026611</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7421817779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3730411529541</t>
+    <t xml:space="preserve">22.7421798706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3730430603027</t>
   </si>
   <si>
     <t xml:space="preserve">22.7181053161621</t>
   </si>
   <si>
-    <t xml:space="preserve">22.862548828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7100811004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5335369110107</t>
+    <t xml:space="preserve">22.8625564575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7100849151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.533540725708</t>
   </si>
   <si>
     <t xml:space="preserve">22.6539096832275</t>
@@ -1025,19 +1025,19 @@
     <t xml:space="preserve">22.292797088623</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7551383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2415504455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9927806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.944637298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.073034286499</t>
+    <t xml:space="preserve">21.7551345825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.241548538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9927864074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9446334838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0730323791504</t>
   </si>
   <si>
     <t xml:space="preserve">21.0489559173584</t>
@@ -1055,16 +1055,16 @@
     <t xml:space="preserve">20.8804359436035</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8643856048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7119159698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5754947662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5995712280273</t>
+    <t xml:space="preserve">20.864387512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.575496673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5995693206787</t>
   </si>
   <si>
     <t xml:space="preserve">20.6477184295654</t>
@@ -1076,13 +1076,13 @@
     <t xml:space="preserve">20.5915431976318</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3508033752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3427734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2866039276123</t>
+    <t xml:space="preserve">20.3508014678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3427772521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2866058349609</t>
   </si>
   <si>
     <t xml:space="preserve">20.7440166473389</t>
@@ -1091,34 +1091,34 @@
     <t xml:space="preserve">20.6717929840088</t>
   </si>
   <si>
-    <t xml:space="preserve">20.495246887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.735990524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2174797058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0168609619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3538970947266</t>
+    <t xml:space="preserve">20.4952526092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7359886169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2174758911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0168571472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3538990020752</t>
   </si>
   <si>
     <t xml:space="preserve">21.2335243225098</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9045085906982</t>
+    <t xml:space="preserve">20.9045104980469</t>
   </si>
   <si>
     <t xml:space="preserve">20.5594463348389</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5353698730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4711742401123</t>
+    <t xml:space="preserve">20.5353717803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4711761474609</t>
   </si>
   <si>
     <t xml:space="preserve">20.7520408630371</t>
@@ -1127,31 +1127,31 @@
     <t xml:space="preserve">21.3779697418213</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0650062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2255001068115</t>
+    <t xml:space="preserve">21.0650081634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2255039215088</t>
   </si>
   <si>
     <t xml:space="preserve">21.3699474334717</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9156303405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4582214355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8032855987549</t>
+    <t xml:space="preserve">21.9156284332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4582195281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8032836914062</t>
   </si>
   <si>
     <t xml:space="preserve">21.795259475708</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3088455200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1403255462646</t>
+    <t xml:space="preserve">22.3088436126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.140323638916</t>
   </si>
   <si>
     <t xml:space="preserve">22.2285976409912</t>
@@ -1160,16 +1160,16 @@
     <t xml:space="preserve">22.2045230865479</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1483478546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6940326690674</t>
+    <t xml:space="preserve">22.1483497619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.694034576416</t>
   </si>
   <si>
     <t xml:space="preserve">22.0921764373779</t>
   </si>
   <si>
-    <t xml:space="preserve">22.108226776123</t>
+    <t xml:space="preserve">22.1082229614258</t>
   </si>
   <si>
     <t xml:space="preserve">22.164400100708</t>
@@ -1178,49 +1178,49 @@
     <t xml:space="preserve">22.7742805480957</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7662563323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5897121429443</t>
+    <t xml:space="preserve">22.7662582397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5897102355957</t>
   </si>
   <si>
     <t xml:space="preserve">22.5415630340576</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4131660461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.517484664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1563720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8353824615479</t>
+    <t xml:space="preserve">22.4131641387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5174884796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1563739776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8353843688965</t>
   </si>
   <si>
     <t xml:space="preserve">22.5495872497559</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2526741027832</t>
+    <t xml:space="preserve">22.2526683807373</t>
   </si>
   <si>
     <t xml:space="preserve">22.2125473022461</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2594356536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9335136413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8612937927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6927738189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.620548248291</t>
+    <t xml:space="preserve">19.2594337463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9335155487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.861291885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6927700042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6205501556396</t>
   </si>
   <si>
     <t xml:space="preserve">19.5403022766113</t>
@@ -1229,34 +1229,34 @@
     <t xml:space="preserve">19.492151260376</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4279537200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7409191131592</t>
+    <t xml:space="preserve">19.4279556274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7409210205078</t>
   </si>
   <si>
     <t xml:space="preserve">19.676721572876</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8051166534424</t>
+    <t xml:space="preserve">19.805118560791</t>
   </si>
   <si>
     <t xml:space="preserve">19.4199314117432</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7569713592529</t>
+    <t xml:space="preserve">19.7569694519043</t>
   </si>
   <si>
     <t xml:space="preserve">19.6606731414795</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1421585083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.230432510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4069728851318</t>
+    <t xml:space="preserve">20.142162322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2304286956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4069747924805</t>
   </si>
   <si>
     <t xml:space="preserve">20.4792003631592</t>
@@ -1274,10 +1274,10 @@
     <t xml:space="preserve">19.9254894256592</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9366111755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0971069335938</t>
+    <t xml:space="preserve">20.9366130828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0971050262451</t>
   </si>
   <si>
     <t xml:space="preserve">20.8162384033203</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">20.3989524841309</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6878414154053</t>
+    <t xml:space="preserve">20.6878433227539</t>
   </si>
   <si>
     <t xml:space="preserve">20.4390754699707</t>
@@ -1298,61 +1298,61 @@
     <t xml:space="preserve">20.4631481170654</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5433959960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4100704193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0088329315186</t>
+    <t xml:space="preserve">20.5433940887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4100723266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0088348388672</t>
   </si>
   <si>
     <t xml:space="preserve">21.6508121490479</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1372318267822</t>
+    <t xml:space="preserve">21.1372299194336</t>
   </si>
   <si>
     <t xml:space="preserve">21.2816753387451</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5063667297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4421710968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9606838226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.345874786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0890808105469</t>
+    <t xml:space="preserve">21.5063705444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4421691894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9606876373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3458728790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0890769958496</t>
   </si>
   <si>
     <t xml:space="preserve">21.6989631652832</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8113079071045</t>
+    <t xml:space="preserve">21.8113117218018</t>
   </si>
   <si>
     <t xml:space="preserve">21.7792110443115</t>
   </si>
   <si>
-    <t xml:space="preserve">21.394021987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7471103668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2495727539062</t>
+    <t xml:space="preserve">21.3940238952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7471084594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2495746612549</t>
   </si>
   <si>
     <t xml:space="preserve">19.5322761535645</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3236331939697</t>
+    <t xml:space="preserve">19.3236312866211</t>
   </si>
   <si>
     <t xml:space="preserve">19.5001773834229</t>
@@ -1364,22 +1364,22 @@
     <t xml:space="preserve">20.0458602905273</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0940113067627</t>
+    <t xml:space="preserve">20.0940132141113</t>
   </si>
   <si>
     <t xml:space="preserve">19.7248687744141</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7088222503662</t>
+    <t xml:space="preserve">19.7088241577148</t>
   </si>
   <si>
     <t xml:space="preserve">19.403881072998</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4841289520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1631374359131</t>
+    <t xml:space="preserve">19.4841270446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1631355285645</t>
   </si>
   <si>
     <t xml:space="preserve">18.8260955810547</t>
@@ -1391,40 +1391,40 @@
     <t xml:space="preserve">18.0075721740723</t>
   </si>
   <si>
-    <t xml:space="preserve">18.585355758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7137489318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.997709274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1261100769043</t>
+    <t xml:space="preserve">18.5853519439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.713752746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9977130889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1261081695557</t>
   </si>
   <si>
     <t xml:space="preserve">20.7199401855469</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1903076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7730197906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8372173309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8211708068848</t>
+    <t xml:space="preserve">20.1903038024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7730178833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.837215423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8211688995361</t>
   </si>
   <si>
     <t xml:space="preserve">19.4359798431396</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1310386657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3557300567627</t>
+    <t xml:space="preserve">19.1310367584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3557319641113</t>
   </si>
   <si>
     <t xml:space="preserve">19.5483264923096</t>
@@ -1433,13 +1433,13 @@
     <t xml:space="preserve">19.9174633026123</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5804271697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0186920166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0026416778564</t>
+    <t xml:space="preserve">19.5804252624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0186901092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0026435852051</t>
   </si>
   <si>
     <t xml:space="preserve">18.8421459197998</t>
@@ -1448,34 +1448,34 @@
     <t xml:space="preserve">19.0828914642334</t>
   </si>
   <si>
-    <t xml:space="preserve">19.885368347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5112953186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1582107543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8936653137207</t>
+    <t xml:space="preserve">19.8853645324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5112972259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1582050323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8936672210693</t>
   </si>
   <si>
     <t xml:space="preserve">20.6596565246582</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5760803222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6763706207275</t>
+    <t xml:space="preserve">20.5760822296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6763687133789</t>
   </si>
   <si>
     <t xml:space="preserve">20.7265148162842</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8435192108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8268051147461</t>
+    <t xml:space="preserve">20.8435211181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8268032073975</t>
   </si>
   <si>
     <t xml:space="preserve">21.4954032897949</t>
@@ -1496,25 +1496,25 @@
     <t xml:space="preserve">20.9772396087646</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7766590118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.475793838501</t>
+    <t xml:space="preserve">20.7766609191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4757919311523</t>
   </si>
   <si>
     <t xml:space="preserve">20.6429405212402</t>
   </si>
   <si>
-    <t xml:space="preserve">20.525936126709</t>
+    <t xml:space="preserve">20.5259342193604</t>
   </si>
   <si>
     <t xml:space="preserve">20.2584972381592</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1247749328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1916370391846</t>
+    <t xml:space="preserve">20.1247806549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1916351318359</t>
   </si>
   <si>
     <t xml:space="preserve">19.9241981506348</t>
@@ -1523,28 +1523,28 @@
     <t xml:space="preserve">19.5063247680664</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1582088470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2417812347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8769512176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7933731079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9939556121826</t>
+    <t xml:space="preserve">20.1582069396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2417850494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8769493103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7933750152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9939575195312</t>
   </si>
   <si>
     <t xml:space="preserve">20.8100910186768</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5927982330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6930866241455</t>
+    <t xml:space="preserve">20.5927963256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6930847167969</t>
   </si>
   <si>
     <t xml:space="preserve">20.3420734405518</t>
@@ -1553,13 +1553,13 @@
     <t xml:space="preserve">20.4925060272217</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5593681335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7570514678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8740558624268</t>
+    <t xml:space="preserve">20.5593662261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7570495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8740577697754</t>
   </si>
   <si>
     <t xml:space="preserve">20.1414928436279</t>
@@ -1568,16 +1568,16 @@
     <t xml:space="preserve">20.2919292449951</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0244903564453</t>
+    <t xml:space="preserve">20.0244884490967</t>
   </si>
   <si>
     <t xml:space="preserve">19.9409160614014</t>
   </si>
   <si>
-    <t xml:space="preserve">20.108060836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2752132415771</t>
+    <t xml:space="preserve">20.1080627441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2752113342285</t>
   </si>
   <si>
     <t xml:space="preserve">20.3922176361084</t>
@@ -1586,43 +1586,43 @@
     <t xml:space="preserve">20.057918548584</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4256477355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.074634552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8239078521729</t>
+    <t xml:space="preserve">20.4256458282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0746364593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8239116668701</t>
   </si>
   <si>
     <t xml:space="preserve">19.6901893615723</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0273838043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2475776672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3144340515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1000385284424</t>
+    <t xml:space="preserve">21.0273818969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2475738525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3144378662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1000347137451</t>
   </si>
   <si>
     <t xml:space="preserve">23.200325012207</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2671852111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5847682952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5346240997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2170391082764</t>
+    <t xml:space="preserve">23.267183303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5847702026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5346221923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.217041015625</t>
   </si>
   <si>
     <t xml:space="preserve">22.8660259246826</t>
@@ -1631,43 +1631,43 @@
     <t xml:space="preserve">22.7991695404053</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8325977325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5484390258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6153030395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9328861236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1167507171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1501789093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2504730224609</t>
+    <t xml:space="preserve">22.8325996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5484447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6153049468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9328880310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1167469024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1501808166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2504711151123</t>
   </si>
   <si>
     <t xml:space="preserve">23.4009037017822</t>
   </si>
   <si>
-    <t xml:space="preserve">23.618200302124</t>
+    <t xml:space="preserve">23.6181983947754</t>
   </si>
   <si>
     <t xml:space="preserve">23.5011940002441</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3841915130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2839031219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0833206176758</t>
+    <t xml:space="preserve">23.3841876983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2839012145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0833225250244</t>
   </si>
   <si>
     <t xml:space="preserve">22.8994560241699</t>
@@ -1682,25 +1682,25 @@
     <t xml:space="preserve">22.331148147583</t>
   </si>
   <si>
-    <t xml:space="preserve">22.815881729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5317249298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1334648132324</t>
+    <t xml:space="preserve">22.8158798217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5317268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1334686279297</t>
   </si>
   <si>
     <t xml:space="preserve">22.9663162231445</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6850605010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3006153106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4343338012695</t>
+    <t xml:space="preserve">23.68505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3006172180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4343376159668</t>
   </si>
   <si>
     <t xml:space="preserve">22.9997463226318</t>
@@ -1709,16 +1709,16 @@
     <t xml:space="preserve">22.8493137359619</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9496002197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7628421783447</t>
+    <t xml:space="preserve">22.9496021270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7628402709961</t>
   </si>
   <si>
     <t xml:space="preserve">21.461971282959</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0440998077393</t>
+    <t xml:space="preserve">21.0441017150879</t>
   </si>
   <si>
     <t xml:space="preserve">20.7098007202148</t>
@@ -1727,7 +1727,7 @@
     <t xml:space="preserve">20.91037940979</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6625518798828</t>
+    <t xml:space="preserve">21.6625499725342</t>
   </si>
   <si>
     <t xml:space="preserve">21.2279624938965</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">21.3616809844971</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5121192932129</t>
+    <t xml:space="preserve">21.5121173858643</t>
   </si>
   <si>
     <t xml:space="preserve">20.9605255126953</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">18.9547348022461</t>
   </si>
   <si>
-    <t xml:space="preserve">19.556468963623</t>
+    <t xml:space="preserve">19.5564708709717</t>
   </si>
   <si>
     <t xml:space="preserve">19.0550212860107</t>
@@ -1769,61 +1769,61 @@
     <t xml:space="preserve">19.3893222808838</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2555999755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3057460784912</t>
+    <t xml:space="preserve">19.2556018829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3057479858398</t>
   </si>
   <si>
     <t xml:space="preserve">19.3726062774658</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8042964935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6037178039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6872959136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6705799102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7040061950684</t>
+    <t xml:space="preserve">18.8043003082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6037197113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.687292098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.670581817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.704008102417</t>
   </si>
   <si>
     <t xml:space="preserve">18.8878746032715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2221698760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6734771728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6567573547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8907661437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0913486480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8406219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5898990631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0884532928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7737655639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.640043258667</t>
+    <t xml:space="preserve">19.2221717834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6734752655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.656759262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8907680511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0913505554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8406257629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.589900970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.088451385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7737636566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6400470733643</t>
   </si>
   <si>
     <t xml:space="preserve">19.4561824798584</t>
@@ -1835,34 +1835,34 @@
     <t xml:space="preserve">19.3391780853271</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5201454162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5506782531738</t>
+    <t xml:space="preserve">18.5201435089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5506801605225</t>
   </si>
   <si>
     <t xml:space="preserve">18.0019836425781</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9016933441162</t>
+    <t xml:space="preserve">17.9016952514648</t>
   </si>
   <si>
     <t xml:space="preserve">18.4699993133545</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2359924316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4365692138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0412044525146</t>
+    <t xml:space="preserve">18.2359886169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4365711212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0412006378174</t>
   </si>
   <si>
     <t xml:space="preserve">20.3086414337158</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9910583496094</t>
+    <t xml:space="preserve">19.991060256958</t>
   </si>
   <si>
     <t xml:space="preserve">20.3253555297852</t>
@@ -1874,79 +1874,79 @@
     <t xml:space="preserve">18.2694206237793</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2192783355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4198570251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6538619995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2527084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3529968261719</t>
+    <t xml:space="preserve">18.219274520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4198551177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.653865814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.25270652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3529930114746</t>
   </si>
   <si>
     <t xml:space="preserve">18.5368595123291</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7541561126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6371479034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1553134918213</t>
+    <t xml:space="preserve">18.7541522979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6371459960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1553115844727</t>
   </si>
   <si>
     <t xml:space="preserve">19.4060363769531</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2723178863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9714469909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3558940887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0215930938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3224601745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7403373718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.174919128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7875823974609</t>
+    <t xml:space="preserve">19.2723159790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9714488983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3558902740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0215911865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3224620819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7403354644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1749248504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7875843048096</t>
   </si>
   <si>
     <t xml:space="preserve">18.9380168914795</t>
   </si>
   <si>
-    <t xml:space="preserve">20.007776260376</t>
+    <t xml:space="preserve">20.0077743530273</t>
   </si>
   <si>
     <t xml:space="preserve">20.2250690460205</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5789794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1443901062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2054576873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0354099273682</t>
+    <t xml:space="preserve">21.5789775848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1443881988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2054557800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0354118347168</t>
   </si>
   <si>
     <t xml:space="preserve">17.6509704589844</t>
@@ -1955,67 +1955,67 @@
     <t xml:space="preserve">17.4336738586426</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5841121673584</t>
+    <t xml:space="preserve">17.5841064453125</t>
   </si>
   <si>
     <t xml:space="preserve">17.1328048706055</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5477828979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1716976165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9961881637573</t>
+    <t xml:space="preserve">16.5477809906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1716957092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.996190071106</t>
   </si>
   <si>
     <t xml:space="preserve">16.3221302032471</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8791856765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7939519882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.768383026123</t>
+    <t xml:space="preserve">15.879186630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7939529418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7683820724487</t>
   </si>
   <si>
     <t xml:space="preserve">15.7769031524658</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3081140518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4018745422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4359674453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5382499694824</t>
+    <t xml:space="preserve">15.3081130981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4018716812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4359655380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5382471084595</t>
   </si>
   <si>
     <t xml:space="preserve">15.163215637207</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3336839675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0524091720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1717405319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.350733757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5552940368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6405277252197</t>
+    <t xml:space="preserve">15.333683013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0524101257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1717367172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3507328033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5552930831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6405305862427</t>
   </si>
   <si>
     <t xml:space="preserve">15.6490507125854</t>
@@ -2024,19 +2024,19 @@
     <t xml:space="preserve">15.6320056915283</t>
   </si>
   <si>
-    <t xml:space="preserve">15.580864906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4103937149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0609359741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8904666900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9842224121094</t>
+    <t xml:space="preserve">15.5808658599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4103965759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0609340667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8904638290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9842233657837</t>
   </si>
   <si>
     <t xml:space="preserve">15.0438852310181</t>
@@ -2048,64 +2048,64 @@
     <t xml:space="preserve">15.4274425506592</t>
   </si>
   <si>
-    <t xml:space="preserve">15.282543182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0865039825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1120729446411</t>
+    <t xml:space="preserve">15.2825441360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0865049362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1120738983154</t>
   </si>
   <si>
     <t xml:space="preserve">15.1546936035156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3251600265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3592538833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9671745300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7455673217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6091928482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6518087387085</t>
+    <t xml:space="preserve">15.325159072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3592557907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9671754837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7455644607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6091899871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6518077850342</t>
   </si>
   <si>
     <t xml:space="preserve">14.5154323577881</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7114734649658</t>
+    <t xml:space="preserve">14.7114725112915</t>
   </si>
   <si>
     <t xml:space="preserve">14.6347608566284</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5410032272339</t>
+    <t xml:space="preserve">14.5410041809082</t>
   </si>
   <si>
     <t xml:space="preserve">14.3534889221191</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3449649810791</t>
+    <t xml:space="preserve">14.3449630737305</t>
   </si>
   <si>
     <t xml:space="preserve">14.447247505188</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4387216567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7540893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4642915725708</t>
+    <t xml:space="preserve">14.4387235641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7540903091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4642934799194</t>
   </si>
   <si>
     <t xml:space="preserve">14.4813385009766</t>
@@ -2114,55 +2114,55 @@
     <t xml:space="preserve">14.3620109558105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2484483718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4956283569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0268411636353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0012693405151</t>
+    <t xml:space="preserve">15.2484493255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4956293106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0268392562866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0012731552124</t>
   </si>
   <si>
     <t xml:space="preserve">14.6859016418457</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5324802398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9784555435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4046277999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0353651046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1376457214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8307991027832</t>
+    <t xml:space="preserve">14.5324783325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9784545898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4046268463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0353622436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1376447677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8308019638062</t>
   </si>
   <si>
     <t xml:space="preserve">14.9586524963379</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2399263381958</t>
+    <t xml:space="preserve">15.2399272918701</t>
   </si>
   <si>
     <t xml:space="preserve">15.8109979629517</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4843482971191</t>
+    <t xml:space="preserve">16.4843502044678</t>
   </si>
   <si>
     <t xml:space="preserve">17.0468978881836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7911968231201</t>
+    <t xml:space="preserve">16.7911949157715</t>
   </si>
   <si>
     <t xml:space="preserve">16.5269680023193</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">17.0128021240234</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5781116485596</t>
+    <t xml:space="preserve">16.5781097412109</t>
   </si>
   <si>
     <t xml:space="preserve">16.3138809204102</t>
@@ -2180,34 +2180,34 @@
     <t xml:space="preserve">16.2371692657471</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9303255081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.921802520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3933477401733</t>
+    <t xml:space="preserve">15.9303274154663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9218053817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3933486938477</t>
   </si>
   <si>
     <t xml:space="preserve">14.9416074752808</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5239553451538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9330825805664</t>
+    <t xml:space="preserve">14.5239582061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9330816268921</t>
   </si>
   <si>
     <t xml:space="preserve">14.6603317260742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2512054443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1318788528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.617714881897</t>
+    <t xml:space="preserve">14.2512044906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1318769454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6177167892456</t>
   </si>
   <si>
     <t xml:space="preserve">14.4557676315308</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">14.5750970840454</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7370443344116</t>
+    <t xml:space="preserve">14.7370452880859</t>
   </si>
   <si>
     <t xml:space="preserve">14.7796602249146</t>
@@ -2228,40 +2228,40 @@
     <t xml:space="preserve">14.8393249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8478479385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6688566207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2341594696045</t>
+    <t xml:space="preserve">14.8478507995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6688537597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2341623306274</t>
   </si>
   <si>
     <t xml:space="preserve">14.1404027938843</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0636901855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8222770690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.626238822937</t>
+    <t xml:space="preserve">14.0636920928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8222780227661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6262369155884</t>
   </si>
   <si>
     <t xml:space="preserve">15.0183172225952</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1291217803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2058353424072</t>
+    <t xml:space="preserve">15.1291227340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2058334350586</t>
   </si>
   <si>
     <t xml:space="preserve">15.5467691421509</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8195219039917</t>
+    <t xml:space="preserve">15.8195199966431</t>
   </si>
   <si>
     <t xml:space="preserve">16.0326061248779</t>
@@ -2270,13 +2270,13 @@
     <t xml:space="preserve">16.4502544403076</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4928760528564</t>
+    <t xml:space="preserve">16.4928741455078</t>
   </si>
   <si>
     <t xml:space="preserve">16.0155620574951</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1519336700439</t>
+    <t xml:space="preserve">16.1519374847412</t>
   </si>
   <si>
     <t xml:space="preserve">16.2030773162842</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">16.0752258300781</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8962306976318</t>
+    <t xml:space="preserve">15.8962326049805</t>
   </si>
   <si>
     <t xml:space="preserve">16.2883110046387</t>
@@ -2297,7 +2297,7 @@
     <t xml:space="preserve">16.2627410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1263656616211</t>
+    <t xml:space="preserve">16.1263675689697</t>
   </si>
   <si>
     <t xml:space="preserve">16.1178417205811</t>
@@ -2306,31 +2306,31 @@
     <t xml:space="preserve">16.1945533752441</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2286491394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1689796447754</t>
+    <t xml:space="preserve">16.2286472320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.168981552124</t>
   </si>
   <si>
     <t xml:space="preserve">16.0667018890381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2797870635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.109317779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7087173461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6746225357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9729423522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7428102493286</t>
+    <t xml:space="preserve">16.2797889709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1093158721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7087144851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6746215820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9729433059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7428112030029</t>
   </si>
   <si>
     <t xml:space="preserve">15.3422088623047</t>
@@ -2339,73 +2339,73 @@
     <t xml:space="preserve">15.2910690307617</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1035509109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5665740966797</t>
+    <t xml:space="preserve">15.103551864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5665760040283</t>
   </si>
   <si>
     <t xml:space="preserve">14.2853012084961</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2426834106445</t>
+    <t xml:space="preserve">14.2426805496216</t>
   </si>
   <si>
     <t xml:space="preserve">13.5949010848999</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7057065963745</t>
+    <t xml:space="preserve">13.7057056427002</t>
   </si>
   <si>
     <t xml:space="preserve">14.6944274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5069093704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0694599151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4615354537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4444885253906</t>
+    <t xml:space="preserve">14.506911277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0694580078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4615364074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4444894790649</t>
   </si>
   <si>
     <t xml:space="preserve">15.4700603485107</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6149578094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2740211486816</t>
+    <t xml:space="preserve">15.6149597167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2740201950073</t>
   </si>
   <si>
     <t xml:space="preserve">15.2995910644531</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7142305374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.381814956665</t>
+    <t xml:space="preserve">13.7142286300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3818140029907</t>
   </si>
   <si>
     <t xml:space="preserve">13.5522832870483</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1772527694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2965803146362</t>
+    <t xml:space="preserve">13.1772518157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2965812683105</t>
   </si>
   <si>
     <t xml:space="preserve">13.2624855041504</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0323524475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7596025466919</t>
+    <t xml:space="preserve">13.0323534011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7596044540405</t>
   </si>
   <si>
     <t xml:space="preserve">12.6232280731201</t>
@@ -2414,25 +2414,25 @@
     <t xml:space="preserve">12.3590021133423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6600770950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1912870407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8333024978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74230289459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6543111801147</t>
+    <t xml:space="preserve">11.6600780487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1912879943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8333044052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74230194091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6543121337891</t>
   </si>
   <si>
     <t xml:space="preserve">11.6430311203003</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8220243453979</t>
+    <t xml:space="preserve">11.8220252990723</t>
   </si>
   <si>
     <t xml:space="preserve">11.6686010360718</t>
@@ -2441,34 +2441,34 @@
     <t xml:space="preserve">12.0351104736328</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3306732177734</t>
+    <t xml:space="preserve">13.3306751251221</t>
   </si>
   <si>
     <t xml:space="preserve">13.722752571106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2767772674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0749711990356</t>
+    <t xml:space="preserve">14.2767763137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0749702453613</t>
   </si>
   <si>
     <t xml:space="preserve">13.5011434555054</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4500026702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9897356033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0834941864014</t>
+    <t xml:space="preserve">13.4500017166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9897375106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0834951400757</t>
   </si>
   <si>
     <t xml:space="preserve">13.1175880432129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4953765869141</t>
+    <t xml:space="preserve">12.4953756332397</t>
   </si>
   <si>
     <t xml:space="preserve">13.023829460144</t>
@@ -2489,25 +2489,25 @@
     <t xml:space="preserve">12.6999387741089</t>
   </si>
   <si>
-    <t xml:space="preserve">12.904501914978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0664463043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2113466262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3988609313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.313627243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8079872131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8932218551636</t>
+    <t xml:space="preserve">12.9045028686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0664482116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2113456726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3988618850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3136262893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8079891204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8932209014893</t>
   </si>
   <si>
     <t xml:space="preserve">13.9358386993408</t>
@@ -2516,7 +2516,7 @@
     <t xml:space="preserve">14.0551662445068</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8846988677979</t>
+    <t xml:space="preserve">13.8846979141235</t>
   </si>
   <si>
     <t xml:space="preserve">14.4898633956909</t>
@@ -2525,31 +2525,31 @@
     <t xml:space="preserve">14.7029495239258</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2000637054443</t>
+    <t xml:space="preserve">14.2000665664673</t>
   </si>
   <si>
     <t xml:space="preserve">14.4983863830566</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4131526947021</t>
+    <t xml:space="preserve">14.4131507873535</t>
   </si>
   <si>
     <t xml:space="preserve">15.1205987930298</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7711362838745</t>
+    <t xml:space="preserve">14.7711372375488</t>
   </si>
   <si>
     <t xml:space="preserve">14.856369972229</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4189195632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9388513565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7513332366943</t>
+    <t xml:space="preserve">15.4189186096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9388484954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7513341903687</t>
   </si>
   <si>
     <t xml:space="preserve">16.6207237243652</t>
@@ -2558,22 +2558,22 @@
     <t xml:space="preserve">16.4161624908447</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2456932067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5440139770508</t>
+    <t xml:space="preserve">16.2456912994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5440158843994</t>
   </si>
   <si>
     <t xml:space="preserve">16.7826709747314</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3707904815674</t>
+    <t xml:space="preserve">17.3707866668701</t>
   </si>
   <si>
     <t xml:space="preserve">18.427698135376</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2629928588867</t>
+    <t xml:space="preserve">19.2629947662354</t>
   </si>
   <si>
     <t xml:space="preserve">19.0754795074463</t>
@@ -2588,25 +2588,25 @@
     <t xml:space="preserve">19.6039333343506</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6380271911621</t>
+    <t xml:space="preserve">19.6380252838135</t>
   </si>
   <si>
     <t xml:space="preserve">20.0641994476318</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8766822814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7744007110596</t>
+    <t xml:space="preserve">19.8766841888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7744026184082</t>
   </si>
   <si>
     <t xml:space="preserve">20.1494331359863</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0471534729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4846057891846</t>
+    <t xml:space="preserve">20.0471515655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4846038818359</t>
   </si>
   <si>
     <t xml:space="preserve">19.8425903320312</t>
@@ -2615,49 +2615,49 @@
     <t xml:space="preserve">19.8084945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7119827270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9506359100342</t>
+    <t xml:space="preserve">20.7119789123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9506378173828</t>
   </si>
   <si>
     <t xml:space="preserve">20.6778869628906</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8483562469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8824481964111</t>
+    <t xml:space="preserve">20.8483543395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8824501037598</t>
   </si>
   <si>
     <t xml:space="preserve">21.0529193878174</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9335899353027</t>
+    <t xml:space="preserve">20.9335880279541</t>
   </si>
   <si>
     <t xml:space="preserve">21.0870113372803</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1551990509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.291576385498</t>
+    <t xml:space="preserve">21.1552028656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2915744781494</t>
   </si>
   <si>
     <t xml:space="preserve">21.2574825286865</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2233905792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0699634552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3086223602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8994979858398</t>
+    <t xml:space="preserve">21.2233867645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0699653625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3086242675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8994960784912</t>
   </si>
   <si>
     <t xml:space="preserve">20.9676837921143</t>
@@ -2666,40 +2666,40 @@
     <t xml:space="preserve">20.7631225585938</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9165439605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1609649658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6382808685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0133113861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9167995452881</t>
+    <t xml:space="preserve">20.9165458679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1609668731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6382789611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.013313293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9167976379395</t>
   </si>
   <si>
     <t xml:space="preserve">23.8145160675049</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9679374694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0020332336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5758590698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8656578063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7974681854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5247230529785</t>
+    <t xml:space="preserve">23.9679393768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0020294189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5758571624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8656558990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7974720001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5247211456299</t>
   </si>
   <si>
     <t xml:space="preserve">23.5929088592529</t>
@@ -2708,19 +2708,19 @@
     <t xml:space="preserve">23.6610927581787</t>
   </si>
   <si>
-    <t xml:space="preserve">23.848611831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6781406402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4394836425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7292804718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7463283538818</t>
+    <t xml:space="preserve">23.8486080169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6781425476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4394855499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7292785644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7463302612305</t>
   </si>
   <si>
     <t xml:space="preserve">23.6951866149902</t>
@@ -2729,31 +2729,31 @@
     <t xml:space="preserve">23.4906253814697</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7633724212646</t>
+    <t xml:space="preserve">23.7633762359619</t>
   </si>
   <si>
     <t xml:space="preserve">23.1496868133545</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9849872589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8997497558594</t>
+    <t xml:space="preserve">23.9849853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8997535705566</t>
   </si>
   <si>
     <t xml:space="preserve">24.4963912963867</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2123622894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5304870605469</t>
+    <t xml:space="preserve">25.2123641967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5304851531982</t>
   </si>
   <si>
     <t xml:space="preserve">25.1100788116455</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0647048950195</t>
+    <t xml:space="preserve">26.0647068023682</t>
   </si>
   <si>
     <t xml:space="preserve">25.4680633544922</t>
@@ -2762,31 +2762,31 @@
     <t xml:space="preserve">25.5533008575439</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4851112365723</t>
+    <t xml:space="preserve">25.4851131439209</t>
   </si>
   <si>
     <t xml:space="preserve">25.1271286010742</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0589389801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0759868621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8202819824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8884696960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1953144073486</t>
+    <t xml:space="preserve">25.0589408874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.075984954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8202838897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8884716033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1953125</t>
   </si>
   <si>
     <t xml:space="preserve">24.7180042266846</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3487358093262</t>
+    <t xml:space="preserve">25.3487377166748</t>
   </si>
   <si>
     <t xml:space="preserve">25.2294082641602</t>
@@ -2795,76 +2795,76 @@
     <t xml:space="preserve">25.4339714050293</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3657836914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9453773498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8829574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7636299133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0306129455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9283294677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0135650634766</t>
+    <t xml:space="preserve">25.3657855987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9453792572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8829593658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7636280059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0306148529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9283313751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0135688781738</t>
   </si>
   <si>
     <t xml:space="preserve">25.144172668457</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9566555023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4224395751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2690124511719</t>
+    <t xml:space="preserve">24.9566593170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4224376678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2690143585205</t>
   </si>
   <si>
     <t xml:space="preserve">23.4053897857666</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4565334320068</t>
+    <t xml:space="preserve">23.4565315246582</t>
   </si>
   <si>
     <t xml:space="preserve">24.837329864502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0930309295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5703468322754</t>
+    <t xml:space="preserve">25.0930347442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5703449249268</t>
   </si>
   <si>
     <t xml:space="preserve">25.6385364532471</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3600158691406</t>
+    <t xml:space="preserve">24.3600177764893</t>
   </si>
   <si>
     <t xml:space="preserve">24.13840675354</t>
   </si>
   <si>
-    <t xml:space="preserve">25.911283493042</t>
+    <t xml:space="preserve">25.9112854003906</t>
   </si>
   <si>
     <t xml:space="preserve">24.5475311279297</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8315601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5588150024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1213607788086</t>
+    <t xml:space="preserve">23.8315620422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5588111877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.12135887146</t>
   </si>
   <si>
     <t xml:space="preserve">23.5417671203613</t>
@@ -2873,58 +2873,58 @@
     <t xml:space="preserve">23.0985450744629</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2747802734375</t>
+    <t xml:space="preserve">24.2747821807861</t>
   </si>
   <si>
     <t xml:space="preserve">24.9396114349365</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2918281555176</t>
+    <t xml:space="preserve">24.2918300628662</t>
   </si>
   <si>
     <t xml:space="preserve">24.0702209472656</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5076732635498</t>
+    <t xml:space="preserve">23.5076713562012</t>
   </si>
   <si>
     <t xml:space="preserve">23.3372020721436</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1837787628174</t>
+    <t xml:space="preserve">23.1837825775146</t>
   </si>
   <si>
     <t xml:space="preserve">22.6894226074219</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1667327880859</t>
+    <t xml:space="preserve">23.1667346954346</t>
   </si>
   <si>
     <t xml:space="preserve">23.2860622406006</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2029094696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3768405914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6984977722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5941333770752</t>
+    <t xml:space="preserve">23.2029075622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3768424987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6984939575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5941352844238</t>
   </si>
   <si>
     <t xml:space="preserve">22.8202495574951</t>
   </si>
   <si>
-    <t xml:space="preserve">22.420202255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7854633331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2898769378662</t>
+    <t xml:space="preserve">22.4202003479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7854652404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2898750305176</t>
   </si>
   <si>
     <t xml:space="preserve">22.8028564453125</t>
@@ -2933,16 +2933,16 @@
     <t xml:space="preserve">22.8724308013916</t>
   </si>
   <si>
-    <t xml:space="preserve">22.750675201416</t>
+    <t xml:space="preserve">22.7506771087646</t>
   </si>
   <si>
     <t xml:space="preserve">22.7158908843994</t>
   </si>
   <si>
-    <t xml:space="preserve">22.246265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3332347869873</t>
+    <t xml:space="preserve">22.2462673187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.33323097229</t>
   </si>
   <si>
     <t xml:space="preserve">22.4723796844482</t>
@@ -2951,28 +2951,28 @@
     <t xml:space="preserve">23.2550868988037</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5769939422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3596992492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5510272979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1945838928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4207000732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7597522735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4033088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0294742584229</t>
+    <t xml:space="preserve">24.5769920349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3596973419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.551025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1945896148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4207019805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7597503662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4033069610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0294723510742</t>
   </si>
   <si>
     <t xml:space="preserve">27.186014175415</t>
@@ -2981,34 +2981,34 @@
     <t xml:space="preserve">27.1164417266846</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0120792388916</t>
+    <t xml:space="preserve">27.0120811462402</t>
   </si>
   <si>
     <t xml:space="preserve">28.1426563262939</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8036079406738</t>
+    <t xml:space="preserve">28.8036060333252</t>
   </si>
   <si>
     <t xml:space="preserve">29.0992965698242</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3775939941406</t>
+    <t xml:space="preserve">29.3775901794434</t>
   </si>
   <si>
     <t xml:space="preserve">29.5863151550293</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0385437011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2210483551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.081901550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7688255310059</t>
+    <t xml:space="preserve">30.0385494232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2210521697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0818996429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7688217163086</t>
   </si>
   <si>
     <t xml:space="preserve">28.4035568237305</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">27.6904258728027</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7859630584717</t>
+    <t xml:space="preserve">26.7859649658203</t>
   </si>
   <si>
     <t xml:space="preserve">26.5946350097656</t>
@@ -3026,19 +3026,19 @@
     <t xml:space="preserve">27.412130355835</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6294231414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6208534240723</t>
+    <t xml:space="preserve">26.6294250488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6208515167236</t>
   </si>
   <si>
     <t xml:space="preserve">26.6468162536621</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5250625610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2034072875977</t>
+    <t xml:space="preserve">26.5250606536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2034091949463</t>
   </si>
   <si>
     <t xml:space="preserve">27.307767868042</t>
@@ -3050,22 +3050,22 @@
     <t xml:space="preserve">30.1081199645996</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1340885162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0471172332764</t>
+    <t xml:space="preserve">29.1340827941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0471229553223</t>
   </si>
   <si>
     <t xml:space="preserve">29.2906284332275</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8905773162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3080215454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8560371398926</t>
+    <t xml:space="preserve">28.8905792236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3080177307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8560409545898</t>
   </si>
   <si>
     <t xml:space="preserve">30.7342853546143</t>
@@ -3074,43 +3074,43 @@
     <t xml:space="preserve">30.2298736572266</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3690185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4385929107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0559425354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.299446105957</t>
+    <t xml:space="preserve">30.3690204620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4385948181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0559406280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2994537353516</t>
   </si>
   <si>
     <t xml:space="preserve">29.9515819549561</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6125316619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.995189666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6039581298828</t>
+    <t xml:space="preserve">30.6125354766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9951858520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6039600372314</t>
   </si>
   <si>
     <t xml:space="preserve">31.8300724029541</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5691738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.864860534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7778949737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4996013641357</t>
+    <t xml:space="preserve">31.5691757202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8648643493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7778930664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4995975494385</t>
   </si>
   <si>
     <t xml:space="preserve">32.0387992858887</t>
@@ -3122,37 +3122,37 @@
     <t xml:space="preserve">31.3430595397949</t>
   </si>
   <si>
-    <t xml:space="preserve">31.447416305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2734813690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7605037689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7083187103271</t>
+    <t xml:space="preserve">31.4474201202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2734794616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7605018615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7083206176758</t>
   </si>
   <si>
     <t xml:space="preserve">31.5865650177002</t>
   </si>
   <si>
-    <t xml:space="preserve">31.743106842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6387462615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6735305786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3866691589355</t>
+    <t xml:space="preserve">31.7431049346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6387500762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6735343933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3866729736328</t>
   </si>
   <si>
     <t xml:space="preserve">32.5605964660645</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8474655151367</t>
+    <t xml:space="preserve">31.8474674224854</t>
   </si>
   <si>
     <t xml:space="preserve">32.5432052612305</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">31.8996486663818</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5169925689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7952880859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8126811981201</t>
+    <t xml:space="preserve">31.5169944763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7952899932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8126831054688</t>
   </si>
   <si>
     <t xml:space="preserve">31.6213531494141</t>
@@ -3179,13 +3179,13 @@
     <t xml:space="preserve">31.3952388763428</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1553268432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9081153869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7845039367676</t>
+    <t xml:space="preserve">32.155330657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9081134796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7845115661621</t>
   </si>
   <si>
     <t xml:space="preserve">32.1376724243164</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">32.1729850769043</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2612762451172</t>
+    <t xml:space="preserve">32.2612800598145</t>
   </si>
   <si>
     <t xml:space="preserve">32.278938293457</t>
@@ -3203,16 +3203,16 @@
     <t xml:space="preserve">31.7491931915283</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7668476104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8728008270264</t>
+    <t xml:space="preserve">31.7668533325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8727970123291</t>
   </si>
   <si>
     <t xml:space="preserve">32.6674118041992</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0029182434082</t>
+    <t xml:space="preserve">33.0029144287109</t>
   </si>
   <si>
     <t xml:space="preserve">33.4443702697754</t>
@@ -3224,16 +3224,16 @@
     <t xml:space="preserve">34.3096122741699</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9982719421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9806137084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2808036804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7863845825195</t>
+    <t xml:space="preserve">34.9982795715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9806175231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2808074951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7863807678223</t>
   </si>
   <si>
     <t xml:space="preserve">33.9564514160156</t>
@@ -3242,25 +3242,25 @@
     <t xml:space="preserve">33.7975273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3384132385254</t>
+    <t xml:space="preserve">33.3384170532227</t>
   </si>
   <si>
     <t xml:space="preserve">32.9499435424805</t>
   </si>
   <si>
-    <t xml:space="preserve">33.179500579834</t>
+    <t xml:space="preserve">33.1794967651367</t>
   </si>
   <si>
     <t xml:space="preserve">33.2148094177246</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0912017822266</t>
+    <t xml:space="preserve">33.0912055969238</t>
   </si>
   <si>
     <t xml:space="preserve">32.4378623962402</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0205726623535</t>
+    <t xml:space="preserve">33.0205764770508</t>
   </si>
   <si>
     <t xml:space="preserve">32.843994140625</t>
@@ -3269,13 +3269,13 @@
     <t xml:space="preserve">33.1441841125488</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0317192077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3319053649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7027282714844</t>
+    <t xml:space="preserve">32.0317230224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3319091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7027244567871</t>
   </si>
   <si>
     <t xml:space="preserve">33.2677879333496</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">33.4267120361328</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8616523742676</t>
+    <t xml:space="preserve">32.8616561889648</t>
   </si>
   <si>
     <t xml:space="preserve">32.2083015441895</t>
@@ -3302,43 +3302,43 @@
     <t xml:space="preserve">33.126522064209</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9322853088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9257717132568</t>
+    <t xml:space="preserve">32.9322814941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9257755279541</t>
   </si>
   <si>
     <t xml:space="preserve">32.5438041687012</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0270805358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8681602478027</t>
+    <t xml:space="preserve">34.0270843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8681640625</t>
   </si>
   <si>
     <t xml:space="preserve">34.0800552368164</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3449325561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3802452087402</t>
+    <t xml:space="preserve">34.3449287414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3802375793457</t>
   </si>
   <si>
     <t xml:space="preserve">34.1330299377441</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5215110778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1506881713867</t>
+    <t xml:space="preserve">34.5215072631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.150691986084</t>
   </si>
   <si>
     <t xml:space="preserve">34.2036628723145</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1153717041016</t>
+    <t xml:space="preserve">34.1153755187988</t>
   </si>
   <si>
     <t xml:space="preserve">33.938793182373</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">33.6209526062012</t>
   </si>
   <si>
-    <t xml:space="preserve">33.691577911377</t>
+    <t xml:space="preserve">33.6915817260742</t>
   </si>
   <si>
     <t xml:space="preserve">34.2919540405273</t>
@@ -3359,13 +3359,13 @@
     <t xml:space="preserve">32.914623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">33.197151184082</t>
+    <t xml:space="preserve">33.1971549987793</t>
   </si>
   <si>
     <t xml:space="preserve">33.5149993896484</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5503158569336</t>
+    <t xml:space="preserve">33.5503120422363</t>
   </si>
   <si>
     <t xml:space="preserve">33.815185546875</t>
@@ -3374,55 +3374,55 @@
     <t xml:space="preserve">34.6451187133789</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1395416259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8570137023926</t>
+    <t xml:space="preserve">35.1395378112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8570098876953</t>
   </si>
   <si>
     <t xml:space="preserve">34.6804275512695</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0865707397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3272666931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2371101379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4248390197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1776237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0716762542725</t>
+    <t xml:space="preserve">35.0865669250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3272743225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2371063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4248371124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1776275634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0716800689697</t>
   </si>
   <si>
     <t xml:space="preserve">29.559591293335</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6125679016113</t>
+    <t xml:space="preserve">29.61256980896</t>
   </si>
   <si>
     <t xml:space="preserve">29.6478862762451</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2306041717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3477001190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0121936798096</t>
+    <t xml:space="preserve">30.2306003570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3476982116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0121917724609</t>
   </si>
   <si>
     <t xml:space="preserve">28.2882137298584</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8467636108398</t>
+    <t xml:space="preserve">27.8467617034912</t>
   </si>
   <si>
     <t xml:space="preserve">27.4406261444092</t>
@@ -3434,40 +3434,40 @@
     <t xml:space="preserve">28.09397315979</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7937850952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6348628997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0763130187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0410003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3058738708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2240886688232</t>
+    <t xml:space="preserve">27.7937870025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6348648071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0763149261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0410022735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.305871963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2240905761719</t>
   </si>
   <si>
     <t xml:space="preserve">29.1004848480225</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4713039398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1358013153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3123836517334</t>
+    <t xml:space="preserve">29.4713020324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.135799407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3123817443848</t>
   </si>
   <si>
     <t xml:space="preserve">29.8244647979736</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9480686187744</t>
+    <t xml:space="preserve">29.948070526123</t>
   </si>
   <si>
     <t xml:space="preserve">29.7891521453857</t>
@@ -3476,22 +3476,22 @@
     <t xml:space="preserve">29.2417488098145</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8421230316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0010414123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9833869934082</t>
+    <t xml:space="preserve">29.8421192169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0010452270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9833850860596</t>
   </si>
   <si>
     <t xml:space="preserve">30.5661010742188</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9545803070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1952838897705</t>
+    <t xml:space="preserve">30.9545822143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1952857971191</t>
   </si>
   <si>
     <t xml:space="preserve">30.1246490478516</t>
@@ -3509,2025 +3509,2025 @@
     <t xml:space="preserve">26.9462013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6106986999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2817058563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7231559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3876514434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6989898681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8755664825439</t>
+    <t xml:space="preserve">26.6106967926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2817039489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7231540679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3876533508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6989879608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8755683898926</t>
   </si>
   <si>
     <t xml:space="preserve">27.0698070526123</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7807693481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4341163635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1162738800049</t>
+    <t xml:space="preserve">25.7807712554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4341201782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1162719726562</t>
   </si>
   <si>
     <t xml:space="preserve">26.85791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3634872436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1339321136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3988018035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.140438079834</t>
+    <t xml:space="preserve">26.3634853363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1339302062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3987998962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1404399871826</t>
   </si>
   <si>
     <t xml:space="preserve">26.575382232666</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7519607543945</t>
+    <t xml:space="preserve">26.7519588470459</t>
   </si>
   <si>
     <t xml:space="preserve">26.3105087280273</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4694309234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8225917816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2110710144043</t>
+    <t xml:space="preserve">26.4694328308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8225936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2110729217529</t>
   </si>
   <si>
     <t xml:space="preserve">27.0521488189697</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3523368835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9815158843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9350528717041</t>
+    <t xml:space="preserve">27.3523387908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9815139770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9350509643555</t>
   </si>
   <si>
     <t xml:space="preserve">27.8291034698486</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4053115844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7761287689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6525249481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3699951171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4164581298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9155235290527</t>
+    <t xml:space="preserve">27.405309677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7761306762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6525211334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3699932098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4164562225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9155216217041</t>
   </si>
   <si>
     <t xml:space="preserve">25.0214729309082</t>
   </si>
   <si>
+    <t xml:space="preserve">24.7212829589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8978652954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2686862945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5447025299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1032524108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8383827209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6924800872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.451774597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5112571716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9703674316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2993621826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9285430908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5289173126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.475944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9638595581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3811416625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8932247161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1757545471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7872791290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0986137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4629230499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8095741271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2333679199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.127420425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7389450073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1738872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4080791473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4192295074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3662528991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6906089782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0660648345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9424591064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3551044464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7723903656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7788963317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4610538482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2844734191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2314968109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8077068328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5251750946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4722023010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5604915618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.990795135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3374481201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8430213928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7547302246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7900466918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5958080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3839111328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9601173400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1896724700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.136697769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4015674591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7658805847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8365116119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0595550537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9359493255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3774013519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5186653137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8653182983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0065822601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7835369110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5363235473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.041898727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1943130493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4238681793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7770290374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3420886993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3355770111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5474739074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6710815429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9111518859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0677719116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4711284637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1311645507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3878479003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9012107849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6995315551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3145122528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.64453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0944995880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4061832427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1678371429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5811367034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3061180114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3710651397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7560882568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0127696990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0960483551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0861034393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.729362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9493732452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2801704406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2618312835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.179328918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2343330383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0968246459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.757640838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2626094818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1617698669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1709384918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9875946044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3817825317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7851390838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0601577758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.188497543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4635105133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9501495361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4092864990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6843013763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9043140411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0693225860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9593162536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1334934234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8676452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3359470367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8500852584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8218078613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5284576416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1151580810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8852062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6560230255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6376895904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8859786987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4726791381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5643501281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6835250854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6651916503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2159976959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3351707458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9868183135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0784893035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8584785461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4001178741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9967603683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9417552947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0425968170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0150947570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6392383575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9142580032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0525398254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2542190551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2175493240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1992149353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6117401123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0059261322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6942434310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9883689880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5758447647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5850114822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.860803604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8058004379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6041231155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3841104507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.585786819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7599639892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.924973487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.310772895813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8149671554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5032835006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8883037567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5124502182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6591243743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3382740020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4482793807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8516368865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5307846069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8424692153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1908226013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3466653823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6033477783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1816549301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5483436584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8233594894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5659017562866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7217454910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9050903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1526031494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7026348114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2434978485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5093479156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2427234649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5528564453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.717866897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4161262512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1594429016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0494384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6178035736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2595062255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7094783782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3794555664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.562801361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8928203582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6544742584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8561515808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4527950286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5261306762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7278118133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3695125579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8378162384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3244514465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9760990142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9577655792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2144470214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6728038787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.232780456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0578289031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1128311157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2961769104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5161895751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8179321289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2495651245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9928817749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7728710174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8828792572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0478858947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8095397949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7362022399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7828121185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.764476776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2511157989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8660945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3977909088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3427886962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4894638061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5994682312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3511791229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8744850158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1495018005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0761642456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0394954681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9745483398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2128963470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5795841217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6345882415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6529216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6162548065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5429153442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6812000274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3045673370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6628665924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4245185852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5711936950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.966157913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5077991485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3611259460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5444660186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9294891357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0211601257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6460800170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4444026947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.481071472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.609411239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.407735824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3343982696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9210987091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2877864837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1961135864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1044425964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7201480865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6169319152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8756294250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5378246307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7348766326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6410427093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2469348907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1437168121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1718654632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0498809814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0029640197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0311126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9560451507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8903617858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9091281890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.078031539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1852855682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2885055541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5659732818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0070018768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9225482940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8662490844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8005619049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5753555297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7536449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9319324493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9882335662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3354244232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5137119293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7858333587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5230941772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7483005523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4855613708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7817974090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8474807739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4386425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0056934356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1558284759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3435001373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7804870605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8555564880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.874324798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.198709487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2925453186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6678867340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2737770080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4989833831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.362268447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7939109802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6759624481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.826099395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0325355529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1639060974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0888366699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8073310852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1826725006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2389736175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2952747344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.482946395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9574680328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8448657989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7698001861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7134952545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.995002746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5767822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.670618057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.970890045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9145889282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1585597991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2711620330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1397953033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4882888793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8824005126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8636322021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9252796173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0003471374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1692523956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2443199157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8877449035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6813068389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1182975769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3998012542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8930912017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2174777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3488464355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7992553710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7054195404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0807609558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.742956161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6115837097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4239139556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4426803588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9359703063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9172039031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2684345245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6866512298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1236400604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9922714233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9118576049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4051475524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8180255889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9681606292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.606237411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4695243835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7162284851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5848579406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6974601745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5044422149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.922664642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8475971221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4293766021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0486907958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.710880279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2363586425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8422527313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9360847473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6170463562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7484169006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0674571990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5741653442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3114280700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4615631103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7806053161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9119720458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0058097839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.231014251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1184120178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1559467315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8932075500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6814231872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.718957901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4749870300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7377243041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1693668365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9629287719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6573123931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.507173538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6385440826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9307403564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7752590179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8878593444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4321041107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8074493408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2766246795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8449821472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7136135101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1881351470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8315601348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7940273284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9253959655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2819690704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1640224456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.944164276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2444362640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6063556671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1130657196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5500545501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1934795379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7243022918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2175922393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.874439239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4374504089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3060836791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7055358886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8181381225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0996437072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1318321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.206901550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9951190948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0192317962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4884071350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2900447845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5527858734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1533317565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4777164459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5152530670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3838806152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0460739135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1211414337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6519660949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9897727966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0836086273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6894989013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7270336151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4026489257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2712783813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9334697723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5259399414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3007373809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0943012237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0379962921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1506004333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8503284454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5205974578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9763488769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.483060836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7645683288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9575843811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1452541351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.00319480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.946891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7779903411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3973026275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5581302642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7029228210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3463478088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4455280303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2953910827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4392318725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7460899353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1323719024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6310176849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5543041229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7242012023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6064205169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6091289520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3570957183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8968086242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8776302337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4940567016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.299560546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2803802490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9159889221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8392734527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7050228118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2420272827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9543437957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7077331542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6858425140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0694179534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4556999206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4913482666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7817363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.47216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.014591217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4227619171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4419403076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0008335113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5761909484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8638725280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.359806060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2063770294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4365196228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2830905914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8009147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2612018585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4146308898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0885944366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6474857330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3022708892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8584518432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3241596221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4584083557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7487983703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5378341674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9432964324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1021461486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5459651947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1432113647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8720016479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3131122589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0446090698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2172183990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0637874603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9295387268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5432548522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4281806945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8692932128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.041898727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1953277587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0610771179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.444652557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0802574157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6939735412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9843635559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.524076461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5624351501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6802158355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3158206939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.584321975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3925361633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0281429290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7952880859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2939319610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9487171173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4857196807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7733993530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6418590545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7761077880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1213226318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7377510070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6583251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0829677581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9678936004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1405029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1596832275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8528232574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8144645690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9103584289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9870738983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6993942260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4884300231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.756929397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2966403961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3514671325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0967254638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7706871032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5980815887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5789012908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8309345245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3541774749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7542190551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6747951507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6391487121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3076915740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.557014465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7515106201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7323303222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4062938690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3898258209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7925777435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0227222442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8501129150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.214506149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3487567901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.962474822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6337280273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1131935119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3049793243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0556564331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9597644805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7296199798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7104434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.981653213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.40358543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2474460601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8830509185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6912631988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4611206054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.809045791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6172580718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9049396514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6666641235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9351654052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1077728271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2228469848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6037101745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1050605773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6804275512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3352088928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5269927978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2584915161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2776718139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8365631103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7598495483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2009582519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.661247253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8913879394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9105682373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4694595336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.584529876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0475273132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6228866577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3708534240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6420669555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2968521118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9708118438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4338092803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9735221862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9762325286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.532413482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1104831695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8995189666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2447357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2639122009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.841983795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6501960754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2090854644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6856365203857</t>
+  </si>
+  <si>
     <t xml:space="preserve">24.721284866333</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8978652954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.268684387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5447025299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1032524108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8383827209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6924781799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4517765045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5112571716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9703693389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2993621826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9285430908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5289173126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4759407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9638595581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3811416625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8932247161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1757564544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7872772216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0986137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4629230499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8095760345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2333679199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1274185180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7389430999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1738834381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4080772399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4192276000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3662528991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6906089782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0660648345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9424591064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3551044464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.772388458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7788982391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4610538482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2844734191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2314968109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8077049255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5251750946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4722023010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5604934692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.990795135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3374462127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8430213928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7547302246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7900466918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5958099365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3839111328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9601192474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1896705627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1366996765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4015693664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7658805847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8365135192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0595550537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9359512329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3774013519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5186672210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8653182983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0065841674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7835369110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5363235473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0419006347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1943111419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.423864364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.777027130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3420886993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3355751037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5474720001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6710796356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.911153793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0677719116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4711284637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1311645507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3878498077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9012107849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6995334625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.314510345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6445331573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0944976806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4061832427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1678352355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5811347961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3061199188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3710651397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7560882568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.012767791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0960483551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0861053466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.729362487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9493751525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2801704406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2618350982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1793270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2343330383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0968246459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7576389312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2626094818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1617698669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1709365844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9875946044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3817844390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7851390838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0601558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.188497543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4635124206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9501476287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4092845916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6842994689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9043140411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0693225860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9593181610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1334934234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8676452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3359470367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8500862121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8218078613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5284595489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1151580810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8852043151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6560249328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6376895904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8859786987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4726791381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5643520355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6835269927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6651916503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2159976959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3351726531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9868183135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0784873962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8584747314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4001159667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9967613220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9417572021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0425968170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0150966644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6392383575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9142560958862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0525388717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2542181015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.21755027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1992149353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6117372512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0059261322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6942453384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9883689880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5758438110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5850114822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.860803604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8058004379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6041231155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3841094970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5857877731323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7599649429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.924973487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3107738494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8149671554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5032825469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8883047103882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5124502182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6591243743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3382730484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4482793807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8516368865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5307846069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8424692153931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1908226013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3466644287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.603346824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1816549301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5483427047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8233585357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5659036636353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7217445373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9050884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1526050567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7026348114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2434997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.509349822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2427253723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5528602600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7178688049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4161262512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.15944480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0494365692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6178035736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2595062255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7094764709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3794555664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.562801361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.892822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6544742584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8561515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4527950286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5261306762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7278118133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3695125579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8378162384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3244533538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9761009216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9577655792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2144470214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6728057861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2327823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0578308105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1128330230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2961750030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5161895751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8179321289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2495651245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9928817749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7728691101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8828773498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0478858947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8095397949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7362041473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7828121185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7644786834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2511177062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8660926818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3977928161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3427886962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4894638061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5994682312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3511810302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8744850158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1495018005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0761623382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0394954681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9745502471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2128963470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5795841217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6345901489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6529235839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6162528991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5429153442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6811981201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3045673370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6628646850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4245185852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5711936950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.966157913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5077972412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3611240386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5444641113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9294910430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0211620330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6460819244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4444046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.481071472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.609411239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4077339172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3343944549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9210948944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.287784576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1961135864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1044406890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7201499938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6169300079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8756294250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5378246307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7348785400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.641040802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2469329833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1437168121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1718654632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0498809814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0029621124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0311126708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9560451507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.89035987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9091262817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.078031539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1852855682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2885074615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5659732818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0069999694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.922550201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8662490844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8005599975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5753593444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7536468505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9319324493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9882316589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3354263305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5137100219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7858333587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5230960845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7482986450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4855613708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7817974090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8474807739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4386425018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0056915283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1558284759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3435001373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7804889678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8555583953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.874324798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.198709487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2925453186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6678848266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2737789154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4989833831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.362268447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.793909072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6759643554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8260974884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0325355529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1639060974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0888385772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8073310852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1826725006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2389755249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2952766418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4829444885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9574661254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8448657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.76979637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7134971618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.995002746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5767803192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.670618057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.970890045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9145889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1585597991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2711620330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1397914886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4882926940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8824005126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8636322021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9252796173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0003471374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1692504882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2443180084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8877468109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6813087463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1182975769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3998012542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8930931091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2174758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3488464355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7992553710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7054214477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0807609558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.742956161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6115837097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4239139556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4426803588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3300800323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9359722137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9172039031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2684326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.686653137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1236419677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9922714233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9118595123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4051456451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8180236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9681587219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.606237411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4695243835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7162265777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5848579406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6974601745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5044422149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9226627349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8475952148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4293766021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0486869812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.710880279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2363586425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8422527313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9360866546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6170463562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7484169006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.067455291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5741672515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3114280700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4615650177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7806053161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9119739532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0058116912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.231014251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1184120178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1559467315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8932056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6814231872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7189598083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4749851226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7377243041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1693687438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9629287719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6573104858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.507173538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6385440826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9307422637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.775260925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8878593444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4321060180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8074474334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2766246795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8449821472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7136135101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1881370544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8315601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7940292358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9253959655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2819690704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1640224456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9441623687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2444362640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6063556671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1130657196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5500545501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1934814453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7243022918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2175941467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.874439239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4374504089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3060817718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7055339813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8181381225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0996437072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1318321228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.206901550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9951171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.019229888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4884090423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2900466918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5527877807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1533336639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4777164459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.515251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3838806152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0460739135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1211414337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6519660949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9897708892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.083610534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6895008087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7270336151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4026489257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2712783813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9334716796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5259399414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3007373809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0942993164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0379962921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1506004333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8503284454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5205955505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9763526916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4830627441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7645683288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9575862884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1452541351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0031967163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9468936920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7779884338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3973007202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5581321716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7029228210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3463478088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4455261230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2953910827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4392318725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7460899353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1323719024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6310176849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5543022155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7242012023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6064167022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6091289520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3570995330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8968086242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8776321411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4940547943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2995586395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2803802490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9159889221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8392715454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7050228118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2420272827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9543437957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7077312469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6858425140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0694179534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4556999206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4913463592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7817344665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4721698760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0145893096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4227619171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4419422149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0008335113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5761909484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8638706207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.359806060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2063789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4365196228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2830905914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8009147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2611999511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4146308898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0885944366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6474857330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3022708892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8584518432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3241596221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4584102630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7487983703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5378341674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9432964324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.102144241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5459632873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1432113647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8720016479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3131122589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0446090698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2172164916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0637893676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.929536819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5432548522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4281826019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8692932128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0419006347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1953296661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0610771179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.444652557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0802574157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6939735412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9843635559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.524076461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5624332427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6802158355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3158206939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5843238830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3925342559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0281410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7952861785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2939319610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9487152099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4857196807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7733974456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6418590545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7761077880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1213245391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7377510070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6583271026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0829677581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9678955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1405029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1596813201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8528232574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8144664764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9103603363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9870738983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6993942260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4884281158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7569313049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2966423034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3514671325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0967254638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7706871032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5980815887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5789012908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8309326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3541793823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7542190551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6747951507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6391487121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.307689666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.557014465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7515106201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7323303222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4062938690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3898258209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7925777435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0227203369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8501129150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2145080566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3487586975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.962474822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6337280273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1131954193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3049812316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0556564331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9597663879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7296199798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7104434967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.981653213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.40358543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2474460601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8830509185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6912631988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4611206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.809045791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.617259979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9049377441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6666641235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9351654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1077728271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2228488922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6037063598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1050643920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6804275512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3352088928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5269927978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2584953308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2776718139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8365631103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7598476409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2009582519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.661247253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8913879394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9105682373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4694595336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.584529876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0475234985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6228866577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3708534240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6420669555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2968482971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9708137512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4338111877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9735221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9762344360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5324153900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1104831695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8995189666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2447357177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2639122009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.841983795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6501960754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2090854644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6856346130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7212829589844</t>
-  </si>
-  <si>
     <t xml:space="preserve">23.9157791137695</t>
   </si>
   <si>
@@ -5549,7 +5549,7 @@
     <t xml:space="preserve">25.2774639129639</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6829261779785</t>
+    <t xml:space="preserve">24.6829242706299</t>
   </si>
   <si>
     <t xml:space="preserve">25.1048564910889</t>
@@ -5561,13 +5561,13 @@
     <t xml:space="preserve">25.5267868041992</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5816116333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6199684143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4090042114258</t>
+    <t xml:space="preserve">26.5816097259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6199703216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4090061187744</t>
   </si>
   <si>
     <t xml:space="preserve">27.7131519317627</t>
@@ -5576,7 +5576,7 @@
     <t xml:space="preserve">29.611837387085</t>
   </si>
   <si>
-    <t xml:space="preserve">28.902229309082</t>
+    <t xml:space="preserve">28.9022274017334</t>
   </si>
   <si>
     <t xml:space="preserve">28.6145496368408</t>
@@ -5844,6 +5844,9 @@
   </si>
   <si>
     <t xml:space="preserve">28.0599994659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2800006866455</t>
   </si>
 </sst>
 </file>
@@ -70896,7 +70899,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6494675926</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>150592</v>
@@ -70917,6 +70920,32 @@
         <v>1943</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.649375</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>248401</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>29.3199996948242</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>27.9599990844727</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>28.2399997711182</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>29.2800006866455</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>1944</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DLG.MI.xlsx
+++ b/data/DLG.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7391414642334</t>
+    <t xml:space="preserve">20.7391452789307</t>
   </si>
   <si>
     <t xml:space="preserve">DLG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5564212799072</t>
+    <t xml:space="preserve">20.5564193725586</t>
   </si>
   <si>
     <t xml:space="preserve">20.6553974151611</t>
@@ -56,34 +56,34 @@
     <t xml:space="preserve">19.9777965545654</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7722301483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4905338287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8864364624023</t>
+    <t xml:space="preserve">19.7722320556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4905300140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8864345550537</t>
   </si>
   <si>
     <t xml:space="preserve">18.5160045623779</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6328372955322</t>
+    <t xml:space="preserve">17.6328430175781</t>
   </si>
   <si>
     <t xml:space="preserve">17.4348907470703</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5262546539307</t>
+    <t xml:space="preserve">17.526252746582</t>
   </si>
   <si>
     <t xml:space="preserve">17.0542163848877</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8943309783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0135154724121</t>
+    <t xml:space="preserve">16.8943328857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0135173797607</t>
   </si>
   <si>
     <t xml:space="preserve">16.63547706604</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">16.7116088867188</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8029689788818</t>
+    <t xml:space="preserve">16.8029708862305</t>
   </si>
   <si>
     <t xml:space="preserve">16.6735420227051</t>
@@ -104,49 +104,49 @@
     <t xml:space="preserve">16.1329822540283</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9654903411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6533355712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9909601211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7777824401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3335666656494</t>
+    <t xml:space="preserve">15.9654884338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6533336639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9909610748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7777814865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.333568572998</t>
   </si>
   <si>
     <t xml:space="preserve">14.4123373031616</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7397165298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4553823471069</t>
+    <t xml:space="preserve">14.7397136688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.455379486084</t>
   </si>
   <si>
     <t xml:space="preserve">15.2574329376221</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4097013473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7523078918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3868627548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9121942520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9578723907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5848112106323</t>
+    <t xml:space="preserve">15.4097032546997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.75230884552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3868598937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9121932983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9578733444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.584813117981</t>
   </si>
   <si>
     <t xml:space="preserve">16.1253719329834</t>
@@ -158,82 +158,82 @@
     <t xml:space="preserve">16.5593395233154</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7496738433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8817386627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2193660736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792476654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0873031616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7142400741577</t>
+    <t xml:space="preserve">16.7496757507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8817367553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2193651199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792495727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0873012542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7142429351807</t>
   </si>
   <si>
     <t xml:space="preserve">15.2878866195679</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8969659805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3183422088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6076536178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9274187088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9883289337158</t>
+    <t xml:space="preserve">15.8969640731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3183441162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6076526641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9274206161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9883260726929</t>
   </si>
   <si>
     <t xml:space="preserve">15.8893527984619</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6152667999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.356409072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1356143951416</t>
+    <t xml:space="preserve">15.6152687072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3564043045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1356134414673</t>
   </si>
   <si>
     <t xml:space="preserve">15.2269773483276</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3487911224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0442562103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2345924377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0594816207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1432323455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5493783950806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7853975296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8234643936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7831678390503</t>
+    <t xml:space="preserve">15.3487939834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0442552566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2345914840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0594825744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1432294845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5493793487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7853946685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8234605789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7831649780273</t>
   </si>
   <si>
     <t xml:space="preserve">14.9779872894287</t>
@@ -242,22 +242,22 @@
     <t xml:space="preserve">15.1572275161743</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1494331359863</t>
+    <t xml:space="preserve">15.149432182312</t>
   </si>
   <si>
     <t xml:space="preserve">14.9624032974243</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9857797622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9546098709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8533029556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4689435958862</t>
+    <t xml:space="preserve">14.9857816696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9546127319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8533000946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4689445495605</t>
   </si>
   <si>
     <t xml:space="preserve">15.671558380127</t>
@@ -266,10 +266,10 @@
     <t xml:space="preserve">16.21706199646</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7572803497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0300331115723</t>
+    <t xml:space="preserve">15.7572832107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0300312042236</t>
   </si>
   <si>
     <t xml:space="preserve">16.240442276001</t>
@@ -278,43 +278,43 @@
     <t xml:space="preserve">16.1469249725342</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3495407104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5054016113281</t>
+    <t xml:space="preserve">16.3495426177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5053997039795</t>
   </si>
   <si>
     <t xml:space="preserve">16.3105792999268</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7288856506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7937393188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0742835998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.762565612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7547760009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8482875823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1132488250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3002777099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7678527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9081249237061</t>
+    <t xml:space="preserve">17.7288913726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7937355041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0742816925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7625675201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7547740936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8482894897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1132469177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3002815246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7678546905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9081268310547</t>
   </si>
   <si>
     <t xml:space="preserve">17.9470901489258</t>
@@ -326,61 +326,61 @@
     <t xml:space="preserve">18.4848003387451</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7887287139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4614219665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3367385864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.274393081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0795707702637</t>
+    <t xml:space="preserve">18.7887229919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4614276885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3367404937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2743949890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0795726776123</t>
   </si>
   <si>
     <t xml:space="preserve">18.6484546661377</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8276882171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4536285400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8379898071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3937950134277</t>
+    <t xml:space="preserve">18.8276901245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4536304473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8379878997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3937931060791</t>
   </si>
   <si>
     <t xml:space="preserve">17.2535209655762</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0820770263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4951019287109</t>
+    <t xml:space="preserve">17.0820789337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4951038360596</t>
   </si>
   <si>
     <t xml:space="preserve">17.9237117767334</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8224048614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7834396362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9315032958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6768436431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.523494720459</t>
+    <t xml:space="preserve">17.8224029541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7834415435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9315052032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6768474578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5234899520874</t>
   </si>
   <si>
     <t xml:space="preserve">16.1157531738281</t>
@@ -389,70 +389,70 @@
     <t xml:space="preserve">16.3651294708252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6612586975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6300868988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8975534439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7806596755981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5468730926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7884540557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3729209899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1858940124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1625156402588</t>
+    <t xml:space="preserve">16.6612567901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6300888061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8975515365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7806587219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5468721389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7884531021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3729228973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1858901977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1625137329102</t>
   </si>
   <si>
     <t xml:space="preserve">16.419677734375</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5209865570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5287761688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8404941558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9184226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8716659545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8015327453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6119956970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2223491668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5964107513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4171733856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6587505340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.315860748291</t>
+    <t xml:space="preserve">16.5209884643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5287780761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8404979705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9184265136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8716678619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8015308380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6119937896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2223510742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5964069366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4171714782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6587524414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3158626556396</t>
   </si>
   <si>
     <t xml:space="preserve">17.3236560821533</t>
@@ -464,85 +464,85 @@
     <t xml:space="preserve">18.0561923980713</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5393524169922</t>
+    <t xml:space="preserve">18.5393543243408</t>
   </si>
   <si>
     <t xml:space="preserve">18.7030029296875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6640377044678</t>
+    <t xml:space="preserve">18.664041519165</t>
   </si>
   <si>
     <t xml:space="preserve">18.812105178833</t>
   </si>
   <si>
-    <t xml:space="preserve">18.095157623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1497058868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9003353118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1574993133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8769569396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6665458679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9704685211182</t>
+    <t xml:space="preserve">18.0951557159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1497077941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.900333404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1574974060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6665477752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9704704284668</t>
   </si>
   <si>
     <t xml:space="preserve">18.0328140258789</t>
   </si>
   <si>
-    <t xml:space="preserve">17.510684967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5730323791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3626232147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4015846252441</t>
+    <t xml:space="preserve">17.5106887817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5730304718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3626270294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4015865325928</t>
   </si>
   <si>
     <t xml:space="preserve">17.2379341125488</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4093818664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.144416809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8171195983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.614501953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6846408843994</t>
+    <t xml:space="preserve">17.4093799591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1444187164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8171157836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6145038604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6846389770508</t>
   </si>
   <si>
     <t xml:space="preserve">17.0197315216064</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1288375854492</t>
+    <t xml:space="preserve">17.128833770752</t>
   </si>
   <si>
     <t xml:space="preserve">17.2691059112549</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9963550567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4405498504639</t>
+    <t xml:space="preserve">16.9963531494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4405517578125</t>
   </si>
   <si>
     <t xml:space="preserve">17.4639301300049</t>
@@ -551,19 +551,19 @@
     <t xml:space="preserve">16.8327026367188</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8249111175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9028377532959</t>
+    <t xml:space="preserve">16.8249092102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9028396606445</t>
   </si>
   <si>
     <t xml:space="preserve">16.7859477996826</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7469806671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2769012451172</t>
+    <t xml:space="preserve">16.7469825744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2768955230713</t>
   </si>
   <si>
     <t xml:space="preserve">17.2457256317139</t>
@@ -572,16 +572,16 @@
     <t xml:space="preserve">17.0509033203125</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0976657867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.957389831543</t>
+    <t xml:space="preserve">17.0976638793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9573879241943</t>
   </si>
   <si>
     <t xml:space="preserve">17.2301425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">17.20676612854</t>
+    <t xml:space="preserve">17.2067623138428</t>
   </si>
   <si>
     <t xml:space="preserve">17.4327583312988</t>
@@ -590,40 +590,40 @@
     <t xml:space="preserve">17.2846927642822</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0664920806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9521026611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9832754135132</t>
+    <t xml:space="preserve">17.0664901733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9521017074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9832782745361</t>
   </si>
   <si>
     <t xml:space="preserve">16.2560272216797</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3339557647705</t>
+    <t xml:space="preserve">16.3339576721191</t>
   </si>
   <si>
     <t xml:space="preserve">15.9988622665405</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4065980911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.313081741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.118260383606</t>
+    <t xml:space="preserve">15.4066009521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.313084602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1182613372803</t>
   </si>
   <si>
     <t xml:space="preserve">16.5131931304932</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0923767089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9131393432617</t>
+    <t xml:space="preserve">16.0923748016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9131383895874</t>
   </si>
   <si>
     <t xml:space="preserve">16.1780967712402</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">16.4664363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2248573303223</t>
+    <t xml:space="preserve">16.224853515625</t>
   </si>
   <si>
     <t xml:space="preserve">15.9754829406738</t>
@@ -647,19 +647,19 @@
     <t xml:space="preserve">16.7080173492432</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4976062774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6924324035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5599517822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7703609466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8638763427734</t>
+    <t xml:space="preserve">16.4976081848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6924285888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5599536895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7703590393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8638706207275</t>
   </si>
   <si>
     <t xml:space="preserve">17.0275287628174</t>
@@ -668,31 +668,31 @@
     <t xml:space="preserve">17.4561367034912</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4483413696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8847484588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.118537902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2354278564453</t>
+    <t xml:space="preserve">17.4483432769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8847465515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1185340881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2354259490967</t>
   </si>
   <si>
     <t xml:space="preserve">18.0172290802002</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8457832336426</t>
+    <t xml:space="preserve">17.8457813262939</t>
   </si>
   <si>
     <t xml:space="preserve">17.9626770019531</t>
   </si>
   <si>
-    <t xml:space="preserve">17.869161605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6353721618652</t>
+    <t xml:space="preserve">17.8691596984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6353740692139</t>
   </si>
   <si>
     <t xml:space="preserve">17.7912330627441</t>
@@ -701,19 +701,19 @@
     <t xml:space="preserve">17.5808238983154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6509590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1107387542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9782619476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3133602142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2042579650879</t>
+    <t xml:space="preserve">17.6509571075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1107406616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9782638549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3133583068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2042541503906</t>
   </si>
   <si>
     <t xml:space="preserve">18.4692153930664</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">19.0848579406738</t>
   </si>
   <si>
-    <t xml:space="preserve">19.349817276001</t>
+    <t xml:space="preserve">19.3498134613037</t>
   </si>
   <si>
     <t xml:space="preserve">19.2952651977539</t>
@@ -731,46 +731,46 @@
     <t xml:space="preserve">19.4667091369629</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2485084533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3186473846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0614776611328</t>
+    <t xml:space="preserve">19.2485065460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3186454772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0614757537842</t>
   </si>
   <si>
     <t xml:space="preserve">19.4199523925781</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2407169342041</t>
+    <t xml:space="preserve">19.2407150268555</t>
   </si>
   <si>
     <t xml:space="preserve">19.0926494598389</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4511222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8588619232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6406593322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9056224822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2329196929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4978847503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1914520263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9888362884521</t>
+    <t xml:space="preserve">19.4511241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8588638305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.640661239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9056205749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2329235076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4978828430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1914501190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9888324737549</t>
   </si>
   <si>
     <t xml:space="preserve">20.1213150024414</t>
@@ -779,16 +779,16 @@
     <t xml:space="preserve">19.9732494354248</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9551563262939</t>
+    <t xml:space="preserve">20.9551582336426</t>
   </si>
   <si>
     <t xml:space="preserve">20.6278553009033</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2201175689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0408802032471</t>
+    <t xml:space="preserve">21.2201156616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0408782958984</t>
   </si>
   <si>
     <t xml:space="preserve">20.7915058135986</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">20.7447490692139</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8616409301758</t>
+    <t xml:space="preserve">20.8616428375244</t>
   </si>
   <si>
     <t xml:space="preserve">21.2434959411621</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9006042480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0330867767334</t>
+    <t xml:space="preserve">20.9006080627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0330829620361</t>
   </si>
   <si>
     <t xml:space="preserve">20.978536605835</t>
@@ -815,31 +815,31 @@
     <t xml:space="preserve">21.6721038818359</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4149398803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3136310577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1967391967773</t>
+    <t xml:space="preserve">21.4149379730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3136329650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1967353820801</t>
   </si>
   <si>
     <t xml:space="preserve">21.4227313995361</t>
   </si>
   <si>
-    <t xml:space="preserve">21.578592300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1884708404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1002006530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.947732925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0279788970947</t>
+    <t xml:space="preserve">21.5785903930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1884727478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1002025604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9477291107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0279808044434</t>
   </si>
   <si>
     <t xml:space="preserve">21.9878520965576</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">22.348970413208</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4693412780762</t>
+    <t xml:space="preserve">22.4693393707275</t>
   </si>
   <si>
     <t xml:space="preserve">22.8946533203125</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">23.3199615478516</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2878684997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8786029815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0310726165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4483585357666</t>
+    <t xml:space="preserve">23.2878646850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.878604888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0310745239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4483604431152</t>
   </si>
   <si>
     <t xml:space="preserve">23.0230484008789</t>
@@ -878,103 +878,103 @@
     <t xml:space="preserve">22.9026775360107</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6218128204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5014419555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2557678222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8434066772461</t>
+    <t xml:space="preserve">22.6218090057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5014400482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2557640075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8434047698975</t>
   </si>
   <si>
     <t xml:space="preserve">22.0600776672363</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6298370361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7341556549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9267539978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2316951751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1434211730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1674957275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6570053100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7693519592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6730499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8495998382568</t>
+    <t xml:space="preserve">22.6298351287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7341575622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9267520904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2316913604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1434192657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1674938201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.65700340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7693538665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6730556488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8495960235596</t>
   </si>
   <si>
     <t xml:space="preserve">23.7613277435303</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4002151489258</t>
+    <t xml:space="preserve">23.4002132415771</t>
   </si>
   <si>
     <t xml:space="preserve">23.2958908081055</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4323101043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7051563262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0069999694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8304538726807</t>
+    <t xml:space="preserve">23.4323120117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7051525115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0069980621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.830451965332</t>
   </si>
   <si>
     <t xml:space="preserve">22.7903289794922</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0631732940674</t>
+    <t xml:space="preserve">23.0631713867188</t>
   </si>
   <si>
     <t xml:space="preserve">23.8255252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3921852111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2637920379639</t>
+    <t xml:space="preserve">23.3921890258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2637901306152</t>
   </si>
   <si>
     <t xml:space="preserve">23.2718162536621</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1915702819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9989738464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9076061248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0199565887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0761280059814</t>
+    <t xml:space="preserve">23.1915683746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9989757537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9076080322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0199546813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0761241912842</t>
   </si>
   <si>
     <t xml:space="preserve">21.554515838623</t>
@@ -986,7 +986,7 @@
     <t xml:space="preserve">21.6267414093018</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7711868286133</t>
+    <t xml:space="preserve">21.7711849212646</t>
   </si>
   <si>
     <t xml:space="preserve">21.7390880584717</t>
@@ -995,19 +995,19 @@
     <t xml:space="preserve">21.8674831390381</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8594570159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5255126953125</t>
+    <t xml:space="preserve">21.8594589233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5255146026611</t>
   </si>
   <si>
     <t xml:space="preserve">22.7421817779541</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3730430603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7181072235107</t>
+    <t xml:space="preserve">22.3730411529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7181091308594</t>
   </si>
   <si>
     <t xml:space="preserve">22.8625526428223</t>
@@ -1016,28 +1016,28 @@
     <t xml:space="preserve">22.7100811004639</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5335388183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6539096832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2927951812744</t>
+    <t xml:space="preserve">22.5335369110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6539077758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.292797088623</t>
   </si>
   <si>
     <t xml:space="preserve">21.7551345825195</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2415504455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9927806854248</t>
+    <t xml:space="preserve">21.2415523529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9927845001221</t>
   </si>
   <si>
     <t xml:space="preserve">20.9446334838867</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0730323791504</t>
+    <t xml:space="preserve">21.073034286499</t>
   </si>
   <si>
     <t xml:space="preserve">21.0489559173584</t>
@@ -1046,22 +1046,22 @@
     <t xml:space="preserve">20.6396942138672</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4310512542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4872245788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8804359436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8643856048584</t>
+    <t xml:space="preserve">20.4310493469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4872226715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8804378509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.864387512207</t>
   </si>
   <si>
     <t xml:space="preserve">20.7119159698486</t>
   </si>
   <si>
-    <t xml:space="preserve">20.575496673584</t>
+    <t xml:space="preserve">20.5754928588867</t>
   </si>
   <si>
     <t xml:space="preserve">20.5995712280273</t>
@@ -1070,25 +1070,25 @@
     <t xml:space="preserve">20.6477184295654</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6156215667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5915431976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3508033752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3427772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2866039276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7440185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6717948913574</t>
+    <t xml:space="preserve">20.6156196594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5915470123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3508052825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3427791595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2866058349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7440166473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6717910766602</t>
   </si>
   <si>
     <t xml:space="preserve">20.4952487945557</t>
@@ -1100,16 +1100,16 @@
     <t xml:space="preserve">21.2174777984619</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0168552398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3539009094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2335243225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9045104980469</t>
+    <t xml:space="preserve">21.0168590545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3538970947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2335262298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9045124053955</t>
   </si>
   <si>
     <t xml:space="preserve">20.5594463348389</t>
@@ -1118,28 +1118,28 @@
     <t xml:space="preserve">20.5353717803955</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4711723327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7520389556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3779735565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0650043487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2255039215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.369945526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9156322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4582176208496</t>
+    <t xml:space="preserve">20.4711761474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7520427703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3779716491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0650081634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2255020141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3699436187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9156284332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4582195281982</t>
   </si>
   <si>
     <t xml:space="preserve">21.8032836914062</t>
@@ -1151,52 +1151,52 @@
     <t xml:space="preserve">22.3088436126709</t>
   </si>
   <si>
-    <t xml:space="preserve">22.140323638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2285938262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2045230865479</t>
+    <t xml:space="preserve">22.1403255462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2285976409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2045249938965</t>
   </si>
   <si>
     <t xml:space="preserve">22.1483516693115</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6940326690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0921783447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1082210540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1643981933594</t>
+    <t xml:space="preserve">22.694034576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0921764373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1082229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.164400100708</t>
   </si>
   <si>
     <t xml:space="preserve">22.7742786407471</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7662563323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5897121429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5415649414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4131641387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5174865722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1563720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8353824615479</t>
+    <t xml:space="preserve">22.7662582397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5897102355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5415630340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4131660461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5174884796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1563739776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8353843688965</t>
   </si>
   <si>
     <t xml:space="preserve">22.5495872497559</t>
@@ -1205,34 +1205,34 @@
     <t xml:space="preserve">22.2526683807373</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2125453948975</t>
+    <t xml:space="preserve">22.2125511169434</t>
   </si>
   <si>
     <t xml:space="preserve">19.2594337463379</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9335174560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.861291885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6927719116211</t>
+    <t xml:space="preserve">19.9335155487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8612880706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6927680969238</t>
   </si>
   <si>
     <t xml:space="preserve">19.620548248291</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5403022766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4921550750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4279537200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7409172058105</t>
+    <t xml:space="preserve">19.5403003692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.492151260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4279518127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7409191131592</t>
   </si>
   <si>
     <t xml:space="preserve">19.676721572876</t>
@@ -1241,64 +1241,64 @@
     <t xml:space="preserve">19.805118560791</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4199314117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7569694519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6606750488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1421585083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2304306030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4069786071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4791965484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2545032501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9415397644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0619125366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9254894256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9366092681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0971050262451</t>
+    <t xml:space="preserve">19.4199295043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7569713592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6606712341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1421604156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2304344177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4069766998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4791984558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2545051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9415378570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0619106292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9254913330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9366130828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0971088409424</t>
   </si>
   <si>
     <t xml:space="preserve">20.8162403106689</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3989486694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6878433227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4390735626221</t>
+    <t xml:space="preserve">20.3989524841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6878452301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4390754699707</t>
   </si>
   <si>
     <t xml:space="preserve">20.2464790344238</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4631500244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5433959960938</t>
+    <t xml:space="preserve">20.4631519317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.543399810791</t>
   </si>
   <si>
     <t xml:space="preserve">21.4100723266602</t>
@@ -1319,34 +1319,34 @@
     <t xml:space="preserve">21.506368637085</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4421710968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9606838226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3458728790283</t>
+    <t xml:space="preserve">21.4421691894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9606857299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.345874786377</t>
   </si>
   <si>
     <t xml:space="preserve">21.0890808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6989650726318</t>
+    <t xml:space="preserve">21.6989631652832</t>
   </si>
   <si>
     <t xml:space="preserve">21.8113098144531</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7792072296143</t>
+    <t xml:space="preserve">21.7792110443115</t>
   </si>
   <si>
     <t xml:space="preserve">21.394021987915</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7471141815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2495765686035</t>
+    <t xml:space="preserve">21.7471103668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2495746612549</t>
   </si>
   <si>
     <t xml:space="preserve">19.5322761535645</t>
@@ -1355,58 +1355,58 @@
     <t xml:space="preserve">19.3236331939697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5001754760742</t>
+    <t xml:space="preserve">19.5001735687256</t>
   </si>
   <si>
     <t xml:space="preserve">19.5162258148193</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0458602905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0940093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7248687744141</t>
+    <t xml:space="preserve">20.045862197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0940113067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7248668670654</t>
   </si>
   <si>
     <t xml:space="preserve">19.7088222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">19.403881072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.484130859375</t>
+    <t xml:space="preserve">19.4038791656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4841270446777</t>
   </si>
   <si>
     <t xml:space="preserve">19.1631355285645</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8260974884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6014041900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0075702667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5853538513184</t>
+    <t xml:space="preserve">18.8260936737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6014022827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0075740814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.585355758667</t>
   </si>
   <si>
     <t xml:space="preserve">18.7137508392334</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9977111816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1261100769043</t>
+    <t xml:space="preserve">19.9977130889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1261081695557</t>
   </si>
   <si>
     <t xml:space="preserve">20.7199420928955</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1903057098389</t>
+    <t xml:space="preserve">20.1903076171875</t>
   </si>
   <si>
     <t xml:space="preserve">19.7730178833008</t>
@@ -1418,58 +1418,58 @@
     <t xml:space="preserve">19.8211669921875</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4359798431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1310386657715</t>
+    <t xml:space="preserve">19.435977935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1310367584229</t>
   </si>
   <si>
     <t xml:space="preserve">19.3557319641113</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5483283996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9174652099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5804271697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0186901092529</t>
+    <t xml:space="preserve">19.5483245849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9174633026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5804214477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0186920166016</t>
   </si>
   <si>
     <t xml:space="preserve">19.0026416778564</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8421478271484</t>
+    <t xml:space="preserve">18.8421459197998</t>
   </si>
   <si>
     <t xml:space="preserve">19.0828895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8853664398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5112953186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1582126617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8936672210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6596565246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5760803222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6763725280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7265148162842</t>
+    <t xml:space="preserve">19.8853645324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5112991333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1582088470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8936653137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6596546173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5760841369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6763706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7265167236328</t>
   </si>
   <si>
     <t xml:space="preserve">20.8435211181641</t>
@@ -1481,55 +1481,55 @@
     <t xml:space="preserve">21.4954032897949</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1276779174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2781085968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1778202056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0942478179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9772396087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7766609191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4757900238037</t>
+    <t xml:space="preserve">21.1276760101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2781066894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1778182983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0942459106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9772415161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7766628265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.475793838501</t>
   </si>
   <si>
     <t xml:space="preserve">20.6429424285889</t>
   </si>
   <si>
-    <t xml:space="preserve">20.525936126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2584991455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.12477684021</t>
+    <t xml:space="preserve">20.5259380340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2584972381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1247787475586</t>
   </si>
   <si>
     <t xml:space="preserve">20.1916389465332</t>
   </si>
   <si>
-    <t xml:space="preserve">19.924201965332</t>
+    <t xml:space="preserve">19.9241981506348</t>
   </si>
   <si>
     <t xml:space="preserve">19.5063247680664</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2417831420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8769474029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7933769226074</t>
+    <t xml:space="preserve">20.2417812347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8769493103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7933750152588</t>
   </si>
   <si>
     <t xml:space="preserve">20.993953704834</t>
@@ -1541,7 +1541,7 @@
     <t xml:space="preserve">20.5927963256836</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6930885314941</t>
+    <t xml:space="preserve">20.6930847167969</t>
   </si>
   <si>
     <t xml:space="preserve">20.3420715332031</t>
@@ -1553,10 +1553,10 @@
     <t xml:space="preserve">20.5593662261963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7570514678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8740558624268</t>
+    <t xml:space="preserve">19.7570476531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8740539550781</t>
   </si>
   <si>
     <t xml:space="preserve">20.1414947509766</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">20.0244903564453</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9409160614014</t>
+    <t xml:space="preserve">19.9409122467041</t>
   </si>
   <si>
     <t xml:space="preserve">20.1080627441406</t>
@@ -1589,7 +1589,7 @@
     <t xml:space="preserve">20.074634552002</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8239097595215</t>
+    <t xml:space="preserve">19.8239116668701</t>
   </si>
   <si>
     <t xml:space="preserve">19.6901893615723</t>
@@ -1604,16 +1604,16 @@
     <t xml:space="preserve">22.3144340515137</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1000366210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2003269195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2671852111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5847663879395</t>
+    <t xml:space="preserve">23.1000347137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.200325012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.267183303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5847682952881</t>
   </si>
   <si>
     <t xml:space="preserve">23.5346221923828</t>
@@ -1625,73 +1625,73 @@
     <t xml:space="preserve">22.8660278320312</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7991676330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8325977325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5484428405762</t>
+    <t xml:space="preserve">22.799165725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8325958251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5484447479248</t>
   </si>
   <si>
     <t xml:space="preserve">22.6153030395508</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9328899383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1167526245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1501789093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2504692077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4009037017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6181983947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5011959075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3841896057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.283899307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0833225250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8994579315186</t>
+    <t xml:space="preserve">22.9328880310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1167488098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1501808166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2504711151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4009056091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.618200302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5011940002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3841876983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2839031219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0833206176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8994560241699</t>
   </si>
   <si>
     <t xml:space="preserve">22.5651588439941</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5818748474121</t>
+    <t xml:space="preserve">22.5818767547607</t>
   </si>
   <si>
     <t xml:space="preserve">22.331148147583</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8158798217773</t>
+    <t xml:space="preserve">22.815881729126</t>
   </si>
   <si>
     <t xml:space="preserve">22.5317287445068</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1334667205811</t>
+    <t xml:space="preserve">23.1334686279297</t>
   </si>
   <si>
     <t xml:space="preserve">22.9663181304932</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6850547790527</t>
+    <t xml:space="preserve">23.6850605010986</t>
   </si>
   <si>
     <t xml:space="preserve">23.3006153106689</t>
@@ -1703,55 +1703,55 @@
     <t xml:space="preserve">22.9997463226318</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8493137359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9496021270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7628421783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.461971282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0441017150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7098026275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.91037940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6625537872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2279663085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4285411834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.927095413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3616809844971</t>
+    <t xml:space="preserve">22.8493118286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9496002197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7628402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4619750976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0440979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7098007202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9103813171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6625518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2279605865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4285430908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9270973205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3616828918457</t>
   </si>
   <si>
     <t xml:space="preserve">21.5121173858643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9605274200439</t>
+    <t xml:space="preserve">20.9605236053467</t>
   </si>
   <si>
     <t xml:space="preserve">19.8573417663574</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5397529602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9547348022461</t>
+    <t xml:space="preserve">19.5397548675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9547328948975</t>
   </si>
   <si>
     <t xml:space="preserve">19.556468963623</t>
@@ -1763,7 +1763,7 @@
     <t xml:space="preserve">19.4394664764404</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3893222808838</t>
+    <t xml:space="preserve">19.3893203735352</t>
   </si>
   <si>
     <t xml:space="preserve">19.2556037902832</t>
@@ -1772,37 +1772,37 @@
     <t xml:space="preserve">19.3057479858398</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3726043701172</t>
+    <t xml:space="preserve">19.3726062774658</t>
   </si>
   <si>
     <t xml:space="preserve">18.8043003082275</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6037178039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6872940063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6705780029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.704008102417</t>
+    <t xml:space="preserve">18.6037216186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6872959136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6705799102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7040100097656</t>
   </si>
   <si>
     <t xml:space="preserve">18.8878746032715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2221736907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6734752655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.656759262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8907699584961</t>
+    <t xml:space="preserve">19.2221717834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6734771728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6567611694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8907680511475</t>
   </si>
   <si>
     <t xml:space="preserve">20.0913505554199</t>
@@ -1811,16 +1811,16 @@
     <t xml:space="preserve">19.8406238555908</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5899028778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0884532928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7737636566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.640043258667</t>
+    <t xml:space="preserve">19.589900970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.088451385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7737655639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6400451660156</t>
   </si>
   <si>
     <t xml:space="preserve">19.4561824798584</t>
@@ -1829,16 +1829,16 @@
     <t xml:space="preserve">18.9213027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3391780853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5201454162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5506782531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0019855499268</t>
+    <t xml:space="preserve">19.3391761779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5201435089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5506763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0019836425781</t>
   </si>
   <si>
     <t xml:space="preserve">17.9016914367676</t>
@@ -1847,40 +1847,40 @@
     <t xml:space="preserve">18.4699993133545</t>
   </si>
   <si>
-    <t xml:space="preserve">18.235990524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4365692138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0412006378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3086414337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.991060256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3253555297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2861366271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2694225311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2192764282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4198570251465</t>
+    <t xml:space="preserve">18.2359886169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4365711212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0412063598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3086395263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9910583496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3253574371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2861347198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2694206237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.219274520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4198551177979</t>
   </si>
   <si>
     <t xml:space="preserve">18.6538639068604</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2527046203613</t>
+    <t xml:space="preserve">18.25270652771</t>
   </si>
   <si>
     <t xml:space="preserve">18.3529949188232</t>
@@ -1889,7 +1889,7 @@
     <t xml:space="preserve">18.5368595123291</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7541542053223</t>
+    <t xml:space="preserve">18.7541561126709</t>
   </si>
   <si>
     <t xml:space="preserve">18.6371479034424</t>
@@ -1898,43 +1898,43 @@
     <t xml:space="preserve">19.1553134918213</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4060344696045</t>
+    <t xml:space="preserve">19.4060363769531</t>
   </si>
   <si>
     <t xml:space="preserve">19.2723159790039</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9714488983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3558902740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0215930938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3224639892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7403373718262</t>
+    <t xml:space="preserve">18.9714469909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3558940887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0215911865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3224620819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7403354644775</t>
   </si>
   <si>
     <t xml:space="preserve">20.1749229431152</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7875843048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9380168914795</t>
+    <t xml:space="preserve">18.7875823974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9380187988281</t>
   </si>
   <si>
     <t xml:space="preserve">20.0077743530273</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2250709533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5789794921875</t>
+    <t xml:space="preserve">20.2250690460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5789775848389</t>
   </si>
   <si>
     <t xml:space="preserve">21.1443881988525</t>
@@ -1943,136 +1943,136 @@
     <t xml:space="preserve">19.2054557800293</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0354118347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6509685516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4336738586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5841083526611</t>
+    <t xml:space="preserve">18.0354099273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6509704589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4336757659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5841102600098</t>
   </si>
   <si>
     <t xml:space="preserve">17.1328048706055</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5477828979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1716957092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9961891174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3221282958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8791856765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7939519882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7683820724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7769041061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3081140518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4018697738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4359655380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5382461547852</t>
+    <t xml:space="preserve">16.5477848052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1716976165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9961910247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3221321105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8791847229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7939510345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7683811187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7769050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3081130981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4018707275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4359664916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5382490158081</t>
   </si>
   <si>
     <t xml:space="preserve">15.1632175445557</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3336839675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0524101257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1717376708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.350733757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5552921295166</t>
+    <t xml:space="preserve">15.3336849212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0524082183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1717405319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3507308959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5552940368652</t>
   </si>
   <si>
     <t xml:space="preserve">15.6405296325684</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6490516662598</t>
+    <t xml:space="preserve">15.6490535736084</t>
   </si>
   <si>
     <t xml:space="preserve">15.6320056915283</t>
   </si>
   <si>
-    <t xml:space="preserve">15.580864906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4103965759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0609359741211</t>
+    <t xml:space="preserve">15.5808658599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4103946685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0609321594238</t>
   </si>
   <si>
     <t xml:space="preserve">14.8904638290405</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9842233657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0438871383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3763027191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4274415969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2825450897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0865058898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1120729446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1546926498413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3251619338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3592548370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9671783447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7455644607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6091918945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6518087387085</t>
+    <t xml:space="preserve">14.984224319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0438852310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3763017654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4274444580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.282546043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0865049362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1120738983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1546936035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3251628875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3592538833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9671764373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7455654144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6091909408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6518077850342</t>
   </si>
   <si>
     <t xml:space="preserve">14.515435218811</t>
@@ -2081,49 +2081,49 @@
     <t xml:space="preserve">14.7114706039429</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6347608566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5410041809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3534879684448</t>
+    <t xml:space="preserve">14.6347627639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5410013198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3534889221191</t>
   </si>
   <si>
     <t xml:space="preserve">14.3449640274048</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4472465515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4387216567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7540893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4642925262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4813385009766</t>
+    <t xml:space="preserve">14.4472455978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.438720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7540903091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4642915725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4813413619995</t>
   </si>
   <si>
     <t xml:space="preserve">14.3620119094849</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2484464645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4956293106079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0268383026123</t>
+    <t xml:space="preserve">15.2484502792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4956312179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0268392562866</t>
   </si>
   <si>
     <t xml:space="preserve">15.0012702941895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6859016418457</t>
+    <t xml:space="preserve">14.68590259552</t>
   </si>
   <si>
     <t xml:space="preserve">14.5324811935425</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">15.0353631973267</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1376447677612</t>
+    <t xml:space="preserve">15.1376485824585</t>
   </si>
   <si>
     <t xml:space="preserve">14.8308019638062</t>
@@ -2147,13 +2147,13 @@
     <t xml:space="preserve">14.9586515426636</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2399263381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.810996055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4843482971191</t>
+    <t xml:space="preserve">15.2399244308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8109951019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4843521118164</t>
   </si>
   <si>
     <t xml:space="preserve">17.0468978881836</t>
@@ -2168,43 +2168,43 @@
     <t xml:space="preserve">17.0128040313721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5781078338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3138790130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2371711730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9303255081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9218053817749</t>
+    <t xml:space="preserve">16.5781097412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3138809204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2371692657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9303274154663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9218044281006</t>
   </si>
   <si>
     <t xml:space="preserve">15.393346786499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9416074752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5239591598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9330816268921</t>
+    <t xml:space="preserve">14.9416055679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5239582061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9330835342407</t>
   </si>
   <si>
     <t xml:space="preserve">14.6603326797485</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2512054443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1318778991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.617714881897</t>
+    <t xml:space="preserve">14.2512044906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1318788528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6177139282227</t>
   </si>
   <si>
     <t xml:space="preserve">14.4557676315308</t>
@@ -2213,25 +2213,25 @@
     <t xml:space="preserve">14.5580501556396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5750961303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7370433807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7796592712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8393230438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8478469848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6688537597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2341623306274</t>
+    <t xml:space="preserve">14.5750980377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7370443344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7796611785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8393249511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8478479385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6688547134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2341604232788</t>
   </si>
   <si>
     <t xml:space="preserve">14.14040184021</t>
@@ -2240,103 +2240,103 @@
     <t xml:space="preserve">14.0636911392212</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8222770690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6262378692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0183162689209</t>
+    <t xml:space="preserve">14.8222789764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.626238822937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0183172225952</t>
   </si>
   <si>
     <t xml:space="preserve">15.1291208267212</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2058334350586</t>
+    <t xml:space="preserve">15.2058305740356</t>
   </si>
   <si>
     <t xml:space="preserve">15.5467700958252</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8195180892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0326061248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4502544403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4928722381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0155601501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1519355773926</t>
+    <t xml:space="preserve">15.8195190429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0326080322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4502563476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4928703308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0155620574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1519374847412</t>
   </si>
   <si>
     <t xml:space="preserve">16.2030754089355</t>
   </si>
   <si>
-    <t xml:space="preserve">16.041130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0752239227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8962335586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2883110046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2627391815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1263637542725</t>
+    <t xml:space="preserve">16.0411319732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0752258300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8962326049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2883129119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2627410888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1263656616211</t>
   </si>
   <si>
     <t xml:space="preserve">16.1178417205811</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1945533752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.228645324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1689834594727</t>
+    <t xml:space="preserve">16.1945514678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2286472320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.168981552124</t>
   </si>
   <si>
     <t xml:space="preserve">16.0666999816895</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2797870635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1093158721924</t>
+    <t xml:space="preserve">16.2797889709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1093196868896</t>
   </si>
   <si>
     <t xml:space="preserve">15.7087144851685</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6746225357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9729413986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7428102493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3422079086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2910690307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.103551864624</t>
+    <t xml:space="preserve">15.6746234893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9729452133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.74280834198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3422069549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2910680770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1035509109497</t>
   </si>
   <si>
     <t xml:space="preserve">14.566575050354</t>
@@ -2348,13 +2348,13 @@
     <t xml:space="preserve">14.2426815032959</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5949001312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7057046890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6944274902344</t>
+    <t xml:space="preserve">13.5949010848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7057056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6944255828857</t>
   </si>
   <si>
     <t xml:space="preserve">14.5069103240967</t>
@@ -2366,16 +2366,16 @@
     <t xml:space="preserve">15.4615364074707</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4444904327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4700584411621</t>
+    <t xml:space="preserve">15.4444885253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4700603485107</t>
   </si>
   <si>
     <t xml:space="preserve">15.6149597167969</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2740211486816</t>
+    <t xml:space="preserve">15.2740201950073</t>
   </si>
   <si>
     <t xml:space="preserve">15.2995910644531</t>
@@ -2384,28 +2384,28 @@
     <t xml:space="preserve">13.7142295837402</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3818140029907</t>
+    <t xml:space="preserve">13.381814956665</t>
   </si>
   <si>
     <t xml:space="preserve">13.5522832870483</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1772518157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2965793609619</t>
+    <t xml:space="preserve">13.1772527694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2965803146362</t>
   </si>
   <si>
     <t xml:space="preserve">13.2624864578247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0323534011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7596035003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6232280731201</t>
+    <t xml:space="preserve">13.0323543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7596025466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6232290267944</t>
   </si>
   <si>
     <t xml:space="preserve">12.3590002059937</t>
@@ -2414,46 +2414,46 @@
     <t xml:space="preserve">11.6600770950317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1912889480591</t>
+    <t xml:space="preserve">11.1912879943848</t>
   </si>
   <si>
     <t xml:space="preserve">10.8333044052124</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74230098724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6543102264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6430311203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8220243453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6686010360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0351104736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3306741714478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7227544784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2767782211304</t>
+    <t xml:space="preserve">9.74230289459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6543121337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6430320739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8220233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6686019897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0351095199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3306732177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7227535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2767763137817</t>
   </si>
   <si>
     <t xml:space="preserve">13.0749702453613</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5011434555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4500007629395</t>
+    <t xml:space="preserve">13.5011425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4500017166138</t>
   </si>
   <si>
     <t xml:space="preserve">12.9897356033325</t>
@@ -2462,13 +2462,13 @@
     <t xml:space="preserve">13.0834941864014</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1175880432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4953746795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0238285064697</t>
+    <t xml:space="preserve">13.1175870895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4953765869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0238313674927</t>
   </si>
   <si>
     <t xml:space="preserve">13.3562450408936</t>
@@ -2477,16 +2477,16 @@
     <t xml:space="preserve">13.4244327545166</t>
   </si>
   <si>
-    <t xml:space="preserve">13.61194896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8192672729492</t>
+    <t xml:space="preserve">13.6119480133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8192682266235</t>
   </si>
   <si>
     <t xml:space="preserve">12.6999378204346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.904501914978</t>
+    <t xml:space="preserve">12.9045009613037</t>
   </si>
   <si>
     <t xml:space="preserve">13.0664472579956</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">13.2113456726074</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3988618850708</t>
+    <t xml:space="preserve">13.3988628387451</t>
   </si>
   <si>
     <t xml:space="preserve">13.313627243042</t>
@@ -2504,16 +2504,16 @@
     <t xml:space="preserve">13.8079872131348</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8932209014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9358386993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0551662445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8846979141235</t>
+    <t xml:space="preserve">13.8932199478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9358406066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0551671981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8846998214722</t>
   </si>
   <si>
     <t xml:space="preserve">14.4898633956909</t>
@@ -2522,37 +2522,37 @@
     <t xml:space="preserve">14.7029476165771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2000665664673</t>
+    <t xml:space="preserve">14.200065612793</t>
   </si>
   <si>
     <t xml:space="preserve">14.4983863830566</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4131536483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1205987930298</t>
+    <t xml:space="preserve">14.4131517410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1205978393555</t>
   </si>
   <si>
     <t xml:space="preserve">14.7711381912231</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8563709259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4189195632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9388475418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7513341903687</t>
+    <t xml:space="preserve">14.856372833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4189186096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9388513565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.75133228302</t>
   </si>
   <si>
     <t xml:space="preserve">16.6207237243652</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4161605834961</t>
+    <t xml:space="preserve">16.4161643981934</t>
   </si>
   <si>
     <t xml:space="preserve">16.2456912994385</t>
@@ -2561,13 +2561,13 @@
     <t xml:space="preserve">16.5440139770508</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7826690673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3707885742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4276962280273</t>
+    <t xml:space="preserve">16.7826728820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3707866668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.427698135376</t>
   </si>
   <si>
     <t xml:space="preserve">19.2629947662354</t>
@@ -2576,19 +2576,19 @@
     <t xml:space="preserve">19.0754795074463</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6493072509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9050121307373</t>
+    <t xml:space="preserve">18.6493053436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9050102233887</t>
   </si>
   <si>
     <t xml:space="preserve">19.603931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6380271911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0641975402832</t>
+    <t xml:space="preserve">19.6380290985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0641994476318</t>
   </si>
   <si>
     <t xml:space="preserve">19.8766841888428</t>
@@ -2597,28 +2597,28 @@
     <t xml:space="preserve">19.7744007110596</t>
   </si>
   <si>
-    <t xml:space="preserve">20.149435043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0471515655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4846019744873</t>
+    <t xml:space="preserve">20.1494331359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0471534729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4846057891846</t>
   </si>
   <si>
     <t xml:space="preserve">19.8425903320312</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8084926605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7119808197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9506378173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6778888702393</t>
+    <t xml:space="preserve">19.8084964752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7119789123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9506359100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6778869628906</t>
   </si>
   <si>
     <t xml:space="preserve">20.8483562469482</t>
@@ -2630,49 +2630,49 @@
     <t xml:space="preserve">21.0529193878174</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9335918426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0870132446289</t>
+    <t xml:space="preserve">20.9335899353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0870094299316</t>
   </si>
   <si>
     <t xml:space="preserve">21.1551990509033</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2915725708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2574825286865</t>
+    <t xml:space="preserve">21.291576385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2574806213379</t>
   </si>
   <si>
     <t xml:space="preserve">21.2233867645264</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0699653625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3086204528809</t>
+    <t xml:space="preserve">21.0699634552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3086242675781</t>
   </si>
   <si>
     <t xml:space="preserve">20.8994960784912</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9676856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7631244659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9165420532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1609687805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6382789611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0133113861084</t>
+    <t xml:space="preserve">20.9676837921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7631225585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9165458679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1609668731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6382808685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.013313293457</t>
   </si>
   <si>
     <t xml:space="preserve">23.9167957305908</t>
@@ -2681,16 +2681,16 @@
     <t xml:space="preserve">23.8145160675049</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9679412841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0020313262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5758590698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8656578063965</t>
+    <t xml:space="preserve">23.9679393768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0020294189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5758571624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8656558990479</t>
   </si>
   <si>
     <t xml:space="preserve">23.7974700927734</t>
@@ -2702,13 +2702,13 @@
     <t xml:space="preserve">23.5929069519043</t>
   </si>
   <si>
-    <t xml:space="preserve">23.661096572876</t>
+    <t xml:space="preserve">23.6610946655273</t>
   </si>
   <si>
     <t xml:space="preserve">23.8486099243164</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6781425476074</t>
+    <t xml:space="preserve">23.6781406402588</t>
   </si>
   <si>
     <t xml:space="preserve">23.4394855499268</t>
@@ -2717,28 +2717,28 @@
     <t xml:space="preserve">23.7292823791504</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7463283538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6951866149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4906253814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7633743286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1496887207031</t>
+    <t xml:space="preserve">23.7463302612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6951885223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4906234741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7633762359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1496868133545</t>
   </si>
   <si>
     <t xml:space="preserve">23.9849853515625</t>
   </si>
   <si>
-    <t xml:space="preserve">23.899751663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4963893890381</t>
+    <t xml:space="preserve">23.8997497558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4963932037354</t>
   </si>
   <si>
     <t xml:space="preserve">25.2123622894287</t>
@@ -2747,34 +2747,34 @@
     <t xml:space="preserve">24.5304870605469</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1100788116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0647068023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4680652618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5533008575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4851150512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1271266937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0589389801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0759868621826</t>
+    <t xml:space="preserve">25.1100769042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0647087097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4680633544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5532970428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4851112365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.127124786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0589408874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0759887695312</t>
   </si>
   <si>
     <t xml:space="preserve">24.8202838897705</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8884716033936</t>
+    <t xml:space="preserve">24.8884735107422</t>
   </si>
   <si>
     <t xml:space="preserve">25.1953144073486</t>
@@ -2786,13 +2786,13 @@
     <t xml:space="preserve">25.3487377166748</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2294082641602</t>
+    <t xml:space="preserve">25.2294101715088</t>
   </si>
   <si>
     <t xml:space="preserve">25.4339714050293</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3657836914062</t>
+    <t xml:space="preserve">25.3657855987549</t>
   </si>
   <si>
     <t xml:space="preserve">25.9453773498535</t>
@@ -2801,31 +2801,31 @@
     <t xml:space="preserve">26.8829574584961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7636280059814</t>
+    <t xml:space="preserve">26.7636299133301</t>
   </si>
   <si>
     <t xml:space="preserve">26.0306148529053</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9283332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0135631561279</t>
+    <t xml:space="preserve">25.9283313751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0135669708252</t>
   </si>
   <si>
     <t xml:space="preserve">25.1441745758057</t>
   </si>
   <si>
-    <t xml:space="preserve">24.956657409668</t>
+    <t xml:space="preserve">24.9566593170166</t>
   </si>
   <si>
     <t xml:space="preserve">23.4224376678467</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2690143585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.405387878418</t>
+    <t xml:space="preserve">23.2690162658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4053916931152</t>
   </si>
   <si>
     <t xml:space="preserve">23.4565315246582</t>
@@ -2834,43 +2834,43 @@
     <t xml:space="preserve">24.837329864502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0930309295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5703449249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6385345458984</t>
+    <t xml:space="preserve">25.0930366516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5703468322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6385364532471</t>
   </si>
   <si>
     <t xml:space="preserve">24.3600158691406</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1384086608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.911283493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5475311279297</t>
+    <t xml:space="preserve">24.13840675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9112815856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5475330352783</t>
   </si>
   <si>
     <t xml:space="preserve">23.831563949585</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5588130950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1213607788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5417652130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0985431671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2747802734375</t>
+    <t xml:space="preserve">23.5588111877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1213626861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5417671203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0985469818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2747821807861</t>
   </si>
   <si>
     <t xml:space="preserve">24.9396114349365</t>
@@ -2879,136 +2879,136 @@
     <t xml:space="preserve">24.2918281555176</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0702209472656</t>
+    <t xml:space="preserve">24.070219039917</t>
   </si>
   <si>
     <t xml:space="preserve">23.5076713562012</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3372020721436</t>
+    <t xml:space="preserve">23.3372039794922</t>
   </si>
   <si>
     <t xml:space="preserve">23.183780670166</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6894207000732</t>
+    <t xml:space="preserve">22.6894226074219</t>
   </si>
   <si>
     <t xml:space="preserve">23.1667327880859</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2860622406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2029094696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3768405914307</t>
+    <t xml:space="preserve">23.2860641479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2029075622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3768424987793</t>
   </si>
   <si>
     <t xml:space="preserve">22.6984958648682</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5941352844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8202476501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.420202255249</t>
+    <t xml:space="preserve">22.5941371917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8202514648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4202003479004</t>
   </si>
   <si>
     <t xml:space="preserve">22.7854633331299</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2898750305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8028564453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8724308013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7506771087646</t>
+    <t xml:space="preserve">23.2898769378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8028545379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.872428894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7506732940674</t>
   </si>
   <si>
     <t xml:space="preserve">22.7158908843994</t>
   </si>
   <si>
-    <t xml:space="preserve">22.246265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3332328796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4723796844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2550868988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5769939422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3596992492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5510272979736</t>
+    <t xml:space="preserve">22.2462635040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3332347869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4723815917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2550888061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5769901275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3596973419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.551025390625</t>
   </si>
   <si>
     <t xml:space="preserve">26.1945877075195</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4207000732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7597484588623</t>
+    <t xml:space="preserve">26.4207019805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7597522735596</t>
   </si>
   <si>
     <t xml:space="preserve">26.4033088684082</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0294723510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.186014175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1164436340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.012077331543</t>
+    <t xml:space="preserve">27.0294742584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1860160827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1164398193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0120792388916</t>
   </si>
   <si>
     <t xml:space="preserve">28.1426582336426</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8036079406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0992984771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3775939941406</t>
+    <t xml:space="preserve">28.8036098480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0993003845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.377592086792</t>
   </si>
   <si>
     <t xml:space="preserve">29.5863151550293</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0385475158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2210502624512</t>
+    <t xml:space="preserve">30.0385494232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2210521697998</t>
   </si>
   <si>
     <t xml:space="preserve">29.081901550293</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7688217163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4035568237305</t>
+    <t xml:space="preserve">28.7688236236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4035587310791</t>
   </si>
   <si>
     <t xml:space="preserve">27.6904258728027</t>
@@ -3017,16 +3017,16 @@
     <t xml:space="preserve">26.7859649658203</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5946369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.412130355835</t>
+    <t xml:space="preserve">26.5946350097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4121322631836</t>
   </si>
   <si>
     <t xml:space="preserve">26.6294231414795</t>
   </si>
   <si>
-    <t xml:space="preserve">27.620849609375</t>
+    <t xml:space="preserve">27.6208515167236</t>
   </si>
   <si>
     <t xml:space="preserve">26.6468162536621</t>
@@ -3038,67 +3038,67 @@
     <t xml:space="preserve">27.2034072875977</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3077659606934</t>
+    <t xml:space="preserve">27.3077697753906</t>
   </si>
   <si>
     <t xml:space="preserve">27.707820892334</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1081199645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1340885162354</t>
+    <t xml:space="preserve">30.108118057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1340847015381</t>
   </si>
   <si>
     <t xml:space="preserve">29.0471210479736</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2906265258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8905811309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3080196380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8560390472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7342872619629</t>
+    <t xml:space="preserve">29.2906246185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8905754089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3080215454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8560447692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7342853546143</t>
   </si>
   <si>
     <t xml:space="preserve">30.2298755645752</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3690185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4385986328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0559387207031</t>
+    <t xml:space="preserve">30.3690223693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4385967254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0559425354004</t>
   </si>
   <si>
     <t xml:space="preserve">30.2994480133057</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9515800476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6125297546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9951858520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6039581298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8300762176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5691680908203</t>
+    <t xml:space="preserve">29.9515781402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6125316619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9951877593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6039619445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8300704956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5691738128662</t>
   </si>
   <si>
     <t xml:space="preserve">31.8648624420166</t>
@@ -3113,121 +3113,121 @@
     <t xml:space="preserve">32.0387992858887</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6909236907959</t>
+    <t xml:space="preserve">31.6909255981445</t>
   </si>
   <si>
     <t xml:space="preserve">31.3430557250977</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4474182128906</t>
+    <t xml:space="preserve">31.447416305542</t>
   </si>
   <si>
     <t xml:space="preserve">31.2734813690186</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7605018615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7083206176758</t>
+    <t xml:space="preserve">31.7604999542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7083187103271</t>
   </si>
   <si>
     <t xml:space="preserve">31.5865669250488</t>
   </si>
   <si>
-    <t xml:space="preserve">31.743106842041</t>
+    <t xml:space="preserve">31.7431106567383</t>
   </si>
   <si>
     <t xml:space="preserve">31.6387481689453</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6735324859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3866653442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5605926513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8474712371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5432052612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8996486663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5169944763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7952899932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8126831054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6213569641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4822044372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3952369689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1553268432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9081134796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7845115661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1376686096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1729888916016</t>
+    <t xml:space="preserve">31.6735363006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3866691589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5606002807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8474655151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5432090759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8996524810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5169925689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7952919006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8126811981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6213474273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4822063446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3952388763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.155330657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9081153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7845058441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1376724243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1729850769043</t>
   </si>
   <si>
     <t xml:space="preserve">32.2612762451172</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2789344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7491931915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7668514251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8727970123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.667407989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0029144287109</t>
+    <t xml:space="preserve">32.278938293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7491912841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7668495178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8728008270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6674118041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0029182434082</t>
   </si>
   <si>
     <t xml:space="preserve">33.4443626403809</t>
   </si>
   <si>
-    <t xml:space="preserve">33.303108215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3096084594727</t>
+    <t xml:space="preserve">33.3031005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3096122741699</t>
   </si>
   <si>
     <t xml:space="preserve">34.9982757568359</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9806175231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2808074951172</t>
+    <t xml:space="preserve">34.9806213378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2808036804199</t>
   </si>
   <si>
     <t xml:space="preserve">34.786376953125</t>
@@ -3242,10 +3242,10 @@
     <t xml:space="preserve">33.3384170532227</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9499435424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1794967651367</t>
+    <t xml:space="preserve">32.9499397277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.179500579834</t>
   </si>
   <si>
     <t xml:space="preserve">33.2148094177246</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">32.437858581543</t>
   </si>
   <si>
-    <t xml:space="preserve">33.020580291748</t>
+    <t xml:space="preserve">33.0205764770508</t>
   </si>
   <si>
     <t xml:space="preserve">32.843994140625</t>
@@ -3269,13 +3269,13 @@
     <t xml:space="preserve">32.0317230224609</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3319091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7027244567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2677841186523</t>
+    <t xml:space="preserve">32.3319053649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7027320861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2677879333496</t>
   </si>
   <si>
     <t xml:space="preserve">33.4267082214355</t>
@@ -3287,31 +3287,31 @@
     <t xml:space="preserve">32.2083015441895</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2017955780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1135063171387</t>
+    <t xml:space="preserve">31.2017936706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1135025024414</t>
   </si>
   <si>
     <t xml:space="preserve">31.9610900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">33.126522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9322853088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9257698059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5438079833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0270843505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8681602478027</t>
+    <t xml:space="preserve">33.1265182495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9322814941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9257717132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5438041687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0270805358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8681640625</t>
   </si>
   <si>
     <t xml:space="preserve">34.0800552368164</t>
@@ -3326,19 +3326,19 @@
     <t xml:space="preserve">34.1330299377441</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5215034484863</t>
+    <t xml:space="preserve">34.5215110778809</t>
   </si>
   <si>
     <t xml:space="preserve">34.150691986084</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2036628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1153755187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9387893676758</t>
+    <t xml:space="preserve">34.2036666870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1153717041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.938793182373</t>
   </si>
   <si>
     <t xml:space="preserve">33.6209487915039</t>
@@ -3350,19 +3350,19 @@
     <t xml:space="preserve">34.2919540405273</t>
   </si>
   <si>
-    <t xml:space="preserve">34.503849029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.914623260498</t>
+    <t xml:space="preserve">34.5038528442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9146270751953</t>
   </si>
   <si>
     <t xml:space="preserve">33.1971549987793</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5149955749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5503120422363</t>
+    <t xml:space="preserve">33.5149993896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5503158569336</t>
   </si>
   <si>
     <t xml:space="preserve">33.815185546875</t>
@@ -3371,43 +3371,43 @@
     <t xml:space="preserve">34.6451148986816</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1395416259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8570098876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6804313659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0865631103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3272743225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2371101379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4248390197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1776237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0716800689697</t>
+    <t xml:space="preserve">35.139533996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8570137023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6804351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0865707397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3272705078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2371139526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4248371124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1776256561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0716781616211</t>
   </si>
   <si>
     <t xml:space="preserve">29.5595932006836</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6125679016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6478824615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2306022644043</t>
+    <t xml:space="preserve">29.6125659942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6478862762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2306003570557</t>
   </si>
   <si>
     <t xml:space="preserve">29.3476982116699</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">29.0121936798096</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2882118225098</t>
+    <t xml:space="preserve">28.2882137298584</t>
   </si>
   <si>
     <t xml:space="preserve">27.8467617034912</t>
@@ -3431,13 +3431,13 @@
     <t xml:space="preserve">28.09397315979</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7937870025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6348628997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0763168334961</t>
+    <t xml:space="preserve">27.7937889099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6348648071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0763149261475</t>
   </si>
   <si>
     <t xml:space="preserve">28.0410003662109</t>
@@ -3446,13 +3446,13 @@
     <t xml:space="preserve">28.3058738708496</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2240867614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1004848480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4713020324707</t>
+    <t xml:space="preserve">29.2240886688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1004829406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4713077545166</t>
   </si>
   <si>
     <t xml:space="preserve">29.1358013153076</t>
@@ -3467,61 +3467,61 @@
     <t xml:space="preserve">29.9480686187744</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7891521453857</t>
+    <t xml:space="preserve">29.7891502380371</t>
   </si>
   <si>
     <t xml:space="preserve">29.2417488098145</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8421230316162</t>
+    <t xml:space="preserve">29.8421211242676</t>
   </si>
   <si>
     <t xml:space="preserve">30.0010452270508</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9833869934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5661029815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9545822143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1952838897705</t>
+    <t xml:space="preserve">29.9833889007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5661010742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9545803070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1952819824219</t>
   </si>
   <si>
     <t xml:space="preserve">30.1246509552002</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3300399780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2287273406982</t>
+    <t xml:space="preserve">29.3300380706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2287311553955</t>
   </si>
   <si>
     <t xml:space="preserve">26.8402519226074</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9461994171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6106948852539</t>
+    <t xml:space="preserve">26.9462013244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6106967926025</t>
   </si>
   <si>
     <t xml:space="preserve">27.2817039489746</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7231540679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3876533508301</t>
+    <t xml:space="preserve">27.7231559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3876552581787</t>
   </si>
   <si>
     <t xml:space="preserve">26.6989860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8755683898926</t>
+    <t xml:space="preserve">26.8755702972412</t>
   </si>
   <si>
     <t xml:space="preserve">27.0698070526123</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">25.7807693481445</t>
   </si>
   <si>
-    <t xml:space="preserve">26.434118270874</t>
+    <t xml:space="preserve">26.4341163635254</t>
   </si>
   <si>
     <t xml:space="preserve">26.1162719726562</t>
@@ -3539,10 +3539,10 @@
     <t xml:space="preserve">26.85791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3634853363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1339302062988</t>
+    <t xml:space="preserve">26.3634834289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1339321136475</t>
   </si>
   <si>
     <t xml:space="preserve">26.3987998962402</t>
@@ -3554,16 +3554,16 @@
     <t xml:space="preserve">26.575382232666</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7519588470459</t>
+    <t xml:space="preserve">26.7519626617432</t>
   </si>
   <si>
     <t xml:space="preserve">26.310510635376</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4694309234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8225955963135</t>
+    <t xml:space="preserve">26.4694347381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8225936889648</t>
   </si>
   <si>
     <t xml:space="preserve">27.2110729217529</t>
@@ -3584,1947 +3584,1947 @@
     <t xml:space="preserve">27.8291053771973</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4053134918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7761287689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6525211334229</t>
+    <t xml:space="preserve">27.405309677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7761268615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6525249481201</t>
   </si>
   <si>
     <t xml:space="preserve">27.3699932098389</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4164600372314</t>
+    <t xml:space="preserve">26.4164581298828</t>
   </si>
   <si>
     <t xml:space="preserve">24.9155216217041</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0214729309082</t>
+    <t xml:space="preserve">25.0214710235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7212867736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8978672027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2686862945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5447025299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.10325050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8383808135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.692476272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4517726898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5112571716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9703674316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2993602752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9285430908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5289154052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4759426116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9638595581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3811416625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8932247161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1757545471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7872772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0986137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4629230499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8095760345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2333698272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1274185180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7389430999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1738834381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4080791473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4192295074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3662548065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6906070709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.066068649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9424610137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3551025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.772388458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7788982391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4610538482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2844715118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2314987182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8077049255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5251770019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4722003936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5604915618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.990795135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3374462127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8430213928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7547302246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7900466918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5958061218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3839111328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9601173400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1896724700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.136697769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4015712738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7658786773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8365116119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0595550537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9359512329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3774032592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5186653137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8653202056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0065841674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7835388183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5363235473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.041898727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1943130493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4238662719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7770290374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3420886993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3355770111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5474720001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6710815429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9111518859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0677719116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4711303710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1311645507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3878479003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9012107849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6995315551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3145122528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6445293426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0944976806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4061851501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1678371429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5811367034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.306116104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3710651397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7560882568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0127696990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0960502624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0861053466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.729362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9493751525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2801704406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.261833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1793308258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2343330383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0968227386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.757640838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2626075744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1617698669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1709384918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9875946044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3817863464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7851390838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0601558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.188497543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4635124206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9501495361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4092864990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6843013763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9043140411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0693225860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9593162536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1334934234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8676452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3359470367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8500871658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8218078613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5284595489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1151580810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8852043151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6560230255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6376876831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8859786987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4726791381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5643520355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6835250854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6651916503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2159976959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3351726531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9868183135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0784893035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8584766387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4001178741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9967622756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9417572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0425968170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0150947570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6392402648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9142560958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0525388717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2542181015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2175493240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1992158889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6117401123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0059280395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6942434310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9883699417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5758438110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5850114822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.860803604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8058004379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6041231155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3841104507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5857877731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7599649429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9249744415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3107719421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8149671554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5032815933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8883047103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5124502182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6591243743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3382730484009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4482793807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8516359329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5307846069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8424701690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1908226013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3466653823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.603346824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1816549301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5483427047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8233594894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5659017562866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7217454910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9050903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1526031494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7026348114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2434997558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.509349822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2427234649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5528583526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.717866897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4161262512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1594429016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0494384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.617805480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2595081329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7094764709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3794555664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.562801361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8928184509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6544742584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8561515808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4527969360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5261306762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7278099060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.369514465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8378162384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3244514465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9760990142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9577655792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2144470214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6728076934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2327823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0578289031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1128311157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2961769104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5161895751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8179321289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2495651245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9928855895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7728710174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8828773498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0478858947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8095397949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7362022399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7828121185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7644786834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2511157989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8660945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3977909088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3427886962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4894638061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5994701385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3511810302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8744850158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1494998931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0761623382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0394973754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9745483398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2128963470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5795860290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6345863342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6529216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6162509918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5429153442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6811981201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3045673370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6628646850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4245204925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5711936950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.966157913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5077991485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3611221313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5444660186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9294891357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0211601257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6460819244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4444026947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.481071472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6094093322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4077339172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3343963623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9210948944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2877864837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1961116790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1044425964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7201499938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6169300079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8756313323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5378246307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7348785400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6410427093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2469329833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1437168121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1718654632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0498809814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0029621124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0311126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9560451507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.89035987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9091281890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.078031539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1852855682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2885055541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.565975189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0069999694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.922550201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8662490844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8005619049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5753593444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7536468505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9319343566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9882335662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3354263305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5137119293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7858333587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5230960845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7483005523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4855613708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7817974090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8474807739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4386425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0056934356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1558284759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3435001373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7804870605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8555564880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.874324798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.198709487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2925453186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6678848266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2737789154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4989833831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3622665405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7939109802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6759643554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.826099395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0325355529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1639060974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0888385772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8073310852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1826705932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2389755249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2952766418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.482946395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9574661254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8448677062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7697982788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7134971618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.995002746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5767803192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.670618057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9708881378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.914587020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.158561706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2711639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1397933959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4882926940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8824005126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8636322021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9252796173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0003471374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1692504882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2443180084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8877468109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6813106536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1182975769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3998012542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8930931091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2174758911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3488483428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7992553710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7054195404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0807628631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.742956161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6115837097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4239139556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4426803588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3300800323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9359703063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9172039031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2684326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.686653137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1236419677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9922695159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9118595123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4051475524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.818021774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9681606292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.606237411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4695243835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7162265777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5848598480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6974601745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5044441223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.922664642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8475971221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4293766021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0486869812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.710880279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2363605499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8422527313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9360847473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6170463562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7484169006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.067455291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5741672515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3114280700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4615650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7806053161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9119758605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0058116912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.231014251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1184120178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1559467315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8932075500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6814250946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7189598083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4749851226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7377262115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1693687438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9629287719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6573123931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5071754455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6385440826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9307422637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.775260925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8878612518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4321060180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8074474334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2766265869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8449802398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7136135101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1881351470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8315601348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7940292358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9253959655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2819690704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1640224456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.944164276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2444343566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6063556671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1130657196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5500545501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1934795379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7243022918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2175941467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.874439239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4374504089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3060817718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7055339813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8181381225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0996437072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1318321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.206901550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9951171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.019229888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4884090423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2900447845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5527877807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1533317565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4777145385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.515251159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.383882522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0460758209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1211414337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6519660949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9897708892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.083610534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6894989013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7270336151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4026489257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2712783813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9334716796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5259418487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3007354736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0942993164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0379962921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1506004333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8503284454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5205955505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9763507843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4830627441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7645683288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9575843811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1452541351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0031967163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9468936920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7779903411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3973007202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5581321716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7029209136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3463478088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4455280303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2953910827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4392318725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7460899353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1323719024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6310176849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5543022155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7242012023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6064167022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6091289520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3570995330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8968086242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8776321411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4940547943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2995586395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2803802490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9159889221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8392715454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7050228118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2420272827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9543437957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7077312469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6858425140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0694179534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4556999206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4913463592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7817344665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4721698760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0145893096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4227619171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4419422149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0008335113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5761909484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8638706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.359806060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2063789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4365196228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2830905914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8009147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2611999511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4146308898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0885944366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6474857330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3022708892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8584518432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3241596221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4584102630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7487983703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5378341674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9432964324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.102144241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5459632873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1432113647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8720016479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3131122589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0446090698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2172164916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0637893676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.929536819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5432548522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4281826019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8692932128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0419006347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1953296661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0610771179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.444652557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0802574157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6939735412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9843635559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.524076461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5624332427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6802158355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3158206939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5843238830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3925342559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0281410217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7952861785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2939319610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9487152099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4857196807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7733974456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6418590545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7761077880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1213245391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7377510070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6583271026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0829677581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9678955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1405029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1596813201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8528232574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8144664764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9103603363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9870738983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6993942260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4884281158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7569313049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2966423034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3514671325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0967254638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7706871032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5980815887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5789012908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8309326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3541793823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7542190551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6747951507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6391487121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.307689666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.557014465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7515106201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7323303222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4062938690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3898258209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7925777435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0227203369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8501129150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2145080566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3487586975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.962474822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6337280273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1131954193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3049812316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0556564331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9597663879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7296199798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7104434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.981653213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.40358543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2474460601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8830509185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6912631988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4611206054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.809045791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.617259979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9049377441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6666641235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9351654052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1077728271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2228488922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6037063598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1050643920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6804275512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3352088928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5269927978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2584953308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2776718139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8365631103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7598476409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2009582519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.661247253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8913879394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9105682373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4694595336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.584529876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0475234985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6228866577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3708534240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6420669555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2968482971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9708137512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4338111877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9735221862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9762344360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5324153900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1104831695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8995189666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2447357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2639122009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.841983795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6501960754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2090854644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6856346130371</t>
   </si>
   <si>
     <t xml:space="preserve">24.7212829589844</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8978672027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2686862945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5447044372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1032543182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8383827209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6924781799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.451774597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5112571716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9703712463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2993621826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9285449981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5289154052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.475944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9638614654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3811416625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8932266235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1757564544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7872791290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0986137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4629230499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8095760345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2333679199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.127420425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7389430999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1738872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4080772399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4192276000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3662548065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6906089782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0660667419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9424591064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3551044464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.772388458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7789001464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4610538482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2844715118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2314987182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8077068328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5251750946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4722003936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5604915618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.990795135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3374462127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8430213928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7547302246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7900485992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5958080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3839111328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9601154327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1896724700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1366996765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4015712738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7658786773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8365135192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0595569610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9359512329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3774032592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5186634063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8653182983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0065803527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7835388183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5363235473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0418968200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1943111419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4238662719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7770290374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3420886993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3355751037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5474720001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6710796356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.911153793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0677700042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4711284637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1311664581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3878479003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9012126922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6995334625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.314510345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.64453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0944976806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4061851501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1678333282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5811347961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3061199188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3710651397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7560882568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.012767791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0960483551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0861053466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.729362487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9493751525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2801704406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.261833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.179328918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2343330383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0968246459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7576370239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2626094818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1617698669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1709365844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9875946044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3817825317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7851409912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0601558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.188497543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4635105133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9501495361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4092845916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6842994689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9043121337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0693244934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9593162536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1334934234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8676433563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3359489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8500862121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8218078613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5284576416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1151580810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8852043151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6560249328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6376914978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8859786987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.472677230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5643501281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6835269927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6651916503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2159996032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3351707458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9868202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0784912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8584766387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4001178741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9967622756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9417572021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0425968170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0150947570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6392402648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9142570495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0525398254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2542181015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2175493240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1992149353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6117401123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0059261322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6942443847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9883689880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5758447647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5850124359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.860803604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8058004379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6041231155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3841094970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.585786819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7599649429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9249744415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.310772895813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8149671554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5032825469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8883037567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5124502182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.659125328064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3382730484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4482793807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8516359329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5307846069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8424692153931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1908226013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3466644287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.603346824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1816549301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5483436584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8233594894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5659027099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7217445373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9050912857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1526050567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7026348114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2434978485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5093479156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2427253723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5528583526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7178688049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4161262512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1594429016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0494384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.617805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2595081329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7094764709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3794555664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5627994537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.892822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6544742584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8561515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4527950286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5261325836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7278099060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3695125579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8378162384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3244552612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9760990142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9577655792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2144470214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6728057861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2327823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0578289031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1128349304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2961769104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5161895751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8179302215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2495651245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.992883682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7728691101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8828773498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.047887802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8095397949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7362022399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7828121185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.764476776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2511177062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8660926818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3977928161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3427886962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4894618988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5994701385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3511810302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8744831085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1495018005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0761623382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0394973754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9745502471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2128963470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5795860290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6345882415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6529235839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6162528991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5429153442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6812000274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3045673370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.66286277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4245185852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5711917877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.966157913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5077991485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3611221313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5444679260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9294891357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0211601257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6460819244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4444046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4810695648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6094131469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4077339172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3343963623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9210968017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.287784576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1961135864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1044425964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7201480865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6169319152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8756294250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5378246307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7348766326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6410427093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2469348907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1437168121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1718654632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0498809814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0029640197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0311126708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9560451507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8903617858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9091281890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.078031539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1852855682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2885055541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5659732818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0070018768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9225482940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8662490844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8005619049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5753555297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7536449432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9319324493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9882335662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3354244232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5137119293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7858333587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5230941772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7483005523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4855613708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7817974090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8474807739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4386425018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0056934356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1558284759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3435001373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7804870605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8555564880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.874324798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.198709487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2925453186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6678867340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2737770080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4989833831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.362268447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7939109802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6759624481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.826099395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0325355529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1639060974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0888366699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8073310852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1826725006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2389736175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2952747344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.482946395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9574680328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8448657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7698001861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7134952545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.995002746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5767822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.670618057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.970890045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9145889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1585597991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2711620330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1397953033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4882888793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8824005126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8636322021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9252796173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0003471374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1692523956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2443199157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8877449035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6813068389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1182975769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3998012542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8930912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2174777984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3488464355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7992553710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7054195404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0807609558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.742956161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6115837097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4239139556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4426803588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9359703063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9172039031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2684345245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6866512298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1236400604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9922714233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9118576049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4051475524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8180255889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9681606292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.606237411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4695243835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7162284851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5848579406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6974601745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5044422149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.922664642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8475971221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4293766021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0486907958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.710880279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2363586425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8422527313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9360847473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6170463562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7484169006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0674571990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5741653442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3114280700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4615631103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7806053161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9119720458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0058097839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.231014251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1184120178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1559467315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8932075500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6814231872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.718957901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4749870300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7377243041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1693668365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9629287719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6573123931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.507173538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6385440826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9307403564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7752590179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8878593444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4321041107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8074493408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2766246795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8449821472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7136135101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1881351470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8315601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7940273284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9253959655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2819690704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1640224456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.944164276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2444362640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6063556671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1130657196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5500545501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1934795379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7243022918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2175922393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.874439239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4374504089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3060836791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7055358886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8181381225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0996437072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1318321228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.206901550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9951190948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0192317962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4884071350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2900447845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5527858734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1533317565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4777164459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5152530670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3838806152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0460739135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1211414337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6519660949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9897727966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0836086273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6894989013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7270336151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4026489257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2712783813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9334697723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5259399414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3007373809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0943012237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0379962921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1506004333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8503284454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5205974578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9763488769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.483060836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7645683288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9575843811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1452541351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.00319480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.946891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7779903411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3973026275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5581302642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7029228210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3463478088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4455280303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2953910827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4392318725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7460899353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1323719024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6310176849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5543041229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7242012023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6064205169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6091289520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3570957183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8968086242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8776302337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4940567016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.299560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2803802490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9159889221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8392734527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7050228118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2420272827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9543437957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7077331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6858425140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0694179534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4556999206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4913482666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7817363739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.47216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.014591217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4227619171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4419403076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0008335113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5761909484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8638725280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.359806060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2063770294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4365196228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2830905914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8009147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2612018585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4146308898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0885944366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6474857330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3022708892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8584518432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3241596221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4584083557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7487983703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5378341674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9432964324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1021461486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5459651947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1432113647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8720016479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3131122589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0446090698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2172183990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0637874603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9295387268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5432548522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4281806945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8692932128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.041898727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1953277587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0610771179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.444652557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0802574157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6939735412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9843635559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.524076461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5624351501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6802158355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3158206939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.584321975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3925361633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0281429290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7952880859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2939319610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9487171173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4857196807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7733993530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6418590545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7761077880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1213226318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7377510070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6583251953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0829677581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9678936004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1405029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1596832275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8528232574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8144645690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9103584289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9870738983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6993942260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4884300231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.756929397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2966403961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3514671325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0967254638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7706871032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5980815887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5789012908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8309345245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3541774749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7542190551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6747951507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6391487121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3076915740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.557014465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7515106201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7323303222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4062938690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3898258209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7925777435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0227222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8501129150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.214506149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3487567901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.962474822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6337280273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1131935119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3049793243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0556564331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9597644805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7296199798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7104434967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.981653213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.40358543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2474460601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8830509185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6912631988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4611206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.809045791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6172580718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9049396514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6666641235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9351654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1077728271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2228469848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6037101745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1050605773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6804275512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3352088928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5269927978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2584915161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2776718139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8365631103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7598495483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2009582519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.661247253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8913879394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9105682373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4694595336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.584529876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0475273132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6228866577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3708534240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6420669555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2968521118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9708118438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4338092803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9735221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9762325286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.532413482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1104831695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8995189666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2447357177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2639122009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.841983795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6501960754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2090854644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6856365203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.721284866333</t>
-  </si>
-  <si>
     <t xml:space="preserve">23.9157791137695</t>
   </si>
   <si>
@@ -5546,7 +5546,7 @@
     <t xml:space="preserve">25.2774639129639</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6829242706299</t>
+    <t xml:space="preserve">24.6829261779785</t>
   </si>
   <si>
     <t xml:space="preserve">25.1048564910889</t>
@@ -5558,13 +5558,13 @@
     <t xml:space="preserve">25.5267868041992</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5816097259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6199703216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4090061187744</t>
+    <t xml:space="preserve">26.5816116333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6199684143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4090042114258</t>
   </si>
   <si>
     <t xml:space="preserve">27.7131519317627</t>
@@ -5573,7 +5573,7 @@
     <t xml:space="preserve">29.611837387085</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9022274017334</t>
+    <t xml:space="preserve">28.902229309082</t>
   </si>
   <si>
     <t xml:space="preserve">28.6145496368408</t>
@@ -70951,7 +70951,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6494907407</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>260505</v>
@@ -70972,6 +70972,32 @@
         <v>1944</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6494444444</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>150984</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>31.1399993896484</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>30.3999996185303</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>30.6399993896484</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>30.4799995422363</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1944</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DLG.MI.xlsx
+++ b/data/DLG.MI.xlsx
@@ -44,34 +44,34 @@
     <t xml:space="preserve">DLG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5564193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6553897857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1757488250732</t>
+    <t xml:space="preserve">20.5564231872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6553955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1757469177246</t>
   </si>
   <si>
     <t xml:space="preserve">19.9777927398682</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7722301483154</t>
+    <t xml:space="preserve">19.7722358703613</t>
   </si>
   <si>
     <t xml:space="preserve">19.4905319213867</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8864326477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5160045623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6328430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4348888397217</t>
+    <t xml:space="preserve">19.8864345550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5160064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6328411102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.434886932373</t>
   </si>
   <si>
     <t xml:space="preserve">17.5262546539307</t>
@@ -83,148 +83,148 @@
     <t xml:space="preserve">16.8943328857422</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0135135650635</t>
+    <t xml:space="preserve">18.0135173797607</t>
   </si>
   <si>
     <t xml:space="preserve">16.6354751586914</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4451370239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7116069793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8029708862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6735401153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1329860687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9654884338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6533346176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9909610748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7777833938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3335647583008</t>
+    <t xml:space="preserve">16.4451351165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7116107940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8029689788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6735439300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.132984161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9654855728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6533317565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9909620285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7777814865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3335704803467</t>
   </si>
   <si>
     <t xml:space="preserve">14.4123363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7397155761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4553842544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2574291229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4097003936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7523097991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3868618011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9121932983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9578733444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5848140716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1253719329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1938934326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5593357086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7496776580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.881739616394</t>
+    <t xml:space="preserve">14.7397174835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4553813934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2574338912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4096994400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.752311706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3868598937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9121923446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9578714370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5848121643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1253700256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1938915252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5593395233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7496757507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8817386627197</t>
   </si>
   <si>
     <t xml:space="preserve">15.2193651199341</t>
   </si>
   <si>
-    <t xml:space="preserve">15.379246711731</t>
+    <t xml:space="preserve">15.3792495727539</t>
   </si>
   <si>
     <t xml:space="preserve">16.0873031616211</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7142400741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2878866195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8969659805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.318341255188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6076526641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9274187088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9883298873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8893527984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6152667999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.356409072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1356163024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.226978302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3487939834595</t>
+    <t xml:space="preserve">15.7142419815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2878885269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8969669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.318338394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6076545715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9274196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9883270263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8893547058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6152677536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3564100265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1356143951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2269763946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3487930297852</t>
   </si>
   <si>
     <t xml:space="preserve">15.0442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2345933914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0594806671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1432294845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5493812561035</t>
+    <t xml:space="preserve">15.2345914840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0594816207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1432313919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5493793487549</t>
   </si>
   <si>
     <t xml:space="preserve">14.7853965759277</t>
@@ -233,58 +233,58 @@
     <t xml:space="preserve">14.8234624862671</t>
   </si>
   <si>
-    <t xml:space="preserve">14.783164024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9779872894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1572284698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.149435043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.96240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.985782623291</t>
+    <t xml:space="preserve">14.783166885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.977988243103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1494331359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9624052047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9857788085938</t>
   </si>
   <si>
     <t xml:space="preserve">14.954610824585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8533000946045</t>
+    <t xml:space="preserve">14.8533020019531</t>
   </si>
   <si>
     <t xml:space="preserve">15.4689445495605</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6715602874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.21706199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7572803497314</t>
+    <t xml:space="preserve">15.6715574264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2170639038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7572822570801</t>
   </si>
   <si>
     <t xml:space="preserve">16.0300312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2404403686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1469268798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3495445251465</t>
+    <t xml:space="preserve">16.240442276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1469230651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3495426177979</t>
   </si>
   <si>
     <t xml:space="preserve">16.5053997039795</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3105792999268</t>
+    <t xml:space="preserve">16.3105773925781</t>
   </si>
   <si>
     <t xml:space="preserve">17.728889465332</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">16.793737411499</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0742835998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7625675201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7547740936279</t>
+    <t xml:space="preserve">17.0742855072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7625694274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7547760009766</t>
   </si>
   <si>
     <t xml:space="preserve">16.8482894897461</t>
@@ -311,112 +311,112 @@
     <t xml:space="preserve">17.3002796173096</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7678546905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9081268310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9470882415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0639820098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4848022460938</t>
+    <t xml:space="preserve">17.7678527832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9081249237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9470920562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0639839172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4848003387451</t>
   </si>
   <si>
     <t xml:space="preserve">18.7887268066406</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4614219665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3367385864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.274393081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0795707702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6484546661377</t>
+    <t xml:space="preserve">18.46142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3367366790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2743968963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.079568862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6484527587891</t>
   </si>
   <si>
     <t xml:space="preserve">18.8276920318604</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4536304473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8379878997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3937950134277</t>
+    <t xml:space="preserve">18.4536323547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8379917144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3937931060791</t>
   </si>
   <si>
     <t xml:space="preserve">17.2535190582275</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0820770263672</t>
+    <t xml:space="preserve">17.0820789337158</t>
   </si>
   <si>
     <t xml:space="preserve">17.4951019287109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.923713684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8224048614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7834415435791</t>
+    <t xml:space="preserve">17.9237117767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8224067687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7834396362305</t>
   </si>
   <si>
     <t xml:space="preserve">17.9315052032471</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6768455505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5234956741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1157550811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3651313781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6612586975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6300888061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8975534439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7806587219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7884511947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3729228973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1858901977539</t>
+    <t xml:space="preserve">16.6768436431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5234909057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1157569885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3651275634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6612567901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6300849914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8975553512573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7806577682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5468711853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7884531021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3729190826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1858940124512</t>
   </si>
   <si>
     <t xml:space="preserve">16.1625118255615</t>
   </si>
   <si>
-    <t xml:space="preserve">16.419677734375</t>
+    <t xml:space="preserve">16.4196758270264</t>
   </si>
   <si>
     <t xml:space="preserve">16.5209865570068</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">16.8404979705811</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9184246063232</t>
+    <t xml:space="preserve">16.9184265136719</t>
   </si>
   <si>
     <t xml:space="preserve">16.8716659545898</t>
@@ -437,31 +437,31 @@
     <t xml:space="preserve">16.8015308380127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6119976043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2223491668701</t>
+    <t xml:space="preserve">17.6119956970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2223529815674</t>
   </si>
   <si>
     <t xml:space="preserve">17.5964088439941</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4171714782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6587524414062</t>
+    <t xml:space="preserve">17.4171695709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6587543487549</t>
   </si>
   <si>
     <t xml:space="preserve">17.3158645629883</t>
   </si>
   <si>
-    <t xml:space="preserve">17.323657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.502893447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0561943054199</t>
+    <t xml:space="preserve">17.3236522674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5028915405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0561923980713</t>
   </si>
   <si>
     <t xml:space="preserve">18.5393505096436</t>
@@ -470,10 +470,10 @@
     <t xml:space="preserve">18.7030029296875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6640396118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.812105178833</t>
+    <t xml:space="preserve">18.6640377044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8121089935303</t>
   </si>
   <si>
     <t xml:space="preserve">18.0951557159424</t>
@@ -482,28 +482,28 @@
     <t xml:space="preserve">18.1497077941895</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9003295898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1574974060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8769550323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6665439605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9704704284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0328140258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5106868743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5730304718018</t>
+    <t xml:space="preserve">17.9003314971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1574993133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6665420532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9704666137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0328121185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.510684967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5730285644531</t>
   </si>
   <si>
     <t xml:space="preserve">17.3626232147217</t>
@@ -512,166 +512,166 @@
     <t xml:space="preserve">17.4015846252441</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2379360198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4093799591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1444225311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.81711769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6145000457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6846389770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0197315216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.128833770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2691059112549</t>
+    <t xml:space="preserve">17.2379379272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4093780517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1444206237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8171157836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.614501953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6846370697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0197334289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1288375854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2691097259521</t>
   </si>
   <si>
     <t xml:space="preserve">16.9963550567627</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4405517578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4639301300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8327045440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8249111175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9028396606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7859477996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7469787597656</t>
+    <t xml:space="preserve">17.4405498504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4639282226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8327026367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8249073028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9028415679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.785945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7469825744629</t>
   </si>
   <si>
     <t xml:space="preserve">17.2768974304199</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2457275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0509071350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0976638793945</t>
+    <t xml:space="preserve">17.2457294464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0509052276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0976619720459</t>
   </si>
   <si>
     <t xml:space="preserve">16.9573879241943</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2301425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2067642211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4327564239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2846927642822</t>
+    <t xml:space="preserve">17.2301406860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.20676612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4327583312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2846908569336</t>
   </si>
   <si>
     <t xml:space="preserve">17.0664901733398</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9521055221558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9832763671875</t>
+    <t xml:space="preserve">15.9521026611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9832744598389</t>
   </si>
   <si>
     <t xml:space="preserve">16.2560291290283</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3339557647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9988603591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4066009521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.313084602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1182594299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5131950378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0923748016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9131364822388</t>
+    <t xml:space="preserve">16.3339538574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9988622665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4065999984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3130836486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1182622909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5131912231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0923767089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9131383895874</t>
   </si>
   <si>
     <t xml:space="preserve">16.1780967712402</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7158088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0587005615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4664363861084</t>
+    <t xml:space="preserve">16.7158107757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0586967468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4664344787598</t>
   </si>
   <si>
     <t xml:space="preserve">16.2248554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9754810333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7080154418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4976100921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6924285888672</t>
+    <t xml:space="preserve">15.9754848480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7080173492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4976062774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6924324035645</t>
   </si>
   <si>
     <t xml:space="preserve">16.5599517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7703609466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8638725280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0275249481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4561386108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4483432769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8847503662109</t>
+    <t xml:space="preserve">16.7703590393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8638744354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0275268554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4561347961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4483413696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8847484588623</t>
   </si>
   <si>
     <t xml:space="preserve">18.1185340881348</t>
@@ -680,13 +680,13 @@
     <t xml:space="preserve">18.2354278564453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0172290802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8457813262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9626731872559</t>
+    <t xml:space="preserve">18.0172271728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8457832336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9626750946045</t>
   </si>
   <si>
     <t xml:space="preserve">17.8691635131836</t>
@@ -698,73 +698,73 @@
     <t xml:space="preserve">17.7912330627441</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5808200836182</t>
+    <t xml:space="preserve">17.5808219909668</t>
   </si>
   <si>
     <t xml:space="preserve">17.6509590148926</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1107387542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9782600402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3133583068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2042560577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4692192077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0848560333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.349817276001</t>
+    <t xml:space="preserve">18.1107406616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9782619476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3133544921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2042579650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.469217300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0848579406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3498134613037</t>
   </si>
   <si>
     <t xml:space="preserve">19.2952671051025</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4667072296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2485084533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3186435699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0614757537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4199542999268</t>
+    <t xml:space="preserve">19.4667091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2485065460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3186454772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0614776611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4199504852295</t>
   </si>
   <si>
     <t xml:space="preserve">19.2407150268555</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0926494598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4511222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8588638305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.640661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9056186676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2329177856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4978809356689</t>
+    <t xml:space="preserve">19.0926513671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4511241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8588676452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6406631469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9056205749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2329216003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4978828430176</t>
   </si>
   <si>
     <t xml:space="preserve">20.1914501190186</t>
@@ -773,16 +773,16 @@
     <t xml:space="preserve">19.9888343811035</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1213150024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9732513427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9551544189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6278533935547</t>
+    <t xml:space="preserve">20.1213130950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9732475280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9551563262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6278514862061</t>
   </si>
   <si>
     <t xml:space="preserve">21.2201156616211</t>
@@ -794,31 +794,31 @@
     <t xml:space="preserve">20.7915077209473</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7447471618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8616428375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2434940338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9006061553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0330848693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9785327911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6721038818359</t>
+    <t xml:space="preserve">20.7447509765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8616409301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2434978485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9006080627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0330867767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9785385131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6721057891846</t>
   </si>
   <si>
     <t xml:space="preserve">21.4149379730225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3136329650879</t>
+    <t xml:space="preserve">21.3136310577393</t>
   </si>
   <si>
     <t xml:space="preserve">21.1967391967773</t>
@@ -830,19 +830,19 @@
     <t xml:space="preserve">21.5785903930664</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1884708404541</t>
+    <t xml:space="preserve">22.1884727478027</t>
   </si>
   <si>
     <t xml:space="preserve">22.1002025604248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.947732925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0279808044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9878520965576</t>
+    <t xml:space="preserve">21.9477291107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0279769897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9878540039062</t>
   </si>
   <si>
     <t xml:space="preserve">21.8273620605469</t>
@@ -851,25 +851,25 @@
     <t xml:space="preserve">22.348970413208</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4693374633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8946514129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3199634552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2878646850586</t>
+    <t xml:space="preserve">22.4693412780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8946533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3199653625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2878665924072</t>
   </si>
   <si>
     <t xml:space="preserve">22.8786010742188</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0310726165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4483585357666</t>
+    <t xml:space="preserve">23.0310745239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4483604431152</t>
   </si>
   <si>
     <t xml:space="preserve">23.0230484008789</t>
@@ -881,16 +881,16 @@
     <t xml:space="preserve">22.6218109130859</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5014381408691</t>
+    <t xml:space="preserve">22.5014419555664</t>
   </si>
   <si>
     <t xml:space="preserve">23.2557640075684</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8434085845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0600757598877</t>
+    <t xml:space="preserve">21.8434066772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0600776672363</t>
   </si>
   <si>
     <t xml:space="preserve">22.6298370361328</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">22.7341575622559</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9267501831055</t>
+    <t xml:space="preserve">22.9267482757568</t>
   </si>
   <si>
     <t xml:space="preserve">23.2316913604736</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1434192657471</t>
+    <t xml:space="preserve">23.1434230804443</t>
   </si>
   <si>
     <t xml:space="preserve">23.1674957275391</t>
@@ -914,70 +914,70 @@
     <t xml:space="preserve">23.6570053100586</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7693500518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6730575561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8495998382568</t>
+    <t xml:space="preserve">23.7693538665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6730537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8495960235596</t>
   </si>
   <si>
     <t xml:space="preserve">23.7613277435303</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4002132415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2958908081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4323120117188</t>
+    <t xml:space="preserve">23.4002094268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2958927154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4323139190674</t>
   </si>
   <si>
     <t xml:space="preserve">23.7051544189453</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0070018768311</t>
+    <t xml:space="preserve">23.0069999694824</t>
   </si>
   <si>
     <t xml:space="preserve">22.8304557800293</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7903289794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0631713867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8255271911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3921852111816</t>
+    <t xml:space="preserve">22.7903270721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0631732940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8255252838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3921871185303</t>
   </si>
   <si>
     <t xml:space="preserve">23.2637901306152</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2718162536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1915664672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9989738464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9076042175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0199527740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0761280059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5545177459717</t>
+    <t xml:space="preserve">23.2718181610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1915683746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9989757537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9076061248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0199546813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0761241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.554515838623</t>
   </si>
   <si>
     <t xml:space="preserve">21.4742698669434</t>
@@ -989,34 +989,34 @@
     <t xml:space="preserve">21.7711849212646</t>
   </si>
   <si>
-    <t xml:space="preserve">21.739086151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8674812316895</t>
+    <t xml:space="preserve">21.7390880584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8674793243408</t>
   </si>
   <si>
     <t xml:space="preserve">21.8594570159912</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5255126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7421798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3730411529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.718111038208</t>
+    <t xml:space="preserve">22.5255146026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7421817779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3730392456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7181072235107</t>
   </si>
   <si>
     <t xml:space="preserve">22.8625526428223</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7100811004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5335369110107</t>
+    <t xml:space="preserve">22.7100849151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5335388183594</t>
   </si>
   <si>
     <t xml:space="preserve">22.6539096832275</t>
@@ -1031,61 +1031,61 @@
     <t xml:space="preserve">21.241548538208</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9927825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9446353912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0730323791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.048957824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6396942138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4310512542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4872245788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8804340362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8643856048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7119178771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5754947662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.599573135376</t>
+    <t xml:space="preserve">20.9927845001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9446334838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0730304718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0489559173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6396923065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4310474395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4872226715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8804359436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8643894195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7119159698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5754928588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5995712280273</t>
   </si>
   <si>
     <t xml:space="preserve">20.6477203369141</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6156215667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5915470123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3508052825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3427772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2866058349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7440185546875</t>
+    <t xml:space="preserve">20.6156196594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5915451049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3508033752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3427810668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2866039276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7440166473389</t>
   </si>
   <si>
     <t xml:space="preserve">20.6717929840088</t>
@@ -1097,22 +1097,22 @@
     <t xml:space="preserve">20.735990524292</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2174777984619</t>
+    <t xml:space="preserve">21.2174758911133</t>
   </si>
   <si>
     <t xml:space="preserve">21.0168590545654</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3538970947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2335243225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9045104980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5594482421875</t>
+    <t xml:space="preserve">21.3538990020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2335262298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9045085906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5594463348389</t>
   </si>
   <si>
     <t xml:space="preserve">20.5353736877441</t>
@@ -1121,85 +1121,85 @@
     <t xml:space="preserve">20.4711723327637</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7520427703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3779735565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0650081634521</t>
+    <t xml:space="preserve">20.7520389556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3779697418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0650043487549</t>
   </si>
   <si>
     <t xml:space="preserve">21.2255020141602</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3699474334717</t>
+    <t xml:space="preserve">21.369945526123</t>
   </si>
   <si>
     <t xml:space="preserve">21.9156303405762</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4582195281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8032817840576</t>
+    <t xml:space="preserve">21.4582214355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8032855987549</t>
   </si>
   <si>
     <t xml:space="preserve">21.795259475708</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5785884857178</t>
+    <t xml:space="preserve">21.578592300415</t>
   </si>
   <si>
     <t xml:space="preserve">22.3088455200195</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1403274536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2285957336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2045230865479</t>
+    <t xml:space="preserve">22.140323638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2285976409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2045249938965</t>
   </si>
   <si>
     <t xml:space="preserve">22.1483497619629</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6940364837646</t>
+    <t xml:space="preserve">22.6940307617188</t>
   </si>
   <si>
     <t xml:space="preserve">22.0921745300293</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1082229614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.164400100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7742786407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7662563323975</t>
+    <t xml:space="preserve">22.1082248687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1643981933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7742805480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7662582397461</t>
   </si>
   <si>
     <t xml:space="preserve">22.5897121429443</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5415649414062</t>
+    <t xml:space="preserve">22.5415630340576</t>
   </si>
   <si>
     <t xml:space="preserve">22.4131679534912</t>
   </si>
   <si>
-    <t xml:space="preserve">22.517484664917</t>
+    <t xml:space="preserve">22.5174884796143</t>
   </si>
   <si>
     <t xml:space="preserve">22.1563758850098</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8353805541992</t>
+    <t xml:space="preserve">21.8353824615479</t>
   </si>
   <si>
     <t xml:space="preserve">22.5495872497559</t>
@@ -1217,55 +1217,55 @@
     <t xml:space="preserve">19.9335136413574</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8612880706787</t>
+    <t xml:space="preserve">19.8612899780273</t>
   </si>
   <si>
     <t xml:space="preserve">19.6927700042725</t>
   </si>
   <si>
-    <t xml:space="preserve">19.620548248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5402984619141</t>
+    <t xml:space="preserve">19.6205501556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5403003692627</t>
   </si>
   <si>
     <t xml:space="preserve">19.4921531677246</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4279556274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7409191131592</t>
+    <t xml:space="preserve">19.4279537200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7409210205078</t>
   </si>
   <si>
     <t xml:space="preserve">19.6767234802246</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8051166534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4199295043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7569675445557</t>
+    <t xml:space="preserve">19.805118560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4199333190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7569713592529</t>
   </si>
   <si>
     <t xml:space="preserve">19.6606731414795</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1421604156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2304306030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4069747924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4791965484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2545070648193</t>
+    <t xml:space="preserve">20.1421585083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2304286956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4069766998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4791984558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2545032501221</t>
   </si>
   <si>
     <t xml:space="preserve">19.9415397644043</t>
@@ -1274,28 +1274,28 @@
     <t xml:space="preserve">20.0619106292725</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9254875183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9366111755371</t>
+    <t xml:space="preserve">19.9254913330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9366092681885</t>
   </si>
   <si>
     <t xml:space="preserve">21.0971069335938</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8162384033203</t>
+    <t xml:space="preserve">20.8162403106689</t>
   </si>
   <si>
     <t xml:space="preserve">20.3989505767822</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6878433227539</t>
+    <t xml:space="preserve">20.6878452301025</t>
   </si>
   <si>
     <t xml:space="preserve">20.4390735626221</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2464828491211</t>
+    <t xml:space="preserve">20.2464771270752</t>
   </si>
   <si>
     <t xml:space="preserve">20.4631500244141</t>
@@ -1304,31 +1304,31 @@
     <t xml:space="preserve">20.5433979034424</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4100742340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0088367462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6508140563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1372299194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2816772460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5063667297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4421672821045</t>
+    <t xml:space="preserve">21.4100704193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0088348388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6508159637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.137228012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2816753387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.506368637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4421691894531</t>
   </si>
   <si>
     <t xml:space="preserve">20.9606857299805</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3458728790283</t>
+    <t xml:space="preserve">21.345874786377</t>
   </si>
   <si>
     <t xml:space="preserve">21.0890789031982</t>
@@ -1343,55 +1343,55 @@
     <t xml:space="preserve">21.7792110443115</t>
   </si>
   <si>
-    <t xml:space="preserve">21.394021987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7471122741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2495746612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5322723388672</t>
+    <t xml:space="preserve">21.3940200805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7471103668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2495727539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5322742462158</t>
   </si>
   <si>
     <t xml:space="preserve">19.3236331939697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5001754760742</t>
+    <t xml:space="preserve">19.5001773834229</t>
   </si>
   <si>
     <t xml:space="preserve">19.5162258148193</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0458602905273</t>
+    <t xml:space="preserve">20.045862197876</t>
   </si>
   <si>
     <t xml:space="preserve">20.0940113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7248687744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7088203430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.403881072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4841270446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1631355285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8260936737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6014041900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0075721740723</t>
+    <t xml:space="preserve">19.7248706817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7088222503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4038791656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4841289520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1631336212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8260974884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6014022827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0075702667236</t>
   </si>
   <si>
     <t xml:space="preserve">18.5853538513184</t>
@@ -1403,16 +1403,16 @@
     <t xml:space="preserve">19.9977111816406</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1261119842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7199420928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1903076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7730178833008</t>
+    <t xml:space="preserve">20.1261081695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7199401855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1903057098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7730159759521</t>
   </si>
   <si>
     <t xml:space="preserve">19.8372173309326</t>
@@ -1421,40 +1421,40 @@
     <t xml:space="preserve">19.8211669921875</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4359760284424</t>
+    <t xml:space="preserve">19.4359798431396</t>
   </si>
   <si>
     <t xml:space="preserve">19.1310367584229</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3557319641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5483245849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9174652099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5804252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0186939239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0026416778564</t>
+    <t xml:space="preserve">19.3557300567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5483264923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9174633026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5804233551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0186920166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0026435852051</t>
   </si>
   <si>
     <t xml:space="preserve">18.8421478271484</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0828895568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8853664398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5112953186035</t>
+    <t xml:space="preserve">19.0828876495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.885368347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5113010406494</t>
   </si>
   <si>
     <t xml:space="preserve">20.1582088470459</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">20.8936634063721</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6596565246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5760803222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6763706207275</t>
+    <t xml:space="preserve">20.6596584320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5760841369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6763725280762</t>
   </si>
   <si>
     <t xml:space="preserve">20.7265167236328</t>
@@ -1478,43 +1478,43 @@
     <t xml:space="preserve">20.8435192108154</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8268051147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4954013824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1276760101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2781085968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1778202056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0942459106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9772415161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7766590118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.475793838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6429424285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.525936126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2584953308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1247787475586</t>
+    <t xml:space="preserve">20.8268032073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4954032897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1276721954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2781066894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1778182983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0942440032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9772396087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7766628265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4757919311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6429405212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5259380340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2584972381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1247806549072</t>
   </si>
   <si>
     <t xml:space="preserve">20.1916389465332</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">19.9241981506348</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5063228607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1582107543945</t>
+    <t xml:space="preserve">19.506326675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1582069396973</t>
   </si>
   <si>
     <t xml:space="preserve">20.2417812347412</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">20.7933750152588</t>
   </si>
   <si>
-    <t xml:space="preserve">20.993953704834</t>
+    <t xml:space="preserve">20.9939575195312</t>
   </si>
   <si>
     <t xml:space="preserve">20.8100910186768</t>
@@ -1547,10 +1547,10 @@
     <t xml:space="preserve">20.5927963256836</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6930885314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3420696258545</t>
+    <t xml:space="preserve">20.6930866241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3420734405518</t>
   </si>
   <si>
     <t xml:space="preserve">20.4925079345703</t>
@@ -1562,10 +1562,10 @@
     <t xml:space="preserve">19.7570476531982</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8740558624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1414928436279</t>
+    <t xml:space="preserve">19.8740520477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1414947509766</t>
   </si>
   <si>
     <t xml:space="preserve">20.2919273376465</t>
@@ -1574,25 +1574,25 @@
     <t xml:space="preserve">20.0244884490967</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9409141540527</t>
+    <t xml:space="preserve">19.9409160614014</t>
   </si>
   <si>
     <t xml:space="preserve">20.1080627441406</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2752113342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3922176361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0579204559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.425651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.074634552002</t>
+    <t xml:space="preserve">20.2752132415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3922157287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0579166412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4256477355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0746326446533</t>
   </si>
   <si>
     <t xml:space="preserve">19.8239097595215</t>
@@ -1601,25 +1601,25 @@
     <t xml:space="preserve">19.6901912689209</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0273857116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2475776672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3144340515137</t>
+    <t xml:space="preserve">21.0273818969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2475757598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.314432144165</t>
   </si>
   <si>
     <t xml:space="preserve">23.1000366210938</t>
   </si>
   <si>
-    <t xml:space="preserve">23.200325012207</t>
+    <t xml:space="preserve">23.2003269195557</t>
   </si>
   <si>
     <t xml:space="preserve">23.2671871185303</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5847702026367</t>
+    <t xml:space="preserve">23.5847682952881</t>
   </si>
   <si>
     <t xml:space="preserve">23.5346240997314</t>
@@ -1634,97 +1634,97 @@
     <t xml:space="preserve">22.7991676330566</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8325958251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5484428405762</t>
+    <t xml:space="preserve">22.8325977325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5484466552734</t>
   </si>
   <si>
     <t xml:space="preserve">22.6153030395508</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9328861236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1167507171631</t>
+    <t xml:space="preserve">22.9328899383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1167526245117</t>
   </si>
   <si>
     <t xml:space="preserve">23.1501789093018</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2504692077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4009037017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.618200302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5011959075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3841896057129</t>
+    <t xml:space="preserve">23.2504711151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4009056091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6181983947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5011940002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3841876983643</t>
   </si>
   <si>
     <t xml:space="preserve">23.2839012145996</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0833206176758</t>
+    <t xml:space="preserve">23.0833225250244</t>
   </si>
   <si>
     <t xml:space="preserve">22.8994560241699</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5651588439941</t>
+    <t xml:space="preserve">22.5651569366455</t>
   </si>
   <si>
     <t xml:space="preserve">22.5818729400635</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3311462402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8158798217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5317287445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1334667205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9663162231445</t>
+    <t xml:space="preserve">22.331148147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.815881729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5317268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1334686279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9663143157959</t>
   </si>
   <si>
     <t xml:space="preserve">23.6850566864014</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3006153106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4343338012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9997482299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8493118286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9496040344238</t>
+    <t xml:space="preserve">23.3006134033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4343357086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9997463226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8493137359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9496002197266</t>
   </si>
   <si>
     <t xml:space="preserve">21.7628421783447</t>
   </si>
   <si>
-    <t xml:space="preserve">21.461971282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0440979003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7098026275635</t>
+    <t xml:space="preserve">21.4619731903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0441017150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7098045349121</t>
   </si>
   <si>
     <t xml:space="preserve">20.9103813171387</t>
@@ -1733,64 +1733,64 @@
     <t xml:space="preserve">21.6625518798828</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2279663085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4285430908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9270992279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3616809844971</t>
+    <t xml:space="preserve">21.2279624938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4285411834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.927095413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3616847991943</t>
   </si>
   <si>
     <t xml:space="preserve">21.5121192932129</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9605274200439</t>
+    <t xml:space="preserve">20.9605255126953</t>
   </si>
   <si>
     <t xml:space="preserve">19.8573398590088</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5397529602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9547328948975</t>
+    <t xml:space="preserve">19.5397548675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9547348022461</t>
   </si>
   <si>
     <t xml:space="preserve">19.556468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0550231933594</t>
+    <t xml:space="preserve">19.0550212860107</t>
   </si>
   <si>
     <t xml:space="preserve">19.4394664764404</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3893203735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2556018829346</t>
+    <t xml:space="preserve">19.3893222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2556037902832</t>
   </si>
   <si>
     <t xml:space="preserve">19.3057479858398</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3726081848145</t>
+    <t xml:space="preserve">19.3726043701172</t>
   </si>
   <si>
     <t xml:space="preserve">18.8042984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6037216186523</t>
+    <t xml:space="preserve">18.6037197113037</t>
   </si>
   <si>
     <t xml:space="preserve">18.6872940063477</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6705799102783</t>
+    <t xml:space="preserve">18.6705780029297</t>
   </si>
   <si>
     <t xml:space="preserve">18.704008102417</t>
@@ -1805,49 +1805,49 @@
     <t xml:space="preserve">19.6734752655029</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6567611694336</t>
+    <t xml:space="preserve">19.656759262085</t>
   </si>
   <si>
     <t xml:space="preserve">19.8907680511475</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0913524627686</t>
+    <t xml:space="preserve">20.0913486480713</t>
   </si>
   <si>
     <t xml:space="preserve">19.8406257629395</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5899028778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0884552001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7737655639648</t>
+    <t xml:space="preserve">19.5898990631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.088451385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7737617492676</t>
   </si>
   <si>
     <t xml:space="preserve">19.640043258667</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4561805725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9213008880615</t>
+    <t xml:space="preserve">19.4561824798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9213027954102</t>
   </si>
   <si>
     <t xml:space="preserve">19.3391780853271</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5201435089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5506801605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0019836425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9016914367676</t>
+    <t xml:space="preserve">18.5201454162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5506763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0019817352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9016933441162</t>
   </si>
   <si>
     <t xml:space="preserve">18.4700012207031</t>
@@ -1859,22 +1859,22 @@
     <t xml:space="preserve">18.4365692138672</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0412006378174</t>
+    <t xml:space="preserve">20.041202545166</t>
   </si>
   <si>
     <t xml:space="preserve">20.3086414337158</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9910583496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3253574371338</t>
+    <t xml:space="preserve">19.991060256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3253593444824</t>
   </si>
   <si>
     <t xml:space="preserve">18.2861347198486</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2694225311279</t>
+    <t xml:space="preserve">18.2694206237793</t>
   </si>
   <si>
     <t xml:space="preserve">18.219274520874</t>
@@ -1889,10 +1889,10 @@
     <t xml:space="preserve">18.25270652771</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3529949188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5368595123291</t>
+    <t xml:space="preserve">18.3529930114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5368576049805</t>
   </si>
   <si>
     <t xml:space="preserve">18.7541542053223</t>
@@ -1901,70 +1901,70 @@
     <t xml:space="preserve">18.637149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1553134918213</t>
+    <t xml:space="preserve">19.1553153991699</t>
   </si>
   <si>
     <t xml:space="preserve">19.4060363769531</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2723178863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9714508056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3558921813965</t>
+    <t xml:space="preserve">19.2723159790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9714488983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3558940887451</t>
   </si>
   <si>
     <t xml:space="preserve">19.0215930938721</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3224639892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7403354644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1749229431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7875804901123</t>
+    <t xml:space="preserve">19.3224620819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7403373718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1749248504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7875823974609</t>
   </si>
   <si>
     <t xml:space="preserve">18.9380187988281</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0077705383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2250671386719</t>
+    <t xml:space="preserve">20.0077743530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2250709533691</t>
   </si>
   <si>
     <t xml:space="preserve">21.5789775848389</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1443901062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2054595947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0354118347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6509685516357</t>
+    <t xml:space="preserve">21.1443881988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2054557800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0354099273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6509666442871</t>
   </si>
   <si>
     <t xml:space="preserve">17.4336738586426</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5841083526611</t>
+    <t xml:space="preserve">17.5841121673584</t>
   </si>
   <si>
     <t xml:space="preserve">17.1328048706055</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5477828979492</t>
+    <t xml:space="preserve">16.5477809906006</t>
   </si>
   <si>
     <t xml:space="preserve">16.1716976165771</t>
@@ -1973,85 +1973,85 @@
     <t xml:space="preserve">15.996187210083</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3221321105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.879186630249</t>
+    <t xml:space="preserve">16.3221302032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8791837692261</t>
   </si>
   <si>
     <t xml:space="preserve">15.7939510345459</t>
   </si>
   <si>
-    <t xml:space="preserve">15.768383026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7769050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3081130981445</t>
+    <t xml:space="preserve">15.7683801651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7769041061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3081150054932</t>
   </si>
   <si>
     <t xml:space="preserve">15.4018726348877</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4359683990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5382490158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1632165908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3336839675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0524110794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1717376708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3507308959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5552921295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6405296325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6490535736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6320056915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5808639526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4103946685791</t>
+    <t xml:space="preserve">15.4359664916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5382480621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1632146835327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.333685874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0524101257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1717395782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3507318496704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5552940368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6405277252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6490507125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6320066452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5808668136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4103965759277</t>
   </si>
   <si>
     <t xml:space="preserve">15.0609331130981</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8904647827148</t>
+    <t xml:space="preserve">14.8904638290405</t>
   </si>
   <si>
     <t xml:space="preserve">14.984224319458</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0438842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3763017654419</t>
+    <t xml:space="preserve">15.0438852310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3763036727905</t>
   </si>
   <si>
     <t xml:space="preserve">15.4274444580078</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2825441360474</t>
+    <t xml:space="preserve">15.282546043396</t>
   </si>
   <si>
     <t xml:space="preserve">15.0865058898926</t>
@@ -2060,25 +2060,25 @@
     <t xml:space="preserve">15.1120748519897</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1546926498413</t>
+    <t xml:space="preserve">15.1546907424927</t>
   </si>
   <si>
     <t xml:space="preserve">15.3251609802246</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3592557907104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9671764373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7455673217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6091899871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6518096923828</t>
+    <t xml:space="preserve">15.3592567443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9671754837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7455654144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6091918945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6518087387085</t>
   </si>
   <si>
     <t xml:space="preserve">14.5154342651367</t>
@@ -2087,25 +2087,25 @@
     <t xml:space="preserve">14.7114734649658</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6347627639771</t>
+    <t xml:space="preserve">14.6347637176514</t>
   </si>
   <si>
     <t xml:space="preserve">14.5410032272339</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3534860610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3449649810791</t>
+    <t xml:space="preserve">14.3534870147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3449630737305</t>
   </si>
   <si>
     <t xml:space="preserve">14.4472455978394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4387235641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7540903091431</t>
+    <t xml:space="preserve">14.4387216567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7540893554688</t>
   </si>
   <si>
     <t xml:space="preserve">14.4642915725708</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">14.4813385009766</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3620119094849</t>
+    <t xml:space="preserve">14.3620109558105</t>
   </si>
   <si>
     <t xml:space="preserve">15.2484502792358</t>
@@ -2126,49 +2126,49 @@
     <t xml:space="preserve">15.0268392562866</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0012712478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.68590259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5324792861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9784555435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4046297073364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.035364151001</t>
+    <t xml:space="preserve">15.0012683868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6859035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5324811935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9784564971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4046277999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0353651046753</t>
   </si>
   <si>
     <t xml:space="preserve">15.1376447677612</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8308000564575</t>
+    <t xml:space="preserve">14.8308019638062</t>
   </si>
   <si>
     <t xml:space="preserve">14.9586524963379</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2399272918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8109970092773</t>
+    <t xml:space="preserve">15.2399253845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8109951019287</t>
   </si>
   <si>
     <t xml:space="preserve">16.4843502044678</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0468978881836</t>
+    <t xml:space="preserve">17.0468940734863</t>
   </si>
   <si>
     <t xml:space="preserve">16.7911949157715</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5269680023193</t>
+    <t xml:space="preserve">16.5269660949707</t>
   </si>
   <si>
     <t xml:space="preserve">17.0128040313721</t>
@@ -2177,67 +2177,67 @@
     <t xml:space="preserve">16.5781097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3138790130615</t>
+    <t xml:space="preserve">16.3138809204102</t>
   </si>
   <si>
     <t xml:space="preserve">16.2371673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9303255081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9218044281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3933486938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9416065216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5239572525024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9330816268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6603317260742</t>
+    <t xml:space="preserve">15.930326461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.921802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3933477401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9416046142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5239591598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9330835342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6603326797485</t>
   </si>
   <si>
     <t xml:space="preserve">14.2512054443359</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1318788528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6177158355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4557685852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.558051109314</t>
+    <t xml:space="preserve">14.1318778991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.617714881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4557676315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5580520629883</t>
   </si>
   <si>
     <t xml:space="preserve">14.5750980377197</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7370443344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7796611785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8393249511719</t>
+    <t xml:space="preserve">14.7370452880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7796602249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8393230438232</t>
   </si>
   <si>
     <t xml:space="preserve">14.8478479385376</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6688547134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2341604232788</t>
+    <t xml:space="preserve">14.6688556671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2341613769531</t>
   </si>
   <si>
     <t xml:space="preserve">14.14040184021</t>
@@ -2246,16 +2246,16 @@
     <t xml:space="preserve">14.0636901855469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8222770690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6262378692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0183181762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1291217803955</t>
+    <t xml:space="preserve">14.8222780227661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6262397766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0183172225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1291227340698</t>
   </si>
   <si>
     <t xml:space="preserve">15.20583152771</t>
@@ -2264,40 +2264,40 @@
     <t xml:space="preserve">15.5467700958252</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8195209503174</t>
+    <t xml:space="preserve">15.8195219039917</t>
   </si>
   <si>
     <t xml:space="preserve">16.0326080322266</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4502563476562</t>
+    <t xml:space="preserve">16.450252532959</t>
   </si>
   <si>
     <t xml:space="preserve">16.4928741455078</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0155620574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1519374847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2030754089355</t>
+    <t xml:space="preserve">16.0155639648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1519355773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2030773162842</t>
   </si>
   <si>
     <t xml:space="preserve">16.0411319732666</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0752220153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8962306976318</t>
+    <t xml:space="preserve">16.0752258300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8962316513062</t>
   </si>
   <si>
     <t xml:space="preserve">16.2883110046387</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2627410888672</t>
+    <t xml:space="preserve">16.2627391815186</t>
   </si>
   <si>
     <t xml:space="preserve">16.1263656616211</t>
@@ -2306,19 +2306,19 @@
     <t xml:space="preserve">16.1178417205811</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1945552825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2286472320557</t>
+    <t xml:space="preserve">16.1945533752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2286491394043</t>
   </si>
   <si>
     <t xml:space="preserve">16.168981552124</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0666999816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.27978515625</t>
+    <t xml:space="preserve">16.0667037963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2797908782959</t>
   </si>
   <si>
     <t xml:space="preserve">16.109317779541</t>
@@ -2330,46 +2330,46 @@
     <t xml:space="preserve">15.6746215820312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9729433059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.74280834198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3422069549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.291069984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.103551864624</t>
+    <t xml:space="preserve">15.9729423522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7428092956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3422079086304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2910671234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1035499572754</t>
   </si>
   <si>
     <t xml:space="preserve">14.5665760040283</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2853002548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2426824569702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5949010848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7057056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6944246292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5069103240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0694589614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4615364074707</t>
+    <t xml:space="preserve">14.2853012084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2426815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5949001312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7057065963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6944255828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5069093704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0694580078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4615354537964</t>
   </si>
   <si>
     <t xml:space="preserve">15.4444904327393</t>
@@ -2378,16 +2378,16 @@
     <t xml:space="preserve">15.4700603485107</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6149578094482</t>
+    <t xml:space="preserve">15.6149568557739</t>
   </si>
   <si>
     <t xml:space="preserve">15.2740201950073</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2995910644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7142305374146</t>
+    <t xml:space="preserve">15.2995901107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7142286300659</t>
   </si>
   <si>
     <t xml:space="preserve">13.381814956665</t>
@@ -2396,40 +2396,40 @@
     <t xml:space="preserve">13.5522832870483</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1772527694702</t>
+    <t xml:space="preserve">13.1772508621216</t>
   </si>
   <si>
     <t xml:space="preserve">13.2965803146362</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2624855041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0323543548584</t>
+    <t xml:space="preserve">13.2624864578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0323524475098</t>
   </si>
   <si>
     <t xml:space="preserve">12.7596035003662</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6232261657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.359001159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6600770950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1912889480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8333034515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74230289459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6543111801147</t>
+    <t xml:space="preserve">12.6232290267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3590002059937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6600780487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1912899017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8333044052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7423038482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6543102264404</t>
   </si>
   <si>
     <t xml:space="preserve">11.6430320739746</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">11.6686010360718</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0351104736328</t>
+    <t xml:space="preserve">12.0351095199585</t>
   </si>
   <si>
     <t xml:space="preserve">13.3306732177734</t>
@@ -2450,67 +2450,67 @@
     <t xml:space="preserve">13.7227544784546</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2767772674561</t>
+    <t xml:space="preserve">14.2767763137817</t>
   </si>
   <si>
     <t xml:space="preserve">13.0749702453613</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5011434555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4500026702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9897346496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0834941864014</t>
+    <t xml:space="preserve">13.5011425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4500007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9897365570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0834951400757</t>
   </si>
   <si>
     <t xml:space="preserve">13.1175880432129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4953765869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.023829460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3562450408936</t>
+    <t xml:space="preserve">12.4953756332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0238304138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3562440872192</t>
   </si>
   <si>
     <t xml:space="preserve">13.4244327545166</t>
   </si>
   <si>
-    <t xml:space="preserve">13.61194896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8192672729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6999397277832</t>
+    <t xml:space="preserve">13.6119480133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8192663192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6999378204346</t>
   </si>
   <si>
     <t xml:space="preserve">12.904501914978</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0664482116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2113456726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3988618850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.313627243042</t>
+    <t xml:space="preserve">13.0664472579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2113437652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3988628387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3136281967163</t>
   </si>
   <si>
     <t xml:space="preserve">13.8079872131348</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8932209014893</t>
+    <t xml:space="preserve">13.8932189941406</t>
   </si>
   <si>
     <t xml:space="preserve">13.9358406066895</t>
@@ -2522,10 +2522,10 @@
     <t xml:space="preserve">13.8846998214722</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4898633956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7029504776001</t>
+    <t xml:space="preserve">14.4898624420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7029485702515</t>
   </si>
   <si>
     <t xml:space="preserve">14.200065612793</t>
@@ -2534,22 +2534,22 @@
     <t xml:space="preserve">14.4983863830566</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4131526947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1205987930298</t>
+    <t xml:space="preserve">14.4131507873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1205978393555</t>
   </si>
   <si>
     <t xml:space="preserve">14.7711372375488</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8563709259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4189186096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9388494491577</t>
+    <t xml:space="preserve">14.8563718795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4189195632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9388513565063</t>
   </si>
   <si>
     <t xml:space="preserve">15.7513332366943</t>
@@ -2558,19 +2558,19 @@
     <t xml:space="preserve">16.6207237243652</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4161643981934</t>
+    <t xml:space="preserve">16.4161624908447</t>
   </si>
   <si>
     <t xml:space="preserve">16.2456912994385</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5440139770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7826709747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3707866668701</t>
+    <t xml:space="preserve">16.5440158843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7826747894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3707885742188</t>
   </si>
   <si>
     <t xml:space="preserve">18.427698135376</t>
@@ -2582,19 +2582,19 @@
     <t xml:space="preserve">19.0754776000977</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6493053436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9050102233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.603931427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6380271911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0641994476318</t>
+    <t xml:space="preserve">18.6493015289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9050121307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6039333343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6380290985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0641975402832</t>
   </si>
   <si>
     <t xml:space="preserve">19.8766841888428</t>
@@ -2606,49 +2606,49 @@
     <t xml:space="preserve">20.1494312286377</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0471534729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4846057891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8425884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8084964752197</t>
+    <t xml:space="preserve">20.0471515655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4846076965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8425922393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8084945678711</t>
   </si>
   <si>
     <t xml:space="preserve">20.7119789123535</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9506359100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6778869628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8483562469482</t>
+    <t xml:space="preserve">20.9506378173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6778888702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8483543395996</t>
   </si>
   <si>
     <t xml:space="preserve">20.8824520111084</t>
   </si>
   <si>
-    <t xml:space="preserve">21.052921295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9335899353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0870113372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.155200958252</t>
+    <t xml:space="preserve">21.0529174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9335918426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0870151519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1551990509033</t>
   </si>
   <si>
     <t xml:space="preserve">21.2915744781494</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2574806213379</t>
+    <t xml:space="preserve">21.2574825286865</t>
   </si>
   <si>
     <t xml:space="preserve">21.2233867645264</t>
@@ -2657,13 +2657,13 @@
     <t xml:space="preserve">21.0699653625488</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3086223602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8994998931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9676837921143</t>
+    <t xml:space="preserve">21.3086204528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8994979858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9676856994629</t>
   </si>
   <si>
     <t xml:space="preserve">20.7631225585938</t>
@@ -2672,43 +2672,43 @@
     <t xml:space="preserve">20.9165439605713</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1609668731689</t>
+    <t xml:space="preserve">22.1609649658203</t>
   </si>
   <si>
     <t xml:space="preserve">22.6382808685303</t>
   </si>
   <si>
-    <t xml:space="preserve">23.013313293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9167938232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8145160675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9679412841797</t>
+    <t xml:space="preserve">23.0133113861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9167957305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8145179748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9679393768311</t>
   </si>
   <si>
     <t xml:space="preserve">24.0020332336426</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5758571624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8656539916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7974700927734</t>
+    <t xml:space="preserve">23.5758590698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8656578063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7974681854248</t>
   </si>
   <si>
     <t xml:space="preserve">23.5247192382812</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5929069519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6610946655273</t>
+    <t xml:space="preserve">23.5929050445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6610908508301</t>
   </si>
   <si>
     <t xml:space="preserve">23.8486099243164</t>
@@ -2717,25 +2717,25 @@
     <t xml:space="preserve">23.6781425476074</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4394836425781</t>
+    <t xml:space="preserve">23.4394855499268</t>
   </si>
   <si>
     <t xml:space="preserve">23.7292823791504</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7463283538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6951885223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4906234741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7633743286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1496887207031</t>
+    <t xml:space="preserve">23.7463321685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6951866149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4906253814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7633762359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1496868133545</t>
   </si>
   <si>
     <t xml:space="preserve">23.9849853515625</t>
@@ -2744,22 +2744,22 @@
     <t xml:space="preserve">23.8997497558594</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4963912963867</t>
+    <t xml:space="preserve">24.4963932037354</t>
   </si>
   <si>
     <t xml:space="preserve">25.2123622894287</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5304870605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1100807189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0647087097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4680652618408</t>
+    <t xml:space="preserve">24.5304889678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1100769042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0647048950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4680633544922</t>
   </si>
   <si>
     <t xml:space="preserve">25.5532989501953</t>
@@ -2768,16 +2768,16 @@
     <t xml:space="preserve">25.4851131439209</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1271266937256</t>
+    <t xml:space="preserve">25.1271286010742</t>
   </si>
   <si>
     <t xml:space="preserve">25.0589389801025</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0759868621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8202857971191</t>
+    <t xml:space="preserve">25.075984954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8202838897705</t>
   </si>
   <si>
     <t xml:space="preserve">24.8884716033936</t>
@@ -2786,34 +2786,34 @@
     <t xml:space="preserve">25.1953163146973</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7180023193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3487358093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2294101715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4339733123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3657875061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9453754425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8829593658447</t>
+    <t xml:space="preserve">24.7180004119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3487339019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2294082641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4339714050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3657836914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9453792572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8829574584961</t>
   </si>
   <si>
     <t xml:space="preserve">26.7636299133301</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0306167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9283313751221</t>
+    <t xml:space="preserve">26.0306148529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9283332824707</t>
   </si>
   <si>
     <t xml:space="preserve">26.0135669708252</t>
@@ -2822,37 +2822,37 @@
     <t xml:space="preserve">25.1441764831543</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9566593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4224376678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2690162658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4053936004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4565315246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8373279571533</t>
+    <t xml:space="preserve">24.956657409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.422435760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2690143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4053897857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4565296173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.837329864502</t>
   </si>
   <si>
     <t xml:space="preserve">25.0930347442627</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5703449249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6385345458984</t>
+    <t xml:space="preserve">25.5703468322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6385326385498</t>
   </si>
   <si>
     <t xml:space="preserve">24.3600158691406</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1384048461914</t>
+    <t xml:space="preserve">24.13840675354</t>
   </si>
   <si>
     <t xml:space="preserve">25.9112854003906</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">24.5475330352783</t>
   </si>
   <si>
-    <t xml:space="preserve">23.831563949585</t>
+    <t xml:space="preserve">23.8315620422363</t>
   </si>
   <si>
     <t xml:space="preserve">23.5588130950928</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">24.12135887146</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5417671203613</t>
+    <t xml:space="preserve">23.5417652130127</t>
   </si>
   <si>
     <t xml:space="preserve">23.0985469818115</t>
@@ -2885,31 +2885,31 @@
     <t xml:space="preserve">24.2918300628662</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0702209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5076732635498</t>
+    <t xml:space="preserve">24.070219039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5076713562012</t>
   </si>
   <si>
     <t xml:space="preserve">23.3372020721436</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1837825775146</t>
+    <t xml:space="preserve">23.183780670166</t>
   </si>
   <si>
     <t xml:space="preserve">22.6894226074219</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1667327880859</t>
+    <t xml:space="preserve">23.1667366027832</t>
   </si>
   <si>
     <t xml:space="preserve">23.2860641479492</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2029094696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3768424987793</t>
+    <t xml:space="preserve">23.2029075622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3768405914307</t>
   </si>
   <si>
     <t xml:space="preserve">22.6984977722168</t>
@@ -2921,10 +2921,10 @@
     <t xml:space="preserve">22.8202514648438</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4201984405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7854633331299</t>
+    <t xml:space="preserve">22.4202003479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7854652404785</t>
   </si>
   <si>
     <t xml:space="preserve">23.2898750305176</t>
@@ -2936,7 +2936,7 @@
     <t xml:space="preserve">22.872428894043</t>
   </si>
   <si>
-    <t xml:space="preserve">22.750675201416</t>
+    <t xml:space="preserve">22.7506732940674</t>
   </si>
   <si>
     <t xml:space="preserve">22.7158889770508</t>
@@ -2948,70 +2948,70 @@
     <t xml:space="preserve">22.3332347869873</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4723815917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.255090713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5769920349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3596973419189</t>
+    <t xml:space="preserve">22.4723796844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2550888061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5769939422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3596992492676</t>
   </si>
   <si>
     <t xml:space="preserve">25.551025390625</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1945877075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4207019805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7597503662109</t>
+    <t xml:space="preserve">26.1945858001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4207038879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7597522735596</t>
   </si>
   <si>
     <t xml:space="preserve">26.4033088684082</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0294742584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.186014175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1164417266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0120811462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1426582336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8036098480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0992984771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.377592086792</t>
+    <t xml:space="preserve">27.0294761657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1860160827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1164436340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.012077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1426563262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8036079406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0992965698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3775901794434</t>
   </si>
   <si>
     <t xml:space="preserve">29.5863151550293</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0385456085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2210521697998</t>
+    <t xml:space="preserve">30.0385494232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2210502624512</t>
   </si>
   <si>
     <t xml:space="preserve">29.081901550293</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7688217163086</t>
+    <t xml:space="preserve">28.7688236236572</t>
   </si>
   <si>
     <t xml:space="preserve">28.4035587310791</t>
@@ -3020,7 +3020,7 @@
     <t xml:space="preserve">27.6904258728027</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7859630584717</t>
+    <t xml:space="preserve">26.7859649658203</t>
   </si>
   <si>
     <t xml:space="preserve">26.5946350097656</t>
@@ -3032,16 +3032,16 @@
     <t xml:space="preserve">26.6294231414795</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6208515167236</t>
+    <t xml:space="preserve">27.620849609375</t>
   </si>
   <si>
     <t xml:space="preserve">26.6468162536621</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5250644683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2034091949463</t>
+    <t xml:space="preserve">26.5250625610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2034072875977</t>
   </si>
   <si>
     <t xml:space="preserve">27.3077697753906</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">30.108118057251</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1340866088867</t>
+    <t xml:space="preserve">29.1340847015381</t>
   </si>
   <si>
     <t xml:space="preserve">29.0471210479736</t>
@@ -3068,70 +3068,70 @@
     <t xml:space="preserve">29.3080196380615</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8560409545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7342872619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2298736572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3690223693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4385948181152</t>
+    <t xml:space="preserve">30.8560390472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7342834472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2298698425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3690204620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4385967254639</t>
   </si>
   <si>
     <t xml:space="preserve">30.0559425354004</t>
   </si>
   <si>
-    <t xml:space="preserve">30.299446105957</t>
+    <t xml:space="preserve">30.2994480133057</t>
   </si>
   <si>
     <t xml:space="preserve">29.9515781402588</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6125316619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9951915740967</t>
+    <t xml:space="preserve">30.61252784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9951877593994</t>
   </si>
   <si>
     <t xml:space="preserve">31.6039619445801</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8300743103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5691699981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8648662567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7778949737549</t>
+    <t xml:space="preserve">31.8300704956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5691738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8648586273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7778968811035</t>
   </si>
   <si>
     <t xml:space="preserve">31.4995994567871</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0387992858887</t>
+    <t xml:space="preserve">32.0387954711914</t>
   </si>
   <si>
     <t xml:space="preserve">31.6909255981445</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3430557250977</t>
+    <t xml:space="preserve">31.3430614471436</t>
   </si>
   <si>
     <t xml:space="preserve">31.4474201202393</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2734813690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7604961395264</t>
+    <t xml:space="preserve">31.2734832763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7604999542236</t>
   </si>
   <si>
     <t xml:space="preserve">31.7083225250244</t>
@@ -3140,10 +3140,10 @@
     <t xml:space="preserve">31.5865669250488</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7431106567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6387481689453</t>
+    <t xml:space="preserve">31.743106842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.638744354248</t>
   </si>
   <si>
     <t xml:space="preserve">31.6735363006592</t>
@@ -3152,34 +3152,34 @@
     <t xml:space="preserve">32.3866691589355</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5606002807617</t>
+    <t xml:space="preserve">32.560604095459</t>
   </si>
   <si>
     <t xml:space="preserve">31.847469329834</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5432090759277</t>
+    <t xml:space="preserve">32.5432052612305</t>
   </si>
   <si>
     <t xml:space="preserve">31.8996524810791</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5169925689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7952880859375</t>
+    <t xml:space="preserve">31.5169944763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7952919006348</t>
   </si>
   <si>
     <t xml:space="preserve">31.8126811981201</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6213474273682</t>
+    <t xml:space="preserve">31.6213550567627</t>
   </si>
   <si>
     <t xml:space="preserve">31.4822101593018</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3952350616455</t>
+    <t xml:space="preserve">31.3952388763428</t>
   </si>
   <si>
     <t xml:space="preserve">32.155330657959</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">31.9081153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7845058441162</t>
+    <t xml:space="preserve">31.7845077514648</t>
   </si>
   <si>
     <t xml:space="preserve">32.1376724243164</t>
@@ -3197,19 +3197,19 @@
     <t xml:space="preserve">32.1729850769043</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2612762451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2789344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7491912841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7668533325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8727970123291</t>
+    <t xml:space="preserve">32.2612800598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.278938293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7491931915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7668552398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8728008270264</t>
   </si>
   <si>
     <t xml:space="preserve">32.6674118041992</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">33.3031044006348</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3096122741699</t>
+    <t xml:space="preserve">34.3096084594727</t>
   </si>
   <si>
     <t xml:space="preserve">34.9982719421387</t>
@@ -3233,10 +3233,10 @@
     <t xml:space="preserve">34.9806175231934</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2808074951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.786376953125</t>
+    <t xml:space="preserve">35.2808036804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7863807678223</t>
   </si>
   <si>
     <t xml:space="preserve">33.9564476013184</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">33.3384170532227</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9499435424805</t>
+    <t xml:space="preserve">32.9499397277832</t>
   </si>
   <si>
     <t xml:space="preserve">33.179500579834</t>
@@ -3260,13 +3260,13 @@
     <t xml:space="preserve">33.0912055969238</t>
   </si>
   <si>
-    <t xml:space="preserve">32.437858581543</t>
+    <t xml:space="preserve">32.4378623962402</t>
   </si>
   <si>
     <t xml:space="preserve">33.0205764770508</t>
   </si>
   <si>
-    <t xml:space="preserve">32.843994140625</t>
+    <t xml:space="preserve">32.8439903259277</t>
   </si>
   <si>
     <t xml:space="preserve">33.1441802978516</t>
@@ -3281,19 +3281,19 @@
     <t xml:space="preserve">32.7027282714844</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2677879333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4267082214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8616485595703</t>
+    <t xml:space="preserve">33.2677841186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4267120361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8616523742676</t>
   </si>
   <si>
     <t xml:space="preserve">32.2083015441895</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2017955780029</t>
+    <t xml:space="preserve">31.2017917633057</t>
   </si>
   <si>
     <t xml:space="preserve">31.1135025024414</t>
@@ -3302,61 +3302,61 @@
     <t xml:space="preserve">31.9610939025879</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1265182495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9322776794434</t>
+    <t xml:space="preserve">33.126522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9322814941406</t>
   </si>
   <si>
     <t xml:space="preserve">31.9257755279541</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5438079833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0270843505859</t>
+    <t xml:space="preserve">32.5438041687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0270805358887</t>
   </si>
   <si>
     <t xml:space="preserve">33.8681602478027</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0800552368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3449287414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3802452087402</t>
+    <t xml:space="preserve">34.0800514221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3449325561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3802375793457</t>
   </si>
   <si>
     <t xml:space="preserve">34.1330299377441</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5215072631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.150691986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2036666870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1153678894043</t>
+    <t xml:space="preserve">34.5215110778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1506881713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2036628723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1153717041016</t>
   </si>
   <si>
     <t xml:space="preserve">33.938793182373</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6209487915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6915817260742</t>
+    <t xml:space="preserve">33.6209526062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.691577911377</t>
   </si>
   <si>
     <t xml:space="preserve">34.2919540405273</t>
   </si>
   <si>
-    <t xml:space="preserve">34.503849029541</t>
+    <t xml:space="preserve">34.5038528442383</t>
   </si>
   <si>
     <t xml:space="preserve">32.914623260498</t>
@@ -3365,10 +3365,10 @@
     <t xml:space="preserve">33.1971549987793</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5149955749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5503120422363</t>
+    <t xml:space="preserve">33.5149993896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5503158569336</t>
   </si>
   <si>
     <t xml:space="preserve">33.815185546875</t>
@@ -3377,10 +3377,10 @@
     <t xml:space="preserve">34.6451187133789</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1395378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8570098876953</t>
+    <t xml:space="preserve">35.1395416259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8570137023926</t>
   </si>
   <si>
     <t xml:space="preserve">34.6804351806641</t>
@@ -3389,19 +3389,19 @@
     <t xml:space="preserve">35.0865707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3272705078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2371120452881</t>
+    <t xml:space="preserve">34.3272666931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2371101379395</t>
   </si>
   <si>
     <t xml:space="preserve">30.424840927124</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1776275634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0716781616211</t>
+    <t xml:space="preserve">30.1776294708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0716800689697</t>
   </si>
   <si>
     <t xml:space="preserve">29.5595932006836</t>
@@ -3413,28 +3413,28 @@
     <t xml:space="preserve">29.6478843688965</t>
   </si>
   <si>
-    <t xml:space="preserve">30.230598449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3476982116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0121936798096</t>
+    <t xml:space="preserve">30.2306003570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3477001190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0121955871582</t>
   </si>
   <si>
     <t xml:space="preserve">28.2882137298584</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8467636108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4406261444092</t>
+    <t xml:space="preserve">27.8467617034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4406280517578</t>
   </si>
   <si>
     <t xml:space="preserve">28.5530853271484</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0939750671387</t>
+    <t xml:space="preserve">28.09397315979</t>
   </si>
   <si>
     <t xml:space="preserve">27.7937870025635</t>
@@ -3446,13 +3446,13 @@
     <t xml:space="preserve">28.0763149261475</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0410003662109</t>
+    <t xml:space="preserve">28.0409984588623</t>
   </si>
   <si>
     <t xml:space="preserve">28.3058738708496</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2240886688232</t>
+    <t xml:space="preserve">29.2240905761719</t>
   </si>
   <si>
     <t xml:space="preserve">29.1004829406738</t>
@@ -3467,22 +3467,22 @@
     <t xml:space="preserve">29.3123817443848</t>
   </si>
   <si>
-    <t xml:space="preserve">29.824462890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.948070526123</t>
+    <t xml:space="preserve">29.8244609832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9480667114258</t>
   </si>
   <si>
     <t xml:space="preserve">29.7891502380371</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2417488098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8421230316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0010452270508</t>
+    <t xml:space="preserve">29.2417469024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8421211242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0010433197021</t>
   </si>
   <si>
     <t xml:space="preserve">29.9833850860596</t>
@@ -3491,19 +3491,19 @@
     <t xml:space="preserve">30.5661010742188</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9545822143555</t>
+    <t xml:space="preserve">30.9545783996582</t>
   </si>
   <si>
     <t xml:space="preserve">30.1952857971191</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1246490478516</t>
+    <t xml:space="preserve">30.1246509552002</t>
   </si>
   <si>
     <t xml:space="preserve">29.3300380706787</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2287311553955</t>
+    <t xml:space="preserve">27.2287292480469</t>
   </si>
   <si>
     <t xml:space="preserve">26.8402519226074</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">26.9462013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6106986999512</t>
+    <t xml:space="preserve">26.6106967926025</t>
   </si>
   <si>
     <t xml:space="preserve">27.2817039489746</t>
@@ -3527,52 +3527,52 @@
     <t xml:space="preserve">26.6989879608154</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8755683898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0698051452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7807712554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4341163635254</t>
+    <t xml:space="preserve">26.8755702972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0698070526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7807693481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.434118270874</t>
   </si>
   <si>
     <t xml:space="preserve">26.1162719726562</t>
   </si>
   <si>
-    <t xml:space="preserve">26.85791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3634834289551</t>
+    <t xml:space="preserve">26.8579120635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3634853363037</t>
   </si>
   <si>
     <t xml:space="preserve">26.1339302062988</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3987998962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1404361724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5753803253174</t>
+    <t xml:space="preserve">26.3988018035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.140438079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.575382232666</t>
   </si>
   <si>
     <t xml:space="preserve">26.7519607543945</t>
   </si>
   <si>
-    <t xml:space="preserve">26.310510635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4694328308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8225936889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2110729217529</t>
+    <t xml:space="preserve">26.3105087280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4694309234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8225955963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2110710144043</t>
   </si>
   <si>
     <t xml:space="preserve">27.0521488189697</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">26.981517791748</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9350528717041</t>
+    <t xml:space="preserve">27.9350509643555</t>
   </si>
   <si>
     <t xml:space="preserve">27.8291034698486</t>
@@ -3593,19 +3593,19 @@
     <t xml:space="preserve">27.405309677124</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7761268615723</t>
+    <t xml:space="preserve">27.7761287689209</t>
   </si>
   <si>
     <t xml:space="preserve">27.6525249481201</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3699932098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4164581298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9155216217041</t>
+    <t xml:space="preserve">27.3699913024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4164562225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9155235290527</t>
   </si>
   <si>
     <t xml:space="preserve">25.0214710235596</t>
@@ -3617,25 +3617,25 @@
     <t xml:space="preserve">24.8978672027588</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2686862945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5447044372559</t>
+    <t xml:space="preserve">25.268684387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5447025299072</t>
   </si>
   <si>
     <t xml:space="preserve">24.10325050354</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8383808135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.692476272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4517726898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5112552642822</t>
+    <t xml:space="preserve">23.8383827209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6924781799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.451774597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5112590789795</t>
   </si>
   <si>
     <t xml:space="preserve">27.9703674316406</t>
@@ -3644,10 +3644,10 @@
     <t xml:space="preserve">27.2993602752686</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9285449981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5289173126221</t>
+    <t xml:space="preserve">26.9285430908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5289192199707</t>
   </si>
   <si>
     <t xml:space="preserve">27.4759426116943</t>
@@ -3659,7 +3659,7 @@
     <t xml:space="preserve">26.3811416625977</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8932228088379</t>
+    <t xml:space="preserve">26.8932247161865</t>
   </si>
   <si>
     <t xml:space="preserve">27.1757564544678</t>
@@ -3671,28 +3671,28 @@
     <t xml:space="preserve">26.0986156463623</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4629249572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8095741271973</t>
+    <t xml:space="preserve">25.4629230499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8095760345459</t>
   </si>
   <si>
     <t xml:space="preserve">25.2333679199219</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1274185180664</t>
+    <t xml:space="preserve">25.1274166107178</t>
   </si>
   <si>
     <t xml:space="preserve">24.7389450073242</t>
   </si>
   <si>
-    <t xml:space="preserve">24.173885345459</t>
+    <t xml:space="preserve">24.1738834381104</t>
   </si>
   <si>
     <t xml:space="preserve">22.4080791473389</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4192276000977</t>
+    <t xml:space="preserve">21.4192295074463</t>
   </si>
   <si>
     <t xml:space="preserve">21.3662548065186</t>
@@ -3701,7 +3701,7 @@
     <t xml:space="preserve">22.6906070709229</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0660667419434</t>
+    <t xml:space="preserve">21.066068649292</t>
   </si>
   <si>
     <t xml:space="preserve">20.9424591064453</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">21.8077030181885</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5251750946045</t>
+    <t xml:space="preserve">21.5251731872559</t>
   </si>
   <si>
     <t xml:space="preserve">21.4722023010254</t>
@@ -3740,13 +3740,13 @@
     <t xml:space="preserve">22.990795135498</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3374462127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8430213928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7547302246094</t>
+    <t xml:space="preserve">22.3374443054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8430233001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.754732131958</t>
   </si>
   <si>
     <t xml:space="preserve">21.7900485992432</t>
@@ -3758,13 +3758,13 @@
     <t xml:space="preserve">21.3839111328125</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9601173400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1896724700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.136697769165</t>
+    <t xml:space="preserve">20.9601192474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1896705627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1366996765137</t>
   </si>
   <si>
     <t xml:space="preserve">21.4015674591064</t>
@@ -3776,34 +3776,34 @@
     <t xml:space="preserve">20.8365116119385</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0595550537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9359493255615</t>
+    <t xml:space="preserve">20.0595569610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9359512329102</t>
   </si>
   <si>
     <t xml:space="preserve">20.3774013519287</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5186672210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8653202056885</t>
+    <t xml:space="preserve">20.5186653137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8653182983398</t>
   </si>
   <si>
     <t xml:space="preserve">20.0065822601318</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7835388183594</t>
+    <t xml:space="preserve">20.7835369110107</t>
   </si>
   <si>
     <t xml:space="preserve">20.5363254547119</t>
   </si>
   <si>
-    <t xml:space="preserve">20.041898727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1943130493164</t>
+    <t xml:space="preserve">20.0418968200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1943111419678</t>
   </si>
   <si>
     <t xml:space="preserve">19.4238662719727</t>
@@ -3818,13 +3818,13 @@
     <t xml:space="preserve">19.3355751037598</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5474720001221</t>
+    <t xml:space="preserve">19.5474739074707</t>
   </si>
   <si>
     <t xml:space="preserve">19.6710815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">19.911153793335</t>
+    <t xml:space="preserve">19.9111518859863</t>
   </si>
   <si>
     <t xml:space="preserve">19.0677719116211</t>
@@ -3842,19 +3842,19 @@
     <t xml:space="preserve">20.9012107849121</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6995315551758</t>
+    <t xml:space="preserve">20.6995334625244</t>
   </si>
   <si>
     <t xml:space="preserve">20.3145122528076</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6445293426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0944995880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4061851501465</t>
+    <t xml:space="preserve">20.64453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0944976806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4061832427979</t>
   </si>
   <si>
     <t xml:space="preserve">20.1678371429443</t>
@@ -3866,43 +3866,43 @@
     <t xml:space="preserve">19.3061180114746</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3710651397705</t>
+    <t xml:space="preserve">18.3710670471191</t>
   </si>
   <si>
     <t xml:space="preserve">18.7560882568359</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0127696990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0960483551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0861034393311</t>
+    <t xml:space="preserve">19.012767791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0960502624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0861053466797</t>
   </si>
   <si>
     <t xml:space="preserve">17.729362487793</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9493751525879</t>
+    <t xml:space="preserve">17.9493770599365</t>
   </si>
   <si>
     <t xml:space="preserve">17.2801704406738</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2618312835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1793308258057</t>
+    <t xml:space="preserve">17.261833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.179328918457</t>
   </si>
   <si>
     <t xml:space="preserve">17.2343330383301</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0968246459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.757640838623</t>
+    <t xml:space="preserve">17.0968227386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7576389312744</t>
   </si>
   <si>
     <t xml:space="preserve">16.2626094818115</t>
@@ -3911,13 +3911,13 @@
     <t xml:space="preserve">16.1617698669434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1709384918213</t>
+    <t xml:space="preserve">16.1709365844727</t>
   </si>
   <si>
     <t xml:space="preserve">15.9875946044922</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3817844390869</t>
+    <t xml:space="preserve">16.3817863464355</t>
   </si>
   <si>
     <t xml:space="preserve">16.7851390838623</t>
@@ -3926,13 +3926,13 @@
     <t xml:space="preserve">17.0601558685303</t>
   </si>
   <si>
-    <t xml:space="preserve">17.188497543335</t>
+    <t xml:space="preserve">17.1884994506836</t>
   </si>
   <si>
     <t xml:space="preserve">17.4635124206543</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9501495361328</t>
+    <t xml:space="preserve">16.9501476287842</t>
   </si>
   <si>
     <t xml:space="preserve">16.4092845916748</t>
@@ -3941,7 +3941,7 @@
     <t xml:space="preserve">16.6843013763428</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9043140411377</t>
+    <t xml:space="preserve">16.9043121337891</t>
   </si>
   <si>
     <t xml:space="preserve">17.0693225860596</t>
@@ -3956,10 +3956,10 @@
     <t xml:space="preserve">16.8676452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3359489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8500871658325</t>
+    <t xml:space="preserve">16.3359470367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8500881195068</t>
   </si>
   <si>
     <t xml:space="preserve">16.8218078613281</t>
@@ -3968,10 +3968,10 @@
     <t xml:space="preserve">16.5284595489502</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1151599884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8852062225342</t>
+    <t xml:space="preserve">17.1151580810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8852024078369</t>
   </si>
   <si>
     <t xml:space="preserve">17.6560230255127</t>
@@ -3995,25 +3995,25 @@
     <t xml:space="preserve">17.6651916503906</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2159976959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3351707458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9868183135986</t>
+    <t xml:space="preserve">17.2159996032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3351726531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.98681640625</t>
   </si>
   <si>
     <t xml:space="preserve">17.0784893035889</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8584785461426</t>
+    <t xml:space="preserve">16.8584766387939</t>
   </si>
   <si>
     <t xml:space="preserve">16.4001178741455</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9967622756958</t>
+    <t xml:space="preserve">15.9967613220215</t>
   </si>
   <si>
     <t xml:space="preserve">15.9417572021484</t>
@@ -4040,19 +4040,19 @@
     <t xml:space="preserve">15.2175493240356</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1992149353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6117401123047</t>
+    <t xml:space="preserve">15.1992158889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6117391586304</t>
   </si>
   <si>
     <t xml:space="preserve">16.0059280395508</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6942415237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9883708953857</t>
+    <t xml:space="preserve">15.6942434310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9883699417114</t>
   </si>
   <si>
     <t xml:space="preserve">14.5758438110352</t>
@@ -4061,7 +4061,7 @@
     <t xml:space="preserve">14.5850114822388</t>
   </si>
   <si>
-    <t xml:space="preserve">13.860803604126</t>
+    <t xml:space="preserve">13.8608026504517</t>
   </si>
   <si>
     <t xml:space="preserve">13.8058004379272</t>
@@ -4070,31 +4070,31 @@
     <t xml:space="preserve">13.6041231155396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3841104507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.585786819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7599639892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.924973487854</t>
+    <t xml:space="preserve">13.3841094970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5857877731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7599649429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9249744415283</t>
   </si>
   <si>
     <t xml:space="preserve">13.3107719421387</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8149681091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5032825469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8883037567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5124502182007</t>
+    <t xml:space="preserve">13.8149671554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5032815933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8883047103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.512451171875</t>
   </si>
   <si>
     <t xml:space="preserve">13.6591243743896</t>
@@ -4106,28 +4106,28 @@
     <t xml:space="preserve">13.4482793807983</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8516368865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5307836532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8424701690674</t>
+    <t xml:space="preserve">13.8516359329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5307846069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8424692153931</t>
   </si>
   <si>
     <t xml:space="preserve">14.1908226013184</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3466644287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.603346824646</t>
+    <t xml:space="preserve">14.3466653823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6033458709717</t>
   </si>
   <si>
     <t xml:space="preserve">14.1816549301147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5483436584473</t>
+    <t xml:space="preserve">14.5483427047729</t>
   </si>
   <si>
     <t xml:space="preserve">14.8233594894409</t>
@@ -4136,22 +4136,22 @@
     <t xml:space="preserve">15.5659017562866</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7217454910278</t>
+    <t xml:space="preserve">15.7217445373535</t>
   </si>
   <si>
     <t xml:space="preserve">15.9050903320312</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1526031494141</t>
+    <t xml:space="preserve">16.1526050567627</t>
   </si>
   <si>
     <t xml:space="preserve">16.7026348114014</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2434997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5093479156494</t>
+    <t xml:space="preserve">17.243501663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.509349822998</t>
   </si>
   <si>
     <t xml:space="preserve">18.2427234649658</t>
@@ -4163,10 +4163,10 @@
     <t xml:space="preserve">20.717866897583</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4161243438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1594429016113</t>
+    <t xml:space="preserve">19.4161262512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.15944480896</t>
   </si>
   <si>
     <t xml:space="preserve">19.0494384765625</t>
@@ -4175,13 +4175,13 @@
     <t xml:space="preserve">19.617805480957</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2595081329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7094783782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3794574737549</t>
+    <t xml:space="preserve">20.2595100402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7094764709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3794555664062</t>
   </si>
   <si>
     <t xml:space="preserve">19.562801361084</t>
@@ -4190,22 +4190,22 @@
     <t xml:space="preserve">19.8928203582764</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6544723510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8561496734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4527969360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5261306762695</t>
+    <t xml:space="preserve">19.6544742584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8561515808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4527950286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5261325836182</t>
   </si>
   <si>
     <t xml:space="preserve">19.7278099060059</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3695125579834</t>
+    <t xml:space="preserve">20.369514465332</t>
   </si>
   <si>
     <t xml:space="preserve">19.8378162384033</t>
@@ -4217,22 +4217,22 @@
     <t xml:space="preserve">18.9760990142822</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9577655792236</t>
+    <t xml:space="preserve">18.9577674865723</t>
   </si>
   <si>
     <t xml:space="preserve">19.2144470214844</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6728057861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2327823638916</t>
+    <t xml:space="preserve">19.6728076934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.232780456543</t>
   </si>
   <si>
     <t xml:space="preserve">20.0578289031982</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1128311157227</t>
+    <t xml:space="preserve">20.1128330230713</t>
   </si>
   <si>
     <t xml:space="preserve">20.2961769104004</t>
@@ -4250,19 +4250,19 @@
     <t xml:space="preserve">20.992883682251</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7728710174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8828792572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0478858947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8095397949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7362022399902</t>
+    <t xml:space="preserve">20.7728691101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8828773498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.047887802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8095378875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7362041473389</t>
   </si>
   <si>
     <t xml:space="preserve">19.7828121185303</t>
@@ -4274,7 +4274,7 @@
     <t xml:space="preserve">19.2511157989502</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8660945892334</t>
+    <t xml:space="preserve">18.8660926818848</t>
   </si>
   <si>
     <t xml:space="preserve">19.3977909088135</t>
@@ -4298,10 +4298,10 @@
     <t xml:space="preserve">20.1495018005371</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0761642456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0394973754883</t>
+    <t xml:space="preserve">20.0761623382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0394954681396</t>
   </si>
   <si>
     <t xml:space="preserve">20.9745483398438</t>
@@ -4310,28 +4310,28 @@
     <t xml:space="preserve">21.2128963470459</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5795860290527</t>
+    <t xml:space="preserve">21.5795841217041</t>
   </si>
   <si>
     <t xml:space="preserve">21.6345882415771</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6529235839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6162528991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5429153442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6812000274658</t>
+    <t xml:space="preserve">21.6529216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6162509918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5429172515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6811981201172</t>
   </si>
   <si>
     <t xml:space="preserve">21.3045673370361</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6628665924072</t>
+    <t xml:space="preserve">20.6628646850586</t>
   </si>
   <si>
     <t xml:space="preserve">20.4245204925537</t>
@@ -4340,13 +4340,13 @@
     <t xml:space="preserve">20.5711936950684</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9661598205566</t>
+    <t xml:space="preserve">19.966157913208</t>
   </si>
   <si>
     <t xml:space="preserve">19.5077991485596</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3611240386963</t>
+    <t xml:space="preserve">19.3611221313477</t>
   </si>
   <si>
     <t xml:space="preserve">19.5444660186768</t>
@@ -4358,7 +4358,7 @@
     <t xml:space="preserve">20.0211601257324</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6460819244385</t>
+    <t xml:space="preserve">18.6460800170898</t>
   </si>
   <si>
     <t xml:space="preserve">18.4444026947021</t>
@@ -4367,25 +4367,25 @@
     <t xml:space="preserve">18.481071472168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.609411239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.407735824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3343963623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9210968017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2877864837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1961135864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1044425964355</t>
+    <t xml:space="preserve">18.6094093322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4077339172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3343944549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9210948944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.287784576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1961116790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1044406890869</t>
   </si>
   <si>
     <t xml:space="preserve">18.7201499938965</t>
@@ -4400,13 +4400,13 @@
     <t xml:space="preserve">17.5378246307373</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7348766326904</t>
+    <t xml:space="preserve">17.7348785400391</t>
   </si>
   <si>
     <t xml:space="preserve">17.6410427093506</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2469348907471</t>
+    <t xml:space="preserve">17.2469329833984</t>
   </si>
   <si>
     <t xml:space="preserve">17.1437168121338</t>
@@ -4424,7 +4424,7 @@
     <t xml:space="preserve">17.0311126708984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9560432434082</t>
+    <t xml:space="preserve">16.9560451507568</t>
   </si>
   <si>
     <t xml:space="preserve">16.89035987854</t>
@@ -4436,19 +4436,19 @@
     <t xml:space="preserve">17.078031539917</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1852874755859</t>
+    <t xml:space="preserve">18.1852855682373</t>
   </si>
   <si>
     <t xml:space="preserve">18.2885055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5659732818604</t>
+    <t xml:space="preserve">17.565975189209</t>
   </si>
   <si>
     <t xml:space="preserve">18.0069999694824</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9225482940674</t>
+    <t xml:space="preserve">17.922550201416</t>
   </si>
   <si>
     <t xml:space="preserve">17.8662490844727</t>
@@ -4457,28 +4457,28 @@
     <t xml:space="preserve">17.8005619049072</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5753574371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7536449432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9319324493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9882354736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3354244232178</t>
+    <t xml:space="preserve">17.5753593444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7536468505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9319343566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9882335662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3354263305664</t>
   </si>
   <si>
     <t xml:space="preserve">18.5137119293213</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7858352661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5230941772461</t>
+    <t xml:space="preserve">18.7858333587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5230960845947</t>
   </si>
   <si>
     <t xml:space="preserve">18.7483005523682</t>
@@ -4505,13 +4505,13 @@
     <t xml:space="preserve">20.3435001373291</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7804889678955</t>
+    <t xml:space="preserve">19.7804870605469</t>
   </si>
   <si>
     <t xml:space="preserve">19.8555564880371</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8743228912354</t>
+    <t xml:space="preserve">19.874324798584</t>
   </si>
   <si>
     <t xml:space="preserve">19.198709487915</t>
@@ -4523,19 +4523,19 @@
     <t xml:space="preserve">19.6678848266602</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2737770080566</t>
+    <t xml:space="preserve">19.2737789154053</t>
   </si>
   <si>
     <t xml:space="preserve">19.4989833831787</t>
   </si>
   <si>
-    <t xml:space="preserve">20.362268447876</t>
+    <t xml:space="preserve">20.3622665405273</t>
   </si>
   <si>
     <t xml:space="preserve">20.7939109802246</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6759624481201</t>
+    <t xml:space="preserve">21.6759643554688</t>
   </si>
   <si>
     <t xml:space="preserve">21.826099395752</t>
@@ -4544,7 +4544,7 @@
     <t xml:space="preserve">22.0325355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1639080047607</t>
+    <t xml:space="preserve">22.1639060974121</t>
   </si>
   <si>
     <t xml:space="preserve">22.0888385772705</t>
@@ -4559,19 +4559,19 @@
     <t xml:space="preserve">22.2389755249023</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2952747344971</t>
+    <t xml:space="preserve">22.2952766418457</t>
   </si>
   <si>
     <t xml:space="preserve">22.482946395874</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9574680328369</t>
+    <t xml:space="preserve">21.9574661254883</t>
   </si>
   <si>
     <t xml:space="preserve">21.8448677062988</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7698001861572</t>
+    <t xml:space="preserve">21.7697982788086</t>
   </si>
   <si>
     <t xml:space="preserve">21.7134971618652</t>
@@ -4580,13 +4580,13 @@
     <t xml:space="preserve">21.995002746582</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5767822265625</t>
+    <t xml:space="preserve">22.5767803192139</t>
   </si>
   <si>
     <t xml:space="preserve">22.670618057251</t>
   </si>
   <si>
-    <t xml:space="preserve">22.970890045166</t>
+    <t xml:space="preserve">22.9708881378174</t>
   </si>
   <si>
     <t xml:space="preserve">22.914587020874</t>
@@ -4595,13 +4595,13 @@
     <t xml:space="preserve">23.158561706543</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2711620330811</t>
+    <t xml:space="preserve">23.2711639404297</t>
   </si>
   <si>
     <t xml:space="preserve">23.1397933959961</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4882907867432</t>
+    <t xml:space="preserve">21.4882926940918</t>
   </si>
   <si>
     <t xml:space="preserve">21.8824005126953</t>
@@ -4610,37 +4610,37 @@
     <t xml:space="preserve">21.8636322021484</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9252777099609</t>
+    <t xml:space="preserve">20.9252796173096</t>
   </si>
   <si>
     <t xml:space="preserve">21.0003471374512</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1692523956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2443199157715</t>
+    <t xml:space="preserve">21.1692504882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2443180084229</t>
   </si>
   <si>
     <t xml:space="preserve">20.8877468109131</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6813087463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1182956695557</t>
+    <t xml:space="preserve">20.6813106536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1182975769043</t>
   </si>
   <si>
     <t xml:space="preserve">20.3998012542725</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8930912017822</t>
+    <t xml:space="preserve">19.8930931091309</t>
   </si>
   <si>
     <t xml:space="preserve">19.2174758911133</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3488464355469</t>
+    <t xml:space="preserve">19.3488483428955</t>
   </si>
   <si>
     <t xml:space="preserve">19.7992553710938</t>
@@ -4664,7 +4664,7 @@
     <t xml:space="preserve">19.4426803588867</t>
   </si>
   <si>
-    <t xml:space="preserve">19.330078125</t>
+    <t xml:space="preserve">19.3300800323486</t>
   </si>
   <si>
     <t xml:space="preserve">18.9359703063965</t>
@@ -4679,7 +4679,7 @@
     <t xml:space="preserve">19.686653137207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1236400604248</t>
+    <t xml:space="preserve">19.1236419677734</t>
   </si>
   <si>
     <t xml:space="preserve">18.9922695159912</t>
@@ -4691,7 +4691,7 @@
     <t xml:space="preserve">19.4051475524902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8180236816406</t>
+    <t xml:space="preserve">19.818021774292</t>
   </si>
   <si>
     <t xml:space="preserve">19.9681606292725</t>
@@ -4700,13 +4700,13 @@
     <t xml:space="preserve">20.606237411499</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4695224761963</t>
+    <t xml:space="preserve">21.4695243835449</t>
   </si>
   <si>
     <t xml:space="preserve">24.7162265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5848579406738</t>
+    <t xml:space="preserve">24.5848598480225</t>
   </si>
   <si>
     <t xml:space="preserve">24.6974601745605</t>
@@ -4718,13 +4718,13 @@
     <t xml:space="preserve">24.922664642334</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8475952148438</t>
+    <t xml:space="preserve">24.8475971221924</t>
   </si>
   <si>
     <t xml:space="preserve">25.4293766021729</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0486888885498</t>
+    <t xml:space="preserve">26.0486869812012</t>
   </si>
   <si>
     <t xml:space="preserve">25.710880279541</t>
@@ -4733,7 +4733,7 @@
     <t xml:space="preserve">26.2363605499268</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8422508239746</t>
+    <t xml:space="preserve">25.8422527313232</t>
   </si>
   <si>
     <t xml:space="preserve">25.9360847473145</t>
@@ -4745,10 +4745,10 @@
     <t xml:space="preserve">25.7484169006348</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0674571990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5741653442383</t>
+    <t xml:space="preserve">26.067455291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5741672515869</t>
   </si>
   <si>
     <t xml:space="preserve">26.3114280700684</t>
@@ -4760,13 +4760,13 @@
     <t xml:space="preserve">26.7806053161621</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9119739532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0058097839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2310161590576</t>
+    <t xml:space="preserve">26.9119758605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0058116912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.231014251709</t>
   </si>
   <si>
     <t xml:space="preserve">27.1184120178223</t>
@@ -4781,16 +4781,16 @@
     <t xml:space="preserve">27.6814250946045</t>
   </si>
   <si>
-    <t xml:space="preserve">27.718957901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4749870300293</t>
+    <t xml:space="preserve">27.7189598083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4749851226807</t>
   </si>
   <si>
     <t xml:space="preserve">27.7377262115479</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1693668365479</t>
+    <t xml:space="preserve">28.1693687438965</t>
   </si>
   <si>
     <t xml:space="preserve">27.9629287719727</t>
@@ -4799,25 +4799,25 @@
     <t xml:space="preserve">28.6573123931885</t>
   </si>
   <si>
-    <t xml:space="preserve">28.507173538208</t>
+    <t xml:space="preserve">28.5071754455566</t>
   </si>
   <si>
     <t xml:space="preserve">28.6385440826416</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9307403564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7752590179443</t>
+    <t xml:space="preserve">26.9307422637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.775260925293</t>
   </si>
   <si>
     <t xml:space="preserve">27.8878612518311</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4321041107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8074493408203</t>
+    <t xml:space="preserve">28.4321060180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8074474334717</t>
   </si>
   <si>
     <t xml:space="preserve">29.2766265869141</t>
@@ -4832,16 +4832,16 @@
     <t xml:space="preserve">28.1881351470947</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8315620422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7940273284912</t>
+    <t xml:space="preserve">27.8315601348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7940292358398</t>
   </si>
   <si>
     <t xml:space="preserve">27.9253959655762</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2819709777832</t>
+    <t xml:space="preserve">28.2819690704346</t>
   </si>
   <si>
     <t xml:space="preserve">29.1640224456787</t>
@@ -4862,13 +4862,13 @@
     <t xml:space="preserve">27.5500545501709</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1934776306152</t>
+    <t xml:space="preserve">27.1934795379639</t>
   </si>
   <si>
     <t xml:space="preserve">26.7243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2175922393799</t>
+    <t xml:space="preserve">26.2175941467285</t>
   </si>
   <si>
     <t xml:space="preserve">26.874439239502</t>
@@ -4895,10 +4895,10 @@
     <t xml:space="preserve">28.206901550293</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9951190948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0192317962646</t>
+    <t xml:space="preserve">28.9951171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.019229888916</t>
   </si>
   <si>
     <t xml:space="preserve">28.4884090423584</t>
@@ -4922,16 +4922,16 @@
     <t xml:space="preserve">30.383882522583</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0460739135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1211395263672</t>
+    <t xml:space="preserve">30.0460758209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1211414337158</t>
   </si>
   <si>
     <t xml:space="preserve">29.6519660949707</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9897727966309</t>
+    <t xml:space="preserve">29.9897708892822</t>
   </si>
   <si>
     <t xml:space="preserve">30.083610534668</t>
@@ -4952,13 +4952,13 @@
     <t xml:space="preserve">29.9334716796875</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5259399414062</t>
+    <t xml:space="preserve">28.5259418487549</t>
   </si>
   <si>
     <t xml:space="preserve">28.3007354736328</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0943012237549</t>
+    <t xml:space="preserve">28.0942993164062</t>
   </si>
   <si>
     <t xml:space="preserve">28.0379962921143</t>
@@ -4973,13 +4973,13 @@
     <t xml:space="preserve">29.5205955505371</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9763488769531</t>
+    <t xml:space="preserve">28.9763507843018</t>
   </si>
   <si>
     <t xml:space="preserve">29.4830627441406</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7645664215088</t>
+    <t xml:space="preserve">29.7645683288574</t>
   </si>
   <si>
     <t xml:space="preserve">28.9575843811035</t>
@@ -4997,7 +4997,7 @@
     <t xml:space="preserve">30.7779903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3973026275635</t>
+    <t xml:space="preserve">31.3973007202148</t>
   </si>
   <si>
     <t xml:space="preserve">29.5581321716309</t>
@@ -71012,7 +71012,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.649537037</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>156027</v>
@@ -71033,6 +71033,32 @@
         <v>1947</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6506365741</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>146846</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>31.0599994659424</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>30.3400001525879</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>30.8799991607666</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>30.8999996185303</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>1947</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DLG.MI.xlsx
+++ b/data/DLG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1951" uniqueCount="1951">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="1952">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">20.739143371582</t>
+    <t xml:space="preserve">20.7391452789307</t>
   </si>
   <si>
     <t xml:space="preserve">DLG.MI</t>
@@ -47,37 +47,37 @@
     <t xml:space="preserve">20.5564193725586</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6553936004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1757469177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9777946472168</t>
+    <t xml:space="preserve">20.6553974151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.175745010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9777965545654</t>
   </si>
   <si>
     <t xml:space="preserve">19.7722320556641</t>
   </si>
   <si>
-    <t xml:space="preserve">19.490535736084</t>
+    <t xml:space="preserve">19.4905319213867</t>
   </si>
   <si>
     <t xml:space="preserve">19.8864307403564</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5160083770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6328430175781</t>
+    <t xml:space="preserve">18.5160064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6328411102295</t>
   </si>
   <si>
     <t xml:space="preserve">17.4348926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5262546539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0542163848877</t>
+    <t xml:space="preserve">17.526252746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0542182922363</t>
   </si>
   <si>
     <t xml:space="preserve">16.8943328857422</t>
@@ -89,25 +89,25 @@
     <t xml:space="preserve">16.6354732513428</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4451370239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7116088867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8029727935791</t>
+    <t xml:space="preserve">16.4451351165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7116107940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8029708862305</t>
   </si>
   <si>
     <t xml:space="preserve">16.6735401153564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.132984161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9654855728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6533308029175</t>
+    <t xml:space="preserve">16.1329860687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9654884338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6533317565918</t>
   </si>
   <si>
     <t xml:space="preserve">14.9909620285034</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">14.7777814865112</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3335666656494</t>
+    <t xml:space="preserve">15.3335647583008</t>
   </si>
   <si>
     <t xml:space="preserve">14.4123373031616</t>
@@ -125,22 +125,22 @@
     <t xml:space="preserve">14.7397155761719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4553813934326</t>
+    <t xml:space="preserve">15.4553823471069</t>
   </si>
   <si>
     <t xml:space="preserve">15.2574319839478</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4097013473511</t>
+    <t xml:space="preserve">15.4097051620483</t>
   </si>
   <si>
     <t xml:space="preserve">15.7523097991943</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3868589401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9121913909912</t>
+    <t xml:space="preserve">15.3868618011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9121923446655</t>
   </si>
   <si>
     <t xml:space="preserve">15.9578723907471</t>
@@ -149,25 +149,25 @@
     <t xml:space="preserve">15.5848121643066</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1253700256348</t>
+    <t xml:space="preserve">16.1253719329834</t>
   </si>
   <si>
     <t xml:space="preserve">16.1938934326172</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5593376159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7496757507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8817377090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2193689346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792476654053</t>
+    <t xml:space="preserve">16.5593395233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7496738433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.881739616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2193651199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792495727539</t>
   </si>
   <si>
     <t xml:space="preserve">16.0873012542725</t>
@@ -176,52 +176,52 @@
     <t xml:space="preserve">15.7142391204834</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2878856658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8969640731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3183403015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6076526641846</t>
+    <t xml:space="preserve">15.2878837585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8969669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3183393478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6076536178589</t>
   </si>
   <si>
     <t xml:space="preserve">15.9274206161499</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9883251190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8893518447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6152667999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3564052581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1356134414673</t>
+    <t xml:space="preserve">15.9883279800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8893537521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6152677536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3564071655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1356143951416</t>
   </si>
   <si>
     <t xml:space="preserve">15.226978302002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3487939834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0442543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2345914840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0594825744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1432294845581</t>
+    <t xml:space="preserve">15.3487920761108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0442562103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2345933914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0594835281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1432256698608</t>
   </si>
   <si>
     <t xml:space="preserve">14.5493783950806</t>
@@ -230,37 +230,37 @@
     <t xml:space="preserve">14.7853946685791</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8234596252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.783164024353</t>
+    <t xml:space="preserve">14.82346534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.783166885376</t>
   </si>
   <si>
     <t xml:space="preserve">14.977988243103</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.149432182312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9624032974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9857797622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.954607963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8533010482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4689426422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.671558380127</t>
+    <t xml:space="preserve">15.1572256088257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1494331359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9624052047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9857778549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9546098709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8533020019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4689435958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6715574264526</t>
   </si>
   <si>
     <t xml:space="preserve">16.21706199646</t>
@@ -269,46 +269,46 @@
     <t xml:space="preserve">15.7572793960571</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0300350189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.240442276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1469268798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3495445251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5053977966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3105792999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.728889465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7937393188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0742816925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7625694274902</t>
+    <t xml:space="preserve">16.030029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2404403686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1469287872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3495407104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5054016113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3105773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7288875579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.793737411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0742835998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.762565612793</t>
   </si>
   <si>
     <t xml:space="preserve">16.7547740936279</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8482913970947</t>
+    <t xml:space="preserve">16.8482894897461</t>
   </si>
   <si>
     <t xml:space="preserve">17.1132469177246</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3002796173096</t>
+    <t xml:space="preserve">17.3002777099609</t>
   </si>
   <si>
     <t xml:space="preserve">17.7678527832031</t>
@@ -317,22 +317,22 @@
     <t xml:space="preserve">17.9081268310547</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9470920562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0639839172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4848022460938</t>
+    <t xml:space="preserve">17.947093963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.063985824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4848003387451</t>
   </si>
   <si>
     <t xml:space="preserve">18.788724899292</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4614238739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3367347717285</t>
+    <t xml:space="preserve">18.46142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3367385864258</t>
   </si>
   <si>
     <t xml:space="preserve">18.274393081665</t>
@@ -344,16 +344,16 @@
     <t xml:space="preserve">18.6484527587891</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8276920318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4536323547363</t>
+    <t xml:space="preserve">18.8276882171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4536304473877</t>
   </si>
   <si>
     <t xml:space="preserve">17.8379898071289</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3937950134277</t>
+    <t xml:space="preserve">17.3937931060791</t>
   </si>
   <si>
     <t xml:space="preserve">17.2535190582275</t>
@@ -371,109 +371,109 @@
     <t xml:space="preserve">17.8224048614502</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7834396362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9315032958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6768455505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5234928131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1157569885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3651256561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6612586975098</t>
+    <t xml:space="preserve">17.7834377288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9315052032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6768436431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5234937667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1157550811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3651313781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6612567901611</t>
   </si>
   <si>
     <t xml:space="preserve">16.6300888061523</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8975563049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7806577682495</t>
+    <t xml:space="preserve">15.8975534439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7806606292725</t>
   </si>
   <si>
     <t xml:space="preserve">15.5468740463257</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7884521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3729209899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1858940124512</t>
+    <t xml:space="preserve">15.7884550094604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3729228973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1858921051025</t>
   </si>
   <si>
     <t xml:space="preserve">16.1625118255615</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4196758270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5209884643555</t>
+    <t xml:space="preserve">16.4196796417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5209865570068</t>
   </si>
   <si>
     <t xml:space="preserve">16.5287799835205</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8404979705811</t>
+    <t xml:space="preserve">16.8404960632324</t>
   </si>
   <si>
     <t xml:space="preserve">16.9184246063232</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8716678619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8015327453613</t>
+    <t xml:space="preserve">16.8716659545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8015308380127</t>
   </si>
   <si>
     <t xml:space="preserve">17.6119956970215</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2223510742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5964069366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4171695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6587543487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3158645629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3236541748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5028953552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.056188583374</t>
+    <t xml:space="preserve">17.2223453521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5964107513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4171733856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6587505340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3158664703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.323657989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5028915405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0561904907227</t>
   </si>
   <si>
     <t xml:space="preserve">18.5393543243408</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7030029296875</t>
+    <t xml:space="preserve">18.7030048370361</t>
   </si>
   <si>
     <t xml:space="preserve">18.6640377044678</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8121070861816</t>
+    <t xml:space="preserve">18.8121032714844</t>
   </si>
   <si>
     <t xml:space="preserve">18.0951538085938</t>
@@ -488,43 +488,43 @@
     <t xml:space="preserve">18.1574993133545</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8769550323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6665458679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9704685211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0328140258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.510684967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5730304718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3626232147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4015846252441</t>
+    <t xml:space="preserve">17.8769569396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6665439605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9704704284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0328121185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5106868743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5730285644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.362621307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4015884399414</t>
   </si>
   <si>
     <t xml:space="preserve">17.2379341125488</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4093799591064</t>
+    <t xml:space="preserve">17.4093818664551</t>
   </si>
   <si>
     <t xml:space="preserve">17.1444206237793</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8171157836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6145038604736</t>
+    <t xml:space="preserve">16.8171215057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6145000457764</t>
   </si>
   <si>
     <t xml:space="preserve">16.6846389770508</t>
@@ -545,19 +545,19 @@
     <t xml:space="preserve">17.4405498504639</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4639282226562</t>
+    <t xml:space="preserve">17.4639301300049</t>
   </si>
   <si>
     <t xml:space="preserve">16.8327026367188</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8249092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9028377532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7859439849854</t>
+    <t xml:space="preserve">16.8249111175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9028396606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7859477996826</t>
   </si>
   <si>
     <t xml:space="preserve">16.7469806671143</t>
@@ -566,37 +566,37 @@
     <t xml:space="preserve">17.2768993377686</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2457294464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0509052276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0976619720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.957389831543</t>
+    <t xml:space="preserve">17.2457275390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0509071350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0976638793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9573917388916</t>
   </si>
   <si>
     <t xml:space="preserve">17.2301425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2067680358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4327602386475</t>
+    <t xml:space="preserve">17.2067623138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4327564239502</t>
   </si>
   <si>
     <t xml:space="preserve">17.2846927642822</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0664882659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9521045684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9832773208618</t>
+    <t xml:space="preserve">17.0664901733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9521036148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9832754135132</t>
   </si>
   <si>
     <t xml:space="preserve">16.2560272216797</t>
@@ -605,37 +605,37 @@
     <t xml:space="preserve">16.3339557647705</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9988603591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4065990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3130836486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1182613372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5131931304932</t>
+    <t xml:space="preserve">15.9988641738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4065999984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3130855560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1182594299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5131969451904</t>
   </si>
   <si>
     <t xml:space="preserve">16.0923748016357</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9131393432617</t>
+    <t xml:space="preserve">15.9131422042847</t>
   </si>
   <si>
     <t xml:space="preserve">16.1780986785889</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7158126831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0586967468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.466438293457</t>
+    <t xml:space="preserve">16.7158069610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0586948394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4664344787598</t>
   </si>
   <si>
     <t xml:space="preserve">16.2248554229736</t>
@@ -644,13 +644,13 @@
     <t xml:space="preserve">15.9754829406738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7080192565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4976062774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6924324035645</t>
+    <t xml:space="preserve">16.7080173492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4976100921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6924285888672</t>
   </si>
   <si>
     <t xml:space="preserve">16.5599517822266</t>
@@ -659,10 +659,10 @@
     <t xml:space="preserve">16.7703590393066</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8638744354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0275230407715</t>
+    <t xml:space="preserve">16.8638763427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0275268554688</t>
   </si>
   <si>
     <t xml:space="preserve">17.4561367034912</t>
@@ -674,10 +674,10 @@
     <t xml:space="preserve">17.8847465515137</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1185359954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2354278564453</t>
+    <t xml:space="preserve">18.1185340881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2354259490967</t>
   </si>
   <si>
     <t xml:space="preserve">18.0172290802002</t>
@@ -689,28 +689,28 @@
     <t xml:space="preserve">17.9626750946045</t>
   </si>
   <si>
-    <t xml:space="preserve">17.869161605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6353740692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7912349700928</t>
+    <t xml:space="preserve">17.8691596984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6353702545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7912311553955</t>
   </si>
   <si>
     <t xml:space="preserve">17.5808238983154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6509590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1107406616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9782619476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3133602142334</t>
+    <t xml:space="preserve">17.6509609222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1107387542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9782600402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3133583068848</t>
   </si>
   <si>
     <t xml:space="preserve">18.2042560577393</t>
@@ -719,13 +719,13 @@
     <t xml:space="preserve">18.469217300415</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0848560333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.349817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2952671051025</t>
+    <t xml:space="preserve">19.0848579406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3498153686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2952651977539</t>
   </si>
   <si>
     <t xml:space="preserve">19.4667091369629</t>
@@ -746,64 +746,64 @@
     <t xml:space="preserve">19.2407150268555</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0926513671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4511222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8588600158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6406631469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9056186676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2329235076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4978866577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1914501190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9888362884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1213150024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9732475280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9551544189453</t>
+    <t xml:space="preserve">19.0926494598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4511241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.858865737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.640661239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9056205749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2329216003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4978809356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1914520263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9888343811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.12131690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9732494354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9551582336426</t>
   </si>
   <si>
     <t xml:space="preserve">20.6278533935547</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2201137542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0408802032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7915058135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7447509765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8616390228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2434959411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9006042480469</t>
+    <t xml:space="preserve">21.2201175689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0408782958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7915077209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7447471618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.861644744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2434940338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9006061553955</t>
   </si>
   <si>
     <t xml:space="preserve">21.0330848693848</t>
@@ -815,70 +815,70 @@
     <t xml:space="preserve">21.6721057891846</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4149379730225</t>
+    <t xml:space="preserve">21.4149360656738</t>
   </si>
   <si>
     <t xml:space="preserve">21.3136310577393</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1967391967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4227333068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5785884857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1884708404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1002006530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9477291107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0279788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9878520965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8273601531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.348970413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4693374633789</t>
+    <t xml:space="preserve">21.1967372894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4227313995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.578592300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1884727478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1002025604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9477310180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0279750823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9878540039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8273582458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3489685058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4693393707275</t>
   </si>
   <si>
     <t xml:space="preserve">22.8946514129639</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3199672698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2878665924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8786010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0310764312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4483623504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0230503082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9026794433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6218128204346</t>
+    <t xml:space="preserve">23.3199653625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2878684997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.878604888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0310726165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4483604431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0230484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9026775360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6218109130859</t>
   </si>
   <si>
     <t xml:space="preserve">22.5014400482178</t>
@@ -887,22 +887,22 @@
     <t xml:space="preserve">23.2557678222656</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8434085845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.060079574585</t>
+    <t xml:space="preserve">21.8434066772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0600757598877</t>
   </si>
   <si>
     <t xml:space="preserve">22.6298351287842</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7341594696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9267520904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2316913604736</t>
+    <t xml:space="preserve">22.7341575622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9267501831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2316970825195</t>
   </si>
   <si>
     <t xml:space="preserve">23.1434211730957</t>
@@ -911,49 +911,49 @@
     <t xml:space="preserve">23.1674938201904</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6570053100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7693538665771</t>
+    <t xml:space="preserve">23.6570072174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7693519592285</t>
   </si>
   <si>
     <t xml:space="preserve">23.6730556488037</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8495998382568</t>
+    <t xml:space="preserve">23.8495979309082</t>
   </si>
   <si>
     <t xml:space="preserve">23.7613296508789</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4002094268799</t>
+    <t xml:space="preserve">23.4002151489258</t>
   </si>
   <si>
     <t xml:space="preserve">23.2958908081055</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4323139190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7051563262939</t>
+    <t xml:space="preserve">23.4323101043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7051544189453</t>
   </si>
   <si>
     <t xml:space="preserve">23.0069999694824</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8304538726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7903308868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.063175201416</t>
+    <t xml:space="preserve">22.8304557800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7903289794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0631713867188</t>
   </si>
   <si>
     <t xml:space="preserve">23.8255252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3921890258789</t>
+    <t xml:space="preserve">23.3921852111816</t>
   </si>
   <si>
     <t xml:space="preserve">23.2637920379639</t>
@@ -962,19 +962,19 @@
     <t xml:space="preserve">23.2718162536621</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1915683746338</t>
+    <t xml:space="preserve">23.1915702819824</t>
   </si>
   <si>
     <t xml:space="preserve">22.9989738464355</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9076061248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0199565887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0761280059814</t>
+    <t xml:space="preserve">21.9076042175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0199546813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0761299133301</t>
   </si>
   <si>
     <t xml:space="preserve">21.5545196533203</t>
@@ -983,13 +983,13 @@
     <t xml:space="preserve">21.4742698669434</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6267395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.771183013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7390880584717</t>
+    <t xml:space="preserve">21.6267414093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7711849212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.739086151123</t>
   </si>
   <si>
     <t xml:space="preserve">21.8674831390381</t>
@@ -998,16 +998,16 @@
     <t xml:space="preserve">21.8594589233398</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5255146026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7421817779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3730411529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7181053161621</t>
+    <t xml:space="preserve">22.5255107879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7421798706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3730430603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7181091308594</t>
   </si>
   <si>
     <t xml:space="preserve">22.8625545501709</t>
@@ -1016,13 +1016,13 @@
     <t xml:space="preserve">22.7100811004639</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5335388183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6539077758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2927951812744</t>
+    <t xml:space="preserve">22.5335369110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6539115905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.292797088623</t>
   </si>
   <si>
     <t xml:space="preserve">21.7551364898682</t>
@@ -1031,109 +1031,109 @@
     <t xml:space="preserve">21.2415504455566</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9927825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9446334838867</t>
+    <t xml:space="preserve">20.9927864074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9446353912354</t>
   </si>
   <si>
     <t xml:space="preserve">21.0730323791504</t>
   </si>
   <si>
-    <t xml:space="preserve">21.048957824707</t>
+    <t xml:space="preserve">21.0489559173584</t>
   </si>
   <si>
     <t xml:space="preserve">20.6396942138672</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4310512542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4872245788574</t>
+    <t xml:space="preserve">20.4310474395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4872264862061</t>
   </si>
   <si>
     <t xml:space="preserve">20.8804378509521</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8643856048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7119159698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5754947662354</t>
+    <t xml:space="preserve">20.864387512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7119178771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.575496673584</t>
   </si>
   <si>
     <t xml:space="preserve">20.5995693206787</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6477146148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6156158447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5915431976318</t>
+    <t xml:space="preserve">20.6477203369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6156196594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5915451049805</t>
   </si>
   <si>
     <t xml:space="preserve">20.3508033752441</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3427772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2866020202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7440166473389</t>
+    <t xml:space="preserve">20.3427791595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2866039276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7440147399902</t>
   </si>
   <si>
     <t xml:space="preserve">20.6717929840088</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4952507019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.735990524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2174797058105</t>
+    <t xml:space="preserve">20.4952526092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7359886169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2174758911133</t>
   </si>
   <si>
     <t xml:space="preserve">21.0168590545654</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3538990020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2335243225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9045085906982</t>
+    <t xml:space="preserve">21.3538970947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2335262298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9045104980469</t>
   </si>
   <si>
     <t xml:space="preserve">20.5594482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5353698730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4711761474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7520408630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3779716491699</t>
+    <t xml:space="preserve">20.5353736877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4711742401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7520389556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3779697418213</t>
   </si>
   <si>
     <t xml:space="preserve">21.0650062561035</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2255058288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.369945526123</t>
+    <t xml:space="preserve">21.2255039215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3699474334717</t>
   </si>
   <si>
     <t xml:space="preserve">21.9156303405762</t>
@@ -1145,16 +1145,13 @@
     <t xml:space="preserve">21.8032855987549</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7952575683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5785903930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3088455200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1403255462646</t>
+    <t xml:space="preserve">21.795259475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3088436126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.140323638916</t>
   </si>
   <si>
     <t xml:space="preserve">22.2285995483398</t>
@@ -1163,25 +1160,25 @@
     <t xml:space="preserve">22.2045230865479</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1483497619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.694034576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0921783447266</t>
+    <t xml:space="preserve">22.1483516693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6940364837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0921764373779</t>
   </si>
   <si>
     <t xml:space="preserve">22.1082248687744</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1643981933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7742824554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7662544250488</t>
+    <t xml:space="preserve">22.164400100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7742805480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7662601470947</t>
   </si>
   <si>
     <t xml:space="preserve">22.5897121429443</t>
@@ -1190,13 +1187,13 @@
     <t xml:space="preserve">22.5415630340576</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4131679534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5174884796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1563758850098</t>
+    <t xml:space="preserve">22.4131660461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.517484664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1563739776611</t>
   </si>
   <si>
     <t xml:space="preserve">21.8353824615479</t>
@@ -1205,28 +1202,28 @@
     <t xml:space="preserve">22.5495872497559</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2526721954346</t>
+    <t xml:space="preserve">22.2526702880859</t>
   </si>
   <si>
     <t xml:space="preserve">22.2125492095947</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2594337463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9335117340088</t>
+    <t xml:space="preserve">19.2594356536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9335155487061</t>
   </si>
   <si>
     <t xml:space="preserve">19.8612899780273</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6927719116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.620548248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5403022766113</t>
+    <t xml:space="preserve">19.6927738189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6205501556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5402984619141</t>
   </si>
   <si>
     <t xml:space="preserve">19.4921550750732</t>
@@ -1235,40 +1232,40 @@
     <t xml:space="preserve">19.4279537200928</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7409229278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6767234802246</t>
+    <t xml:space="preserve">19.7409191131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6767196655273</t>
   </si>
   <si>
     <t xml:space="preserve">19.805118560791</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4199275970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7569694519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6606750488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1421604156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2304306030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4069766998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4791965484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2545051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9415378570557</t>
+    <t xml:space="preserve">19.4199333190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7569675445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6606731414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1421585083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2304286956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4069747924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4792003631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2545070648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9415416717529</t>
   </si>
   <si>
     <t xml:space="preserve">20.0619106292725</t>
@@ -1277,55 +1274,55 @@
     <t xml:space="preserve">19.9254894256592</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9366092681885</t>
+    <t xml:space="preserve">20.9366111755371</t>
   </si>
   <si>
     <t xml:space="preserve">21.0971069335938</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8162364959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3989505767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6878433227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4390735626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2464828491211</t>
+    <t xml:space="preserve">20.8162384033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3989524841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6878414154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4390716552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2464790344238</t>
   </si>
   <si>
     <t xml:space="preserve">20.4631500244141</t>
   </si>
   <si>
-    <t xml:space="preserve">20.543399810791</t>
+    <t xml:space="preserve">20.5433959960938</t>
   </si>
   <si>
     <t xml:space="preserve">21.4100723266602</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0088329315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6508121490479</t>
+    <t xml:space="preserve">21.0088348388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6508140563965</t>
   </si>
   <si>
     <t xml:space="preserve">21.1372299194336</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2816734313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.506368637085</t>
+    <t xml:space="preserve">21.2816772460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5063667297363</t>
   </si>
   <si>
     <t xml:space="preserve">21.4421691894531</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9606857299805</t>
+    <t xml:space="preserve">20.9606838226318</t>
   </si>
   <si>
     <t xml:space="preserve">21.3458728790283</t>
@@ -1337,34 +1334,34 @@
     <t xml:space="preserve">21.6989631652832</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8113098144531</t>
+    <t xml:space="preserve">21.8113059997559</t>
   </si>
   <si>
     <t xml:space="preserve">21.7792110443115</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3940238952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7471141815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2495746612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5322742462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3236351013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5001754760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5162258148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.045862197876</t>
+    <t xml:space="preserve">21.394021987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7471122741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2495765686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5322780609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3236312866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5001773834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.516227722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0458602905273</t>
   </si>
   <si>
     <t xml:space="preserve">20.0940113067627</t>
@@ -1373,7 +1370,7 @@
     <t xml:space="preserve">19.7248706817627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7088222503662</t>
+    <t xml:space="preserve">19.7088203430176</t>
   </si>
   <si>
     <t xml:space="preserve">19.403881072998</t>
@@ -1385,55 +1382,55 @@
     <t xml:space="preserve">19.1631355285645</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8260936737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6014022827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0075721740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5853538513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7137489318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9977111816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1261081695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7199420928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1903057098389</t>
+    <t xml:space="preserve">18.8260974884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6014041900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0075702667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.585355758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7137508392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9977130889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1261100769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7199440002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1903038024902</t>
   </si>
   <si>
     <t xml:space="preserve">19.7730178833008</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8372173309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8211688995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.435977935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1310367584229</t>
+    <t xml:space="preserve">19.837215423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8211669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4359798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1310386657715</t>
   </si>
   <si>
     <t xml:space="preserve">19.3557300567627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5483264923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9174652099609</t>
+    <t xml:space="preserve">19.5483283996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9174633026123</t>
   </si>
   <si>
     <t xml:space="preserve">19.5804252624512</t>
@@ -1445,61 +1442,61 @@
     <t xml:space="preserve">19.0026416778564</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8421478271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0828895568848</t>
+    <t xml:space="preserve">18.8421440124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0828914642334</t>
   </si>
   <si>
     <t xml:space="preserve">19.8853664398193</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5112972259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1582107543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8936672210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6596565246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5760841369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6763725280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7265148162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8435211181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8268032073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4954013824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1276721954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2781085968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1778202056885</t>
+    <t xml:space="preserve">20.5112953186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1582088470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8936653137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6596546173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.576078414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6763706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7265110015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8435230255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8268051147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4954032897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1276741027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2781066894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1778182983398</t>
   </si>
   <si>
     <t xml:space="preserve">21.0942459106445</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9772415161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7766609191895</t>
+    <t xml:space="preserve">20.9772396087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7766628265381</t>
   </si>
   <si>
     <t xml:space="preserve">20.4757919311523</t>
@@ -1508,13 +1505,13 @@
     <t xml:space="preserve">20.6429405212402</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5259380340576</t>
+    <t xml:space="preserve">20.525936126709</t>
   </si>
   <si>
     <t xml:space="preserve">20.2584972381592</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1247787475586</t>
+    <t xml:space="preserve">20.12477684021</t>
   </si>
   <si>
     <t xml:space="preserve">20.1916370391846</t>
@@ -1523,13 +1520,16 @@
     <t xml:space="preserve">19.9242000579834</t>
   </si>
   <si>
-    <t xml:space="preserve">19.506326675415</t>
+    <t xml:space="preserve">19.5063228607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1582069396973</t>
   </si>
   <si>
     <t xml:space="preserve">20.2417831420898</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8769512176514</t>
+    <t xml:space="preserve">20.8769493103027</t>
   </si>
   <si>
     <t xml:space="preserve">20.7933750152588</t>
@@ -1538,70 +1538,70 @@
     <t xml:space="preserve">20.9939556121826</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8100891113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5927963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6930866241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3420715332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4925098419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5593681335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7570457458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8740520477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1414966583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2919254302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0244903564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9409160614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1080627441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2752113342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3922157287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.057918548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4256477355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0746326446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8239116668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6901893615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0273838043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2475776672363</t>
+    <t xml:space="preserve">20.8100910186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.592794418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6930847167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3420734405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.492504119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5593662261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7570495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8740558624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1414928436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2919292449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0244884490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9409141540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.108060836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2752132415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3922176361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0579204559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4256458282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.074634552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8239078521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6901912689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0273818969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2475738525391</t>
   </si>
   <si>
     <t xml:space="preserve">22.3144359588623</t>
@@ -1613,40 +1613,40 @@
     <t xml:space="preserve">23.200325012207</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2671871185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5847663879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5346260070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.217041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8660278320312</t>
+    <t xml:space="preserve">23.2671852111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5847702026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5346221923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2170429229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8660259246826</t>
   </si>
   <si>
     <t xml:space="preserve">22.799165725708</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8325996398926</t>
+    <t xml:space="preserve">22.8325977325439</t>
   </si>
   <si>
     <t xml:space="preserve">22.5484428405762</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6153011322021</t>
+    <t xml:space="preserve">22.6153049468994</t>
   </si>
   <si>
     <t xml:space="preserve">22.9328880310059</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1167526245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1501808166504</t>
+    <t xml:space="preserve">23.1167507171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.150182723999</t>
   </si>
   <si>
     <t xml:space="preserve">23.2504692077637</t>
@@ -1655,25 +1655,25 @@
     <t xml:space="preserve">23.4009037017822</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6182022094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5011940002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3841876983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2839031219482</t>
+    <t xml:space="preserve">23.6181983947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5011920928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3841896057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2839012145996</t>
   </si>
   <si>
     <t xml:space="preserve">23.0833225250244</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8994541168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5651607513428</t>
+    <t xml:space="preserve">22.8994560241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5651569366455</t>
   </si>
   <si>
     <t xml:space="preserve">22.5818729400635</t>
@@ -1685,13 +1685,13 @@
     <t xml:space="preserve">22.8158798217773</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5317268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1334667205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9663162231445</t>
+    <t xml:space="preserve">22.5317287445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1334686279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9663143157959</t>
   </si>
   <si>
     <t xml:space="preserve">23.6850566864014</t>
@@ -1706,25 +1706,25 @@
     <t xml:space="preserve">22.9997482299805</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8493118286133</t>
+    <t xml:space="preserve">22.8493137359619</t>
   </si>
   <si>
     <t xml:space="preserve">22.9496002197266</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7628421783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4619750976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0440979003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7098026275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9103813171387</t>
+    <t xml:space="preserve">21.7628402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.461971282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0440998077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7098007202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.91037940979</t>
   </si>
   <si>
     <t xml:space="preserve">21.6625518798828</t>
@@ -1733,19 +1733,19 @@
     <t xml:space="preserve">21.2279624938965</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4285411834717</t>
+    <t xml:space="preserve">21.4285430908203</t>
   </si>
   <si>
     <t xml:space="preserve">20.9270973205566</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3616847991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5121173858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9605236053467</t>
+    <t xml:space="preserve">21.3616809844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5121154785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9605255126953</t>
   </si>
   <si>
     <t xml:space="preserve">19.8573379516602</t>
@@ -1754,16 +1754,16 @@
     <t xml:space="preserve">19.5397548675537</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9547348022461</t>
+    <t xml:space="preserve">18.9547328948975</t>
   </si>
   <si>
     <t xml:space="preserve">19.556468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0550231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4394645690918</t>
+    <t xml:space="preserve">19.0550212860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4394664764404</t>
   </si>
   <si>
     <t xml:space="preserve">19.3893222808838</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">18.8042984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6037197113037</t>
+    <t xml:space="preserve">18.6037178039551</t>
   </si>
   <si>
     <t xml:space="preserve">18.6872940063477</t>
@@ -1799,28 +1799,28 @@
     <t xml:space="preserve">19.2221717834473</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6734752655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.656759262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8907680511475</t>
+    <t xml:space="preserve">19.6734733581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6567611694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8907699584961</t>
   </si>
   <si>
     <t xml:space="preserve">20.0913486480713</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8406257629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.589900970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0884532928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7737636566162</t>
+    <t xml:space="preserve">19.8406238555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5898990631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.088451385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7737655639648</t>
   </si>
   <si>
     <t xml:space="preserve">19.6400451660156</t>
@@ -1829,46 +1829,46 @@
     <t xml:space="preserve">19.4561824798584</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9212989807129</t>
+    <t xml:space="preserve">18.9213008880615</t>
   </si>
   <si>
     <t xml:space="preserve">19.3391761779785</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5201454162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5506763458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0019817352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9016933441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4700012207031</t>
+    <t xml:space="preserve">18.5201435089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5506820678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0019855499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9016895294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4699974060059</t>
   </si>
   <si>
     <t xml:space="preserve">18.235990524292</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4365692138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0412063598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3086395263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.991060256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3253574371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2861347198486</t>
+    <t xml:space="preserve">18.4365673065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.041202545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3086433410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9910583496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3253593444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2861366271973</t>
   </si>
   <si>
     <t xml:space="preserve">18.2694225311279</t>
@@ -1883,19 +1883,19 @@
     <t xml:space="preserve">18.6538639068604</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2527084350586</t>
+    <t xml:space="preserve">18.25270652771</t>
   </si>
   <si>
     <t xml:space="preserve">18.3529949188232</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5368576049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7541561126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.637149810791</t>
+    <t xml:space="preserve">18.5368595123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7541522979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6371479034424</t>
   </si>
   <si>
     <t xml:space="preserve">19.1553153991699</t>
@@ -1907,46 +1907,46 @@
     <t xml:space="preserve">19.2723178863525</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9714469909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3558902740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0215892791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3224620819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7403335571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1749210357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7875843048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9380187988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.007776260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2250690460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5789775848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1443862915039</t>
+    <t xml:space="preserve">18.9714488983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3558921813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0215930938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3224639892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7403354644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1749229431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7875823974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9380168914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0077743530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2250709533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5789794921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1443881988525</t>
   </si>
   <si>
     <t xml:space="preserve">19.2054576873779</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0354099273682</t>
+    <t xml:space="preserve">18.0354156494141</t>
   </si>
   <si>
     <t xml:space="preserve">17.6509666442871</t>
@@ -1955,217 +1955,217 @@
     <t xml:space="preserve">17.4336738586426</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5841102600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1328048706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5477828979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1716976165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.996190071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3221321105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8791837692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7939510345459</t>
+    <t xml:space="preserve">17.5841083526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1328067779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.547779083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1716957092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9961881637573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3221302032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.879186630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7939529418945</t>
   </si>
   <si>
     <t xml:space="preserve">15.7683801651001</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7769050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3081140518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4018726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4359674453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5382471084595</t>
+    <t xml:space="preserve">15.7769031524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3081130981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4018707275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4359655380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5382490158081</t>
   </si>
   <si>
     <t xml:space="preserve">15.1632165908813</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3336849212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0524101257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1717376708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3507308959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5552940368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6405277252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6490507125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6320028305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5808668136597</t>
+    <t xml:space="preserve">15.333685874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0524091720581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1717386245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3507318496704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5552930831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.640528678894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6490545272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6320056915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5808658599854</t>
   </si>
   <si>
     <t xml:space="preserve">15.4103965759277</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0609331130981</t>
+    <t xml:space="preserve">15.0609350204468</t>
   </si>
   <si>
     <t xml:space="preserve">14.8904647827148</t>
   </si>
   <si>
-    <t xml:space="preserve">14.984224319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0438861846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3763055801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4274444580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2825450897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0865049362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1120748519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1546907424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3251628875732</t>
+    <t xml:space="preserve">14.9842233657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.043888092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3763017654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4274425506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.282543182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0865058898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1120738983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1546926498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3251609802246</t>
   </si>
   <si>
     <t xml:space="preserve">15.3592557907104</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9671764373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7455644607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6091909408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6518087387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5154342651367</t>
+    <t xml:space="preserve">14.9671745300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7455635070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6091918945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6518077850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5154323577881</t>
   </si>
   <si>
     <t xml:space="preserve">14.7114734649658</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6347627639771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5410041809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3534870147705</t>
+    <t xml:space="preserve">14.6347608566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5410060882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3534879684448</t>
   </si>
   <si>
     <t xml:space="preserve">14.3449630737305</t>
   </si>
   <si>
-    <t xml:space="preserve">14.447244644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.438720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7540884017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4642906188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4813394546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3620100021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2484502792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4956293106079</t>
+    <t xml:space="preserve">14.4472465515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4387226104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7540903091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4642934799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4813365936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3620109558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2484483718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4956312179565</t>
   </si>
   <si>
     <t xml:space="preserve">15.0268402099609</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0012702941895</t>
+    <t xml:space="preserve">15.0012722015381</t>
   </si>
   <si>
     <t xml:space="preserve">14.6859035491943</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5324811935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9784574508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4046277999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.035364151001</t>
+    <t xml:space="preserve">14.5324792861938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9784545898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4046268463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0353622436523</t>
   </si>
   <si>
     <t xml:space="preserve">15.1376447677612</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8308019638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9586505889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2399253845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8109951019287</t>
+    <t xml:space="preserve">14.8308010101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9586515426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2399263381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8109979629517</t>
   </si>
   <si>
     <t xml:space="preserve">16.4843502044678</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0468978881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7911949157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5269680023193</t>
+    <t xml:space="preserve">17.046895980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7911930084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5269660949707</t>
   </si>
   <si>
     <t xml:space="preserve">17.0128040313721</t>
@@ -2180,22 +2180,22 @@
     <t xml:space="preserve">16.2371692657471</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9303255081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.921802520752</t>
+    <t xml:space="preserve">15.9303274154663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9218015670776</t>
   </si>
   <si>
     <t xml:space="preserve">15.3933486938477</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9416046142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5239582061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9330825805664</t>
+    <t xml:space="preserve">14.9416055679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5239591598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9330835342407</t>
   </si>
   <si>
     <t xml:space="preserve">14.6603326797485</t>
@@ -2204,70 +2204,70 @@
     <t xml:space="preserve">14.2512044906616</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1318798065186</t>
+    <t xml:space="preserve">14.1318778991699</t>
   </si>
   <si>
     <t xml:space="preserve">14.6177158355713</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4557666778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5580501556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.575098991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7370433807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7796621322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8393239974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8478469848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6688556671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2341613769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.14040184021</t>
+    <t xml:space="preserve">14.4557695388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5580492019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5750980377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7370443344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7796592712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8393259048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8478488922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6688537597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2341604232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1404027938843</t>
   </si>
   <si>
     <t xml:space="preserve">14.0636901855469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8222780227661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6262397766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0183181762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1291217803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.20583152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5467700958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8195199966431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0326080322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4502563476562</t>
+    <t xml:space="preserve">14.8222761154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6262407302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0183162689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1291227340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2058334350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5467710494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8195219039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0326061248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4502544403076</t>
   </si>
   <si>
     <t xml:space="preserve">16.4928741455078</t>
@@ -2276,25 +2276,25 @@
     <t xml:space="preserve">16.0155620574951</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1519374847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2030773162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0411319732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0752258300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8962297439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2883129119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2627429962158</t>
+    <t xml:space="preserve">16.1519355773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2030754089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.041130065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0752239227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8962326049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2883110046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2627410888672</t>
   </si>
   <si>
     <t xml:space="preserve">16.1263656616211</t>
@@ -2303,10 +2303,10 @@
     <t xml:space="preserve">16.1178436279297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1945495605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2286472320557</t>
+    <t xml:space="preserve">16.1945533752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.228645324707</t>
   </si>
   <si>
     <t xml:space="preserve">16.168981552124</t>
@@ -2318,127 +2318,127 @@
     <t xml:space="preserve">16.2797889709473</t>
   </si>
   <si>
-    <t xml:space="preserve">16.109317779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7087163925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6746225357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9729452133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.74280834198</t>
+    <t xml:space="preserve">16.1093196868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7087144851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6746215820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9729433059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7428073883057</t>
   </si>
   <si>
     <t xml:space="preserve">15.3422079086304</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2910661697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1035490036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5665740966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2853012084961</t>
+    <t xml:space="preserve">15.2910690307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1035509109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5665731430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2853002548218</t>
   </si>
   <si>
     <t xml:space="preserve">14.2426815032959</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5949010848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7057056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6944255828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5069093704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0694589614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4615354537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4444894790649</t>
+    <t xml:space="preserve">13.5949001312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7057065963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6944265365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.506911277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0694580078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4615345001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4444913864136</t>
   </si>
   <si>
     <t xml:space="preserve">15.4700584411621</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6149578094482</t>
+    <t xml:space="preserve">15.6149597167969</t>
   </si>
   <si>
     <t xml:space="preserve">15.2740201950073</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2995910644531</t>
+    <t xml:space="preserve">15.2995891571045</t>
   </si>
   <si>
     <t xml:space="preserve">13.7142295837402</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3818159103394</t>
+    <t xml:space="preserve">13.381814956665</t>
   </si>
   <si>
     <t xml:space="preserve">13.552282333374</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1772518157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2965812683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2624855041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0323534011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7596025466919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6232290267944</t>
+    <t xml:space="preserve">13.1772527694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2965803146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.262487411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0323524475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7596035003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6232271194458</t>
   </si>
   <si>
     <t xml:space="preserve">12.359001159668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6600780487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1912899017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8333034515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7423038482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6543121337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6430320739746</t>
+    <t xml:space="preserve">11.6600790023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1912879943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8333044052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74230194091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6543111801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6430311203003</t>
   </si>
   <si>
     <t xml:space="preserve">11.8220243453979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6686010360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0351104736328</t>
+    <t xml:space="preserve">11.6686000823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0351095199585</t>
   </si>
   <si>
     <t xml:space="preserve">13.3306751251221</t>
@@ -2450,16 +2450,16 @@
     <t xml:space="preserve">14.2767772674561</t>
   </si>
   <si>
-    <t xml:space="preserve">13.074969291687</t>
+    <t xml:space="preserve">13.0749702453613</t>
   </si>
   <si>
     <t xml:space="preserve">13.5011434555054</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4500007629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9897365570068</t>
+    <t xml:space="preserve">13.4500017166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9897356033325</t>
   </si>
   <si>
     <t xml:space="preserve">13.0834941864014</t>
@@ -2468,22 +2468,22 @@
     <t xml:space="preserve">13.1175880432129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4953765869141</t>
+    <t xml:space="preserve">12.4953756332397</t>
   </si>
   <si>
     <t xml:space="preserve">13.023829460144</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3562431335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4244327545166</t>
+    <t xml:space="preserve">13.3562450408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4244337081909</t>
   </si>
   <si>
     <t xml:space="preserve">13.6119480133057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8192663192749</t>
+    <t xml:space="preserve">12.8192672729492</t>
   </si>
   <si>
     <t xml:space="preserve">12.6999387741089</t>
@@ -2492,40 +2492,40 @@
     <t xml:space="preserve">12.904501914978</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0664472579956</t>
+    <t xml:space="preserve">13.066445350647</t>
   </si>
   <si>
     <t xml:space="preserve">13.2113456726074</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3988628387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.313627243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8079872131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8932199478149</t>
+    <t xml:space="preserve">13.3988618850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3136262893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8079881668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8932209014893</t>
   </si>
   <si>
     <t xml:space="preserve">13.9358396530151</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0551671981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8846998214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4898614883423</t>
+    <t xml:space="preserve">14.0551662445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8846988677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4898633956909</t>
   </si>
   <si>
     <t xml:space="preserve">14.7029495239258</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2000646591187</t>
+    <t xml:space="preserve">14.200065612793</t>
   </si>
   <si>
     <t xml:space="preserve">14.4983854293823</t>
@@ -2534,43 +2534,43 @@
     <t xml:space="preserve">14.4131517410278</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1205968856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7711381912231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8563709259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4189205169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9388542175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7513313293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6207237243652</t>
+    <t xml:space="preserve">15.1205987930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7711391448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8563718795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4189186096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.938850402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.75133228302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6207256317139</t>
   </si>
   <si>
     <t xml:space="preserve">16.4161624908447</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2456951141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5440120697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7826728820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3707885742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.427698135376</t>
+    <t xml:space="preserve">16.2456932067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5440139770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7826709747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3707866668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4276962280273</t>
   </si>
   <si>
     <t xml:space="preserve">19.2629947662354</t>
@@ -2579,13 +2579,13 @@
     <t xml:space="preserve">19.0754776000977</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6493053436279</t>
+    <t xml:space="preserve">18.6493072509766</t>
   </si>
   <si>
     <t xml:space="preserve">18.90500831604</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6039333343506</t>
+    <t xml:space="preserve">19.6039352416992</t>
   </si>
   <si>
     <t xml:space="preserve">19.6380290985107</t>
@@ -2597,31 +2597,31 @@
     <t xml:space="preserve">19.8766822814941</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7744007110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1494293212891</t>
+    <t xml:space="preserve">19.7744026184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1494331359863</t>
   </si>
   <si>
     <t xml:space="preserve">20.0471515655518</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4846076965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8425903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8084964752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7119789123535</t>
+    <t xml:space="preserve">19.4846038818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8425884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8084926605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7119808197021</t>
   </si>
   <si>
     <t xml:space="preserve">20.9506378173828</t>
   </si>
   <si>
-    <t xml:space="preserve">20.677885055542</t>
+    <t xml:space="preserve">20.6778888702393</t>
   </si>
   <si>
     <t xml:space="preserve">20.8483543395996</t>
@@ -2630,10 +2630,10 @@
     <t xml:space="preserve">20.8824501037598</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0529193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9335918426514</t>
+    <t xml:space="preserve">21.052921295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9335899353027</t>
   </si>
   <si>
     <t xml:space="preserve">21.0870132446289</t>
@@ -2642,52 +2642,52 @@
     <t xml:space="preserve">21.1551990509033</t>
   </si>
   <si>
-    <t xml:space="preserve">21.291576385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2574825286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2233867645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0699653625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3086242675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8994979858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9676856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7631206512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9165458679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1609668731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6382808685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.013313293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9167957305908</t>
+    <t xml:space="preserve">21.2915744781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2574806213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2233848571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0699634552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3086223602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8994960784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9676837921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7631225585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9165439605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1609687805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6382789611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0133113861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9167976379395</t>
   </si>
   <si>
     <t xml:space="preserve">23.8145179748535</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9679374694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0020332336426</t>
+    <t xml:space="preserve">23.9679393768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0020294189453</t>
   </si>
   <si>
     <t xml:space="preserve">23.5758609771729</t>
@@ -2699,19 +2699,19 @@
     <t xml:space="preserve">23.7974700927734</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5247173309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5929088592529</t>
+    <t xml:space="preserve">23.5247211456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5929069519043</t>
   </si>
   <si>
     <t xml:space="preserve">23.6610927581787</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8486080169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6781406402588</t>
+    <t xml:space="preserve">23.8486099243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6781425476074</t>
   </si>
   <si>
     <t xml:space="preserve">23.4394855499268</t>
@@ -2726,70 +2726,70 @@
     <t xml:space="preserve">23.6951866149902</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4906234741211</t>
+    <t xml:space="preserve">23.4906272888184</t>
   </si>
   <si>
     <t xml:space="preserve">23.7633743286133</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1496849060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9849872589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8997497558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.496395111084</t>
+    <t xml:space="preserve">23.1496868133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9849853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.899751663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4963932037354</t>
   </si>
   <si>
     <t xml:space="preserve">25.2123622894287</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5304889678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1100769042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0647068023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4680652618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5532970428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4851131439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1271266937256</t>
+    <t xml:space="preserve">24.5304870605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1100788116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0647048950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4680633544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5533008575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4851112365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1271286010742</t>
   </si>
   <si>
     <t xml:space="preserve">25.0589389801025</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0759868621826</t>
+    <t xml:space="preserve">25.075984954834</t>
   </si>
   <si>
     <t xml:space="preserve">24.8202838897705</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8884716033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1953163146973</t>
+    <t xml:space="preserve">24.8884696960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1953144073486</t>
   </si>
   <si>
     <t xml:space="preserve">24.7180023193359</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3487339019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2294101715088</t>
+    <t xml:space="preserve">25.3487358093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2294082641602</t>
   </si>
   <si>
     <t xml:space="preserve">25.4339733123779</t>
@@ -2804,22 +2804,22 @@
     <t xml:space="preserve">26.8829593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7636318206787</t>
+    <t xml:space="preserve">26.7636299133301</t>
   </si>
   <si>
     <t xml:space="preserve">26.0306148529053</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9283313751221</t>
+    <t xml:space="preserve">25.9283332824707</t>
   </si>
   <si>
     <t xml:space="preserve">26.0135669708252</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1441745758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.956657409668</t>
+    <t xml:space="preserve">25.144172668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9566593170166</t>
   </si>
   <si>
     <t xml:space="preserve">23.4224376678467</t>
@@ -2831,34 +2831,34 @@
     <t xml:space="preserve">23.4053897857666</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4565315246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.837329864502</t>
+    <t xml:space="preserve">23.4565334320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8373317718506</t>
   </si>
   <si>
     <t xml:space="preserve">25.0930328369141</t>
   </si>
   <si>
-    <t xml:space="preserve">25.570348739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6385326385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.360013961792</t>
+    <t xml:space="preserve">25.5703449249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6385345458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3600158691406</t>
   </si>
   <si>
     <t xml:space="preserve">24.13840675354</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9112854003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5475311279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.831563949585</t>
+    <t xml:space="preserve">25.911283493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5475330352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8315620422363</t>
   </si>
   <si>
     <t xml:space="preserve">23.5588111877441</t>
@@ -2867,175 +2867,175 @@
     <t xml:space="preserve">24.12135887146</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5417652130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0985488891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2747821807861</t>
+    <t xml:space="preserve">23.5417671203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0985431671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2747840881348</t>
   </si>
   <si>
     <t xml:space="preserve">24.9396114349365</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2918300628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0702209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5076694488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3372020721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1837844848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6894245147705</t>
+    <t xml:space="preserve">24.2918281555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.070219039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5076713562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3372001647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.183780670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6894226074219</t>
   </si>
   <si>
     <t xml:space="preserve">23.1667327880859</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2860641479492</t>
+    <t xml:space="preserve">23.2860622406006</t>
   </si>
   <si>
     <t xml:space="preserve">23.2029094696045</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3768405914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6984958648682</t>
+    <t xml:space="preserve">23.3768424987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6984977722168</t>
   </si>
   <si>
     <t xml:space="preserve">22.5941352844238</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8202514648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4202003479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7854671478271</t>
+    <t xml:space="preserve">22.8202495574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.420202255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7854633331299</t>
   </si>
   <si>
     <t xml:space="preserve">23.2898750305176</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8028583526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8724308013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7506771087646</t>
+    <t xml:space="preserve">22.8028564453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8724327087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7506790161133</t>
   </si>
   <si>
     <t xml:space="preserve">22.7158908843994</t>
   </si>
   <si>
-    <t xml:space="preserve">22.246265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3332328796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4723796844482</t>
+    <t xml:space="preserve">22.2462673187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.33323097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4723777770996</t>
   </si>
   <si>
     <t xml:space="preserve">23.2550868988037</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5769939422607</t>
+    <t xml:space="preserve">24.5769920349121</t>
   </si>
   <si>
     <t xml:space="preserve">25.3596973419189</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5510292053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1945858001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4207019805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7597522735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4033107757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0294742584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1860179901123</t>
+    <t xml:space="preserve">25.5510272979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1945877075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4207000732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7597503662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4033069610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0294704437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.186014175415</t>
   </si>
   <si>
     <t xml:space="preserve">27.1164417266846</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0120811462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1426544189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8036098480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0992946624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3775901794434</t>
+    <t xml:space="preserve">27.0120792388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1426563262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8036060333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0992965698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.377592086792</t>
   </si>
   <si>
     <t xml:space="preserve">29.5863132476807</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0385494232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2210521697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.081901550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7688236236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4035587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6904258728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.785961151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5946350097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4121322631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6294231414795</t>
+    <t xml:space="preserve">30.0385475158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2210502624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0818996429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7688217163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4035606384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6904277801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7859630584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5946369171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.412130355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6294250488281</t>
   </si>
   <si>
     <t xml:space="preserve">27.6208515167236</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6468162536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5250625610352</t>
+    <t xml:space="preserve">26.6468181610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5250606536865</t>
   </si>
   <si>
     <t xml:space="preserve">27.2034091949463</t>
@@ -3044,7 +3044,7 @@
     <t xml:space="preserve">27.3077697753906</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7078170776367</t>
+    <t xml:space="preserve">27.707820892334</t>
   </si>
   <si>
     <t xml:space="preserve">30.1081199645996</t>
@@ -3053,10 +3053,10 @@
     <t xml:space="preserve">29.1340847015381</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0471210479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2906246185303</t>
+    <t xml:space="preserve">29.047119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2906265258789</t>
   </si>
   <si>
     <t xml:space="preserve">28.8905773162842</t>
@@ -3065,31 +3065,31 @@
     <t xml:space="preserve">29.3080196380615</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8560371398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7342853546143</t>
+    <t xml:space="preserve">30.8560447692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7342872619629</t>
   </si>
   <si>
     <t xml:space="preserve">30.2298736572266</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3690223693848</t>
+    <t xml:space="preserve">30.3690204620361</t>
   </si>
   <si>
     <t xml:space="preserve">30.4385948181152</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0559406280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2994480133057</t>
+    <t xml:space="preserve">30.0559368133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2994518280029</t>
   </si>
   <si>
     <t xml:space="preserve">29.9515800476074</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6125316619873</t>
+    <t xml:space="preserve">30.6125335693359</t>
   </si>
   <si>
     <t xml:space="preserve">30.9951858520508</t>
@@ -3098,94 +3098,94 @@
     <t xml:space="preserve">31.6039600372314</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8300743103027</t>
+    <t xml:space="preserve">31.8300762176514</t>
   </si>
   <si>
     <t xml:space="preserve">31.5691719055176</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8648624420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7778987884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4996032714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0387954711914</t>
+    <t xml:space="preserve">31.8648681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7778930664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4996013641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0387992858887</t>
   </si>
   <si>
     <t xml:space="preserve">31.6909275054932</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3430614471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4474220275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2734870910645</t>
+    <t xml:space="preserve">31.3430557250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.447416305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2734832763672</t>
   </si>
   <si>
     <t xml:space="preserve">31.7605018615723</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7083206176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5865669250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7431087493896</t>
+    <t xml:space="preserve">31.7083225250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5865650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7431049346924</t>
   </si>
   <si>
     <t xml:space="preserve">31.6387462615967</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6735305786133</t>
+    <t xml:space="preserve">31.6735382080078</t>
   </si>
   <si>
     <t xml:space="preserve">32.3866691589355</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5606002807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.847469329834</t>
+    <t xml:space="preserve">32.5605964660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8474674224854</t>
   </si>
   <si>
     <t xml:space="preserve">32.5432052612305</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8996486663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5169925689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7952919006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8126850128174</t>
+    <t xml:space="preserve">31.8996467590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5169982910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7952899932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8126831054688</t>
   </si>
   <si>
     <t xml:space="preserve">31.6213531494141</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4822101593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3952407836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1553268432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9081153869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7845096588135</t>
+    <t xml:space="preserve">31.4822082519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3952388763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.155330657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9081134796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7845077514648</t>
   </si>
   <si>
     <t xml:space="preserve">32.1376724243164</t>
@@ -3200,7 +3200,7 @@
     <t xml:space="preserve">32.278938293457</t>
   </si>
   <si>
-    <t xml:space="preserve">31.749195098877</t>
+    <t xml:space="preserve">31.7491931915283</t>
   </si>
   <si>
     <t xml:space="preserve">31.7668533325195</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">31.8728008270264</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6674118041992</t>
+    <t xml:space="preserve">32.6674156188965</t>
   </si>
   <si>
     <t xml:space="preserve">33.0029144287109</t>
@@ -3218,13 +3218,13 @@
     <t xml:space="preserve">33.4443664550781</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3031044006348</t>
+    <t xml:space="preserve">33.3031005859375</t>
   </si>
   <si>
     <t xml:space="preserve">34.3096122741699</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9982719421387</t>
+    <t xml:space="preserve">34.9982757568359</t>
   </si>
   <si>
     <t xml:space="preserve">34.9806175231934</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">34.7863807678223</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9564437866211</t>
+    <t xml:space="preserve">33.9564476013184</t>
   </si>
   <si>
     <t xml:space="preserve">33.7975273132324</t>
@@ -3248,34 +3248,34 @@
     <t xml:space="preserve">32.9499397277832</t>
   </si>
   <si>
-    <t xml:space="preserve">33.179500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2148132324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0912094116211</t>
+    <t xml:space="preserve">33.1794967651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2148094177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0912055969238</t>
   </si>
   <si>
     <t xml:space="preserve">32.437858581543</t>
   </si>
   <si>
-    <t xml:space="preserve">33.020580291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8439903259277</t>
+    <t xml:space="preserve">33.0205764770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.843994140625</t>
   </si>
   <si>
     <t xml:space="preserve">33.1441802978516</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0317192077637</t>
+    <t xml:space="preserve">32.0317230224609</t>
   </si>
   <si>
     <t xml:space="preserve">32.3319091796875</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7027320861816</t>
+    <t xml:space="preserve">32.7027282714844</t>
   </si>
   <si>
     <t xml:space="preserve">33.2677879333496</t>
@@ -3284,76 +3284,76 @@
     <t xml:space="preserve">33.4267120361328</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8616485595703</t>
+    <t xml:space="preserve">32.8616523742676</t>
   </si>
   <si>
     <t xml:space="preserve">32.2083015441895</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2017936706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.11350440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9610939025879</t>
+    <t xml:space="preserve">31.2017955780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1135063171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9610900878906</t>
   </si>
   <si>
     <t xml:space="preserve">33.126522064209</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9322776794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9257755279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5438041687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0270805358887</t>
+    <t xml:space="preserve">32.9322814941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9257717132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5438079833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0270843505859</t>
   </si>
   <si>
     <t xml:space="preserve">33.8681602478027</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0800552368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3449287414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.380241394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1330337524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5215110778809</t>
+    <t xml:space="preserve">34.0800514221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3449325561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3802375793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1330299377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5215072631836</t>
   </si>
   <si>
     <t xml:space="preserve">34.150691986084</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2036666870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1153717041016</t>
+    <t xml:space="preserve">34.2036628723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1153755187988</t>
   </si>
   <si>
     <t xml:space="preserve">33.938793182373</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6209487915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6915817260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2919502258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5038528442383</t>
+    <t xml:space="preserve">33.6209526062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.691577911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2919540405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.503849029541</t>
   </si>
   <si>
     <t xml:space="preserve">32.914623260498</t>
@@ -3362,13 +3362,13 @@
     <t xml:space="preserve">33.1971549987793</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5149955749512</t>
+    <t xml:space="preserve">33.5149993896484</t>
   </si>
   <si>
     <t xml:space="preserve">33.5503120422363</t>
   </si>
   <si>
-    <t xml:space="preserve">33.815185546875</t>
+    <t xml:space="preserve">33.8151893615723</t>
   </si>
   <si>
     <t xml:space="preserve">34.6451187133789</t>
@@ -3377,40 +3377,40 @@
     <t xml:space="preserve">35.1395378112793</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8570137023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6804351806641</t>
+    <t xml:space="preserve">34.8570098876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6804313659668</t>
   </si>
   <si>
     <t xml:space="preserve">35.0865707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3272666931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2371120452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.424840927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1776275634766</t>
+    <t xml:space="preserve">34.3272743225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2371101379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4248390197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1776237487793</t>
   </si>
   <si>
     <t xml:space="preserve">30.0716781616211</t>
   </si>
   <si>
-    <t xml:space="preserve">29.559591293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6125679016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6478862762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2306003570557</t>
+    <t xml:space="preserve">29.5595951080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.61256980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6478843688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2306022644043</t>
   </si>
   <si>
     <t xml:space="preserve">29.3476982116699</t>
@@ -3425,25 +3425,25 @@
     <t xml:space="preserve">27.8467617034912</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4406261444092</t>
+    <t xml:space="preserve">27.4406280517578</t>
   </si>
   <si>
     <t xml:space="preserve">28.5530834197998</t>
   </si>
   <si>
-    <t xml:space="preserve">28.09397315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7937889099121</t>
+    <t xml:space="preserve">28.0939750671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7937870025635</t>
   </si>
   <si>
     <t xml:space="preserve">27.6348648071289</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0763130187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0409984588623</t>
+    <t xml:space="preserve">28.0763149261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0410003662109</t>
   </si>
   <si>
     <t xml:space="preserve">28.3058738708496</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">29.2240886688232</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1004829406738</t>
+    <t xml:space="preserve">29.1004810333252</t>
   </si>
   <si>
     <t xml:space="preserve">29.471305847168</t>
@@ -3461,16 +3461,16 @@
     <t xml:space="preserve">29.1358013153076</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3123817443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8244609832764</t>
+    <t xml:space="preserve">29.3123798370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.824462890625</t>
   </si>
   <si>
     <t xml:space="preserve">29.9480667114258</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7891502380371</t>
+    <t xml:space="preserve">29.7891521453857</t>
   </si>
   <si>
     <t xml:space="preserve">29.2417488098145</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">29.8421211242676</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0010433197021</t>
+    <t xml:space="preserve">30.001049041748</t>
   </si>
   <si>
     <t xml:space="preserve">29.9833850860596</t>
@@ -3491,25 +3491,25 @@
     <t xml:space="preserve">30.9545783996582</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1952857971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1246528625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3300380706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2287311553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8402538299561</t>
+    <t xml:space="preserve">30.1952838897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1246490478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.330041885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2287292480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8402500152588</t>
   </si>
   <si>
     <t xml:space="preserve">26.9462013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6106967926025</t>
+    <t xml:space="preserve">26.6106986999512</t>
   </si>
   <si>
     <t xml:space="preserve">27.2817039489746</t>
@@ -3521,43 +3521,43 @@
     <t xml:space="preserve">27.3876533508301</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6989860534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8755722045898</t>
+    <t xml:space="preserve">26.6989879608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8755702972412</t>
   </si>
   <si>
     <t xml:space="preserve">27.0698070526123</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7807693481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4341163635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1162719726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8579120635986</t>
+    <t xml:space="preserve">25.7807712554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.434118270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1162700653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.85791015625</t>
   </si>
   <si>
     <t xml:space="preserve">26.3634834289551</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1339321136475</t>
+    <t xml:space="preserve">26.1339302062988</t>
   </si>
   <si>
     <t xml:space="preserve">26.3987998962402</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1404361724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5753803253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7519626617432</t>
+    <t xml:space="preserve">27.1404399871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.575382232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7519607543945</t>
   </si>
   <si>
     <t xml:space="preserve">26.310510635376</t>
@@ -3566,7 +3566,7 @@
     <t xml:space="preserve">26.4694328308105</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8225955963135</t>
+    <t xml:space="preserve">26.8225936889648</t>
   </si>
   <si>
     <t xml:space="preserve">27.2110710144043</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">27.3523349761963</t>
   </si>
   <si>
-    <t xml:space="preserve">26.981517791748</t>
+    <t xml:space="preserve">26.9815158843994</t>
   </si>
   <si>
     <t xml:space="preserve">27.9350509643555</t>
@@ -3602,19 +3602,19 @@
     <t xml:space="preserve">26.4164581298828</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9155216217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0214729309082</t>
+    <t xml:space="preserve">24.9155235290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0214710235596</t>
   </si>
   <si>
     <t xml:space="preserve">24.721284866333</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8978672027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.268684387207</t>
+    <t xml:space="preserve">24.8978652954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2686862945557</t>
   </si>
   <si>
     <t xml:space="preserve">24.5447025299072</t>
@@ -3623,13 +3623,13 @@
     <t xml:space="preserve">24.1032524108887</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8383808135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.692476272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.451774597168</t>
+    <t xml:space="preserve">23.8383827209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6924781799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4517726898193</t>
   </si>
   <si>
     <t xml:space="preserve">27.5112571716309</t>
@@ -3638,43 +3638,43 @@
     <t xml:space="preserve">27.9703674316406</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2993602752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9285430908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5289173126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4759407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9638595581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3811416625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8932266235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1757545471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7872791290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0986156463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4629249572754</t>
+    <t xml:space="preserve">27.2993621826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9285411834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5289192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.475944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9638614654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3811435699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8932247161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1757564544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7872772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0986137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4629230499268</t>
   </si>
   <si>
     <t xml:space="preserve">24.8095741271973</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2333679199219</t>
+    <t xml:space="preserve">25.2333660125732</t>
   </si>
   <si>
     <t xml:space="preserve">25.1274185180664</t>
@@ -3689,37 +3689,37 @@
     <t xml:space="preserve">22.4080791473389</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4192276000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3662528991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6906070709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0660667419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9424610137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3551025390625</t>
+    <t xml:space="preserve">21.4192295074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3662548065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6906089782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.066068649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9424591064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3551044464111</t>
   </si>
   <si>
     <t xml:space="preserve">21.772388458252</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7788982391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4610557556152</t>
+    <t xml:space="preserve">22.7789001464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4610538482666</t>
   </si>
   <si>
     <t xml:space="preserve">22.2844715118408</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2314987182617</t>
+    <t xml:space="preserve">22.2314968109131</t>
   </si>
   <si>
     <t xml:space="preserve">21.8077049255371</t>
@@ -3728,31 +3728,31 @@
     <t xml:space="preserve">21.5251750946045</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4722003936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5604915618896</t>
+    <t xml:space="preserve">21.4722023010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5604934692383</t>
   </si>
   <si>
     <t xml:space="preserve">22.990795135498</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3374443054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8430213928223</t>
+    <t xml:space="preserve">22.3374462127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8430194854736</t>
   </si>
   <si>
     <t xml:space="preserve">21.7547302246094</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7900485992432</t>
+    <t xml:space="preserve">21.7900466918945</t>
   </si>
   <si>
     <t xml:space="preserve">21.5958061218262</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3839111328125</t>
+    <t xml:space="preserve">21.3839130401611</t>
   </si>
   <si>
     <t xml:space="preserve">20.9601192474365</t>
@@ -3761,7 +3761,7 @@
     <t xml:space="preserve">21.1896724700928</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1366996765137</t>
+    <t xml:space="preserve">21.136697769165</t>
   </si>
   <si>
     <t xml:space="preserve">21.4015674591064</t>
@@ -3770,16 +3770,16 @@
     <t xml:space="preserve">20.7658786773682</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8365097045898</t>
+    <t xml:space="preserve">20.8365116119385</t>
   </si>
   <si>
     <t xml:space="preserve">20.0595550537109</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9359493255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3774032592773</t>
+    <t xml:space="preserve">19.9359512329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3774013519287</t>
   </si>
   <si>
     <t xml:space="preserve">20.5186653137207</t>
@@ -3809,37 +3809,37 @@
     <t xml:space="preserve">19.7770290374756</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3420886993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3355751037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5474720001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6710834503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9111518859863</t>
+    <t xml:space="preserve">20.3420867919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3355770111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5474739074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6710815429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.911153793335</t>
   </si>
   <si>
     <t xml:space="preserve">19.0677719116211</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4711303710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1311645507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3878479003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9012107849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6995315551758</t>
+    <t xml:space="preserve">19.4711284637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1311664581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3878498077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9012126922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6995334625244</t>
   </si>
   <si>
     <t xml:space="preserve">20.3145122528076</t>
@@ -3848,31 +3848,31 @@
     <t xml:space="preserve">20.6445293426514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0944976806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4061851501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1678371429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5811367034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.306116104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3710651397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7560882568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0127696990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0960502624512</t>
+    <t xml:space="preserve">20.0944995880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4061832427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1678352355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5811347961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3061180114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3710670471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7560863494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0127716064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0960483551025</t>
   </si>
   <si>
     <t xml:space="preserve">19.0861053466797</t>
@@ -3890,19 +3890,19 @@
     <t xml:space="preserve">17.261833190918</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1793308258057</t>
+    <t xml:space="preserve">17.179328918457</t>
   </si>
   <si>
     <t xml:space="preserve">17.2343330383301</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0968227386475</t>
+    <t xml:space="preserve">17.0968246459961</t>
   </si>
   <si>
     <t xml:space="preserve">16.757640838623</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2626075744629</t>
+    <t xml:space="preserve">16.2626094818115</t>
   </si>
   <si>
     <t xml:space="preserve">16.1617698669434</t>
@@ -3911,10 +3911,10 @@
     <t xml:space="preserve">16.1709384918213</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9875946044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3817863464355</t>
+    <t xml:space="preserve">15.9875926971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3817825317383</t>
   </si>
   <si>
     <t xml:space="preserve">16.7851390838623</t>
@@ -3932,7 +3932,7 @@
     <t xml:space="preserve">16.9501495361328</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4092864990234</t>
+    <t xml:space="preserve">16.4092845916748</t>
   </si>
   <si>
     <t xml:space="preserve">16.6843013763428</t>
@@ -3941,10 +3941,10 @@
     <t xml:space="preserve">16.9043140411377</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0693225860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9593162536621</t>
+    <t xml:space="preserve">17.0693244934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9593181610107</t>
   </si>
   <si>
     <t xml:space="preserve">17.1334934234619</t>
@@ -3956,7 +3956,7 @@
     <t xml:space="preserve">16.3359470367432</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8500871658325</t>
+    <t xml:space="preserve">15.8500881195068</t>
   </si>
   <si>
     <t xml:space="preserve">16.8218078613281</t>
@@ -3965,13 +3965,13 @@
     <t xml:space="preserve">16.5284595489502</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1151580810547</t>
+    <t xml:space="preserve">17.1151599884033</t>
   </si>
   <si>
     <t xml:space="preserve">17.8852043151855</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6560230255127</t>
+    <t xml:space="preserve">17.6560249328613</t>
   </si>
   <si>
     <t xml:space="preserve">17.6376876831055</t>
@@ -3995,13 +3995,13 @@
     <t xml:space="preserve">17.2159976959229</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3351726531982</t>
+    <t xml:space="preserve">17.3351707458496</t>
   </si>
   <si>
     <t xml:space="preserve">16.9868183135986</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0784893035889</t>
+    <t xml:space="preserve">17.0784912109375</t>
   </si>
   <si>
     <t xml:space="preserve">16.8584766387939</t>
@@ -4016,13 +4016,13 @@
     <t xml:space="preserve">15.9417572021484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0425968170166</t>
+    <t xml:space="preserve">16.0425987243652</t>
   </si>
   <si>
     <t xml:space="preserve">16.0150947570801</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6392402648926</t>
+    <t xml:space="preserve">15.6392383575439</t>
   </si>
   <si>
     <t xml:space="preserve">15.9142560958862</t>
@@ -4034,19 +4034,19 @@
     <t xml:space="preserve">15.2542181015015</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2175493240356</t>
+    <t xml:space="preserve">15.2175483703613</t>
   </si>
   <si>
     <t xml:space="preserve">15.1992158889771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6117401123047</t>
+    <t xml:space="preserve">15.6117391586304</t>
   </si>
   <si>
     <t xml:space="preserve">16.0059280395508</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6942434310913</t>
+    <t xml:space="preserve">15.6942443847656</t>
   </si>
   <si>
     <t xml:space="preserve">14.9883699417114</t>
@@ -4055,7 +4055,7 @@
     <t xml:space="preserve">14.5758438110352</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5850114822388</t>
+    <t xml:space="preserve">14.5850124359131</t>
   </si>
   <si>
     <t xml:space="preserve">13.860803604126</t>
@@ -4076,16 +4076,16 @@
     <t xml:space="preserve">13.7599649429321</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9249744415283</t>
+    <t xml:space="preserve">13.924973487854</t>
   </si>
   <si>
     <t xml:space="preserve">13.3107719421387</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8149671554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5032815933228</t>
+    <t xml:space="preserve">13.8149681091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5032825469971</t>
   </si>
   <si>
     <t xml:space="preserve">13.8883047103882</t>
@@ -4094,7 +4094,7 @@
     <t xml:space="preserve">13.5124502182007</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6591243743896</t>
+    <t xml:space="preserve">13.659125328064</t>
   </si>
   <si>
     <t xml:space="preserve">13.3382730484009</t>
@@ -4106,13 +4106,13 @@
     <t xml:space="preserve">13.8516359329224</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5307846069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8424701690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1908226013184</t>
+    <t xml:space="preserve">13.5307836532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8424692153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1908235549927</t>
   </si>
   <si>
     <t xml:space="preserve">14.3466653823853</t>
@@ -4124,7 +4124,7 @@
     <t xml:space="preserve">14.1816549301147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5483427047729</t>
+    <t xml:space="preserve">14.5483436584473</t>
   </si>
   <si>
     <t xml:space="preserve">14.8233594894409</t>
@@ -4133,19 +4133,19 @@
     <t xml:space="preserve">15.5659017562866</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7217454910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9050903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1526031494141</t>
+    <t xml:space="preserve">15.7217445373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9050893783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1526050567627</t>
   </si>
   <si>
     <t xml:space="preserve">16.7026348114014</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2434997558594</t>
+    <t xml:space="preserve">17.2434978485107</t>
   </si>
   <si>
     <t xml:space="preserve">17.509349822998</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">18.2427234649658</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5528583526611</t>
+    <t xml:space="preserve">20.5528564453125</t>
   </si>
   <si>
     <t xml:space="preserve">20.717866897583</t>
@@ -4184,19 +4184,19 @@
     <t xml:space="preserve">19.562801361084</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8928184509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6544742584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8561515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4527969360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5261306762695</t>
+    <t xml:space="preserve">19.8928203582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6544723510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8561496734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4527931213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5261325836182</t>
   </si>
   <si>
     <t xml:space="preserve">19.7278099060059</t>
@@ -4208,7 +4208,7 @@
     <t xml:space="preserve">19.8378162384033</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3244514465332</t>
+    <t xml:space="preserve">19.3244552612305</t>
   </si>
   <si>
     <t xml:space="preserve">18.9760990142822</t>
@@ -4226,31 +4226,31 @@
     <t xml:space="preserve">19.2327823638916</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0578289031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1128311157227</t>
+    <t xml:space="preserve">20.0578269958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1128330230713</t>
   </si>
   <si>
     <t xml:space="preserve">20.2961769104004</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5161895751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8179321289062</t>
+    <t xml:space="preserve">20.5161876678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8179302215576</t>
   </si>
   <si>
     <t xml:space="preserve">21.2495651245117</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9928855895996</t>
+    <t xml:space="preserve">20.992883682251</t>
   </si>
   <si>
     <t xml:space="preserve">20.7728710174561</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8828773498535</t>
+    <t xml:space="preserve">20.8828792572021</t>
   </si>
   <si>
     <t xml:space="preserve">21.0478858947754</t>
@@ -4259,7 +4259,7 @@
     <t xml:space="preserve">20.8095397949219</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7362022399902</t>
+    <t xml:space="preserve">20.7362041473389</t>
   </si>
   <si>
     <t xml:space="preserve">19.7828121185303</t>
@@ -4271,16 +4271,16 @@
     <t xml:space="preserve">19.2511157989502</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8660945892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3977909088135</t>
+    <t xml:space="preserve">18.8660926818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3977928161621</t>
   </si>
   <si>
     <t xml:space="preserve">19.3427886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4894638061523</t>
+    <t xml:space="preserve">19.4894618988037</t>
   </si>
   <si>
     <t xml:space="preserve">19.5994701385498</t>
@@ -4289,19 +4289,19 @@
     <t xml:space="preserve">20.3511810302734</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8744850158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1494998931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0761623382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0394973754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9745483398438</t>
+    <t xml:space="preserve">19.8744869232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1495018005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0761642456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0394954681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9745502471924</t>
   </si>
   <si>
     <t xml:space="preserve">21.2128963470459</t>
@@ -4310,10 +4310,10 @@
     <t xml:space="preserve">21.5795860290527</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6345863342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6529216766357</t>
+    <t xml:space="preserve">21.6345882415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6529235839844</t>
   </si>
   <si>
     <t xml:space="preserve">21.6162509918213</t>
@@ -4322,7 +4322,7 @@
     <t xml:space="preserve">21.5429153442383</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6811981201172</t>
+    <t xml:space="preserve">20.6812000274658</t>
   </si>
   <si>
     <t xml:space="preserve">21.3045673370361</t>
@@ -4334,10 +4334,10 @@
     <t xml:space="preserve">20.4245204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5711936950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.966157913208</t>
+    <t xml:space="preserve">20.5711917877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9661560058594</t>
   </si>
   <si>
     <t xml:space="preserve">19.5077991485596</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">19.9294891357422</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0211601257324</t>
+    <t xml:space="preserve">20.0211620330811</t>
   </si>
   <si>
     <t xml:space="preserve">18.6460819244385</t>
@@ -4364,25 +4364,25 @@
     <t xml:space="preserve">18.481071472168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6094093322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4077339172363</t>
+    <t xml:space="preserve">18.6094131469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.407735824585</t>
   </si>
   <si>
     <t xml:space="preserve">18.3343963623047</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9210948944092</t>
+    <t xml:space="preserve">18.9210968017578</t>
   </si>
   <si>
     <t xml:space="preserve">19.2877864837646</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1961116790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1044425964355</t>
+    <t xml:space="preserve">19.1961135864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1044406890869</t>
   </si>
   <si>
     <t xml:space="preserve">18.7201499938965</t>
@@ -4397,13 +4397,13 @@
     <t xml:space="preserve">17.5378246307373</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7348785400391</t>
+    <t xml:space="preserve">17.7348766326904</t>
   </si>
   <si>
     <t xml:space="preserve">17.6410427093506</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2469329833984</t>
+    <t xml:space="preserve">17.2469348907471</t>
   </si>
   <si>
     <t xml:space="preserve">17.1437168121338</t>
@@ -4421,7 +4421,7 @@
     <t xml:space="preserve">17.0311126708984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9560451507568</t>
+    <t xml:space="preserve">16.9560432434082</t>
   </si>
   <si>
     <t xml:space="preserve">16.89035987854</t>
@@ -4433,19 +4433,19 @@
     <t xml:space="preserve">17.078031539917</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1852855682373</t>
+    <t xml:space="preserve">18.1852874755859</t>
   </si>
   <si>
     <t xml:space="preserve">18.2885055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.565975189209</t>
+    <t xml:space="preserve">17.5659732818604</t>
   </si>
   <si>
     <t xml:space="preserve">18.0069999694824</t>
   </si>
   <si>
-    <t xml:space="preserve">17.922550201416</t>
+    <t xml:space="preserve">17.9225482940674</t>
   </si>
   <si>
     <t xml:space="preserve">17.8662490844727</t>
@@ -4454,28 +4454,28 @@
     <t xml:space="preserve">17.8005619049072</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5753593444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7536468505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9319343566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9882335662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3354263305664</t>
+    <t xml:space="preserve">17.5753574371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7536449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9319324493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9882354736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3354244232178</t>
   </si>
   <si>
     <t xml:space="preserve">18.5137119293213</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7858333587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5230960845947</t>
+    <t xml:space="preserve">18.7858352661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5230941772461</t>
   </si>
   <si>
     <t xml:space="preserve">18.7483005523682</t>
@@ -4502,13 +4502,13 @@
     <t xml:space="preserve">20.3435001373291</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7804870605469</t>
+    <t xml:space="preserve">19.7804889678955</t>
   </si>
   <si>
     <t xml:space="preserve">19.8555564880371</t>
   </si>
   <si>
-    <t xml:space="preserve">19.874324798584</t>
+    <t xml:space="preserve">19.8743228912354</t>
   </si>
   <si>
     <t xml:space="preserve">19.198709487915</t>
@@ -4520,19 +4520,19 @@
     <t xml:space="preserve">19.6678848266602</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2737789154053</t>
+    <t xml:space="preserve">19.2737770080566</t>
   </si>
   <si>
     <t xml:space="preserve">19.4989833831787</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3622665405273</t>
+    <t xml:space="preserve">20.362268447876</t>
   </si>
   <si>
     <t xml:space="preserve">20.7939109802246</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6759643554688</t>
+    <t xml:space="preserve">21.6759624481201</t>
   </si>
   <si>
     <t xml:space="preserve">21.826099395752</t>
@@ -4541,7 +4541,7 @@
     <t xml:space="preserve">22.0325355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1639060974121</t>
+    <t xml:space="preserve">22.1639080047607</t>
   </si>
   <si>
     <t xml:space="preserve">22.0888385772705</t>
@@ -4556,19 +4556,19 @@
     <t xml:space="preserve">22.2389755249023</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2952766418457</t>
+    <t xml:space="preserve">22.2952747344971</t>
   </si>
   <si>
     <t xml:space="preserve">22.482946395874</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9574661254883</t>
+    <t xml:space="preserve">21.9574680328369</t>
   </si>
   <si>
     <t xml:space="preserve">21.8448677062988</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7697982788086</t>
+    <t xml:space="preserve">21.7698001861572</t>
   </si>
   <si>
     <t xml:space="preserve">21.7134971618652</t>
@@ -4577,13 +4577,13 @@
     <t xml:space="preserve">21.995002746582</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5767803192139</t>
+    <t xml:space="preserve">22.5767822265625</t>
   </si>
   <si>
     <t xml:space="preserve">22.670618057251</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9708881378174</t>
+    <t xml:space="preserve">22.970890045166</t>
   </si>
   <si>
     <t xml:space="preserve">22.914587020874</t>
@@ -4592,13 +4592,13 @@
     <t xml:space="preserve">23.158561706543</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2711639404297</t>
+    <t xml:space="preserve">23.2711620330811</t>
   </si>
   <si>
     <t xml:space="preserve">23.1397933959961</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4882926940918</t>
+    <t xml:space="preserve">21.4882907867432</t>
   </si>
   <si>
     <t xml:space="preserve">21.8824005126953</t>
@@ -4607,37 +4607,37 @@
     <t xml:space="preserve">21.8636322021484</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9252796173096</t>
+    <t xml:space="preserve">20.9252777099609</t>
   </si>
   <si>
     <t xml:space="preserve">21.0003471374512</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1692504882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2443180084229</t>
+    <t xml:space="preserve">21.1692523956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2443199157715</t>
   </si>
   <si>
     <t xml:space="preserve">20.8877468109131</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6813106536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1182975769043</t>
+    <t xml:space="preserve">20.6813087463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1182956695557</t>
   </si>
   <si>
     <t xml:space="preserve">20.3998012542725</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8930931091309</t>
+    <t xml:space="preserve">19.8930912017822</t>
   </si>
   <si>
     <t xml:space="preserve">19.2174758911133</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3488483428955</t>
+    <t xml:space="preserve">19.3488464355469</t>
   </si>
   <si>
     <t xml:space="preserve">19.7992553710938</t>
@@ -4661,7 +4661,7 @@
     <t xml:space="preserve">19.4426803588867</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3300800323486</t>
+    <t xml:space="preserve">19.330078125</t>
   </si>
   <si>
     <t xml:space="preserve">18.9359703063965</t>
@@ -4676,7 +4676,7 @@
     <t xml:space="preserve">19.686653137207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1236419677734</t>
+    <t xml:space="preserve">19.1236400604248</t>
   </si>
   <si>
     <t xml:space="preserve">18.9922695159912</t>
@@ -4688,7 +4688,7 @@
     <t xml:space="preserve">19.4051475524902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.818021774292</t>
+    <t xml:space="preserve">19.8180236816406</t>
   </si>
   <si>
     <t xml:space="preserve">19.9681606292725</t>
@@ -4697,13 +4697,13 @@
     <t xml:space="preserve">20.606237411499</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4695243835449</t>
+    <t xml:space="preserve">21.4695224761963</t>
   </si>
   <si>
     <t xml:space="preserve">24.7162265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5848598480225</t>
+    <t xml:space="preserve">24.5848579406738</t>
   </si>
   <si>
     <t xml:space="preserve">24.6974601745605</t>
@@ -4715,13 +4715,13 @@
     <t xml:space="preserve">24.922664642334</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8475971221924</t>
+    <t xml:space="preserve">24.8475952148438</t>
   </si>
   <si>
     <t xml:space="preserve">25.4293766021729</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0486869812012</t>
+    <t xml:space="preserve">26.0486888885498</t>
   </si>
   <si>
     <t xml:space="preserve">25.710880279541</t>
@@ -4730,7 +4730,7 @@
     <t xml:space="preserve">26.2363605499268</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8422527313232</t>
+    <t xml:space="preserve">25.8422508239746</t>
   </si>
   <si>
     <t xml:space="preserve">25.9360847473145</t>
@@ -4742,10 +4742,10 @@
     <t xml:space="preserve">25.7484169006348</t>
   </si>
   <si>
-    <t xml:space="preserve">26.067455291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5741672515869</t>
+    <t xml:space="preserve">26.0674571990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5741653442383</t>
   </si>
   <si>
     <t xml:space="preserve">26.3114280700684</t>
@@ -4757,13 +4757,13 @@
     <t xml:space="preserve">26.7806053161621</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9119758605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0058116912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.231014251709</t>
+    <t xml:space="preserve">26.9119739532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0058097839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2310161590576</t>
   </si>
   <si>
     <t xml:space="preserve">27.1184120178223</t>
@@ -4778,16 +4778,16 @@
     <t xml:space="preserve">27.6814250946045</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7189598083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4749851226807</t>
+    <t xml:space="preserve">27.718957901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4749870300293</t>
   </si>
   <si>
     <t xml:space="preserve">27.7377262115479</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1693687438965</t>
+    <t xml:space="preserve">28.1693668365479</t>
   </si>
   <si>
     <t xml:space="preserve">27.9629287719727</t>
@@ -4796,25 +4796,25 @@
     <t xml:space="preserve">28.6573123931885</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5071754455566</t>
+    <t xml:space="preserve">28.507173538208</t>
   </si>
   <si>
     <t xml:space="preserve">28.6385440826416</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9307422637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.775260925293</t>
+    <t xml:space="preserve">26.9307403564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7752590179443</t>
   </si>
   <si>
     <t xml:space="preserve">27.8878612518311</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4321060180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8074474334717</t>
+    <t xml:space="preserve">28.4321041107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8074493408203</t>
   </si>
   <si>
     <t xml:space="preserve">29.2766265869141</t>
@@ -4829,16 +4829,16 @@
     <t xml:space="preserve">28.1881351470947</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8315601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7940292358398</t>
+    <t xml:space="preserve">27.8315620422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7940273284912</t>
   </si>
   <si>
     <t xml:space="preserve">27.9253959655762</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2819690704346</t>
+    <t xml:space="preserve">28.2819709777832</t>
   </si>
   <si>
     <t xml:space="preserve">29.1640224456787</t>
@@ -4859,13 +4859,13 @@
     <t xml:space="preserve">27.5500545501709</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1934795379639</t>
+    <t xml:space="preserve">27.1934776306152</t>
   </si>
   <si>
     <t xml:space="preserve">26.7243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2175941467285</t>
+    <t xml:space="preserve">26.2175922393799</t>
   </si>
   <si>
     <t xml:space="preserve">26.874439239502</t>
@@ -4892,10 +4892,10 @@
     <t xml:space="preserve">28.206901550293</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9951171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.019229888916</t>
+    <t xml:space="preserve">28.9951190948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0192317962646</t>
   </si>
   <si>
     <t xml:space="preserve">28.4884090423584</t>
@@ -4919,16 +4919,16 @@
     <t xml:space="preserve">30.383882522583</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0460758209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1211414337158</t>
+    <t xml:space="preserve">30.0460739135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1211395263672</t>
   </si>
   <si>
     <t xml:space="preserve">29.6519660949707</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9897708892822</t>
+    <t xml:space="preserve">29.9897727966309</t>
   </si>
   <si>
     <t xml:space="preserve">30.083610534668</t>
@@ -4949,13 +4949,13 @@
     <t xml:space="preserve">29.9334716796875</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5259418487549</t>
+    <t xml:space="preserve">28.5259399414062</t>
   </si>
   <si>
     <t xml:space="preserve">28.3007354736328</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0942993164062</t>
+    <t xml:space="preserve">28.0943012237549</t>
   </si>
   <si>
     <t xml:space="preserve">28.0379962921143</t>
@@ -4970,13 +4970,13 @@
     <t xml:space="preserve">29.5205955505371</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9763507843018</t>
+    <t xml:space="preserve">28.9763488769531</t>
   </si>
   <si>
     <t xml:space="preserve">29.4830627441406</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7645683288574</t>
+    <t xml:space="preserve">29.7645664215088</t>
   </si>
   <si>
     <t xml:space="preserve">28.9575843811035</t>
@@ -4994,7 +4994,7 @@
     <t xml:space="preserve">30.7779903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3973007202148</t>
+    <t xml:space="preserve">31.3973026275635</t>
   </si>
   <si>
     <t xml:space="preserve">29.5581321716309</t>
@@ -5865,6 +5865,9 @@
   </si>
   <si>
     <t xml:space="preserve">31.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3400001525879</t>
   </si>
 </sst>
 </file>
@@ -18025,7 +18028,7 @@
         <v>26.8899993896484</v>
       </c>
       <c r="G455" t="s">
-        <v>378</v>
+        <v>271</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -18051,7 +18054,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G456" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -18077,7 +18080,7 @@
         <v>27.5900001525879</v>
       </c>
       <c r="G457" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -18103,7 +18106,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G458" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -18129,7 +18132,7 @@
         <v>27.6700000762939</v>
       </c>
       <c r="G459" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -18155,7 +18158,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G460" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -18181,7 +18184,7 @@
         <v>28.2800006866455</v>
       </c>
       <c r="G461" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -18233,7 +18236,7 @@
         <v>27.5300006866455</v>
       </c>
       <c r="G463" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -18259,7 +18262,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G464" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -18285,7 +18288,7 @@
         <v>27.6200008392334</v>
       </c>
       <c r="G465" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -18311,7 +18314,7 @@
         <v>27.5300006866455</v>
       </c>
       <c r="G466" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -18363,7 +18366,7 @@
         <v>28.3799991607666</v>
       </c>
       <c r="G468" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -18389,7 +18392,7 @@
         <v>28.3700008392334</v>
       </c>
       <c r="G469" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -18415,7 +18418,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G470" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -18467,7 +18470,7 @@
         <v>28.0900001525879</v>
       </c>
       <c r="G472" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -18493,7 +18496,7 @@
         <v>27.9300003051758</v>
       </c>
       <c r="G473" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -18519,7 +18522,7 @@
         <v>28.0599994659424</v>
       </c>
       <c r="G474" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -18545,7 +18548,7 @@
         <v>27.6100006103516</v>
       </c>
       <c r="G475" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -18571,7 +18574,7 @@
         <v>27.2099990844727</v>
       </c>
       <c r="G476" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -18597,7 +18600,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G477" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -18623,7 +18626,7 @@
         <v>27.7299995422363</v>
       </c>
       <c r="G478" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -18649,7 +18652,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G479" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -18675,7 +18678,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G480" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -18701,7 +18704,7 @@
         <v>24</v>
       </c>
       <c r="G481" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -18727,7 +18730,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G482" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -18753,7 +18756,7 @@
         <v>24.75</v>
       </c>
       <c r="G483" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -18779,7 +18782,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G484" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -18805,7 +18808,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G485" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -18831,7 +18834,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G486" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -18857,7 +18860,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G487" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -18883,7 +18886,7 @@
         <v>24.2099990844727</v>
       </c>
       <c r="G488" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -18909,7 +18912,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G489" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -18935,7 +18938,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G490" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -18961,7 +18964,7 @@
         <v>24.5200004577637</v>
       </c>
       <c r="G491" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -18987,7 +18990,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G492" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -19013,7 +19016,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G493" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -19039,7 +19042,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G494" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -19065,7 +19068,7 @@
         <v>24.5</v>
       </c>
       <c r="G495" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -19091,7 +19094,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G496" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -19117,7 +19120,7 @@
         <v>25.2099990844727</v>
       </c>
       <c r="G497" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -19143,7 +19146,7 @@
         <v>25.4300003051758</v>
       </c>
       <c r="G498" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -19169,7 +19172,7 @@
         <v>25.5200004577637</v>
       </c>
       <c r="G499" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -19195,7 +19198,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G500" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -19221,7 +19224,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G501" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -19247,7 +19250,7 @@
         <v>25</v>
       </c>
       <c r="G502" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -19273,7 +19276,7 @@
         <v>24.8299999237061</v>
       </c>
       <c r="G503" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -19299,7 +19302,7 @@
         <v>26.0900001525879</v>
       </c>
       <c r="G504" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -19325,7 +19328,7 @@
         <v>26.2900009155273</v>
       </c>
       <c r="G505" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -19351,7 +19354,7 @@
         <v>25.9400005340576</v>
       </c>
       <c r="G506" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -19377,7 +19380,7 @@
         <v>25.4200000762939</v>
       </c>
       <c r="G507" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -19403,7 +19406,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G508" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -19455,7 +19458,7 @@
         <v>25.4699993133545</v>
       </c>
       <c r="G510" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -19481,7 +19484,7 @@
         <v>25.2299995422363</v>
       </c>
       <c r="G511" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -19507,7 +19510,7 @@
         <v>25.5</v>
       </c>
       <c r="G512" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -19533,7 +19536,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G513" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -19585,7 +19588,7 @@
         <v>26.6800003051758</v>
       </c>
       <c r="G515" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -19611,7 +19614,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G516" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -19637,7 +19640,7 @@
         <v>26.9799995422363</v>
       </c>
       <c r="G517" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -19663,7 +19666,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G518" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -19689,7 +19692,7 @@
         <v>26.5200004577637</v>
       </c>
       <c r="G519" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -19715,7 +19718,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G520" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -19741,7 +19744,7 @@
         <v>26.7199993133545</v>
       </c>
       <c r="G521" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -19767,7 +19770,7 @@
         <v>26.6800003051758</v>
       </c>
       <c r="G522" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -19819,7 +19822,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G524" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -19845,7 +19848,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G525" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -19871,7 +19874,7 @@
         <v>26.2800006866455</v>
       </c>
       <c r="G526" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -19923,7 +19926,7 @@
         <v>27.0400009155273</v>
       </c>
       <c r="G528" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -19949,7 +19952,7 @@
         <v>26.7199993133545</v>
       </c>
       <c r="G529" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -19975,7 +19978,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G530" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -20001,7 +20004,7 @@
         <v>27.1399993896484</v>
       </c>
       <c r="G531" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -20027,7 +20030,7 @@
         <v>26.6599998474121</v>
       </c>
       <c r="G532" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -20053,7 +20056,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G533" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -20105,7 +20108,7 @@
         <v>26.7199993133545</v>
       </c>
       <c r="G535" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -20131,7 +20134,7 @@
         <v>26.4799995422363</v>
       </c>
       <c r="G536" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -20183,7 +20186,7 @@
         <v>25.5</v>
       </c>
       <c r="G538" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -20209,7 +20212,7 @@
         <v>24.3400001525879</v>
       </c>
       <c r="G539" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -20235,7 +20238,7 @@
         <v>24.0799999237061</v>
       </c>
       <c r="G540" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -20261,7 +20264,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G541" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -20287,7 +20290,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G542" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -20313,7 +20316,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G543" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -20339,7 +20342,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G544" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -20365,7 +20368,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G545" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -20391,7 +20394,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G546" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -20417,7 +20420,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G547" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -20443,7 +20446,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G548" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -20469,7 +20472,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G549" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -20495,7 +20498,7 @@
         <v>24.2800006866455</v>
       </c>
       <c r="G550" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -20521,7 +20524,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G551" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -20547,7 +20550,7 @@
         <v>23.4599990844727</v>
       </c>
       <c r="G552" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -20573,7 +20576,7 @@
         <v>23.1800003051758</v>
       </c>
       <c r="G553" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -20599,7 +20602,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G554" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -20625,7 +20628,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G555" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -20651,7 +20654,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G556" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -20677,7 +20680,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G557" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -20703,7 +20706,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G558" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -20729,7 +20732,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G559" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -20781,7 +20784,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G561" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -20833,7 +20836,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G563" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -20859,7 +20862,7 @@
         <v>25.1599998474121</v>
       </c>
       <c r="G564" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -20885,7 +20888,7 @@
         <v>24.6399993896484</v>
       </c>
       <c r="G565" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -20911,7 +20914,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G566" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -20937,7 +20940,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G567" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -20963,7 +20966,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G568" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -20989,7 +20992,7 @@
         <v>24.2199993133545</v>
       </c>
       <c r="G569" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -21015,7 +21018,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G570" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -21041,7 +21044,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G571" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -21067,7 +21070,7 @@
         <v>24.3400001525879</v>
       </c>
       <c r="G572" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -21093,7 +21096,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G573" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -21119,7 +21122,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G574" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -21145,7 +21148,7 @@
         <v>24.5</v>
       </c>
       <c r="G575" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -21171,7 +21174,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G576" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -21197,7 +21200,7 @@
         <v>24.8199996948242</v>
       </c>
       <c r="G577" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -21223,7 +21226,7 @@
         <v>24.5200004577637</v>
       </c>
       <c r="G578" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -21249,7 +21252,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G579" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -21275,7 +21278,7 @@
         <v>24</v>
       </c>
       <c r="G580" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -21301,7 +21304,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G581" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -21327,7 +21330,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G582" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -21353,7 +21356,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G583" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -21379,7 +21382,7 @@
         <v>23.4799995422363</v>
       </c>
       <c r="G584" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -21405,7 +21408,7 @@
         <v>23.7800006866455</v>
       </c>
       <c r="G585" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -21431,7 +21434,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G586" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -21457,7 +21460,7 @@
         <v>25.5599994659424</v>
       </c>
       <c r="G587" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -21483,7 +21486,7 @@
         <v>25.1200008392334</v>
       </c>
       <c r="G588" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -21509,7 +21512,7 @@
         <v>25</v>
       </c>
       <c r="G589" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -21535,7 +21538,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G590" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -21561,7 +21564,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G591" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -21587,7 +21590,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G592" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -21613,7 +21616,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G593" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -21639,7 +21642,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G594" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -21665,7 +21668,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G595" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -21691,7 +21694,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G596" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -21717,7 +21720,7 @@
         <v>25</v>
       </c>
       <c r="G597" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -21743,7 +21746,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G598" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -21769,7 +21772,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G599" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -21795,7 +21798,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G600" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -21821,7 +21824,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G601" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -21847,7 +21850,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G602" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -21873,7 +21876,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G603" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -21899,7 +21902,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G604" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -21925,7 +21928,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G605" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -21951,7 +21954,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G606" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -21977,7 +21980,7 @@
         <v>24.5</v>
       </c>
       <c r="G607" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -22003,7 +22006,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G608" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -22029,7 +22032,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G609" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -22055,7 +22058,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G610" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -22081,7 +22084,7 @@
         <v>24.0799999237061</v>
       </c>
       <c r="G611" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -22107,7 +22110,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G612" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -22133,7 +22136,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G613" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -22159,7 +22162,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G614" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -22185,7 +22188,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G615" t="s">
-        <v>481</v>
+        <v>503</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -22237,7 +22240,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G617" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -22341,7 +22344,7 @@
         <v>25</v>
       </c>
       <c r="G621" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -22367,7 +22370,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G622" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -22419,7 +22422,7 @@
         <v>25</v>
       </c>
       <c r="G624" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -22627,7 +22630,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G632" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -22653,7 +22656,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G633" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -22809,7 +22812,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G639" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -22887,7 +22890,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G642" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -23017,7 +23020,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G647" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -23043,7 +23046,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G648" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -23069,7 +23072,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G649" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -23147,7 +23150,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G652" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -24837,7 +24840,7 @@
         <v>25</v>
       </c>
       <c r="G717" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -26215,7 +26218,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G770" t="s">
-        <v>481</v>
+        <v>503</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -26293,7 +26296,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G773" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -26371,7 +26374,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G776" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -26449,7 +26452,7 @@
         <v>24.0799999237061</v>
       </c>
       <c r="G779" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -27203,7 +27206,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G808" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -27515,7 +27518,7 @@
         <v>24.0799999237061</v>
       </c>
       <c r="G820" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -27645,7 +27648,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G825" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -27905,7 +27908,7 @@
         <v>25</v>
       </c>
       <c r="G835" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -27931,7 +27934,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G836" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -27983,7 +27986,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G838" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -71151,7 +71154,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6914583333</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>86826</v>
@@ -71172,6 +71175,32 @@
         <v>1950</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6912037037</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>92824</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>31.5799999237061</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>31.2000007629395</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>31.5799999237061</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>31.3400001525879</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1951</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DLG.MI.xlsx
+++ b/data/DLG.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">DLG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5564193725586</t>
+    <t xml:space="preserve">20.5564212799072</t>
   </si>
   <si>
     <t xml:space="preserve">20.6553974151611</t>
@@ -59,10 +59,10 @@
     <t xml:space="preserve">19.7722320556641</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4905319213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8864307403564</t>
+    <t xml:space="preserve">19.4905338287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8864345550537</t>
   </si>
   <si>
     <t xml:space="preserve">18.5160064697266</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">17.4348926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">17.526252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0542182922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8943328857422</t>
+    <t xml:space="preserve">17.5262508392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0542144775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8943347930908</t>
   </si>
   <si>
     <t xml:space="preserve">18.0135154724121</t>
@@ -89,67 +89,67 @@
     <t xml:space="preserve">16.6354732513428</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4451351165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7116107940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8029708862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6735401153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1329860687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9654884338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6533317565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9909620285034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7777814865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3335647583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4123373031616</t>
+    <t xml:space="preserve">16.4451389312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7116088867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8029670715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6735420227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1329822540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9654855728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6533298492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9909601211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7777824401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3335666656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.412335395813</t>
   </si>
   <si>
     <t xml:space="preserve">14.7397155761719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4553823471069</t>
+    <t xml:space="preserve">15.4553804397583</t>
   </si>
   <si>
     <t xml:space="preserve">15.2574319839478</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4097051620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7523097991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3868618011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9121923446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9578723907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5848121643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1253719329834</t>
+    <t xml:space="preserve">15.4097032546997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7523107528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3868598937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9121932983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9578704833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5848093032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1253700256348</t>
   </si>
   <si>
     <t xml:space="preserve">16.1938934326172</t>
@@ -158,82 +158,82 @@
     <t xml:space="preserve">16.5593395233154</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7496738433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.881739616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2193651199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792495727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0873012542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7142391204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2878837585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8969669342041</t>
+    <t xml:space="preserve">16.7496776580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8817386627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2193660736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792486190796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0873031616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7142429351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2878856658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8969650268555</t>
   </si>
   <si>
     <t xml:space="preserve">15.3183393478394</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6076536178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9274206161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9883279800415</t>
+    <t xml:space="preserve">15.6076545715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9274196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9883260726929</t>
   </si>
   <si>
     <t xml:space="preserve">15.8893537521362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6152677536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3564071655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1356143951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.226978302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3487920761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0442562103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2345933914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0594835281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1432256698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5493783950806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7853946685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.82346534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.783166885376</t>
+    <t xml:space="preserve">15.6152658462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.356409072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1356172561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.226975440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3487939834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0442543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2345914840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0594816207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1432304382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5493774414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7853956222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8234663009644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7831659317017</t>
   </si>
   <si>
     <t xml:space="preserve">14.977988243103</t>
@@ -242,64 +242,64 @@
     <t xml:space="preserve">15.1572256088257</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1494331359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9624052047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9857778549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9546098709106</t>
+    <t xml:space="preserve">15.149432182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.96240234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.985782623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.954610824585</t>
   </si>
   <si>
     <t xml:space="preserve">14.8533020019531</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4689435958862</t>
+    <t xml:space="preserve">15.4689426422119</t>
   </si>
   <si>
     <t xml:space="preserve">15.6715574264526</t>
   </si>
   <si>
-    <t xml:space="preserve">16.21706199646</t>
+    <t xml:space="preserve">16.2170639038086</t>
   </si>
   <si>
     <t xml:space="preserve">15.7572793960571</t>
   </si>
   <si>
-    <t xml:space="preserve">16.030029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2404403686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1469287872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3495407104492</t>
+    <t xml:space="preserve">16.0300331115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.240442276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1469268798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3495426177979</t>
   </si>
   <si>
     <t xml:space="preserve">16.5054016113281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3105773925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7288875579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.793737411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0742835998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.762565612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7547740936279</t>
+    <t xml:space="preserve">16.3105754852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7288856506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7937393188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0742816925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7625675201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7547760009766</t>
   </si>
   <si>
     <t xml:space="preserve">16.8482894897461</t>
@@ -308,28 +308,28 @@
     <t xml:space="preserve">17.1132469177246</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3002777099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7678527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9081268310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.947093963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.063985824585</t>
+    <t xml:space="preserve">17.3002815246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7678508758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9081249237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9470901489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0639839172363</t>
   </si>
   <si>
     <t xml:space="preserve">18.4848003387451</t>
   </si>
   <si>
-    <t xml:space="preserve">18.788724899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.46142578125</t>
+    <t xml:space="preserve">18.7887268066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4614238739014</t>
   </si>
   <si>
     <t xml:space="preserve">18.3367385864258</t>
@@ -341,13 +341,13 @@
     <t xml:space="preserve">18.0795707702637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6484527587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8276882171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4536304473877</t>
+    <t xml:space="preserve">18.6484546661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8276863098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4536323547363</t>
   </si>
   <si>
     <t xml:space="preserve">17.8379898071289</t>
@@ -359,34 +359,34 @@
     <t xml:space="preserve">17.2535190582275</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0820751190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4951038360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9237117767334</t>
+    <t xml:space="preserve">17.0820770263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4951019287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9237098693848</t>
   </si>
   <si>
     <t xml:space="preserve">17.8224048614502</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7834377288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9315052032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6768436431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5234937667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1157550811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3651313781738</t>
+    <t xml:space="preserve">17.7834396362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9315071105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6768455505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5234928131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1157531738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3651275634766</t>
   </si>
   <si>
     <t xml:space="preserve">16.6612567901611</t>
@@ -395,103 +395,103 @@
     <t xml:space="preserve">16.6300888061523</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8975534439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7806606292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5468740463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7884550094604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3729228973389</t>
+    <t xml:space="preserve">15.8975515365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7806587219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5468711853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7884521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3729209899902</t>
   </si>
   <si>
     <t xml:space="preserve">16.1858921051025</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1625118255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4196796417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5209865570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5287799835205</t>
+    <t xml:space="preserve">16.1625099182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.419677734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5209884643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5287780761719</t>
   </si>
   <si>
     <t xml:space="preserve">16.8404960632324</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9184246063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8716659545898</t>
+    <t xml:space="preserve">16.9184265136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8716678619385</t>
   </si>
   <si>
     <t xml:space="preserve">16.8015308380127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6119956970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2223453521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5964107513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4171733856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6587505340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3158664703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.323657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5028915405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0561904907227</t>
+    <t xml:space="preserve">17.6119918823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2223510742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5964088439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4171695709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6587524414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3158626556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3236560821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5028953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0561923980713</t>
   </si>
   <si>
     <t xml:space="preserve">18.5393543243408</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7030048370361</t>
+    <t xml:space="preserve">18.7030029296875</t>
   </si>
   <si>
     <t xml:space="preserve">18.6640377044678</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8121032714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0951538085938</t>
+    <t xml:space="preserve">18.812105178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0951557159424</t>
   </si>
   <si>
     <t xml:space="preserve">18.1497058868408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.900333404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1574993133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8769569396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6665439605713</t>
+    <t xml:space="preserve">17.9003353118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1575012207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8769550323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6665458679199</t>
   </si>
   <si>
     <t xml:space="preserve">17.9704704284668</t>
@@ -500,55 +500,55 @@
     <t xml:space="preserve">18.0328121185303</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5106868743896</t>
+    <t xml:space="preserve">17.510684967041</t>
   </si>
   <si>
     <t xml:space="preserve">17.5730285644531</t>
   </si>
   <si>
-    <t xml:space="preserve">17.362621307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4015884399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2379341125488</t>
+    <t xml:space="preserve">17.3626232147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4015846252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2379379272461</t>
   </si>
   <si>
     <t xml:space="preserve">17.4093818664551</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1444206237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8171215057373</t>
+    <t xml:space="preserve">17.1444225311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.81711769104</t>
   </si>
   <si>
     <t xml:space="preserve">16.6145000457764</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6846389770508</t>
+    <t xml:space="preserve">16.6846370697021</t>
   </si>
   <si>
     <t xml:space="preserve">17.0197334289551</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1288356781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2691059112549</t>
+    <t xml:space="preserve">17.128833770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2691040039062</t>
   </si>
   <si>
     <t xml:space="preserve">16.9963550567627</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4405498504639</t>
+    <t xml:space="preserve">17.4405536651611</t>
   </si>
   <si>
     <t xml:space="preserve">17.4639301300049</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8327026367188</t>
+    <t xml:space="preserve">16.8327045440674</t>
   </si>
   <si>
     <t xml:space="preserve">16.8249111175537</t>
@@ -560,22 +560,22 @@
     <t xml:space="preserve">16.7859477996826</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7469806671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2768993377686</t>
+    <t xml:space="preserve">16.7469825744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2769012451172</t>
   </si>
   <si>
     <t xml:space="preserve">17.2457275390625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0509071350098</t>
+    <t xml:space="preserve">17.0509014129639</t>
   </si>
   <si>
     <t xml:space="preserve">17.0976638793945</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9573917388916</t>
+    <t xml:space="preserve">16.957389831543</t>
   </si>
   <si>
     <t xml:space="preserve">17.2301425933838</t>
@@ -584,79 +584,79 @@
     <t xml:space="preserve">17.2067623138428</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4327564239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2846927642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0664901733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9521036148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9832754135132</t>
+    <t xml:space="preserve">17.4327583312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2846946716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0664920806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9521017074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9832744598389</t>
   </si>
   <si>
     <t xml:space="preserve">16.2560272216797</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3339557647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9988641738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4065999984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3130855560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1182594299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5131969451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0923748016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9131422042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1780986785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7158069610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0586948394775</t>
+    <t xml:space="preserve">16.3339538574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9988632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4065990447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.313084602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1182622909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5131931304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0923767089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.913140296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1780967712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7158088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0586967468262</t>
   </si>
   <si>
     <t xml:space="preserve">16.4664344787598</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2248554229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9754829406738</t>
+    <t xml:space="preserve">16.224853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9754838943481</t>
   </si>
   <si>
     <t xml:space="preserve">16.7080173492432</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4976100921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6924285888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5599517822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7703590393066</t>
+    <t xml:space="preserve">16.4976062774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6924304962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5599536895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.770357131958</t>
   </si>
   <si>
     <t xml:space="preserve">16.8638763427734</t>
@@ -665,79 +665,79 @@
     <t xml:space="preserve">17.0275268554688</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4561367034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4483451843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8847465515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1185340881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2354259490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0172290802002</t>
+    <t xml:space="preserve">17.4561347961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4483413696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.884744644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1185359954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2354278564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0172309875488</t>
   </si>
   <si>
     <t xml:space="preserve">17.8457832336426</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9626750946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8691596984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6353702545166</t>
+    <t xml:space="preserve">17.9626770019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.869161605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6353721618652</t>
   </si>
   <si>
     <t xml:space="preserve">17.7912311553955</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5808238983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6509609222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1107387542725</t>
+    <t xml:space="preserve">17.5808258056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6509590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1107406616211</t>
   </si>
   <si>
     <t xml:space="preserve">17.9782600402832</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3133583068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2042560577393</t>
+    <t xml:space="preserve">18.3133602142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2042541503906</t>
   </si>
   <si>
     <t xml:space="preserve">18.469217300415</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0848579406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3498153686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2952651977539</t>
+    <t xml:space="preserve">19.0848598480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.349817276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2952632904053</t>
   </si>
   <si>
     <t xml:space="preserve">19.4667091369629</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2485065460205</t>
+    <t xml:space="preserve">19.2485084533691</t>
   </si>
   <si>
     <t xml:space="preserve">19.3186435699463</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0614757537842</t>
+    <t xml:space="preserve">19.0614776611328</t>
   </si>
   <si>
     <t xml:space="preserve">19.4199523925781</t>
@@ -746,46 +746,46 @@
     <t xml:space="preserve">19.2407150268555</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0926494598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4511241912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.858865737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.640661239624</t>
+    <t xml:space="preserve">19.0926475524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4511260986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8588638305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6406574249268</t>
   </si>
   <si>
     <t xml:space="preserve">18.9056205749512</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2329216003418</t>
+    <t xml:space="preserve">19.2329235076904</t>
   </si>
   <si>
     <t xml:space="preserve">19.4978809356689</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1914520263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9888343811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.12131690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9732494354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9551582336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6278533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2201175689697</t>
+    <t xml:space="preserve">20.1914482116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9888381958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1213130950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9732475280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9551563262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6278514862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2201156616211</t>
   </si>
   <si>
     <t xml:space="preserve">21.0408782958984</t>
@@ -794,31 +794,31 @@
     <t xml:space="preserve">20.7915077209473</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7447471618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.861644744873</t>
+    <t xml:space="preserve">20.7447490692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8616466522217</t>
   </si>
   <si>
     <t xml:space="preserve">21.2434940338135</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9006061553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0330848693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9785346984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6721057891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4149360656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3136310577393</t>
+    <t xml:space="preserve">20.9006042480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0330867767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.978536605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6721038818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4149379730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3136291503906</t>
   </si>
   <si>
     <t xml:space="preserve">21.1967372894287</t>
@@ -836,34 +836,34 @@
     <t xml:space="preserve">22.1002025604248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9477310180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0279750823975</t>
+    <t xml:space="preserve">21.9477291107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0279769897461</t>
   </si>
   <si>
     <t xml:space="preserve">21.9878540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8273582458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3489685058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4693393707275</t>
+    <t xml:space="preserve">21.8273601531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.348970413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4693412780762</t>
   </si>
   <si>
     <t xml:space="preserve">22.8946514129639</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3199653625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2878684997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.878604888916</t>
+    <t xml:space="preserve">23.3199634552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2878665924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8786029815674</t>
   </si>
   <si>
     <t xml:space="preserve">23.0310726165771</t>
@@ -872,151 +872,151 @@
     <t xml:space="preserve">23.4483604431152</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0230484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9026775360107</t>
+    <t xml:space="preserve">23.0230464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9026737213135</t>
   </si>
   <si>
     <t xml:space="preserve">22.6218109130859</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5014400482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2557678222656</t>
+    <t xml:space="preserve">22.5014381408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.255765914917</t>
   </si>
   <si>
     <t xml:space="preserve">21.8434066772461</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0600757598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6298351287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7341575622559</t>
+    <t xml:space="preserve">22.0600776672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6298389434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7341537475586</t>
   </si>
   <si>
     <t xml:space="preserve">22.9267501831055</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2316970825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1434211730957</t>
+    <t xml:space="preserve">23.2316932678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1434173583984</t>
   </si>
   <si>
     <t xml:space="preserve">23.1674938201904</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6570072174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7693519592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6730556488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8495979309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7613296508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4002151489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2958908081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4323101043701</t>
+    <t xml:space="preserve">23.6570053100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7693538665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6730537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8495960235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7613277435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4002132415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2958927154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4323120117188</t>
   </si>
   <si>
     <t xml:space="preserve">23.7051544189453</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0069999694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8304557800293</t>
+    <t xml:space="preserve">23.0069980621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.830451965332</t>
   </si>
   <si>
     <t xml:space="preserve">22.7903289794922</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0631713867188</t>
+    <t xml:space="preserve">23.0631732940674</t>
   </si>
   <si>
     <t xml:space="preserve">23.8255252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3921852111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2637920379639</t>
+    <t xml:space="preserve">23.3921871185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2637901306152</t>
   </si>
   <si>
     <t xml:space="preserve">23.2718162536621</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1915702819824</t>
+    <t xml:space="preserve">23.1915683746338</t>
   </si>
   <si>
     <t xml:space="preserve">22.9989738464355</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9076042175293</t>
+    <t xml:space="preserve">21.9076061248779</t>
   </si>
   <si>
     <t xml:space="preserve">22.0199546813965</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0761299133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5545196533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4742698669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6267414093018</t>
+    <t xml:space="preserve">22.0761260986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5545177459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4742679595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6267395019531</t>
   </si>
   <si>
     <t xml:space="preserve">21.7711849212646</t>
   </si>
   <si>
-    <t xml:space="preserve">21.739086151123</t>
+    <t xml:space="preserve">21.7390880584717</t>
   </si>
   <si>
     <t xml:space="preserve">21.8674831390381</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8594589233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5255107879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7421798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3730430603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7181091308594</t>
+    <t xml:space="preserve">21.8594570159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5255146026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7421817779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3730411529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7181072235107</t>
   </si>
   <si>
     <t xml:space="preserve">22.8625545501709</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7100811004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5335369110107</t>
+    <t xml:space="preserve">22.7100830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5335388183594</t>
   </si>
   <si>
     <t xml:space="preserve">22.6539115905762</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">21.2415504455566</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9927864074707</t>
+    <t xml:space="preserve">20.9927825927734</t>
   </si>
   <si>
     <t xml:space="preserve">20.9446353912354</t>
@@ -1040,70 +1040,70 @@
     <t xml:space="preserve">21.0730323791504</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0489559173584</t>
+    <t xml:space="preserve">21.048957824707</t>
   </si>
   <si>
     <t xml:space="preserve">20.6396942138672</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4310474395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4872264862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8804378509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.864387512207</t>
+    <t xml:space="preserve">20.4310493469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4872226715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8804397583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8643856048584</t>
   </si>
   <si>
     <t xml:space="preserve">20.7119178771973</t>
   </si>
   <si>
-    <t xml:space="preserve">20.575496673584</t>
+    <t xml:space="preserve">20.5754947662354</t>
   </si>
   <si>
     <t xml:space="preserve">20.5995693206787</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6477203369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6156196594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5915451049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3508033752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3427791595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2866039276123</t>
+    <t xml:space="preserve">20.6477184295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6156177520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5915470123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3508052825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3427772521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2866058349609</t>
   </si>
   <si>
     <t xml:space="preserve">20.7440147399902</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6717929840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4952526092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7359886169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2174758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0168590545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3538970947266</t>
+    <t xml:space="preserve">20.6717891693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.495246887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7359924316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2174797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0168571472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3539009094238</t>
   </si>
   <si>
     <t xml:space="preserve">21.2335262298584</t>
@@ -1112,19 +1112,19 @@
     <t xml:space="preserve">20.9045104980469</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5594482421875</t>
+    <t xml:space="preserve">20.5594463348389</t>
   </si>
   <si>
     <t xml:space="preserve">20.5353736877441</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4711742401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7520389556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3779697418213</t>
+    <t xml:space="preserve">20.4711761474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7520408630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3779716491699</t>
   </si>
   <si>
     <t xml:space="preserve">21.0650062561035</t>
@@ -1133,55 +1133,55 @@
     <t xml:space="preserve">21.2255039215088</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3699474334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9156303405762</t>
+    <t xml:space="preserve">21.369945526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9156284332275</t>
   </si>
   <si>
     <t xml:space="preserve">21.4582195281982</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8032855987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.795259475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3088436126709</t>
+    <t xml:space="preserve">21.8032836914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7952575683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3088455200195</t>
   </si>
   <si>
     <t xml:space="preserve">22.140323638916</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2285995483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2045230865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1483516693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6940364837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0921764373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1082248687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.164400100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7742805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7662601470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5897121429443</t>
+    <t xml:space="preserve">22.2285976409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2045211791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1483497619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.694034576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0921745300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1082229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1644020080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7742824554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7662582397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5897102355957</t>
   </si>
   <si>
     <t xml:space="preserve">22.5415630340576</t>
@@ -1190,25 +1190,25 @@
     <t xml:space="preserve">22.4131660461426</t>
   </si>
   <si>
-    <t xml:space="preserve">22.517484664917</t>
+    <t xml:space="preserve">22.5174884796143</t>
   </si>
   <si>
     <t xml:space="preserve">22.1563739776611</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8353824615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5495872497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2526702880859</t>
+    <t xml:space="preserve">21.8353843688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5495853424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2526683807373</t>
   </si>
   <si>
     <t xml:space="preserve">22.2125492095947</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2594356536865</t>
+    <t xml:space="preserve">19.2594337463379</t>
   </si>
   <si>
     <t xml:space="preserve">19.9335155487061</t>
@@ -1217,67 +1217,67 @@
     <t xml:space="preserve">19.8612899780273</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6927738189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6205501556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5402984619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4921550750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4279537200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7409191131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6767196655273</t>
+    <t xml:space="preserve">19.6927700042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6205520629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5403003692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.492151260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4279518127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7409172058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.676721572876</t>
   </si>
   <si>
     <t xml:space="preserve">19.805118560791</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4199333190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7569675445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6606731414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1421585083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2304286956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4069747924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4792003631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2545070648193</t>
+    <t xml:space="preserve">19.4199314117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7569713592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6606712341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1421604156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.230432510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4069766998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4791984558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2545051574707</t>
   </si>
   <si>
     <t xml:space="preserve">19.9415416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0619106292725</t>
+    <t xml:space="preserve">20.0619125366211</t>
   </si>
   <si>
     <t xml:space="preserve">19.9254894256592</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9366111755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0971069335938</t>
+    <t xml:space="preserve">20.9366092681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0971050262451</t>
   </si>
   <si>
     <t xml:space="preserve">20.8162384033203</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">20.6878414154053</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4390716552734</t>
+    <t xml:space="preserve">20.4390735626221</t>
   </si>
   <si>
     <t xml:space="preserve">20.2464790344238</t>
@@ -1298,19 +1298,19 @@
     <t xml:space="preserve">20.4631500244141</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5433959960938</t>
+    <t xml:space="preserve">20.5433979034424</t>
   </si>
   <si>
     <t xml:space="preserve">21.4100723266602</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0088348388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6508140563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1372299194336</t>
+    <t xml:space="preserve">21.0088329315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6508121490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.137228012085</t>
   </si>
   <si>
     <t xml:space="preserve">21.2816772460938</t>
@@ -1319,34 +1319,34 @@
     <t xml:space="preserve">21.5063667297363</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4421691894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9606838226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3458728790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0890827178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6989631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8113059997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7792110443115</t>
+    <t xml:space="preserve">21.4421672821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9606857299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.345874786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0890789031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6989612579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8113098144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7792091369629</t>
   </si>
   <si>
     <t xml:space="preserve">21.394021987915</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7471122741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2495765686035</t>
+    <t xml:space="preserve">21.7471103668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2495746612549</t>
   </si>
   <si>
     <t xml:space="preserve">19.5322780609131</t>
@@ -1355,10 +1355,10 @@
     <t xml:space="preserve">19.3236312866211</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5001773834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.516227722168</t>
+    <t xml:space="preserve">19.5001754760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5162258148193</t>
   </si>
   <si>
     <t xml:space="preserve">20.0458602905273</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">20.0940113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7248706817627</t>
+    <t xml:space="preserve">19.7248687744141</t>
   </si>
   <si>
     <t xml:space="preserve">19.7088203430176</t>
@@ -1376,19 +1376,19 @@
     <t xml:space="preserve">19.403881072998</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4841289520264</t>
+    <t xml:space="preserve">19.4841270446777</t>
   </si>
   <si>
     <t xml:space="preserve">19.1631355285645</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8260974884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6014041900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0075702667236</t>
+    <t xml:space="preserve">18.8260955810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6014022827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0075740814209</t>
   </si>
   <si>
     <t xml:space="preserve">18.585355758667</t>
@@ -1400,52 +1400,52 @@
     <t xml:space="preserve">19.9977130889893</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1261100769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7199440002441</t>
+    <t xml:space="preserve">20.1261119842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7199420928955</t>
   </si>
   <si>
     <t xml:space="preserve">20.1903038024902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7730178833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.837215423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8211669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4359798431396</t>
+    <t xml:space="preserve">19.7730197906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8372173309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8211688995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4359817504883</t>
   </si>
   <si>
     <t xml:space="preserve">19.1310386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3557300567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5483283996582</t>
+    <t xml:space="preserve">19.3557319641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5483264923096</t>
   </si>
   <si>
     <t xml:space="preserve">19.9174633026123</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5804252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0186920166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0026416778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8421440124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0828914642334</t>
+    <t xml:space="preserve">19.5804214477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0186901092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0026435852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8421459197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0828876495361</t>
   </si>
   <si>
     <t xml:space="preserve">19.8853664398193</t>
@@ -1454,79 +1454,79 @@
     <t xml:space="preserve">20.5112953186035</t>
   </si>
   <si>
+    <t xml:space="preserve">20.1582069396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8936672210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6596565246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5760841369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6763706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7265148162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8435211181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8268051147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4954032897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1276760101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2781085968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1778163909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0942440032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9772415161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7766628265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4757900238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6429424285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.525936126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2584991455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.12477684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1916389465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9242000579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5063247680664</t>
+  </si>
+  <si>
     <t xml:space="preserve">20.1582088470459</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8936653137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6596546173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.576078414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6763706207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7265110015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8435230255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8268051147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4954032897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1276741027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2781066894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1778182983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0942459106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9772396087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7766628265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4757919311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6429405212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.525936126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2584972381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.12477684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1916370391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9242000579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5063228607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1582069396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2417831420898</t>
+    <t xml:space="preserve">20.2417850494385</t>
   </si>
   <si>
     <t xml:space="preserve">20.8769493103027</t>
@@ -1535,13 +1535,13 @@
     <t xml:space="preserve">20.7933750152588</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9939556121826</t>
+    <t xml:space="preserve">20.993953704834</t>
   </si>
   <si>
     <t xml:space="preserve">20.8100910186768</t>
   </si>
   <si>
-    <t xml:space="preserve">20.592794418335</t>
+    <t xml:space="preserve">20.5927963256836</t>
   </si>
   <si>
     <t xml:space="preserve">20.6930847167969</t>
@@ -1550,61 +1550,61 @@
     <t xml:space="preserve">20.3420734405518</t>
   </si>
   <si>
-    <t xml:space="preserve">20.492504119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5593662261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7570495605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8740558624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1414928436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2919292449951</t>
+    <t xml:space="preserve">20.4925060272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5593643188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7570476531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8740520477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1414947509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2919273376465</t>
   </si>
   <si>
     <t xml:space="preserve">20.0244884490967</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9409141540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.108060836792</t>
+    <t xml:space="preserve">19.94091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1080646514893</t>
   </si>
   <si>
     <t xml:space="preserve">20.2752132415771</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3922176361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0579204559326</t>
+    <t xml:space="preserve">20.3922138214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.057918548584</t>
   </si>
   <si>
     <t xml:space="preserve">20.4256458282471</t>
   </si>
   <si>
-    <t xml:space="preserve">20.074634552002</t>
+    <t xml:space="preserve">20.0746326446533</t>
   </si>
   <si>
     <t xml:space="preserve">19.8239078521729</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6901912689209</t>
+    <t xml:space="preserve">19.6901893615723</t>
   </si>
   <si>
     <t xml:space="preserve">21.0273818969727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2475738525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3144359588623</t>
+    <t xml:space="preserve">22.2475757598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.314432144165</t>
   </si>
   <si>
     <t xml:space="preserve">23.1000366210938</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">23.2671852111816</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5847702026367</t>
+    <t xml:space="preserve">23.5847663879395</t>
   </si>
   <si>
     <t xml:space="preserve">23.5346221923828</t>
@@ -1628,31 +1628,31 @@
     <t xml:space="preserve">22.8660259246826</t>
   </si>
   <si>
-    <t xml:space="preserve">22.799165725708</t>
+    <t xml:space="preserve">22.7991676330566</t>
   </si>
   <si>
     <t xml:space="preserve">22.8325977325439</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5484428405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6153049468994</t>
+    <t xml:space="preserve">22.5484409332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6153030395508</t>
   </si>
   <si>
     <t xml:space="preserve">22.9328880310059</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1167507171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.150182723999</t>
+    <t xml:space="preserve">23.1167526245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1501808166504</t>
   </si>
   <si>
     <t xml:space="preserve">23.2504692077637</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4009037017822</t>
+    <t xml:space="preserve">23.4009056091309</t>
   </si>
   <si>
     <t xml:space="preserve">23.6181983947754</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">23.2839012145996</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0833225250244</t>
+    <t xml:space="preserve">23.083324432373</t>
   </si>
   <si>
     <t xml:space="preserve">22.8994560241699</t>
@@ -1679,10 +1679,10 @@
     <t xml:space="preserve">22.5818729400635</t>
   </si>
   <si>
-    <t xml:space="preserve">22.331148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8158798217773</t>
+    <t xml:space="preserve">22.3311462402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.815881729126</t>
   </si>
   <si>
     <t xml:space="preserve">22.5317287445068</t>
@@ -1691,31 +1691,31 @@
     <t xml:space="preserve">23.1334686279297</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9663143157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6850566864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3006153106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4343357086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9997482299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8493137359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9496002197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7628402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.461971282959</t>
+    <t xml:space="preserve">22.9663181304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.68505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3006134033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4343338012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9997444152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8493118286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9495983123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7628421783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4619731903076</t>
   </si>
   <si>
     <t xml:space="preserve">21.0440998077393</t>
@@ -1724,16 +1724,16 @@
     <t xml:space="preserve">20.7098007202148</t>
   </si>
   <si>
-    <t xml:space="preserve">20.91037940979</t>
+    <t xml:space="preserve">20.9103813171387</t>
   </si>
   <si>
     <t xml:space="preserve">21.6625518798828</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2279624938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4285430908203</t>
+    <t xml:space="preserve">21.2279644012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4285411834717</t>
   </si>
   <si>
     <t xml:space="preserve">20.9270973205566</t>
@@ -1742,28 +1742,28 @@
     <t xml:space="preserve">21.3616809844971</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5121154785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9605255126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8573379516602</t>
+    <t xml:space="preserve">21.5121173858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9605274200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8573398590088</t>
   </si>
   <si>
     <t xml:space="preserve">19.5397548675537</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9547328948975</t>
+    <t xml:space="preserve">18.9547348022461</t>
   </si>
   <si>
     <t xml:space="preserve">19.556468963623</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0550212860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4394664764404</t>
+    <t xml:space="preserve">19.0550231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4394645690918</t>
   </si>
   <si>
     <t xml:space="preserve">19.3893222808838</t>
@@ -1775,19 +1775,19 @@
     <t xml:space="preserve">19.3057479858398</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3726062774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8042984008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6037178039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6872940063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.670581817627</t>
+    <t xml:space="preserve">19.3726043701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8043003082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6037197113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6872959136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6705799102783</t>
   </si>
   <si>
     <t xml:space="preserve">18.704008102417</t>
@@ -1796,76 +1796,76 @@
     <t xml:space="preserve">18.8878726959229</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2221717834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6734733581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6567611694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8907699584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0913486480713</t>
+    <t xml:space="preserve">19.2221698760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6734771728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.656759262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8907680511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0913524627686</t>
   </si>
   <si>
     <t xml:space="preserve">19.8406238555908</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5898990631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.088451385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7737655639648</t>
+    <t xml:space="preserve">19.5899028778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0884532928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7737636566162</t>
   </si>
   <si>
     <t xml:space="preserve">19.6400451660156</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4561824798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9213008880615</t>
+    <t xml:space="preserve">19.4561805725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9213027954102</t>
   </si>
   <si>
     <t xml:space="preserve">19.3391761779785</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5201435089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5506820678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0019855499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9016895294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4699974060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.235990524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4365673065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.041202545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3086433410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9910583496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3253593444824</t>
+    <t xml:space="preserve">18.5201454162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5506763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0019817352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9016914367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4700031280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2359886169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4365692138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0412044525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3086414337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.991060256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3253555297852</t>
   </si>
   <si>
     <t xml:space="preserve">18.2861366271973</t>
@@ -1877,34 +1877,34 @@
     <t xml:space="preserve">18.219274520874</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4198570251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6538639068604</t>
+    <t xml:space="preserve">18.4198551177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6538619995117</t>
   </si>
   <si>
     <t xml:space="preserve">18.25270652771</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3529949188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5368595123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7541522979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6371479034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1553153991699</t>
+    <t xml:space="preserve">18.3529930114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5368576049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7541561126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.637149810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1553134918213</t>
   </si>
   <si>
     <t xml:space="preserve">19.4060344696045</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2723178863525</t>
+    <t xml:space="preserve">19.2723159790039</t>
   </si>
   <si>
     <t xml:space="preserve">18.9714488983154</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">19.0215930938721</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3224639892578</t>
+    <t xml:space="preserve">19.3224601745605</t>
   </si>
   <si>
     <t xml:space="preserve">19.7403354644775</t>
@@ -1925,34 +1925,34 @@
     <t xml:space="preserve">20.1749229431152</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7875823974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9380168914795</t>
+    <t xml:space="preserve">18.7875843048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9380187988281</t>
   </si>
   <si>
     <t xml:space="preserve">20.0077743530273</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2250709533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5789794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1443881988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2054576873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0354156494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6509666442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4336738586426</t>
+    <t xml:space="preserve">20.2250690460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5789775848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1443901062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2054557800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0354118347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6509685516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4336757659912</t>
   </si>
   <si>
     <t xml:space="preserve">17.5841083526611</t>
@@ -1961,43 +1961,43 @@
     <t xml:space="preserve">17.1328067779541</t>
   </si>
   <si>
-    <t xml:space="preserve">16.547779083252</t>
+    <t xml:space="preserve">16.5477809906006</t>
   </si>
   <si>
     <t xml:space="preserve">16.1716957092285</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9961881637573</t>
+    <t xml:space="preserve">15.9961891174316</t>
   </si>
   <si>
     <t xml:space="preserve">16.3221302032471</t>
   </si>
   <si>
-    <t xml:space="preserve">15.879186630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7939529418945</t>
+    <t xml:space="preserve">15.8791837692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7939519882202</t>
   </si>
   <si>
     <t xml:space="preserve">15.7683801651001</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7769031524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3081130981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4018707275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4359655380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5382490158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1632165908813</t>
+    <t xml:space="preserve">15.7769041061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3081150054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4018726348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4359674453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5382480621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1632175445557</t>
   </si>
   <si>
     <t xml:space="preserve">15.333685874939</t>
@@ -2006,25 +2006,25 @@
     <t xml:space="preserve">15.0524091720581</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1717386245728</t>
+    <t xml:space="preserve">15.1717376708984</t>
   </si>
   <si>
     <t xml:space="preserve">15.3507318496704</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5552930831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.640528678894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6490545272827</t>
+    <t xml:space="preserve">15.5552940368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6405277252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6490516662598</t>
   </si>
   <si>
     <t xml:space="preserve">15.6320056915283</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5808658599854</t>
+    <t xml:space="preserve">15.580864906311</t>
   </si>
   <si>
     <t xml:space="preserve">15.4103965759277</t>
@@ -2039,34 +2039,34 @@
     <t xml:space="preserve">14.9842233657837</t>
   </si>
   <si>
-    <t xml:space="preserve">15.043888092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3763017654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4274425506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.282543182373</t>
+    <t xml:space="preserve">15.0438861846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3763027191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4274435043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2825450897217</t>
   </si>
   <si>
     <t xml:space="preserve">15.0865058898926</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1120738983154</t>
+    <t xml:space="preserve">15.1120748519897</t>
   </si>
   <si>
     <t xml:space="preserve">15.1546926498413</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3251609802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3592557907104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9671745300293</t>
+    <t xml:space="preserve">15.3251600265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3592576980591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9671764373779</t>
   </si>
   <si>
     <t xml:space="preserve">14.7455635070801</t>
@@ -2078,22 +2078,22 @@
     <t xml:space="preserve">14.6518077850342</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5154323577881</t>
+    <t xml:space="preserve">14.515435218811</t>
   </si>
   <si>
     <t xml:space="preserve">14.7114734649658</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6347608566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5410060882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3534879684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3449630737305</t>
+    <t xml:space="preserve">14.6347637176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5410022735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3534870147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3449640274048</t>
   </si>
   <si>
     <t xml:space="preserve">14.4472465515137</t>
@@ -2102,94 +2102,94 @@
     <t xml:space="preserve">14.4387226104736</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7540903091431</t>
+    <t xml:space="preserve">14.7540893554688</t>
   </si>
   <si>
     <t xml:space="preserve">14.4642934799194</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4813365936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3620109558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2484483718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4956312179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0268402099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0012722015381</t>
+    <t xml:space="preserve">14.4813404083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3620119094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2484502792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4956283569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0268383026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0012693405151</t>
   </si>
   <si>
     <t xml:space="preserve">14.6859035491943</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5324792861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9784545898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4046268463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0353622436523</t>
+    <t xml:space="preserve">14.5324811935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9784555435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4046287536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0353631973267</t>
   </si>
   <si>
     <t xml:space="preserve">15.1376447677612</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8308010101318</t>
+    <t xml:space="preserve">14.8307991027832</t>
   </si>
   <si>
     <t xml:space="preserve">14.9586515426636</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2399263381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8109979629517</t>
+    <t xml:space="preserve">15.2399244308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.810996055603</t>
   </si>
   <si>
     <t xml:space="preserve">16.4843502044678</t>
   </si>
   <si>
-    <t xml:space="preserve">17.046895980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7911930084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5269660949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0128040313721</t>
+    <t xml:space="preserve">17.0468978881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7911949157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5269641876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0128021240234</t>
   </si>
   <si>
     <t xml:space="preserve">16.5781097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3138809204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2371692657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9303274154663</t>
+    <t xml:space="preserve">16.3138790130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2371711730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9303255081177</t>
   </si>
   <si>
     <t xml:space="preserve">15.9218015670776</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3933486938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9416055679321</t>
+    <t xml:space="preserve">15.393346786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9416065216064</t>
   </si>
   <si>
     <t xml:space="preserve">14.5239591598511</t>
@@ -2204,31 +2204,31 @@
     <t xml:space="preserve">14.2512044906616</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1318778991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6177158355713</t>
+    <t xml:space="preserve">14.1318788528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.617714881897</t>
   </si>
   <si>
     <t xml:space="preserve">14.4557695388794</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5580492019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5750980377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7370443344116</t>
+    <t xml:space="preserve">14.558051109314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5750999450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7370452880859</t>
   </si>
   <si>
     <t xml:space="preserve">14.7796592712402</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8393259048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8478488922119</t>
+    <t xml:space="preserve">14.8393230438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.847846031189</t>
   </si>
   <si>
     <t xml:space="preserve">14.6688537597656</t>
@@ -2237,19 +2237,19 @@
     <t xml:space="preserve">14.2341604232788</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1404027938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0636901855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8222761154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6262407302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0183162689209</t>
+    <t xml:space="preserve">14.14040184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0636911392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8222780227661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.626238822937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0183181762695</t>
   </si>
   <si>
     <t xml:space="preserve">15.1291227340698</t>
@@ -2258,184 +2258,184 @@
     <t xml:space="preserve">15.2058334350586</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5467710494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8195219039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0326061248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4502544403076</t>
+    <t xml:space="preserve">15.5467700958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8195199966431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0326080322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4502563476562</t>
   </si>
   <si>
     <t xml:space="preserve">16.4928741455078</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0155620574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1519355773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2030754089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.041130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0752239227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8962326049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2883110046387</t>
+    <t xml:space="preserve">16.0155582427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1519374847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2030773162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0411281585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0752258300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8962316513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2883129119873</t>
   </si>
   <si>
     <t xml:space="preserve">16.2627410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1263656616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1178436279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1945533752441</t>
+    <t xml:space="preserve">16.1263637542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1178398132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1945514678955</t>
   </si>
   <si>
     <t xml:space="preserve">16.228645324707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.168981552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0667018890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2797889709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1093196868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7087144851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6746215820312</t>
+    <t xml:space="preserve">16.1689796447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0666999816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2797870635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1093158721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7087163925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6746225357056</t>
   </si>
   <si>
     <t xml:space="preserve">15.9729433059692</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7428073883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3422079086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2910690307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1035509109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5665731430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2853002548218</t>
+    <t xml:space="preserve">15.74280834198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3422060012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2910671234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.103551864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5665740966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2853021621704</t>
   </si>
   <si>
     <t xml:space="preserve">14.2426815032959</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5949001312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7057065963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6944265365601</t>
+    <t xml:space="preserve">13.5949020385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7057046890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6944236755371</t>
   </si>
   <si>
     <t xml:space="preserve">14.506911277771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0694580078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4615345001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4444913864136</t>
+    <t xml:space="preserve">15.0694608688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.461537361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4444894790649</t>
   </si>
   <si>
     <t xml:space="preserve">15.4700584411621</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6149597167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2740201950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2995891571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7142295837402</t>
+    <t xml:space="preserve">15.6149578094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2740211486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2995910644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7142305374146</t>
   </si>
   <si>
     <t xml:space="preserve">13.381814956665</t>
   </si>
   <si>
-    <t xml:space="preserve">13.552282333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1772527694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2965803146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.262487411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0323524475098</t>
+    <t xml:space="preserve">13.5522832870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1772518157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2965812683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2624864578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0323534011841</t>
   </si>
   <si>
     <t xml:space="preserve">12.7596035003662</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6232271194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.359001159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6600790023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1912879943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8333044052124</t>
+    <t xml:space="preserve">12.6232290267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3590002059937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6600780487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1912889480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8333034515381</t>
   </si>
   <si>
     <t xml:space="preserve">9.74230194091797</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6543111801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6430311203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8220243453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6686000823975</t>
+    <t xml:space="preserve">10.6543092727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6430320739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8220252990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6686019897461</t>
   </si>
   <si>
     <t xml:space="preserve">12.0351095199585</t>
@@ -2444,16 +2444,16 @@
     <t xml:space="preserve">13.3306751251221</t>
   </si>
   <si>
-    <t xml:space="preserve">13.722752571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2767772674561</t>
+    <t xml:space="preserve">13.7227544784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2767782211304</t>
   </si>
   <si>
     <t xml:space="preserve">13.0749702453613</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5011434555054</t>
+    <t xml:space="preserve">13.5011425018311</t>
   </si>
   <si>
     <t xml:space="preserve">13.4500017166138</t>
@@ -2465,16 +2465,16 @@
     <t xml:space="preserve">13.0834941864014</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1175880432129</t>
+    <t xml:space="preserve">13.1175889968872</t>
   </si>
   <si>
     <t xml:space="preserve">12.4953756332397</t>
   </si>
   <si>
-    <t xml:space="preserve">13.023829460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3562450408936</t>
+    <t xml:space="preserve">13.0238304138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3562440872192</t>
   </si>
   <si>
     <t xml:space="preserve">13.4244337081909</t>
@@ -2483,16 +2483,16 @@
     <t xml:space="preserve">13.6119480133057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8192672729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6999387741089</t>
+    <t xml:space="preserve">12.8192682266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6999378204346</t>
   </si>
   <si>
     <t xml:space="preserve">12.904501914978</t>
   </si>
   <si>
-    <t xml:space="preserve">13.066445350647</t>
+    <t xml:space="preserve">13.0664472579956</t>
   </si>
   <si>
     <t xml:space="preserve">13.2113456726074</t>
@@ -2501,13 +2501,13 @@
     <t xml:space="preserve">13.3988618850708</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3136262893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8079881668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8932209014893</t>
+    <t xml:space="preserve">13.313627243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8079862594604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8932199478149</t>
   </si>
   <si>
     <t xml:space="preserve">13.9358396530151</t>
@@ -2519,16 +2519,16 @@
     <t xml:space="preserve">13.8846988677979</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4898633956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7029495239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.200065612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4983854293823</t>
+    <t xml:space="preserve">14.4898624420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7029485702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2000646591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4983863830566</t>
   </si>
   <si>
     <t xml:space="preserve">14.4131517410278</t>
@@ -2537,16 +2537,16 @@
     <t xml:space="preserve">15.1205987930298</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7711391448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8563718795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4189186096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.938850402832</t>
+    <t xml:space="preserve">14.7711353302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8563709259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4189195632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9388513565063</t>
   </si>
   <si>
     <t xml:space="preserve">15.75133228302</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">16.6207256317139</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4161624908447</t>
+    <t xml:space="preserve">16.4161605834961</t>
   </si>
   <si>
     <t xml:space="preserve">16.2456932067871</t>
@@ -2564,10 +2564,10 @@
     <t xml:space="preserve">16.5440139770508</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7826709747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3707866668701</t>
+    <t xml:space="preserve">16.7826728820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3707885742188</t>
   </si>
   <si>
     <t xml:space="preserve">18.4276962280273</t>
@@ -2579,13 +2579,13 @@
     <t xml:space="preserve">19.0754776000977</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6493072509766</t>
+    <t xml:space="preserve">18.6493053436279</t>
   </si>
   <si>
     <t xml:space="preserve">18.90500831604</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6039352416992</t>
+    <t xml:space="preserve">19.6039295196533</t>
   </si>
   <si>
     <t xml:space="preserve">19.6380290985107</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">19.7744026184082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1494331359863</t>
+    <t xml:space="preserve">20.1494312286377</t>
   </si>
   <si>
     <t xml:space="preserve">20.0471515655518</t>
@@ -2609,16 +2609,16 @@
     <t xml:space="preserve">19.4846038818359</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8425884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8084926605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7119808197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9506378173828</t>
+    <t xml:space="preserve">19.8425922393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8084945678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7119789123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9506340026855</t>
   </si>
   <si>
     <t xml:space="preserve">20.6778888702393</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">20.8824501037598</t>
   </si>
   <si>
-    <t xml:space="preserve">21.052921295166</t>
+    <t xml:space="preserve">21.0529174804688</t>
   </si>
   <si>
     <t xml:space="preserve">20.9335899353027</t>
@@ -2648,28 +2648,28 @@
     <t xml:space="preserve">21.2574806213379</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2233848571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0699634552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3086223602295</t>
+    <t xml:space="preserve">21.2233867645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0699653625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3086185455322</t>
   </si>
   <si>
     <t xml:space="preserve">20.8994960784912</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9676837921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7631225585938</t>
+    <t xml:space="preserve">20.9676856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7631206512451</t>
   </si>
   <si>
     <t xml:space="preserve">20.9165439605713</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1609687805176</t>
+    <t xml:space="preserve">22.1609668731689</t>
   </si>
   <si>
     <t xml:space="preserve">22.6382789611816</t>
@@ -2678,16 +2678,16 @@
     <t xml:space="preserve">23.0133113861084</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9167976379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8145179748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9679393768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0020294189453</t>
+    <t xml:space="preserve">23.9167957305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8145160675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9679374694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0020313262939</t>
   </si>
   <si>
     <t xml:space="preserve">23.5758609771729</t>
@@ -2696,10 +2696,10 @@
     <t xml:space="preserve">23.8656558990479</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7974700927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5247211456299</t>
+    <t xml:space="preserve">23.7974681854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5247192382812</t>
   </si>
   <si>
     <t xml:space="preserve">23.5929069519043</t>
@@ -2717,16 +2717,16 @@
     <t xml:space="preserve">23.4394855499268</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7292823791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7463302612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6951866149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4906272888184</t>
+    <t xml:space="preserve">23.729284286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7463321685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6951885223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4906253814697</t>
   </si>
   <si>
     <t xml:space="preserve">23.7633743286133</t>
@@ -2735,31 +2735,31 @@
     <t xml:space="preserve">23.1496868133545</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9849853515625</t>
+    <t xml:space="preserve">23.9849872589111</t>
   </si>
   <si>
     <t xml:space="preserve">23.899751663208</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4963932037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2123622894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5304870605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1100788116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0647048950195</t>
+    <t xml:space="preserve">24.4963893890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2123603820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5304889678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1100769042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0647068023682</t>
   </si>
   <si>
     <t xml:space="preserve">25.4680633544922</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5533008575439</t>
+    <t xml:space="preserve">25.5532989501953</t>
   </si>
   <si>
     <t xml:space="preserve">25.4851112365723</t>
@@ -2771,31 +2771,31 @@
     <t xml:space="preserve">25.0589389801025</t>
   </si>
   <si>
-    <t xml:space="preserve">25.075984954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8202838897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8884696960449</t>
+    <t xml:space="preserve">25.0759887695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8202819824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8884716033936</t>
   </si>
   <si>
     <t xml:space="preserve">25.1953144073486</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7180023193359</t>
+    <t xml:space="preserve">24.7180004119873</t>
   </si>
   <si>
     <t xml:space="preserve">25.3487358093262</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2294082641602</t>
+    <t xml:space="preserve">25.2294101715088</t>
   </si>
   <si>
     <t xml:space="preserve">25.4339733123779</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3657855987549</t>
+    <t xml:space="preserve">25.3657836914062</t>
   </si>
   <si>
     <t xml:space="preserve">25.9453792572021</t>
@@ -2807,22 +2807,22 @@
     <t xml:space="preserve">26.7636299133301</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0306148529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9283332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0135669708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.144172668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9566593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4224376678467</t>
+    <t xml:space="preserve">26.0306129455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9283313751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0135631561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1441764831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.956657409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.422435760498</t>
   </si>
   <si>
     <t xml:space="preserve">23.2690143585205</t>
@@ -2837,19 +2837,19 @@
     <t xml:space="preserve">24.8373317718506</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0930328369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5703449249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6385345458984</t>
+    <t xml:space="preserve">25.0930347442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5703468322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6385364532471</t>
   </si>
   <si>
     <t xml:space="preserve">24.3600158691406</t>
   </si>
   <si>
-    <t xml:space="preserve">24.13840675354</t>
+    <t xml:space="preserve">24.1384086608887</t>
   </si>
   <si>
     <t xml:space="preserve">25.911283493042</t>
@@ -2858,28 +2858,28 @@
     <t xml:space="preserve">24.5475330352783</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8315620422363</t>
+    <t xml:space="preserve">23.8315658569336</t>
   </si>
   <si>
     <t xml:space="preserve">23.5588111877441</t>
   </si>
   <si>
-    <t xml:space="preserve">24.12135887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5417671203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0985431671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2747840881348</t>
+    <t xml:space="preserve">24.1213607788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.54176902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0985469818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2747821807861</t>
   </si>
   <si>
     <t xml:space="preserve">24.9396114349365</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2918281555176</t>
+    <t xml:space="preserve">24.2918300628662</t>
   </si>
   <si>
     <t xml:space="preserve">24.070219039917</t>
@@ -2888,28 +2888,28 @@
     <t xml:space="preserve">23.5076713562012</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3372001647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.183780670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6894226074219</t>
+    <t xml:space="preserve">23.3372039794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1837825775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6894207000732</t>
   </si>
   <si>
     <t xml:space="preserve">23.1667327880859</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2860622406006</t>
+    <t xml:space="preserve">23.2860641479492</t>
   </si>
   <si>
     <t xml:space="preserve">23.2029094696045</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3768424987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6984977722168</t>
+    <t xml:space="preserve">23.3768405914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6984958648682</t>
   </si>
   <si>
     <t xml:space="preserve">22.5941352844238</t>
@@ -2927,37 +2927,37 @@
     <t xml:space="preserve">23.2898750305176</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8028564453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8724327087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7506790161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7158908843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2462673187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.33323097229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4723777770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2550868988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5769920349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3596973419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5510272979736</t>
+    <t xml:space="preserve">22.8028545379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8724308013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.750675201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7158889770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2462635040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3332347869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4723815917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2550888061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5769939422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3596992492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.551025390625</t>
   </si>
   <si>
     <t xml:space="preserve">26.1945877075195</t>
@@ -2969,25 +2969,25 @@
     <t xml:space="preserve">25.7597503662109</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4033069610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0294704437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.186014175415</t>
+    <t xml:space="preserve">26.4033088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0294723510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1860160827637</t>
   </si>
   <si>
     <t xml:space="preserve">27.1164417266846</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0120792388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1426563262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8036060333252</t>
+    <t xml:space="preserve">27.012077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1426582336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8036098480225</t>
   </si>
   <si>
     <t xml:space="preserve">29.0992965698242</t>
@@ -2996,16 +2996,16 @@
     <t xml:space="preserve">29.377592086792</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5863132476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0385475158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2210502624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0818996429443</t>
+    <t xml:space="preserve">29.5863151550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0385437011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2210540771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.081901550293</t>
   </si>
   <si>
     <t xml:space="preserve">28.7688217163086</t>
@@ -3023,40 +3023,40 @@
     <t xml:space="preserve">26.5946369171143</t>
   </si>
   <si>
-    <t xml:space="preserve">27.412130355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6294250488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6208515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6468181610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5250606536865</t>
+    <t xml:space="preserve">27.4121284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6294231414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.620849609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6468162536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5250644683838</t>
   </si>
   <si>
     <t xml:space="preserve">27.2034091949463</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3077697753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.707820892334</t>
+    <t xml:space="preserve">27.307767868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7078189849854</t>
   </si>
   <si>
     <t xml:space="preserve">30.1081199645996</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1340847015381</t>
+    <t xml:space="preserve">29.1340866088867</t>
   </si>
   <si>
     <t xml:space="preserve">29.047119140625</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2906265258789</t>
+    <t xml:space="preserve">29.2906246185303</t>
   </si>
   <si>
     <t xml:space="preserve">28.8905773162842</t>
@@ -3065,103 +3065,103 @@
     <t xml:space="preserve">29.3080196380615</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8560447692871</t>
+    <t xml:space="preserve">30.8560390472412</t>
   </si>
   <si>
     <t xml:space="preserve">30.7342872619629</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2298736572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3690204620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4385948181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0559368133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2994518280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9515800476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6125335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9951858520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6039600372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8300762176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5691719055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8648681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7778930664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4996013641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0387992858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6909275054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3430557250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.447416305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2734832763672</t>
+    <t xml:space="preserve">30.2298755645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3690223693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4385986328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0559406280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2994441986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9515781402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6125297546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.995189666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6039619445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8300724029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5691680908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8648624420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7778949737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4995994567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0387954711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6909255981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3430595397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4474220275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2734813690186</t>
   </si>
   <si>
     <t xml:space="preserve">31.7605018615723</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7083225250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5865650177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7431049346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6387462615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6735382080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3866691589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5605964660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8474674224854</t>
+    <t xml:space="preserve">31.7083206176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5865669250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7431106567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.638744354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6735286712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3866653442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5606002807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8474712371826</t>
   </si>
   <si>
     <t xml:space="preserve">32.5432052612305</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8996467590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5169982910156</t>
+    <t xml:space="preserve">31.8996486663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5169906616211</t>
   </si>
   <si>
     <t xml:space="preserve">31.7952899932861</t>
@@ -3170,16 +3170,16 @@
     <t xml:space="preserve">31.8126831054688</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6213531494141</t>
+    <t xml:space="preserve">31.6213493347168</t>
   </si>
   <si>
     <t xml:space="preserve">31.4822082519531</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3952388763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.155330657959</t>
+    <t xml:space="preserve">31.3952369689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1553268432617</t>
   </si>
   <si>
     <t xml:space="preserve">31.9081134796143</t>
@@ -3191,10 +3191,10 @@
     <t xml:space="preserve">32.1376724243164</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1729850769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2612800598145</t>
+    <t xml:space="preserve">32.1729888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2612762451172</t>
   </si>
   <si>
     <t xml:space="preserve">32.278938293457</t>
@@ -3203,37 +3203,37 @@
     <t xml:space="preserve">31.7491931915283</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7668533325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8728008270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6674156188965</t>
+    <t xml:space="preserve">31.7668514251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8727970123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.667407989502</t>
   </si>
   <si>
     <t xml:space="preserve">33.0029144287109</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4443664550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3031005859375</t>
+    <t xml:space="preserve">33.4443626403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.303108215332</t>
   </si>
   <si>
     <t xml:space="preserve">34.3096122741699</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9982757568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9806175231934</t>
+    <t xml:space="preserve">34.9982719421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9806137084961</t>
   </si>
   <si>
     <t xml:space="preserve">35.2808074951172</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7863807678223</t>
+    <t xml:space="preserve">34.786376953125</t>
   </si>
   <si>
     <t xml:space="preserve">33.9564476013184</t>
@@ -3245,16 +3245,16 @@
     <t xml:space="preserve">33.3384170532227</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9499397277832</t>
+    <t xml:space="preserve">32.9499435424805</t>
   </si>
   <si>
     <t xml:space="preserve">33.1794967651367</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2148094177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0912055969238</t>
+    <t xml:space="preserve">33.2148132324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0912094116211</t>
   </si>
   <si>
     <t xml:space="preserve">32.437858581543</t>
@@ -3266,25 +3266,25 @@
     <t xml:space="preserve">32.843994140625</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1441802978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0317230224609</t>
+    <t xml:space="preserve">33.1441764831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0317192077637</t>
   </si>
   <si>
     <t xml:space="preserve">32.3319091796875</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7027282714844</t>
+    <t xml:space="preserve">32.7027320861816</t>
   </si>
   <si>
     <t xml:space="preserve">33.2677879333496</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4267120361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8616523742676</t>
+    <t xml:space="preserve">33.4267082214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8616485595703</t>
   </si>
   <si>
     <t xml:space="preserve">32.2083015441895</t>
@@ -3293,37 +3293,37 @@
     <t xml:space="preserve">31.2017955780029</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1135063171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9610900878906</t>
+    <t xml:space="preserve">31.1135025024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9610939025879</t>
   </si>
   <si>
     <t xml:space="preserve">33.126522064209</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9322814941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9257717132568</t>
+    <t xml:space="preserve">32.9322853088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9257736206055</t>
   </si>
   <si>
     <t xml:space="preserve">32.5438079833984</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0270843505859</t>
+    <t xml:space="preserve">34.0270805358887</t>
   </si>
   <si>
     <t xml:space="preserve">33.8681602478027</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0800514221191</t>
+    <t xml:space="preserve">34.0800590515137</t>
   </si>
   <si>
     <t xml:space="preserve">34.3449325561523</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3802375793457</t>
+    <t xml:space="preserve">34.380241394043</t>
   </si>
   <si>
     <t xml:space="preserve">34.1330299377441</t>
@@ -3338,16 +3338,16 @@
     <t xml:space="preserve">34.2036628723145</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1153755187988</t>
+    <t xml:space="preserve">34.1153717041016</t>
   </si>
   <si>
     <t xml:space="preserve">33.938793182373</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6209526062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.691577911377</t>
+    <t xml:space="preserve">33.6209449768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6915817260742</t>
   </si>
   <si>
     <t xml:space="preserve">34.2919540405273</t>
@@ -3356,7 +3356,7 @@
     <t xml:space="preserve">34.503849029541</t>
   </si>
   <si>
-    <t xml:space="preserve">32.914623260498</t>
+    <t xml:space="preserve">32.9146270751953</t>
   </si>
   <si>
     <t xml:space="preserve">33.1971549987793</t>
@@ -3368,13 +3368,13 @@
     <t xml:space="preserve">33.5503120422363</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8151893615723</t>
+    <t xml:space="preserve">33.815185546875</t>
   </si>
   <si>
     <t xml:space="preserve">34.6451187133789</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1395378112793</t>
+    <t xml:space="preserve">35.1395416259766</t>
   </si>
   <si>
     <t xml:space="preserve">34.8570098876953</t>
@@ -3395,28 +3395,28 @@
     <t xml:space="preserve">30.4248390197754</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1776237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0716781616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5595951080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.61256980896</t>
+    <t xml:space="preserve">30.1776275634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0716800689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5595932006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6125659942627</t>
   </si>
   <si>
     <t xml:space="preserve">29.6478843688965</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2306022644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3476982116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0121936798096</t>
+    <t xml:space="preserve">30.230598449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3477001190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0121917724609</t>
   </si>
   <si>
     <t xml:space="preserve">28.2882137298584</t>
@@ -3425,25 +3425,25 @@
     <t xml:space="preserve">27.8467617034912</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4406280517578</t>
+    <t xml:space="preserve">27.4406261444092</t>
   </si>
   <si>
     <t xml:space="preserve">28.5530834197998</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0939750671387</t>
+    <t xml:space="preserve">28.09397315979</t>
   </si>
   <si>
     <t xml:space="preserve">27.7937870025635</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6348648071289</t>
+    <t xml:space="preserve">27.6348628997803</t>
   </si>
   <si>
     <t xml:space="preserve">28.0763149261475</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0410003662109</t>
+    <t xml:space="preserve">28.0409984588623</t>
   </si>
   <si>
     <t xml:space="preserve">28.3058738708496</t>
@@ -3455,73 +3455,73 @@
     <t xml:space="preserve">29.1004810333252</t>
   </si>
   <si>
-    <t xml:space="preserve">29.471305847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1358013153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3123798370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.824462890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9480667114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7891521453857</t>
+    <t xml:space="preserve">29.4713020324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.135799407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3123817443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8244647979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9480686187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7891502380371</t>
   </si>
   <si>
     <t xml:space="preserve">29.2417488098145</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8421211242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.001049041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9833850860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5661010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9545783996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1952838897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1246490478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.330041885376</t>
+    <t xml:space="preserve">29.8421230316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0010452270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9833831787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5661029815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9545822143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1952877044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1246471405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3300399780273</t>
   </si>
   <si>
     <t xml:space="preserve">27.2287292480469</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8402500152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9462013244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6106986999512</t>
+    <t xml:space="preserve">26.8402519226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9461994171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6106967926025</t>
   </si>
   <si>
     <t xml:space="preserve">27.2817039489746</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7231559753418</t>
+    <t xml:space="preserve">27.7231540679932</t>
   </si>
   <si>
     <t xml:space="preserve">27.3876533508301</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6989879608154</t>
+    <t xml:space="preserve">26.6989860534668</t>
   </si>
   <si>
     <t xml:space="preserve">26.8755702972412</t>
@@ -3530,40 +3530,40 @@
     <t xml:space="preserve">27.0698070526123</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7807712554932</t>
+    <t xml:space="preserve">25.7807693481445</t>
   </si>
   <si>
     <t xml:space="preserve">26.434118270874</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1162700653076</t>
+    <t xml:space="preserve">26.1162719726562</t>
   </si>
   <si>
     <t xml:space="preserve">26.85791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3634834289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1339302062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3987998962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1404399871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.575382232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7519607543945</t>
+    <t xml:space="preserve">26.3634853363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1339282989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3988018035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1404361724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5753803253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7519588470459</t>
   </si>
   <si>
     <t xml:space="preserve">26.310510635376</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4694328308105</t>
+    <t xml:space="preserve">26.4694309234619</t>
   </si>
   <si>
     <t xml:space="preserve">26.8225936889648</t>
@@ -3578,16 +3578,16 @@
     <t xml:space="preserve">27.3523349761963</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9815158843994</t>
+    <t xml:space="preserve">26.9815196990967</t>
   </si>
   <si>
     <t xml:space="preserve">27.9350509643555</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8291053771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.405309677124</t>
+    <t xml:space="preserve">27.8291034698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4053115844727</t>
   </si>
   <si>
     <t xml:space="preserve">27.7761287689209</t>
@@ -3596,19 +3596,19 @@
     <t xml:space="preserve">27.6525230407715</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3699932098389</t>
+    <t xml:space="preserve">27.3699951171875</t>
   </si>
   <si>
     <t xml:space="preserve">26.4164581298828</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9155235290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0214710235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.721284866333</t>
+    <t xml:space="preserve">24.9155216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0214729309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7212829589844</t>
   </si>
   <si>
     <t xml:space="preserve">24.8978652954102</t>
@@ -3617,43 +3617,43 @@
     <t xml:space="preserve">25.2686862945557</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5447025299072</t>
+    <t xml:space="preserve">24.5447063446045</t>
   </si>
   <si>
     <t xml:space="preserve">24.1032524108887</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8383827209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6924781799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4517726898193</t>
+    <t xml:space="preserve">23.8383808135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.692476272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.451774597168</t>
   </si>
   <si>
     <t xml:space="preserve">27.5112571716309</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9703674316406</t>
+    <t xml:space="preserve">27.9703693389893</t>
   </si>
   <si>
     <t xml:space="preserve">27.2993621826172</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9285411834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5289192199707</t>
+    <t xml:space="preserve">26.9285449981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5289154052734</t>
   </si>
   <si>
     <t xml:space="preserve">27.475944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9638614654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3811435699463</t>
+    <t xml:space="preserve">26.9638595581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.381139755249</t>
   </si>
   <si>
     <t xml:space="preserve">26.8932247161865</t>
@@ -3662,10 +3662,10 @@
     <t xml:space="preserve">27.1757564544678</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7872772216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0986137390137</t>
+    <t xml:space="preserve">26.7872791290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0986156463623</t>
   </si>
   <si>
     <t xml:space="preserve">25.4629230499268</t>
@@ -3674,31 +3674,31 @@
     <t xml:space="preserve">24.8095741271973</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2333660125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1274185180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7389430999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1738834381104</t>
+    <t xml:space="preserve">25.2333679199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.127420425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7389450073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1738872528076</t>
   </si>
   <si>
     <t xml:space="preserve">22.4080791473389</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4192295074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3662548065186</t>
+    <t xml:space="preserve">21.4192276000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3662567138672</t>
   </si>
   <si>
     <t xml:space="preserve">22.6906089782715</t>
   </si>
   <si>
-    <t xml:space="preserve">21.066068649292</t>
+    <t xml:space="preserve">21.0660667419434</t>
   </si>
   <si>
     <t xml:space="preserve">20.9424591064453</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">22.2844715118408</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2314968109131</t>
+    <t xml:space="preserve">22.2314987182617</t>
   </si>
   <si>
     <t xml:space="preserve">21.8077049255371</t>
@@ -3728,10 +3728,10 @@
     <t xml:space="preserve">21.5251750946045</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4722023010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5604934692383</t>
+    <t xml:space="preserve">21.4722003936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5604915618896</t>
   </si>
   <si>
     <t xml:space="preserve">22.990795135498</t>
@@ -3740,67 +3740,67 @@
     <t xml:space="preserve">22.3374462127686</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8430194854736</t>
+    <t xml:space="preserve">21.8430233001709</t>
   </si>
   <si>
     <t xml:space="preserve">21.7547302246094</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7900466918945</t>
+    <t xml:space="preserve">21.7900485992432</t>
   </si>
   <si>
     <t xml:space="preserve">21.5958061218262</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3839130401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9601192474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1896724700928</t>
+    <t xml:space="preserve">21.3839111328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9601173400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1896705627441</t>
   </si>
   <si>
     <t xml:space="preserve">21.136697769165</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4015674591064</t>
+    <t xml:space="preserve">21.4015693664551</t>
   </si>
   <si>
     <t xml:space="preserve">20.7658786773682</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8365116119385</t>
+    <t xml:space="preserve">20.8365135192871</t>
   </si>
   <si>
     <t xml:space="preserve">20.0595550537109</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9359512329102</t>
+    <t xml:space="preserve">19.9359493255615</t>
   </si>
   <si>
     <t xml:space="preserve">20.3774013519287</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5186653137207</t>
+    <t xml:space="preserve">20.5186634063721</t>
   </si>
   <si>
     <t xml:space="preserve">19.8653202056885</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0065822601318</t>
+    <t xml:space="preserve">20.0065803527832</t>
   </si>
   <si>
     <t xml:space="preserve">20.7835388183594</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5363235473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.041898727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1943130493164</t>
+    <t xml:space="preserve">20.5363254547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0418968200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1943111419678</t>
   </si>
   <si>
     <t xml:space="preserve">19.4238662719727</t>
@@ -3809,37 +3809,37 @@
     <t xml:space="preserve">19.7770290374756</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3420867919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3355770111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5474739074707</t>
+    <t xml:space="preserve">20.3420886993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3355751037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5474720001221</t>
   </si>
   <si>
     <t xml:space="preserve">19.6710815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">19.911153793335</t>
+    <t xml:space="preserve">19.9111557006836</t>
   </si>
   <si>
     <t xml:space="preserve">19.0677719116211</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4711284637451</t>
+    <t xml:space="preserve">19.4711265563965</t>
   </si>
   <si>
     <t xml:space="preserve">20.1311664581299</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3878498077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9012126922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6995334625244</t>
+    <t xml:space="preserve">20.3878479003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9012107849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6995315551758</t>
   </si>
   <si>
     <t xml:space="preserve">20.3145122528076</t>
@@ -3860,22 +3860,22 @@
     <t xml:space="preserve">19.5811347961426</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3061180114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3710670471191</t>
+    <t xml:space="preserve">19.3061199188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3710651397705</t>
   </si>
   <si>
     <t xml:space="preserve">18.7560863494873</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0127716064453</t>
+    <t xml:space="preserve">19.0127696990967</t>
   </si>
   <si>
     <t xml:space="preserve">18.0960483551025</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0861053466797</t>
+    <t xml:space="preserve">19.0861034393311</t>
   </si>
   <si>
     <t xml:space="preserve">17.729362487793</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">17.2801704406738</t>
   </si>
   <si>
-    <t xml:space="preserve">17.261833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.179328918457</t>
+    <t xml:space="preserve">17.2618312835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1793308258057</t>
   </si>
   <si>
     <t xml:space="preserve">17.2343330383301</t>
@@ -3899,10 +3899,10 @@
     <t xml:space="preserve">17.0968246459961</t>
   </si>
   <si>
-    <t xml:space="preserve">16.757640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2626094818115</t>
+    <t xml:space="preserve">16.7576389312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2626113891602</t>
   </si>
   <si>
     <t xml:space="preserve">16.1617698669434</t>
@@ -3911,28 +3911,28 @@
     <t xml:space="preserve">16.1709384918213</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9875926971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3817825317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7851390838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0601558685303</t>
+    <t xml:space="preserve">15.9875946044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3817844390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7851409912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0601539611816</t>
   </si>
   <si>
     <t xml:space="preserve">17.188497543335</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4635124206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9501495361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4092845916748</t>
+    <t xml:space="preserve">17.4635105133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9501476287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4092826843262</t>
   </si>
   <si>
     <t xml:space="preserve">16.6843013763428</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">17.0693244934082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9593181610107</t>
+    <t xml:space="preserve">16.9593162536621</t>
   </si>
   <si>
     <t xml:space="preserve">17.1334934234619</t>
@@ -3953,10 +3953,10 @@
     <t xml:space="preserve">16.8676452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3359470367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8500881195068</t>
+    <t xml:space="preserve">16.3359489440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8500862121582</t>
   </si>
   <si>
     <t xml:space="preserve">16.8218078613281</t>
@@ -3968,13 +3968,13 @@
     <t xml:space="preserve">17.1151599884033</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8852043151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6560249328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6376876831055</t>
+    <t xml:space="preserve">17.8852062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6560230255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6376895904541</t>
   </si>
   <si>
     <t xml:space="preserve">16.8859786987305</t>
@@ -3986,10 +3986,10 @@
     <t xml:space="preserve">17.5643520355225</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6835250854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6651916503906</t>
+    <t xml:space="preserve">17.6835269927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.665189743042</t>
   </si>
   <si>
     <t xml:space="preserve">17.2159976959229</t>
@@ -3998,7 +3998,7 @@
     <t xml:space="preserve">17.3351707458496</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9868183135986</t>
+    <t xml:space="preserve">16.9868202209473</t>
   </si>
   <si>
     <t xml:space="preserve">17.0784912109375</t>
@@ -4016,7 +4016,7 @@
     <t xml:space="preserve">15.9417572021484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0425987243652</t>
+    <t xml:space="preserve">16.0425968170166</t>
   </si>
   <si>
     <t xml:space="preserve">16.0150947570801</t>
@@ -4031,13 +4031,13 @@
     <t xml:space="preserve">15.0525388717651</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2542181015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2175483703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1992158889771</t>
+    <t xml:space="preserve">15.2542171478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2175493240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1992149353027</t>
   </si>
   <si>
     <t xml:space="preserve">15.6117391586304</t>
@@ -4046,10 +4046,10 @@
     <t xml:space="preserve">16.0059280395508</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6942443847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9883699417114</t>
+    <t xml:space="preserve">15.694242477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9883708953857</t>
   </si>
   <si>
     <t xml:space="preserve">14.5758438110352</t>
@@ -4061,16 +4061,16 @@
     <t xml:space="preserve">13.860803604126</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8058004379272</t>
+    <t xml:space="preserve">13.8058013916016</t>
   </si>
   <si>
     <t xml:space="preserve">13.6041231155396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3841104507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5857877731323</t>
+    <t xml:space="preserve">13.3841094970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.585786819458</t>
   </si>
   <si>
     <t xml:space="preserve">13.7599649429321</t>
@@ -4088,7 +4088,7 @@
     <t xml:space="preserve">13.5032825469971</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8883047103882</t>
+    <t xml:space="preserve">13.8883037567139</t>
   </si>
   <si>
     <t xml:space="preserve">13.5124502182007</t>
@@ -4097,13 +4097,13 @@
     <t xml:space="preserve">13.659125328064</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3382730484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4482793807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8516359329224</t>
+    <t xml:space="preserve">13.3382720947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4482803344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8516368865967</t>
   </si>
   <si>
     <t xml:space="preserve">13.5307836532593</t>
@@ -4112,25 +4112,25 @@
     <t xml:space="preserve">13.8424692153931</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1908235549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3466653823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.603346824646</t>
+    <t xml:space="preserve">14.1908226013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3466644287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6033458709717</t>
   </si>
   <si>
     <t xml:space="preserve">14.1816549301147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5483436584473</t>
+    <t xml:space="preserve">14.5483427047729</t>
   </si>
   <si>
     <t xml:space="preserve">14.8233594894409</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5659017562866</t>
+    <t xml:space="preserve">15.5659008026123</t>
   </si>
   <si>
     <t xml:space="preserve">15.7217445373535</t>
@@ -4139,25 +4139,25 @@
     <t xml:space="preserve">15.9050893783569</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1526050567627</t>
+    <t xml:space="preserve">16.1526031494141</t>
   </si>
   <si>
     <t xml:space="preserve">16.7026348114014</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2434978485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.509349822998</t>
+    <t xml:space="preserve">17.2434997558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5093479156494</t>
   </si>
   <si>
     <t xml:space="preserve">18.2427234649658</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5528564453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.717866897583</t>
+    <t xml:space="preserve">20.5528583526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7178688049316</t>
   </si>
   <si>
     <t xml:space="preserve">19.4161262512207</t>
@@ -4175,7 +4175,7 @@
     <t xml:space="preserve">20.2595081329346</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7094764709473</t>
+    <t xml:space="preserve">19.7094783782959</t>
   </si>
   <si>
     <t xml:space="preserve">19.3794555664062</t>
@@ -4193,16 +4193,16 @@
     <t xml:space="preserve">19.8561496734619</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4527931213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5261325836182</t>
+    <t xml:space="preserve">19.4527950286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5261306762695</t>
   </si>
   <si>
     <t xml:space="preserve">19.7278099060059</t>
   </si>
   <si>
-    <t xml:space="preserve">20.369514465332</t>
+    <t xml:space="preserve">20.3695125579834</t>
   </si>
   <si>
     <t xml:space="preserve">19.8378162384033</t>
@@ -4220,7 +4220,7 @@
     <t xml:space="preserve">19.2144470214844</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6728076934814</t>
+    <t xml:space="preserve">19.6728057861328</t>
   </si>
   <si>
     <t xml:space="preserve">19.2327823638916</t>
@@ -4235,7 +4235,7 @@
     <t xml:space="preserve">20.2961769104004</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5161876678467</t>
+    <t xml:space="preserve">20.5161895751953</t>
   </si>
   <si>
     <t xml:space="preserve">21.8179302215576</t>
@@ -4247,7 +4247,7 @@
     <t xml:space="preserve">20.992883682251</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7728710174561</t>
+    <t xml:space="preserve">20.7728691101074</t>
   </si>
   <si>
     <t xml:space="preserve">20.8828792572021</t>
@@ -4289,19 +4289,19 @@
     <t xml:space="preserve">20.3511810302734</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8744869232178</t>
+    <t xml:space="preserve">19.8744850158691</t>
   </si>
   <si>
     <t xml:space="preserve">20.1495018005371</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0761642456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0394954681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9745502471924</t>
+    <t xml:space="preserve">20.0761623382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0394973754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9745483398438</t>
   </si>
   <si>
     <t xml:space="preserve">21.2128963470459</t>
@@ -4337,10 +4337,10 @@
     <t xml:space="preserve">20.5711917877197</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9661560058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5077991485596</t>
+    <t xml:space="preserve">19.966157913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5078010559082</t>
   </si>
   <si>
     <t xml:space="preserve">19.3611221313477</t>
@@ -4376,13 +4376,13 @@
     <t xml:space="preserve">18.9210968017578</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2877864837646</t>
+    <t xml:space="preserve">19.287784576416</t>
   </si>
   <si>
     <t xml:space="preserve">19.1961135864258</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1044406890869</t>
+    <t xml:space="preserve">19.1044425964355</t>
   </si>
   <si>
     <t xml:space="preserve">18.7201499938965</t>
@@ -5525,9 +5525,6 @@
     <t xml:space="preserve">23.6856346130371</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7212829589844</t>
-  </si>
-  <si>
     <t xml:space="preserve">23.9157791137695</t>
   </si>
   <si>
@@ -5868,6 +5865,9 @@
   </si>
   <si>
     <t xml:space="preserve">31.3400001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6800003051758</t>
   </si>
 </sst>
 </file>
@@ -67506,7 +67506,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G2358" t="s">
-        <v>1837</v>
+        <v>1198</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67532,7 +67532,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G2359" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67558,7 +67558,7 @@
         <v>26.0599994659424</v>
       </c>
       <c r="G2360" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67584,7 +67584,7 @@
         <v>26.2399997711182</v>
       </c>
       <c r="G2361" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67610,7 +67610,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G2362" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67636,7 +67636,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G2363" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -67662,7 +67662,7 @@
         <v>26.7199993133545</v>
       </c>
       <c r="G2364" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67688,7 +67688,7 @@
         <v>26.3600006103516</v>
       </c>
       <c r="G2365" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67714,7 +67714,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G2366" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67740,7 +67740,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G2367" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67792,7 +67792,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G2369" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67818,7 +67818,7 @@
         <v>26.6200008392334</v>
       </c>
       <c r="G2370" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -67896,7 +67896,7 @@
         <v>27.7199993133545</v>
       </c>
       <c r="G2373" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -67948,7 +67948,7 @@
         <v>27.7600002288818</v>
       </c>
       <c r="G2375" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -68000,7 +68000,7 @@
         <v>27.5400009155273</v>
       </c>
       <c r="G2377" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -68052,7 +68052,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G2379" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -68078,7 +68078,7 @@
         <v>30.8799991607666</v>
       </c>
       <c r="G2380" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -68104,7 +68104,7 @@
         <v>30.1399993896484</v>
       </c>
       <c r="G2381" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -68130,7 +68130,7 @@
         <v>29.8400001525879</v>
       </c>
       <c r="G2382" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -68182,7 +68182,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G2384" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -68208,7 +68208,7 @@
         <v>29.0200004577637</v>
       </c>
       <c r="G2385" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -68234,7 +68234,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G2386" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -68260,7 +68260,7 @@
         <v>28.3799991607666</v>
       </c>
       <c r="G2387" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -68286,7 +68286,7 @@
         <v>27.9799995422363</v>
       </c>
       <c r="G2388" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -68312,7 +68312,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -68338,7 +68338,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G2390" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -68364,7 +68364,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G2391" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -68390,7 +68390,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G2392" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -68416,7 +68416,7 @@
         <v>28.8199996948242</v>
       </c>
       <c r="G2393" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -68442,7 +68442,7 @@
         <v>28.4400005340576</v>
       </c>
       <c r="G2394" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68468,7 +68468,7 @@
         <v>28.3400001525879</v>
       </c>
       <c r="G2395" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68494,7 +68494,7 @@
         <v>28.2800006866455</v>
       </c>
       <c r="G2396" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68520,7 +68520,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G2397" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68546,7 +68546,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G2398" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68572,7 +68572,7 @@
         <v>28.4200000762939</v>
       </c>
       <c r="G2399" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68598,7 +68598,7 @@
         <v>28.5599994659424</v>
       </c>
       <c r="G2400" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68624,7 +68624,7 @@
         <v>28.5799999237061</v>
       </c>
       <c r="G2401" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68650,7 +68650,7 @@
         <v>28.0599994659424</v>
       </c>
       <c r="G2402" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68676,7 +68676,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G2403" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68702,7 +68702,7 @@
         <v>27.9400005340576</v>
       </c>
       <c r="G2404" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68728,7 +68728,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G2405" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68754,7 +68754,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G2406" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68780,7 +68780,7 @@
         <v>27.0400009155273</v>
       </c>
       <c r="G2407" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68806,7 +68806,7 @@
         <v>27.1599998474121</v>
       </c>
       <c r="G2408" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68832,7 +68832,7 @@
         <v>27.1200008392334</v>
       </c>
       <c r="G2409" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68858,7 +68858,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G2410" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68884,7 +68884,7 @@
         <v>27.5400009155273</v>
       </c>
       <c r="G2411" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -68910,7 +68910,7 @@
         <v>27.9799995422363</v>
       </c>
       <c r="G2412" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -68936,7 +68936,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G2413" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -68962,7 +68962,7 @@
         <v>28.5</v>
       </c>
       <c r="G2414" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -68988,7 +68988,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G2415" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -69014,7 +69014,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G2416" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -69040,7 +69040,7 @@
         <v>29.0400009155273</v>
       </c>
       <c r="G2417" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -69066,7 +69066,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G2418" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -69092,7 +69092,7 @@
         <v>29.2800006866455</v>
       </c>
       <c r="G2419" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -69118,7 +69118,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G2420" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -69144,7 +69144,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G2421" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -69170,7 +69170,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G2422" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -69196,7 +69196,7 @@
         <v>29.8199996948242</v>
       </c>
       <c r="G2423" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -69222,7 +69222,7 @@
         <v>29.3400001525879</v>
       </c>
       <c r="G2424" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -69248,7 +69248,7 @@
         <v>29.7800006866455</v>
       </c>
       <c r="G2425" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -69274,7 +69274,7 @@
         <v>29.5599994659424</v>
       </c>
       <c r="G2426" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -69300,7 +69300,7 @@
         <v>29.7199993133545</v>
       </c>
       <c r="G2427" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -69326,7 +69326,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G2428" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -69352,7 +69352,7 @@
         <v>29.2199993133545</v>
       </c>
       <c r="G2429" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -69378,7 +69378,7 @@
         <v>28.4799995422363</v>
       </c>
       <c r="G2430" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -69404,7 +69404,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G2431" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -69430,7 +69430,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G2432" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -69456,7 +69456,7 @@
         <v>28.6599998474121</v>
       </c>
       <c r="G2433" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -69482,7 +69482,7 @@
         <v>28.9599990844727</v>
       </c>
       <c r="G2434" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69508,7 +69508,7 @@
         <v>28.8400001525879</v>
       </c>
       <c r="G2435" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69534,7 +69534,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G2436" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69560,7 +69560,7 @@
         <v>28.8600006103516</v>
       </c>
       <c r="G2437" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69586,7 +69586,7 @@
         <v>28.3799991607666</v>
       </c>
       <c r="G2438" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69612,7 +69612,7 @@
         <v>29</v>
       </c>
       <c r="G2439" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69638,7 +69638,7 @@
         <v>29.2600002288818</v>
       </c>
       <c r="G2440" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69664,7 +69664,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G2441" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69690,7 +69690,7 @@
         <v>29.8400001525879</v>
       </c>
       <c r="G2442" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69716,7 +69716,7 @@
         <v>29.9200000762939</v>
       </c>
       <c r="G2443" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69742,7 +69742,7 @@
         <v>29.3600006103516</v>
       </c>
       <c r="G2444" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69768,7 +69768,7 @@
         <v>29.3600006103516</v>
       </c>
       <c r="G2445" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69794,7 +69794,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G2446" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -69820,7 +69820,7 @@
         <v>29.5</v>
       </c>
       <c r="G2447" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -69846,7 +69846,7 @@
         <v>29.7199993133545</v>
       </c>
       <c r="G2448" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -69872,7 +69872,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G2449" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -69898,7 +69898,7 @@
         <v>29.8600006103516</v>
       </c>
       <c r="G2450" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -69924,7 +69924,7 @@
         <v>30.2600002288818</v>
       </c>
       <c r="G2451" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -69950,7 +69950,7 @@
         <v>30.4799995422363</v>
       </c>
       <c r="G2452" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -69976,7 +69976,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G2453" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -70002,7 +70002,7 @@
         <v>30.4200000762939</v>
       </c>
       <c r="G2454" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -70028,7 +70028,7 @@
         <v>30.2600002288818</v>
       </c>
       <c r="G2455" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -70054,7 +70054,7 @@
         <v>30.4400005340576</v>
       </c>
       <c r="G2456" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -70080,7 +70080,7 @@
         <v>29.9400005340576</v>
       </c>
       <c r="G2457" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -70106,7 +70106,7 @@
         <v>30.2399997711182</v>
       </c>
       <c r="G2458" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -70132,7 +70132,7 @@
         <v>29.7800006866455</v>
       </c>
       <c r="G2459" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -70158,7 +70158,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G2460" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -70184,7 +70184,7 @@
         <v>29.2600002288818</v>
       </c>
       <c r="G2461" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -70210,7 +70210,7 @@
         <v>29.5400009155273</v>
       </c>
       <c r="G2462" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -70236,7 +70236,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G2463" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -70262,7 +70262,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G2464" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -70288,7 +70288,7 @@
         <v>29.3199996948242</v>
       </c>
       <c r="G2465" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -70314,7 +70314,7 @@
         <v>30.5400009155273</v>
       </c>
       <c r="G2466" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -70340,7 +70340,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G2467" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -70366,7 +70366,7 @@
         <v>30.6200008392334</v>
       </c>
       <c r="G2468" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -70392,7 +70392,7 @@
         <v>30.7600002288818</v>
       </c>
       <c r="G2469" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -70418,7 +70418,7 @@
         <v>30.2600002288818</v>
       </c>
       <c r="G2470" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -70444,7 +70444,7 @@
         <v>30.8199996948242</v>
       </c>
       <c r="G2471" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -70470,7 +70470,7 @@
         <v>30.9400005340576</v>
       </c>
       <c r="G2472" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70496,7 +70496,7 @@
         <v>30.2199993133545</v>
       </c>
       <c r="G2473" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -70522,7 +70522,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G2474" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -70548,7 +70548,7 @@
         <v>30.3199996948242</v>
       </c>
       <c r="G2475" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -70574,7 +70574,7 @@
         <v>29.7399997711182</v>
       </c>
       <c r="G2476" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -70600,7 +70600,7 @@
         <v>30.2199993133545</v>
       </c>
       <c r="G2477" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -70626,7 +70626,7 @@
         <v>30.5799999237061</v>
       </c>
       <c r="G2478" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -70652,7 +70652,7 @@
         <v>30.7800006866455</v>
       </c>
       <c r="G2479" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -70678,7 +70678,7 @@
         <v>31.3199996948242</v>
       </c>
       <c r="G2480" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -70704,7 +70704,7 @@
         <v>31.9400005340576</v>
       </c>
       <c r="G2481" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -70730,7 +70730,7 @@
         <v>32.4799995422363</v>
       </c>
       <c r="G2482" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -70756,7 +70756,7 @@
         <v>31.1599998474121</v>
       </c>
       <c r="G2483" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -70782,7 +70782,7 @@
         <v>31.0200004577637</v>
       </c>
       <c r="G2484" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -70808,7 +70808,7 @@
         <v>31.0599994659424</v>
       </c>
       <c r="G2485" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -70834,7 +70834,7 @@
         <v>30.4400005340576</v>
       </c>
       <c r="G2486" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -70860,7 +70860,7 @@
         <v>29</v>
       </c>
       <c r="G2487" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -70886,7 +70886,7 @@
         <v>29.1599998474121</v>
       </c>
       <c r="G2488" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -70912,7 +70912,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G2489" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -70938,7 +70938,7 @@
         <v>28.0599994659424</v>
       </c>
       <c r="G2490" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -70964,7 +70964,7 @@
         <v>29.2800006866455</v>
       </c>
       <c r="G2491" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -70990,7 +70990,7 @@
         <v>30.4799995422363</v>
       </c>
       <c r="G2492" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -71016,7 +71016,7 @@
         <v>30.4799995422363</v>
       </c>
       <c r="G2493" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -71042,7 +71042,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G2494" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -71068,7 +71068,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G2495" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -71094,7 +71094,7 @@
         <v>30.9799995422363</v>
       </c>
       <c r="G2496" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -71120,7 +71120,7 @@
         <v>30.8799991607666</v>
       </c>
       <c r="G2497" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -71146,7 +71146,7 @@
         <v>31.0400009155273</v>
       </c>
       <c r="G2498" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -71172,7 +71172,7 @@
         <v>31.5</v>
       </c>
       <c r="G2499" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -71180,7 +71180,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6912037037</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>92824</v>
@@ -71198,9 +71198,35 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G2500" t="s">
+        <v>1950</v>
+      </c>
+      <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.6910185185</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>101801</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>31.6800003051758</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>31.3199996948242</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>31.4799995422363</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>31.6800003051758</v>
+      </c>
+      <c r="G2501" t="s">
         <v>1951</v>
       </c>
-      <c r="H2500" t="s">
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DLG.MI.xlsx
+++ b/data/DLG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="1952">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1954" uniqueCount="1954">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7391452789307</t>
+    <t xml:space="preserve">20.739143371582</t>
   </si>
   <si>
     <t xml:space="preserve">DLG.MI</t>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">20.5564212799072</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6553974151611</t>
+    <t xml:space="preserve">20.6553955078125</t>
   </si>
   <si>
     <t xml:space="preserve">20.175745010376</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9777965545654</t>
+    <t xml:space="preserve">19.9777946472168</t>
   </si>
   <si>
     <t xml:space="preserve">19.7722320556641</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4905338287354</t>
+    <t xml:space="preserve">19.4905300140381</t>
   </si>
   <si>
     <t xml:space="preserve">19.8864345550537</t>
@@ -71,199 +71,199 @@
     <t xml:space="preserve">17.6328411102295</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4348926544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5262508392334</t>
+    <t xml:space="preserve">17.4348888397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.526252746582</t>
   </si>
   <si>
     <t xml:space="preserve">17.0542144775391</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8943347930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0135154724121</t>
+    <t xml:space="preserve">16.8943309783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0135173797607</t>
   </si>
   <si>
     <t xml:space="preserve">16.6354732513428</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4451389312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7116088867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8029670715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6735420227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1329822540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9654855728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6533298492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9909601211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7777824401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3335666656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.412335395813</t>
+    <t xml:space="preserve">16.4451370239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7116107940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8029708862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6735401153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1329860687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9654865264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6533346176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9909582138062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7777853012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3335657119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4123373031616</t>
   </si>
   <si>
     <t xml:space="preserve">14.7397155761719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4553804397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2574319839478</t>
+    <t xml:space="preserve">15.4553842544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2574338912964</t>
   </si>
   <si>
     <t xml:space="preserve">15.4097032546997</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7523107528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3868598937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9121932983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9578704833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5848093032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1253700256348</t>
+    <t xml:space="preserve">15.7523078918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3868579864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9121942520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9578723907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.584813117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1253719329834</t>
   </si>
   <si>
     <t xml:space="preserve">16.1938934326172</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5593395233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7496776580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8817386627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2193660736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792486190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0873031616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7142429351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2878856658936</t>
+    <t xml:space="preserve">16.5593376159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7496738433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8817405700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2193651199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792476654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0873012542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7142400741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2878847122192</t>
   </si>
   <si>
     <t xml:space="preserve">15.8969650268555</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3183393478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6076545715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9274196624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9883260726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8893537521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6152658462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.356409072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1356172561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.226975440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3487939834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0442543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2345914840698</t>
+    <t xml:space="preserve">15.3183431625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6076488494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9274168014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9883279800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8893547058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6152648925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3564100265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1356143951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2269773483276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3487949371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0442523956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2345905303955</t>
   </si>
   <si>
     <t xml:space="preserve">15.0594816207886</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1432304382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5493774414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7853956222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8234663009644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7831659317017</t>
+    <t xml:space="preserve">15.1432294845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5493803024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7853975296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8234643936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7831630706787</t>
   </si>
   <si>
     <t xml:space="preserve">14.977988243103</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1572256088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.149432182312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.96240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.985782623291</t>
+    <t xml:space="preserve">15.1572246551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1494312286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9624032974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9857835769653</t>
   </si>
   <si>
     <t xml:space="preserve">14.954610824585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8533020019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4689426422119</t>
+    <t xml:space="preserve">14.8533010482788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4689435958862</t>
   </si>
   <si>
     <t xml:space="preserve">15.6715574264526</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2170639038086</t>
+    <t xml:space="preserve">16.21706199646</t>
   </si>
   <si>
     <t xml:space="preserve">15.7572793960571</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">16.0300331115723</t>
   </si>
   <si>
-    <t xml:space="preserve">16.240442276001</t>
+    <t xml:space="preserve">16.2404403686523</t>
   </si>
   <si>
     <t xml:space="preserve">16.1469268798828</t>
@@ -284,52 +284,52 @@
     <t xml:space="preserve">16.5054016113281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3105754852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7288856506348</t>
+    <t xml:space="preserve">16.3105773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7288875579834</t>
   </si>
   <si>
     <t xml:space="preserve">16.7937393188477</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0742816925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7625675201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7547760009766</t>
+    <t xml:space="preserve">17.0742835998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.762565612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7547740936279</t>
   </si>
   <si>
     <t xml:space="preserve">16.8482894897461</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1132469177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3002815246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7678508758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9081249237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9470901489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0639839172363</t>
+    <t xml:space="preserve">17.1132507324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3002796173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7678546905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9081287384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9470920562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.063985824585</t>
   </si>
   <si>
     <t xml:space="preserve">18.4848003387451</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7887268066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4614238739014</t>
+    <t xml:space="preserve">18.788724899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4614219665527</t>
   </si>
   <si>
     <t xml:space="preserve">18.3367385864258</t>
@@ -338,58 +338,58 @@
     <t xml:space="preserve">18.274393081665</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0795707702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6484546661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8276863098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4536323547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8379898071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3937931060791</t>
+    <t xml:space="preserve">18.079568862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6484527587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8276920318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4536285400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8379878997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3937911987305</t>
   </si>
   <si>
     <t xml:space="preserve">17.2535190582275</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0820770263672</t>
+    <t xml:space="preserve">17.0820789337158</t>
   </si>
   <si>
     <t xml:space="preserve">17.4951019287109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9237098693848</t>
+    <t xml:space="preserve">17.9237117767334</t>
   </si>
   <si>
     <t xml:space="preserve">17.8224048614502</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7834396362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9315071105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6768455505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5234928131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1157531738281</t>
+    <t xml:space="preserve">17.7834377288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9315013885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6768436431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.523494720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1157550811768</t>
   </si>
   <si>
     <t xml:space="preserve">16.3651275634766</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6612567901611</t>
+    <t xml:space="preserve">16.6612548828125</t>
   </si>
   <si>
     <t xml:space="preserve">16.6300888061523</t>
@@ -398,82 +398,82 @@
     <t xml:space="preserve">15.8975515365601</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7806587219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5468711853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7884521484375</t>
+    <t xml:space="preserve">15.7806596755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5468721389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7884531021118</t>
   </si>
   <si>
     <t xml:space="preserve">16.3729209899902</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1858921051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1625099182129</t>
+    <t xml:space="preserve">16.1858901977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1625137329102</t>
   </si>
   <si>
     <t xml:space="preserve">16.419677734375</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5209884643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5287780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8404960632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9184265136719</t>
+    <t xml:space="preserve">16.5209865570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5287818908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8404979705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9184226989746</t>
   </si>
   <si>
     <t xml:space="preserve">16.8716678619385</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8015308380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6119918823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2223510742188</t>
+    <t xml:space="preserve">16.8015289306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6119956970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2223491668701</t>
   </si>
   <si>
     <t xml:space="preserve">17.5964088439941</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4171695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6587524414062</t>
+    <t xml:space="preserve">17.4171733856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6587543487549</t>
   </si>
   <si>
     <t xml:space="preserve">17.3158626556396</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3236560821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5028953552246</t>
+    <t xml:space="preserve">17.3236598968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.502893447876</t>
   </si>
   <si>
     <t xml:space="preserve">18.0561923980713</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5393543243408</t>
+    <t xml:space="preserve">18.5393524169922</t>
   </si>
   <si>
     <t xml:space="preserve">18.7030029296875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6640377044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.812105178833</t>
+    <t xml:space="preserve">18.664041519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8121070861816</t>
   </si>
   <si>
     <t xml:space="preserve">18.0951557159424</t>
@@ -485,49 +485,49 @@
     <t xml:space="preserve">17.9003353118896</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1575012207031</t>
+    <t xml:space="preserve">18.1574993133545</t>
   </si>
   <si>
     <t xml:space="preserve">17.8769550323486</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6665458679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9704704284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0328121185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.510684967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5730285644531</t>
+    <t xml:space="preserve">17.6665477752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9704666137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0328140258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5106887817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5730323791504</t>
   </si>
   <si>
     <t xml:space="preserve">17.3626232147217</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4015846252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2379379272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4093818664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1444225311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.81711769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6145000457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6846370697021</t>
+    <t xml:space="preserve">17.4015865325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2379341125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4093780517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1444187164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8171157836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.614501953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6846389770508</t>
   </si>
   <si>
     <t xml:space="preserve">17.0197334289551</t>
@@ -536,52 +536,52 @@
     <t xml:space="preserve">17.128833770752</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2691040039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9963550567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4405536651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4639301300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8327045440674</t>
+    <t xml:space="preserve">17.2691078186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9963531494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4405517578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4639282226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8327026367188</t>
   </si>
   <si>
     <t xml:space="preserve">16.8249111175537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9028396606445</t>
+    <t xml:space="preserve">16.9028377532959</t>
   </si>
   <si>
     <t xml:space="preserve">16.7859477996826</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7469825744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2769012451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2457275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0509014129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0976638793945</t>
+    <t xml:space="preserve">16.7469844818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2768993377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2457256317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0509052276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0976619720459</t>
   </si>
   <si>
     <t xml:space="preserve">16.957389831543</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2301425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2067623138428</t>
+    <t xml:space="preserve">17.2301406860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2067642211914</t>
   </si>
   <si>
     <t xml:space="preserve">17.4327583312988</t>
@@ -590,34 +590,34 @@
     <t xml:space="preserve">17.2846946716309</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0664920806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9521017074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9832744598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2560272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3339538574219</t>
+    <t xml:space="preserve">17.0664882659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9521045684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9832725524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2560291290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3339557647705</t>
   </si>
   <si>
     <t xml:space="preserve">15.9988632202148</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4065990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.313084602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1182622909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5131931304932</t>
+    <t xml:space="preserve">15.4065999984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3130855560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1182594299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5131950378418</t>
   </si>
   <si>
     <t xml:space="preserve">16.0923767089844</t>
@@ -626,37 +626,37 @@
     <t xml:space="preserve">15.913140296936</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1780967712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7158088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0586967468262</t>
+    <t xml:space="preserve">16.1781024932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7158126831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0586948394775</t>
   </si>
   <si>
     <t xml:space="preserve">16.4664344787598</t>
   </si>
   <si>
-    <t xml:space="preserve">16.224853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9754838943481</t>
+    <t xml:space="preserve">16.2248554229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9754800796509</t>
   </si>
   <si>
     <t xml:space="preserve">16.7080173492432</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4976062774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6924304962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5599536895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.770357131958</t>
+    <t xml:space="preserve">16.4976100921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6924285888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5599517822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7703590393066</t>
   </si>
   <si>
     <t xml:space="preserve">16.8638763427734</t>
@@ -665,28 +665,28 @@
     <t xml:space="preserve">17.0275268554688</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4561347961426</t>
+    <t xml:space="preserve">17.4561367034912</t>
   </si>
   <si>
     <t xml:space="preserve">17.4483413696289</t>
   </si>
   <si>
-    <t xml:space="preserve">17.884744644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1185359954834</t>
+    <t xml:space="preserve">17.8847465515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1185321807861</t>
   </si>
   <si>
     <t xml:space="preserve">18.2354278564453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0172309875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8457832336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9626770019531</t>
+    <t xml:space="preserve">18.0172290802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8457813262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9626750946045</t>
   </si>
   <si>
     <t xml:space="preserve">17.869161605835</t>
@@ -695,40 +695,40 @@
     <t xml:space="preserve">17.6353721618652</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7912311553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5808258056641</t>
+    <t xml:space="preserve">17.7912330627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5808238983154</t>
   </si>
   <si>
     <t xml:space="preserve">17.6509590148926</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1107406616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9782600402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3133602142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2042541503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.469217300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0848598480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.349817276001</t>
+    <t xml:space="preserve">18.1107425689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9782619476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3133583068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2042560577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4692153930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0848579406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3498153686523</t>
   </si>
   <si>
     <t xml:space="preserve">19.2952632904053</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4667091369629</t>
+    <t xml:space="preserve">19.4667110443115</t>
   </si>
   <si>
     <t xml:space="preserve">19.2485084533691</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">19.3186435699463</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0614776611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4199523925781</t>
+    <t xml:space="preserve">19.0614814758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4199542999268</t>
   </si>
   <si>
     <t xml:space="preserve">19.2407150268555</t>
@@ -749,67 +749,67 @@
     <t xml:space="preserve">19.0926475524902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4511260986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8588638305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6406574249268</t>
+    <t xml:space="preserve">19.4511222839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8588600158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6406593322754</t>
   </si>
   <si>
     <t xml:space="preserve">18.9056205749512</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2329235076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4978809356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1914482116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9888381958008</t>
+    <t xml:space="preserve">19.2329216003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4978828430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1914520263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9888362884521</t>
   </si>
   <si>
     <t xml:space="preserve">20.1213130950928</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9732475280762</t>
+    <t xml:space="preserve">19.9732494354248</t>
   </si>
   <si>
     <t xml:space="preserve">20.9551563262939</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6278514862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2201156616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0408782958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7915077209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7447490692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8616466522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2434940338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9006042480469</t>
+    <t xml:space="preserve">20.6278533935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2201175689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0408802032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7915096282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7447471618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.861644744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2434978485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9006080627441</t>
   </si>
   <si>
     <t xml:space="preserve">21.0330867767334</t>
   </si>
   <si>
-    <t xml:space="preserve">20.978536605835</t>
+    <t xml:space="preserve">20.9785346984863</t>
   </si>
   <si>
     <t xml:space="preserve">21.6721038818359</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">21.4149379730225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3136291503906</t>
+    <t xml:space="preserve">21.3136329650879</t>
   </si>
   <si>
     <t xml:space="preserve">21.1967372894287</t>
@@ -827,151 +827,151 @@
     <t xml:space="preserve">21.4227313995361</t>
   </si>
   <si>
-    <t xml:space="preserve">21.578592300415</t>
+    <t xml:space="preserve">21.5785903930664</t>
   </si>
   <si>
     <t xml:space="preserve">22.1884727478027</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1002025604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9477291107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0279769897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9878540039062</t>
+    <t xml:space="preserve">22.1002044677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.947732925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0279808044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9878520965576</t>
   </si>
   <si>
     <t xml:space="preserve">21.8273601531982</t>
   </si>
   <si>
-    <t xml:space="preserve">22.348970413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4693412780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8946514129639</t>
+    <t xml:space="preserve">22.3489685058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4693374633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8946533203125</t>
   </si>
   <si>
     <t xml:space="preserve">23.3199634552002</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2878665924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8786029815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0310726165771</t>
+    <t xml:space="preserve">23.2878646850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.878604888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0310745239258</t>
   </si>
   <si>
     <t xml:space="preserve">23.4483604431152</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0230464935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9026737213135</t>
+    <t xml:space="preserve">23.0230484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9026775360107</t>
   </si>
   <si>
     <t xml:space="preserve">22.6218109130859</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5014381408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.255765914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8434066772461</t>
+    <t xml:space="preserve">22.501443862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2557678222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8434104919434</t>
   </si>
   <si>
     <t xml:space="preserve">22.0600776672363</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6298389434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7341537475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9267501831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2316932678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1434173583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1674938201904</t>
+    <t xml:space="preserve">22.6298351287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7341575622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9267520904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2316951751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1434211730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1674919128418</t>
   </si>
   <si>
     <t xml:space="preserve">23.6570053100586</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7693538665771</t>
+    <t xml:space="preserve">23.7693500518799</t>
   </si>
   <si>
     <t xml:space="preserve">23.6730537414551</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8495960235596</t>
+    <t xml:space="preserve">23.8495979309082</t>
   </si>
   <si>
     <t xml:space="preserve">23.7613277435303</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4002132415771</t>
+    <t xml:space="preserve">23.4002113342285</t>
   </si>
   <si>
     <t xml:space="preserve">23.2958927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4323120117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7051544189453</t>
+    <t xml:space="preserve">23.4323139190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7051563262939</t>
   </si>
   <si>
     <t xml:space="preserve">23.0069980621338</t>
   </si>
   <si>
-    <t xml:space="preserve">22.830451965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7903289794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0631732940674</t>
+    <t xml:space="preserve">22.8304538726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7903308868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0631713867188</t>
   </si>
   <si>
     <t xml:space="preserve">23.8255252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3921871185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2637901306152</t>
+    <t xml:space="preserve">23.3921852111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2637920379639</t>
   </si>
   <si>
     <t xml:space="preserve">23.2718162536621</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1915683746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9989738464355</t>
+    <t xml:space="preserve">23.1915702819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9989757537842</t>
   </si>
   <si>
     <t xml:space="preserve">21.9076061248779</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0199546813965</t>
+    <t xml:space="preserve">22.0199527740479</t>
   </si>
   <si>
     <t xml:space="preserve">22.0761260986328</t>
@@ -980,10 +980,10 @@
     <t xml:space="preserve">21.5545177459717</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4742679595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6267395019531</t>
+    <t xml:space="preserve">21.4742660522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6267414093018</t>
   </si>
   <si>
     <t xml:space="preserve">21.7711849212646</t>
@@ -998,13 +998,13 @@
     <t xml:space="preserve">21.8594570159912</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5255146026611</t>
+    <t xml:space="preserve">22.5255126953125</t>
   </si>
   <si>
     <t xml:space="preserve">22.7421817779541</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3730411529541</t>
+    <t xml:space="preserve">22.3730430603027</t>
   </si>
   <si>
     <t xml:space="preserve">22.7181072235107</t>
@@ -1013,25 +1013,25 @@
     <t xml:space="preserve">22.8625545501709</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7100830078125</t>
+    <t xml:space="preserve">22.7100811004639</t>
   </si>
   <si>
     <t xml:space="preserve">22.5335388183594</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6539115905762</t>
+    <t xml:space="preserve">22.6539096832275</t>
   </si>
   <si>
     <t xml:space="preserve">22.292797088623</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7551364898682</t>
+    <t xml:space="preserve">21.7551345825195</t>
   </si>
   <si>
     <t xml:space="preserve">21.2415504455566</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9927825927734</t>
+    <t xml:space="preserve">20.9927864074707</t>
   </si>
   <si>
     <t xml:space="preserve">20.9446353912354</t>
@@ -1040,10 +1040,10 @@
     <t xml:space="preserve">21.0730323791504</t>
   </si>
   <si>
-    <t xml:space="preserve">21.048957824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6396942138672</t>
+    <t xml:space="preserve">21.0489559173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6396961212158</t>
   </si>
   <si>
     <t xml:space="preserve">20.4310493469238</t>
@@ -1052,19 +1052,19 @@
     <t xml:space="preserve">20.4872226715088</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8804397583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8643856048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7119178771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5754947662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5995693206787</t>
+    <t xml:space="preserve">20.8804340362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.864387512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.575496673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5995712280273</t>
   </si>
   <si>
     <t xml:space="preserve">20.6477184295654</t>
@@ -1073,109 +1073,112 @@
     <t xml:space="preserve">20.6156177520752</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5915470123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3508052825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3427772521973</t>
+    <t xml:space="preserve">20.5915431976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3508033752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3427791595459</t>
   </si>
   <si>
     <t xml:space="preserve">20.2866058349609</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7440147399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6717891693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.495246887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7359924316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2174797058105</t>
+    <t xml:space="preserve">20.7440166473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6717948913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4952487945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.735990524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2174758911133</t>
   </si>
   <si>
     <t xml:space="preserve">21.0168571472168</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3539009094238</t>
+    <t xml:space="preserve">21.3538990020752</t>
   </si>
   <si>
     <t xml:space="preserve">21.2335262298584</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9045104980469</t>
+    <t xml:space="preserve">20.9045143127441</t>
   </si>
   <si>
     <t xml:space="preserve">20.5594463348389</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5353736877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4711761474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7520408630371</t>
+    <t xml:space="preserve">20.5353717803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4711742401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7520427703857</t>
   </si>
   <si>
     <t xml:space="preserve">21.3779716491699</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0650062561035</t>
+    <t xml:space="preserve">21.0650081634521</t>
   </si>
   <si>
     <t xml:space="preserve">21.2255039215088</t>
   </si>
   <si>
-    <t xml:space="preserve">21.369945526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9156284332275</t>
+    <t xml:space="preserve">21.3699474334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9156322479248</t>
   </si>
   <si>
     <t xml:space="preserve">21.4582195281982</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8032836914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7952575683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3088455200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.140323638916</t>
+    <t xml:space="preserve">21.8032855987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7952613830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5785884857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3088417053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1403255462646</t>
   </si>
   <si>
     <t xml:space="preserve">22.2285976409912</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2045211791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1483497619629</t>
+    <t xml:space="preserve">22.2045230865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1483516693115</t>
   </si>
   <si>
     <t xml:space="preserve">22.694034576416</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0921745300293</t>
+    <t xml:space="preserve">22.0921764373779</t>
   </si>
   <si>
     <t xml:space="preserve">22.1082229614258</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1644020080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7742824554443</t>
+    <t xml:space="preserve">22.1643981933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7742805480957</t>
   </si>
   <si>
     <t xml:space="preserve">22.7662582397461</t>
@@ -1187,25 +1190,25 @@
     <t xml:space="preserve">22.5415630340576</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4131660461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5174884796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1563739776611</t>
+    <t xml:space="preserve">22.4131641387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5174865722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1563758850098</t>
   </si>
   <si>
     <t xml:space="preserve">21.8353843688965</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5495853424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2526683807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2125492095947</t>
+    <t xml:space="preserve">22.5495891571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2526721954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2125453948975</t>
   </si>
   <si>
     <t xml:space="preserve">19.2594337463379</t>
@@ -1214,25 +1217,25 @@
     <t xml:space="preserve">19.9335155487061</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8612899780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6927700042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6205520629883</t>
+    <t xml:space="preserve">19.861291885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6927719116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.620548248291</t>
   </si>
   <si>
     <t xml:space="preserve">19.5403003692627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.492151260376</t>
+    <t xml:space="preserve">19.4921550750732</t>
   </si>
   <si>
     <t xml:space="preserve">19.4279518127441</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7409172058105</t>
+    <t xml:space="preserve">19.7409210205078</t>
   </si>
   <si>
     <t xml:space="preserve">19.676721572876</t>
@@ -1241,10 +1244,10 @@
     <t xml:space="preserve">19.805118560791</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4199314117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7569713592529</t>
+    <t xml:space="preserve">19.4199275970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7569694519043</t>
   </si>
   <si>
     <t xml:space="preserve">19.6606712341309</t>
@@ -1253,22 +1256,22 @@
     <t xml:space="preserve">20.1421604156494</t>
   </si>
   <si>
-    <t xml:space="preserve">20.230432510376</t>
+    <t xml:space="preserve">20.2304306030273</t>
   </si>
   <si>
     <t xml:space="preserve">20.4069766998291</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4791984558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2545051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9415416717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0619125366211</t>
+    <t xml:space="preserve">20.4792003631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2545032501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9415397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0619106292725</t>
   </si>
   <si>
     <t xml:space="preserve">19.9254894256592</t>
@@ -1277,7 +1280,7 @@
     <t xml:space="preserve">20.9366092681885</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0971050262451</t>
+    <t xml:space="preserve">21.0971069335938</t>
   </si>
   <si>
     <t xml:space="preserve">20.8162384033203</t>
@@ -1286,19 +1289,19 @@
     <t xml:space="preserve">20.3989524841309</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6878414154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4390735626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2464790344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4631500244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5433979034424</t>
+    <t xml:space="preserve">20.6878433227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4390754699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2464809417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4631481170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5433959960938</t>
   </si>
   <si>
     <t xml:space="preserve">21.4100723266602</t>
@@ -1310,31 +1313,31 @@
     <t xml:space="preserve">21.6508121490479</t>
   </si>
   <si>
-    <t xml:space="preserve">21.137228012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2816772460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5063667297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4421672821045</t>
+    <t xml:space="preserve">21.1372299194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2816753387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.506368637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4421730041504</t>
   </si>
   <si>
     <t xml:space="preserve">20.9606857299805</t>
   </si>
   <si>
-    <t xml:space="preserve">21.345874786377</t>
+    <t xml:space="preserve">21.3458728790283</t>
   </si>
   <si>
     <t xml:space="preserve">21.0890789031982</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6989612579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8113098144531</t>
+    <t xml:space="preserve">21.6989631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8113079071045</t>
   </si>
   <si>
     <t xml:space="preserve">21.7792091369629</t>
@@ -1346,7 +1349,7 @@
     <t xml:space="preserve">21.7471103668213</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2495746612549</t>
+    <t xml:space="preserve">21.2495765686035</t>
   </si>
   <si>
     <t xml:space="preserve">19.5322780609131</t>
@@ -1355,7 +1358,7 @@
     <t xml:space="preserve">19.3236312866211</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5001754760742</t>
+    <t xml:space="preserve">19.5001773834229</t>
   </si>
   <si>
     <t xml:space="preserve">19.5162258148193</t>
@@ -1364,19 +1367,19 @@
     <t xml:space="preserve">20.0458602905273</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0940113067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7248687744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7088203430176</t>
+    <t xml:space="preserve">20.0940132141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7248706817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7088222503662</t>
   </si>
   <si>
     <t xml:space="preserve">19.403881072998</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4841270446777</t>
+    <t xml:space="preserve">19.4841289520264</t>
   </si>
   <si>
     <t xml:space="preserve">19.1631355285645</t>
@@ -1385,46 +1388,46 @@
     <t xml:space="preserve">18.8260955810547</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6014022827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0075740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.585355758667</t>
+    <t xml:space="preserve">18.6014041900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0075721740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5853519439697</t>
   </si>
   <si>
     <t xml:space="preserve">18.7137508392334</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9977130889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1261119842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7199420928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1903038024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7730197906494</t>
+    <t xml:space="preserve">19.9977149963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1261081695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7199401855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1903057098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7730178833008</t>
   </si>
   <si>
     <t xml:space="preserve">19.8372173309326</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8211688995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4359817504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1310386657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3557319641113</t>
+    <t xml:space="preserve">19.8211708068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4359798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1310405731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3557300567627</t>
   </si>
   <si>
     <t xml:space="preserve">19.5483264923096</t>
@@ -1433,7 +1436,7 @@
     <t xml:space="preserve">19.9174633026123</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5804214477539</t>
+    <t xml:space="preserve">19.5804252624512</t>
   </si>
   <si>
     <t xml:space="preserve">19.0186901092529</t>
@@ -1448,22 +1451,22 @@
     <t xml:space="preserve">19.0828876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8853664398193</t>
+    <t xml:space="preserve">19.8853645324707</t>
   </si>
   <si>
     <t xml:space="preserve">20.5112953186035</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1582069396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8936672210693</t>
+    <t xml:space="preserve">20.1582050323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8936653137207</t>
   </si>
   <si>
     <t xml:space="preserve">20.6596565246582</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5760841369629</t>
+    <t xml:space="preserve">20.5760822296143</t>
   </si>
   <si>
     <t xml:space="preserve">20.6763706207275</t>
@@ -1472,22 +1475,22 @@
     <t xml:space="preserve">20.7265148162842</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8435211181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8268051147461</t>
+    <t xml:space="preserve">20.8435192108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8268070220947</t>
   </si>
   <si>
     <t xml:space="preserve">21.4954032897949</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1276760101318</t>
+    <t xml:space="preserve">21.1276741027832</t>
   </si>
   <si>
     <t xml:space="preserve">21.2781085968018</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1778163909912</t>
+    <t xml:space="preserve">21.1778182983398</t>
   </si>
   <si>
     <t xml:space="preserve">21.0942440032959</t>
@@ -1496,7 +1499,7 @@
     <t xml:space="preserve">20.9772415161133</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7766628265381</t>
+    <t xml:space="preserve">20.7766609191895</t>
   </si>
   <si>
     <t xml:space="preserve">20.4757900238037</t>
@@ -1505,28 +1508,25 @@
     <t xml:space="preserve">20.6429424285889</t>
   </si>
   <si>
-    <t xml:space="preserve">20.525936126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2584991455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.12477684021</t>
+    <t xml:space="preserve">20.5259380340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2584972381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1247787475586</t>
   </si>
   <si>
     <t xml:space="preserve">20.1916389465332</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9242000579834</t>
+    <t xml:space="preserve">19.924201965332</t>
   </si>
   <si>
     <t xml:space="preserve">19.5063247680664</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1582088470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2417850494385</t>
+    <t xml:space="preserve">20.2417831420898</t>
   </si>
   <si>
     <t xml:space="preserve">20.8769493103027</t>
@@ -1538,10 +1538,10 @@
     <t xml:space="preserve">20.993953704834</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8100910186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5927963256836</t>
+    <t xml:space="preserve">20.8100929260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.592794418335</t>
   </si>
   <si>
     <t xml:space="preserve">20.6930847167969</t>
@@ -1553,19 +1553,19 @@
     <t xml:space="preserve">20.4925060272217</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5593643188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7570476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8740520477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1414947509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2919273376465</t>
+    <t xml:space="preserve">20.5593662261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7570495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8740558624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1414928436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2919292449951</t>
   </si>
   <si>
     <t xml:space="preserve">20.0244884490967</t>
@@ -1574,13 +1574,13 @@
     <t xml:space="preserve">19.94091796875</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1080646514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2752132415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3922138214111</t>
+    <t xml:space="preserve">20.108060836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2752113342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3922157287598</t>
   </si>
   <si>
     <t xml:space="preserve">20.057918548584</t>
@@ -1589,10 +1589,10 @@
     <t xml:space="preserve">20.4256458282471</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0746326446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8239078521729</t>
+    <t xml:space="preserve">20.074634552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8239116668701</t>
   </si>
   <si>
     <t xml:space="preserve">19.6901893615723</t>
@@ -1601,31 +1601,31 @@
     <t xml:space="preserve">21.0273818969727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2475757598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.314432144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1000366210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.200325012207</t>
+    <t xml:space="preserve">22.2475738525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3144378662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1000347137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2003269195557</t>
   </si>
   <si>
     <t xml:space="preserve">23.2671852111816</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5847663879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5346221923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2170429229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8660259246826</t>
+    <t xml:space="preserve">23.5847682952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5346240997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.217041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8660278320312</t>
   </si>
   <si>
     <t xml:space="preserve">22.7991676330566</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">22.8325977325439</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5484409332275</t>
+    <t xml:space="preserve">22.5484447479248</t>
   </si>
   <si>
     <t xml:space="preserve">22.6153030395508</t>
@@ -1643,22 +1643,22 @@
     <t xml:space="preserve">22.9328880310059</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1167526245117</t>
+    <t xml:space="preserve">23.1167488098145</t>
   </si>
   <si>
     <t xml:space="preserve">23.1501808166504</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2504692077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4009056091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6181983947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5011920928955</t>
+    <t xml:space="preserve">23.250467300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4009017944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.618200302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5011940002441</t>
   </si>
   <si>
     <t xml:space="preserve">23.3841896057129</t>
@@ -1667,88 +1667,88 @@
     <t xml:space="preserve">23.2839012145996</t>
   </si>
   <si>
-    <t xml:space="preserve">23.083324432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8994560241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5651569366455</t>
+    <t xml:space="preserve">23.0833206176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8994579315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5651588439941</t>
   </si>
   <si>
     <t xml:space="preserve">22.5818729400635</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3311462402344</t>
+    <t xml:space="preserve">22.3311519622803</t>
   </si>
   <si>
     <t xml:space="preserve">22.815881729126</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5317287445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1334686279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9663181304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.68505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3006134033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4343338012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9997444152832</t>
+    <t xml:space="preserve">22.5317268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1334648132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9663143157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6850566864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3006153106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4343376159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9997463226318</t>
   </si>
   <si>
     <t xml:space="preserve">22.8493118286133</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9495983123779</t>
+    <t xml:space="preserve">22.9496021270752</t>
   </si>
   <si>
     <t xml:space="preserve">21.7628421783447</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4619731903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0440998077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7098007202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9103813171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6625518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2279644012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4285411834717</t>
+    <t xml:space="preserve">21.461971282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0440979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7098026275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.91037940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6625499725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2279624938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4285430908203</t>
   </si>
   <si>
     <t xml:space="preserve">20.9270973205566</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3616809844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5121173858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9605274200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8573398590088</t>
+    <t xml:space="preserve">21.3616790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5121154785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9605236053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8573379516602</t>
   </si>
   <si>
     <t xml:space="preserve">19.5397548675537</t>
@@ -1757,31 +1757,31 @@
     <t xml:space="preserve">18.9547348022461</t>
   </si>
   <si>
-    <t xml:space="preserve">19.556468963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0550231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4394645690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3893222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2556037902832</t>
+    <t xml:space="preserve">19.5564708709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0550212860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4394664764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3893203735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2556018829346</t>
   </si>
   <si>
     <t xml:space="preserve">19.3057479858398</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3726043701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8043003082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6037197113037</t>
+    <t xml:space="preserve">19.3726062774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8042984008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6037178039551</t>
   </si>
   <si>
     <t xml:space="preserve">18.6872959136963</t>
@@ -1790,46 +1790,46 @@
     <t xml:space="preserve">18.6705799102783</t>
   </si>
   <si>
-    <t xml:space="preserve">18.704008102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8878726959229</t>
+    <t xml:space="preserve">18.7040061950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8878746032715</t>
   </si>
   <si>
     <t xml:space="preserve">19.2221698760986</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6734771728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.656759262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8907680511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0913524627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8406238555908</t>
+    <t xml:space="preserve">19.6734752655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6567611694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8907699584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0913505554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8406276702881</t>
   </si>
   <si>
     <t xml:space="preserve">19.5899028778076</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0884532928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7737636566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6400451660156</t>
+    <t xml:space="preserve">19.088451385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7737655639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6400489807129</t>
   </si>
   <si>
     <t xml:space="preserve">19.4561805725098</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9213027954102</t>
+    <t xml:space="preserve">18.9213008880615</t>
   </si>
   <si>
     <t xml:space="preserve">19.3391761779785</t>
@@ -1838,46 +1838,46 @@
     <t xml:space="preserve">18.5201454162598</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5506763458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0019817352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9016914367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4700031280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2359886169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4365692138672</t>
+    <t xml:space="preserve">17.5506801605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0019836425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9016933441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4699993133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.235990524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4365711212158</t>
   </si>
   <si>
     <t xml:space="preserve">20.0412044525146</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3086414337158</t>
+    <t xml:space="preserve">20.3086433410645</t>
   </si>
   <si>
     <t xml:space="preserve">19.991060256958</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3253555297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2861366271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2694225311279</t>
+    <t xml:space="preserve">20.3253574371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2861347198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2694206237793</t>
   </si>
   <si>
     <t xml:space="preserve">18.219274520874</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4198551177979</t>
+    <t xml:space="preserve">18.4198570251465</t>
   </si>
   <si>
     <t xml:space="preserve">18.6538619995117</t>
@@ -1886,49 +1886,49 @@
     <t xml:space="preserve">18.25270652771</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3529930114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5368576049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7541561126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.637149810791</t>
+    <t xml:space="preserve">18.3529949188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5368614196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7541522979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6371479034424</t>
   </si>
   <si>
     <t xml:space="preserve">19.1553134918213</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4060344696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2723159790039</t>
+    <t xml:space="preserve">19.4060363769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2723121643066</t>
   </si>
   <si>
     <t xml:space="preserve">18.9714488983154</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3558921813965</t>
+    <t xml:space="preserve">19.3558902740479</t>
   </si>
   <si>
     <t xml:space="preserve">19.0215930938721</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3224601745605</t>
+    <t xml:space="preserve">19.3224620819092</t>
   </si>
   <si>
     <t xml:space="preserve">19.7403354644775</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1749229431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7875843048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9380187988281</t>
+    <t xml:space="preserve">20.1749248504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7875823974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9380168914795</t>
   </si>
   <si>
     <t xml:space="preserve">20.0077743530273</t>
@@ -1940,16 +1940,16 @@
     <t xml:space="preserve">21.5789775848389</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1443901062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2054557800293</t>
+    <t xml:space="preserve">21.1443881988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2054576873779</t>
   </si>
   <si>
     <t xml:space="preserve">18.0354118347168</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6509685516357</t>
+    <t xml:space="preserve">17.6509704589844</t>
   </si>
   <si>
     <t xml:space="preserve">17.4336757659912</t>
@@ -1958,49 +1958,49 @@
     <t xml:space="preserve">17.5841083526611</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1328067779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5477809906006</t>
+    <t xml:space="preserve">17.1328029632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5477828979492</t>
   </si>
   <si>
     <t xml:space="preserve">16.1716957092285</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9961891174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3221302032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8791837692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7939519882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7683801651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7769041061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3081150054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4018726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4359674453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5382480621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1632175445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.333685874939</t>
+    <t xml:space="preserve">15.9961881637573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3221321105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8791847229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7939510345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7683820724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7769031524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3081121444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4018716812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4359655380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5382490158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1632165908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3336839675903</t>
   </si>
   <si>
     <t xml:space="preserve">15.0524091720581</t>
@@ -2009,34 +2009,34 @@
     <t xml:space="preserve">15.1717376708984</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3507318496704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5552940368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6405277252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6490516662598</t>
+    <t xml:space="preserve">15.3507308959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5552930831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.640528678894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6490545272827</t>
   </si>
   <si>
     <t xml:space="preserve">15.6320056915283</t>
   </si>
   <si>
-    <t xml:space="preserve">15.580864906311</t>
+    <t xml:space="preserve">15.5808658599854</t>
   </si>
   <si>
     <t xml:space="preserve">15.4103965759277</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0609350204468</t>
+    <t xml:space="preserve">15.0609331130981</t>
   </si>
   <si>
     <t xml:space="preserve">14.8904647827148</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9842233657837</t>
+    <t xml:space="preserve">14.9842224121094</t>
   </si>
   <si>
     <t xml:space="preserve">15.0438861846924</t>
@@ -2045,202 +2045,202 @@
     <t xml:space="preserve">15.3763027191162</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4274435043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2825450897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0865058898926</t>
+    <t xml:space="preserve">15.4274425506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.282546043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0865049362183</t>
   </si>
   <si>
     <t xml:space="preserve">15.1120748519897</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1546926498413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3251600265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3592576980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9671764373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7455635070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6091918945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6518077850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.515435218811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7114734649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6347637176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5410022735596</t>
+    <t xml:space="preserve">15.1546945571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.325159072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3592557907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9671754837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.745566368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6091909408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6518106460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5154323577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7114725112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6347627639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5410032272339</t>
   </si>
   <si>
     <t xml:space="preserve">14.3534870147705</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3449640274048</t>
+    <t xml:space="preserve">14.3449630737305</t>
   </si>
   <si>
     <t xml:space="preserve">14.4472465515137</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4387226104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7540893554688</t>
+    <t xml:space="preserve">14.438720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7540912628174</t>
   </si>
   <si>
     <t xml:space="preserve">14.4642934799194</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4813404083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3620119094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2484502792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4956283569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0268383026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0012693405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6859035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5324811935425</t>
+    <t xml:space="preserve">14.4813375473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3620128631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2484474182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4956312179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0268421173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0012731552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6859016418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5324792861938</t>
   </si>
   <si>
     <t xml:space="preserve">13.9784555435181</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4046287536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0353631973267</t>
+    <t xml:space="preserve">14.4046268463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.035364151001</t>
   </si>
   <si>
     <t xml:space="preserve">15.1376447677612</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8307991027832</t>
+    <t xml:space="preserve">14.8308019638062</t>
   </si>
   <si>
     <t xml:space="preserve">14.9586515426636</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2399244308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.810996055603</t>
+    <t xml:space="preserve">15.2399253845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8109979629517</t>
   </si>
   <si>
     <t xml:space="preserve">16.4843502044678</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0468978881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7911949157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5269641876221</t>
+    <t xml:space="preserve">17.046895980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7911968231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5269680023193</t>
   </si>
   <si>
     <t xml:space="preserve">17.0128021240234</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5781097412109</t>
+    <t xml:space="preserve">16.5781078338623</t>
   </si>
   <si>
     <t xml:space="preserve">16.3138790130615</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2371711730957</t>
+    <t xml:space="preserve">16.2371692657471</t>
   </si>
   <si>
     <t xml:space="preserve">15.9303255081177</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9218015670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.393346786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9416065216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5239591598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9330835342407</t>
+    <t xml:space="preserve">15.9218053817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3933486938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9416046142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5239582061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9330816268921</t>
   </si>
   <si>
     <t xml:space="preserve">14.6603326797485</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2512044906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1318788528442</t>
+    <t xml:space="preserve">14.2512035369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1318769454956</t>
   </si>
   <si>
     <t xml:space="preserve">14.617714881897</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4557695388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.558051109314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5750999450684</t>
+    <t xml:space="preserve">14.4557676315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5580492019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5750970840454</t>
   </si>
   <si>
     <t xml:space="preserve">14.7370452880859</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7796592712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8393230438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.847846031189</t>
+    <t xml:space="preserve">14.7796602249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8393249511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8478488922119</t>
   </si>
   <si>
     <t xml:space="preserve">14.6688537597656</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2341604232788</t>
+    <t xml:space="preserve">14.2341613769531</t>
   </si>
   <si>
     <t xml:space="preserve">14.14040184021</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0636911392212</t>
+    <t xml:space="preserve">14.0636901855469</t>
   </si>
   <si>
     <t xml:space="preserve">14.8222780227661</t>
@@ -2249,103 +2249,103 @@
     <t xml:space="preserve">14.626238822937</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0183181762695</t>
+    <t xml:space="preserve">15.0183172225952</t>
   </si>
   <si>
     <t xml:space="preserve">15.1291227340698</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2058334350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5467700958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8195199966431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0326080322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4502563476562</t>
+    <t xml:space="preserve">15.2058324813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5467710494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8195219039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0326061248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4502544403076</t>
   </si>
   <si>
     <t xml:space="preserve">16.4928741455078</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0155582427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1519374847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2030773162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0411281585693</t>
+    <t xml:space="preserve">16.0155620574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1519336700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2030735015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.041130065918</t>
   </si>
   <si>
     <t xml:space="preserve">16.0752258300781</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8962316513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2883129119873</t>
+    <t xml:space="preserve">15.8962326049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2883110046387</t>
   </si>
   <si>
     <t xml:space="preserve">16.2627410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1263637542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1178398132324</t>
+    <t xml:space="preserve">16.1263656616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1178417205811</t>
   </si>
   <si>
     <t xml:space="preserve">16.1945514678955</t>
   </si>
   <si>
-    <t xml:space="preserve">16.228645324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1689796447754</t>
+    <t xml:space="preserve">16.2286472320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.168981552124</t>
   </si>
   <si>
     <t xml:space="preserve">16.0666999816895</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2797870635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1093158721924</t>
+    <t xml:space="preserve">16.2797889709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.109317779541</t>
   </si>
   <si>
     <t xml:space="preserve">15.7087163925171</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6746225357056</t>
+    <t xml:space="preserve">15.6746196746826</t>
   </si>
   <si>
     <t xml:space="preserve">15.9729433059692</t>
   </si>
   <si>
-    <t xml:space="preserve">15.74280834198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3422060012817</t>
+    <t xml:space="preserve">15.7428092956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3422069549561</t>
   </si>
   <si>
     <t xml:space="preserve">15.2910671234131</t>
   </si>
   <si>
-    <t xml:space="preserve">15.103551864624</t>
+    <t xml:space="preserve">15.1035509109497</t>
   </si>
   <si>
     <t xml:space="preserve">14.5665740966797</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2853021621704</t>
+    <t xml:space="preserve">14.2853012084961</t>
   </si>
   <si>
     <t xml:space="preserve">14.2426815032959</t>
@@ -2354,22 +2354,22 @@
     <t xml:space="preserve">13.5949020385742</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7057046890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6944236755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.506911277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0694608688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.461537361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4444894790649</t>
+    <t xml:space="preserve">13.7057065963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6944255828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5069093704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0694580078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4615364074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4444932937622</t>
   </si>
   <si>
     <t xml:space="preserve">15.4700584411621</t>
@@ -2378,43 +2378,43 @@
     <t xml:space="preserve">15.6149578094482</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2740211486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2995910644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7142305374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.381814956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5522832870483</t>
+    <t xml:space="preserve">15.2740230560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2995891571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7142295837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3818140029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.552282333374</t>
   </si>
   <si>
     <t xml:space="preserve">13.1772518157959</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2965812683105</t>
+    <t xml:space="preserve">13.2965793609619</t>
   </si>
   <si>
     <t xml:space="preserve">13.2624864578247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0323534011841</t>
+    <t xml:space="preserve">13.0323543548584</t>
   </si>
   <si>
     <t xml:space="preserve">12.7596035003662</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6232290267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3590002059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6600780487061</t>
+    <t xml:space="preserve">12.6232271194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.359001159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6600790023804</t>
   </si>
   <si>
     <t xml:space="preserve">11.1912889480591</t>
@@ -2423,76 +2423,76 @@
     <t xml:space="preserve">10.8333034515381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74230194091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6543092727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6430320739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8220252990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6686019897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0351095199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3306751251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7227544784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2767782211304</t>
+    <t xml:space="preserve">9.74230098724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6543111801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.643030166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8220243453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6686000823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0351085662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3306741714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7227535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2767772674561</t>
   </si>
   <si>
     <t xml:space="preserve">13.0749702453613</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5011425018311</t>
+    <t xml:space="preserve">13.5011434555054</t>
   </si>
   <si>
     <t xml:space="preserve">13.4500017166138</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9897356033325</t>
+    <t xml:space="preserve">12.9897375106812</t>
   </si>
   <si>
     <t xml:space="preserve">13.0834941864014</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1175889968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4953756332397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0238304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3562440872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4244337081909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6119480133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8192682266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6999378204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.904501914978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0664472579956</t>
+    <t xml:space="preserve">13.1175880432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4953765869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0238285064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3562450408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4244318008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6119470596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8192672729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6999387741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9045038223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0664463043213</t>
   </si>
   <si>
     <t xml:space="preserve">13.2113456726074</t>
@@ -2501,13 +2501,13 @@
     <t xml:space="preserve">13.3988618850708</t>
   </si>
   <si>
-    <t xml:space="preserve">13.313627243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8079862594604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8932199478149</t>
+    <t xml:space="preserve">13.3136253356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8079891204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8932218551636</t>
   </si>
   <si>
     <t xml:space="preserve">13.9358396530151</t>
@@ -2519,13 +2519,13 @@
     <t xml:space="preserve">13.8846988677979</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4898624420166</t>
+    <t xml:space="preserve">14.4898633956909</t>
   </si>
   <si>
     <t xml:space="preserve">14.7029485702515</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2000646591187</t>
+    <t xml:space="preserve">14.2000665664673</t>
   </si>
   <si>
     <t xml:space="preserve">14.4983863830566</t>
@@ -2534,25 +2534,25 @@
     <t xml:space="preserve">14.4131517410278</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1205987930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7711353302002</t>
+    <t xml:space="preserve">15.1205997467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7711381912231</t>
   </si>
   <si>
     <t xml:space="preserve">14.8563709259033</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4189195632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9388513565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.75133228302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6207256317139</t>
+    <t xml:space="preserve">15.4189186096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9388484954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7513341903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6207237243652</t>
   </si>
   <si>
     <t xml:space="preserve">16.4161605834961</t>
@@ -2561,16 +2561,16 @@
     <t xml:space="preserve">16.2456932067871</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5440139770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7826728820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3707885742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4276962280273</t>
+    <t xml:space="preserve">16.544017791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7826690673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3707866668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.427698135376</t>
   </si>
   <si>
     <t xml:space="preserve">19.2629947662354</t>
@@ -2582,58 +2582,58 @@
     <t xml:space="preserve">18.6493053436279</t>
   </si>
   <si>
-    <t xml:space="preserve">18.90500831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6039295196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6380290985107</t>
+    <t xml:space="preserve">18.9050102233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.603931427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6380252838135</t>
   </si>
   <si>
     <t xml:space="preserve">20.0641994476318</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8766822814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7744026184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1494312286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0471515655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4846038818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8425922393799</t>
+    <t xml:space="preserve">19.8766841888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7744007110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1494331359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0471534729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4846019744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8425884246826</t>
   </si>
   <si>
     <t xml:space="preserve">19.8084945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7119789123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9506340026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6778888702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8483543395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8824501037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0529174804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9335899353027</t>
+    <t xml:space="preserve">20.7119808197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9506378173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6778869628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8483562469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8824481964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.052921295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9335918426514</t>
   </si>
   <si>
     <t xml:space="preserve">21.0870132446289</t>
@@ -2648,22 +2648,22 @@
     <t xml:space="preserve">21.2574806213379</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2233867645264</t>
+    <t xml:space="preserve">21.223388671875</t>
   </si>
   <si>
     <t xml:space="preserve">21.0699653625488</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3086185455322</t>
+    <t xml:space="preserve">21.3086223602295</t>
   </si>
   <si>
     <t xml:space="preserve">20.8994960784912</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9676856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7631206512451</t>
+    <t xml:space="preserve">20.9676837921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7631225585938</t>
   </si>
   <si>
     <t xml:space="preserve">20.9165439605713</t>
@@ -2672,25 +2672,25 @@
     <t xml:space="preserve">22.1609668731689</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6382789611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0133113861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9167957305908</t>
+    <t xml:space="preserve">22.6382808685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.013313293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9167976379395</t>
   </si>
   <si>
     <t xml:space="preserve">23.8145160675049</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9679374694824</t>
+    <t xml:space="preserve">23.9679393768311</t>
   </si>
   <si>
     <t xml:space="preserve">24.0020313262939</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5758609771729</t>
+    <t xml:space="preserve">23.5758590698242</t>
   </si>
   <si>
     <t xml:space="preserve">23.8656558990479</t>
@@ -2699,13 +2699,13 @@
     <t xml:space="preserve">23.7974681854248</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5247192382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5929069519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6610927581787</t>
+    <t xml:space="preserve">23.5247211456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5929050445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6610946655273</t>
   </si>
   <si>
     <t xml:space="preserve">23.8486099243164</t>
@@ -2714,16 +2714,16 @@
     <t xml:space="preserve">23.6781425476074</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4394855499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.729284286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7463321685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6951885223389</t>
+    <t xml:space="preserve">23.4394836425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7292823791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7463302612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6951847076416</t>
   </si>
   <si>
     <t xml:space="preserve">23.4906253814697</t>
@@ -2732,43 +2732,43 @@
     <t xml:space="preserve">23.7633743286133</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1496868133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9849872589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.899751663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4963893890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2123603820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5304889678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1100769042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0647068023682</t>
+    <t xml:space="preserve">23.1496887207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9849834442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8997535705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4963932037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2123622894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5304870605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1100788116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0647087097168</t>
   </si>
   <si>
     <t xml:space="preserve">25.4680633544922</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5532989501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4851112365723</t>
+    <t xml:space="preserve">25.5533008575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4851131439209</t>
   </si>
   <si>
     <t xml:space="preserve">25.1271286010742</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0589389801025</t>
+    <t xml:space="preserve">25.0589408874512</t>
   </si>
   <si>
     <t xml:space="preserve">25.0759887695312</t>
@@ -2783,19 +2783,19 @@
     <t xml:space="preserve">25.1953144073486</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7180004119873</t>
+    <t xml:space="preserve">24.7180023193359</t>
   </si>
   <si>
     <t xml:space="preserve">25.3487358093262</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2294101715088</t>
+    <t xml:space="preserve">25.2294082641602</t>
   </si>
   <si>
     <t xml:space="preserve">25.4339733123779</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3657836914062</t>
+    <t xml:space="preserve">25.3657855987549</t>
   </si>
   <si>
     <t xml:space="preserve">25.9453792572021</t>
@@ -2804,94 +2804,94 @@
     <t xml:space="preserve">26.8829593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7636299133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0306129455566</t>
+    <t xml:space="preserve">26.7636280059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0306148529053</t>
   </si>
   <si>
     <t xml:space="preserve">25.9283313751221</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0135631561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1441764831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.956657409668</t>
+    <t xml:space="preserve">26.0135669708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.144172668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9566593170166</t>
   </si>
   <si>
     <t xml:space="preserve">23.422435760498</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2690143585205</t>
+    <t xml:space="preserve">23.2690162658691</t>
   </si>
   <si>
     <t xml:space="preserve">23.4053897857666</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4565334320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8373317718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0930347442627</t>
+    <t xml:space="preserve">23.4565315246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.837329864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0930328369141</t>
   </si>
   <si>
     <t xml:space="preserve">25.5703468322754</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6385364532471</t>
+    <t xml:space="preserve">25.6385345458984</t>
   </si>
   <si>
     <t xml:space="preserve">24.3600158691406</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1384086608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.911283493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5475330352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8315658569336</t>
+    <t xml:space="preserve">24.13840675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9112854003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.547534942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8315620422363</t>
   </si>
   <si>
     <t xml:space="preserve">23.5588111877441</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1213607788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.54176902771</t>
+    <t xml:space="preserve">24.12135887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5417652130127</t>
   </si>
   <si>
     <t xml:space="preserve">23.0985469818115</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2747821807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9396114349365</t>
+    <t xml:space="preserve">24.2747840881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9396095275879</t>
   </si>
   <si>
     <t xml:space="preserve">24.2918300628662</t>
   </si>
   <si>
-    <t xml:space="preserve">24.070219039917</t>
+    <t xml:space="preserve">24.0702171325684</t>
   </si>
   <si>
     <t xml:space="preserve">23.5076713562012</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3372039794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1837825775146</t>
+    <t xml:space="preserve">23.3372001647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.183780670166</t>
   </si>
   <si>
     <t xml:space="preserve">22.6894207000732</t>
@@ -2900,16 +2900,16 @@
     <t xml:space="preserve">23.1667327880859</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2860641479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2029094696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3768405914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6984958648682</t>
+    <t xml:space="preserve">23.286060333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2029075622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3768424987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6984939575195</t>
   </si>
   <si>
     <t xml:space="preserve">22.5941352844238</t>
@@ -2918,124 +2918,124 @@
     <t xml:space="preserve">22.8202495574951</t>
   </si>
   <si>
-    <t xml:space="preserve">22.420202255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7854633331299</t>
+    <t xml:space="preserve">22.4202003479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7854652404785</t>
   </si>
   <si>
     <t xml:space="preserve">23.2898750305176</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8028545379639</t>
+    <t xml:space="preserve">22.8028564453125</t>
   </si>
   <si>
     <t xml:space="preserve">22.8724308013916</t>
   </si>
   <si>
-    <t xml:space="preserve">22.750675201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7158889770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2462635040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3332347869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4723815917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2550888061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5769939422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3596992492676</t>
+    <t xml:space="preserve">22.7506771087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7158908843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2462673187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.33323097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4723796844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2550868988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5769920349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3596973419189</t>
   </si>
   <si>
     <t xml:space="preserve">25.551025390625</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1945877075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4207000732422</t>
+    <t xml:space="preserve">26.1945896148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4207019805908</t>
   </si>
   <si>
     <t xml:space="preserve">25.7597503662109</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4033088684082</t>
+    <t xml:space="preserve">26.4033069610596</t>
   </si>
   <si>
     <t xml:space="preserve">27.0294723510742</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1860160827637</t>
+    <t xml:space="preserve">27.186014175415</t>
   </si>
   <si>
     <t xml:space="preserve">27.1164417266846</t>
   </si>
   <si>
-    <t xml:space="preserve">27.012077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1426582336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8036098480225</t>
+    <t xml:space="preserve">27.0120811462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1426563262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8036060333252</t>
   </si>
   <si>
     <t xml:space="preserve">29.0992965698242</t>
   </si>
   <si>
-    <t xml:space="preserve">29.377592086792</t>
+    <t xml:space="preserve">29.3775901794434</t>
   </si>
   <si>
     <t xml:space="preserve">29.5863151550293</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0385437011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2210540771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.081901550293</t>
+    <t xml:space="preserve">30.0385494232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2210521697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0818996429443</t>
   </si>
   <si>
     <t xml:space="preserve">28.7688217163086</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4035606384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6904277801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7859630584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5946369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4121284484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6294231414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.620849609375</t>
+    <t xml:space="preserve">28.4035568237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6904258728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7859649658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5946350097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.412130355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6294250488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6208515167236</t>
   </si>
   <si>
     <t xml:space="preserve">26.6468162536621</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5250644683838</t>
+    <t xml:space="preserve">26.5250606536865</t>
   </si>
   <si>
     <t xml:space="preserve">27.2034091949463</t>
@@ -3050,82 +3050,82 @@
     <t xml:space="preserve">30.1081199645996</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1340866088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.047119140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2906246185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8905773162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3080196380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8560390472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7342872619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2298755645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3690223693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4385986328125</t>
+    <t xml:space="preserve">29.1340827941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0471229553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2906284332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8905792236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3080177307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8560409545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7342853546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2298736572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3690204620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4385948181152</t>
   </si>
   <si>
     <t xml:space="preserve">30.0559406280518</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2994441986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9515781402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6125297546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.995189666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6039619445801</t>
+    <t xml:space="preserve">30.2994537353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9515819549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6125354766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9951858520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6039600372314</t>
   </si>
   <si>
     <t xml:space="preserve">31.8300724029541</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5691680908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8648624420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7778949737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4995994567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0387954711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6909255981445</t>
+    <t xml:space="preserve">31.5691757202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8648643493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7778930664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4995975494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0387992858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6909275054932</t>
   </si>
   <si>
     <t xml:space="preserve">31.3430595397949</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4474220275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2734813690186</t>
+    <t xml:space="preserve">31.4474201202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2734794616699</t>
   </si>
   <si>
     <t xml:space="preserve">31.7605018615723</t>
@@ -3134,25 +3134,25 @@
     <t xml:space="preserve">31.7083206176758</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5865669250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7431106567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.638744354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6735286712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3866653442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5606002807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8474712371826</t>
+    <t xml:space="preserve">31.5865650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7431049346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6387500762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6735343933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3866729736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5605964660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8474674224854</t>
   </si>
   <si>
     <t xml:space="preserve">32.5432052612305</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">31.8996486663818</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5169906616211</t>
+    <t xml:space="preserve">31.5169944763184</t>
   </si>
   <si>
     <t xml:space="preserve">31.7952899932861</t>
@@ -3170,31 +3170,31 @@
     <t xml:space="preserve">31.8126831054688</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6213493347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4822082519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3952369689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1553268432617</t>
+    <t xml:space="preserve">31.6213531494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4822044372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3952388763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.155330657959</t>
   </si>
   <si>
     <t xml:space="preserve">31.9081134796143</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7845077514648</t>
+    <t xml:space="preserve">31.7845115661621</t>
   </si>
   <si>
     <t xml:space="preserve">32.1376724243164</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1729888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2612762451172</t>
+    <t xml:space="preserve">32.1729850769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2612800598145</t>
   </si>
   <si>
     <t xml:space="preserve">32.278938293457</t>
@@ -3203,40 +3203,40 @@
     <t xml:space="preserve">31.7491931915283</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7668514251709</t>
+    <t xml:space="preserve">31.7668533325195</t>
   </si>
   <si>
     <t xml:space="preserve">31.8727970123291</t>
   </si>
   <si>
-    <t xml:space="preserve">32.667407989502</t>
+    <t xml:space="preserve">32.6674118041992</t>
   </si>
   <si>
     <t xml:space="preserve">33.0029144287109</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4443626403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.303108215332</t>
+    <t xml:space="preserve">33.4443702697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3031044006348</t>
   </si>
   <si>
     <t xml:space="preserve">34.3096122741699</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9982719421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9806137084961</t>
+    <t xml:space="preserve">34.9982795715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9806175231934</t>
   </si>
   <si>
     <t xml:space="preserve">35.2808074951172</t>
   </si>
   <si>
-    <t xml:space="preserve">34.786376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9564476013184</t>
+    <t xml:space="preserve">34.7863807678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9564514160156</t>
   </si>
   <si>
     <t xml:space="preserve">33.7975273132324</t>
@@ -3251,13 +3251,13 @@
     <t xml:space="preserve">33.1794967651367</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2148132324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0912094116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.437858581543</t>
+    <t xml:space="preserve">33.2148094177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0912055969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4378623962402</t>
   </si>
   <si>
     <t xml:space="preserve">33.0205764770508</t>
@@ -3266,64 +3266,64 @@
     <t xml:space="preserve">32.843994140625</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1441764831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0317192077637</t>
+    <t xml:space="preserve">33.1441841125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0317230224609</t>
   </si>
   <si>
     <t xml:space="preserve">32.3319091796875</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7027320861816</t>
+    <t xml:space="preserve">32.7027244567871</t>
   </si>
   <si>
     <t xml:space="preserve">33.2677879333496</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4267082214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8616485595703</t>
+    <t xml:space="preserve">33.4267120361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8616561889648</t>
   </si>
   <si>
     <t xml:space="preserve">32.2083015441895</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2017955780029</t>
+    <t xml:space="preserve">31.2017917633057</t>
   </si>
   <si>
     <t xml:space="preserve">31.1135025024414</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9610939025879</t>
+    <t xml:space="preserve">31.9610900878906</t>
   </si>
   <si>
     <t xml:space="preserve">33.126522064209</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9322853088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9257736206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5438079833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0270805358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8681602478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0800590515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3449325561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.380241394043</t>
+    <t xml:space="preserve">32.9322814941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9257755279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5438041687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0270843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0800552368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3449287414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3802375793457</t>
   </si>
   <si>
     <t xml:space="preserve">34.1330299377441</t>
@@ -3338,13 +3338,13 @@
     <t xml:space="preserve">34.2036628723145</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1153717041016</t>
+    <t xml:space="preserve">34.1153755187988</t>
   </si>
   <si>
     <t xml:space="preserve">33.938793182373</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6209449768066</t>
+    <t xml:space="preserve">33.6209526062012</t>
   </si>
   <si>
     <t xml:space="preserve">33.6915817260742</t>
@@ -3356,7 +3356,7 @@
     <t xml:space="preserve">34.503849029541</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9146270751953</t>
+    <t xml:space="preserve">32.914623260498</t>
   </si>
   <si>
     <t xml:space="preserve">33.1971549987793</t>
@@ -3374,25 +3374,25 @@
     <t xml:space="preserve">34.6451187133789</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1395416259766</t>
+    <t xml:space="preserve">35.1395378112793</t>
   </si>
   <si>
     <t xml:space="preserve">34.8570098876953</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6804313659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0865707397461</t>
+    <t xml:space="preserve">34.6804275512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0865669250488</t>
   </si>
   <si>
     <t xml:space="preserve">34.3272743225098</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2371101379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4248390197754</t>
+    <t xml:space="preserve">31.2371063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4248371124268</t>
   </si>
   <si>
     <t xml:space="preserve">30.1776275634766</t>
@@ -3401,19 +3401,19 @@
     <t xml:space="preserve">30.0716800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5595932006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6125659942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6478843688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.230598449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3477001190186</t>
+    <t xml:space="preserve">29.559591293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.61256980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6478862762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2306003570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3476982116699</t>
   </si>
   <si>
     <t xml:space="preserve">29.0121917724609</t>
@@ -3437,22 +3437,22 @@
     <t xml:space="preserve">27.7937870025635</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6348628997803</t>
+    <t xml:space="preserve">27.6348648071289</t>
   </si>
   <si>
     <t xml:space="preserve">28.0763149261475</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0409984588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3058738708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2240886688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1004810333252</t>
+    <t xml:space="preserve">28.0410022735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.305871963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2240905761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1004848480225</t>
   </si>
   <si>
     <t xml:space="preserve">29.4713020324707</t>
@@ -3467,34 +3467,34 @@
     <t xml:space="preserve">29.8244647979736</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9480686187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7891502380371</t>
+    <t xml:space="preserve">29.948070526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7891521453857</t>
   </si>
   <si>
     <t xml:space="preserve">29.2417488098145</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8421230316162</t>
+    <t xml:space="preserve">29.8421192169189</t>
   </si>
   <si>
     <t xml:space="preserve">30.0010452270508</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9833831787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5661029815674</t>
+    <t xml:space="preserve">29.9833850860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5661010742188</t>
   </si>
   <si>
     <t xml:space="preserve">30.9545822143555</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1952877044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1246471405029</t>
+    <t xml:space="preserve">30.1952857971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1246490478516</t>
   </si>
   <si>
     <t xml:space="preserve">29.3300399780273</t>
@@ -3503,10 +3503,10 @@
     <t xml:space="preserve">27.2287292480469</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8402519226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9461994171143</t>
+    <t xml:space="preserve">26.8402500152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9462013244629</t>
   </si>
   <si>
     <t xml:space="preserve">26.6106967926025</t>
@@ -3521,19 +3521,19 @@
     <t xml:space="preserve">27.3876533508301</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6989860534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8755702972412</t>
+    <t xml:space="preserve">26.6989879608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8755683898926</t>
   </si>
   <si>
     <t xml:space="preserve">27.0698070526123</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7807693481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.434118270874</t>
+    <t xml:space="preserve">25.7807712554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4341201782227</t>
   </si>
   <si>
     <t xml:space="preserve">26.1162719726562</t>
@@ -3545,40 +3545,40 @@
     <t xml:space="preserve">26.3634853363037</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1339282989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3988018035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1404361724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5753803253174</t>
+    <t xml:space="preserve">26.1339302062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3987998962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1404399871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.575382232666</t>
   </si>
   <si>
     <t xml:space="preserve">26.7519588470459</t>
   </si>
   <si>
-    <t xml:space="preserve">26.310510635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4694309234619</t>
+    <t xml:space="preserve">26.3105087280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4694328308105</t>
   </si>
   <si>
     <t xml:space="preserve">26.8225936889648</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2110710144043</t>
+    <t xml:space="preserve">27.2110729217529</t>
   </si>
   <si>
     <t xml:space="preserve">27.0521488189697</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3523349761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9815196990967</t>
+    <t xml:space="preserve">27.3523387908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9815139770508</t>
   </si>
   <si>
     <t xml:space="preserve">27.9350509643555</t>
@@ -3587,19 +3587,19 @@
     <t xml:space="preserve">27.8291034698486</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4053115844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7761287689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6525230407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3699951171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4164581298828</t>
+    <t xml:space="preserve">27.405309677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7761306762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6525211334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3699932098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4164562225342</t>
   </si>
   <si>
     <t xml:space="preserve">24.9155216217041</t>
@@ -3617,16 +3617,16 @@
     <t xml:space="preserve">25.2686862945557</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5447063446045</t>
+    <t xml:space="preserve">24.5447025299072</t>
   </si>
   <si>
     <t xml:space="preserve">24.1032524108887</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8383808135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.692476272583</t>
+    <t xml:space="preserve">23.8383827209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6924800872803</t>
   </si>
   <si>
     <t xml:space="preserve">26.451774597168</t>
@@ -3635,16 +3635,16 @@
     <t xml:space="preserve">27.5112571716309</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9703693389893</t>
+    <t xml:space="preserve">27.9703674316406</t>
   </si>
   <si>
     <t xml:space="preserve">27.2993621826172</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9285449981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5289154052734</t>
+    <t xml:space="preserve">26.9285430908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5289173126221</t>
   </si>
   <si>
     <t xml:space="preserve">27.475944519043</t>
@@ -3653,19 +3653,19 @@
     <t xml:space="preserve">26.9638595581055</t>
   </si>
   <si>
-    <t xml:space="preserve">26.381139755249</t>
+    <t xml:space="preserve">26.3811416625977</t>
   </si>
   <si>
     <t xml:space="preserve">26.8932247161865</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1757564544678</t>
+    <t xml:space="preserve">27.1757545471191</t>
   </si>
   <si>
     <t xml:space="preserve">26.7872791290283</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0986156463623</t>
+    <t xml:space="preserve">26.0986137390137</t>
   </si>
   <si>
     <t xml:space="preserve">25.4629230499268</t>
@@ -3689,16 +3689,16 @@
     <t xml:space="preserve">22.4080791473389</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4192276000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3662567138672</t>
+    <t xml:space="preserve">21.4192295074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3662528991699</t>
   </si>
   <si>
     <t xml:space="preserve">22.6906089782715</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0660667419434</t>
+    <t xml:space="preserve">21.0660648345947</t>
   </si>
   <si>
     <t xml:space="preserve">20.9424591064453</t>
@@ -3707,28 +3707,28 @@
     <t xml:space="preserve">22.3551044464111</t>
   </si>
   <si>
-    <t xml:space="preserve">21.772388458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7789001464844</t>
+    <t xml:space="preserve">21.7723903656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7788963317871</t>
   </si>
   <si>
     <t xml:space="preserve">22.4610538482666</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2844715118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2314987182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8077049255371</t>
+    <t xml:space="preserve">22.2844734191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2314968109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8077068328857</t>
   </si>
   <si>
     <t xml:space="preserve">21.5251750946045</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4722003936768</t>
+    <t xml:space="preserve">21.4722023010254</t>
   </si>
   <si>
     <t xml:space="preserve">21.5604915618896</t>
@@ -3737,19 +3737,19 @@
     <t xml:space="preserve">22.990795135498</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3374462127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8430233001709</t>
+    <t xml:space="preserve">22.3374481201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8430213928223</t>
   </si>
   <si>
     <t xml:space="preserve">21.7547302246094</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7900485992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5958061218262</t>
+    <t xml:space="preserve">21.7900466918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5958080291748</t>
   </si>
   <si>
     <t xml:space="preserve">21.3839111328125</t>
@@ -3758,19 +3758,19 @@
     <t xml:space="preserve">20.9601173400879</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1896705627441</t>
+    <t xml:space="preserve">21.1896724700928</t>
   </si>
   <si>
     <t xml:space="preserve">21.136697769165</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4015693664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7658786773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8365135192871</t>
+    <t xml:space="preserve">21.4015674591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7658805847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8365116119385</t>
   </si>
   <si>
     <t xml:space="preserve">20.0595550537109</t>
@@ -3782,28 +3782,28 @@
     <t xml:space="preserve">20.3774013519287</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5186634063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8653202056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0065803527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7835388183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5363254547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0418968200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1943111419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4238662719727</t>
+    <t xml:space="preserve">20.5186653137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8653182983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0065822601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7835369110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5363235473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.041898727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1943130493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4238681793213</t>
   </si>
   <si>
     <t xml:space="preserve">19.7770290374756</t>
@@ -3812,25 +3812,25 @@
     <t xml:space="preserve">20.3420886993408</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3355751037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5474720001221</t>
+    <t xml:space="preserve">19.3355770111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5474739074707</t>
   </si>
   <si>
     <t xml:space="preserve">19.6710815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9111557006836</t>
+    <t xml:space="preserve">19.9111518859863</t>
   </si>
   <si>
     <t xml:space="preserve">19.0677719116211</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4711265563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1311664581299</t>
+    <t xml:space="preserve">19.4711284637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1311645507812</t>
   </si>
   <si>
     <t xml:space="preserve">20.3878479003906</t>
@@ -3845,7 +3845,7 @@
     <t xml:space="preserve">20.3145122528076</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6445293426514</t>
+    <t xml:space="preserve">20.64453125</t>
   </si>
   <si>
     <t xml:space="preserve">20.0944995880127</t>
@@ -3854,19 +3854,19 @@
     <t xml:space="preserve">20.4061832427979</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1678352355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5811347961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3061199188232</t>
+    <t xml:space="preserve">20.1678371429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5811367034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3061180114746</t>
   </si>
   <si>
     <t xml:space="preserve">18.3710651397705</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7560863494873</t>
+    <t xml:space="preserve">18.7560882568359</t>
   </si>
   <si>
     <t xml:space="preserve">19.0127696990967</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">17.729362487793</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9493751525879</t>
+    <t xml:space="preserve">17.9493732452393</t>
   </si>
   <si>
     <t xml:space="preserve">17.2801704406738</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">17.2618312835693</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1793308258057</t>
+    <t xml:space="preserve">17.179328918457</t>
   </si>
   <si>
     <t xml:space="preserve">17.2343330383301</t>
@@ -3899,10 +3899,10 @@
     <t xml:space="preserve">17.0968246459961</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7576389312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2626113891602</t>
+    <t xml:space="preserve">16.757640838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2626094818115</t>
   </si>
   <si>
     <t xml:space="preserve">16.1617698669434</t>
@@ -3914,13 +3914,13 @@
     <t xml:space="preserve">15.9875946044922</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3817844390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7851409912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0601539611816</t>
+    <t xml:space="preserve">16.3817825317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7851390838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0601577758789</t>
   </si>
   <si>
     <t xml:space="preserve">17.188497543335</t>
@@ -3929,10 +3929,10 @@
     <t xml:space="preserve">17.4635105133057</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9501476287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4092826843262</t>
+    <t xml:space="preserve">16.9501495361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4092864990234</t>
   </si>
   <si>
     <t xml:space="preserve">16.6843013763428</t>
@@ -3941,7 +3941,7 @@
     <t xml:space="preserve">16.9043140411377</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0693244934082</t>
+    <t xml:space="preserve">17.0693225860596</t>
   </si>
   <si>
     <t xml:space="preserve">16.9593162536621</t>
@@ -3953,19 +3953,19 @@
     <t xml:space="preserve">16.8676452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3359489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8500862121582</t>
+    <t xml:space="preserve">16.3359470367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8500852584839</t>
   </si>
   <si>
     <t xml:space="preserve">16.8218078613281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5284595489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1151599884033</t>
+    <t xml:space="preserve">16.5284576416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1151580810547</t>
   </si>
   <si>
     <t xml:space="preserve">17.8852062225342</t>
@@ -3983,13 +3983,13 @@
     <t xml:space="preserve">17.4726791381836</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5643520355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6835269927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.665189743042</t>
+    <t xml:space="preserve">17.5643501281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6835250854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6651916503906</t>
   </si>
   <si>
     <t xml:space="preserve">17.2159976959229</t>
@@ -3998,22 +3998,22 @@
     <t xml:space="preserve">17.3351707458496</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9868202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0784912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8584766387939</t>
+    <t xml:space="preserve">16.9868183135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0784893035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8584785461426</t>
   </si>
   <si>
     <t xml:space="preserve">16.4001178741455</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9967622756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9417572021484</t>
+    <t xml:space="preserve">15.9967603683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9417552947998</t>
   </si>
   <si>
     <t xml:space="preserve">16.0425968170166</t>
@@ -4025,13 +4025,13 @@
     <t xml:space="preserve">15.6392383575439</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9142560958862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0525388717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2542171478271</t>
+    <t xml:space="preserve">15.9142580032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0525398254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2542190551758</t>
   </si>
   <si>
     <t xml:space="preserve">15.2175493240356</t>
@@ -4040,52 +4040,52 @@
     <t xml:space="preserve">15.1992149353027</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6117391586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0059280395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.694242477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9883708953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5758438110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5850124359131</t>
+    <t xml:space="preserve">15.6117401123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0059261322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6942434310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9883689880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5758447647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5850114822388</t>
   </si>
   <si>
     <t xml:space="preserve">13.860803604126</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8058013916016</t>
+    <t xml:space="preserve">13.8058004379272</t>
   </si>
   <si>
     <t xml:space="preserve">13.6041231155396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3841094970703</t>
+    <t xml:space="preserve">13.3841104507446</t>
   </si>
   <si>
     <t xml:space="preserve">13.585786819458</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7599649429321</t>
+    <t xml:space="preserve">13.7599639892578</t>
   </si>
   <si>
     <t xml:space="preserve">13.924973487854</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3107719421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8149681091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5032825469971</t>
+    <t xml:space="preserve">13.310772895813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8149671554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5032835006714</t>
   </si>
   <si>
     <t xml:space="preserve">13.8883037567139</t>
@@ -4094,19 +4094,19 @@
     <t xml:space="preserve">13.5124502182007</t>
   </si>
   <si>
-    <t xml:space="preserve">13.659125328064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3382720947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4482803344727</t>
+    <t xml:space="preserve">13.6591243743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3382740020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4482793807983</t>
   </si>
   <si>
     <t xml:space="preserve">13.8516368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5307836532593</t>
+    <t xml:space="preserve">13.5307846069336</t>
   </si>
   <si>
     <t xml:space="preserve">13.8424692153931</t>
@@ -4115,28 +4115,28 @@
     <t xml:space="preserve">14.1908226013184</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3466644287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6033458709717</t>
+    <t xml:space="preserve">14.3466653823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6033477783203</t>
   </si>
   <si>
     <t xml:space="preserve">14.1816549301147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5483427047729</t>
+    <t xml:space="preserve">14.5483436584473</t>
   </si>
   <si>
     <t xml:space="preserve">14.8233594894409</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5659008026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7217445373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9050893783569</t>
+    <t xml:space="preserve">15.5659017562866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7217454910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9050903320312</t>
   </si>
   <si>
     <t xml:space="preserve">16.1526031494141</t>
@@ -4145,7 +4145,7 @@
     <t xml:space="preserve">16.7026348114014</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2434997558594</t>
+    <t xml:space="preserve">17.2434978485107</t>
   </si>
   <si>
     <t xml:space="preserve">17.5093479156494</t>
@@ -4154,10 +4154,10 @@
     <t xml:space="preserve">18.2427234649658</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5528583526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7178688049316</t>
+    <t xml:space="preserve">20.5528564453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.717866897583</t>
   </si>
   <si>
     <t xml:space="preserve">19.4161262512207</t>
@@ -4169,10 +4169,10 @@
     <t xml:space="preserve">19.0494384765625</t>
   </si>
   <si>
-    <t xml:space="preserve">19.617805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2595081329346</t>
+    <t xml:space="preserve">19.6178035736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2595062255859</t>
   </si>
   <si>
     <t xml:space="preserve">19.7094783782959</t>
@@ -4187,10 +4187,10 @@
     <t xml:space="preserve">19.8928203582764</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6544723510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8561496734619</t>
+    <t xml:space="preserve">19.6544742584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8561515808105</t>
   </si>
   <si>
     <t xml:space="preserve">19.4527950286865</t>
@@ -4199,7 +4199,7 @@
     <t xml:space="preserve">19.5261306762695</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7278099060059</t>
+    <t xml:space="preserve">19.7278118133545</t>
   </si>
   <si>
     <t xml:space="preserve">20.3695125579834</t>
@@ -4208,7 +4208,7 @@
     <t xml:space="preserve">19.8378162384033</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3244552612305</t>
+    <t xml:space="preserve">19.3244514465332</t>
   </si>
   <si>
     <t xml:space="preserve">18.9760990142822</t>
@@ -4220,16 +4220,16 @@
     <t xml:space="preserve">19.2144470214844</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6728057861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2327823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0578269958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1128330230713</t>
+    <t xml:space="preserve">19.6728038787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.232780456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0578289031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1128311157227</t>
   </si>
   <si>
     <t xml:space="preserve">20.2961769104004</t>
@@ -4238,16 +4238,16 @@
     <t xml:space="preserve">20.5161895751953</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8179302215576</t>
+    <t xml:space="preserve">21.8179321289062</t>
   </si>
   <si>
     <t xml:space="preserve">21.2495651245117</t>
   </si>
   <si>
-    <t xml:space="preserve">20.992883682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7728691101074</t>
+    <t xml:space="preserve">20.9928817749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7728710174561</t>
   </si>
   <si>
     <t xml:space="preserve">20.8828792572021</t>
@@ -4259,34 +4259,34 @@
     <t xml:space="preserve">20.8095397949219</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7362041473389</t>
+    <t xml:space="preserve">20.7362022399902</t>
   </si>
   <si>
     <t xml:space="preserve">19.7828121185303</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7644786834717</t>
+    <t xml:space="preserve">19.764476776123</t>
   </si>
   <si>
     <t xml:space="preserve">19.2511157989502</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8660926818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3977928161621</t>
+    <t xml:space="preserve">18.8660945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3977909088135</t>
   </si>
   <si>
     <t xml:space="preserve">19.3427886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4894618988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5994701385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3511810302734</t>
+    <t xml:space="preserve">19.4894638061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5994682312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3511791229248</t>
   </si>
   <si>
     <t xml:space="preserve">19.8744850158691</t>
@@ -4295,10 +4295,10 @@
     <t xml:space="preserve">20.1495018005371</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0761623382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0394973754883</t>
+    <t xml:space="preserve">20.0761642456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0394954681396</t>
   </si>
   <si>
     <t xml:space="preserve">20.9745483398438</t>
@@ -4307,16 +4307,16 @@
     <t xml:space="preserve">21.2128963470459</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5795860290527</t>
+    <t xml:space="preserve">21.5795841217041</t>
   </si>
   <si>
     <t xml:space="preserve">21.6345882415771</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6529235839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6162509918213</t>
+    <t xml:space="preserve">21.6529216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6162548065186</t>
   </si>
   <si>
     <t xml:space="preserve">21.5429153442383</t>
@@ -4328,22 +4328,22 @@
     <t xml:space="preserve">21.3045673370361</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6628646850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4245204925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5711917877197</t>
+    <t xml:space="preserve">20.6628665924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4245185852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5711936950684</t>
   </si>
   <si>
     <t xml:space="preserve">19.966157913208</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5078010559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3611221313477</t>
+    <t xml:space="preserve">19.5077991485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3611259460449</t>
   </si>
   <si>
     <t xml:space="preserve">19.5444660186768</t>
@@ -4352,10 +4352,10 @@
     <t xml:space="preserve">19.9294891357422</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0211620330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6460819244385</t>
+    <t xml:space="preserve">20.0211601257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6460800170898</t>
   </si>
   <si>
     <t xml:space="preserve">18.4444026947021</t>
@@ -4364,19 +4364,19 @@
     <t xml:space="preserve">18.481071472168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6094131469727</t>
+    <t xml:space="preserve">18.609411239624</t>
   </si>
   <si>
     <t xml:space="preserve">18.407735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3343963623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9210968017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.287784576416</t>
+    <t xml:space="preserve">18.3343982696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9210987091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2877864837646</t>
   </si>
   <si>
     <t xml:space="preserve">19.1961135864258</t>
@@ -4385,13 +4385,13 @@
     <t xml:space="preserve">19.1044425964355</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7201499938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6169300079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8756313323975</t>
+    <t xml:space="preserve">18.7201480865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6169319152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8756294250488</t>
   </si>
   <si>
     <t xml:space="preserve">17.5378246307373</t>
@@ -4415,16 +4415,16 @@
     <t xml:space="preserve">17.0498809814453</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0029621124268</t>
+    <t xml:space="preserve">17.0029640197754</t>
   </si>
   <si>
     <t xml:space="preserve">17.0311126708984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9560432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.89035987854</t>
+    <t xml:space="preserve">16.9560451507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8903617858887</t>
   </si>
   <si>
     <t xml:space="preserve">16.9091281890869</t>
@@ -4433,7 +4433,7 @@
     <t xml:space="preserve">17.078031539917</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1852874755859</t>
+    <t xml:space="preserve">18.1852855682373</t>
   </si>
   <si>
     <t xml:space="preserve">18.2885055541992</t>
@@ -4442,7 +4442,7 @@
     <t xml:space="preserve">17.5659732818604</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0069999694824</t>
+    <t xml:space="preserve">18.0070018768311</t>
   </si>
   <si>
     <t xml:space="preserve">17.9225482940674</t>
@@ -4454,7 +4454,7 @@
     <t xml:space="preserve">17.8005619049072</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5753574371338</t>
+    <t xml:space="preserve">17.5753555297852</t>
   </si>
   <si>
     <t xml:space="preserve">17.7536449432373</t>
@@ -4463,7 +4463,7 @@
     <t xml:space="preserve">17.9319324493408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9882354736328</t>
+    <t xml:space="preserve">17.9882335662842</t>
   </si>
   <si>
     <t xml:space="preserve">18.3354244232178</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">18.5137119293213</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7858352661133</t>
+    <t xml:space="preserve">18.7858333587646</t>
   </si>
   <si>
     <t xml:space="preserve">18.5230941772461</t>
@@ -4502,13 +4502,13 @@
     <t xml:space="preserve">20.3435001373291</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7804889678955</t>
+    <t xml:space="preserve">19.7804870605469</t>
   </si>
   <si>
     <t xml:space="preserve">19.8555564880371</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8743228912354</t>
+    <t xml:space="preserve">19.874324798584</t>
   </si>
   <si>
     <t xml:space="preserve">19.198709487915</t>
@@ -4517,7 +4517,7 @@
     <t xml:space="preserve">19.2925453186035</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6678848266602</t>
+    <t xml:space="preserve">19.6678867340088</t>
   </si>
   <si>
     <t xml:space="preserve">19.2737770080566</t>
@@ -4541,19 +4541,19 @@
     <t xml:space="preserve">22.0325355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1639080047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0888385772705</t>
+    <t xml:space="preserve">22.1639060974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0888366699219</t>
   </si>
   <si>
     <t xml:space="preserve">21.8073310852051</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1826705932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2389755249023</t>
+    <t xml:space="preserve">22.1826725006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2389736175537</t>
   </si>
   <si>
     <t xml:space="preserve">22.2952747344971</t>
@@ -4565,13 +4565,13 @@
     <t xml:space="preserve">21.9574680328369</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8448677062988</t>
+    <t xml:space="preserve">21.8448657989502</t>
   </si>
   <si>
     <t xml:space="preserve">21.7698001861572</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7134971618652</t>
+    <t xml:space="preserve">21.7134952545166</t>
   </si>
   <si>
     <t xml:space="preserve">21.995002746582</t>
@@ -4586,19 +4586,19 @@
     <t xml:space="preserve">22.970890045166</t>
   </si>
   <si>
-    <t xml:space="preserve">22.914587020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.158561706543</t>
+    <t xml:space="preserve">22.9145889282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1585597991943</t>
   </si>
   <si>
     <t xml:space="preserve">23.2711620330811</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1397933959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4882907867432</t>
+    <t xml:space="preserve">23.1397953033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4882888793945</t>
   </si>
   <si>
     <t xml:space="preserve">21.8824005126953</t>
@@ -4607,7 +4607,7 @@
     <t xml:space="preserve">21.8636322021484</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9252777099609</t>
+    <t xml:space="preserve">20.9252796173096</t>
   </si>
   <si>
     <t xml:space="preserve">21.0003471374512</t>
@@ -4619,13 +4619,13 @@
     <t xml:space="preserve">21.2443199157715</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8877468109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6813087463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1182956695557</t>
+    <t xml:space="preserve">20.8877449035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6813068389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1182975769043</t>
   </si>
   <si>
     <t xml:space="preserve">20.3998012542725</t>
@@ -4634,7 +4634,7 @@
     <t xml:space="preserve">19.8930912017822</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2174758911133</t>
+    <t xml:space="preserve">19.2174777984619</t>
   </si>
   <si>
     <t xml:space="preserve">19.3488464355469</t>
@@ -4646,7 +4646,7 @@
     <t xml:space="preserve">19.7054195404053</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0807628631592</t>
+    <t xml:space="preserve">20.0807609558105</t>
   </si>
   <si>
     <t xml:space="preserve">19.742956161499</t>
@@ -4670,25 +4670,25 @@
     <t xml:space="preserve">18.9172039031982</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2684326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.686653137207</t>
+    <t xml:space="preserve">20.2684345245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6866512298584</t>
   </si>
   <si>
     <t xml:space="preserve">19.1236400604248</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9922695159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9118595123291</t>
+    <t xml:space="preserve">18.9922714233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9118576049805</t>
   </si>
   <si>
     <t xml:space="preserve">19.4051475524902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8180236816406</t>
+    <t xml:space="preserve">19.8180255889893</t>
   </si>
   <si>
     <t xml:space="preserve">19.9681606292725</t>
@@ -4697,10 +4697,10 @@
     <t xml:space="preserve">20.606237411499</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4695224761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7162265777588</t>
+    <t xml:space="preserve">21.4695243835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7162284851074</t>
   </si>
   <si>
     <t xml:space="preserve">24.5848579406738</t>
@@ -4709,28 +4709,28 @@
     <t xml:space="preserve">24.6974601745605</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5044441223145</t>
+    <t xml:space="preserve">25.5044422149658</t>
   </si>
   <si>
     <t xml:space="preserve">24.922664642334</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8475952148438</t>
+    <t xml:space="preserve">24.8475971221924</t>
   </si>
   <si>
     <t xml:space="preserve">25.4293766021729</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0486888885498</t>
+    <t xml:space="preserve">26.0486907958984</t>
   </si>
   <si>
     <t xml:space="preserve">25.710880279541</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2363605499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8422508239746</t>
+    <t xml:space="preserve">26.2363586425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8422527313232</t>
   </si>
   <si>
     <t xml:space="preserve">25.9360847473145</t>
@@ -4751,19 +4751,19 @@
     <t xml:space="preserve">26.3114280700684</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4615650177002</t>
+    <t xml:space="preserve">26.4615631103516</t>
   </si>
   <si>
     <t xml:space="preserve">26.7806053161621</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9119739532471</t>
+    <t xml:space="preserve">26.9119720458984</t>
   </si>
   <si>
     <t xml:space="preserve">27.0058097839355</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2310161590576</t>
+    <t xml:space="preserve">27.231014251709</t>
   </si>
   <si>
     <t xml:space="preserve">27.1184120178223</t>
@@ -4775,7 +4775,7 @@
     <t xml:space="preserve">26.8932075500488</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6814250946045</t>
+    <t xml:space="preserve">27.6814231872559</t>
   </si>
   <si>
     <t xml:space="preserve">27.718957901001</t>
@@ -4784,7 +4784,7 @@
     <t xml:space="preserve">27.4749870300293</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7377262115479</t>
+    <t xml:space="preserve">27.7377243041992</t>
   </si>
   <si>
     <t xml:space="preserve">28.1693668365479</t>
@@ -4808,7 +4808,7 @@
     <t xml:space="preserve">27.7752590179443</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8878612518311</t>
+    <t xml:space="preserve">27.8878593444824</t>
   </si>
   <si>
     <t xml:space="preserve">28.4321041107178</t>
@@ -4817,10 +4817,10 @@
     <t xml:space="preserve">28.8074493408203</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2766265869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8449802398682</t>
+    <t xml:space="preserve">29.2766246795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8449821472168</t>
   </si>
   <si>
     <t xml:space="preserve">28.7136135101318</t>
@@ -4829,7 +4829,7 @@
     <t xml:space="preserve">28.1881351470947</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8315620422363</t>
+    <t xml:space="preserve">27.8315601348877</t>
   </si>
   <si>
     <t xml:space="preserve">27.7940273284912</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">27.9253959655762</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2819709777832</t>
+    <t xml:space="preserve">28.2819690704346</t>
   </si>
   <si>
     <t xml:space="preserve">29.1640224456787</t>
@@ -4847,7 +4847,7 @@
     <t xml:space="preserve">27.944164276123</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2444343566895</t>
+    <t xml:space="preserve">28.2444362640381</t>
   </si>
   <si>
     <t xml:space="preserve">27.6063556671143</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">27.5500545501709</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1934776306152</t>
+    <t xml:space="preserve">27.1934795379639</t>
   </si>
   <si>
     <t xml:space="preserve">26.7243022918701</t>
@@ -4874,10 +4874,10 @@
     <t xml:space="preserve">27.4374504089355</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3060817718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7055339813232</t>
+    <t xml:space="preserve">27.3060836791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7055358886719</t>
   </si>
   <si>
     <t xml:space="preserve">26.8181381225586</t>
@@ -4898,31 +4898,31 @@
     <t xml:space="preserve">28.0192317962646</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4884090423584</t>
+    <t xml:space="preserve">28.4884071350098</t>
   </si>
   <si>
     <t xml:space="preserve">30.2900447845459</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5527877807617</t>
+    <t xml:space="preserve">30.5527858734131</t>
   </si>
   <si>
     <t xml:space="preserve">31.1533317565918</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4777145385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.515251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.383882522583</t>
+    <t xml:space="preserve">30.4777164459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5152530670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3838806152344</t>
   </si>
   <si>
     <t xml:space="preserve">30.0460739135742</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1211395263672</t>
+    <t xml:space="preserve">30.1211414337158</t>
   </si>
   <si>
     <t xml:space="preserve">29.6519660949707</t>
@@ -4931,7 +4931,7 @@
     <t xml:space="preserve">29.9897727966309</t>
   </si>
   <si>
-    <t xml:space="preserve">30.083610534668</t>
+    <t xml:space="preserve">30.0836086273193</t>
   </si>
   <si>
     <t xml:space="preserve">29.6894989013672</t>
@@ -4946,13 +4946,13 @@
     <t xml:space="preserve">30.2712783813477</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9334716796875</t>
+    <t xml:space="preserve">29.9334697723389</t>
   </si>
   <si>
     <t xml:space="preserve">28.5259399414062</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3007354736328</t>
+    <t xml:space="preserve">28.3007373809814</t>
   </si>
   <si>
     <t xml:space="preserve">28.0943012237549</t>
@@ -4967,16 +4967,16 @@
     <t xml:space="preserve">27.8503284454346</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5205955505371</t>
+    <t xml:space="preserve">29.5205974578857</t>
   </si>
   <si>
     <t xml:space="preserve">28.9763488769531</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4830627441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7645664215088</t>
+    <t xml:space="preserve">29.483060836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7645683288574</t>
   </si>
   <si>
     <t xml:space="preserve">28.9575843811035</t>
@@ -4985,10 +4985,10 @@
     <t xml:space="preserve">29.1452541351318</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0031967163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9468936920166</t>
+    <t xml:space="preserve">31.00319480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.946891784668</t>
   </si>
   <si>
     <t xml:space="preserve">30.7779903411865</t>
@@ -4997,10 +4997,10 @@
     <t xml:space="preserve">31.3973026275635</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5581321716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7029209136963</t>
+    <t xml:space="preserve">29.5581302642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7029228210449</t>
   </si>
   <si>
     <t xml:space="preserve">30.3463478088379</t>
@@ -5024,31 +5024,31 @@
     <t xml:space="preserve">29.6310176849365</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5543022155762</t>
+    <t xml:space="preserve">29.5543041229248</t>
   </si>
   <si>
     <t xml:space="preserve">30.7242012023926</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6064167022705</t>
+    <t xml:space="preserve">31.6064205169678</t>
   </si>
   <si>
     <t xml:space="preserve">30.6091289520264</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3570995330811</t>
+    <t xml:space="preserve">31.3570957183838</t>
   </si>
   <si>
     <t xml:space="preserve">30.8968086242676</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8776321411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4940547943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2995586395264</t>
+    <t xml:space="preserve">30.8776302337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4940567016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.299560546875</t>
   </si>
   <si>
     <t xml:space="preserve">31.2803802490234</t>
@@ -5057,7 +5057,7 @@
     <t xml:space="preserve">30.9159889221191</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8392715454102</t>
+    <t xml:space="preserve">30.8392734527588</t>
   </si>
   <si>
     <t xml:space="preserve">30.7050228118896</t>
@@ -5069,7 +5069,7 @@
     <t xml:space="preserve">30.9543437957764</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7077312469482</t>
+    <t xml:space="preserve">29.7077331542969</t>
   </si>
   <si>
     <t xml:space="preserve">30.6858425140381</t>
@@ -5081,22 +5081,22 @@
     <t xml:space="preserve">30.4556999206543</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4913463592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7817344665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4721698760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0145893096924</t>
+    <t xml:space="preserve">31.4913482666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7817363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.47216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.014591217041</t>
   </si>
   <si>
     <t xml:space="preserve">28.4227619171143</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4419422149658</t>
+    <t xml:space="preserve">28.4419403076172</t>
   </si>
   <si>
     <t xml:space="preserve">28.0008335113525</t>
@@ -5105,13 +5105,13 @@
     <t xml:space="preserve">28.5761909484863</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8638706207275</t>
+    <t xml:space="preserve">28.8638725280762</t>
   </si>
   <si>
     <t xml:space="preserve">30.359806060791</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2063789367676</t>
+    <t xml:space="preserve">30.2063770294189</t>
   </si>
   <si>
     <t xml:space="preserve">30.4365196228027</t>
@@ -5123,7 +5123,7 @@
     <t xml:space="preserve">30.8009147644043</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2611999511719</t>
+    <t xml:space="preserve">31.2612018585205</t>
   </si>
   <si>
     <t xml:space="preserve">31.4146308898926</t>
@@ -5144,7 +5144,7 @@
     <t xml:space="preserve">29.3241596221924</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4584102630615</t>
+    <t xml:space="preserve">29.4584083557129</t>
   </si>
   <si>
     <t xml:space="preserve">28.7487983703613</t>
@@ -5156,10 +5156,10 @@
     <t xml:space="preserve">27.9432964324951</t>
   </si>
   <si>
-    <t xml:space="preserve">26.102144241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5459632873535</t>
+    <t xml:space="preserve">26.1021461486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5459651947021</t>
   </si>
   <si>
     <t xml:space="preserve">25.1432113647461</t>
@@ -5174,28 +5174,28 @@
     <t xml:space="preserve">26.0446090698242</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2172164916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0637893676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.929536819458</t>
+    <t xml:space="preserve">26.2172183990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0637874603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9295387268066</t>
   </si>
   <si>
     <t xml:space="preserve">26.5432548522949</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4281826019287</t>
+    <t xml:space="preserve">26.4281806945801</t>
   </si>
   <si>
     <t xml:space="preserve">26.8692932128906</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0419006347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1953296661377</t>
+    <t xml:space="preserve">27.041898727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1953277587891</t>
   </si>
   <si>
     <t xml:space="preserve">27.0610771179199</t>
@@ -5216,7 +5216,7 @@
     <t xml:space="preserve">26.524076461792</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5624332427979</t>
+    <t xml:space="preserve">26.5624351501465</t>
   </si>
   <si>
     <t xml:space="preserve">25.6802158355713</t>
@@ -5225,28 +5225,28 @@
     <t xml:space="preserve">25.3158206939697</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5843238830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3925342559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0281410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7952861785889</t>
+    <t xml:space="preserve">25.584321975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3925361633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0281429290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7952880859375</t>
   </si>
   <si>
     <t xml:space="preserve">26.2939319610596</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9487152099609</t>
+    <t xml:space="preserve">25.9487171173096</t>
   </si>
   <si>
     <t xml:space="preserve">26.4857196807861</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7733974456787</t>
+    <t xml:space="preserve">26.7733993530273</t>
   </si>
   <si>
     <t xml:space="preserve">25.6418590545654</t>
@@ -5255,34 +5255,34 @@
     <t xml:space="preserve">25.7761077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1213245391846</t>
+    <t xml:space="preserve">26.1213226318359</t>
   </si>
   <si>
     <t xml:space="preserve">25.7377510070801</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6583271026611</t>
+    <t xml:space="preserve">26.6583251953125</t>
   </si>
   <si>
     <t xml:space="preserve">26.0829677581787</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9678955078125</t>
+    <t xml:space="preserve">25.9678936004639</t>
   </si>
   <si>
     <t xml:space="preserve">26.1405029296875</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1596813201904</t>
+    <t xml:space="preserve">26.1596832275391</t>
   </si>
   <si>
     <t xml:space="preserve">25.8528232574463</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8144664764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9103603363037</t>
+    <t xml:space="preserve">25.8144645690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9103584289551</t>
   </si>
   <si>
     <t xml:space="preserve">25.9870738983154</t>
@@ -5291,13 +5291,13 @@
     <t xml:space="preserve">25.6993942260742</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4884281158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7569313049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2966423034668</t>
+    <t xml:space="preserve">25.4884300231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.756929397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2966403961182</t>
   </si>
   <si>
     <t xml:space="preserve">26.3514671325684</t>
@@ -5315,10 +5315,10 @@
     <t xml:space="preserve">27.5789012908936</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8309326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3541793823242</t>
+    <t xml:space="preserve">26.8309345245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3541774749756</t>
   </si>
   <si>
     <t xml:space="preserve">26.7542190551758</t>
@@ -5330,7 +5330,7 @@
     <t xml:space="preserve">26.6391487121582</t>
   </si>
   <si>
-    <t xml:space="preserve">28.307689666748</t>
+    <t xml:space="preserve">28.3076915740967</t>
   </si>
   <si>
     <t xml:space="preserve">28.557014465332</t>
@@ -5351,16 +5351,16 @@
     <t xml:space="preserve">26.7925777435303</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0227203369141</t>
+    <t xml:space="preserve">27.0227222442627</t>
   </si>
   <si>
     <t xml:space="preserve">26.8501129150391</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2145080566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3487586975098</t>
+    <t xml:space="preserve">27.214506149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3487567901611</t>
   </si>
   <si>
     <t xml:space="preserve">27.962474822998</t>
@@ -5369,16 +5369,16 @@
     <t xml:space="preserve">28.6337280273438</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1131954193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3049812316895</t>
+    <t xml:space="preserve">29.1131935119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3049793243408</t>
   </si>
   <si>
     <t xml:space="preserve">29.0556564331055</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9597663879395</t>
+    <t xml:space="preserve">28.9597644805908</t>
   </si>
   <si>
     <t xml:space="preserve">28.7296199798584</t>
@@ -5408,10 +5408,10 @@
     <t xml:space="preserve">27.809045791626</t>
   </si>
   <si>
-    <t xml:space="preserve">27.617259979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9049377441406</t>
+    <t xml:space="preserve">27.6172580718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9049396514893</t>
   </si>
   <si>
     <t xml:space="preserve">30.6666641235352</t>
@@ -5423,13 +5423,13 @@
     <t xml:space="preserve">31.1077728271484</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2228488922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6037063598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1050643920898</t>
+    <t xml:space="preserve">31.2228469848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6037101745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1050605773926</t>
   </si>
   <si>
     <t xml:space="preserve">32.6804275512695</t>
@@ -5441,7 +5441,7 @@
     <t xml:space="preserve">32.5269927978516</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2584953308105</t>
+    <t xml:space="preserve">32.2584915161133</t>
   </si>
   <si>
     <t xml:space="preserve">32.2776718139648</t>
@@ -5450,7 +5450,7 @@
     <t xml:space="preserve">31.8365631103516</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7598476409912</t>
+    <t xml:space="preserve">31.7598495483398</t>
   </si>
   <si>
     <t xml:space="preserve">32.2009582519531</t>
@@ -5471,7 +5471,7 @@
     <t xml:space="preserve">32.584529876709</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0475234985352</t>
+    <t xml:space="preserve">32.0475273132324</t>
   </si>
   <si>
     <t xml:space="preserve">32.6228866577148</t>
@@ -5483,22 +5483,22 @@
     <t xml:space="preserve">32.6420669555664</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2968482971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9708137512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4338111877441</t>
+    <t xml:space="preserve">32.2968521118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9708118438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4338092803955</t>
   </si>
   <si>
     <t xml:space="preserve">30.9735221862793</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9762344360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5324153900146</t>
+    <t xml:space="preserve">29.9762325286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.532413482666</t>
   </si>
   <si>
     <t xml:space="preserve">30.1104831695557</t>
@@ -5522,7 +5522,10 @@
     <t xml:space="preserve">29.2090854644775</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6856346130371</t>
+    <t xml:space="preserve">23.6856365203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.721284866333</t>
   </si>
   <si>
     <t xml:space="preserve">23.9157791137695</t>
@@ -5546,7 +5549,7 @@
     <t xml:space="preserve">25.2774639129639</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6829261779785</t>
+    <t xml:space="preserve">24.6829242706299</t>
   </si>
   <si>
     <t xml:space="preserve">25.1048564910889</t>
@@ -5558,13 +5561,13 @@
     <t xml:space="preserve">25.5267868041992</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5816116333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6199684143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4090042114258</t>
+    <t xml:space="preserve">26.5816097259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6199703216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4090061187744</t>
   </si>
   <si>
     <t xml:space="preserve">27.7131519317627</t>
@@ -5573,7 +5576,7 @@
     <t xml:space="preserve">29.611837387085</t>
   </si>
   <si>
-    <t xml:space="preserve">28.902229309082</t>
+    <t xml:space="preserve">28.9022274017334</t>
   </si>
   <si>
     <t xml:space="preserve">28.6145496368408</t>
@@ -5868,6 +5871,9 @@
   </si>
   <si>
     <t xml:space="preserve">31.6800003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6200008392334</t>
   </si>
 </sst>
 </file>
@@ -18028,7 +18034,7 @@
         <v>26.8899993896484</v>
       </c>
       <c r="G455" t="s">
-        <v>271</v>
+        <v>378</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -18054,7 +18060,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G456" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -18080,7 +18086,7 @@
         <v>27.5900001525879</v>
       </c>
       <c r="G457" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -18106,7 +18112,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G458" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -18132,7 +18138,7 @@
         <v>27.6700000762939</v>
       </c>
       <c r="G459" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -18158,7 +18164,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G460" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -18184,7 +18190,7 @@
         <v>28.2800006866455</v>
       </c>
       <c r="G461" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -18236,7 +18242,7 @@
         <v>27.5300006866455</v>
       </c>
       <c r="G463" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -18262,7 +18268,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G464" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -18288,7 +18294,7 @@
         <v>27.6200008392334</v>
       </c>
       <c r="G465" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -18314,7 +18320,7 @@
         <v>27.5300006866455</v>
       </c>
       <c r="G466" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -18366,7 +18372,7 @@
         <v>28.3799991607666</v>
       </c>
       <c r="G468" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -18392,7 +18398,7 @@
         <v>28.3700008392334</v>
       </c>
       <c r="G469" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -18418,7 +18424,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G470" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -18470,7 +18476,7 @@
         <v>28.0900001525879</v>
       </c>
       <c r="G472" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -18496,7 +18502,7 @@
         <v>27.9300003051758</v>
       </c>
       <c r="G473" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -18522,7 +18528,7 @@
         <v>28.0599994659424</v>
       </c>
       <c r="G474" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -18548,7 +18554,7 @@
         <v>27.6100006103516</v>
       </c>
       <c r="G475" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -18574,7 +18580,7 @@
         <v>27.2099990844727</v>
       </c>
       <c r="G476" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -18600,7 +18606,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G477" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -18626,7 +18632,7 @@
         <v>27.7299995422363</v>
       </c>
       <c r="G478" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -18652,7 +18658,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G479" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -18678,7 +18684,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G480" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -18704,7 +18710,7 @@
         <v>24</v>
       </c>
       <c r="G481" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -18730,7 +18736,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G482" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -18756,7 +18762,7 @@
         <v>24.75</v>
       </c>
       <c r="G483" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -18782,7 +18788,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G484" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -18808,7 +18814,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G485" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -18834,7 +18840,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G486" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -18860,7 +18866,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G487" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -18886,7 +18892,7 @@
         <v>24.2099990844727</v>
       </c>
       <c r="G488" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -18912,7 +18918,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G489" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -18938,7 +18944,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G490" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -18964,7 +18970,7 @@
         <v>24.5200004577637</v>
       </c>
       <c r="G491" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -18990,7 +18996,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G492" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -19016,7 +19022,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G493" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -19042,7 +19048,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G494" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -19068,7 +19074,7 @@
         <v>24.5</v>
       </c>
       <c r="G495" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -19094,7 +19100,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G496" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -19120,7 +19126,7 @@
         <v>25.2099990844727</v>
       </c>
       <c r="G497" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -19146,7 +19152,7 @@
         <v>25.4300003051758</v>
       </c>
       <c r="G498" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -19172,7 +19178,7 @@
         <v>25.5200004577637</v>
       </c>
       <c r="G499" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -19198,7 +19204,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G500" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -19224,7 +19230,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G501" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -19250,7 +19256,7 @@
         <v>25</v>
       </c>
       <c r="G502" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -19276,7 +19282,7 @@
         <v>24.8299999237061</v>
       </c>
       <c r="G503" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -19302,7 +19308,7 @@
         <v>26.0900001525879</v>
       </c>
       <c r="G504" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -19328,7 +19334,7 @@
         <v>26.2900009155273</v>
       </c>
       <c r="G505" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -19354,7 +19360,7 @@
         <v>25.9400005340576</v>
       </c>
       <c r="G506" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -19380,7 +19386,7 @@
         <v>25.4200000762939</v>
       </c>
       <c r="G507" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -19406,7 +19412,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G508" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -19458,7 +19464,7 @@
         <v>25.4699993133545</v>
       </c>
       <c r="G510" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -19484,7 +19490,7 @@
         <v>25.2299995422363</v>
       </c>
       <c r="G511" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -19510,7 +19516,7 @@
         <v>25.5</v>
       </c>
       <c r="G512" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -19536,7 +19542,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G513" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -19588,7 +19594,7 @@
         <v>26.6800003051758</v>
       </c>
       <c r="G515" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -19614,7 +19620,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G516" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -19640,7 +19646,7 @@
         <v>26.9799995422363</v>
       </c>
       <c r="G517" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -19666,7 +19672,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G518" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -19692,7 +19698,7 @@
         <v>26.5200004577637</v>
       </c>
       <c r="G519" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -19718,7 +19724,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G520" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -19744,7 +19750,7 @@
         <v>26.7199993133545</v>
       </c>
       <c r="G521" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -19770,7 +19776,7 @@
         <v>26.6800003051758</v>
       </c>
       <c r="G522" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -19822,7 +19828,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G524" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -19848,7 +19854,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G525" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -19874,7 +19880,7 @@
         <v>26.2800006866455</v>
       </c>
       <c r="G526" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -19926,7 +19932,7 @@
         <v>27.0400009155273</v>
       </c>
       <c r="G528" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -19952,7 +19958,7 @@
         <v>26.7199993133545</v>
       </c>
       <c r="G529" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -19978,7 +19984,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G530" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -20004,7 +20010,7 @@
         <v>27.1399993896484</v>
       </c>
       <c r="G531" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -20030,7 +20036,7 @@
         <v>26.6599998474121</v>
       </c>
       <c r="G532" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -20056,7 +20062,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G533" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -20108,7 +20114,7 @@
         <v>26.7199993133545</v>
       </c>
       <c r="G535" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -20134,7 +20140,7 @@
         <v>26.4799995422363</v>
       </c>
       <c r="G536" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -20186,7 +20192,7 @@
         <v>25.5</v>
       </c>
       <c r="G538" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -20212,7 +20218,7 @@
         <v>24.3400001525879</v>
       </c>
       <c r="G539" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -20238,7 +20244,7 @@
         <v>24.0799999237061</v>
       </c>
       <c r="G540" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -20264,7 +20270,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G541" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -20290,7 +20296,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G542" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -20316,7 +20322,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G543" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -20342,7 +20348,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G544" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -20368,7 +20374,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G545" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -20394,7 +20400,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G546" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -20420,7 +20426,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G547" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -20446,7 +20452,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G548" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -20472,7 +20478,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G549" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -20498,7 +20504,7 @@
         <v>24.2800006866455</v>
       </c>
       <c r="G550" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -20524,7 +20530,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G551" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -20550,7 +20556,7 @@
         <v>23.4599990844727</v>
       </c>
       <c r="G552" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -20576,7 +20582,7 @@
         <v>23.1800003051758</v>
       </c>
       <c r="G553" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -20602,7 +20608,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G554" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -20628,7 +20634,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G555" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -20654,7 +20660,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G556" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -20680,7 +20686,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G557" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -20706,7 +20712,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G558" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -20732,7 +20738,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G559" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -20784,7 +20790,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G561" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -20836,7 +20842,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G563" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -20862,7 +20868,7 @@
         <v>25.1599998474121</v>
       </c>
       <c r="G564" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -20888,7 +20894,7 @@
         <v>24.6399993896484</v>
       </c>
       <c r="G565" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -20914,7 +20920,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G566" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -20940,7 +20946,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G567" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -20966,7 +20972,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G568" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -20992,7 +20998,7 @@
         <v>24.2199993133545</v>
       </c>
       <c r="G569" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -21018,7 +21024,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G570" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -21044,7 +21050,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G571" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -21070,7 +21076,7 @@
         <v>24.3400001525879</v>
       </c>
       <c r="G572" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -21096,7 +21102,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G573" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -21122,7 +21128,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G574" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -21148,7 +21154,7 @@
         <v>24.5</v>
       </c>
       <c r="G575" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -21174,7 +21180,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G576" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -21200,7 +21206,7 @@
         <v>24.8199996948242</v>
       </c>
       <c r="G577" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -21226,7 +21232,7 @@
         <v>24.5200004577637</v>
       </c>
       <c r="G578" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -21252,7 +21258,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G579" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -21278,7 +21284,7 @@
         <v>24</v>
       </c>
       <c r="G580" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -21304,7 +21310,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G581" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -21330,7 +21336,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G582" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -21356,7 +21362,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G583" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -21382,7 +21388,7 @@
         <v>23.4799995422363</v>
       </c>
       <c r="G584" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -21408,7 +21414,7 @@
         <v>23.7800006866455</v>
       </c>
       <c r="G585" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -21434,7 +21440,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G586" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -21460,7 +21466,7 @@
         <v>25.5599994659424</v>
       </c>
       <c r="G587" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -21486,7 +21492,7 @@
         <v>25.1200008392334</v>
       </c>
       <c r="G588" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -21512,7 +21518,7 @@
         <v>25</v>
       </c>
       <c r="G589" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -21538,7 +21544,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G590" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -21564,7 +21570,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G591" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -21590,7 +21596,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G592" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -21616,7 +21622,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G593" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -21642,7 +21648,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G594" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -21668,7 +21674,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G595" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -21694,7 +21700,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G596" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -21720,7 +21726,7 @@
         <v>25</v>
       </c>
       <c r="G597" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -21746,7 +21752,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G598" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -21772,7 +21778,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G599" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -21798,7 +21804,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G600" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -21824,7 +21830,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G601" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -21850,7 +21856,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G602" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -21876,7 +21882,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G603" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -21902,7 +21908,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G604" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -21928,7 +21934,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G605" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -21954,7 +21960,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G606" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -21980,7 +21986,7 @@
         <v>24.5</v>
       </c>
       <c r="G607" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -22006,7 +22012,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G608" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -22032,7 +22038,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G609" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -22058,7 +22064,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G610" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -22084,7 +22090,7 @@
         <v>24.0799999237061</v>
       </c>
       <c r="G611" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -22110,7 +22116,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G612" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -22136,7 +22142,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G613" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -22162,7 +22168,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G614" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -22188,7 +22194,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G615" t="s">
-        <v>503</v>
+        <v>481</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -22240,7 +22246,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G617" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -22344,7 +22350,7 @@
         <v>25</v>
       </c>
       <c r="G621" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -22370,7 +22376,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G622" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -22422,7 +22428,7 @@
         <v>25</v>
       </c>
       <c r="G624" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -22630,7 +22636,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G632" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -22656,7 +22662,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G633" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -22812,7 +22818,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G639" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -22890,7 +22896,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G642" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -23020,7 +23026,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G647" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -23046,7 +23052,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G648" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -23072,7 +23078,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G649" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -23150,7 +23156,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G652" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -24840,7 +24846,7 @@
         <v>25</v>
       </c>
       <c r="G717" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -26218,7 +26224,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G770" t="s">
-        <v>503</v>
+        <v>481</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -26296,7 +26302,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G773" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -26374,7 +26380,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G776" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -26452,7 +26458,7 @@
         <v>24.0799999237061</v>
       </c>
       <c r="G779" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -27206,7 +27212,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G808" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -27518,7 +27524,7 @@
         <v>24.0799999237061</v>
       </c>
       <c r="G820" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -27648,7 +27654,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G825" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -27908,7 +27914,7 @@
         <v>25</v>
       </c>
       <c r="G835" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -27934,7 +27940,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G836" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -27986,7 +27992,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G838" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -67506,7 +67512,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G2358" t="s">
-        <v>1198</v>
+        <v>1837</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67532,7 +67538,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G2359" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67558,7 +67564,7 @@
         <v>26.0599994659424</v>
       </c>
       <c r="G2360" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67584,7 +67590,7 @@
         <v>26.2399997711182</v>
       </c>
       <c r="G2361" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67610,7 +67616,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G2362" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67636,7 +67642,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G2363" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -67662,7 +67668,7 @@
         <v>26.7199993133545</v>
       </c>
       <c r="G2364" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67688,7 +67694,7 @@
         <v>26.3600006103516</v>
       </c>
       <c r="G2365" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67714,7 +67720,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G2366" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67740,7 +67746,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G2367" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67792,7 +67798,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G2369" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67818,7 +67824,7 @@
         <v>26.6200008392334</v>
       </c>
       <c r="G2370" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -67896,7 +67902,7 @@
         <v>27.7199993133545</v>
       </c>
       <c r="G2373" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -67948,7 +67954,7 @@
         <v>27.7600002288818</v>
       </c>
       <c r="G2375" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -68000,7 +68006,7 @@
         <v>27.5400009155273</v>
       </c>
       <c r="G2377" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -68052,7 +68058,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G2379" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -68078,7 +68084,7 @@
         <v>30.8799991607666</v>
       </c>
       <c r="G2380" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -68104,7 +68110,7 @@
         <v>30.1399993896484</v>
       </c>
       <c r="G2381" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -68130,7 +68136,7 @@
         <v>29.8400001525879</v>
       </c>
       <c r="G2382" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -68182,7 +68188,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G2384" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -68208,7 +68214,7 @@
         <v>29.0200004577637</v>
       </c>
       <c r="G2385" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -68234,7 +68240,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G2386" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -68260,7 +68266,7 @@
         <v>28.3799991607666</v>
       </c>
       <c r="G2387" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -68286,7 +68292,7 @@
         <v>27.9799995422363</v>
       </c>
       <c r="G2388" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -68312,7 +68318,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G2389" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -68338,7 +68344,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G2390" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -68364,7 +68370,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G2391" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -68390,7 +68396,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G2392" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -68416,7 +68422,7 @@
         <v>28.8199996948242</v>
       </c>
       <c r="G2393" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -68442,7 +68448,7 @@
         <v>28.4400005340576</v>
       </c>
       <c r="G2394" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68468,7 +68474,7 @@
         <v>28.3400001525879</v>
       </c>
       <c r="G2395" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68494,7 +68500,7 @@
         <v>28.2800006866455</v>
       </c>
       <c r="G2396" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68520,7 +68526,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G2397" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68546,7 +68552,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G2398" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68572,7 +68578,7 @@
         <v>28.4200000762939</v>
       </c>
       <c r="G2399" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68598,7 +68604,7 @@
         <v>28.5599994659424</v>
       </c>
       <c r="G2400" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68624,7 +68630,7 @@
         <v>28.5799999237061</v>
       </c>
       <c r="G2401" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68650,7 +68656,7 @@
         <v>28.0599994659424</v>
       </c>
       <c r="G2402" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68676,7 +68682,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G2403" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68702,7 +68708,7 @@
         <v>27.9400005340576</v>
       </c>
       <c r="G2404" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68728,7 +68734,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G2405" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68754,7 +68760,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G2406" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68780,7 +68786,7 @@
         <v>27.0400009155273</v>
       </c>
       <c r="G2407" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68806,7 +68812,7 @@
         <v>27.1599998474121</v>
       </c>
       <c r="G2408" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68832,7 +68838,7 @@
         <v>27.1200008392334</v>
       </c>
       <c r="G2409" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68858,7 +68864,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G2410" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68884,7 +68890,7 @@
         <v>27.5400009155273</v>
       </c>
       <c r="G2411" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -68910,7 +68916,7 @@
         <v>27.9799995422363</v>
       </c>
       <c r="G2412" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -68936,7 +68942,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G2413" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -68962,7 +68968,7 @@
         <v>28.5</v>
       </c>
       <c r="G2414" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -68988,7 +68994,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G2415" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -69014,7 +69020,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G2416" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -69040,7 +69046,7 @@
         <v>29.0400009155273</v>
       </c>
       <c r="G2417" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -69066,7 +69072,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G2418" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -69092,7 +69098,7 @@
         <v>29.2800006866455</v>
       </c>
       <c r="G2419" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -69118,7 +69124,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G2420" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -69144,7 +69150,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G2421" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -69170,7 +69176,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G2422" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -69196,7 +69202,7 @@
         <v>29.8199996948242</v>
       </c>
       <c r="G2423" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -69222,7 +69228,7 @@
         <v>29.3400001525879</v>
       </c>
       <c r="G2424" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -69248,7 +69254,7 @@
         <v>29.7800006866455</v>
       </c>
       <c r="G2425" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -69274,7 +69280,7 @@
         <v>29.5599994659424</v>
       </c>
       <c r="G2426" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -69300,7 +69306,7 @@
         <v>29.7199993133545</v>
       </c>
       <c r="G2427" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -69326,7 +69332,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G2428" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -69352,7 +69358,7 @@
         <v>29.2199993133545</v>
       </c>
       <c r="G2429" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -69378,7 +69384,7 @@
         <v>28.4799995422363</v>
       </c>
       <c r="G2430" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -69404,7 +69410,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G2431" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -69430,7 +69436,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G2432" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -69456,7 +69462,7 @@
         <v>28.6599998474121</v>
       </c>
       <c r="G2433" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -69482,7 +69488,7 @@
         <v>28.9599990844727</v>
       </c>
       <c r="G2434" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69508,7 +69514,7 @@
         <v>28.8400001525879</v>
       </c>
       <c r="G2435" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69534,7 +69540,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G2436" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69560,7 +69566,7 @@
         <v>28.8600006103516</v>
       </c>
       <c r="G2437" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69586,7 +69592,7 @@
         <v>28.3799991607666</v>
       </c>
       <c r="G2438" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69612,7 +69618,7 @@
         <v>29</v>
       </c>
       <c r="G2439" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69638,7 +69644,7 @@
         <v>29.2600002288818</v>
       </c>
       <c r="G2440" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69664,7 +69670,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G2441" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69690,7 +69696,7 @@
         <v>29.8400001525879</v>
       </c>
       <c r="G2442" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69716,7 +69722,7 @@
         <v>29.9200000762939</v>
       </c>
       <c r="G2443" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69742,7 +69748,7 @@
         <v>29.3600006103516</v>
       </c>
       <c r="G2444" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69768,7 +69774,7 @@
         <v>29.3600006103516</v>
       </c>
       <c r="G2445" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69794,7 +69800,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G2446" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -69820,7 +69826,7 @@
         <v>29.5</v>
       </c>
       <c r="G2447" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -69846,7 +69852,7 @@
         <v>29.7199993133545</v>
       </c>
       <c r="G2448" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -69872,7 +69878,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G2449" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -69898,7 +69904,7 @@
         <v>29.8600006103516</v>
       </c>
       <c r="G2450" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -69924,7 +69930,7 @@
         <v>30.2600002288818</v>
       </c>
       <c r="G2451" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -69950,7 +69956,7 @@
         <v>30.4799995422363</v>
       </c>
       <c r="G2452" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -69976,7 +69982,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G2453" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -70002,7 +70008,7 @@
         <v>30.4200000762939</v>
       </c>
       <c r="G2454" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -70028,7 +70034,7 @@
         <v>30.2600002288818</v>
       </c>
       <c r="G2455" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -70054,7 +70060,7 @@
         <v>30.4400005340576</v>
       </c>
       <c r="G2456" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -70080,7 +70086,7 @@
         <v>29.9400005340576</v>
       </c>
       <c r="G2457" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -70106,7 +70112,7 @@
         <v>30.2399997711182</v>
       </c>
       <c r="G2458" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -70132,7 +70138,7 @@
         <v>29.7800006866455</v>
       </c>
       <c r="G2459" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -70158,7 +70164,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G2460" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -70184,7 +70190,7 @@
         <v>29.2600002288818</v>
       </c>
       <c r="G2461" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -70210,7 +70216,7 @@
         <v>29.5400009155273</v>
       </c>
       <c r="G2462" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -70236,7 +70242,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G2463" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -70262,7 +70268,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G2464" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -70288,7 +70294,7 @@
         <v>29.3199996948242</v>
       </c>
       <c r="G2465" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -70314,7 +70320,7 @@
         <v>30.5400009155273</v>
       </c>
       <c r="G2466" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -70340,7 +70346,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G2467" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -70366,7 +70372,7 @@
         <v>30.6200008392334</v>
       </c>
       <c r="G2468" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -70392,7 +70398,7 @@
         <v>30.7600002288818</v>
       </c>
       <c r="G2469" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -70418,7 +70424,7 @@
         <v>30.2600002288818</v>
       </c>
       <c r="G2470" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -70444,7 +70450,7 @@
         <v>30.8199996948242</v>
       </c>
       <c r="G2471" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -70470,7 +70476,7 @@
         <v>30.9400005340576</v>
       </c>
       <c r="G2472" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70496,7 +70502,7 @@
         <v>30.2199993133545</v>
       </c>
       <c r="G2473" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -70522,7 +70528,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G2474" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -70548,7 +70554,7 @@
         <v>30.3199996948242</v>
       </c>
       <c r="G2475" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -70574,7 +70580,7 @@
         <v>29.7399997711182</v>
       </c>
       <c r="G2476" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -70600,7 +70606,7 @@
         <v>30.2199993133545</v>
       </c>
       <c r="G2477" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -70626,7 +70632,7 @@
         <v>30.5799999237061</v>
       </c>
       <c r="G2478" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -70652,7 +70658,7 @@
         <v>30.7800006866455</v>
       </c>
       <c r="G2479" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -70678,7 +70684,7 @@
         <v>31.3199996948242</v>
       </c>
       <c r="G2480" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -70704,7 +70710,7 @@
         <v>31.9400005340576</v>
       </c>
       <c r="G2481" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -70730,7 +70736,7 @@
         <v>32.4799995422363</v>
       </c>
       <c r="G2482" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -70756,7 +70762,7 @@
         <v>31.1599998474121</v>
       </c>
       <c r="G2483" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -70782,7 +70788,7 @@
         <v>31.0200004577637</v>
       </c>
       <c r="G2484" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -70808,7 +70814,7 @@
         <v>31.0599994659424</v>
       </c>
       <c r="G2485" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -70834,7 +70840,7 @@
         <v>30.4400005340576</v>
       </c>
       <c r="G2486" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -70860,7 +70866,7 @@
         <v>29</v>
       </c>
       <c r="G2487" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -70886,7 +70892,7 @@
         <v>29.1599998474121</v>
       </c>
       <c r="G2488" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -70912,7 +70918,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G2489" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -70938,7 +70944,7 @@
         <v>28.0599994659424</v>
       </c>
       <c r="G2490" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -70964,7 +70970,7 @@
         <v>29.2800006866455</v>
       </c>
       <c r="G2491" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -70990,7 +70996,7 @@
         <v>30.4799995422363</v>
       </c>
       <c r="G2492" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -71016,7 +71022,7 @@
         <v>30.4799995422363</v>
       </c>
       <c r="G2493" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -71042,7 +71048,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G2494" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -71068,7 +71074,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G2495" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -71094,7 +71100,7 @@
         <v>30.9799995422363</v>
       </c>
       <c r="G2496" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -71120,7 +71126,7 @@
         <v>30.8799991607666</v>
       </c>
       <c r="G2497" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -71146,7 +71152,7 @@
         <v>31.0400009155273</v>
       </c>
       <c r="G2498" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -71172,7 +71178,7 @@
         <v>31.5</v>
       </c>
       <c r="G2499" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -71198,7 +71204,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G2500" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -71206,7 +71212,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6910185185</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>101801</v>
@@ -71224,9 +71230,35 @@
         <v>31.6800003051758</v>
       </c>
       <c r="G2501" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6911111111</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>91226</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>32</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>31.3600006103516</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>32</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>31.6200008392334</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1953</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DLG.MI.xlsx
+++ b/data/DLG.MI.xlsx
@@ -44,64 +44,64 @@
     <t xml:space="preserve">DLG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5564212799072</t>
+    <t xml:space="preserve">20.5564231872559</t>
   </si>
   <si>
     <t xml:space="preserve">20.6553955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">20.175745010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9777946472168</t>
+    <t xml:space="preserve">20.1757469177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9778003692627</t>
   </si>
   <si>
     <t xml:space="preserve">19.7722320556641</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4905300140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8864345550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5160064697266</t>
+    <t xml:space="preserve">19.4905338287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8864364624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5160045623779</t>
   </si>
   <si>
     <t xml:space="preserve">17.6328411102295</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4348888397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.526252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0542144775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8943309783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0135173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6354732513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4451370239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7116107940674</t>
+    <t xml:space="preserve">17.4348907470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5262508392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0542163848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8943328857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0135154724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6354713439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4451332092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7116088867188</t>
   </si>
   <si>
     <t xml:space="preserve">16.8029708862305</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6735401153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1329860687256</t>
+    <t xml:space="preserve">16.6735420227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.132984161377</t>
   </si>
   <si>
     <t xml:space="preserve">15.9654865264893</t>
@@ -110,22 +110,22 @@
     <t xml:space="preserve">15.6533346176147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9909582138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7777853012085</t>
+    <t xml:space="preserve">14.9909601211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7777814865112</t>
   </si>
   <si>
     <t xml:space="preserve">15.3335657119751</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4123373031616</t>
+    <t xml:space="preserve">14.4123363494873</t>
   </si>
   <si>
     <t xml:space="preserve">14.7397155761719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4553842544556</t>
+    <t xml:space="preserve">15.4553833007812</t>
   </si>
   <si>
     <t xml:space="preserve">15.2574338912964</t>
@@ -134,16 +134,16 @@
     <t xml:space="preserve">15.4097032546997</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7523078918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3868579864502</t>
+    <t xml:space="preserve">15.75230884552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3868608474731</t>
   </si>
   <si>
     <t xml:space="preserve">15.9121942520142</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9578723907471</t>
+    <t xml:space="preserve">15.95787525177</t>
   </si>
   <si>
     <t xml:space="preserve">15.584813117981</t>
@@ -152,70 +152,70 @@
     <t xml:space="preserve">16.1253719329834</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1938934326172</t>
+    <t xml:space="preserve">16.1938953399658</t>
   </si>
   <si>
     <t xml:space="preserve">16.5593376159668</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7496738433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8817405700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2193651199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792476654053</t>
+    <t xml:space="preserve">16.7496776580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8817367553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2193660736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792486190796</t>
   </si>
   <si>
     <t xml:space="preserve">16.0873012542725</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7142400741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2878847122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8969650268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3183431625366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6076488494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9274168014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9883279800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8893547058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6152648925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3564100265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1356143951416</t>
+    <t xml:space="preserve">15.7142429351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2878856658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8969631195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3183422088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6076526641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9274206161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9883270263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.889349937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6152658462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.356406211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1356182098389</t>
   </si>
   <si>
     <t xml:space="preserve">15.2269773483276</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3487949371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0442523956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2345905303955</t>
+    <t xml:space="preserve">15.3487939834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0442562103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2345943450928</t>
   </si>
   <si>
     <t xml:space="preserve">15.0594816207886</t>
@@ -224,49 +224,49 @@
     <t xml:space="preserve">15.1432294845581</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5493803024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7853975296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8234643936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7831630706787</t>
+    <t xml:space="preserve">14.5493812561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7853927612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8234634399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7831659317017</t>
   </si>
   <si>
     <t xml:space="preserve">14.977988243103</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1572246551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1494312286377</t>
+    <t xml:space="preserve">15.1572256088257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1494331359863</t>
   </si>
   <si>
     <t xml:space="preserve">14.9624032974243</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9857835769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.954610824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8533010482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4689435958862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6715574264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.21706199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7572793960571</t>
+    <t xml:space="preserve">14.9857807159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9546117782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8533020019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4689426422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6715593338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2170639038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7572784423828</t>
   </si>
   <si>
     <t xml:space="preserve">16.0300331115723</t>
@@ -275,19 +275,19 @@
     <t xml:space="preserve">16.2404403686523</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1469268798828</t>
+    <t xml:space="preserve">16.1469249725342</t>
   </si>
   <si>
     <t xml:space="preserve">16.3495426177979</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5054016113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3105773925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7288875579834</t>
+    <t xml:space="preserve">16.5054035186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3105754852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7288913726807</t>
   </si>
   <si>
     <t xml:space="preserve">16.7937393188477</t>
@@ -302,64 +302,64 @@
     <t xml:space="preserve">16.7547740936279</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8482894897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1132507324219</t>
+    <t xml:space="preserve">16.8482875823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1132469177246</t>
   </si>
   <si>
     <t xml:space="preserve">17.3002796173096</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7678546905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9081287384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9470920562744</t>
+    <t xml:space="preserve">17.7678527832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9081249237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9470901489258</t>
   </si>
   <si>
     <t xml:space="preserve">18.063985824585</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4848003387451</t>
+    <t xml:space="preserve">18.4848022460938</t>
   </si>
   <si>
     <t xml:space="preserve">18.788724899292</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4614219665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3367385864258</t>
+    <t xml:space="preserve">18.46142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3367366790771</t>
   </si>
   <si>
     <t xml:space="preserve">18.274393081665</t>
   </si>
   <si>
-    <t xml:space="preserve">18.079568862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6484527587891</t>
+    <t xml:space="preserve">18.0795726776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6484508514404</t>
   </si>
   <si>
     <t xml:space="preserve">18.8276920318604</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4536285400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8379878997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3937911987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2535190582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0820789337158</t>
+    <t xml:space="preserve">18.4536304473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8379898071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3937931060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2535209655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0820751190186</t>
   </si>
   <si>
     <t xml:space="preserve">17.4951019287109</t>
@@ -368,154 +368,154 @@
     <t xml:space="preserve">17.9237117767334</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8224048614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7834377288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9315013885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6768436431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.523494720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1157550811768</t>
+    <t xml:space="preserve">17.8224029541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7834415435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9315052032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6768455505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5234937667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1157569885254</t>
   </si>
   <si>
     <t xml:space="preserve">16.3651275634766</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6612548828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6300888061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8975515365601</t>
+    <t xml:space="preserve">16.6612586975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6300868988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8975553512573</t>
   </si>
   <si>
     <t xml:space="preserve">15.7806596755981</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5468721389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7884531021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3729209899902</t>
+    <t xml:space="preserve">15.5468730926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7884511947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3729228973389</t>
   </si>
   <si>
     <t xml:space="preserve">16.1858901977539</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1625137329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.419677734375</t>
+    <t xml:space="preserve">16.1625118255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4196815490723</t>
   </si>
   <si>
     <t xml:space="preserve">16.5209865570068</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5287818908691</t>
+    <t xml:space="preserve">16.5287780761719</t>
   </si>
   <si>
     <t xml:space="preserve">16.8404979705811</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9184226989746</t>
+    <t xml:space="preserve">16.9184246063232</t>
   </si>
   <si>
     <t xml:space="preserve">16.8716678619385</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8015289306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6119956970215</t>
+    <t xml:space="preserve">16.8015308380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6119976043701</t>
   </si>
   <si>
     <t xml:space="preserve">17.2223491668701</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5964088439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4171733856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6587543487549</t>
+    <t xml:space="preserve">17.5964107513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4171714782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6587505340576</t>
   </si>
   <si>
     <t xml:space="preserve">17.3158626556396</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3236598968506</t>
+    <t xml:space="preserve">17.323657989502</t>
   </si>
   <si>
     <t xml:space="preserve">17.502893447876</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0561923980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5393524169922</t>
+    <t xml:space="preserve">18.0561904907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5393543243408</t>
   </si>
   <si>
     <t xml:space="preserve">18.7030029296875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.664041519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8121070861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0951557159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1497058868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9003353118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1574993133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8769550323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6665477752686</t>
+    <t xml:space="preserve">18.6640396118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.812105178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0951538085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1497077941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9003314971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1575012207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8769512176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6665458679199</t>
   </si>
   <si>
     <t xml:space="preserve">17.9704666137695</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0328140258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5106887817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5730323791504</t>
+    <t xml:space="preserve">18.0328121185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5106868743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5730285644531</t>
   </si>
   <si>
     <t xml:space="preserve">17.3626232147217</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4015865325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2379341125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4093780517578</t>
+    <t xml:space="preserve">17.4015884399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2379360198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4093799591064</t>
   </si>
   <si>
     <t xml:space="preserve">17.1444187164307</t>
@@ -524,10 +524,10 @@
     <t xml:space="preserve">16.8171157836914</t>
   </si>
   <si>
-    <t xml:space="preserve">16.614501953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6846389770508</t>
+    <t xml:space="preserve">16.6145038604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6846370697021</t>
   </si>
   <si>
     <t xml:space="preserve">17.0197334289551</t>
@@ -536,112 +536,112 @@
     <t xml:space="preserve">17.128833770752</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2691078186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9963531494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4405517578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4639282226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8327026367188</t>
+    <t xml:space="preserve">17.2691059112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9963550567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4405498504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4639301300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8327007293701</t>
   </si>
   <si>
     <t xml:space="preserve">16.8249111175537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9028377532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7859477996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7469844818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2768993377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2457256317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0509052276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0976619720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.957389831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2301406860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2067642211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4327583312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2846946716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0664882659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9521045684814</t>
+    <t xml:space="preserve">16.9028396606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7859497070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7469787597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2769012451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2457275390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0509033203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0976638793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9573917388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2301425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2067623138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4327564239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2846927642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0664901733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9521036148071</t>
   </si>
   <si>
     <t xml:space="preserve">15.9832725524902</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2560291290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3339557647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9988632202148</t>
+    <t xml:space="preserve">16.2560272216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3339595794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9988622665405</t>
   </si>
   <si>
     <t xml:space="preserve">15.4065999984741</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3130855560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1182594299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5131950378418</t>
+    <t xml:space="preserve">15.3130836486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.118260383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5131912231445</t>
   </si>
   <si>
     <t xml:space="preserve">16.0923767089844</t>
   </si>
   <si>
-    <t xml:space="preserve">15.913140296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1781024932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7158126831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0586948394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4664344787598</t>
+    <t xml:space="preserve">15.9131412506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1780948638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7158088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0586986541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4664363861084</t>
   </si>
   <si>
     <t xml:space="preserve">16.2248554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9754800796509</t>
+    <t xml:space="preserve">15.9754829406738</t>
   </si>
   <si>
     <t xml:space="preserve">16.7080173492432</t>
@@ -650,16 +650,16 @@
     <t xml:space="preserve">16.4976100921631</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6924285888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5599517822266</t>
+    <t xml:space="preserve">16.6924304962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5599536895752</t>
   </si>
   <si>
     <t xml:space="preserve">16.7703590393066</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8638763427734</t>
+    <t xml:space="preserve">16.8638725280762</t>
   </si>
   <si>
     <t xml:space="preserve">17.0275268554688</t>
@@ -674,37 +674,37 @@
     <t xml:space="preserve">17.8847465515137</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1185321807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2354278564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0172290802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8457813262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9626750946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.869161605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6353721618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7912330627441</t>
+    <t xml:space="preserve">18.1185359954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2354316711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0172271728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8457832336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9626770019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8691596984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6353740692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7912311553955</t>
   </si>
   <si>
     <t xml:space="preserve">17.5808238983154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6509590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1107425689697</t>
+    <t xml:space="preserve">17.6509571075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1107387542725</t>
   </si>
   <si>
     <t xml:space="preserve">17.9782619476318</t>
@@ -716,94 +716,94 @@
     <t xml:space="preserve">18.2042560577393</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4692153930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0848579406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3498153686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2952632904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4667110443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2485084533691</t>
+    <t xml:space="preserve">18.469217300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0848541259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.349817276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2952690124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4667072296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2485103607178</t>
   </si>
   <si>
     <t xml:space="preserve">19.3186435699463</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0614814758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4199542999268</t>
+    <t xml:space="preserve">19.0614776611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4199523925781</t>
   </si>
   <si>
     <t xml:space="preserve">19.2407150268555</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0926475524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4511222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8588600158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6406593322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9056205749512</t>
+    <t xml:space="preserve">19.0926494598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4511241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8588619232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.640661239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9056186676025</t>
   </si>
   <si>
     <t xml:space="preserve">19.2329216003418</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4978828430176</t>
+    <t xml:space="preserve">19.4978809356689</t>
   </si>
   <si>
     <t xml:space="preserve">20.1914520263672</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9888362884521</t>
+    <t xml:space="preserve">19.9888343811035</t>
   </si>
   <si>
     <t xml:space="preserve">20.1213130950928</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9732494354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9551563262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6278533935547</t>
+    <t xml:space="preserve">19.9732475280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9551544189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6278514862061</t>
   </si>
   <si>
     <t xml:space="preserve">21.2201175689697</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0408802032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7915096282959</t>
+    <t xml:space="preserve">21.0408821105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7915058135986</t>
   </si>
   <si>
     <t xml:space="preserve">20.7447471618652</t>
   </si>
   <si>
-    <t xml:space="preserve">20.861644744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2434978485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9006080627441</t>
+    <t xml:space="preserve">20.8616428375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2434959411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9006042480469</t>
   </si>
   <si>
     <t xml:space="preserve">21.0330867767334</t>
@@ -815,10 +815,10 @@
     <t xml:space="preserve">21.6721038818359</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4149379730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3136329650879</t>
+    <t xml:space="preserve">21.4149398803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3136310577393</t>
   </si>
   <si>
     <t xml:space="preserve">21.1967372894287</t>
@@ -830,43 +830,43 @@
     <t xml:space="preserve">21.5785903930664</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1884727478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1002044677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.947732925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0279808044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9878520965576</t>
+    <t xml:space="preserve">22.1884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1002006530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9477310180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0279769897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9878540039062</t>
   </si>
   <si>
     <t xml:space="preserve">21.8273601531982</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3489685058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4693374633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8946533203125</t>
+    <t xml:space="preserve">22.3489665985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4693393707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8946514129639</t>
   </si>
   <si>
     <t xml:space="preserve">23.3199634552002</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2878646850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.878604888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0310745239258</t>
+    <t xml:space="preserve">23.2878684997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8786029815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0310726165771</t>
   </si>
   <si>
     <t xml:space="preserve">23.4483604431152</t>
@@ -875,85 +875,85 @@
     <t xml:space="preserve">23.0230484008789</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9026775360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6218109130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.501443862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2557678222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8434104919434</t>
+    <t xml:space="preserve">22.9026756286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6218128204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5014400482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.255765914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8434066772461</t>
   </si>
   <si>
     <t xml:space="preserve">22.0600776672363</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6298351287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7341575622559</t>
+    <t xml:space="preserve">22.6298408508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7341594696045</t>
   </si>
   <si>
     <t xml:space="preserve">22.9267520904541</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2316951751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1434211730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1674919128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6570053100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7693500518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6730537414551</t>
+    <t xml:space="preserve">23.2316913604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1434230804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1674957275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6570072174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7693519592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6730575561523</t>
   </si>
   <si>
     <t xml:space="preserve">23.8495979309082</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7613277435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4002113342285</t>
+    <t xml:space="preserve">23.7613296508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4002132415771</t>
   </si>
   <si>
     <t xml:space="preserve">23.2958927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4323139190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7051563262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0069980621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8304538726807</t>
+    <t xml:space="preserve">23.4323120117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7051544189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0069999694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8304557800293</t>
   </si>
   <si>
     <t xml:space="preserve">22.7903308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0631713867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8255252838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3921852111816</t>
+    <t xml:space="preserve">23.063175201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8255271911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3921890258789</t>
   </si>
   <si>
     <t xml:space="preserve">23.2637920379639</t>
@@ -962,43 +962,43 @@
     <t xml:space="preserve">23.2718162536621</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1915702819824</t>
+    <t xml:space="preserve">23.1915683746338</t>
   </si>
   <si>
     <t xml:space="preserve">22.9989757537842</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9076061248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0199527740479</t>
+    <t xml:space="preserve">21.9076080322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0199508666992</t>
   </si>
   <si>
     <t xml:space="preserve">22.0761260986328</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5545177459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4742660522461</t>
+    <t xml:space="preserve">21.554515838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4742698669434</t>
   </si>
   <si>
     <t xml:space="preserve">21.6267414093018</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7711849212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7390880584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8674831390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8594570159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5255126953125</t>
+    <t xml:space="preserve">21.771183013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.739086151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8674812316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8594589233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5255146026611</t>
   </si>
   <si>
     <t xml:space="preserve">22.7421817779541</t>
@@ -1007,16 +1007,16 @@
     <t xml:space="preserve">22.3730430603027</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7181072235107</t>
+    <t xml:space="preserve">22.7181091308594</t>
   </si>
   <si>
     <t xml:space="preserve">22.8625545501709</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7100811004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5335388183594</t>
+    <t xml:space="preserve">22.7100849151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5335350036621</t>
   </si>
   <si>
     <t xml:space="preserve">22.6539096832275</t>
@@ -1025,61 +1025,61 @@
     <t xml:space="preserve">22.292797088623</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7551345825195</t>
+    <t xml:space="preserve">21.7551403045654</t>
   </si>
   <si>
     <t xml:space="preserve">21.2415504455566</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9927864074707</t>
+    <t xml:space="preserve">20.9927845001221</t>
   </si>
   <si>
     <t xml:space="preserve">20.9446353912354</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0730323791504</t>
+    <t xml:space="preserve">21.073034286499</t>
   </si>
   <si>
     <t xml:space="preserve">21.0489559173584</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6396961212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4310493469238</t>
+    <t xml:space="preserve">20.6396903991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4310474395752</t>
   </si>
   <si>
     <t xml:space="preserve">20.4872226715088</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8804340362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.864387512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7119140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.575496673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5995712280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6477184295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6156177520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5915431976318</t>
+    <t xml:space="preserve">20.8804378509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8643856048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7119178771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5754947662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5995693206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6477203369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6156158447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5915412902832</t>
   </si>
   <si>
     <t xml:space="preserve">20.3508033752441</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3427791595459</t>
+    <t xml:space="preserve">20.3427772521973</t>
   </si>
   <si>
     <t xml:space="preserve">20.2866058349609</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">20.7440166473389</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6717948913574</t>
+    <t xml:space="preserve">20.6717929840088</t>
   </si>
   <si>
     <t xml:space="preserve">20.4952487945557</t>
@@ -1097,28 +1097,28 @@
     <t xml:space="preserve">20.735990524292</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2174758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0168571472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3538990020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2335262298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9045143127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5594463348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5353717803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4711742401123</t>
+    <t xml:space="preserve">21.2174777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0168590545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3538970947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2335243225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9045104980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5594482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5353679656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4711723327637</t>
   </si>
   <si>
     <t xml:space="preserve">20.7520427703857</t>
@@ -1127,16 +1127,16 @@
     <t xml:space="preserve">21.3779716491699</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0650081634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2255039215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3699474334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9156322479248</t>
+    <t xml:space="preserve">21.0650043487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2255020141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3699493408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9156303405762</t>
   </si>
   <si>
     <t xml:space="preserve">21.4582195281982</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">21.8032855987549</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7952613830566</t>
+    <t xml:space="preserve">21.795259475708</t>
   </si>
   <si>
     <t xml:space="preserve">21.5785884857178</t>
@@ -1172,10 +1172,10 @@
     <t xml:space="preserve">22.0921764373779</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1082229614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1643981933594</t>
+    <t xml:space="preserve">22.108226776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.164400100708</t>
   </si>
   <si>
     <t xml:space="preserve">22.7742805480957</t>
@@ -1184,10 +1184,10 @@
     <t xml:space="preserve">22.7662582397461</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5897102355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5415630340576</t>
+    <t xml:space="preserve">22.5897121429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.541561126709</t>
   </si>
   <si>
     <t xml:space="preserve">22.4131641387939</t>
@@ -1196,22 +1196,22 @@
     <t xml:space="preserve">22.5174865722656</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1563758850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8353843688965</t>
+    <t xml:space="preserve">22.1563720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8353824615479</t>
   </si>
   <si>
     <t xml:space="preserve">22.5495891571045</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2526721954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2125453948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2594337463379</t>
+    <t xml:space="preserve">22.2526741027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2125492095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2594375610352</t>
   </si>
   <si>
     <t xml:space="preserve">19.9335155487061</t>
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">19.5403003692627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4921550750732</t>
+    <t xml:space="preserve">19.4921531677246</t>
   </si>
   <si>
     <t xml:space="preserve">19.4279518127441</t>
@@ -1244,55 +1244,55 @@
     <t xml:space="preserve">19.805118560791</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4199275970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7569694519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6606712341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1421604156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2304306030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4069766998291</t>
+    <t xml:space="preserve">19.4199295043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7569713592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6606693267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1421585083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2304286956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4069747924805</t>
   </si>
   <si>
     <t xml:space="preserve">20.4792003631592</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2545032501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9415397644043</t>
+    <t xml:space="preserve">20.2545013427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9415416717529</t>
   </si>
   <si>
     <t xml:space="preserve">20.0619106292725</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9254894256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9366092681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0971069335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8162384033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3989524841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6878433227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4390754699707</t>
+    <t xml:space="preserve">19.9254913330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9366130828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0971088409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8162403106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3989505767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6878414154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4390735626221</t>
   </si>
   <si>
     <t xml:space="preserve">20.2464809417725</t>
@@ -1301,43 +1301,43 @@
     <t xml:space="preserve">20.4631481170654</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5433959960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4100723266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0088329315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6508121490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1372299194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2816753387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.506368637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4421730041504</t>
+    <t xml:space="preserve">20.5433979034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4100685119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0088348388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6508159637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1372318267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2816734313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5063667297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4421691894531</t>
   </si>
   <si>
     <t xml:space="preserve">20.9606857299805</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3458728790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0890789031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6989631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8113079071045</t>
+    <t xml:space="preserve">21.3458709716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0890808105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6989650726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8113098144531</t>
   </si>
   <si>
     <t xml:space="preserve">21.7792091369629</t>
@@ -1349,16 +1349,16 @@
     <t xml:space="preserve">21.7471103668213</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2495765686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5322780609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3236312866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5001773834229</t>
+    <t xml:space="preserve">21.2495746612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5322742462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3236331939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5001754760742</t>
   </si>
   <si>
     <t xml:space="preserve">19.5162258148193</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">20.0458602905273</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0940132141113</t>
+    <t xml:space="preserve">20.0940093994141</t>
   </si>
   <si>
     <t xml:space="preserve">19.7248706817627</t>
@@ -1379,13 +1379,13 @@
     <t xml:space="preserve">19.403881072998</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4841289520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1631355285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8260955810547</t>
+    <t xml:space="preserve">19.4841270446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1631374359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.826099395752</t>
   </si>
   <si>
     <t xml:space="preserve">18.6014041900635</t>
@@ -1394,16 +1394,16 @@
     <t xml:space="preserve">18.0075721740723</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5853519439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7137508392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9977149963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1261081695557</t>
+    <t xml:space="preserve">18.5853538513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7137489318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9977111816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1261100769043</t>
   </si>
   <si>
     <t xml:space="preserve">20.7199401855469</t>
@@ -1412,19 +1412,19 @@
     <t xml:space="preserve">20.1903057098389</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7730178833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8372173309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8211708068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4359798431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1310405731201</t>
+    <t xml:space="preserve">19.7730197906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8372192382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8211688995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4359760284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1310386657715</t>
   </si>
   <si>
     <t xml:space="preserve">19.3557300567627</t>
@@ -1433,49 +1433,49 @@
     <t xml:space="preserve">19.5483264923096</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9174633026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5804252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0186901092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0026435852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8421459197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0828876495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8853645324707</t>
+    <t xml:space="preserve">19.9174652099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5804214477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0186920166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0026416778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8421478271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0828895568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.885368347168</t>
   </si>
   <si>
     <t xml:space="preserve">20.5112953186035</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1582050323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8936653137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6596565246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5760822296143</t>
+    <t xml:space="preserve">20.1582088470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8936672210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6596546173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5760803222656</t>
   </si>
   <si>
     <t xml:space="preserve">20.6763706207275</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7265148162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8435192108154</t>
+    <t xml:space="preserve">20.7265129089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8435211181641</t>
   </si>
   <si>
     <t xml:space="preserve">20.8268070220947</t>
@@ -1496,31 +1496,31 @@
     <t xml:space="preserve">21.0942440032959</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9772415161133</t>
+    <t xml:space="preserve">20.9772396087646</t>
   </si>
   <si>
     <t xml:space="preserve">20.7766609191895</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4757900238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6429424285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5259380340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2584972381592</t>
+    <t xml:space="preserve">20.4757919311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6429405212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.525936126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2584991455078</t>
   </si>
   <si>
     <t xml:space="preserve">20.1247787475586</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1916389465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.924201965332</t>
+    <t xml:space="preserve">20.1916370391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9241981506348</t>
   </si>
   <si>
     <t xml:space="preserve">19.5063247680664</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">20.2417831420898</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8769493103027</t>
+    <t xml:space="preserve">20.8769512176514</t>
   </si>
   <si>
     <t xml:space="preserve">20.7933750152588</t>
@@ -1541,22 +1541,22 @@
     <t xml:space="preserve">20.8100929260254</t>
   </si>
   <si>
-    <t xml:space="preserve">20.592794418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6930847167969</t>
+    <t xml:space="preserve">20.5927925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6930866241455</t>
   </si>
   <si>
     <t xml:space="preserve">20.3420734405518</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4925060272217</t>
+    <t xml:space="preserve">20.4925079345703</t>
   </si>
   <si>
     <t xml:space="preserve">20.5593662261963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7570495605469</t>
+    <t xml:space="preserve">19.7570514678955</t>
   </si>
   <si>
     <t xml:space="preserve">19.8740558624268</t>
@@ -1568,16 +1568,16 @@
     <t xml:space="preserve">20.2919292449951</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0244884490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.94091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.108060836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2752113342285</t>
+    <t xml:space="preserve">20.024486541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9409141540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1080627441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2752151489258</t>
   </si>
   <si>
     <t xml:space="preserve">20.3922157287598</t>
@@ -1586,25 +1586,25 @@
     <t xml:space="preserve">20.057918548584</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4256458282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.074634552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8239116668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6901893615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0273818969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2475738525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3144378662109</t>
+    <t xml:space="preserve">20.4256477355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0746307373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8239097595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6901912689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0273857116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2475776672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3144359588623</t>
   </si>
   <si>
     <t xml:space="preserve">23.1000347137451</t>
@@ -1616,31 +1616,31 @@
     <t xml:space="preserve">23.2671852111816</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5847682952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5346240997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.217041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8660278320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7991676330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8325977325439</t>
+    <t xml:space="preserve">23.5847702026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5346221923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2170429229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8660259246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7991695404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8325958251953</t>
   </si>
   <si>
     <t xml:space="preserve">22.5484447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6153030395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9328880310059</t>
+    <t xml:space="preserve">22.6153049468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9328842163086</t>
   </si>
   <si>
     <t xml:space="preserve">23.1167488098145</t>
@@ -1649,13 +1649,13 @@
     <t xml:space="preserve">23.1501808166504</t>
   </si>
   <si>
-    <t xml:space="preserve">23.250467300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4009017944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.618200302124</t>
+    <t xml:space="preserve">23.2504711151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4009056091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6181983947754</t>
   </si>
   <si>
     <t xml:space="preserve">23.5011940002441</t>
@@ -1670,16 +1670,16 @@
     <t xml:space="preserve">23.0833206176758</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8994579315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5651588439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5818729400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3311519622803</t>
+    <t xml:space="preserve">22.8994560241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5651569366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5818748474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3311462402344</t>
   </si>
   <si>
     <t xml:space="preserve">22.815881729126</t>
@@ -1691,43 +1691,43 @@
     <t xml:space="preserve">23.1334648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9663143157959</t>
+    <t xml:space="preserve">22.9663162231445</t>
   </si>
   <si>
     <t xml:space="preserve">23.6850566864014</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3006153106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4343376159668</t>
+    <t xml:space="preserve">23.3006134033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4343357086182</t>
   </si>
   <si>
     <t xml:space="preserve">22.9997463226318</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8493118286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9496021270752</t>
+    <t xml:space="preserve">22.8493137359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9495983123779</t>
   </si>
   <si>
     <t xml:space="preserve">21.7628421783447</t>
   </si>
   <si>
-    <t xml:space="preserve">21.461971282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0440979003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7098026275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.91037940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6625499725342</t>
+    <t xml:space="preserve">21.4619750976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0440998077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7098007202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9103813171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6625518798828</t>
   </si>
   <si>
     <t xml:space="preserve">21.2279624938965</t>
@@ -1736,19 +1736,19 @@
     <t xml:space="preserve">21.4285430908203</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9270973205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3616790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5121154785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9605236053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8573379516602</t>
+    <t xml:space="preserve">20.9270935058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3616809844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5121173858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9605255126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8573398590088</t>
   </si>
   <si>
     <t xml:space="preserve">19.5397548675537</t>
@@ -1757,31 +1757,31 @@
     <t xml:space="preserve">18.9547348022461</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5564708709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0550212860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4394664764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3893203735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2556018829346</t>
+    <t xml:space="preserve">19.5564727783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.055025100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4394645690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3893222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2556037902832</t>
   </si>
   <si>
     <t xml:space="preserve">19.3057479858398</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3726062774658</t>
+    <t xml:space="preserve">19.3726043701172</t>
   </si>
   <si>
     <t xml:space="preserve">18.8042984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6037178039551</t>
+    <t xml:space="preserve">18.6037197113037</t>
   </si>
   <si>
     <t xml:space="preserve">18.6872959136963</t>
@@ -1790,7 +1790,7 @@
     <t xml:space="preserve">18.6705799102783</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7040061950684</t>
+    <t xml:space="preserve">18.704008102417</t>
   </si>
   <si>
     <t xml:space="preserve">18.8878746032715</t>
@@ -1799,43 +1799,43 @@
     <t xml:space="preserve">19.2221698760986</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6734752655029</t>
+    <t xml:space="preserve">19.6734771728516</t>
   </si>
   <si>
     <t xml:space="preserve">19.6567611694336</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8907699584961</t>
+    <t xml:space="preserve">19.8907680511475</t>
   </si>
   <si>
     <t xml:space="preserve">20.0913505554199</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8406276702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5899028778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.088451385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7737655639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6400489807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4561805725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9213008880615</t>
+    <t xml:space="preserve">19.8406257629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.589900970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0884532928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7737636566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.640043258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4561824798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9213027954102</t>
   </si>
   <si>
     <t xml:space="preserve">19.3391761779785</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5201454162598</t>
+    <t xml:space="preserve">18.5201473236084</t>
   </si>
   <si>
     <t xml:space="preserve">17.5506801605225</t>
@@ -1844,34 +1844,34 @@
     <t xml:space="preserve">18.0019836425781</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9016933441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4699993133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.235990524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4365711212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0412044525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3086433410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.991060256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3253574371338</t>
+    <t xml:space="preserve">17.9016914367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4700031280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2359886169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4365673065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.041202545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3086414337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9910583496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3253555297852</t>
   </si>
   <si>
     <t xml:space="preserve">18.2861347198486</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2694206237793</t>
+    <t xml:space="preserve">18.2694225311279</t>
   </si>
   <si>
     <t xml:space="preserve">18.219274520874</t>
@@ -1880,61 +1880,61 @@
     <t xml:space="preserve">18.4198570251465</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6538619995117</t>
+    <t xml:space="preserve">18.6538639068604</t>
   </si>
   <si>
     <t xml:space="preserve">18.25270652771</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3529949188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5368614196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7541522979736</t>
+    <t xml:space="preserve">18.3529968261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5368633270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7541542053223</t>
   </si>
   <si>
     <t xml:space="preserve">18.6371479034424</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1553134918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4060363769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2723121643066</t>
+    <t xml:space="preserve">19.1553115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4060344696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2723178863525</t>
   </si>
   <si>
     <t xml:space="preserve">18.9714488983154</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3558902740479</t>
+    <t xml:space="preserve">19.3558883666992</t>
   </si>
   <si>
     <t xml:space="preserve">19.0215930938721</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3224620819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7403354644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1749248504639</t>
+    <t xml:space="preserve">19.3224639892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7403373718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1749229431152</t>
   </si>
   <si>
     <t xml:space="preserve">18.7875823974609</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9380168914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0077743530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2250690460205</t>
+    <t xml:space="preserve">18.9380187988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0077724456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2250709533691</t>
   </si>
   <si>
     <t xml:space="preserve">21.5789775848389</t>
@@ -1946,19 +1946,19 @@
     <t xml:space="preserve">19.2054576873779</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0354118347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6509704589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4336757659912</t>
+    <t xml:space="preserve">18.0354099273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6509666442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4336738586426</t>
   </si>
   <si>
     <t xml:space="preserve">17.5841083526611</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1328029632568</t>
+    <t xml:space="preserve">17.1328067779541</t>
   </si>
   <si>
     <t xml:space="preserve">16.5477828979492</t>
@@ -1967,85 +1967,85 @@
     <t xml:space="preserve">16.1716957092285</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9961881637573</t>
+    <t xml:space="preserve">15.996190071106</t>
   </si>
   <si>
     <t xml:space="preserve">16.3221321105957</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8791847229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7939510345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7683820724487</t>
+    <t xml:space="preserve">15.8791818618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7939519882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7683792114258</t>
   </si>
   <si>
     <t xml:space="preserve">15.7769031524658</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3081121444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4018716812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4359655380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5382490158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1632165908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3336839675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0524091720581</t>
+    <t xml:space="preserve">15.3081130981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4018726348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4359664916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5382471084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.163215637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3336820602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0524101257324</t>
   </si>
   <si>
     <t xml:space="preserve">15.1717376708984</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3507308959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5552930831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.640528678894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6490545272827</t>
+    <t xml:space="preserve">15.3507318496704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5552940368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6405296325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6490526199341</t>
   </si>
   <si>
     <t xml:space="preserve">15.6320056915283</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5808658599854</t>
+    <t xml:space="preserve">15.5808629989624</t>
   </si>
   <si>
     <t xml:space="preserve">15.4103965759277</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0609331130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8904647827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9842224121094</t>
+    <t xml:space="preserve">15.0609340667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8904638290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9842252731323</t>
   </si>
   <si>
     <t xml:space="preserve">15.0438861846924</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3763027191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4274425506592</t>
+    <t xml:space="preserve">15.3763017654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4274435043335</t>
   </si>
   <si>
     <t xml:space="preserve">15.282546043396</t>
@@ -2057,73 +2057,73 @@
     <t xml:space="preserve">15.1120748519897</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1546945571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.325159072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3592557907104</t>
+    <t xml:space="preserve">15.1546936035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3251619338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3592538833618</t>
   </si>
   <si>
     <t xml:space="preserve">14.9671754837036</t>
   </si>
   <si>
-    <t xml:space="preserve">14.745566368103</t>
+    <t xml:space="preserve">14.7455673217773</t>
   </si>
   <si>
     <t xml:space="preserve">14.6091909408569</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6518106460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5154323577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7114725112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6347627639771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5410032272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3534870147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3449630737305</t>
+    <t xml:space="preserve">14.6518087387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5154342651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7114744186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6347618103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5410041809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3534898757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3449640274048</t>
   </si>
   <si>
     <t xml:space="preserve">14.4472465515137</t>
   </si>
   <si>
-    <t xml:space="preserve">14.438720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7540912628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4642934799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4813375473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3620128631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2484474182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4956312179565</t>
+    <t xml:space="preserve">14.4387235641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7540893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4642915725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4813404083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3620109558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2484502792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4956283569336</t>
   </si>
   <si>
     <t xml:space="preserve">15.0268421173096</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0012731552124</t>
+    <t xml:space="preserve">15.0012693405151</t>
   </si>
   <si>
     <t xml:space="preserve">14.6859016418457</t>
@@ -2135,82 +2135,82 @@
     <t xml:space="preserve">13.9784555435181</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4046268463135</t>
+    <t xml:space="preserve">14.4046287536621</t>
   </si>
   <si>
     <t xml:space="preserve">15.035364151001</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1376447677612</t>
+    <t xml:space="preserve">15.1376457214355</t>
   </si>
   <si>
     <t xml:space="preserve">14.8308019638062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9586515426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2399253845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8109979629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4843502044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.046895980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7911968231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5269680023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0128021240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5781078338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3138790130615</t>
+    <t xml:space="preserve">14.9586505889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2399272918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.810996055603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4843521118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0468978881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7911949157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5269660949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0128040313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5781097412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3138809204102</t>
   </si>
   <si>
     <t xml:space="preserve">16.2371692657471</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9303255081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9218053817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3933486938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9416046142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5239582061768</t>
+    <t xml:space="preserve">15.9303274154663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9218044281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3933477401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9416084289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5239572525024</t>
   </si>
   <si>
     <t xml:space="preserve">14.9330816268921</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6603326797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2512035369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1318769454956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.617714881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4557676315308</t>
+    <t xml:space="preserve">14.6603317260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2512054443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1318788528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6177139282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4557695388794</t>
   </si>
   <si>
     <t xml:space="preserve">14.5580492019653</t>
@@ -2219,31 +2219,31 @@
     <t xml:space="preserve">14.5750970840454</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7370452880859</t>
+    <t xml:space="preserve">14.7370443344116</t>
   </si>
   <si>
     <t xml:space="preserve">14.7796602249146</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8393249511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8478488922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6688537597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2341613769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.14040184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0636901855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8222780227661</t>
+    <t xml:space="preserve">14.8393239974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8478479385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6688547134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2341594696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1404008865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0636911392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8222761154175</t>
   </si>
   <si>
     <t xml:space="preserve">14.626238822937</t>
@@ -2252,31 +2252,31 @@
     <t xml:space="preserve">15.0183172225952</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1291227340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2058324813843</t>
+    <t xml:space="preserve">15.1291208267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2058334350586</t>
   </si>
   <si>
     <t xml:space="preserve">15.5467710494995</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8195219039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0326061248779</t>
+    <t xml:space="preserve">15.8195199966431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0326080322266</t>
   </si>
   <si>
     <t xml:space="preserve">16.4502544403076</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4928741455078</t>
+    <t xml:space="preserve">16.4928722381592</t>
   </si>
   <si>
     <t xml:space="preserve">16.0155620574951</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1519336700439</t>
+    <t xml:space="preserve">16.1519374847412</t>
   </si>
   <si>
     <t xml:space="preserve">16.2030735015869</t>
@@ -2297,46 +2297,46 @@
     <t xml:space="preserve">16.2627410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1263656616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1178417205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1945514678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2286472320557</t>
+    <t xml:space="preserve">16.1263675689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1178436279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1945533752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2286491394043</t>
   </si>
   <si>
     <t xml:space="preserve">16.168981552124</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0666999816895</t>
+    <t xml:space="preserve">16.0667018890381</t>
   </si>
   <si>
     <t xml:space="preserve">16.2797889709473</t>
   </si>
   <si>
-    <t xml:space="preserve">16.109317779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7087163925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6746196746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9729433059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7428092956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3422069549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2910671234131</t>
+    <t xml:space="preserve">16.1093158721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7087154388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6746244430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9729423522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7428102493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.342209815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2910652160645</t>
   </si>
   <si>
     <t xml:space="preserve">15.1035509109497</t>
@@ -2345,19 +2345,19 @@
     <t xml:space="preserve">14.5665740966797</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2853012084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2426815032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5949020385742</t>
+    <t xml:space="preserve">14.2853002548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2426834106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5949010848999</t>
   </si>
   <si>
     <t xml:space="preserve">13.7057065963745</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6944255828857</t>
+    <t xml:space="preserve">14.6944265365601</t>
   </si>
   <si>
     <t xml:space="preserve">14.5069093704224</t>
@@ -2366,22 +2366,22 @@
     <t xml:space="preserve">15.0694580078125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4615364074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4444932937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4700584411621</t>
+    <t xml:space="preserve">15.4615345001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4444904327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4700593948364</t>
   </si>
   <si>
     <t xml:space="preserve">15.6149578094482</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2740230560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2995891571045</t>
+    <t xml:space="preserve">15.274022102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2995910644531</t>
   </si>
   <si>
     <t xml:space="preserve">13.7142295837402</t>
@@ -2390,37 +2390,37 @@
     <t xml:space="preserve">13.3818140029907</t>
   </si>
   <si>
-    <t xml:space="preserve">13.552282333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1772518157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2965793609619</t>
+    <t xml:space="preserve">13.5522832870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1772537231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2965803146362</t>
   </si>
   <si>
     <t xml:space="preserve">13.2624864578247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0323543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7596035003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6232271194458</t>
+    <t xml:space="preserve">13.0323534011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7596025466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6232280731201</t>
   </si>
   <si>
     <t xml:space="preserve">12.359001159668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6600790023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1912889480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8333034515381</t>
+    <t xml:space="preserve">11.6600780487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1912879943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8333044052124</t>
   </si>
   <si>
     <t xml:space="preserve">9.74230098724365</t>
@@ -2429,37 +2429,37 @@
     <t xml:space="preserve">10.6543111801147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.643030166626</t>
+    <t xml:space="preserve">11.6430311203003</t>
   </si>
   <si>
     <t xml:space="preserve">11.8220243453979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6686000823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0351085662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3306741714478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7227535247803</t>
+    <t xml:space="preserve">11.6686010360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0351104736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3306732177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.722752571106</t>
   </si>
   <si>
     <t xml:space="preserve">14.2767772674561</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0749702453613</t>
+    <t xml:space="preserve">13.0749711990356</t>
   </si>
   <si>
     <t xml:space="preserve">13.5011434555054</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4500017166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9897375106812</t>
+    <t xml:space="preserve">13.4500026702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9897356033325</t>
   </si>
   <si>
     <t xml:space="preserve">13.0834941864014</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">12.4953765869141</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0238285064697</t>
+    <t xml:space="preserve">13.023829460144</t>
   </si>
   <si>
     <t xml:space="preserve">13.3562450408936</t>
@@ -2483,157 +2483,157 @@
     <t xml:space="preserve">13.6119470596313</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8192672729492</t>
+    <t xml:space="preserve">12.8192682266235</t>
   </si>
   <si>
     <t xml:space="preserve">12.6999387741089</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9045038223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0664463043213</t>
+    <t xml:space="preserve">12.9045009613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0664472579956</t>
   </si>
   <si>
     <t xml:space="preserve">13.2113456726074</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3988618850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3136253356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8079891204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8932218551636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9358396530151</t>
+    <t xml:space="preserve">13.3988628387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.313627243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8079872131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8932209014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9358386993408</t>
   </si>
   <si>
     <t xml:space="preserve">14.0551662445068</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8846988677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4898633956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7029485702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2000665664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4983863830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4131517410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1205997467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7711381912231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8563709259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4189186096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9388484954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7513341903687</t>
+    <t xml:space="preserve">13.8846998214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4898614883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7029495239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.200065612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.498387336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4131526947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1205987930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7711372375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.856372833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4189176559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9388494491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7513303756714</t>
   </si>
   <si>
     <t xml:space="preserve">16.6207237243652</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4161605834961</t>
+    <t xml:space="preserve">16.4161624908447</t>
   </si>
   <si>
     <t xml:space="preserve">16.2456932067871</t>
   </si>
   <si>
-    <t xml:space="preserve">16.544017791748</t>
+    <t xml:space="preserve">16.5440139770508</t>
   </si>
   <si>
     <t xml:space="preserve">16.7826690673828</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3707866668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.427698135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2629947662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0754776000977</t>
+    <t xml:space="preserve">17.3707904815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4276962280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.262996673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0754795074463</t>
   </si>
   <si>
     <t xml:space="preserve">18.6493053436279</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9050102233887</t>
+    <t xml:space="preserve">18.90500831604</t>
   </si>
   <si>
     <t xml:space="preserve">19.603931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6380252838135</t>
+    <t xml:space="preserve">19.6380290985107</t>
   </si>
   <si>
     <t xml:space="preserve">20.0641994476318</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8766841888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7744007110596</t>
+    <t xml:space="preserve">19.8766822814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7744026184082</t>
   </si>
   <si>
     <t xml:space="preserve">20.1494331359863</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0471534729004</t>
+    <t xml:space="preserve">20.0471515655518</t>
   </si>
   <si>
     <t xml:space="preserve">19.4846019744873</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8425884246826</t>
+    <t xml:space="preserve">19.8425903320312</t>
   </si>
   <si>
     <t xml:space="preserve">19.8084945678711</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7119808197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9506378173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6778869628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8483562469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8824481964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.052921295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9335918426514</t>
+    <t xml:space="preserve">20.7119789123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9506397247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6778888702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8483543395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8824501037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0529193878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9335899353027</t>
   </si>
   <si>
     <t xml:space="preserve">21.0870132446289</t>
@@ -2642,13 +2642,13 @@
     <t xml:space="preserve">21.1551990509033</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2915744781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2574806213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.223388671875</t>
+    <t xml:space="preserve">21.291576385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2574825286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2233867645264</t>
   </si>
   <si>
     <t xml:space="preserve">21.0699653625488</t>
@@ -2660,55 +2660,55 @@
     <t xml:space="preserve">20.8994960784912</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9676837921143</t>
+    <t xml:space="preserve">20.9676856994629</t>
   </si>
   <si>
     <t xml:space="preserve">20.7631225585938</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9165439605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1609668731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6382808685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.013313293457</t>
+    <t xml:space="preserve">20.9165420532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1609649658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6382827758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0133113861084</t>
   </si>
   <si>
     <t xml:space="preserve">23.9167976379395</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8145160675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9679393768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0020313262939</t>
+    <t xml:space="preserve">23.8145179748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9679355621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0020332336426</t>
   </si>
   <si>
     <t xml:space="preserve">23.5758590698242</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8656558990479</t>
+    <t xml:space="preserve">23.8656578063965</t>
   </si>
   <si>
     <t xml:space="preserve">23.7974681854248</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5247211456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5929050445557</t>
+    <t xml:space="preserve">23.5247192382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5929069519043</t>
   </si>
   <si>
     <t xml:space="preserve">23.6610946655273</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8486099243164</t>
+    <t xml:space="preserve">23.8486080169678</t>
   </si>
   <si>
     <t xml:space="preserve">23.6781425476074</t>
@@ -2717,13 +2717,13 @@
     <t xml:space="preserve">23.4394836425781</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7292823791504</t>
+    <t xml:space="preserve">23.7292804718018</t>
   </si>
   <si>
     <t xml:space="preserve">23.7463302612305</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6951847076416</t>
+    <t xml:space="preserve">23.6951885223389</t>
   </si>
   <si>
     <t xml:space="preserve">23.4906253814697</t>
@@ -2735,28 +2735,28 @@
     <t xml:space="preserve">23.1496887207031</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9849834442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8997535705566</t>
+    <t xml:space="preserve">23.9849853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8997497558594</t>
   </si>
   <si>
     <t xml:space="preserve">24.4963932037354</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2123622894287</t>
+    <t xml:space="preserve">25.2123603820801</t>
   </si>
   <si>
     <t xml:space="preserve">24.5304870605469</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1100788116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0647087097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4680633544922</t>
+    <t xml:space="preserve">25.1100826263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0647068023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4680652618408</t>
   </si>
   <si>
     <t xml:space="preserve">25.5533008575439</t>
@@ -2771,34 +2771,34 @@
     <t xml:space="preserve">25.0589408874512</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0759887695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8202819824219</t>
+    <t xml:space="preserve">25.0759868621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8202838897705</t>
   </si>
   <si>
     <t xml:space="preserve">24.8884716033936</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1953144073486</t>
+    <t xml:space="preserve">25.1953163146973</t>
   </si>
   <si>
     <t xml:space="preserve">24.7180023193359</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3487358093262</t>
+    <t xml:space="preserve">25.3487377166748</t>
   </si>
   <si>
     <t xml:space="preserve">25.2294082641602</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4339733123779</t>
+    <t xml:space="preserve">25.4339714050293</t>
   </si>
   <si>
     <t xml:space="preserve">25.3657855987549</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9453792572021</t>
+    <t xml:space="preserve">25.9453773498535</t>
   </si>
   <si>
     <t xml:space="preserve">26.8829593658447</t>
@@ -2810,118 +2810,118 @@
     <t xml:space="preserve">26.0306148529053</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9283313751221</t>
+    <t xml:space="preserve">25.9283332824707</t>
   </si>
   <si>
     <t xml:space="preserve">26.0135669708252</t>
   </si>
   <si>
-    <t xml:space="preserve">25.144172668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9566593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.422435760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2690162658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4053897857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4565315246582</t>
+    <t xml:space="preserve">25.1441745758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.956657409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4224395751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2690143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.405387878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4565334320068</t>
   </si>
   <si>
     <t xml:space="preserve">24.837329864502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0930328369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5703468322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6385345458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3600158691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.13840675354</t>
+    <t xml:space="preserve">25.0930309295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5703506469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6385364532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3600177764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1384086608887</t>
   </si>
   <si>
     <t xml:space="preserve">25.9112854003906</t>
   </si>
   <si>
-    <t xml:space="preserve">24.547534942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8315620422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5588111877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.12135887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5417652130127</t>
+    <t xml:space="preserve">24.5475311279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8315601348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5588130950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1213607788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5417671203613</t>
   </si>
   <si>
     <t xml:space="preserve">23.0985469818115</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2747840881348</t>
+    <t xml:space="preserve">24.2747821807861</t>
   </si>
   <si>
     <t xml:space="preserve">24.9396095275879</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2918300628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0702171325684</t>
+    <t xml:space="preserve">24.2918262481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0702209472656</t>
   </si>
   <si>
     <t xml:space="preserve">23.5076713562012</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3372001647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.183780670166</t>
+    <t xml:space="preserve">23.3372020721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1837787628174</t>
   </si>
   <si>
     <t xml:space="preserve">22.6894207000732</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1667327880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.286060333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2029075622559</t>
+    <t xml:space="preserve">23.1667346954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2860622406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2029094696045</t>
   </si>
   <si>
     <t xml:space="preserve">23.3768424987793</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6984939575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5941352844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8202495574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4202003479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7854652404785</t>
+    <t xml:space="preserve">22.6984977722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5941333770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8202514648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.420202255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7854614257812</t>
   </si>
   <si>
     <t xml:space="preserve">23.2898750305176</t>
@@ -2933,13 +2933,13 @@
     <t xml:space="preserve">22.8724308013916</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7506771087646</t>
+    <t xml:space="preserve">22.750675201416</t>
   </si>
   <si>
     <t xml:space="preserve">22.7158908843994</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2462673187256</t>
+    <t xml:space="preserve">22.246265411377</t>
   </si>
   <si>
     <t xml:space="preserve">22.33323097229</t>
@@ -2954,64 +2954,64 @@
     <t xml:space="preserve">24.5769920349121</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3596973419189</t>
+    <t xml:space="preserve">25.3597011566162</t>
   </si>
   <si>
     <t xml:space="preserve">25.551025390625</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1945896148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4207019805908</t>
+    <t xml:space="preserve">26.1945858001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4207000732422</t>
   </si>
   <si>
     <t xml:space="preserve">25.7597503662109</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4033069610596</t>
+    <t xml:space="preserve">26.4033088684082</t>
   </si>
   <si>
     <t xml:space="preserve">27.0294723510742</t>
   </si>
   <si>
-    <t xml:space="preserve">27.186014175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1164417266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0120811462402</t>
+    <t xml:space="preserve">27.1860160827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1164436340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.012077331543</t>
   </si>
   <si>
     <t xml:space="preserve">28.1426563262939</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8036060333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0992965698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3775901794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5863151550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0385494232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2210521697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0818996429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7688217163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4035568237305</t>
+    <t xml:space="preserve">28.8036079406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0992984771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3775939941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5863208770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0385456085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2210483551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.081901550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7688236236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4035587310791</t>
   </si>
   <si>
     <t xml:space="preserve">27.6904258728027</t>
@@ -3020,94 +3020,94 @@
     <t xml:space="preserve">26.7859649658203</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5946350097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.412130355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6294250488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6208515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6468162536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5250606536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2034091949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.307767868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7078189849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1081199645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1340827941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0471229553223</t>
+    <t xml:space="preserve">26.5946369171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4121284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6294231414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6208534240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6468181610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5250644683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2034072875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3077697753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.707820892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1081218719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1340847015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.047119140625</t>
   </si>
   <si>
     <t xml:space="preserve">29.2906284332275</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8905792236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3080177307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8560409545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7342853546143</t>
+    <t xml:space="preserve">28.8905754089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3080215454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8560390472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7342796325684</t>
   </si>
   <si>
     <t xml:space="preserve">30.2298736572266</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3690204620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4385948181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0559406280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2994537353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9515819549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6125354766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9951858520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6039600372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8300724029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5691757202148</t>
+    <t xml:space="preserve">30.3690223693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4385986328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0559425354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2994480133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9515781402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6125316619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9951877593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6039619445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8300762176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5691738128662</t>
   </si>
   <si>
     <t xml:space="preserve">31.8648643493652</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7778930664062</t>
+    <t xml:space="preserve">31.7778949737549</t>
   </si>
   <si>
     <t xml:space="preserve">31.4995975494385</t>
@@ -3116,139 +3116,139 @@
     <t xml:space="preserve">32.0387992858887</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6909275054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3430595397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4474201202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2734794616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7605018615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7083206176758</t>
+    <t xml:space="preserve">31.6909236907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3430633544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.447416305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2734813690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7605037689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7083187103271</t>
   </si>
   <si>
     <t xml:space="preserve">31.5865650177002</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7431049346924</t>
+    <t xml:space="preserve">31.743106842041</t>
   </si>
   <si>
     <t xml:space="preserve">31.6387500762939</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6735343933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3866729736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5605964660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8474674224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5432052612305</t>
+    <t xml:space="preserve">31.6735305786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3866653442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.560604095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.847469329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5432090759277</t>
   </si>
   <si>
     <t xml:space="preserve">31.8996486663818</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5169944763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7952899932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8126831054688</t>
+    <t xml:space="preserve">31.5169925689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7952880859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.812686920166</t>
   </si>
   <si>
     <t xml:space="preserve">31.6213531494141</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4822044372559</t>
+    <t xml:space="preserve">31.4822082519531</t>
   </si>
   <si>
     <t xml:space="preserve">31.3952388763428</t>
   </si>
   <si>
-    <t xml:space="preserve">32.155330657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9081134796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7845115661621</t>
+    <t xml:space="preserve">32.1553268432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9081153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7845077514648</t>
   </si>
   <si>
     <t xml:space="preserve">32.1376724243164</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1729850769043</t>
+    <t xml:space="preserve">32.172981262207</t>
   </si>
   <si>
     <t xml:space="preserve">32.2612800598145</t>
   </si>
   <si>
-    <t xml:space="preserve">32.278938293457</t>
+    <t xml:space="preserve">32.2789344787598</t>
   </si>
   <si>
     <t xml:space="preserve">31.7491931915283</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7668533325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8727970123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6674118041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0029144287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4443702697754</t>
+    <t xml:space="preserve">31.7668514251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8728008270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.667407989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0029182434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4443664550781</t>
   </si>
   <si>
     <t xml:space="preserve">33.3031044006348</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3096122741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9982795715332</t>
+    <t xml:space="preserve">34.3096084594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9982757568359</t>
   </si>
   <si>
     <t xml:space="preserve">34.9806175231934</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2808074951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7863807678223</t>
+    <t xml:space="preserve">35.2808036804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.786376953125</t>
   </si>
   <si>
     <t xml:space="preserve">33.9564514160156</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7975273132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3384170532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9499435424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1794967651367</t>
+    <t xml:space="preserve">33.7975311279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3384132385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9499397277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.179500579834</t>
   </si>
   <si>
     <t xml:space="preserve">33.2148094177246</t>
@@ -3260,22 +3260,22 @@
     <t xml:space="preserve">32.4378623962402</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0205764770508</t>
+    <t xml:space="preserve">33.0205726623535</t>
   </si>
   <si>
     <t xml:space="preserve">32.843994140625</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1441841125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0317230224609</t>
+    <t xml:space="preserve">33.1441802978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0317192077637</t>
   </si>
   <si>
     <t xml:space="preserve">32.3319091796875</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7027244567871</t>
+    <t xml:space="preserve">32.7027282714844</t>
   </si>
   <si>
     <t xml:space="preserve">33.2677879333496</t>
@@ -3284,19 +3284,19 @@
     <t xml:space="preserve">33.4267120361328</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8616561889648</t>
+    <t xml:space="preserve">32.8616523742676</t>
   </si>
   <si>
     <t xml:space="preserve">32.2083015441895</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2017917633057</t>
+    <t xml:space="preserve">31.2017879486084</t>
   </si>
   <si>
     <t xml:space="preserve">31.1135025024414</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9610900878906</t>
+    <t xml:space="preserve">31.9610939025879</t>
   </si>
   <si>
     <t xml:space="preserve">33.126522064209</t>
@@ -3305,31 +3305,31 @@
     <t xml:space="preserve">32.9322814941406</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9257755279541</t>
+    <t xml:space="preserve">31.9257717132568</t>
   </si>
   <si>
     <t xml:space="preserve">32.5438041687012</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0270843505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0800552368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3449287414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3802375793457</t>
+    <t xml:space="preserve">34.0270805358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8681602478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0800514221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3449325561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.380241394043</t>
   </si>
   <si>
     <t xml:space="preserve">34.1330299377441</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5215072631836</t>
+    <t xml:space="preserve">34.5215110778809</t>
   </si>
   <si>
     <t xml:space="preserve">34.150691986084</t>
@@ -3338,16 +3338,16 @@
     <t xml:space="preserve">34.2036628723145</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1153755187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.938793182373</t>
+    <t xml:space="preserve">34.1153678894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9387893676758</t>
   </si>
   <si>
     <t xml:space="preserve">33.6209526062012</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6915817260742</t>
+    <t xml:space="preserve">33.691577911377</t>
   </si>
   <si>
     <t xml:space="preserve">34.2919540405273</t>
@@ -3359,70 +3359,70 @@
     <t xml:space="preserve">32.914623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1971549987793</t>
+    <t xml:space="preserve">33.197151184082</t>
   </si>
   <si>
     <t xml:space="preserve">33.5149993896484</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5503120422363</t>
+    <t xml:space="preserve">33.5503158569336</t>
   </si>
   <si>
     <t xml:space="preserve">33.815185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6451187133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1395378112793</t>
+    <t xml:space="preserve">34.6451148986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1395416259766</t>
   </si>
   <si>
     <t xml:space="preserve">34.8570098876953</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6804275512695</t>
+    <t xml:space="preserve">34.6804313659668</t>
   </si>
   <si>
     <t xml:space="preserve">35.0865669250488</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3272743225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2371063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4248371124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1776275634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0716800689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.559591293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.61256980896</t>
+    <t xml:space="preserve">34.3272666931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2371101379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.424840927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1776256561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0716781616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5595970153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6125679016113</t>
   </si>
   <si>
     <t xml:space="preserve">29.6478862762451</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2306003570557</t>
+    <t xml:space="preserve">30.2306022644043</t>
   </si>
   <si>
     <t xml:space="preserve">29.3476982116699</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0121917724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2882137298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8467617034912</t>
+    <t xml:space="preserve">29.0121936798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2882118225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8467636108398</t>
   </si>
   <si>
     <t xml:space="preserve">27.4406261444092</t>
@@ -3437,25 +3437,25 @@
     <t xml:space="preserve">27.7937870025635</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6348648071289</t>
+    <t xml:space="preserve">27.6348628997803</t>
   </si>
   <si>
     <t xml:space="preserve">28.0763149261475</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0410022735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.305871963501</t>
+    <t xml:space="preserve">28.0410003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3058738708496</t>
   </si>
   <si>
     <t xml:space="preserve">29.2240905761719</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1004848480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4713020324707</t>
+    <t xml:space="preserve">29.1004829406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4713039398193</t>
   </si>
   <si>
     <t xml:space="preserve">29.135799407959</t>
@@ -3467,43 +3467,43 @@
     <t xml:space="preserve">29.8244647979736</t>
   </si>
   <si>
-    <t xml:space="preserve">29.948070526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7891521453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2417488098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8421192169189</t>
+    <t xml:space="preserve">29.9480686187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7891483306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2417469024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8421211242676</t>
   </si>
   <si>
     <t xml:space="preserve">30.0010452270508</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9833850860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5661010742188</t>
+    <t xml:space="preserve">29.9833869934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.566104888916</t>
   </si>
   <si>
     <t xml:space="preserve">30.9545822143555</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1952857971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1246490478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3300399780273</t>
+    <t xml:space="preserve">30.1952819824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1246528625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3300380706787</t>
   </si>
   <si>
     <t xml:space="preserve">27.2287292480469</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8402500152588</t>
+    <t xml:space="preserve">26.8402519226074</t>
   </si>
   <si>
     <t xml:space="preserve">26.9462013244629</t>
@@ -3515,13 +3515,13 @@
     <t xml:space="preserve">27.2817039489746</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7231540679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3876533508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6989879608154</t>
+    <t xml:space="preserve">27.7231559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3876552581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6989898681641</t>
   </si>
   <si>
     <t xml:space="preserve">26.8755683898926</t>
@@ -3530,10 +3530,10 @@
     <t xml:space="preserve">27.0698070526123</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7807712554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4341201782227</t>
+    <t xml:space="preserve">25.7807693481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.434118270874</t>
   </si>
   <si>
     <t xml:space="preserve">26.1162719726562</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">26.3634853363037</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1339302062988</t>
+    <t xml:space="preserve">26.1339282989502</t>
   </si>
   <si>
     <t xml:space="preserve">26.3987998962402</t>
@@ -3554,1980 +3554,1980 @@
     <t xml:space="preserve">27.1404399871826</t>
   </si>
   <si>
-    <t xml:space="preserve">26.575382232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7519588470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3105087280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4694328308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8225936889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2110729217529</t>
+    <t xml:space="preserve">26.5753841400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7519607543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.310510635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4694309234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8225917816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2110710144043</t>
   </si>
   <si>
     <t xml:space="preserve">27.0521488189697</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3523387908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9815139770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9350509643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8291034698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.405309677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7761306762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6525211334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3699932098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4164562225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9155216217041</t>
+    <t xml:space="preserve">27.3523349761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9815158843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9350528717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8291015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4053134918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7761287689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6525249481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3699913024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4164581298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9155235290527</t>
   </si>
   <si>
     <t xml:space="preserve">25.0214729309082</t>
   </si>
   <si>
+    <t xml:space="preserve">24.721284866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8978672027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.268684387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5447044372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.10325050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8383808135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6924800872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.451774597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5112590789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9703674316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2993602752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9285449981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5289192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.475944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9638576507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3811416625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8932247161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1757564544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7872772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0986156463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4629230499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8095760345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2333698272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1274185180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7389450073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1738834381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4080772399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4192295074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3662528991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6906089782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.066068649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9424610137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3551044464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7723903656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7788982391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4610538482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2844715118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2315006256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8077030181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5251750946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4722023010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5604915618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9907970428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3374462127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8430213928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7547302246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7900485992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5958080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3839111328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9601192474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1896724700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1367015838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4015693664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7658805847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8365116119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0595569610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9359512329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3773994445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5186653137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8653182983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0065822601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7835369110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5363254547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.041898727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1943111419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4238662719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.777027130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3420886993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3355751037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5474700927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6710796356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.911153793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0677719116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4711265563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1311645507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3878479003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9012107849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6995334625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.314510345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6445331573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0944976806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4061832427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1678371429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5811367034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3061199188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3710670471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7560882568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.012767791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0960502624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0861053466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.729362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9493751525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2801704406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.261833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1793270111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2343311309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0968246459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7576389312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2626094818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1617698669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1709365844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9875946044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3817844390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7851390838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0601558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.188497543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4635105133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9501476287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4092845916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6843013763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9043121337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0693225860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9593181610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1334934234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8676452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3359470367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8500862121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8218078613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5284595489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1151599884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8852043151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6560249328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6376914978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8859806060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4726810455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5643520355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6835269927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6651916503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2159996032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3351726531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9868183135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0784893035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8584766387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4001178741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9967613220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9417572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0425968170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0150966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6392383575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9142560958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0525398254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2542181015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2175512313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1992158889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6117372512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0059261322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6942434310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9883699417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5758438110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5850114822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.860803604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8058004379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6041231155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3841094970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5857877731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7599649429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.924973487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.310772895813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8149671554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5032825469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8883047103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.512451171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6591243743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3382730484009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4482803344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8516368865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5307846069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8424692153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1908226013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3466653823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.603346824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1816558837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5483427047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8233594894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5659017562866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7217426300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9050884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1526050567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7026348114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.243501663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.509349822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2427253723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5528583526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.717866897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4161262512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.15944480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0494384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6178035736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2595081329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7094764709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3794574737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.562801361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.892822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6544742584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8561515808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4527950286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5261325836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7278099060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3695125579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.837818145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3244552612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9760990142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9577655792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2144470214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6728057861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.232780456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0578308105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1128330230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2961769104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5161895751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8179321289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2495670318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.992883682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7728691101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8828773498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.047887802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8095378875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7362041473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7828140258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7644786834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2511177062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8660926818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3977928161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3427886962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4894618988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5994663238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3511810302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8744850158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1495018005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0761623382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0394954681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9745483398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2128963470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5795841217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6345901489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6529216766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6162528991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5429172515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6811981201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3045673370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6628646850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4245185852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5711936950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.966157913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5077972412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3611240386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5444641113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9294891357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0211620330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6460800170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4444026947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.481071472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.609411239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4077339172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3343944549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9210948944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.287784576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1961135864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1044406890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7201499938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6169300079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8756294250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5378246307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7348785400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.641040802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2469329833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1437168121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1718654632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0498809814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0029621124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0311126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9560451507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.89035987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9091262817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.078031539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1852855682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2885074615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5659732818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0069999694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.922550201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8662490844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8005599975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5753593444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7536468505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9319324493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9882316589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3354263305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5137100219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7858333587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5230960845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7482986450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4855613708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7817974090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8474807739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4386425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0056915283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1558284759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3435001373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7804889678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8555583953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.874324798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.198709487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2925453186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6678848266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2737789154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4989833831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.362268447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.793909072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6759643554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8260974884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0325355529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1639060974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0888385772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8073310852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1826725006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2389755249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2952766418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4829444885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9574661254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8448657989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.76979637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7134971618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.995002746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5767803192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.670618057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.970890045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9145889282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1585597991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2711620330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1397914886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4882926940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8824005126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8636322021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9252796173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0003471374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1692504882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2443180084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8877468109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6813087463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1182975769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3998012542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8930931091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2174758911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3488464355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7992553710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7054214477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0807609558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.742956161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6115837097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4239139556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4426803588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3300800323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9359722137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9172039031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2684326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.686653137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1236419677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9922714233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9118595123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4051456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8180236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9681587219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.606237411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4695243835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7162265777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5848579406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6974601745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5044422149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9226627349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8475952148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4293766021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0486869812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.710880279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2363586425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8422527313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9360866546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6170463562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7484169006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.067455291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5741672515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3114280700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4615650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7806053161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9119739532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0058116912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.231014251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1184120178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1559467315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8932056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6814231872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7189598083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4749851226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7377243041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1693687438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9629287719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6573104858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.507173538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6385440826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9307422637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.775260925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8878593444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4321060180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8074474334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2766246795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8449821472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7136135101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1881370544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8315601348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7940292358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9253959655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2819690704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1640224456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9441623687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2444362640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6063556671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1130657196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5500545501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1934814453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7243022918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2175941467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.874439239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4374504089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3060817718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7055339813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8181381225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0996437072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1318321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.206901550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9951171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.019229888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4884090423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2900466918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5527877807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1533336639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4777164459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.515251159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3838806152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0460739135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1211414337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6519660949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9897708892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.083610534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6895008087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7270336151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4026489257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2712783813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9334716796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5259399414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3007373809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0942993164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0379962921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1506004333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8503284454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5205955505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9763526916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4830627441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7645683288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9575862884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1452541351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0031967163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9468936920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7779884338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3973007202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5581321716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7029228210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3463478088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4455261230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2953910827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4392318725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7460899353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1323719024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6310176849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5543022155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7242012023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6064167022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6091289520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3570995330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8968086242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8776321411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4940547943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2995586395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2803802490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9159889221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8392715454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7050228118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2420272827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9543437957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7077312469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6858425140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0694179534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4556999206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4913463592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7817344665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4721698760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0145893096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4227619171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4419422149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0008335113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5761909484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8638706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.359806060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2063789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4365196228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2830905914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8009147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2611999511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4146308898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0885944366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6474857330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3022708892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8584518432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3241596221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4584102630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7487983703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5378341674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9432964324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.102144241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5459632873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1432113647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8720016479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3131122589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0446090698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2172164916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0637893676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.929536819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5432548522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4281826019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8692932128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0419006347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1953296661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0610771179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.444652557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0802574157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6939735412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9843635559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.524076461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5624332427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6802158355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3158206939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5843238830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3925342559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0281410217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7952861785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2939319610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9487152099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4857196807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7733974456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6418590545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7761077880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1213245391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7377510070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6583271026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0829677581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9678955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1405029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1596813201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8528232574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8144664764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9103603363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9870738983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6993942260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4884281158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7569313049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2966423034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3514671325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0967254638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7706871032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5980815887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5789012908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8309326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3541793823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7542190551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6747951507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6391487121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.307689666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.557014465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7515106201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7323303222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4062938690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3898258209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7925777435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0227203369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8501129150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2145080566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3487586975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.962474822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6337280273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1131954193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3049812316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0556564331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9597663879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7296199798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7104434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.981653213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.40358543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2474460601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8830509185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6912631988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4611206054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.809045791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.617259979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9049377441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6666641235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9351654052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1077728271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2228488922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6037063598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1050643920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6804275512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3352088928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5269927978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2584953308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2776718139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8365631103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7598476409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2009582519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.661247253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8913879394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9105682373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4694595336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.584529876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0475234985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6228866577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3708534240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6420669555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2968482971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9708137512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4338111877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9735221862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9762344360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5324153900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1104831695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8995189666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2447357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2639122009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.841983795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6501960754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2090854644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6856346130371</t>
+  </si>
+  <si>
     <t xml:space="preserve">24.7212829589844</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8978652954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2686862945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5447025299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1032524108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8383827209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6924800872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.451774597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5112571716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9703674316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2993621826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9285430908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5289173126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.475944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9638595581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3811416625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8932247161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1757545471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7872791290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0986137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4629230499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8095741271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2333679199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.127420425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7389450073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1738872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4080791473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4192295074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3662528991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6906089782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0660648345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9424591064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3551044464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7723903656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7788963317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4610538482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2844734191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2314968109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8077068328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5251750946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4722023010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5604915618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.990795135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3374481201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8430213928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7547302246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7900466918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5958080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3839111328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9601173400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1896724700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.136697769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4015674591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7658805847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8365116119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0595550537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9359493255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3774013519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5186653137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8653182983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0065822601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7835369110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5363235473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.041898727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1943130493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4238681793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7770290374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3420886993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3355770111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5474739074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6710815429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9111518859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0677719116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4711284637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1311645507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3878479003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9012107849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6995315551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3145122528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.64453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0944995880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4061832427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1678371429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5811367034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3061180114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3710651397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7560882568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0127696990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0960483551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0861034393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.729362487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9493732452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2801704406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2618312835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.179328918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2343330383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0968246459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.757640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2626094818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1617698669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1709384918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9875946044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3817825317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7851390838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0601577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.188497543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4635105133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9501495361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4092864990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6843013763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9043140411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0693225860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9593162536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1334934234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8676452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3359470367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8500852584839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8218078613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5284576416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1151580810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8852062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6560230255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6376895904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8859786987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4726791381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5643501281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6835250854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6651916503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2159976959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3351707458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9868183135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0784893035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8584785461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4001178741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9967603683472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9417552947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0425968170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0150947570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6392383575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9142580032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0525398254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2542190551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2175493240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1992149353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6117401123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0059261322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6942434310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9883689880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5758447647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5850114822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.860803604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8058004379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6041231155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3841104507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.585786819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7599639892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.924973487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.310772895813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8149671554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5032835006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8883037567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5124502182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6591243743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3382740020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4482793807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8516368865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5307846069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8424692153931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1908226013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3466653823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6033477783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1816549301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5483436584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8233594894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5659017562866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7217454910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9050903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1526031494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7026348114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2434978485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5093479156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2427234649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5528564453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.717866897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4161262512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1594429016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0494384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6178035736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2595062255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7094783782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3794555664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.562801361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8928203582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6544742584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8561515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4527950286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5261306762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7278118133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3695125579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8378162384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3244514465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9760990142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9577655792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2144470214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6728038787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.232780456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0578289031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1128311157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2961769104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5161895751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8179321289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2495651245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9928817749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7728710174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8828792572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0478858947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8095397949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7362022399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7828121185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.764476776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2511157989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8660945892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3977909088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3427886962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4894638061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5994682312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3511791229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8744850158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1495018005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0761642456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0394954681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9745483398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2128963470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5795841217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6345882415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6529216766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6162548065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5429153442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6812000274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3045673370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6628665924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4245185852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5711936950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.966157913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5077991485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3611259460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5444660186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9294891357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0211601257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6460800170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4444026947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.481071472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.609411239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.407735824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3343982696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9210987091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2877864837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1961135864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1044425964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7201480865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6169319152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8756294250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5378246307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7348766326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6410427093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2469348907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1437168121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1718654632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0498809814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0029640197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0311126708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9560451507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8903617858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9091281890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.078031539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1852855682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2885055541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5659732818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0070018768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9225482940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8662490844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8005619049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5753555297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7536449432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9319324493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9882335662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3354244232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5137119293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7858333587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5230941772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7483005523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4855613708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7817974090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8474807739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4386425018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0056934356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1558284759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3435001373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7804870605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8555564880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.874324798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.198709487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2925453186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6678867340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2737770080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4989833831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.362268447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7939109802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6759624481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.826099395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0325355529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1639060974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0888366699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8073310852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1826725006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2389736175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2952747344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.482946395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9574680328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8448657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7698001861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7134952545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.995002746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5767822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.670618057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.970890045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9145889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1585597991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2711620330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1397953033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4882888793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8824005126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8636322021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9252796173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0003471374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1692523956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2443199157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8877449035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6813068389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1182975769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3998012542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8930912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2174777984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3488464355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7992553710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7054195404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0807609558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.742956161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6115837097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4239139556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4426803588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9359703063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9172039031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2684345245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6866512298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1236400604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9922714233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9118576049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4051475524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8180255889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9681606292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.606237411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4695243835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7162284851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5848579406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6974601745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5044422149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.922664642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8475971221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4293766021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0486907958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.710880279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2363586425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8422527313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9360847473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6170463562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7484169006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0674571990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5741653442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3114280700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4615631103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7806053161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9119720458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0058097839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.231014251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1184120178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1559467315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8932075500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6814231872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.718957901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4749870300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7377243041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1693668365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9629287719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6573123931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.507173538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6385440826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9307403564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7752590179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8878593444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4321041107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8074493408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2766246795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8449821472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7136135101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1881351470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8315601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7940273284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9253959655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2819690704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1640224456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.944164276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2444362640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6063556671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1130657196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5500545501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1934795379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7243022918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2175922393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.874439239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4374504089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3060836791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7055358886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8181381225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0996437072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1318321228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.206901550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9951190948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0192317962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4884071350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2900447845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5527858734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1533317565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4777164459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5152530670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3838806152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0460739135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1211414337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6519660949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9897727966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0836086273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6894989013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7270336151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4026489257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2712783813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9334697723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5259399414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3007373809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0943012237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0379962921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1506004333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8503284454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5205974578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9763488769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.483060836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7645683288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9575843811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1452541351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.00319480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.946891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7779903411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3973026275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5581302642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7029228210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3463478088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4455280303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2953910827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4392318725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7460899353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1323719024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6310176849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5543041229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7242012023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6064205169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6091289520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3570957183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8968086242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8776302337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4940567016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.299560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2803802490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9159889221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8392734527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7050228118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2420272827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9543437957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7077331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6858425140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0694179534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4556999206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4913482666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7817363739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.47216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.014591217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4227619171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4419403076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0008335113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5761909484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8638725280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.359806060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2063770294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4365196228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2830905914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8009147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2612018585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4146308898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0885944366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6474857330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3022708892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8584518432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3241596221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4584083557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7487983703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5378341674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9432964324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1021461486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5459651947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1432113647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8720016479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3131122589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0446090698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2172183990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0637874603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9295387268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5432548522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4281806945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8692932128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.041898727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1953277587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0610771179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.444652557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0802574157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6939735412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9843635559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.524076461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5624351501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6802158355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3158206939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.584321975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3925361633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0281429290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7952880859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2939319610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9487171173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4857196807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7733993530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6418590545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7761077880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1213226318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7377510070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6583251953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0829677581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9678936004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1405029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1596832275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8528232574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8144645690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9103584289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9870738983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6993942260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4884300231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.756929397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2966403961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3514671325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0967254638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7706871032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5980815887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5789012908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8309345245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3541774749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7542190551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6747951507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6391487121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3076915740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.557014465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7515106201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7323303222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4062938690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3898258209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7925777435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0227222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8501129150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.214506149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3487567901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.962474822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6337280273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1131935119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3049793243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0556564331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9597644805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7296199798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7104434967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.981653213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.40358543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2474460601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8830509185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6912631988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4611206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.809045791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6172580718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9049396514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6666641235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9351654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1077728271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2228469848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6037101745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1050605773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6804275512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3352088928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5269927978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2584915161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2776718139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8365631103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7598495483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2009582519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.661247253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8913879394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9105682373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4694595336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.584529876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0475273132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6228866577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3708534240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6420669555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2968521118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9708118438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4338092803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9735221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9762325286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.532413482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1104831695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8995189666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2447357177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2639122009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.841983795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6501960754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2090854644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6856365203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.721284866333</t>
-  </si>
-  <si>
     <t xml:space="preserve">23.9157791137695</t>
   </si>
   <si>
@@ -5549,7 +5549,7 @@
     <t xml:space="preserve">25.2774639129639</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6829242706299</t>
+    <t xml:space="preserve">24.6829261779785</t>
   </si>
   <si>
     <t xml:space="preserve">25.1048564910889</t>
@@ -5561,13 +5561,13 @@
     <t xml:space="preserve">25.5267868041992</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5816097259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6199703216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4090061187744</t>
+    <t xml:space="preserve">26.5816116333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6199684143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4090042114258</t>
   </si>
   <si>
     <t xml:space="preserve">27.7131519317627</t>
@@ -5576,7 +5576,7 @@
     <t xml:space="preserve">29.611837387085</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9022274017334</t>
+    <t xml:space="preserve">28.902229309082</t>
   </si>
   <si>
     <t xml:space="preserve">28.6145496368408</t>
@@ -71238,7 +71238,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6911111111</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>91226</v>
@@ -71259,6 +71259,32 @@
         <v>1953</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6909722222</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>105181</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>31.7600002288818</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>31.1599998474121</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>31.5400009155273</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>31.3400001525879</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1951</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DLG.MI.xlsx
+++ b/data/DLG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1954" uniqueCount="1954">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1955" uniqueCount="1955">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">20.739143371582</t>
+    <t xml:space="preserve">20.7391452789307</t>
   </si>
   <si>
     <t xml:space="preserve">DLG.MI</t>
@@ -47,25 +47,25 @@
     <t xml:space="preserve">20.5564231872559</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6553955078125</t>
+    <t xml:space="preserve">20.6553974151611</t>
   </si>
   <si>
     <t xml:space="preserve">20.1757469177246</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9778003692627</t>
+    <t xml:space="preserve">19.9777946472168</t>
   </si>
   <si>
     <t xml:space="preserve">19.7722320556641</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4905338287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8864364624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5160045623779</t>
+    <t xml:space="preserve">19.490535736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8864326477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5160064697266</t>
   </si>
   <si>
     <t xml:space="preserve">17.6328411102295</t>
@@ -74,142 +74,142 @@
     <t xml:space="preserve">17.4348907470703</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5262508392334</t>
+    <t xml:space="preserve">17.526252746582</t>
   </si>
   <si>
     <t xml:space="preserve">17.0542163848877</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8943328857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0135154724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6354713439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4451332092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7116088867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8029708862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6735420227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.132984161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9654865264893</t>
+    <t xml:space="preserve">16.8943309783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0135192871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6354732513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4451351165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7116107940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8029670715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6735382080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1329860687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9654836654663</t>
   </si>
   <si>
     <t xml:space="preserve">15.6533346176147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9909601211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7777814865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3335657119751</t>
+    <t xml:space="preserve">14.9909610748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7777805328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3335676193237</t>
   </si>
   <si>
     <t xml:space="preserve">14.4123363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7397155761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4553833007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2574338912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4097032546997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.75230884552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3868608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9121942520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.95787525177</t>
+    <t xml:space="preserve">14.7397165298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4553842544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2574310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.409704208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7523097991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3868579864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9121932983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9578723907471</t>
   </si>
   <si>
     <t xml:space="preserve">15.584813117981</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1253719329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1938953399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5593376159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7496776580811</t>
+    <t xml:space="preserve">16.1253681182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1938934326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5593395233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7496757507324</t>
   </si>
   <si>
     <t xml:space="preserve">15.8817367553711</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2193660736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792486190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0873012542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7142429351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2878856658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8969631195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3183422088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6076526641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9274206161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9883270263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.889349937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6152658462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.356406211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1356182098389</t>
+    <t xml:space="preserve">15.219367980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792495727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0872993469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7142448425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2878866195679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8969659805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3183393478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6076517105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9274225234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9883289337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8893537521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6152648925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3564071655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1356191635132</t>
   </si>
   <si>
     <t xml:space="preserve">15.2269773483276</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3487939834595</t>
+    <t xml:space="preserve">15.3487949371338</t>
   </si>
   <si>
     <t xml:space="preserve">15.0442562103271</t>
@@ -218,148 +218,148 @@
     <t xml:space="preserve">15.2345943450928</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0594816207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1432294845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5493812561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7853927612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8234634399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7831659317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.977988243103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1572256088257</t>
+    <t xml:space="preserve">15.0594797134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1432285308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5493783950806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7853965759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.82346534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.783164024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9779872894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1572284698486</t>
   </si>
   <si>
     <t xml:space="preserve">15.1494331359863</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9624032974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9857807159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9546117782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8533020019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4689426422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6715593338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2170639038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7572784423828</t>
+    <t xml:space="preserve">14.9624061584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9857816696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9546098709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8533010482788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4689407348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.671558380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2170600891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7572813034058</t>
   </si>
   <si>
     <t xml:space="preserve">16.0300331115723</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2404403686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1469249725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3495426177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5054035186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3105754852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7288913726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7937393188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0742835998535</t>
+    <t xml:space="preserve">16.240442276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1469230651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3495445251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5054016113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3105792999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.728889465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7937355041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0742855072021</t>
   </si>
   <si>
     <t xml:space="preserve">16.762565612793</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7547740936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8482875823975</t>
+    <t xml:space="preserve">16.7547760009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8482913970947</t>
   </si>
   <si>
     <t xml:space="preserve">17.1132469177246</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3002796173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7678527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9081249237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9470901489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.063985824585</t>
+    <t xml:space="preserve">17.3002815246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7678508758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9081230163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9470920562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0639839172363</t>
   </si>
   <si>
     <t xml:space="preserve">18.4848022460938</t>
   </si>
   <si>
-    <t xml:space="preserve">18.788724899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.46142578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3367366790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.274393081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0795726776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6484508514404</t>
+    <t xml:space="preserve">18.7887287139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4614219665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3367385864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2743949890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.079568862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6484546661377</t>
   </si>
   <si>
     <t xml:space="preserve">18.8276920318604</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4536304473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8379898071289</t>
+    <t xml:space="preserve">18.4536323547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8379878997803</t>
   </si>
   <si>
     <t xml:space="preserve">17.3937931060791</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2535209655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0820751190186</t>
+    <t xml:space="preserve">17.2535190582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0820732116699</t>
   </si>
   <si>
     <t xml:space="preserve">17.4951019287109</t>
@@ -368,13 +368,13 @@
     <t xml:space="preserve">17.9237117767334</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8224029541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7834415435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9315052032471</t>
+    <t xml:space="preserve">17.8224067687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7834377288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9315032958984</t>
   </si>
   <si>
     <t xml:space="preserve">16.6768455505371</t>
@@ -383,70 +383,70 @@
     <t xml:space="preserve">15.5234937667847</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1157569885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3651275634766</t>
+    <t xml:space="preserve">16.1157531738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3651294708252</t>
   </si>
   <si>
     <t xml:space="preserve">16.6612586975098</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6300868988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8975553512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7806596755981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5468730926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7884511947632</t>
+    <t xml:space="preserve">16.6300888061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8975505828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7806615829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5468711853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7884521484375</t>
   </si>
   <si>
     <t xml:space="preserve">16.3729228973389</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1858901977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1625118255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4196815490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5209865570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5287780761719</t>
+    <t xml:space="preserve">16.1858921051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1625099182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4196796417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5209884643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5287799835205</t>
   </si>
   <si>
     <t xml:space="preserve">16.8404979705811</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9184246063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8716678619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8015308380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6119976043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2223491668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5964107513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4171714782715</t>
+    <t xml:space="preserve">16.9184226989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8716697692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8015289306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6119937896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2223510742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5964088439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4171695709229</t>
   </si>
   <si>
     <t xml:space="preserve">17.6587505340576</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">17.3158626556396</t>
   </si>
   <si>
-    <t xml:space="preserve">17.323657989502</t>
+    <t xml:space="preserve">17.3236560821533</t>
   </si>
   <si>
     <t xml:space="preserve">17.502893447876</t>
@@ -464,19 +464,19 @@
     <t xml:space="preserve">18.0561904907227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5393543243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7030029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6640396118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.812105178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0951538085938</t>
+    <t xml:space="preserve">18.5393524169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7030010223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.664041519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8121032714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0951557159424</t>
   </si>
   <si>
     <t xml:space="preserve">18.1497077941895</t>
@@ -485,16 +485,16 @@
     <t xml:space="preserve">17.9003314971924</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1575012207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8769512176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6665458679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9704666137695</t>
+    <t xml:space="preserve">18.1574993133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8769550323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6665439605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9704723358154</t>
   </si>
   <si>
     <t xml:space="preserve">18.0328121185303</t>
@@ -506,31 +506,31 @@
     <t xml:space="preserve">17.5730285644531</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3626232147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4015884399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2379360198975</t>
+    <t xml:space="preserve">17.3626194000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4015865325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2379341125488</t>
   </si>
   <si>
     <t xml:space="preserve">17.4093799591064</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1444187164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8171157836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6145038604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6846370697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0197334289551</t>
+    <t xml:space="preserve">17.1444206237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.81711769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.614501953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6846389770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0197353363037</t>
   </si>
   <si>
     <t xml:space="preserve">17.128833770752</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">17.2691059112549</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9963550567627</t>
+    <t xml:space="preserve">16.9963531494141</t>
   </si>
   <si>
     <t xml:space="preserve">17.4405498504639</t>
@@ -548,22 +548,22 @@
     <t xml:space="preserve">17.4639301300049</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8327007293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8249111175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9028396606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7859497070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7469787597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2769012451172</t>
+    <t xml:space="preserve">16.8327045440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8249130249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9028415679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.785945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7469806671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2768974304199</t>
   </si>
   <si>
     <t xml:space="preserve">17.2457275390625</t>
@@ -575,13 +575,13 @@
     <t xml:space="preserve">17.0976638793945</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9573917388916</t>
+    <t xml:space="preserve">16.9573879241943</t>
   </si>
   <si>
     <t xml:space="preserve">17.2301425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2067623138428</t>
+    <t xml:space="preserve">17.2067642211914</t>
   </si>
   <si>
     <t xml:space="preserve">17.4327564239502</t>
@@ -590,52 +590,52 @@
     <t xml:space="preserve">17.2846927642822</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0664901733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9521036148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9832725524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2560272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3339595794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9988622665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4065999984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3130836486816</t>
+    <t xml:space="preserve">17.0664882659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9521026611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9832754135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.256031036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3339557647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9988603591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4066019058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.313084602356</t>
   </si>
   <si>
     <t xml:space="preserve">15.118260383606</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5131912231445</t>
+    <t xml:space="preserve">16.5131931304932</t>
   </si>
   <si>
     <t xml:space="preserve">16.0923767089844</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9131412506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1780948638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7158088684082</t>
+    <t xml:space="preserve">15.9131383895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1780986785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7158107757568</t>
   </si>
   <si>
     <t xml:space="preserve">17.0586986541748</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4664363861084</t>
+    <t xml:space="preserve">16.4664325714111</t>
   </si>
   <si>
     <t xml:space="preserve">16.2248554229736</t>
@@ -647,13 +647,13 @@
     <t xml:space="preserve">16.7080173492432</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4976100921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6924304962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5599536895752</t>
+    <t xml:space="preserve">16.4976081848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6924285888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5599517822266</t>
   </si>
   <si>
     <t xml:space="preserve">16.7703590393066</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">16.8638725280762</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0275268554688</t>
+    <t xml:space="preserve">17.0275249481201</t>
   </si>
   <si>
     <t xml:space="preserve">17.4561367034912</t>
@@ -671,16 +671,16 @@
     <t xml:space="preserve">17.4483413696289</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8847465515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1185359954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2354316711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0172271728516</t>
+    <t xml:space="preserve">17.8847484588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1185340881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2354278564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0172290802002</t>
   </si>
   <si>
     <t xml:space="preserve">17.8457832336426</t>
@@ -689,28 +689,28 @@
     <t xml:space="preserve">17.9626770019531</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8691596984863</t>
+    <t xml:space="preserve">17.8691635131836</t>
   </si>
   <si>
     <t xml:space="preserve">17.6353740692139</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7912311553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5808238983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6509571075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1107387542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9782619476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3133583068848</t>
+    <t xml:space="preserve">17.7912330627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5808219909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6509590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1107425689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9782600402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3133563995361</t>
   </si>
   <si>
     <t xml:space="preserve">18.2042560577393</t>
@@ -719,40 +719,40 @@
     <t xml:space="preserve">18.469217300415</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0848541259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.349817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2952690124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4667072296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2485103607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3186435699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0614776611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4199523925781</t>
+    <t xml:space="preserve">19.0848579406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3498153686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2952671051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4667110443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2485084533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3186454772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0614757537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4199562072754</t>
   </si>
   <si>
     <t xml:space="preserve">19.2407150268555</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0926494598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4511241912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8588619232178</t>
+    <t xml:space="preserve">19.0926475524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4511222839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8588638305664</t>
   </si>
   <si>
     <t xml:space="preserve">18.640661239624</t>
@@ -761,13 +761,13 @@
     <t xml:space="preserve">18.9056186676025</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2329216003418</t>
+    <t xml:space="preserve">19.2329235076904</t>
   </si>
   <si>
     <t xml:space="preserve">19.4978809356689</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1914520263672</t>
+    <t xml:space="preserve">20.1914501190186</t>
   </si>
   <si>
     <t xml:space="preserve">19.9888343811035</t>
@@ -776,25 +776,25 @@
     <t xml:space="preserve">20.1213130950928</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9732475280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9551544189453</t>
+    <t xml:space="preserve">19.9732494354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9551563262939</t>
   </si>
   <si>
     <t xml:space="preserve">20.6278514862061</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2201175689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0408821105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7915058135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7447471618652</t>
+    <t xml:space="preserve">21.2201156616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0408763885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.79150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7447490692139</t>
   </si>
   <si>
     <t xml:space="preserve">20.8616428375244</t>
@@ -803,34 +803,34 @@
     <t xml:space="preserve">21.2434959411621</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9006042480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0330867767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9785346984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6721038818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4149398803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3136310577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1967372894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4227313995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5785903930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1884765625</t>
+    <t xml:space="preserve">20.9006061553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.033088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9785327911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6721057891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4149379730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3136329650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1967353820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4227333068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.578592300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1884727478027</t>
   </si>
   <si>
     <t xml:space="preserve">22.1002006530762</t>
@@ -839,34 +839,34 @@
     <t xml:space="preserve">21.9477310180664</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0279769897461</t>
+    <t xml:space="preserve">22.0279808044434</t>
   </si>
   <si>
     <t xml:space="preserve">21.9878540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8273601531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3489665985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4693393707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8946514129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3199634552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2878684997559</t>
+    <t xml:space="preserve">21.8273582458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.348970413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4693412780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8946533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3199672698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2878704071045</t>
   </si>
   <si>
     <t xml:space="preserve">22.8786029815674</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0310726165771</t>
+    <t xml:space="preserve">23.0310745239258</t>
   </si>
   <si>
     <t xml:space="preserve">23.4483604431152</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">23.0230484008789</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9026756286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6218128204346</t>
+    <t xml:space="preserve">22.9026775360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6218109130859</t>
   </si>
   <si>
     <t xml:space="preserve">22.5014400482178</t>
@@ -890,52 +890,52 @@
     <t xml:space="preserve">21.8434066772461</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0600776672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6298408508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7341594696045</t>
+    <t xml:space="preserve">22.060079574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6298332214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7341556549072</t>
   </si>
   <si>
     <t xml:space="preserve">22.9267520904541</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2316913604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1434230804443</t>
+    <t xml:space="preserve">23.2316932678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1434192657471</t>
   </si>
   <si>
     <t xml:space="preserve">23.1674957275391</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6570072174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7693519592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6730575561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8495979309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7613296508789</t>
+    <t xml:space="preserve">23.6570053100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7693538665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6730556488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8495998382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7613277435303</t>
   </si>
   <si>
     <t xml:space="preserve">23.4002132415771</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2958927154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4323120117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7051544189453</t>
+    <t xml:space="preserve">23.2958908081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4323139190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7051525115967</t>
   </si>
   <si>
     <t xml:space="preserve">23.0069999694824</t>
@@ -947,13 +947,13 @@
     <t xml:space="preserve">22.7903308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">23.063175201416</t>
+    <t xml:space="preserve">23.0631713867188</t>
   </si>
   <si>
     <t xml:space="preserve">23.8255271911621</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3921890258789</t>
+    <t xml:space="preserve">23.3921871185303</t>
   </si>
   <si>
     <t xml:space="preserve">23.2637920379639</t>
@@ -962,73 +962,73 @@
     <t xml:space="preserve">23.2718162536621</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1915683746338</t>
+    <t xml:space="preserve">23.1915664672852</t>
   </si>
   <si>
     <t xml:space="preserve">22.9989757537842</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9076080322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0199508666992</t>
+    <t xml:space="preserve">21.9076061248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0199546813965</t>
   </si>
   <si>
     <t xml:space="preserve">22.0761260986328</t>
   </si>
   <si>
-    <t xml:space="preserve">21.554515838623</t>
+    <t xml:space="preserve">21.5545177459717</t>
   </si>
   <si>
     <t xml:space="preserve">21.4742698669434</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6267414093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.771183013916</t>
+    <t xml:space="preserve">21.6267395019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7711868286133</t>
   </si>
   <si>
     <t xml:space="preserve">21.739086151123</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8674812316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8594589233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5255146026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7421817779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3730430603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7181091308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8625545501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7100849151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5335350036621</t>
+    <t xml:space="preserve">21.8674831390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8594570159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5255126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7421798706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3730411529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7181034088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8625526428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7100830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5335388183594</t>
   </si>
   <si>
     <t xml:space="preserve">22.6539096832275</t>
   </si>
   <si>
-    <t xml:space="preserve">22.292797088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7551403045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2415504455566</t>
+    <t xml:space="preserve">22.2927932739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7551383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.241548538208</t>
   </si>
   <si>
     <t xml:space="preserve">20.9927845001221</t>
@@ -1037,43 +1037,43 @@
     <t xml:space="preserve">20.9446353912354</t>
   </si>
   <si>
-    <t xml:space="preserve">21.073034286499</t>
+    <t xml:space="preserve">21.0730323791504</t>
   </si>
   <si>
     <t xml:space="preserve">21.0489559173584</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6396903991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4310474395752</t>
+    <t xml:space="preserve">20.6396942138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4310493469238</t>
   </si>
   <si>
     <t xml:space="preserve">20.4872226715088</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8804378509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8643856048584</t>
+    <t xml:space="preserve">20.8804359436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8643894195557</t>
   </si>
   <si>
     <t xml:space="preserve">20.7119178771973</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5754947662354</t>
+    <t xml:space="preserve">20.5754985809326</t>
   </si>
   <si>
     <t xml:space="preserve">20.5995693206787</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6477203369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6156158447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5915412902832</t>
+    <t xml:space="preserve">20.6477184295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6156196594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5915451049805</t>
   </si>
   <si>
     <t xml:space="preserve">20.3508033752441</t>
@@ -1091,52 +1091,52 @@
     <t xml:space="preserve">20.6717929840088</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4952487945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.735990524292</t>
+    <t xml:space="preserve">20.495246887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7359886169434</t>
   </si>
   <si>
     <t xml:space="preserve">21.2174777984619</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0168590545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3538970947266</t>
+    <t xml:space="preserve">21.0168609619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3538990020752</t>
   </si>
   <si>
     <t xml:space="preserve">21.2335243225098</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9045104980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5594482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5353679656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4711723327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7520427703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3779716491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0650043487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2255020141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3699493408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9156303405762</t>
+    <t xml:space="preserve">20.9045085906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5594463348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5353717803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4711742401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7520389556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3779697418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0650062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2255039215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.369945526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9156322479248</t>
   </si>
   <si>
     <t xml:space="preserve">21.4582195281982</t>
@@ -1145,76 +1145,73 @@
     <t xml:space="preserve">21.8032855987549</t>
   </si>
   <si>
-    <t xml:space="preserve">21.795259475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5785884857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3088417053223</t>
+    <t xml:space="preserve">21.7952575683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3088397979736</t>
   </si>
   <si>
     <t xml:space="preserve">22.1403255462646</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2285976409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2045230865479</t>
+    <t xml:space="preserve">22.2285957336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2045211791992</t>
   </si>
   <si>
     <t xml:space="preserve">22.1483516693115</t>
   </si>
   <si>
-    <t xml:space="preserve">22.694034576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0921764373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.108226776123</t>
+    <t xml:space="preserve">22.6940326690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0921783447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1082248687744</t>
   </si>
   <si>
     <t xml:space="preserve">22.164400100708</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7742805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7662582397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5897121429443</t>
+    <t xml:space="preserve">22.7742786407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7662563323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5897102355957</t>
   </si>
   <si>
     <t xml:space="preserve">22.541561126709</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4131641387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5174865722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1563720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8353824615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5495891571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2526741027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2125492095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2594375610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9335155487061</t>
+    <t xml:space="preserve">22.4131679534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5174884796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1563739776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8353843688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5495872497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2526683807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2125453948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2594337463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9335136413574</t>
   </si>
   <si>
     <t xml:space="preserve">19.861291885376</t>
@@ -1223,7 +1220,7 @@
     <t xml:space="preserve">19.6927719116211</t>
   </si>
   <si>
-    <t xml:space="preserve">19.620548248291</t>
+    <t xml:space="preserve">19.6205501556396</t>
   </si>
   <si>
     <t xml:space="preserve">19.5403003692627</t>
@@ -1232,13 +1229,13 @@
     <t xml:space="preserve">19.4921531677246</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4279518127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7409210205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.676721572876</t>
+    <t xml:space="preserve">19.4279537200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7409229278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6767253875732</t>
   </si>
   <si>
     <t xml:space="preserve">19.805118560791</t>
@@ -1250,85 +1247,85 @@
     <t xml:space="preserve">19.7569713592529</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6606693267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1421585083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2304286956787</t>
+    <t xml:space="preserve">19.6606731414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1421604156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2304267883301</t>
   </si>
   <si>
     <t xml:space="preserve">20.4069747924805</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4792003631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2545013427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9415416717529</t>
+    <t xml:space="preserve">20.4791965484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2545032501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9415378570557</t>
   </si>
   <si>
     <t xml:space="preserve">20.0619106292725</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9254913330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9366130828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0971088409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8162403106689</t>
+    <t xml:space="preserve">19.9254875183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9366111755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0971050262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8162384033203</t>
   </si>
   <si>
     <t xml:space="preserve">20.3989505767822</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6878414154053</t>
+    <t xml:space="preserve">20.6878452301025</t>
   </si>
   <si>
     <t xml:space="preserve">20.4390735626221</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2464809417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4631481170654</t>
+    <t xml:space="preserve">20.2464790344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4631462097168</t>
   </si>
   <si>
     <t xml:space="preserve">20.5433979034424</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4100685119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0088348388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6508159637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1372318267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2816734313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5063667297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4421691894531</t>
+    <t xml:space="preserve">21.4100704193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0088329315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6508121490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1372299194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2816753387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.506368637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4421710968018</t>
   </si>
   <si>
     <t xml:space="preserve">20.9606857299805</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3458709716797</t>
+    <t xml:space="preserve">21.345874786377</t>
   </si>
   <si>
     <t xml:space="preserve">21.0890808105469</t>
@@ -1337,37 +1334,37 @@
     <t xml:space="preserve">21.6989650726318</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8113098144531</t>
+    <t xml:space="preserve">21.8113117218018</t>
   </si>
   <si>
     <t xml:space="preserve">21.7792091369629</t>
   </si>
   <si>
-    <t xml:space="preserve">21.394021987915</t>
+    <t xml:space="preserve">21.3940200805664</t>
   </si>
   <si>
     <t xml:space="preserve">21.7471103668213</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2495746612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5322742462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3236331939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5001754760742</t>
+    <t xml:space="preserve">21.2495765686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5322761535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3236312866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5001773834229</t>
   </si>
   <si>
     <t xml:space="preserve">19.5162258148193</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0458602905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0940093994141</t>
+    <t xml:space="preserve">20.045862197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0940113067627</t>
   </si>
   <si>
     <t xml:space="preserve">19.7248706817627</t>
@@ -1379,64 +1376,64 @@
     <t xml:space="preserve">19.403881072998</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4841270446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1631374359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.826099395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6014041900635</t>
+    <t xml:space="preserve">19.484130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1631355285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8260955810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6014003753662</t>
   </si>
   <si>
     <t xml:space="preserve">18.0075721740723</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5853538513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7137489318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9977111816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1261100769043</t>
+    <t xml:space="preserve">18.5853519439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.713752746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9977130889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1261119842529</t>
   </si>
   <si>
     <t xml:space="preserve">20.7199401855469</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1903057098389</t>
+    <t xml:space="preserve">20.1903076171875</t>
   </si>
   <si>
     <t xml:space="preserve">19.7730197906494</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8372192382812</t>
+    <t xml:space="preserve">19.8372173309326</t>
   </si>
   <si>
     <t xml:space="preserve">19.8211688995361</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4359760284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1310386657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3557300567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5483264923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9174652099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5804214477539</t>
+    <t xml:space="preserve">19.435977935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1310367584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3557319641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5483283996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9174613952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5804233551025</t>
   </si>
   <si>
     <t xml:space="preserve">19.0186920166016</t>
@@ -1445,121 +1442,124 @@
     <t xml:space="preserve">19.0026416778564</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8421478271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0828895568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.885368347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5112953186035</t>
+    <t xml:space="preserve">18.8421497344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0828876495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8853664398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5112972259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1582069396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8936634063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6596565246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5760841369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6763744354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7265148162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8435211181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8268051147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4954013824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1276760101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2781085968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1778202056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0942459106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9772396087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7766609191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4757919311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6429405212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5259380340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2584953308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1247749328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1916389465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9241981506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5063247680664</t>
   </si>
   <si>
     <t xml:space="preserve">20.1582088470459</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8936672210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6596546173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5760803222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6763706207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7265129089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8435211181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8268070220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4954032897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1276741027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2781085968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1778182983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0942440032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9772396087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7766609191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4757919311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6429405212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.525936126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2584991455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1247787475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1916370391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9241981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5063247680664</t>
-  </si>
-  <si>
     <t xml:space="preserve">20.2417831420898</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8769512176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7933750152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.993953704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8100929260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5927925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6930866241455</t>
+    <t xml:space="preserve">20.8769493103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7933731079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9939556121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8100891113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.592794418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6930847167969</t>
   </si>
   <si>
     <t xml:space="preserve">20.3420734405518</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4925079345703</t>
+    <t xml:space="preserve">20.4925098419189</t>
   </si>
   <si>
     <t xml:space="preserve">20.5593662261963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7570514678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8740558624268</t>
+    <t xml:space="preserve">19.7570495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8740520477295</t>
   </si>
   <si>
     <t xml:space="preserve">20.1414928436279</t>
@@ -1571,43 +1571,43 @@
     <t xml:space="preserve">20.024486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9409141540527</t>
+    <t xml:space="preserve">19.9409160614014</t>
   </si>
   <si>
     <t xml:space="preserve">20.1080627441406</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2752151489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3922157287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.057918548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4256477355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0746307373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8239097595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6901912689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0273857116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2475776672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3144359588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1000347137451</t>
+    <t xml:space="preserve">20.2752132415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3922176361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0579204559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4256496429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0746326446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8239078521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6901874542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0273838043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2475757598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3144340515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1000366210938</t>
   </si>
   <si>
     <t xml:space="preserve">23.2003269195557</t>
@@ -1616,49 +1616,49 @@
     <t xml:space="preserve">23.2671852111816</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5847702026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5346221923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2170429229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8660259246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7991695404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8325958251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5484447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6153049468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9328842163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1167488098145</t>
+    <t xml:space="preserve">23.5847682952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5346240997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.217041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8660297393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.799165725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8325977325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5484428405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6153030395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9328899383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1167526245117</t>
   </si>
   <si>
     <t xml:space="preserve">23.1501808166504</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2504711151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4009056091309</t>
+    <t xml:space="preserve">23.2504692077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4009037017822</t>
   </si>
   <si>
     <t xml:space="preserve">23.6181983947754</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5011940002441</t>
+    <t xml:space="preserve">23.5011959075928</t>
   </si>
   <si>
     <t xml:space="preserve">23.3841896057129</t>
@@ -1667,88 +1667,88 @@
     <t xml:space="preserve">23.2839012145996</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0833206176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8994560241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5651569366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5818748474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3311462402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.815881729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5317268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1334648132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9663162231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6850566864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3006134033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4343357086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9997463226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8493137359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9495983123779</t>
+    <t xml:space="preserve">23.0833225250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8994579315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5651588439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5818729400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3311500549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8158798217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5317287445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1334629058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9663143157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.68505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3006153106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4343376159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9997482299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8493118286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9496002197266</t>
   </si>
   <si>
     <t xml:space="preserve">21.7628421783447</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4619750976562</t>
+    <t xml:space="preserve">21.461971282959</t>
   </si>
   <si>
     <t xml:space="preserve">21.0440998077393</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7098007202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9103813171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6625518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2279624938965</t>
+    <t xml:space="preserve">20.7097988128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.91037940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6625537872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2279644012451</t>
   </si>
   <si>
     <t xml:space="preserve">21.4285430908203</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9270935058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3616809844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5121173858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9605255126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8573398590088</t>
+    <t xml:space="preserve">20.9270973205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3616828918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5121192932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9605236053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8573379516602</t>
   </si>
   <si>
     <t xml:space="preserve">19.5397548675537</t>
@@ -1760,13 +1760,13 @@
     <t xml:space="preserve">19.5564727783203</t>
   </si>
   <si>
-    <t xml:space="preserve">19.055025100708</t>
+    <t xml:space="preserve">19.0550212860107</t>
   </si>
   <si>
     <t xml:space="preserve">19.4394645690918</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3893222808838</t>
+    <t xml:space="preserve">19.3893203735352</t>
   </si>
   <si>
     <t xml:space="preserve">19.2556037902832</t>
@@ -1775,10 +1775,10 @@
     <t xml:space="preserve">19.3057479858398</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3726043701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8042984008789</t>
+    <t xml:space="preserve">19.3726062774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8043003082275</t>
   </si>
   <si>
     <t xml:space="preserve">18.6037197113037</t>
@@ -1787,49 +1787,49 @@
     <t xml:space="preserve">18.6872959136963</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6705799102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.704008102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8878746032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2221698760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6734771728516</t>
+    <t xml:space="preserve">18.670581817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7040100097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8878765106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2221717834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6734733581543</t>
   </si>
   <si>
     <t xml:space="preserve">19.6567611694336</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8907680511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0913505554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8406257629395</t>
+    <t xml:space="preserve">19.8907718658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0913524627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8406238555908</t>
   </si>
   <si>
     <t xml:space="preserve">19.589900970459</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0884532928467</t>
+    <t xml:space="preserve">19.088451385498</t>
   </si>
   <si>
     <t xml:space="preserve">19.7737636566162</t>
   </si>
   <si>
-    <t xml:space="preserve">19.640043258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4561824798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9213027954102</t>
+    <t xml:space="preserve">19.6400489807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.456184387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9213008880615</t>
   </si>
   <si>
     <t xml:space="preserve">19.3391761779785</t>
@@ -1841,64 +1841,64 @@
     <t xml:space="preserve">17.5506801605225</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0019836425781</t>
+    <t xml:space="preserve">18.0019817352295</t>
   </si>
   <si>
     <t xml:space="preserve">17.9016914367676</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4700031280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2359886169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4365673065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.041202545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3086414337158</t>
+    <t xml:space="preserve">18.4699993133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2359924316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4365711212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0412044525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3086395263672</t>
   </si>
   <si>
     <t xml:space="preserve">19.9910583496094</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3253555297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2861347198486</t>
+    <t xml:space="preserve">20.3253574371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2861366271973</t>
   </si>
   <si>
     <t xml:space="preserve">18.2694225311279</t>
   </si>
   <si>
-    <t xml:space="preserve">18.219274520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4198570251465</t>
+    <t xml:space="preserve">18.2192764282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4198589324951</t>
   </si>
   <si>
     <t xml:space="preserve">18.6538639068604</t>
   </si>
   <si>
-    <t xml:space="preserve">18.25270652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3529968261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5368633270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7541542053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6371479034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1553115844727</t>
+    <t xml:space="preserve">18.2527046203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3529930114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5368576049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7541561126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6371459960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1553134918213</t>
   </si>
   <si>
     <t xml:space="preserve">19.4060344696045</t>
@@ -1913,49 +1913,49 @@
     <t xml:space="preserve">19.3558883666992</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0215930938721</t>
+    <t xml:space="preserve">19.0215911865234</t>
   </si>
   <si>
     <t xml:space="preserve">19.3224639892578</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7403373718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1749229431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7875823974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9380187988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0077724456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2250709533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5789775848389</t>
+    <t xml:space="preserve">19.7403354644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1749210357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7875804901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9380168914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0077743530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2250690460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5789794921875</t>
   </si>
   <si>
     <t xml:space="preserve">21.1443881988525</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2054576873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0354099273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6509666442871</t>
+    <t xml:space="preserve">19.2054557800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0354137420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6509704589844</t>
   </si>
   <si>
     <t xml:space="preserve">17.4336738586426</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5841083526611</t>
+    <t xml:space="preserve">17.5841102600098</t>
   </si>
   <si>
     <t xml:space="preserve">17.1328067779541</t>
@@ -1967,100 +1967,100 @@
     <t xml:space="preserve">16.1716957092285</t>
   </si>
   <si>
-    <t xml:space="preserve">15.996190071106</t>
+    <t xml:space="preserve">15.9961881637573</t>
   </si>
   <si>
     <t xml:space="preserve">16.3221321105957</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8791818618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7939519882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7683792114258</t>
+    <t xml:space="preserve">15.8791875839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7939529418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.768383026123</t>
   </si>
   <si>
     <t xml:space="preserve">15.7769031524658</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3081130981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4018726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4359664916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5382471084595</t>
+    <t xml:space="preserve">15.3081121444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4018716812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4359645843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5382480621338</t>
   </si>
   <si>
     <t xml:space="preserve">15.163215637207</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3336820602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0524101257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1717376708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3507318496704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5552940368652</t>
+    <t xml:space="preserve">15.3336839675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0524082183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1717395782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3507328033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5552930831909</t>
   </si>
   <si>
     <t xml:space="preserve">15.6405296325684</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6490526199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6320056915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5808629989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4103965759277</t>
+    <t xml:space="preserve">15.6490507125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.632004737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5808658599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4103946685791</t>
   </si>
   <si>
     <t xml:space="preserve">15.0609340667725</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8904638290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9842252731323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0438861846924</t>
+    <t xml:space="preserve">14.8904647827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.984224319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0438871383667</t>
   </si>
   <si>
     <t xml:space="preserve">15.3763017654419</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4274435043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.282546043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0865049362183</t>
+    <t xml:space="preserve">15.4274444580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.282543182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0865058898926</t>
   </si>
   <si>
     <t xml:space="preserve">15.1120748519897</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1546936035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3251619338989</t>
+    <t xml:space="preserve">15.1546926498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3251609802246</t>
   </si>
   <si>
     <t xml:space="preserve">15.3592538833618</t>
@@ -2069,49 +2069,49 @@
     <t xml:space="preserve">14.9671754837036</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7455673217773</t>
+    <t xml:space="preserve">14.7455654144287</t>
   </si>
   <si>
     <t xml:space="preserve">14.6091909408569</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6518087387085</t>
+    <t xml:space="preserve">14.6518077850342</t>
   </si>
   <si>
     <t xml:space="preserve">14.5154342651367</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7114744186401</t>
+    <t xml:space="preserve">14.7114725112915</t>
   </si>
   <si>
     <t xml:space="preserve">14.6347618103027</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5410041809082</t>
+    <t xml:space="preserve">14.5410051345825</t>
   </si>
   <si>
     <t xml:space="preserve">14.3534898757935</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3449640274048</t>
+    <t xml:space="preserve">14.3449630737305</t>
   </si>
   <si>
     <t xml:space="preserve">14.4472465515137</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4387235641479</t>
+    <t xml:space="preserve">14.4387216567993</t>
   </si>
   <si>
     <t xml:space="preserve">14.7540893554688</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4642915725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4813404083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3620109558105</t>
+    <t xml:space="preserve">14.4642925262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4813385009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3620100021362</t>
   </si>
   <si>
     <t xml:space="preserve">15.2484502792358</t>
@@ -2120,40 +2120,40 @@
     <t xml:space="preserve">15.4956283569336</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0268421173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0012693405151</t>
+    <t xml:space="preserve">15.0268392562866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0012712478638</t>
   </si>
   <si>
     <t xml:space="preserve">14.6859016418457</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5324792861938</t>
+    <t xml:space="preserve">14.5324802398682</t>
   </si>
   <si>
     <t xml:space="preserve">13.9784555435181</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4046287536621</t>
+    <t xml:space="preserve">14.4046277999878</t>
   </si>
   <si>
     <t xml:space="preserve">15.035364151001</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1376457214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8308019638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9586505889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2399272918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.810996055603</t>
+    <t xml:space="preserve">15.1376447677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8308029174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9586524963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2399253845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8109970092773</t>
   </si>
   <si>
     <t xml:space="preserve">16.4843521118164</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">17.0468978881836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7911949157715</t>
+    <t xml:space="preserve">16.7911930084229</t>
   </si>
   <si>
     <t xml:space="preserve">16.5269660949707</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">16.5781097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3138809204102</t>
+    <t xml:space="preserve">16.3138790130615</t>
   </si>
   <si>
     <t xml:space="preserve">16.2371692657471</t>
@@ -2189,28 +2189,28 @@
     <t xml:space="preserve">15.3933477401733</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9416084289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5239572525024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9330816268921</t>
+    <t xml:space="preserve">14.9416065216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5239582061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9330835342407</t>
   </si>
   <si>
     <t xml:space="preserve">14.6603317260742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2512054443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1318788528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6177139282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4557695388794</t>
+    <t xml:space="preserve">14.2512044906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1318778991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6177167892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4557685852051</t>
   </si>
   <si>
     <t xml:space="preserve">14.5580492019653</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">14.5750970840454</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7370443344116</t>
+    <t xml:space="preserve">14.737042427063</t>
   </si>
   <si>
     <t xml:space="preserve">14.7796602249146</t>
@@ -2228,43 +2228,43 @@
     <t xml:space="preserve">14.8393239974976</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8478479385376</t>
+    <t xml:space="preserve">14.8478488922119</t>
   </si>
   <si>
     <t xml:space="preserve">14.6688547134399</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2341594696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1404008865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0636911392212</t>
+    <t xml:space="preserve">14.2341613769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1404037475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0636901855469</t>
   </si>
   <si>
     <t xml:space="preserve">14.8222761154175</t>
   </si>
   <si>
-    <t xml:space="preserve">14.626238822937</t>
+    <t xml:space="preserve">14.6262378692627</t>
   </si>
   <si>
     <t xml:space="preserve">15.0183172225952</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1291208267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2058334350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5467710494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8195199966431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0326080322266</t>
+    <t xml:space="preserve">15.1291217803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2058324813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5467691421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8195219039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0326042175293</t>
   </si>
   <si>
     <t xml:space="preserve">16.4502544403076</t>
@@ -2273,94 +2273,94 @@
     <t xml:space="preserve">16.4928722381592</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0155620574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1519374847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2030735015869</t>
+    <t xml:space="preserve">16.0155601501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1519355773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2030754089355</t>
   </si>
   <si>
     <t xml:space="preserve">16.041130065918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0752258300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8962326049805</t>
+    <t xml:space="preserve">16.0752239227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8962316513062</t>
   </si>
   <si>
     <t xml:space="preserve">16.2883110046387</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2627410888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1263675689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1178436279297</t>
+    <t xml:space="preserve">16.2627391815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1263656616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1178417205811</t>
   </si>
   <si>
     <t xml:space="preserve">16.1945533752441</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2286491394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.168981552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0667018890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2797889709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1093158721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7087154388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6746244430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9729423522949</t>
+    <t xml:space="preserve">16.2286472320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1689834594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0666999816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2797870635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.109317779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7087163925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6746225357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9729433059692</t>
   </si>
   <si>
     <t xml:space="preserve">15.7428102493286</t>
   </si>
   <si>
-    <t xml:space="preserve">15.342209815979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2910652160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1035509109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5665740966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2853002548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2426834106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5949010848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7057065963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6944265365601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5069093704224</t>
+    <t xml:space="preserve">15.3422060012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.291069984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1035499572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5665731430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2853012084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2426805496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5949001312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7057056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6944274902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5069103240967</t>
   </si>
   <si>
     <t xml:space="preserve">15.0694580078125</t>
@@ -2369,16 +2369,16 @@
     <t xml:space="preserve">15.4615345001221</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4444904327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4700593948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6149578094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.274022102356</t>
+    <t xml:space="preserve">15.4444913864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4700584411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6149587631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2740230560303</t>
   </si>
   <si>
     <t xml:space="preserve">15.2995910644531</t>
@@ -2387,25 +2387,25 @@
     <t xml:space="preserve">13.7142295837402</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3818140029907</t>
+    <t xml:space="preserve">13.381814956665</t>
   </si>
   <si>
     <t xml:space="preserve">13.5522832870483</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1772537231445</t>
+    <t xml:space="preserve">13.1772518157959</t>
   </si>
   <si>
     <t xml:space="preserve">13.2965803146362</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2624864578247</t>
+    <t xml:space="preserve">13.262487411499</t>
   </si>
   <si>
     <t xml:space="preserve">13.0323534011841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596025466919</t>
+    <t xml:space="preserve">12.7596035003662</t>
   </si>
   <si>
     <t xml:space="preserve">12.6232280731201</t>
@@ -2414,16 +2414,16 @@
     <t xml:space="preserve">12.359001159668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6600780487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1912879943848</t>
+    <t xml:space="preserve">11.6600790023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1912889480591</t>
   </si>
   <si>
     <t xml:space="preserve">10.8333044052124</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74230098724365</t>
+    <t xml:space="preserve">9.74230194091797</t>
   </si>
   <si>
     <t xml:space="preserve">10.6543111801147</t>
@@ -2438,25 +2438,25 @@
     <t xml:space="preserve">11.6686010360718</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0351104736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3306732177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.722752571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2767772674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0749711990356</t>
+    <t xml:space="preserve">12.0351085662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3306741714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7227535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2767782211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0749702453613</t>
   </si>
   <si>
     <t xml:space="preserve">13.5011434555054</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4500026702881</t>
+    <t xml:space="preserve">13.4500017166138</t>
   </si>
   <si>
     <t xml:space="preserve">12.9897356033325</t>
@@ -2474,28 +2474,28 @@
     <t xml:space="preserve">13.023829460144</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3562450408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4244318008423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6119470596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8192682266235</t>
+    <t xml:space="preserve">13.3562440872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4244327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6119480133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8192663192749</t>
   </si>
   <si>
     <t xml:space="preserve">12.6999387741089</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9045009613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0664472579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2113456726074</t>
+    <t xml:space="preserve">12.904501914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0664463043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2113466262817</t>
   </si>
   <si>
     <t xml:space="preserve">13.3988628387451</t>
@@ -2504,40 +2504,40 @@
     <t xml:space="preserve">13.313627243042</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8079872131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8932209014893</t>
+    <t xml:space="preserve">13.8079881668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8932218551636</t>
   </si>
   <si>
     <t xml:space="preserve">13.9358386993408</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0551662445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8846998214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4898614883423</t>
+    <t xml:space="preserve">14.0551671981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8846979141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4898633956909</t>
   </si>
   <si>
     <t xml:space="preserve">14.7029495239258</t>
   </si>
   <si>
-    <t xml:space="preserve">14.200065612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.498387336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4131526947021</t>
+    <t xml:space="preserve">14.2000675201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4983854293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4131507873535</t>
   </si>
   <si>
     <t xml:space="preserve">15.1205987930298</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7711372375488</t>
+    <t xml:space="preserve">14.7711381912231</t>
   </si>
   <si>
     <t xml:space="preserve">14.856372833252</t>
@@ -2546,31 +2546,31 @@
     <t xml:space="preserve">15.4189176559448</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9388494491577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7513303756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6207237243652</t>
+    <t xml:space="preserve">15.938850402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7513332366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6207256317139</t>
   </si>
   <si>
     <t xml:space="preserve">16.4161624908447</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2456932067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5440139770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7826690673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3707904815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4276962280273</t>
+    <t xml:space="preserve">16.2456951141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5440158843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7826709747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3707885742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.427698135376</t>
   </si>
   <si>
     <t xml:space="preserve">19.262996673584</t>
@@ -2579,13 +2579,13 @@
     <t xml:space="preserve">19.0754795074463</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6493053436279</t>
+    <t xml:space="preserve">18.6493072509766</t>
   </si>
   <si>
     <t xml:space="preserve">18.90500831604</t>
   </si>
   <si>
-    <t xml:space="preserve">19.603931427002</t>
+    <t xml:space="preserve">19.6039333343506</t>
   </si>
   <si>
     <t xml:space="preserve">19.6380290985107</t>
@@ -2594,25 +2594,25 @@
     <t xml:space="preserve">20.0641994476318</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8766822814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7744026184082</t>
+    <t xml:space="preserve">19.8766860961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7743988037109</t>
   </si>
   <si>
     <t xml:space="preserve">20.1494331359863</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0471515655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4846019744873</t>
+    <t xml:space="preserve">20.0471534729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4846038818359</t>
   </si>
   <si>
     <t xml:space="preserve">19.8425903320312</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8084945678711</t>
+    <t xml:space="preserve">19.8084964752197</t>
   </si>
   <si>
     <t xml:space="preserve">20.7119789123535</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">20.9506397247314</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6778888702393</t>
+    <t xml:space="preserve">20.6778869628906</t>
   </si>
   <si>
     <t xml:space="preserve">20.8483543395996</t>
@@ -2633,16 +2633,16 @@
     <t xml:space="preserve">21.0529193878174</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9335899353027</t>
+    <t xml:space="preserve">20.9335918426514</t>
   </si>
   <si>
     <t xml:space="preserve">21.0870132446289</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1551990509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.291576385498</t>
+    <t xml:space="preserve">21.1551971435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2915744781494</t>
   </si>
   <si>
     <t xml:space="preserve">21.2574825286865</t>
@@ -2657,61 +2657,61 @@
     <t xml:space="preserve">21.3086223602295</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8994960784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9676856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7631225585938</t>
+    <t xml:space="preserve">20.8994979858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9676818847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7631206512451</t>
   </si>
   <si>
     <t xml:space="preserve">20.9165420532227</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1609649658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6382827758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0133113861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9167976379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8145179748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9679355621338</t>
+    <t xml:space="preserve">22.1609668731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6382789611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.013313293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9167957305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8145198822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9679393768311</t>
   </si>
   <si>
     <t xml:space="preserve">24.0020332336426</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5758590698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8656578063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7974681854248</t>
+    <t xml:space="preserve">23.5758609771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8656558990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7974720001221</t>
   </si>
   <si>
     <t xml:space="preserve">23.5247192382812</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5929069519043</t>
+    <t xml:space="preserve">23.5929050445557</t>
   </si>
   <si>
     <t xml:space="preserve">23.6610946655273</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8486080169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6781425476074</t>
+    <t xml:space="preserve">23.8486099243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6781406402588</t>
   </si>
   <si>
     <t xml:space="preserve">23.4394836425781</t>
@@ -2720,7 +2720,7 @@
     <t xml:space="preserve">23.7292804718018</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7463302612305</t>
+    <t xml:space="preserve">23.7463283538818</t>
   </si>
   <si>
     <t xml:space="preserve">23.6951885223389</t>
@@ -2732,40 +2732,40 @@
     <t xml:space="preserve">23.7633743286133</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1496887207031</t>
+    <t xml:space="preserve">23.1496868133545</t>
   </si>
   <si>
     <t xml:space="preserve">23.9849853515625</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8997497558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4963932037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2123603820801</t>
+    <t xml:space="preserve">23.899751663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4963912963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2123641967773</t>
   </si>
   <si>
     <t xml:space="preserve">24.5304870605469</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1100826263428</t>
+    <t xml:space="preserve">25.1100807189941</t>
   </si>
   <si>
     <t xml:space="preserve">26.0647068023682</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4680652618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5533008575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4851131439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1271286010742</t>
+    <t xml:space="preserve">25.4680633544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5532989501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4851112365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1271266937256</t>
   </si>
   <si>
     <t xml:space="preserve">25.0589408874512</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">24.7180023193359</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3487377166748</t>
+    <t xml:space="preserve">25.3487358093262</t>
   </si>
   <si>
     <t xml:space="preserve">25.2294082641602</t>
@@ -2798,37 +2798,37 @@
     <t xml:space="preserve">25.3657855987549</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9453773498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8829593658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7636280059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0306148529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9283332824707</t>
+    <t xml:space="preserve">25.9453811645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8829574584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7636299133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0306129455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9283294677734</t>
   </si>
   <si>
     <t xml:space="preserve">26.0135669708252</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1441745758057</t>
+    <t xml:space="preserve">25.144172668457</t>
   </si>
   <si>
     <t xml:space="preserve">24.956657409668</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4224395751953</t>
+    <t xml:space="preserve">23.422435760498</t>
   </si>
   <si>
     <t xml:space="preserve">23.2690143585205</t>
   </si>
   <si>
-    <t xml:space="preserve">23.405387878418</t>
+    <t xml:space="preserve">23.4053916931152</t>
   </si>
   <si>
     <t xml:space="preserve">23.4565334320068</t>
@@ -2837,22 +2837,22 @@
     <t xml:space="preserve">24.837329864502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0930309295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5703506469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6385364532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3600177764893</t>
+    <t xml:space="preserve">25.0930328369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5703468322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6385326385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3600158691406</t>
   </si>
   <si>
     <t xml:space="preserve">24.1384086608887</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9112854003906</t>
+    <t xml:space="preserve">25.911283493042</t>
   </si>
   <si>
     <t xml:space="preserve">24.5475311279297</t>
@@ -2861,40 +2861,40 @@
     <t xml:space="preserve">23.8315601348877</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5588130950928</t>
+    <t xml:space="preserve">23.5588111877441</t>
   </si>
   <si>
     <t xml:space="preserve">24.1213607788086</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5417671203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0985469818115</t>
+    <t xml:space="preserve">23.5417652130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0985450744629</t>
   </si>
   <si>
     <t xml:space="preserve">24.2747821807861</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9396095275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2918262481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0702209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5076713562012</t>
+    <t xml:space="preserve">24.9396114349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2918319702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0702171325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5076732635498</t>
   </si>
   <si>
     <t xml:space="preserve">23.3372020721436</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1837787628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6894207000732</t>
+    <t xml:space="preserve">23.183780670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6894226074219</t>
   </si>
   <si>
     <t xml:space="preserve">23.1667346954346</t>
@@ -2912,19 +2912,19 @@
     <t xml:space="preserve">22.6984977722168</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5941333770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8202514648438</t>
+    <t xml:space="preserve">22.5941371917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8202495574951</t>
   </si>
   <si>
     <t xml:space="preserve">22.420202255249</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7854614257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2898750305176</t>
+    <t xml:space="preserve">22.7854652404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2898769378662</t>
   </si>
   <si>
     <t xml:space="preserve">22.8028564453125</t>
@@ -2933,10 +2933,10 @@
     <t xml:space="preserve">22.8724308013916</t>
   </si>
   <si>
-    <t xml:space="preserve">22.750675201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7158908843994</t>
+    <t xml:space="preserve">22.7506771087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7158889770508</t>
   </si>
   <si>
     <t xml:space="preserve">22.246265411377</t>
@@ -2945,43 +2945,43 @@
     <t xml:space="preserve">22.33323097229</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4723796844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2550868988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5769920349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3597011566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.551025390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1945858001709</t>
+    <t xml:space="preserve">22.4723777770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2550849914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5769939422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3596992492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5510272979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1945877075195</t>
   </si>
   <si>
     <t xml:space="preserve">26.4207000732422</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7597503662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4033088684082</t>
+    <t xml:space="preserve">25.7597484588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4033069610596</t>
   </si>
   <si>
     <t xml:space="preserve">27.0294723510742</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1860160827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1164436340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.012077331543</t>
+    <t xml:space="preserve">27.186014175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1164417266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0120811462402</t>
   </si>
   <si>
     <t xml:space="preserve">28.1426563262939</t>
@@ -2990,25 +2990,25 @@
     <t xml:space="preserve">28.8036079406738</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0992984771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3775939941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5863208770752</t>
+    <t xml:space="preserve">29.0992965698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3775901794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5863151550293</t>
   </si>
   <si>
     <t xml:space="preserve">30.0385456085205</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2210483551025</t>
+    <t xml:space="preserve">29.2210502624512</t>
   </si>
   <si>
     <t xml:space="preserve">29.081901550293</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7688236236572</t>
+    <t xml:space="preserve">28.7688217163086</t>
   </si>
   <si>
     <t xml:space="preserve">28.4035587310791</t>
@@ -3020,25 +3020,25 @@
     <t xml:space="preserve">26.7859649658203</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5946369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4121284484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6294231414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6208534240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6468181610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5250644683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2034072875977</t>
+    <t xml:space="preserve">26.5946350097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.412130355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6294250488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6208515167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6468162536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5250625610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2034091949463</t>
   </si>
   <si>
     <t xml:space="preserve">27.3077697753906</t>
@@ -3047,10 +3047,10 @@
     <t xml:space="preserve">27.707820892334</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1081218719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1340847015381</t>
+    <t xml:space="preserve">30.108118057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1340866088867</t>
   </si>
   <si>
     <t xml:space="preserve">29.047119140625</t>
@@ -3059,34 +3059,34 @@
     <t xml:space="preserve">29.2906284332275</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8905754089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3080215454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8560390472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7342796325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2298736572266</t>
+    <t xml:space="preserve">28.8905773162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3080196380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8560409545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7342853546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2298717498779</t>
   </si>
   <si>
     <t xml:space="preserve">30.3690223693848</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4385986328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0559425354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2994480133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9515781402588</t>
+    <t xml:space="preserve">30.4385948181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0559368133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2994518280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9515762329102</t>
   </si>
   <si>
     <t xml:space="preserve">30.6125316619873</t>
@@ -3095,46 +3095,46 @@
     <t xml:space="preserve">30.9951877593994</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6039619445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8300762176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5691738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8648643493652</t>
+    <t xml:space="preserve">31.6039638519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8300743103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5691719055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8648624420166</t>
   </si>
   <si>
     <t xml:space="preserve">31.7778949737549</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4995975494385</t>
+    <t xml:space="preserve">31.4995956420898</t>
   </si>
   <si>
     <t xml:space="preserve">32.0387992858887</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6909236907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3430633544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.447416305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2734813690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7605037689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7083187103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5865650177002</t>
+    <t xml:space="preserve">31.6909275054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3430576324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4474182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2734832763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7605018615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.708324432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5865631103516</t>
   </si>
   <si>
     <t xml:space="preserve">31.743106842041</t>
@@ -3146,13 +3146,13 @@
     <t xml:space="preserve">31.6735305786133</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3866653442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.560604095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.847469329834</t>
+    <t xml:space="preserve">32.3866691589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5606002807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8474655151367</t>
   </si>
   <si>
     <t xml:space="preserve">32.5432090759277</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">31.8996486663818</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5169925689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7952880859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.812686920166</t>
+    <t xml:space="preserve">31.516996383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7952919006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8126850128174</t>
   </si>
   <si>
     <t xml:space="preserve">31.6213531494141</t>
@@ -3176,43 +3176,43 @@
     <t xml:space="preserve">31.4822082519531</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3952388763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1553268432617</t>
+    <t xml:space="preserve">31.3952331542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.155330657959</t>
   </si>
   <si>
     <t xml:space="preserve">31.9081153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7845077514648</t>
+    <t xml:space="preserve">31.7845096588135</t>
   </si>
   <si>
     <t xml:space="preserve">32.1376724243164</t>
   </si>
   <si>
-    <t xml:space="preserve">32.172981262207</t>
+    <t xml:space="preserve">32.1729850769043</t>
   </si>
   <si>
     <t xml:space="preserve">32.2612800598145</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2789344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7491931915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7668514251709</t>
+    <t xml:space="preserve">32.278938293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7491912841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7668533325195</t>
   </si>
   <si>
     <t xml:space="preserve">31.8728008270264</t>
   </si>
   <si>
-    <t xml:space="preserve">32.667407989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0029182434082</t>
+    <t xml:space="preserve">32.6674118041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0029144287109</t>
   </si>
   <si>
     <t xml:space="preserve">33.4443664550781</t>
@@ -3221,28 +3221,28 @@
     <t xml:space="preserve">33.3031044006348</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3096084594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9982757568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9806175231934</t>
+    <t xml:space="preserve">34.3096122741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9982719421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9806213378906</t>
   </si>
   <si>
     <t xml:space="preserve">35.2808036804199</t>
   </si>
   <si>
-    <t xml:space="preserve">34.786376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9564514160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7975311279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3384132385254</t>
+    <t xml:space="preserve">34.7863807678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9564476013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7975273132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3384170532227</t>
   </si>
   <si>
     <t xml:space="preserve">32.9499397277832</t>
@@ -3251,19 +3251,19 @@
     <t xml:space="preserve">33.179500579834</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2148094177246</t>
+    <t xml:space="preserve">33.2148132324219</t>
   </si>
   <si>
     <t xml:space="preserve">33.0912055969238</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4378623962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0205726623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.843994140625</t>
+    <t xml:space="preserve">32.437858581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0205764770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8439903259277</t>
   </si>
   <si>
     <t xml:space="preserve">33.1441802978516</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">32.0317192077637</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3319091796875</t>
+    <t xml:space="preserve">32.3319053649902</t>
   </si>
   <si>
     <t xml:space="preserve">32.7027282714844</t>
@@ -3281,22 +3281,22 @@
     <t xml:space="preserve">33.2677879333496</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4267120361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8616523742676</t>
+    <t xml:space="preserve">33.4267082214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8616485595703</t>
   </si>
   <si>
     <t xml:space="preserve">32.2083015441895</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2017879486084</t>
+    <t xml:space="preserve">31.2017936706543</t>
   </si>
   <si>
     <t xml:space="preserve">31.1135025024414</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9610939025879</t>
+    <t xml:space="preserve">31.9610900878906</t>
   </si>
   <si>
     <t xml:space="preserve">33.126522064209</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">32.9322814941406</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9257717132568</t>
+    <t xml:space="preserve">31.9257755279541</t>
   </si>
   <si>
     <t xml:space="preserve">32.5438041687012</t>
@@ -3317,10 +3317,10 @@
     <t xml:space="preserve">33.8681602478027</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0800514221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3449325561523</t>
+    <t xml:space="preserve">34.0800552368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3449287414551</t>
   </si>
   <si>
     <t xml:space="preserve">34.380241394043</t>
@@ -3332,16 +3332,16 @@
     <t xml:space="preserve">34.5215110778809</t>
   </si>
   <si>
-    <t xml:space="preserve">34.150691986084</t>
+    <t xml:space="preserve">34.1506881713867</t>
   </si>
   <si>
     <t xml:space="preserve">34.2036628723145</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1153678894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9387893676758</t>
+    <t xml:space="preserve">34.1153717041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9387969970703</t>
   </si>
   <si>
     <t xml:space="preserve">33.6209526062012</t>
@@ -3353,13 +3353,13 @@
     <t xml:space="preserve">34.2919540405273</t>
   </si>
   <si>
-    <t xml:space="preserve">34.503849029541</t>
+    <t xml:space="preserve">34.5038566589355</t>
   </si>
   <si>
     <t xml:space="preserve">32.914623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">33.197151184082</t>
+    <t xml:space="preserve">33.1971549987793</t>
   </si>
   <si>
     <t xml:space="preserve">33.5149993896484</t>
@@ -3371,19 +3371,19 @@
     <t xml:space="preserve">33.815185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6451148986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1395416259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8570098876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6804313659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0865669250488</t>
+    <t xml:space="preserve">34.6451187133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1395378112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8570137023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6804351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0865707397461</t>
   </si>
   <si>
     <t xml:space="preserve">34.3272666931152</t>
@@ -3395,22 +3395,22 @@
     <t xml:space="preserve">30.424840927124</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1776256561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0716781616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5595970153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6125679016113</t>
+    <t xml:space="preserve">30.1776294708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0716800689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.559591293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6125659942627</t>
   </si>
   <si>
     <t xml:space="preserve">29.6478862762451</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2306022644043</t>
+    <t xml:space="preserve">30.2306003570557</t>
   </si>
   <si>
     <t xml:space="preserve">29.3476982116699</t>
@@ -3419,10 +3419,10 @@
     <t xml:space="preserve">29.0121936798096</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2882118225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8467636108398</t>
+    <t xml:space="preserve">28.2882137298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8467617034912</t>
   </si>
   <si>
     <t xml:space="preserve">27.4406261444092</t>
@@ -3437,64 +3437,64 @@
     <t xml:space="preserve">27.7937870025635</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6348628997803</t>
+    <t xml:space="preserve">27.6348648071289</t>
   </si>
   <si>
     <t xml:space="preserve">28.0763149261475</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0410003662109</t>
+    <t xml:space="preserve">28.0409984588623</t>
   </si>
   <si>
     <t xml:space="preserve">28.3058738708496</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2240905761719</t>
+    <t xml:space="preserve">29.2240886688232</t>
   </si>
   <si>
     <t xml:space="preserve">29.1004829406738</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4713039398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.135799407959</t>
+    <t xml:space="preserve">29.471305847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1358013153076</t>
   </si>
   <si>
     <t xml:space="preserve">29.3123817443848</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8244647979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9480686187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7891483306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2417469024658</t>
+    <t xml:space="preserve">29.8244609832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9480667114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7891502380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2417488098145</t>
   </si>
   <si>
     <t xml:space="preserve">29.8421211242676</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0010452270508</t>
+    <t xml:space="preserve">30.0010433197021</t>
   </si>
   <si>
     <t xml:space="preserve">29.9833869934082</t>
   </si>
   <si>
-    <t xml:space="preserve">30.566104888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9545822143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1952819824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1246528625488</t>
+    <t xml:space="preserve">30.5661010742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9545803070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1952857971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1246509552002</t>
   </si>
   <si>
     <t xml:space="preserve">29.3300380706787</t>
@@ -3518,58 +3518,58 @@
     <t xml:space="preserve">27.7231559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3876552581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6989898681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8755683898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0698070526123</t>
+    <t xml:space="preserve">27.3876533508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6989860534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8755722045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0698051452637</t>
   </si>
   <si>
     <t xml:space="preserve">25.7807693481445</t>
   </si>
   <si>
-    <t xml:space="preserve">26.434118270874</t>
+    <t xml:space="preserve">26.4341163635254</t>
   </si>
   <si>
     <t xml:space="preserve">26.1162719726562</t>
   </si>
   <si>
-    <t xml:space="preserve">26.85791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3634853363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1339282989502</t>
+    <t xml:space="preserve">26.8579120635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3634834289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1339321136475</t>
   </si>
   <si>
     <t xml:space="preserve">26.3987998962402</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1404399871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5753841400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7519607543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.310510635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4694309234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8225917816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2110710144043</t>
+    <t xml:space="preserve">27.140438079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.575382232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7519626617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3105087280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4694328308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8225955963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2110729217529</t>
   </si>
   <si>
     <t xml:space="preserve">27.0521488189697</t>
@@ -3578,16 +3578,16 @@
     <t xml:space="preserve">27.3523349761963</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9815158843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9350528717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4053134918213</t>
+    <t xml:space="preserve">26.981517791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9350509643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8291053771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4053077697754</t>
   </si>
   <si>
     <t xml:space="preserve">27.7761287689209</t>
@@ -3596,28 +3596,28 @@
     <t xml:space="preserve">27.6525249481201</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3699913024902</t>
+    <t xml:space="preserve">27.3699932098389</t>
   </si>
   <si>
     <t xml:space="preserve">26.4164581298828</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9155235290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0214729309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.721284866333</t>
+    <t xml:space="preserve">24.9155216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0214710235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7212867736816</t>
   </si>
   <si>
     <t xml:space="preserve">24.8978672027588</t>
   </si>
   <si>
-    <t xml:space="preserve">25.268684387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5447044372559</t>
+    <t xml:space="preserve">25.2686862945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5447025299072</t>
   </si>
   <si>
     <t xml:space="preserve">24.10325050354</t>
@@ -3626,13 +3626,13 @@
     <t xml:space="preserve">23.8383808135986</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6924800872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.451774597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5112590789795</t>
+    <t xml:space="preserve">25.692476272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4517726898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5112571716309</t>
   </si>
   <si>
     <t xml:space="preserve">27.9703674316406</t>
@@ -3641,16 +3641,16 @@
     <t xml:space="preserve">27.2993602752686</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9285449981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5289192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.475944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9638576507568</t>
+    <t xml:space="preserve">26.9285430908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5289173126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4759407043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9638595581055</t>
   </si>
   <si>
     <t xml:space="preserve">26.3811416625977</t>
@@ -3659,7 +3659,7 @@
     <t xml:space="preserve">26.8932247161865</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1757564544678</t>
+    <t xml:space="preserve">27.1757545471191</t>
   </si>
   <si>
     <t xml:space="preserve">26.7872772216797</t>
@@ -3668,34 +3668,34 @@
     <t xml:space="preserve">26.0986156463623</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4629230499268</t>
+    <t xml:space="preserve">25.4629249572754</t>
   </si>
   <si>
     <t xml:space="preserve">24.8095760345459</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2333698272705</t>
+    <t xml:space="preserve">25.2333679199219</t>
   </si>
   <si>
     <t xml:space="preserve">25.1274185180664</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7389450073242</t>
+    <t xml:space="preserve">24.7389430999756</t>
   </si>
   <si>
     <t xml:space="preserve">24.1738834381104</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4080772399902</t>
+    <t xml:space="preserve">22.4080791473389</t>
   </si>
   <si>
     <t xml:space="preserve">21.4192295074463</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3662528991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6906089782715</t>
+    <t xml:space="preserve">21.3662548065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6906070709229</t>
   </si>
   <si>
     <t xml:space="preserve">21.066068649292</t>
@@ -3704,52 +3704,52 @@
     <t xml:space="preserve">20.9424610137939</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3551044464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7723903656006</t>
+    <t xml:space="preserve">22.3551025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.772388458252</t>
   </si>
   <si>
     <t xml:space="preserve">22.7788982391357</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4610538482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2844715118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2315006256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8077030181885</t>
+    <t xml:space="preserve">22.4610557556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2844696044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2314987182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8077049255371</t>
   </si>
   <si>
     <t xml:space="preserve">21.5251750946045</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4722023010254</t>
+    <t xml:space="preserve">21.4722003936768</t>
   </si>
   <si>
     <t xml:space="preserve">21.5604915618896</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9907970428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3374462127686</t>
+    <t xml:space="preserve">22.990795135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3374443054199</t>
   </si>
   <si>
     <t xml:space="preserve">21.8430213928223</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7547302246094</t>
+    <t xml:space="preserve">21.754732131958</t>
   </si>
   <si>
     <t xml:space="preserve">21.7900485992432</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5958080291748</t>
+    <t xml:space="preserve">21.5958061218262</t>
   </si>
   <si>
     <t xml:space="preserve">21.3839111328125</t>
@@ -3761,52 +3761,52 @@
     <t xml:space="preserve">21.1896724700928</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1367015838623</t>
+    <t xml:space="preserve">21.136697769165</t>
   </si>
   <si>
     <t xml:space="preserve">21.4015693664551</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7658805847168</t>
+    <t xml:space="preserve">20.7658767700195</t>
   </si>
   <si>
     <t xml:space="preserve">20.8365116119385</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0595569610596</t>
+    <t xml:space="preserve">20.0595550537109</t>
   </si>
   <si>
     <t xml:space="preserve">19.9359512329102</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3773994445801</t>
+    <t xml:space="preserve">20.3774032592773</t>
   </si>
   <si>
     <t xml:space="preserve">20.5186653137207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8653182983398</t>
+    <t xml:space="preserve">19.8653202056885</t>
   </si>
   <si>
     <t xml:space="preserve">20.0065822601318</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7835369110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5363254547119</t>
+    <t xml:space="preserve">20.7835388183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5363235473633</t>
   </si>
   <si>
     <t xml:space="preserve">20.041898727417</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1943111419678</t>
+    <t xml:space="preserve">19.1943130493164</t>
   </si>
   <si>
     <t xml:space="preserve">19.4238662719727</t>
   </si>
   <si>
-    <t xml:space="preserve">19.777027130127</t>
+    <t xml:space="preserve">19.7770290374756</t>
   </si>
   <si>
     <t xml:space="preserve">20.3420886993408</t>
@@ -3815,19 +3815,19 @@
     <t xml:space="preserve">19.3355751037598</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5474700927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6710796356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.911153793335</t>
+    <t xml:space="preserve">19.5474739074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6710815429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9111518859863</t>
   </si>
   <si>
     <t xml:space="preserve">19.0677719116211</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4711265563965</t>
+    <t xml:space="preserve">19.4711303710938</t>
   </si>
   <si>
     <t xml:space="preserve">20.1311645507812</t>
@@ -3839,19 +3839,19 @@
     <t xml:space="preserve">20.9012107849121</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6995334625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.314510345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6445331573486</t>
+    <t xml:space="preserve">20.6995315551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3145122528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6445293426514</t>
   </si>
   <si>
     <t xml:space="preserve">20.0944976806641</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4061832427979</t>
+    <t xml:space="preserve">20.4061851501465</t>
   </si>
   <si>
     <t xml:space="preserve">20.1678371429443</t>
@@ -3860,16 +3860,16 @@
     <t xml:space="preserve">19.5811367034912</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3061199188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3710670471191</t>
+    <t xml:space="preserve">19.306116104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3710651397705</t>
   </si>
   <si>
     <t xml:space="preserve">18.7560882568359</t>
   </si>
   <si>
-    <t xml:space="preserve">19.012767791748</t>
+    <t xml:space="preserve">19.0127696990967</t>
   </si>
   <si>
     <t xml:space="preserve">18.0960502624512</t>
@@ -3890,31 +3890,31 @@
     <t xml:space="preserve">17.261833190918</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1793270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2343311309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0968246459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7576389312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2626094818115</t>
+    <t xml:space="preserve">17.1793308258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2343330383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0968227386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.757640838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2626075744629</t>
   </si>
   <si>
     <t xml:space="preserve">16.1617698669434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1709365844727</t>
+    <t xml:space="preserve">16.1709384918213</t>
   </si>
   <si>
     <t xml:space="preserve">15.9875946044922</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3817844390869</t>
+    <t xml:space="preserve">16.3817863464355</t>
   </si>
   <si>
     <t xml:space="preserve">16.7851390838623</t>
@@ -3926,25 +3926,25 @@
     <t xml:space="preserve">17.188497543335</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4635105133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9501476287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4092845916748</t>
+    <t xml:space="preserve">17.4635124206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9501495361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4092864990234</t>
   </si>
   <si>
     <t xml:space="preserve">16.6843013763428</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9043121337891</t>
+    <t xml:space="preserve">16.9043140411377</t>
   </si>
   <si>
     <t xml:space="preserve">17.0693225860596</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9593181610107</t>
+    <t xml:space="preserve">16.9593162536621</t>
   </si>
   <si>
     <t xml:space="preserve">17.1334934234619</t>
@@ -3956,7 +3956,7 @@
     <t xml:space="preserve">16.3359470367432</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8500862121582</t>
+    <t xml:space="preserve">15.8500871658325</t>
   </si>
   <si>
     <t xml:space="preserve">16.8218078613281</t>
@@ -3965,34 +3965,34 @@
     <t xml:space="preserve">16.5284595489502</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1151599884033</t>
+    <t xml:space="preserve">17.1151580810547</t>
   </si>
   <si>
     <t xml:space="preserve">17.8852043151855</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6560249328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6376914978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8859806060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4726810455322</t>
+    <t xml:space="preserve">17.6560230255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6376876831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8859786987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4726791381836</t>
   </si>
   <si>
     <t xml:space="preserve">17.5643520355225</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6835269927979</t>
+    <t xml:space="preserve">17.6835250854492</t>
   </si>
   <si>
     <t xml:space="preserve">17.6651916503906</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2159996032715</t>
+    <t xml:space="preserve">17.2159976959229</t>
   </si>
   <si>
     <t xml:space="preserve">17.3351726531982</t>
@@ -4010,7 +4010,7 @@
     <t xml:space="preserve">16.4001178741455</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9967613220215</t>
+    <t xml:space="preserve">15.9967622756958</t>
   </si>
   <si>
     <t xml:space="preserve">15.9417572021484</t>
@@ -4019,31 +4019,31 @@
     <t xml:space="preserve">16.0425968170166</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0150966644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6392383575439</t>
+    <t xml:space="preserve">16.0150947570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6392402648926</t>
   </si>
   <si>
     <t xml:space="preserve">15.9142560958862</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0525398254395</t>
+    <t xml:space="preserve">15.0525388717651</t>
   </si>
   <si>
     <t xml:space="preserve">15.2542181015015</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2175512313843</t>
+    <t xml:space="preserve">15.2175493240356</t>
   </si>
   <si>
     <t xml:space="preserve">15.1992158889771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6117372512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0059261322021</t>
+    <t xml:space="preserve">15.6117401123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0059280395508</t>
   </si>
   <si>
     <t xml:space="preserve">15.6942434310913</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">13.6041231155396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3841094970703</t>
+    <t xml:space="preserve">13.3841104507446</t>
   </si>
   <si>
     <t xml:space="preserve">13.5857877731323</t>
@@ -4076,22 +4076,22 @@
     <t xml:space="preserve">13.7599649429321</t>
   </si>
   <si>
-    <t xml:space="preserve">13.924973487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.310772895813</t>
+    <t xml:space="preserve">13.9249744415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3107719421387</t>
   </si>
   <si>
     <t xml:space="preserve">13.8149671554565</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5032825469971</t>
+    <t xml:space="preserve">13.5032815933228</t>
   </si>
   <si>
     <t xml:space="preserve">13.8883047103882</t>
   </si>
   <si>
-    <t xml:space="preserve">13.512451171875</t>
+    <t xml:space="preserve">13.5124502182007</t>
   </si>
   <si>
     <t xml:space="preserve">13.6591243743896</t>
@@ -4100,16 +4100,16 @@
     <t xml:space="preserve">13.3382730484009</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4482803344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8516368865967</t>
+    <t xml:space="preserve">13.4482793807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8516359329224</t>
   </si>
   <si>
     <t xml:space="preserve">13.5307846069336</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8424692153931</t>
+    <t xml:space="preserve">13.8424701690674</t>
   </si>
   <si>
     <t xml:space="preserve">14.1908226013184</t>
@@ -4121,7 +4121,7 @@
     <t xml:space="preserve">14.603346824646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1816558837891</t>
+    <t xml:space="preserve">14.1816549301147</t>
   </si>
   <si>
     <t xml:space="preserve">14.5483427047729</t>
@@ -4133,25 +4133,25 @@
     <t xml:space="preserve">15.5659017562866</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7217426300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9050884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1526050567627</t>
+    <t xml:space="preserve">15.7217454910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9050903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1526031494141</t>
   </si>
   <si>
     <t xml:space="preserve">16.7026348114014</t>
   </si>
   <si>
-    <t xml:space="preserve">17.243501663208</t>
+    <t xml:space="preserve">17.2434997558594</t>
   </si>
   <si>
     <t xml:space="preserve">17.509349822998</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2427253723145</t>
+    <t xml:space="preserve">18.2427234649658</t>
   </si>
   <si>
     <t xml:space="preserve">20.5528583526611</t>
@@ -4163,13 +4163,13 @@
     <t xml:space="preserve">19.4161262512207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.15944480896</t>
+    <t xml:space="preserve">19.1594429016113</t>
   </si>
   <si>
     <t xml:space="preserve">19.0494384765625</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6178035736084</t>
+    <t xml:space="preserve">19.617805480957</t>
   </si>
   <si>
     <t xml:space="preserve">20.2595081329346</t>
@@ -4178,13 +4178,13 @@
     <t xml:space="preserve">19.7094764709473</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3794574737549</t>
+    <t xml:space="preserve">19.3794555664062</t>
   </si>
   <si>
     <t xml:space="preserve">19.562801361084</t>
   </si>
   <si>
-    <t xml:space="preserve">19.892822265625</t>
+    <t xml:space="preserve">19.8928184509277</t>
   </si>
   <si>
     <t xml:space="preserve">19.6544742584229</t>
@@ -4193,22 +4193,22 @@
     <t xml:space="preserve">19.8561515808105</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4527950286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5261325836182</t>
+    <t xml:space="preserve">19.4527969360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5261306762695</t>
   </si>
   <si>
     <t xml:space="preserve">19.7278099060059</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3695125579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.837818145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3244552612305</t>
+    <t xml:space="preserve">20.369514465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8378162384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3244514465332</t>
   </si>
   <si>
     <t xml:space="preserve">18.9760990142822</t>
@@ -4220,16 +4220,16 @@
     <t xml:space="preserve">19.2144470214844</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6728057861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.232780456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0578308105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1128330230713</t>
+    <t xml:space="preserve">19.6728076934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2327823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0578289031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1128311157227</t>
   </si>
   <si>
     <t xml:space="preserve">20.2961769104004</t>
@@ -4241,49 +4241,49 @@
     <t xml:space="preserve">21.8179321289062</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2495670318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.992883682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7728691101074</t>
+    <t xml:space="preserve">21.2495651245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9928855895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7728710174561</t>
   </si>
   <si>
     <t xml:space="preserve">20.8828773498535</t>
   </si>
   <si>
-    <t xml:space="preserve">21.047887802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8095378875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7362041473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7828140258789</t>
+    <t xml:space="preserve">21.0478858947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8095397949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7362022399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7828121185303</t>
   </si>
   <si>
     <t xml:space="preserve">19.7644786834717</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2511177062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8660926818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3977928161621</t>
+    <t xml:space="preserve">19.2511157989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8660945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3977909088135</t>
   </si>
   <si>
     <t xml:space="preserve">19.3427886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4894618988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5994663238525</t>
+    <t xml:space="preserve">19.4894638061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5994701385498</t>
   </si>
   <si>
     <t xml:space="preserve">20.3511810302734</t>
@@ -4292,13 +4292,13 @@
     <t xml:space="preserve">19.8744850158691</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1495018005371</t>
+    <t xml:space="preserve">20.1494998931885</t>
   </si>
   <si>
     <t xml:space="preserve">20.0761623382568</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0394954681396</t>
+    <t xml:space="preserve">20.0394973754883</t>
   </si>
   <si>
     <t xml:space="preserve">20.9745483398438</t>
@@ -4307,19 +4307,19 @@
     <t xml:space="preserve">21.2128963470459</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5795841217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6345901489258</t>
+    <t xml:space="preserve">21.5795860290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6345863342285</t>
   </si>
   <si>
     <t xml:space="preserve">21.6529216766357</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6162528991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5429172515869</t>
+    <t xml:space="preserve">21.6162509918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5429153442383</t>
   </si>
   <si>
     <t xml:space="preserve">20.6811981201172</t>
@@ -4331,7 +4331,7 @@
     <t xml:space="preserve">20.6628646850586</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4245185852051</t>
+    <t xml:space="preserve">20.4245204925537</t>
   </si>
   <si>
     <t xml:space="preserve">20.5711936950684</t>
@@ -4340,22 +4340,22 @@
     <t xml:space="preserve">19.966157913208</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5077972412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3611240386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5444641113281</t>
+    <t xml:space="preserve">19.5077991485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3611221313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5444660186768</t>
   </si>
   <si>
     <t xml:space="preserve">19.9294891357422</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0211620330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6460800170898</t>
+    <t xml:space="preserve">20.0211601257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6460819244385</t>
   </si>
   <si>
     <t xml:space="preserve">18.4444026947021</t>
@@ -4364,25 +4364,25 @@
     <t xml:space="preserve">18.481071472168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.609411239624</t>
+    <t xml:space="preserve">18.6094093322754</t>
   </si>
   <si>
     <t xml:space="preserve">18.4077339172363</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3343944549561</t>
+    <t xml:space="preserve">18.3343963623047</t>
   </si>
   <si>
     <t xml:space="preserve">18.9210948944092</t>
   </si>
   <si>
-    <t xml:space="preserve">19.287784576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1961135864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1044406890869</t>
+    <t xml:space="preserve">19.2877864837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1961116790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1044425964355</t>
   </si>
   <si>
     <t xml:space="preserve">18.7201499938965</t>
@@ -4391,7 +4391,7 @@
     <t xml:space="preserve">18.6169300079346</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8756294250488</t>
+    <t xml:space="preserve">17.8756313323975</t>
   </si>
   <si>
     <t xml:space="preserve">17.5378246307373</t>
@@ -4400,7 +4400,7 @@
     <t xml:space="preserve">17.7348785400391</t>
   </si>
   <si>
-    <t xml:space="preserve">17.641040802002</t>
+    <t xml:space="preserve">17.6410427093506</t>
   </si>
   <si>
     <t xml:space="preserve">17.2469329833984</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">16.89035987854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9091262817383</t>
+    <t xml:space="preserve">16.9091281890869</t>
   </si>
   <si>
     <t xml:space="preserve">17.078031539917</t>
@@ -4436,10 +4436,10 @@
     <t xml:space="preserve">18.1852855682373</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2885074615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5659732818604</t>
+    <t xml:space="preserve">18.2885055541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.565975189209</t>
   </si>
   <si>
     <t xml:space="preserve">18.0069999694824</t>
@@ -4451,7 +4451,7 @@
     <t xml:space="preserve">17.8662490844727</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8005599975586</t>
+    <t xml:space="preserve">17.8005619049072</t>
   </si>
   <si>
     <t xml:space="preserve">17.5753593444824</t>
@@ -4460,16 +4460,16 @@
     <t xml:space="preserve">17.7536468505859</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9319324493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9882316589355</t>
+    <t xml:space="preserve">17.9319343566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9882335662842</t>
   </si>
   <si>
     <t xml:space="preserve">18.3354263305664</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5137100219727</t>
+    <t xml:space="preserve">18.5137119293213</t>
   </si>
   <si>
     <t xml:space="preserve">18.7858333587646</t>
@@ -4478,7 +4478,7 @@
     <t xml:space="preserve">18.5230960845947</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7482986450195</t>
+    <t xml:space="preserve">18.7483005523682</t>
   </si>
   <si>
     <t xml:space="preserve">18.4855613708496</t>
@@ -4493,7 +4493,7 @@
     <t xml:space="preserve">18.4386425018311</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0056915283203</t>
+    <t xml:space="preserve">20.0056934356689</t>
   </si>
   <si>
     <t xml:space="preserve">20.1558284759521</t>
@@ -4502,10 +4502,10 @@
     <t xml:space="preserve">20.3435001373291</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7804889678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8555583953857</t>
+    <t xml:space="preserve">19.7804870605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8555564880371</t>
   </si>
   <si>
     <t xml:space="preserve">19.874324798584</t>
@@ -4526,16 +4526,16 @@
     <t xml:space="preserve">19.4989833831787</t>
   </si>
   <si>
-    <t xml:space="preserve">20.362268447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.793909072876</t>
+    <t xml:space="preserve">20.3622665405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7939109802246</t>
   </si>
   <si>
     <t xml:space="preserve">21.6759643554688</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8260974884033</t>
+    <t xml:space="preserve">21.826099395752</t>
   </si>
   <si>
     <t xml:space="preserve">22.0325355529785</t>
@@ -4550,7 +4550,7 @@
     <t xml:space="preserve">21.8073310852051</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1826725006104</t>
+    <t xml:space="preserve">22.1826705932617</t>
   </si>
   <si>
     <t xml:space="preserve">22.2389755249023</t>
@@ -4559,16 +4559,16 @@
     <t xml:space="preserve">22.2952766418457</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4829444885254</t>
+    <t xml:space="preserve">22.482946395874</t>
   </si>
   <si>
     <t xml:space="preserve">21.9574661254883</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8448657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.76979637146</t>
+    <t xml:space="preserve">21.8448677062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7697982788086</t>
   </si>
   <si>
     <t xml:space="preserve">21.7134971618652</t>
@@ -4583,19 +4583,19 @@
     <t xml:space="preserve">22.670618057251</t>
   </si>
   <si>
-    <t xml:space="preserve">22.970890045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9145889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1585597991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2711620330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1397914886475</t>
+    <t xml:space="preserve">22.9708881378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.914587020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.158561706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2711639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1397933959961</t>
   </si>
   <si>
     <t xml:space="preserve">21.4882926940918</t>
@@ -4622,7 +4622,7 @@
     <t xml:space="preserve">20.8877468109131</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6813087463379</t>
+    <t xml:space="preserve">20.6813106536865</t>
   </si>
   <si>
     <t xml:space="preserve">20.1182975769043</t>
@@ -4637,16 +4637,16 @@
     <t xml:space="preserve">19.2174758911133</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3488464355469</t>
+    <t xml:space="preserve">19.3488483428955</t>
   </si>
   <si>
     <t xml:space="preserve">19.7992553710938</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7054214477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0807609558105</t>
+    <t xml:space="preserve">19.7054195404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0807628631592</t>
   </si>
   <si>
     <t xml:space="preserve">19.742956161499</t>
@@ -4664,7 +4664,7 @@
     <t xml:space="preserve">19.3300800323486</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9359722137451</t>
+    <t xml:space="preserve">18.9359703063965</t>
   </si>
   <si>
     <t xml:space="preserve">18.9172039031982</t>
@@ -4679,19 +4679,19 @@
     <t xml:space="preserve">19.1236419677734</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9922714233398</t>
+    <t xml:space="preserve">18.9922695159912</t>
   </si>
   <si>
     <t xml:space="preserve">19.9118595123291</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4051456451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8180236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9681587219238</t>
+    <t xml:space="preserve">19.4051475524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.818021774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9681606292725</t>
   </si>
   <si>
     <t xml:space="preserve">20.606237411499</t>
@@ -4703,19 +4703,19 @@
     <t xml:space="preserve">24.7162265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5848579406738</t>
+    <t xml:space="preserve">24.5848598480225</t>
   </si>
   <si>
     <t xml:space="preserve">24.6974601745605</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5044422149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9226627349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8475952148438</t>
+    <t xml:space="preserve">25.5044441223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.922664642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8475971221924</t>
   </si>
   <si>
     <t xml:space="preserve">25.4293766021729</t>
@@ -4727,13 +4727,13 @@
     <t xml:space="preserve">25.710880279541</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2363586425781</t>
+    <t xml:space="preserve">26.2363605499268</t>
   </si>
   <si>
     <t xml:space="preserve">25.8422527313232</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9360866546631</t>
+    <t xml:space="preserve">25.9360847473145</t>
   </si>
   <si>
     <t xml:space="preserve">25.6170463562012</t>
@@ -4757,7 +4757,7 @@
     <t xml:space="preserve">26.7806053161621</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9119739532471</t>
+    <t xml:space="preserve">26.9119758605957</t>
   </si>
   <si>
     <t xml:space="preserve">27.0058116912842</t>
@@ -4772,10 +4772,10 @@
     <t xml:space="preserve">27.1559467315674</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8932056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6814231872559</t>
+    <t xml:space="preserve">26.8932075500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6814250946045</t>
   </si>
   <si>
     <t xml:space="preserve">27.7189598083496</t>
@@ -4784,7 +4784,7 @@
     <t xml:space="preserve">27.4749851226807</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7377243041992</t>
+    <t xml:space="preserve">27.7377262115479</t>
   </si>
   <si>
     <t xml:space="preserve">28.1693687438965</t>
@@ -4793,10 +4793,10 @@
     <t xml:space="preserve">27.9629287719727</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6573104858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.507173538208</t>
+    <t xml:space="preserve">28.6573123931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5071754455566</t>
   </si>
   <si>
     <t xml:space="preserve">28.6385440826416</t>
@@ -4808,7 +4808,7 @@
     <t xml:space="preserve">27.775260925293</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8878593444824</t>
+    <t xml:space="preserve">27.8878612518311</t>
   </si>
   <si>
     <t xml:space="preserve">28.4321060180664</t>
@@ -4817,16 +4817,16 @@
     <t xml:space="preserve">28.8074474334717</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2766246795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8449821472168</t>
+    <t xml:space="preserve">29.2766265869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8449802398682</t>
   </si>
   <si>
     <t xml:space="preserve">28.7136135101318</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1881370544434</t>
+    <t xml:space="preserve">28.1881351470947</t>
   </si>
   <si>
     <t xml:space="preserve">27.8315601348877</t>
@@ -4844,10 +4844,10 @@
     <t xml:space="preserve">29.1640224456787</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9441623687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2444362640381</t>
+    <t xml:space="preserve">27.944164276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2444343566895</t>
   </si>
   <si>
     <t xml:space="preserve">27.6063556671143</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">27.5500545501709</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1934814453125</t>
+    <t xml:space="preserve">27.1934795379639</t>
   </si>
   <si>
     <t xml:space="preserve">26.7243022918701</t>
@@ -4901,25 +4901,25 @@
     <t xml:space="preserve">28.4884090423584</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2900466918945</t>
+    <t xml:space="preserve">30.2900447845459</t>
   </si>
   <si>
     <t xml:space="preserve">30.5527877807617</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1533336639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4777164459229</t>
+    <t xml:space="preserve">31.1533317565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4777145385742</t>
   </si>
   <si>
     <t xml:space="preserve">30.515251159668</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3838806152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0460739135742</t>
+    <t xml:space="preserve">30.383882522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0460758209229</t>
   </si>
   <si>
     <t xml:space="preserve">30.1211414337158</t>
@@ -4934,7 +4934,7 @@
     <t xml:space="preserve">30.083610534668</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6895008087158</t>
+    <t xml:space="preserve">29.6894989013672</t>
   </si>
   <si>
     <t xml:space="preserve">29.7270336151123</t>
@@ -4949,10 +4949,10 @@
     <t xml:space="preserve">29.9334716796875</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5259399414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3007373809814</t>
+    <t xml:space="preserve">28.5259418487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3007354736328</t>
   </si>
   <si>
     <t xml:space="preserve">28.0942993164062</t>
@@ -4970,7 +4970,7 @@
     <t xml:space="preserve">29.5205955505371</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9763526916504</t>
+    <t xml:space="preserve">28.9763507843018</t>
   </si>
   <si>
     <t xml:space="preserve">29.4830627441406</t>
@@ -4979,7 +4979,7 @@
     <t xml:space="preserve">29.7645683288574</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9575862884521</t>
+    <t xml:space="preserve">28.9575843811035</t>
   </si>
   <si>
     <t xml:space="preserve">29.1452541351318</t>
@@ -4991,7 +4991,7 @@
     <t xml:space="preserve">30.9468936920166</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7779884338379</t>
+    <t xml:space="preserve">30.7779903411865</t>
   </si>
   <si>
     <t xml:space="preserve">31.3973007202148</t>
@@ -5000,13 +5000,13 @@
     <t xml:space="preserve">29.5581321716309</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7029228210449</t>
+    <t xml:space="preserve">30.7029209136963</t>
   </si>
   <si>
     <t xml:space="preserve">30.3463478088379</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4455261230469</t>
+    <t xml:space="preserve">29.4455280303955</t>
   </si>
   <si>
     <t xml:space="preserve">29.2953910827637</t>
@@ -5874,6 +5874,9 @@
   </si>
   <si>
     <t xml:space="preserve">31.6200008392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7600002288818</t>
   </si>
 </sst>
 </file>
@@ -18034,7 +18037,7 @@
         <v>26.8899993896484</v>
       </c>
       <c r="G455" t="s">
-        <v>378</v>
+        <v>271</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -18060,7 +18063,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G456" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -18086,7 +18089,7 @@
         <v>27.5900001525879</v>
       </c>
       <c r="G457" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -18112,7 +18115,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G458" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -18138,7 +18141,7 @@
         <v>27.6700000762939</v>
       </c>
       <c r="G459" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -18164,7 +18167,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G460" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -18190,7 +18193,7 @@
         <v>28.2800006866455</v>
       </c>
       <c r="G461" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -18242,7 +18245,7 @@
         <v>27.5300006866455</v>
       </c>
       <c r="G463" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -18268,7 +18271,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G464" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -18294,7 +18297,7 @@
         <v>27.6200008392334</v>
       </c>
       <c r="G465" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -18320,7 +18323,7 @@
         <v>27.5300006866455</v>
       </c>
       <c r="G466" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -18372,7 +18375,7 @@
         <v>28.3799991607666</v>
       </c>
       <c r="G468" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -18398,7 +18401,7 @@
         <v>28.3700008392334</v>
       </c>
       <c r="G469" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -18424,7 +18427,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G470" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -18476,7 +18479,7 @@
         <v>28.0900001525879</v>
       </c>
       <c r="G472" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -18502,7 +18505,7 @@
         <v>27.9300003051758</v>
       </c>
       <c r="G473" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -18528,7 +18531,7 @@
         <v>28.0599994659424</v>
       </c>
       <c r="G474" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -18554,7 +18557,7 @@
         <v>27.6100006103516</v>
       </c>
       <c r="G475" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -18580,7 +18583,7 @@
         <v>27.2099990844727</v>
       </c>
       <c r="G476" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -18606,7 +18609,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G477" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -18632,7 +18635,7 @@
         <v>27.7299995422363</v>
       </c>
       <c r="G478" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -18658,7 +18661,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G479" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -18684,7 +18687,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G480" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -18710,7 +18713,7 @@
         <v>24</v>
       </c>
       <c r="G481" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -18736,7 +18739,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G482" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -18762,7 +18765,7 @@
         <v>24.75</v>
       </c>
       <c r="G483" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -18788,7 +18791,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G484" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -18814,7 +18817,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G485" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -18840,7 +18843,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G486" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -18866,7 +18869,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G487" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -18892,7 +18895,7 @@
         <v>24.2099990844727</v>
       </c>
       <c r="G488" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -18918,7 +18921,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G489" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -18944,7 +18947,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G490" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -18970,7 +18973,7 @@
         <v>24.5200004577637</v>
       </c>
       <c r="G491" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -18996,7 +18999,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G492" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -19022,7 +19025,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G493" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -19048,7 +19051,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G494" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -19074,7 +19077,7 @@
         <v>24.5</v>
       </c>
       <c r="G495" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -19100,7 +19103,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G496" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -19126,7 +19129,7 @@
         <v>25.2099990844727</v>
       </c>
       <c r="G497" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -19152,7 +19155,7 @@
         <v>25.4300003051758</v>
       </c>
       <c r="G498" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -19178,7 +19181,7 @@
         <v>25.5200004577637</v>
       </c>
       <c r="G499" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -19204,7 +19207,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G500" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -19230,7 +19233,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G501" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -19256,7 +19259,7 @@
         <v>25</v>
       </c>
       <c r="G502" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -19282,7 +19285,7 @@
         <v>24.8299999237061</v>
       </c>
       <c r="G503" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -19308,7 +19311,7 @@
         <v>26.0900001525879</v>
       </c>
       <c r="G504" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -19334,7 +19337,7 @@
         <v>26.2900009155273</v>
       </c>
       <c r="G505" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -19360,7 +19363,7 @@
         <v>25.9400005340576</v>
       </c>
       <c r="G506" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -19386,7 +19389,7 @@
         <v>25.4200000762939</v>
       </c>
       <c r="G507" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -19412,7 +19415,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G508" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -19464,7 +19467,7 @@
         <v>25.4699993133545</v>
       </c>
       <c r="G510" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -19490,7 +19493,7 @@
         <v>25.2299995422363</v>
       </c>
       <c r="G511" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -19516,7 +19519,7 @@
         <v>25.5</v>
       </c>
       <c r="G512" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -19542,7 +19545,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G513" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -19594,7 +19597,7 @@
         <v>26.6800003051758</v>
       </c>
       <c r="G515" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -19620,7 +19623,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G516" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -19646,7 +19649,7 @@
         <v>26.9799995422363</v>
       </c>
       <c r="G517" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -19672,7 +19675,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G518" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -19698,7 +19701,7 @@
         <v>26.5200004577637</v>
       </c>
       <c r="G519" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -19724,7 +19727,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G520" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -19750,7 +19753,7 @@
         <v>26.7199993133545</v>
       </c>
       <c r="G521" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -19776,7 +19779,7 @@
         <v>26.6800003051758</v>
       </c>
       <c r="G522" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -19828,7 +19831,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G524" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -19854,7 +19857,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G525" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -19880,7 +19883,7 @@
         <v>26.2800006866455</v>
       </c>
       <c r="G526" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -19932,7 +19935,7 @@
         <v>27.0400009155273</v>
       </c>
       <c r="G528" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -19958,7 +19961,7 @@
         <v>26.7199993133545</v>
       </c>
       <c r="G529" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -19984,7 +19987,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G530" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -20010,7 +20013,7 @@
         <v>27.1399993896484</v>
       </c>
       <c r="G531" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -20036,7 +20039,7 @@
         <v>26.6599998474121</v>
       </c>
       <c r="G532" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -20062,7 +20065,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G533" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -20114,7 +20117,7 @@
         <v>26.7199993133545</v>
       </c>
       <c r="G535" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -20140,7 +20143,7 @@
         <v>26.4799995422363</v>
       </c>
       <c r="G536" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -20192,7 +20195,7 @@
         <v>25.5</v>
       </c>
       <c r="G538" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -20218,7 +20221,7 @@
         <v>24.3400001525879</v>
       </c>
       <c r="G539" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -20244,7 +20247,7 @@
         <v>24.0799999237061</v>
       </c>
       <c r="G540" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -20270,7 +20273,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G541" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -20296,7 +20299,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G542" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -20322,7 +20325,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G543" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -20348,7 +20351,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G544" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -20374,7 +20377,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G545" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -20400,7 +20403,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G546" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -20426,7 +20429,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G547" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -20452,7 +20455,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G548" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -20478,7 +20481,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G549" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -20504,7 +20507,7 @@
         <v>24.2800006866455</v>
       </c>
       <c r="G550" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -20530,7 +20533,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G551" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -20556,7 +20559,7 @@
         <v>23.4599990844727</v>
       </c>
       <c r="G552" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -20582,7 +20585,7 @@
         <v>23.1800003051758</v>
       </c>
       <c r="G553" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -20608,7 +20611,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G554" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -20634,7 +20637,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G555" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -20660,7 +20663,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G556" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -20686,7 +20689,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G557" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -20712,7 +20715,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G558" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -20738,7 +20741,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G559" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -20790,7 +20793,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G561" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -20842,7 +20845,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G563" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -20868,7 +20871,7 @@
         <v>25.1599998474121</v>
       </c>
       <c r="G564" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -20894,7 +20897,7 @@
         <v>24.6399993896484</v>
       </c>
       <c r="G565" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -20920,7 +20923,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G566" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -20946,7 +20949,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G567" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -20972,7 +20975,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G568" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -20998,7 +21001,7 @@
         <v>24.2199993133545</v>
       </c>
       <c r="G569" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -21024,7 +21027,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G570" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -21050,7 +21053,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G571" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -21076,7 +21079,7 @@
         <v>24.3400001525879</v>
       </c>
       <c r="G572" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -21102,7 +21105,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G573" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -21128,7 +21131,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G574" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -21154,7 +21157,7 @@
         <v>24.5</v>
       </c>
       <c r="G575" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -21180,7 +21183,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G576" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -21206,7 +21209,7 @@
         <v>24.8199996948242</v>
       </c>
       <c r="G577" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -21232,7 +21235,7 @@
         <v>24.5200004577637</v>
       </c>
       <c r="G578" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -21258,7 +21261,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G579" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -21284,7 +21287,7 @@
         <v>24</v>
       </c>
       <c r="G580" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -21310,7 +21313,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G581" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -21336,7 +21339,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G582" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -21362,7 +21365,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G583" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -21388,7 +21391,7 @@
         <v>23.4799995422363</v>
       </c>
       <c r="G584" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -21414,7 +21417,7 @@
         <v>23.7800006866455</v>
       </c>
       <c r="G585" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -21440,7 +21443,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G586" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -21466,7 +21469,7 @@
         <v>25.5599994659424</v>
       </c>
       <c r="G587" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -21492,7 +21495,7 @@
         <v>25.1200008392334</v>
       </c>
       <c r="G588" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -21518,7 +21521,7 @@
         <v>25</v>
       </c>
       <c r="G589" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -21544,7 +21547,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G590" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -21570,7 +21573,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G591" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -21596,7 +21599,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G592" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -21622,7 +21625,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G593" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -21648,7 +21651,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G594" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -21674,7 +21677,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G595" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -21700,7 +21703,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G596" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -21726,7 +21729,7 @@
         <v>25</v>
       </c>
       <c r="G597" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -21752,7 +21755,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G598" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -21778,7 +21781,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G599" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -21804,7 +21807,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G600" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -21830,7 +21833,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G601" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -21856,7 +21859,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G602" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -21882,7 +21885,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G603" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -21908,7 +21911,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G604" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -21934,7 +21937,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G605" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -21960,7 +21963,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G606" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -21986,7 +21989,7 @@
         <v>24.5</v>
       </c>
       <c r="G607" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -22012,7 +22015,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G608" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -22038,7 +22041,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G609" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -22064,7 +22067,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G610" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -22090,7 +22093,7 @@
         <v>24.0799999237061</v>
       </c>
       <c r="G611" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -22116,7 +22119,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G612" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -22142,7 +22145,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G613" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -22168,7 +22171,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G614" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -22194,7 +22197,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G615" t="s">
-        <v>481</v>
+        <v>503</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -22246,7 +22249,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G617" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -22350,7 +22353,7 @@
         <v>25</v>
       </c>
       <c r="G621" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -22376,7 +22379,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G622" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -22428,7 +22431,7 @@
         <v>25</v>
       </c>
       <c r="G624" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -22636,7 +22639,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G632" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -22662,7 +22665,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G633" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -22818,7 +22821,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G639" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -22896,7 +22899,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G642" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -23026,7 +23029,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G647" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -23052,7 +23055,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G648" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -23078,7 +23081,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G649" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -23156,7 +23159,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G652" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -24846,7 +24849,7 @@
         <v>25</v>
       </c>
       <c r="G717" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -26224,7 +26227,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G770" t="s">
-        <v>481</v>
+        <v>503</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -26302,7 +26305,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G773" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -26380,7 +26383,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G776" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -26458,7 +26461,7 @@
         <v>24.0799999237061</v>
       </c>
       <c r="G779" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -27212,7 +27215,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G808" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -27524,7 +27527,7 @@
         <v>24.0799999237061</v>
       </c>
       <c r="G820" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -27654,7 +27657,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G825" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -27914,7 +27917,7 @@
         <v>25</v>
       </c>
       <c r="G835" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -27940,7 +27943,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G836" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -27992,7 +27995,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G838" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -71264,7 +71267,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6909722222</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>105181</v>
@@ -71285,6 +71288,32 @@
         <v>1951</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6909953704</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>144050</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>31.2000007629395</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>30.7199993133545</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>31.2000007629395</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>30.7600002288818</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>1954</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DLG.MI.xlsx
+++ b/data/DLG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1955" uniqueCount="1955">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="1956">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7391452789307</t>
+    <t xml:space="preserve">20.7391471862793</t>
   </si>
   <si>
     <t xml:space="preserve">DLG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5564231872559</t>
+    <t xml:space="preserve">20.5564212799072</t>
   </si>
   <si>
     <t xml:space="preserve">20.6553974151611</t>
@@ -53,37 +53,37 @@
     <t xml:space="preserve">20.1757469177246</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9777946472168</t>
+    <t xml:space="preserve">19.9777965545654</t>
   </si>
   <si>
     <t xml:space="preserve">19.7722320556641</t>
   </si>
   <si>
-    <t xml:space="preserve">19.490535736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8864326477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5160064697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6328411102295</t>
+    <t xml:space="preserve">19.4905338287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8864345550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5160083770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6328430175781</t>
   </si>
   <si>
     <t xml:space="preserve">17.4348907470703</t>
   </si>
   <si>
-    <t xml:space="preserve">17.526252746582</t>
+    <t xml:space="preserve">17.5262508392334</t>
   </si>
   <si>
     <t xml:space="preserve">17.0542163848877</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8943309783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0135192871094</t>
+    <t xml:space="preserve">16.8943347930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0135135650635</t>
   </si>
   <si>
     <t xml:space="preserve">16.6354732513428</t>
@@ -92,67 +92,67 @@
     <t xml:space="preserve">16.4451351165771</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7116107940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8029670715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6735382080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1329860687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9654836654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6533346176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9909610748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7777805328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3335676193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4123363494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7397165298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4553842544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2574310302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.409704208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7523097991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3868579864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9121932983398</t>
+    <t xml:space="preserve">16.7116088867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8029689788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6735401153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1329822540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9654846191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6533336639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9909601211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7777843475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3335666656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4123373031616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7397155761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4553804397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2574319839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4097013473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.75230884552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3868618011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9121913909912</t>
   </si>
   <si>
     <t xml:space="preserve">15.9578723907471</t>
   </si>
   <si>
-    <t xml:space="preserve">15.584813117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1253681182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1938934326172</t>
+    <t xml:space="preserve">15.5848112106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1253719329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1938915252686</t>
   </si>
   <si>
     <t xml:space="preserve">16.5593395233154</t>
@@ -161,145 +161,145 @@
     <t xml:space="preserve">16.7496757507324</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8817367553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.219367980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3792495727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0872993469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7142448425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2878866195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8969659805298</t>
+    <t xml:space="preserve">15.8817405700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2193660736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.379246711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0873031616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.714241027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2878856658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8969650268555</t>
   </si>
   <si>
     <t xml:space="preserve">15.3183393478394</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6076517105103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9274225234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9883289337158</t>
+    <t xml:space="preserve">15.6076507568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9274196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9883260726929</t>
   </si>
   <si>
     <t xml:space="preserve">15.8893537521362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6152648925781</t>
+    <t xml:space="preserve">15.6152658462524</t>
   </si>
   <si>
     <t xml:space="preserve">15.3564071655273</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1356191635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2269773483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3487949371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0442562103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2345943450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0594797134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1432285308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5493783950806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7853965759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.82346534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.783164024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9779872894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1572284698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1494331359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9624061584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9857816696167</t>
+    <t xml:space="preserve">15.1356172561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2269792556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3487939834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0442523956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2345895767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0594816207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1432323455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5493793487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7853956222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8234624862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7831659317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.977988243103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1572256088257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1494340896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.96240234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9857797622681</t>
   </si>
   <si>
     <t xml:space="preserve">14.9546098709106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8533010482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4689407348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.671558380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2170600891113</t>
+    <t xml:space="preserve">14.8533020019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4689445495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6715593338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2170639038086</t>
   </si>
   <si>
     <t xml:space="preserve">15.7572813034058</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0300331115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.240442276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1469230651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3495445251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5054016113281</t>
+    <t xml:space="preserve">16.0300312042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2404441833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1469268798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3495426177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5054035186768</t>
   </si>
   <si>
     <t xml:space="preserve">16.3105792999268</t>
   </si>
   <si>
-    <t xml:space="preserve">17.728889465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7937355041504</t>
+    <t xml:space="preserve">17.7288875579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7937412261963</t>
   </si>
   <si>
     <t xml:space="preserve">17.0742855072021</t>
   </si>
   <si>
-    <t xml:space="preserve">16.762565612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7547760009766</t>
+    <t xml:space="preserve">16.7625675201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7547740936279</t>
   </si>
   <si>
     <t xml:space="preserve">16.8482913970947</t>
@@ -308,46 +308,46 @@
     <t xml:space="preserve">17.1132469177246</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3002815246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7678508758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9081230163574</t>
+    <t xml:space="preserve">17.3002834320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7678527832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9081249237061</t>
   </si>
   <si>
     <t xml:space="preserve">17.9470920562744</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0639839172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4848022460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7887287139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4614219665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3367385864258</t>
+    <t xml:space="preserve">18.0639820098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4848003387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.788724899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4614238739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3367366790771</t>
   </si>
   <si>
     <t xml:space="preserve">18.2743949890137</t>
   </si>
   <si>
-    <t xml:space="preserve">18.079568862915</t>
+    <t xml:space="preserve">18.0795726776123</t>
   </si>
   <si>
     <t xml:space="preserve">18.6484546661377</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8276920318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4536323547363</t>
+    <t xml:space="preserve">18.8276901245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.453634262085</t>
   </si>
   <si>
     <t xml:space="preserve">17.8379878997803</t>
@@ -356,49 +356,49 @@
     <t xml:space="preserve">17.3937931060791</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2535190582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0820732116699</t>
+    <t xml:space="preserve">17.2535209655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0820789337158</t>
   </si>
   <si>
     <t xml:space="preserve">17.4951019287109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9237117767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8224067687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7834377288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9315032958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6768455505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5234937667847</t>
+    <t xml:space="preserve">17.9237098693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8224048614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7834358215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9315052032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6768474578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5234928131104</t>
   </si>
   <si>
     <t xml:space="preserve">16.1157531738281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3651294708252</t>
+    <t xml:space="preserve">16.3651275634766</t>
   </si>
   <si>
     <t xml:space="preserve">16.6612586975098</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6300888061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8975505828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7806615829468</t>
+    <t xml:space="preserve">16.6300868988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8975534439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7806606292725</t>
   </si>
   <si>
     <t xml:space="preserve">15.5468711853027</t>
@@ -407,49 +407,49 @@
     <t xml:space="preserve">15.7884521484375</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3729228973389</t>
+    <t xml:space="preserve">16.3729209899902</t>
   </si>
   <si>
     <t xml:space="preserve">16.1858921051025</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1625099182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4196796417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5209884643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5287799835205</t>
+    <t xml:space="preserve">16.1625118255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.419677734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5209865570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5287818908691</t>
   </si>
   <si>
     <t xml:space="preserve">16.8404979705811</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9184226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8716697692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8015289306641</t>
+    <t xml:space="preserve">16.9184246063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8716659545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8015308380127</t>
   </si>
   <si>
     <t xml:space="preserve">17.6119937896729</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2223510742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5964088439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4171695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6587505340576</t>
+    <t xml:space="preserve">17.2223491668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5964107513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4171733856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6587524414062</t>
   </si>
   <si>
     <t xml:space="preserve">17.3158626556396</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">18.0561904907227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5393524169922</t>
+    <t xml:space="preserve">18.5393543243408</t>
   </si>
   <si>
     <t xml:space="preserve">18.7030010223389</t>
@@ -473,13 +473,13 @@
     <t xml:space="preserve">18.664041519165</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8121032714844</t>
+    <t xml:space="preserve">18.8121013641357</t>
   </si>
   <si>
     <t xml:space="preserve">18.0951557159424</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1497077941895</t>
+    <t xml:space="preserve">18.1497039794922</t>
   </si>
   <si>
     <t xml:space="preserve">17.9003314971924</t>
@@ -488,16 +488,16 @@
     <t xml:space="preserve">18.1574993133545</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8769550323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6665439605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9704723358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0328121185303</t>
+    <t xml:space="preserve">17.8769569396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6665458679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9704685211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0328159332275</t>
   </si>
   <si>
     <t xml:space="preserve">17.5106868743896</t>
@@ -506,28 +506,28 @@
     <t xml:space="preserve">17.5730285644531</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3626194000244</t>
+    <t xml:space="preserve">17.3626232147217</t>
   </si>
   <si>
     <t xml:space="preserve">17.4015865325928</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2379341125488</t>
+    <t xml:space="preserve">17.2379360198975</t>
   </si>
   <si>
     <t xml:space="preserve">17.4093799591064</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1444206237793</t>
+    <t xml:space="preserve">17.1444225311279</t>
   </si>
   <si>
     <t xml:space="preserve">16.81711769104</t>
   </si>
   <si>
-    <t xml:space="preserve">16.614501953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6846389770508</t>
+    <t xml:space="preserve">16.6145000457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6846370697021</t>
   </si>
   <si>
     <t xml:space="preserve">17.0197353363037</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">17.2691059112549</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9963531494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4405498504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4639301300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8327045440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8249130249023</t>
+    <t xml:space="preserve">16.9963569641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4405517578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4639263153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8327026367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8249092102051</t>
   </si>
   <si>
     <t xml:space="preserve">16.9028415679932</t>
@@ -563,61 +563,61 @@
     <t xml:space="preserve">16.7469806671143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2768974304199</t>
+    <t xml:space="preserve">17.2768993377686</t>
   </si>
   <si>
     <t xml:space="preserve">17.2457275390625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0509033203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0976638793945</t>
+    <t xml:space="preserve">17.0509014129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0976600646973</t>
   </si>
   <si>
     <t xml:space="preserve">16.9573879241943</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2301425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2067642211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4327564239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2846927642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0664882659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9521026611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9832754135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.256031036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3339557647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9988603591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4066019058228</t>
+    <t xml:space="preserve">17.2301406860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2067623138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4327602386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2846965789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0664901733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9521036148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9832744598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2560272216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3339576721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9988613128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4065990447998</t>
   </si>
   <si>
     <t xml:space="preserve">15.313084602356</t>
   </si>
   <si>
-    <t xml:space="preserve">15.118260383606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5131931304932</t>
+    <t xml:space="preserve">15.1182622909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5131912231445</t>
   </si>
   <si>
     <t xml:space="preserve">16.0923767089844</t>
@@ -626,25 +626,25 @@
     <t xml:space="preserve">15.9131383895874</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1780986785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7158107757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0586986541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4664325714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2248554229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9754829406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7080173492432</t>
+    <t xml:space="preserve">16.1780967712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7158088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0586967468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4664363861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.224853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9754838943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7080192565918</t>
   </si>
   <si>
     <t xml:space="preserve">16.4976081848145</t>
@@ -653,28 +653,28 @@
     <t xml:space="preserve">16.6924285888672</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5599517822266</t>
+    <t xml:space="preserve">16.5599498748779</t>
   </si>
   <si>
     <t xml:space="preserve">16.7703590393066</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8638725280762</t>
+    <t xml:space="preserve">16.8638763427734</t>
   </si>
   <si>
     <t xml:space="preserve">17.0275249481201</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4561367034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4483413696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8847484588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1185340881348</t>
+    <t xml:space="preserve">17.4561386108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4483432769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8847465515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1185359954834</t>
   </si>
   <si>
     <t xml:space="preserve">18.2354278564453</t>
@@ -683,121 +683,121 @@
     <t xml:space="preserve">18.0172290802002</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8457832336426</t>
+    <t xml:space="preserve">17.8457813262939</t>
   </si>
   <si>
     <t xml:space="preserve">17.9626770019531</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8691635131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6353740692139</t>
+    <t xml:space="preserve">17.869161605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6353721618652</t>
   </si>
   <si>
     <t xml:space="preserve">17.7912330627441</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5808219909668</t>
+    <t xml:space="preserve">17.5808258056641</t>
   </si>
   <si>
     <t xml:space="preserve">17.6509590148926</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1107425689697</t>
+    <t xml:space="preserve">18.1107406616211</t>
   </si>
   <si>
     <t xml:space="preserve">17.9782600402832</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3133563995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2042560577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.469217300415</t>
+    <t xml:space="preserve">18.3133583068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2042541503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4692153930664</t>
   </si>
   <si>
     <t xml:space="preserve">19.0848579406738</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3498153686523</t>
+    <t xml:space="preserve">19.349817276001</t>
   </si>
   <si>
     <t xml:space="preserve">19.2952671051025</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4667110443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2485084533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3186454772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0614757537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4199562072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2407150268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0926475524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4511222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8588638305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.640661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9056186676025</t>
+    <t xml:space="preserve">19.4667129516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2485065460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3186435699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0614795684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4199485778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2407131195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0926494598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4511241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8588619232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6406574249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9056205749512</t>
   </si>
   <si>
     <t xml:space="preserve">19.2329235076904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4978809356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1914501190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9888343811035</t>
+    <t xml:space="preserve">19.4978847503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1914482116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9888381958008</t>
   </si>
   <si>
     <t xml:space="preserve">20.1213130950928</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9732494354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9551563262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6278514862061</t>
+    <t xml:space="preserve">19.9732475280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9551582336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6278495788574</t>
   </si>
   <si>
     <t xml:space="preserve">21.2201156616211</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0408763885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.79150390625</t>
+    <t xml:space="preserve">21.0408802032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7915077209473</t>
   </si>
   <si>
     <t xml:space="preserve">20.7447490692139</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8616428375244</t>
+    <t xml:space="preserve">20.8616466522217</t>
   </si>
   <si>
     <t xml:space="preserve">21.2434959411621</t>
@@ -806,40 +806,40 @@
     <t xml:space="preserve">20.9006061553955</t>
   </si>
   <si>
-    <t xml:space="preserve">21.033088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9785327911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6721057891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4149379730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3136329650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1967353820801</t>
+    <t xml:space="preserve">21.0330848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.978536605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6721019744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4149398803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3136310577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1967391967773</t>
   </si>
   <si>
     <t xml:space="preserve">21.4227333068848</t>
   </si>
   <si>
-    <t xml:space="preserve">21.578592300415</t>
+    <t xml:space="preserve">21.5785903930664</t>
   </si>
   <si>
     <t xml:space="preserve">22.1884727478027</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1002006530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9477310180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0279808044434</t>
+    <t xml:space="preserve">22.1002025604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9477291107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0279769897461</t>
   </si>
   <si>
     <t xml:space="preserve">21.9878540039062</t>
@@ -854,19 +854,19 @@
     <t xml:space="preserve">22.4693412780762</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8946533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3199672698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2878704071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8786029815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0310745239258</t>
+    <t xml:space="preserve">22.8946514129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3199634552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2878684997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8786010742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0310726165771</t>
   </si>
   <si>
     <t xml:space="preserve">23.4483604431152</t>
@@ -875,46 +875,46 @@
     <t xml:space="preserve">23.0230484008789</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9026775360107</t>
+    <t xml:space="preserve">22.9026756286621</t>
   </si>
   <si>
     <t xml:space="preserve">22.6218109130859</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5014400482178</t>
+    <t xml:space="preserve">22.5014381408691</t>
   </si>
   <si>
     <t xml:space="preserve">23.255765914917</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8434066772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.060079574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6298332214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7341556549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9267520904541</t>
+    <t xml:space="preserve">21.8434047698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0600776672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6298370361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7341575622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9267501831055</t>
   </si>
   <si>
     <t xml:space="preserve">23.2316932678223</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1434192657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1674957275391</t>
+    <t xml:space="preserve">23.1434211730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1674938201904</t>
   </si>
   <si>
     <t xml:space="preserve">23.6570053100586</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7693538665771</t>
+    <t xml:space="preserve">23.7693557739258</t>
   </si>
   <si>
     <t xml:space="preserve">23.6730556488037</t>
@@ -923,16 +923,16 @@
     <t xml:space="preserve">23.8495998382568</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7613277435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4002132415771</t>
+    <t xml:space="preserve">23.7613258361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4002113342285</t>
   </si>
   <si>
     <t xml:space="preserve">23.2958908081055</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4323139190674</t>
+    <t xml:space="preserve">23.4323120117188</t>
   </si>
   <si>
     <t xml:space="preserve">23.7051525115967</t>
@@ -941,31 +941,31 @@
     <t xml:space="preserve">23.0069999694824</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8304557800293</t>
+    <t xml:space="preserve">22.8304538726807</t>
   </si>
   <si>
     <t xml:space="preserve">22.7903308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0631713867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8255271911621</t>
+    <t xml:space="preserve">23.0631732940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8255252838135</t>
   </si>
   <si>
     <t xml:space="preserve">23.3921871185303</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2637920379639</t>
+    <t xml:space="preserve">23.2637901306152</t>
   </si>
   <si>
     <t xml:space="preserve">23.2718162536621</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1915664672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9989757537842</t>
+    <t xml:space="preserve">23.1915683746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9989719390869</t>
   </si>
   <si>
     <t xml:space="preserve">21.9076061248779</t>
@@ -983,31 +983,31 @@
     <t xml:space="preserve">21.4742698669434</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6267395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7711868286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.739086151123</t>
+    <t xml:space="preserve">21.6267414093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7711849212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7390880584717</t>
   </si>
   <si>
     <t xml:space="preserve">21.8674831390381</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8594570159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5255126953125</t>
+    <t xml:space="preserve">21.8594589233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5255146026611</t>
   </si>
   <si>
     <t xml:space="preserve">22.7421798706055</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3730411529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7181034088135</t>
+    <t xml:space="preserve">22.3730430603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7181072235107</t>
   </si>
   <si>
     <t xml:space="preserve">22.8625526428223</t>
@@ -1019,13 +1019,13 @@
     <t xml:space="preserve">22.5335388183594</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6539096832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2927932739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7551383972168</t>
+    <t xml:space="preserve">22.6539077758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.292797088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7551364898682</t>
   </si>
   <si>
     <t xml:space="preserve">21.241548538208</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">20.9927845001221</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9446353912354</t>
+    <t xml:space="preserve">20.9446334838867</t>
   </si>
   <si>
     <t xml:space="preserve">21.0730323791504</t>
@@ -1046,25 +1046,25 @@
     <t xml:space="preserve">20.6396942138672</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4310493469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4872226715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8804359436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8643894195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7119178771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5754985809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5995693206787</t>
+    <t xml:space="preserve">20.4310455322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4872207641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8804378509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.864387512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7119159698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5754928588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5995674133301</t>
   </si>
   <si>
     <t xml:space="preserve">20.6477184295654</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">20.6156196594238</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5915451049805</t>
+    <t xml:space="preserve">20.5915431976318</t>
   </si>
   <si>
     <t xml:space="preserve">20.3508033752441</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">20.7440166473389</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6717929840088</t>
+    <t xml:space="preserve">20.6717910766602</t>
   </si>
   <si>
     <t xml:space="preserve">20.495246887207</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">21.2174777984619</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0168609619141</t>
+    <t xml:space="preserve">21.0168590545654</t>
   </si>
   <si>
     <t xml:space="preserve">21.3538990020752</t>
@@ -1109,25 +1109,25 @@
     <t xml:space="preserve">21.2335243225098</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9045085906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5594463348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5353717803955</t>
+    <t xml:space="preserve">20.9045104980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5594482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5353736877441</t>
   </si>
   <si>
     <t xml:space="preserve">20.4711742401123</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7520389556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3779697418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0650062561035</t>
+    <t xml:space="preserve">20.7520408630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3779716491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0650043487549</t>
   </si>
   <si>
     <t xml:space="preserve">21.2255039215088</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">21.369945526123</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9156322479248</t>
+    <t xml:space="preserve">21.9156303405762</t>
   </si>
   <si>
     <t xml:space="preserve">21.4582195281982</t>
@@ -1145,52 +1145,52 @@
     <t xml:space="preserve">21.8032855987549</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7952575683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3088397979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1403255462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2285957336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2045211791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1483516693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6940326690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0921783447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1082248687744</t>
+    <t xml:space="preserve">21.795259475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3088455200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.140323638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2285976409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2045230865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1483497619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6940364837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0921764373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1082229614258</t>
   </si>
   <si>
     <t xml:space="preserve">22.164400100708</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7742786407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7662563323975</t>
+    <t xml:space="preserve">22.7742805480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7662582397461</t>
   </si>
   <si>
     <t xml:space="preserve">22.5897102355957</t>
   </si>
   <si>
-    <t xml:space="preserve">22.541561126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4131679534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5174884796143</t>
+    <t xml:space="preserve">22.5415668487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4131660461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5174865722656</t>
   </si>
   <si>
     <t xml:space="preserve">22.1563739776611</t>
@@ -1202,16 +1202,16 @@
     <t xml:space="preserve">22.5495872497559</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2526683807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2125453948975</t>
+    <t xml:space="preserve">22.2526702880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2125492095947</t>
   </si>
   <si>
     <t xml:space="preserve">19.2594337463379</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9335136413574</t>
+    <t xml:space="preserve">19.9335155487061</t>
   </si>
   <si>
     <t xml:space="preserve">19.861291885376</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">19.6205501556396</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5403003692627</t>
+    <t xml:space="preserve">19.5402984619141</t>
   </si>
   <si>
     <t xml:space="preserve">19.4921531677246</t>
@@ -1232,46 +1232,46 @@
     <t xml:space="preserve">19.4279537200928</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7409229278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6767253875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.805118560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4199295043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7569713592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6606731414795</t>
+    <t xml:space="preserve">19.7409191131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6767196655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8051204681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4199333190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7569694519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6606712341309</t>
   </si>
   <si>
     <t xml:space="preserve">20.1421604156494</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2304267883301</t>
+    <t xml:space="preserve">20.230432510376</t>
   </si>
   <si>
     <t xml:space="preserve">20.4069747924805</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4791965484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2545032501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9415378570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0619106292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9254875183105</t>
+    <t xml:space="preserve">20.4792003631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2545070648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9415416717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0619125366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9254894256592</t>
   </si>
   <si>
     <t xml:space="preserve">20.9366111755371</t>
@@ -1283,25 +1283,25 @@
     <t xml:space="preserve">20.8162384033203</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3989505767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6878452301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4390735626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2464790344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4631462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5433979034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4100704193115</t>
+    <t xml:space="preserve">20.3989524841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6878433227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4390716552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2464771270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4631481170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5433959960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4100723266602</t>
   </si>
   <si>
     <t xml:space="preserve">21.0088329315186</t>
@@ -1310,19 +1310,19 @@
     <t xml:space="preserve">21.6508121490479</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1372299194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2816753387451</t>
+    <t xml:space="preserve">21.137228012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2816772460938</t>
   </si>
   <si>
     <t xml:space="preserve">21.506368637085</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4421710968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9606857299805</t>
+    <t xml:space="preserve">21.4421691894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9606876373291</t>
   </si>
   <si>
     <t xml:space="preserve">21.345874786377</t>
@@ -1331,31 +1331,31 @@
     <t xml:space="preserve">21.0890808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6989650726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8113117218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7792091369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3940200805664</t>
+    <t xml:space="preserve">21.6989631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8113079071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7792129516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.394021987915</t>
   </si>
   <si>
     <t xml:space="preserve">21.7471103668213</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2495765686035</t>
+    <t xml:space="preserve">21.2495746612549</t>
   </si>
   <si>
     <t xml:space="preserve">19.5322761535645</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3236312866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5001773834229</t>
+    <t xml:space="preserve">19.3236331939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5001754760742</t>
   </si>
   <si>
     <t xml:space="preserve">19.5162258148193</t>
@@ -1364,7 +1364,7 @@
     <t xml:space="preserve">20.045862197876</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0940113067627</t>
+    <t xml:space="preserve">20.0940132141113</t>
   </si>
   <si>
     <t xml:space="preserve">19.7248706817627</t>
@@ -1373,10 +1373,10 @@
     <t xml:space="preserve">19.7088222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">19.403881072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.484130859375</t>
+    <t xml:space="preserve">19.4038791656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4841270446777</t>
   </si>
   <si>
     <t xml:space="preserve">19.1631355285645</t>
@@ -1385,13 +1385,13 @@
     <t xml:space="preserve">18.8260955810547</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6014003753662</t>
+    <t xml:space="preserve">18.6014022827148</t>
   </si>
   <si>
     <t xml:space="preserve">18.0075721740723</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5853519439697</t>
+    <t xml:space="preserve">18.5853538513184</t>
   </si>
   <si>
     <t xml:space="preserve">18.713752746582</t>
@@ -1403,34 +1403,34 @@
     <t xml:space="preserve">20.1261119842529</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7199401855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1903076171875</t>
+    <t xml:space="preserve">20.7199420928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1903057098389</t>
   </si>
   <si>
     <t xml:space="preserve">19.7730197906494</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8372173309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8211688995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.435977935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1310367584229</t>
+    <t xml:space="preserve">19.8372135162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8211669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4359798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1310386657715</t>
   </si>
   <si>
     <t xml:space="preserve">19.3557319641113</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5483283996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9174613952637</t>
+    <t xml:space="preserve">19.5483264923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9174633026123</t>
   </si>
   <si>
     <t xml:space="preserve">19.5804233551025</t>
@@ -1439,16 +1439,16 @@
     <t xml:space="preserve">19.0186920166016</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0026416778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8421497344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0828876495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8853664398193</t>
+    <t xml:space="preserve">19.0026435852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8421459197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0828895568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.885368347168</t>
   </si>
   <si>
     <t xml:space="preserve">20.5112972259521</t>
@@ -1457,19 +1457,19 @@
     <t xml:space="preserve">20.1582069396973</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8936634063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6596565246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5760841369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6763744354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7265148162842</t>
+    <t xml:space="preserve">20.8936672210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6596527099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5760803222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6763706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7265167236328</t>
   </si>
   <si>
     <t xml:space="preserve">20.8435211181641</t>
@@ -1478,28 +1478,28 @@
     <t xml:space="preserve">20.8268051147461</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4954013824463</t>
+    <t xml:space="preserve">21.4954032897949</t>
   </si>
   <si>
     <t xml:space="preserve">21.1276760101318</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2781085968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1778202056885</t>
+    <t xml:space="preserve">21.2781047821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1778182983398</t>
   </si>
   <si>
     <t xml:space="preserve">21.0942459106445</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9772396087646</t>
+    <t xml:space="preserve">20.9772415161133</t>
   </si>
   <si>
     <t xml:space="preserve">20.7766609191895</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4757919311523</t>
+    <t xml:space="preserve">20.4757900238037</t>
   </si>
   <si>
     <t xml:space="preserve">20.6429405212402</t>
@@ -1508,19 +1508,19 @@
     <t xml:space="preserve">20.5259380340576</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2584953308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1247749328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1916389465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9241981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5063247680664</t>
+    <t xml:space="preserve">20.2584991455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1247787475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1916408538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9242000579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.506326675415</t>
   </si>
   <si>
     <t xml:space="preserve">20.1582088470459</t>
@@ -1529,28 +1529,28 @@
     <t xml:space="preserve">20.2417831420898</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8769493103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7933731079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9939556121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8100891113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.592794418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6930847167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3420734405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4925098419189</t>
+    <t xml:space="preserve">20.8769512176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7933750152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.993953704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8100910186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5927963256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6930866241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3420715332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.492504119873</t>
   </si>
   <si>
     <t xml:space="preserve">20.5593662261963</t>
@@ -1559,43 +1559,43 @@
     <t xml:space="preserve">19.7570495605469</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8740520477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1414928436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2919292449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.024486541748</t>
+    <t xml:space="preserve">19.8740539550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1414947509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2919273376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0244903564453</t>
   </si>
   <si>
     <t xml:space="preserve">19.9409160614014</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1080627441406</t>
+    <t xml:space="preserve">20.1080646514893</t>
   </si>
   <si>
     <t xml:space="preserve">20.2752132415771</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3922176361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0579204559326</t>
+    <t xml:space="preserve">20.3922157287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.057918548584</t>
   </si>
   <si>
     <t xml:space="preserve">20.4256496429443</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0746326446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8239078521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6901874542236</t>
+    <t xml:space="preserve">20.074634552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8239116668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6901893615723</t>
   </si>
   <si>
     <t xml:space="preserve">21.0273838043213</t>
@@ -1616,31 +1616,31 @@
     <t xml:space="preserve">23.2671852111816</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5847682952881</t>
+    <t xml:space="preserve">23.5847663879395</t>
   </si>
   <si>
     <t xml:space="preserve">23.5346240997314</t>
   </si>
   <si>
-    <t xml:space="preserve">23.217041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8660297393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.799165725708</t>
+    <t xml:space="preserve">23.2170429229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8660278320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7991695404053</t>
   </si>
   <si>
     <t xml:space="preserve">22.8325977325439</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5484428405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6153030395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9328899383545</t>
+    <t xml:space="preserve">22.5484409332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6153011322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9328880310059</t>
   </si>
   <si>
     <t xml:space="preserve">23.1167526245117</t>
@@ -1652,16 +1652,16 @@
     <t xml:space="preserve">23.2504692077637</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4009037017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6181983947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5011959075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3841896057129</t>
+    <t xml:space="preserve">23.4009056091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.618200302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5011940002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3841876983643</t>
   </si>
   <si>
     <t xml:space="preserve">23.2839012145996</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">23.0833225250244</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8994579315186</t>
+    <t xml:space="preserve">22.8994560241699</t>
   </si>
   <si>
     <t xml:space="preserve">22.5651588439941</t>
@@ -1679,34 +1679,34 @@
     <t xml:space="preserve">22.5818729400635</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3311500549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8158798217773</t>
+    <t xml:space="preserve">22.331148147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.815881729126</t>
   </si>
   <si>
     <t xml:space="preserve">22.5317287445068</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1334629058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9663143157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.68505859375</t>
+    <t xml:space="preserve">23.1334686279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9663181304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6850566864014</t>
   </si>
   <si>
     <t xml:space="preserve">23.3006153106689</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4343376159668</t>
+    <t xml:space="preserve">23.4343338012695</t>
   </si>
   <si>
     <t xml:space="preserve">22.9997482299805</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8493118286133</t>
+    <t xml:space="preserve">22.8493137359619</t>
   </si>
   <si>
     <t xml:space="preserve">22.9496002197266</t>
@@ -1715,58 +1715,58 @@
     <t xml:space="preserve">21.7628421783447</t>
   </si>
   <si>
-    <t xml:space="preserve">21.461971282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0440998077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7097988128662</t>
+    <t xml:space="preserve">21.4619750976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0441017150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7098026275635</t>
   </si>
   <si>
     <t xml:space="preserve">20.91037940979</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6625537872314</t>
+    <t xml:space="preserve">21.6625556945801</t>
   </si>
   <si>
     <t xml:space="preserve">21.2279644012451</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4285430908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9270973205566</t>
+    <t xml:space="preserve">21.428539276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9270992279053</t>
   </si>
   <si>
     <t xml:space="preserve">21.3616828918457</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5121192932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9605236053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8573379516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5397548675537</t>
+    <t xml:space="preserve">21.5121154785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9605274200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8573398590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5397529602051</t>
   </si>
   <si>
     <t xml:space="preserve">18.9547348022461</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5564727783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0550212860107</t>
+    <t xml:space="preserve">19.556468963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0550231933594</t>
   </si>
   <si>
     <t xml:space="preserve">19.4394645690918</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3893203735352</t>
+    <t xml:space="preserve">19.3893222808838</t>
   </si>
   <si>
     <t xml:space="preserve">19.2556037902832</t>
@@ -1775,58 +1775,58 @@
     <t xml:space="preserve">19.3057479858398</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3726062774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8043003082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6037197113037</t>
+    <t xml:space="preserve">19.3726043701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8042984008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6037178039551</t>
   </si>
   <si>
     <t xml:space="preserve">18.6872959136963</t>
   </si>
   <si>
-    <t xml:space="preserve">18.670581817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7040100097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8878765106201</t>
+    <t xml:space="preserve">18.6705799102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.704008102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8878746032715</t>
   </si>
   <si>
     <t xml:space="preserve">19.2221717834473</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6734733581543</t>
+    <t xml:space="preserve">19.6734752655029</t>
   </si>
   <si>
     <t xml:space="preserve">19.6567611694336</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8907718658447</t>
+    <t xml:space="preserve">19.8907699584961</t>
   </si>
   <si>
     <t xml:space="preserve">20.0913524627686</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8406238555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.589900970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.088451385498</t>
+    <t xml:space="preserve">19.8406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5899028778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0884532928467</t>
   </si>
   <si>
     <t xml:space="preserve">19.7737636566162</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6400489807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.456184387207</t>
+    <t xml:space="preserve">19.6400451660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4561824798584</t>
   </si>
   <si>
     <t xml:space="preserve">18.9213008880615</t>
@@ -1835,34 +1835,34 @@
     <t xml:space="preserve">19.3391761779785</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5201473236084</t>
+    <t xml:space="preserve">18.5201454162598</t>
   </si>
   <si>
     <t xml:space="preserve">17.5506801605225</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0019817352295</t>
+    <t xml:space="preserve">18.0019836425781</t>
   </si>
   <si>
     <t xml:space="preserve">17.9016914367676</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4699993133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2359924316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4365711212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0412044525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3086395263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9910583496094</t>
+    <t xml:space="preserve">18.4700012207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.235990524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4365673065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.041202545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3086414337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.991060256958</t>
   </si>
   <si>
     <t xml:space="preserve">20.3253574371338</t>
@@ -1877,130 +1877,130 @@
     <t xml:space="preserve">18.2192764282227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4198589324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6538639068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2527046203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3529930114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5368576049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7541561126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6371459960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1553134918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4060344696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2723178863525</t>
+    <t xml:space="preserve">18.4198551177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.653865814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.25270652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3529949188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5368595123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7541542053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6371479034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1553153991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4060363769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2723159790039</t>
   </si>
   <si>
     <t xml:space="preserve">18.9714488983154</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3558883666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0215911865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3224639892578</t>
+    <t xml:space="preserve">19.3558902740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0215950012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3224620819092</t>
   </si>
   <si>
     <t xml:space="preserve">19.7403354644775</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1749210357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7875804901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9380168914795</t>
+    <t xml:space="preserve">20.1749229431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7875843048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9380187988281</t>
   </si>
   <si>
     <t xml:space="preserve">20.0077743530273</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2250690460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5789794921875</t>
+    <t xml:space="preserve">20.2250709533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5789775848389</t>
   </si>
   <si>
     <t xml:space="preserve">21.1443881988525</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2054557800293</t>
+    <t xml:space="preserve">19.2054576873779</t>
   </si>
   <si>
     <t xml:space="preserve">18.0354137420654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6509704589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4336738586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5841102600098</t>
+    <t xml:space="preserve">17.6509685516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4336776733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5841121673584</t>
   </si>
   <si>
     <t xml:space="preserve">17.1328067779541</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5477828979492</t>
+    <t xml:space="preserve">16.5477809906006</t>
   </si>
   <si>
     <t xml:space="preserve">16.1716957092285</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9961881637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3221321105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8791875839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7939529418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.768383026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7769031524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3081121444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4018716812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4359645843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5382480621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.163215637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3336839675903</t>
+    <t xml:space="preserve">15.9961910247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3221302032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8791837692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7939500808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7683801651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7769041061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3081140518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4018707275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4359674453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5382461547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1632175445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3336877822876</t>
   </si>
   <si>
     <t xml:space="preserve">15.0524082183838</t>
@@ -2009,49 +2009,49 @@
     <t xml:space="preserve">15.1717395782471</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3507328033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5552930831909</t>
+    <t xml:space="preserve">15.350733757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5552921295166</t>
   </si>
   <si>
     <t xml:space="preserve">15.6405296325684</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6490507125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.632004737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5808658599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4103946685791</t>
+    <t xml:space="preserve">15.6490535736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6320056915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.580864906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4103956222534</t>
   </si>
   <si>
     <t xml:space="preserve">15.0609340667725</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8904647827148</t>
+    <t xml:space="preserve">14.8904619216919</t>
   </si>
   <si>
     <t xml:space="preserve">14.984224319458</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0438871383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3763017654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4274444580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.282543182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0865058898926</t>
+    <t xml:space="preserve">15.0438861846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3763027191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4274435043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2825450897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0865077972412</t>
   </si>
   <si>
     <t xml:space="preserve">15.1120748519897</t>
@@ -2060,82 +2060,82 @@
     <t xml:space="preserve">15.1546926498413</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3251609802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3592538833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9671754837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7455654144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6091909408569</t>
+    <t xml:space="preserve">15.3251619338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3592548370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9671764373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7455635070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6091918945312</t>
   </si>
   <si>
     <t xml:space="preserve">14.6518077850342</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5154342651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7114725112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6347618103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5410051345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3534898757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3449630737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4472465515137</t>
+    <t xml:space="preserve">14.515435218811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7114715576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6347627639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5410013198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3534879684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3449640274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4472455978394</t>
   </si>
   <si>
     <t xml:space="preserve">14.4387216567993</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7540893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4642925262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4813385009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3620100021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2484502792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4956283569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0268392562866</t>
+    <t xml:space="preserve">14.7540884017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4642934799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4813404083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3620128631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2484483718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4956293106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0268402099609</t>
   </si>
   <si>
     <t xml:space="preserve">15.0012712478638</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6859016418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5324802398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9784555435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4046277999878</t>
+    <t xml:space="preserve">14.6859045028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5324811935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9784564971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4046268463135</t>
   </si>
   <si>
     <t xml:space="preserve">15.035364151001</t>
@@ -2144,16 +2144,16 @@
     <t xml:space="preserve">15.1376447677612</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8308029174805</t>
+    <t xml:space="preserve">14.8308010101318</t>
   </si>
   <si>
     <t xml:space="preserve">14.9586524963379</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2399253845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8109970092773</t>
+    <t xml:space="preserve">15.2399244308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8109979629517</t>
   </si>
   <si>
     <t xml:space="preserve">16.4843521118164</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">17.0468978881836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7911930084229</t>
+    <t xml:space="preserve">16.7911949157715</t>
   </si>
   <si>
     <t xml:space="preserve">16.5269660949707</t>
@@ -2171,28 +2171,28 @@
     <t xml:space="preserve">17.0128040313721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5781097412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3138790130615</t>
+    <t xml:space="preserve">16.5781116485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3138809204102</t>
   </si>
   <si>
     <t xml:space="preserve">16.2371692657471</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9303274154663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9218044281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3933477401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9416065216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5239582061768</t>
+    <t xml:space="preserve">15.9303255081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9218015670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3933486938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9416055679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5239591598511</t>
   </si>
   <si>
     <t xml:space="preserve">14.9330835342407</t>
@@ -2204,82 +2204,82 @@
     <t xml:space="preserve">14.2512044906616</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1318778991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6177167892456</t>
+    <t xml:space="preserve">14.1318788528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6177158355713</t>
   </si>
   <si>
     <t xml:space="preserve">14.4557685852051</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5580492019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5750970840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.737042427063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7796602249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8393239974976</t>
+    <t xml:space="preserve">14.5580501556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5750980377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7370452880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7796611785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8393230438232</t>
   </si>
   <si>
     <t xml:space="preserve">14.8478488922119</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6688547134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2341613769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1404037475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0636901855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8222761154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6262378692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0183172225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1291217803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2058324813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5467691421509</t>
+    <t xml:space="preserve">14.6688556671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2341604232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1403999328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0636911392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8222780227661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.626238822937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0183181762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1291227340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2058334350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5467681884766</t>
   </si>
   <si>
     <t xml:space="preserve">15.8195219039917</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0326042175293</t>
+    <t xml:space="preserve">16.0326061248779</t>
   </si>
   <si>
     <t xml:space="preserve">16.4502544403076</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4928722381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0155601501465</t>
+    <t xml:space="preserve">16.4928703308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0155582427979</t>
   </si>
   <si>
     <t xml:space="preserve">16.1519355773926</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2030754089355</t>
+    <t xml:space="preserve">16.2030735015869</t>
   </si>
   <si>
     <t xml:space="preserve">16.041130065918</t>
@@ -2288,13 +2288,13 @@
     <t xml:space="preserve">16.0752239227295</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8962316513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2883110046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2627391815186</t>
+    <t xml:space="preserve">15.8962297439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2883129119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2627410888672</t>
   </si>
   <si>
     <t xml:space="preserve">16.1263656616211</t>
@@ -2303,25 +2303,25 @@
     <t xml:space="preserve">16.1178417205811</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1945533752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2286472320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1689834594727</t>
+    <t xml:space="preserve">16.1945495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.228645324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.168981552124</t>
   </si>
   <si>
     <t xml:space="preserve">16.0666999816895</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2797870635986</t>
+    <t xml:space="preserve">16.2797889709473</t>
   </si>
   <si>
     <t xml:space="preserve">16.109317779541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7087163925171</t>
+    <t xml:space="preserve">15.7087144851685</t>
   </si>
   <si>
     <t xml:space="preserve">15.6746225357056</t>
@@ -2333,64 +2333,64 @@
     <t xml:space="preserve">15.7428102493286</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3422060012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.291069984436</t>
+    <t xml:space="preserve">15.342209815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2910671234131</t>
   </si>
   <si>
     <t xml:space="preserve">15.1035499572754</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5665731430054</t>
+    <t xml:space="preserve">14.566575050354</t>
   </si>
   <si>
     <t xml:space="preserve">14.2853012084961</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2426805496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5949001312256</t>
+    <t xml:space="preserve">14.2426815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5949010848999</t>
   </si>
   <si>
     <t xml:space="preserve">13.7057056427002</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6944274902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5069103240967</t>
+    <t xml:space="preserve">14.6944265365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.506911277771</t>
   </si>
   <si>
     <t xml:space="preserve">15.0694580078125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4615345001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4444913864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4700584411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6149587631226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2740230560303</t>
+    <t xml:space="preserve">15.4615364074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4444894790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4700593948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6149578094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2740211486816</t>
   </si>
   <si>
     <t xml:space="preserve">15.2995910644531</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7142295837402</t>
+    <t xml:space="preserve">13.7142305374146</t>
   </si>
   <si>
     <t xml:space="preserve">13.381814956665</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5522832870483</t>
+    <t xml:space="preserve">13.552282333374</t>
   </si>
   <si>
     <t xml:space="preserve">13.1772518157959</t>
@@ -2405,22 +2405,22 @@
     <t xml:space="preserve">13.0323534011841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596035003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6232280731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.359001159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6600790023804</t>
+    <t xml:space="preserve">12.7596025466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6232299804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3590002059937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6600780487061</t>
   </si>
   <si>
     <t xml:space="preserve">11.1912889480591</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8333044052124</t>
+    <t xml:space="preserve">10.8333034515381</t>
   </si>
   <si>
     <t xml:space="preserve">9.74230194091797</t>
@@ -2432,13 +2432,13 @@
     <t xml:space="preserve">11.6430311203003</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8220243453979</t>
+    <t xml:space="preserve">11.8220233917236</t>
   </si>
   <si>
     <t xml:space="preserve">11.6686010360718</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0351085662842</t>
+    <t xml:space="preserve">12.0351095199585</t>
   </si>
   <si>
     <t xml:space="preserve">13.3306741714478</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">13.7227535247803</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2767782211304</t>
+    <t xml:space="preserve">14.2767772674561</t>
   </si>
   <si>
     <t xml:space="preserve">13.0749702453613</t>
@@ -2456,22 +2456,22 @@
     <t xml:space="preserve">13.5011434555054</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4500017166138</t>
+    <t xml:space="preserve">13.4500007629395</t>
   </si>
   <si>
     <t xml:space="preserve">12.9897356033325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0834941864014</t>
+    <t xml:space="preserve">13.0834951400757</t>
   </si>
   <si>
     <t xml:space="preserve">13.1175880432129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4953765869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.023829460144</t>
+    <t xml:space="preserve">12.4953756332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0238304138184</t>
   </si>
   <si>
     <t xml:space="preserve">13.3562440872192</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">13.6119480133057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8192663192749</t>
+    <t xml:space="preserve">12.8192682266235</t>
   </si>
   <si>
     <t xml:space="preserve">12.6999387741089</t>
@@ -2495,61 +2495,61 @@
     <t xml:space="preserve">13.0664463043213</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2113466262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3988628387451</t>
+    <t xml:space="preserve">13.2113456726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3988618850708</t>
   </si>
   <si>
     <t xml:space="preserve">13.313627243042</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8079881668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8932218551636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9358386993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0551671981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8846979141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4898633956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7029495239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2000675201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4983854293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4131507873535</t>
+    <t xml:space="preserve">13.8079872131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8932199478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9358396530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0551652908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8846998214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4898614883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7029466629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.200065612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.498387336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4131517410278</t>
   </si>
   <si>
     <t xml:space="preserve">15.1205987930298</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7711381912231</t>
+    <t xml:space="preserve">14.7711372375488</t>
   </si>
   <si>
     <t xml:space="preserve">14.856372833252</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4189176559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.938850402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7513332366943</t>
+    <t xml:space="preserve">15.4189195632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9388513565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.75133228302</t>
   </si>
   <si>
     <t xml:space="preserve">16.6207256317139</t>
@@ -2558,13 +2558,13 @@
     <t xml:space="preserve">16.4161624908447</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2456951141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5440158843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7826709747314</t>
+    <t xml:space="preserve">16.2456932067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5440139770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7826728820801</t>
   </si>
   <si>
     <t xml:space="preserve">17.3707885742188</t>
@@ -2573,19 +2573,19 @@
     <t xml:space="preserve">18.427698135376</t>
   </si>
   <si>
-    <t xml:space="preserve">19.262996673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0754795074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6493072509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.90500831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6039333343506</t>
+    <t xml:space="preserve">19.2629928588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0754814147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6493034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9050102233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6039295196533</t>
   </si>
   <si>
     <t xml:space="preserve">19.6380290985107</t>
@@ -2594,16 +2594,16 @@
     <t xml:space="preserve">20.0641994476318</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8766860961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7743988037109</t>
+    <t xml:space="preserve">19.8766822814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7744026184082</t>
   </si>
   <si>
     <t xml:space="preserve">20.1494331359863</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0471534729004</t>
+    <t xml:space="preserve">20.0471515655518</t>
   </si>
   <si>
     <t xml:space="preserve">19.4846038818359</t>
@@ -2612,58 +2612,58 @@
     <t xml:space="preserve">19.8425903320312</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8084964752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7119789123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9506397247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6778869628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8483543395996</t>
+    <t xml:space="preserve">19.8084945678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7119808197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9506359100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6778888702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8483562469482</t>
   </si>
   <si>
     <t xml:space="preserve">20.8824501037598</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0529193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9335918426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0870132446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1551971435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2915744781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2574825286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2233867645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0699653625488</t>
+    <t xml:space="preserve">21.0529174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9335899353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0870113372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.155200958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.291576385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2574806213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2233848571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0699634552002</t>
   </si>
   <si>
     <t xml:space="preserve">21.3086223602295</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8994979858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9676818847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7631206512451</t>
+    <t xml:space="preserve">20.8994960784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9676837921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7631225585938</t>
   </si>
   <si>
     <t xml:space="preserve">20.9165420532227</t>
@@ -2675,34 +2675,34 @@
     <t xml:space="preserve">22.6382789611816</t>
   </si>
   <si>
-    <t xml:space="preserve">23.013313293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9167957305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8145198822021</t>
+    <t xml:space="preserve">23.0133113861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9167976379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8145141601562</t>
   </si>
   <si>
     <t xml:space="preserve">23.9679393768311</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0020332336426</t>
+    <t xml:space="preserve">24.0020294189453</t>
   </si>
   <si>
     <t xml:space="preserve">23.5758609771729</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8656558990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7974720001221</t>
+    <t xml:space="preserve">23.8656578063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7974700927734</t>
   </si>
   <si>
     <t xml:space="preserve">23.5247192382812</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5929050445557</t>
+    <t xml:space="preserve">23.5929069519043</t>
   </si>
   <si>
     <t xml:space="preserve">23.6610946655273</t>
@@ -2714,16 +2714,16 @@
     <t xml:space="preserve">23.6781406402588</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4394836425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7292804718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7463283538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6951885223389</t>
+    <t xml:space="preserve">23.4394874572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.729284286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7463321685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6951866149902</t>
   </si>
   <si>
     <t xml:space="preserve">23.4906253814697</t>
@@ -2735,31 +2735,31 @@
     <t xml:space="preserve">23.1496868133545</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9849853515625</t>
+    <t xml:space="preserve">23.9849834442139</t>
   </si>
   <si>
     <t xml:space="preserve">23.899751663208</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4963912963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2123641967773</t>
+    <t xml:space="preserve">24.4963932037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2123603820801</t>
   </si>
   <si>
     <t xml:space="preserve">24.5304870605469</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1100807189941</t>
+    <t xml:space="preserve">25.1100788116455</t>
   </si>
   <si>
     <t xml:space="preserve">26.0647068023682</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4680633544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5532989501953</t>
+    <t xml:space="preserve">25.4680652618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5533008575439</t>
   </si>
   <si>
     <t xml:space="preserve">25.4851112365723</t>
@@ -2768,37 +2768,37 @@
     <t xml:space="preserve">25.1271266937256</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0589408874512</t>
+    <t xml:space="preserve">25.0589389801025</t>
   </si>
   <si>
     <t xml:space="preserve">25.0759868621826</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8202838897705</t>
+    <t xml:space="preserve">24.8202819824219</t>
   </si>
   <si>
     <t xml:space="preserve">24.8884716033936</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1953163146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7180023193359</t>
+    <t xml:space="preserve">25.1953144073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7180004119873</t>
   </si>
   <si>
     <t xml:space="preserve">25.3487358093262</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2294082641602</t>
+    <t xml:space="preserve">25.2294101715088</t>
   </si>
   <si>
     <t xml:space="preserve">25.4339714050293</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3657855987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9453811645508</t>
+    <t xml:space="preserve">25.3657836914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9453792572021</t>
   </si>
   <si>
     <t xml:space="preserve">26.8829574584961</t>
@@ -2807,43 +2807,43 @@
     <t xml:space="preserve">26.7636299133301</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0306129455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9283294677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0135669708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.144172668457</t>
+    <t xml:space="preserve">26.0306148529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9283313751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0135650634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1441764831543</t>
   </si>
   <si>
     <t xml:space="preserve">24.956657409668</t>
   </si>
   <si>
-    <t xml:space="preserve">23.422435760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2690143585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4053916931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4565334320068</t>
+    <t xml:space="preserve">23.4224376678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2690162658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4053897857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4565315246582</t>
   </si>
   <si>
     <t xml:space="preserve">24.837329864502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0930328369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5703468322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6385326385498</t>
+    <t xml:space="preserve">25.0930366516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.570348739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6385364532471</t>
   </si>
   <si>
     <t xml:space="preserve">24.3600158691406</t>
@@ -2852,22 +2852,22 @@
     <t xml:space="preserve">24.1384086608887</t>
   </si>
   <si>
-    <t xml:space="preserve">25.911283493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5475311279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8315601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5588111877441</t>
+    <t xml:space="preserve">25.9112815856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5475330352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8315620422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5588130950928</t>
   </si>
   <si>
     <t xml:space="preserve">24.1213607788086</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5417652130127</t>
+    <t xml:space="preserve">23.54176902771</t>
   </si>
   <si>
     <t xml:space="preserve">23.0985450744629</t>
@@ -2876,40 +2876,40 @@
     <t xml:space="preserve">24.2747821807861</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9396114349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2918319702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0702171325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5076732635498</t>
+    <t xml:space="preserve">24.9396133422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2918262481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.070219039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5076694488525</t>
   </si>
   <si>
     <t xml:space="preserve">23.3372020721436</t>
   </si>
   <si>
-    <t xml:space="preserve">23.183780670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6894226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1667346954346</t>
+    <t xml:space="preserve">23.1837825775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6894207000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1667327880859</t>
   </si>
   <si>
     <t xml:space="preserve">23.2860622406006</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2029094696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3768424987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6984977722168</t>
+    <t xml:space="preserve">23.2029075622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3768405914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6984958648682</t>
   </si>
   <si>
     <t xml:space="preserve">22.5941371917725</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">22.7854652404785</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2898769378662</t>
+    <t xml:space="preserve">23.2898750305176</t>
   </si>
   <si>
     <t xml:space="preserve">22.8028564453125</t>
@@ -2933,22 +2933,22 @@
     <t xml:space="preserve">22.8724308013916</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7506771087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7158889770508</t>
+    <t xml:space="preserve">22.750675201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7158908843994</t>
   </si>
   <si>
     <t xml:space="preserve">22.246265411377</t>
   </si>
   <si>
-    <t xml:space="preserve">22.33323097229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4723777770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2550849914551</t>
+    <t xml:space="preserve">22.3332366943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4723796844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2550888061523</t>
   </si>
   <si>
     <t xml:space="preserve">24.5769939422607</t>
@@ -2960,13 +2960,13 @@
     <t xml:space="preserve">25.5510272979736</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1945877075195</t>
+    <t xml:space="preserve">26.1945858001709</t>
   </si>
   <si>
     <t xml:space="preserve">26.4207000732422</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7597484588623</t>
+    <t xml:space="preserve">25.7597522735596</t>
   </si>
   <si>
     <t xml:space="preserve">26.4033069610596</t>
@@ -2975,34 +2975,34 @@
     <t xml:space="preserve">27.0294723510742</t>
   </si>
   <si>
-    <t xml:space="preserve">27.186014175415</t>
+    <t xml:space="preserve">27.1860160827637</t>
   </si>
   <si>
     <t xml:space="preserve">27.1164417266846</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0120811462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1426563262939</t>
+    <t xml:space="preserve">27.012077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1426582336426</t>
   </si>
   <si>
     <t xml:space="preserve">28.8036079406738</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0992965698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3775901794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5863151550293</t>
+    <t xml:space="preserve">29.0992984771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.377592086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5863132476807</t>
   </si>
   <si>
     <t xml:space="preserve">30.0385456085205</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2210502624512</t>
+    <t xml:space="preserve">29.2210521697998</t>
   </si>
   <si>
     <t xml:space="preserve">29.081901550293</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">28.7688217163086</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4035587310791</t>
+    <t xml:space="preserve">28.4035606384277</t>
   </si>
   <si>
     <t xml:space="preserve">27.6904258728027</t>
@@ -3020,55 +3020,55 @@
     <t xml:space="preserve">26.7859649658203</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5946350097656</t>
+    <t xml:space="preserve">26.5946369171143</t>
   </si>
   <si>
     <t xml:space="preserve">27.412130355835</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6294250488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6208515167236</t>
+    <t xml:space="preserve">26.6294231414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.620849609375</t>
   </si>
   <si>
     <t xml:space="preserve">26.6468162536621</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5250625610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2034091949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3077697753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.707820892334</t>
+    <t xml:space="preserve">26.5250644683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2034072875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.307767868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7078189849854</t>
   </si>
   <si>
     <t xml:space="preserve">30.108118057251</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1340866088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.047119140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2906284332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8905773162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3080196380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8560409545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7342853546143</t>
+    <t xml:space="preserve">29.1340847015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0471229553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2906246185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8905792236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3080215454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8560390472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7342872619629</t>
   </si>
   <si>
     <t xml:space="preserve">30.2298717498779</t>
@@ -3077,28 +3077,28 @@
     <t xml:space="preserve">30.3690223693848</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4385948181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0559368133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2994518280029</t>
+    <t xml:space="preserve">30.4385986328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0559406280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2994480133057</t>
   </si>
   <si>
     <t xml:space="preserve">29.9515762329102</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6125316619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9951877593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6039638519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8300743103027</t>
+    <t xml:space="preserve">30.6125335693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9951858520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6039581298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8300685882568</t>
   </si>
   <si>
     <t xml:space="preserve">31.5691719055176</t>
@@ -3110,40 +3110,40 @@
     <t xml:space="preserve">31.7778949737549</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4995956420898</t>
+    <t xml:space="preserve">31.4996032714844</t>
   </si>
   <si>
     <t xml:space="preserve">32.0387992858887</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6909275054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3430576324463</t>
+    <t xml:space="preserve">31.6909255981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3430557250977</t>
   </si>
   <si>
     <t xml:space="preserve">31.4474182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2734832763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7605018615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.708324432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5865631103516</t>
+    <t xml:space="preserve">31.2734851837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7604999542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7083206176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5865669250488</t>
   </si>
   <si>
     <t xml:space="preserve">31.743106842041</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6387500762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6735305786133</t>
+    <t xml:space="preserve">31.638744354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6735324859619</t>
   </si>
   <si>
     <t xml:space="preserve">32.3866691589355</t>
@@ -3152,58 +3152,58 @@
     <t xml:space="preserve">32.5606002807617</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8474655151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5432090759277</t>
+    <t xml:space="preserve">31.8474712371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5432052612305</t>
   </si>
   <si>
     <t xml:space="preserve">31.8996486663818</t>
   </si>
   <si>
-    <t xml:space="preserve">31.516996383667</t>
+    <t xml:space="preserve">31.5169906616211</t>
   </si>
   <si>
     <t xml:space="preserve">31.7952919006348</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8126850128174</t>
+    <t xml:space="preserve">31.8126831054688</t>
   </si>
   <si>
     <t xml:space="preserve">31.6213531494141</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4822082519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3952331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.155330657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9081153869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7845096588135</t>
+    <t xml:space="preserve">31.4822044372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3952369689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1553268432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9081134796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7845077514648</t>
   </si>
   <si>
     <t xml:space="preserve">32.1376724243164</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1729850769043</t>
+    <t xml:space="preserve">32.1729888916016</t>
   </si>
   <si>
     <t xml:space="preserve">32.2612800598145</t>
   </si>
   <si>
-    <t xml:space="preserve">32.278938293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7491912841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7668533325195</t>
+    <t xml:space="preserve">32.2789421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7491931915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7668514251709</t>
   </si>
   <si>
     <t xml:space="preserve">31.8728008270264</t>
@@ -3215,7 +3215,7 @@
     <t xml:space="preserve">33.0029144287109</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4443664550781</t>
+    <t xml:space="preserve">33.4443626403809</t>
   </si>
   <si>
     <t xml:space="preserve">33.3031044006348</t>
@@ -3224,13 +3224,13 @@
     <t xml:space="preserve">34.3096122741699</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9982719421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9806213378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2808036804199</t>
+    <t xml:space="preserve">34.9982757568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9806175231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2808074951172</t>
   </si>
   <si>
     <t xml:space="preserve">34.7863807678223</t>
@@ -3245,13 +3245,13 @@
     <t xml:space="preserve">33.3384170532227</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9499397277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.179500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2148132324219</t>
+    <t xml:space="preserve">32.9499435424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1794967651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2148094177246</t>
   </si>
   <si>
     <t xml:space="preserve">33.0912055969238</t>
@@ -3263,10 +3263,10 @@
     <t xml:space="preserve">33.0205764770508</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8439903259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1441802978516</t>
+    <t xml:space="preserve">32.843994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1441764831543</t>
   </si>
   <si>
     <t xml:space="preserve">32.0317192077637</t>
@@ -3281,37 +3281,37 @@
     <t xml:space="preserve">33.2677879333496</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4267082214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8616485595703</t>
+    <t xml:space="preserve">33.4267120361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8616523742676</t>
   </si>
   <si>
     <t xml:space="preserve">32.2083015441895</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2017936706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1135025024414</t>
+    <t xml:space="preserve">31.2017955780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1135063171387</t>
   </si>
   <si>
     <t xml:space="preserve">31.9610900878906</t>
   </si>
   <si>
-    <t xml:space="preserve">33.126522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9322814941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9257755279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5438041687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0270805358887</t>
+    <t xml:space="preserve">33.1265258789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9322853088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9257698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5438079833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0270843505859</t>
   </si>
   <si>
     <t xml:space="preserve">33.8681602478027</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">34.0800552368164</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3449287414551</t>
+    <t xml:space="preserve">34.3449325561523</t>
   </si>
   <si>
     <t xml:space="preserve">34.380241394043</t>
@@ -3329,22 +3329,22 @@
     <t xml:space="preserve">34.1330299377441</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5215110778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1506881713867</t>
+    <t xml:space="preserve">34.5215072631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.150691986084</t>
   </si>
   <si>
     <t xml:space="preserve">34.2036628723145</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1153717041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9387969970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6209526062012</t>
+    <t xml:space="preserve">34.1153755187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.938793182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6209487915039</t>
   </si>
   <si>
     <t xml:space="preserve">33.691577911377</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">34.2919540405273</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5038566589355</t>
+    <t xml:space="preserve">34.503849029541</t>
   </si>
   <si>
     <t xml:space="preserve">32.914623260498</t>
@@ -3365,52 +3365,52 @@
     <t xml:space="preserve">33.5149993896484</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5503158569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.815185546875</t>
+    <t xml:space="preserve">33.5503120422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8151893615723</t>
   </si>
   <si>
     <t xml:space="preserve">34.6451187133789</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1395378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8570137023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6804351806641</t>
+    <t xml:space="preserve">35.1395416259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8570098876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6804313659668</t>
   </si>
   <si>
     <t xml:space="preserve">35.0865707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3272666931152</t>
+    <t xml:space="preserve">34.3272743225098</t>
   </si>
   <si>
     <t xml:space="preserve">31.2371101379395</t>
   </si>
   <si>
-    <t xml:space="preserve">30.424840927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1776294708252</t>
+    <t xml:space="preserve">30.4248390197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1776237487793</t>
   </si>
   <si>
     <t xml:space="preserve">30.0716800689697</t>
   </si>
   <si>
-    <t xml:space="preserve">29.559591293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6125659942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6478862762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2306003570557</t>
+    <t xml:space="preserve">29.5595932006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6125679016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6478824615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2306022644043</t>
   </si>
   <si>
     <t xml:space="preserve">29.3476982116699</t>
@@ -3425,7 +3425,7 @@
     <t xml:space="preserve">27.8467617034912</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4406261444092</t>
+    <t xml:space="preserve">27.4406280517578</t>
   </si>
   <si>
     <t xml:space="preserve">28.5530834197998</t>
@@ -3452,25 +3452,25 @@
     <t xml:space="preserve">29.2240886688232</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1004829406738</t>
+    <t xml:space="preserve">29.1004810333252</t>
   </si>
   <si>
     <t xml:space="preserve">29.471305847168</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1358013153076</t>
+    <t xml:space="preserve">29.135799407959</t>
   </si>
   <si>
     <t xml:space="preserve">29.3123817443848</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8244609832764</t>
+    <t xml:space="preserve">29.824462890625</t>
   </si>
   <si>
     <t xml:space="preserve">29.9480667114258</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7891502380371</t>
+    <t xml:space="preserve">29.7891521453857</t>
   </si>
   <si>
     <t xml:space="preserve">29.2417488098145</t>
@@ -3479,25 +3479,25 @@
     <t xml:space="preserve">29.8421211242676</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0010433197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9833869934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5661010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9545803070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1952857971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1246509552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3300380706787</t>
+    <t xml:space="preserve">30.0010471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9833850860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5660991668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9545783996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1952838897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1246471405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.330041885376</t>
   </si>
   <si>
     <t xml:space="preserve">27.2287292480469</t>
@@ -3524,28 +3524,28 @@
     <t xml:space="preserve">26.6989860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8755722045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0698051452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7807693481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4341163635254</t>
+    <t xml:space="preserve">26.8755702972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0698070526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7807712554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.434118270874</t>
   </si>
   <si>
     <t xml:space="preserve">26.1162719726562</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8579120635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3634834289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1339321136475</t>
+    <t xml:space="preserve">26.85791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3634853363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1339282989502</t>
   </si>
   <si>
     <t xml:space="preserve">26.3987998962402</t>
@@ -3557,19 +3557,19 @@
     <t xml:space="preserve">26.575382232666</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7519626617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3105087280273</t>
+    <t xml:space="preserve">26.7519607543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.310510635376</t>
   </si>
   <si>
     <t xml:space="preserve">26.4694328308105</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8225955963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2110729217529</t>
+    <t xml:space="preserve">26.8225936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2110710144043</t>
   </si>
   <si>
     <t xml:space="preserve">27.0521488189697</t>
@@ -3587,13 +3587,13 @@
     <t xml:space="preserve">27.8291053771973</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4053077697754</t>
+    <t xml:space="preserve">27.4053115844727</t>
   </si>
   <si>
     <t xml:space="preserve">27.7761287689209</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6525249481201</t>
+    <t xml:space="preserve">27.6525211334229</t>
   </si>
   <si>
     <t xml:space="preserve">27.3699932098389</t>
@@ -3602,43 +3602,43 @@
     <t xml:space="preserve">26.4164581298828</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9155216217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0214710235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7212867736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8978672027588</t>
+    <t xml:space="preserve">24.9155235290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0214729309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.721284866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8978652954102</t>
   </si>
   <si>
     <t xml:space="preserve">25.2686862945557</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5447025299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.10325050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8383808135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.692476272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4517726898193</t>
+    <t xml:space="preserve">24.5447044372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1032524108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8383827209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6924781799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.451774597168</t>
   </si>
   <si>
     <t xml:space="preserve">27.5112571716309</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9703674316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2993602752686</t>
+    <t xml:space="preserve">27.9703693389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2993621826172</t>
   </si>
   <si>
     <t xml:space="preserve">26.9285430908203</t>
@@ -3647,10 +3647,10 @@
     <t xml:space="preserve">27.5289173126221</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4759407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9638595581055</t>
+    <t xml:space="preserve">27.475944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9638614654541</t>
   </si>
   <si>
     <t xml:space="preserve">26.3811416625977</t>
@@ -3665,61 +3665,61 @@
     <t xml:space="preserve">26.7872772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0986156463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4629249572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8095760345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2333679199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1274185180664</t>
+    <t xml:space="preserve">26.0986137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4629230499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8095741271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2333660125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.127420425415</t>
   </si>
   <si>
     <t xml:space="preserve">24.7389430999756</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1738834381104</t>
+    <t xml:space="preserve">24.173885345459</t>
   </si>
   <si>
     <t xml:space="preserve">22.4080791473389</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4192295074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3662548065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6906070709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.066068649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9424610137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3551025390625</t>
+    <t xml:space="preserve">21.4192276000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3662567138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6906089782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0660667419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9424591064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3551044464111</t>
   </si>
   <si>
     <t xml:space="preserve">21.772388458252</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7788982391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4610557556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2844696044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2314987182617</t>
+    <t xml:space="preserve">22.7789001464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4610538482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2844715118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2314968109131</t>
   </si>
   <si>
     <t xml:space="preserve">21.8077049255371</t>
@@ -3731,19 +3731,19 @@
     <t xml:space="preserve">21.4722003936768</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5604915618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.990795135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3374443054199</t>
+    <t xml:space="preserve">21.5604934692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9907932281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3374462127686</t>
   </si>
   <si>
     <t xml:space="preserve">21.8430213928223</t>
   </si>
   <si>
-    <t xml:space="preserve">21.754732131958</t>
+    <t xml:space="preserve">21.7547302246094</t>
   </si>
   <si>
     <t xml:space="preserve">21.7900485992432</t>
@@ -3752,10 +3752,10 @@
     <t xml:space="preserve">21.5958061218262</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3839111328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9601192474365</t>
+    <t xml:space="preserve">21.3839130401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9601173400879</t>
   </si>
   <si>
     <t xml:space="preserve">21.1896724700928</t>
@@ -3767,10 +3767,10 @@
     <t xml:space="preserve">21.4015693664551</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7658767700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8365116119385</t>
+    <t xml:space="preserve">20.7658786773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8365135192871</t>
   </si>
   <si>
     <t xml:space="preserve">20.0595550537109</t>
@@ -3779,10 +3779,10 @@
     <t xml:space="preserve">19.9359512329102</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3774032592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5186653137207</t>
+    <t xml:space="preserve">20.3774013519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5186634063721</t>
   </si>
   <si>
     <t xml:space="preserve">19.8653202056885</t>
@@ -3797,10 +3797,10 @@
     <t xml:space="preserve">20.5363235473633</t>
   </si>
   <si>
-    <t xml:space="preserve">20.041898727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1943130493164</t>
+    <t xml:space="preserve">20.0418968200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1943111419678</t>
   </si>
   <si>
     <t xml:space="preserve">19.4238662719727</t>
@@ -3809,37 +3809,37 @@
     <t xml:space="preserve">19.7770290374756</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3420886993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3355751037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5474739074707</t>
+    <t xml:space="preserve">20.3420867919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3355770111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5474720001221</t>
   </si>
   <si>
     <t xml:space="preserve">19.6710815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9111518859863</t>
+    <t xml:space="preserve">19.911153793335</t>
   </si>
   <si>
     <t xml:space="preserve">19.0677719116211</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4711303710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1311645507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3878479003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9012107849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6995315551758</t>
+    <t xml:space="preserve">19.4711284637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1311664581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3878498077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9012126922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6995334625244</t>
   </si>
   <si>
     <t xml:space="preserve">20.3145122528076</t>
@@ -3848,31 +3848,31 @@
     <t xml:space="preserve">20.6445293426514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0944976806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4061851501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1678371429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5811367034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.306116104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3710651397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7560882568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0127696990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0960502624512</t>
+    <t xml:space="preserve">20.0944995880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4061832427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1678352355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5811347961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3061180114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3710670471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7560863494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0127716064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0960483551025</t>
   </si>
   <si>
     <t xml:space="preserve">19.0861053466797</t>
@@ -3890,19 +3890,19 @@
     <t xml:space="preserve">17.261833190918</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1793308258057</t>
+    <t xml:space="preserve">17.179328918457</t>
   </si>
   <si>
     <t xml:space="preserve">17.2343330383301</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0968227386475</t>
+    <t xml:space="preserve">17.0968246459961</t>
   </si>
   <si>
     <t xml:space="preserve">16.757640838623</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2626075744629</t>
+    <t xml:space="preserve">16.2626094818115</t>
   </si>
   <si>
     <t xml:space="preserve">16.1617698669434</t>
@@ -3911,10 +3911,10 @@
     <t xml:space="preserve">16.1709384918213</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9875946044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3817863464355</t>
+    <t xml:space="preserve">15.9875926971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3817825317383</t>
   </si>
   <si>
     <t xml:space="preserve">16.7851390838623</t>
@@ -3932,7 +3932,7 @@
     <t xml:space="preserve">16.9501495361328</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4092864990234</t>
+    <t xml:space="preserve">16.4092845916748</t>
   </si>
   <si>
     <t xml:space="preserve">16.6843013763428</t>
@@ -3941,10 +3941,10 @@
     <t xml:space="preserve">16.9043140411377</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0693225860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9593162536621</t>
+    <t xml:space="preserve">17.0693244934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9593181610107</t>
   </si>
   <si>
     <t xml:space="preserve">17.1334934234619</t>
@@ -3956,7 +3956,7 @@
     <t xml:space="preserve">16.3359470367432</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8500871658325</t>
+    <t xml:space="preserve">15.8500881195068</t>
   </si>
   <si>
     <t xml:space="preserve">16.8218078613281</t>
@@ -3965,13 +3965,13 @@
     <t xml:space="preserve">16.5284595489502</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1151580810547</t>
+    <t xml:space="preserve">17.1151599884033</t>
   </si>
   <si>
     <t xml:space="preserve">17.8852043151855</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6560230255127</t>
+    <t xml:space="preserve">17.6560249328613</t>
   </si>
   <si>
     <t xml:space="preserve">17.6376876831055</t>
@@ -3995,13 +3995,13 @@
     <t xml:space="preserve">17.2159976959229</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3351726531982</t>
+    <t xml:space="preserve">17.3351707458496</t>
   </si>
   <si>
     <t xml:space="preserve">16.9868183135986</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0784893035889</t>
+    <t xml:space="preserve">17.0784912109375</t>
   </si>
   <si>
     <t xml:space="preserve">16.8584766387939</t>
@@ -4016,13 +4016,13 @@
     <t xml:space="preserve">15.9417572021484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0425968170166</t>
+    <t xml:space="preserve">16.0425987243652</t>
   </si>
   <si>
     <t xml:space="preserve">16.0150947570801</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6392402648926</t>
+    <t xml:space="preserve">15.6392383575439</t>
   </si>
   <si>
     <t xml:space="preserve">15.9142560958862</t>
@@ -4034,19 +4034,19 @@
     <t xml:space="preserve">15.2542181015015</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2175493240356</t>
+    <t xml:space="preserve">15.2175483703613</t>
   </si>
   <si>
     <t xml:space="preserve">15.1992158889771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6117401123047</t>
+    <t xml:space="preserve">15.6117391586304</t>
   </si>
   <si>
     <t xml:space="preserve">16.0059280395508</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6942434310913</t>
+    <t xml:space="preserve">15.6942443847656</t>
   </si>
   <si>
     <t xml:space="preserve">14.9883699417114</t>
@@ -4055,7 +4055,7 @@
     <t xml:space="preserve">14.5758438110352</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5850114822388</t>
+    <t xml:space="preserve">14.5850124359131</t>
   </si>
   <si>
     <t xml:space="preserve">13.860803604126</t>
@@ -4076,16 +4076,16 @@
     <t xml:space="preserve">13.7599649429321</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9249744415283</t>
+    <t xml:space="preserve">13.924973487854</t>
   </si>
   <si>
     <t xml:space="preserve">13.3107719421387</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8149671554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5032815933228</t>
+    <t xml:space="preserve">13.8149681091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5032825469971</t>
   </si>
   <si>
     <t xml:space="preserve">13.8883047103882</t>
@@ -4094,7 +4094,7 @@
     <t xml:space="preserve">13.5124502182007</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6591243743896</t>
+    <t xml:space="preserve">13.659125328064</t>
   </si>
   <si>
     <t xml:space="preserve">13.3382730484009</t>
@@ -4106,13 +4106,13 @@
     <t xml:space="preserve">13.8516359329224</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5307846069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8424701690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1908226013184</t>
+    <t xml:space="preserve">13.5307836532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8424692153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1908235549927</t>
   </si>
   <si>
     <t xml:space="preserve">14.3466653823853</t>
@@ -4124,7 +4124,7 @@
     <t xml:space="preserve">14.1816549301147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5483427047729</t>
+    <t xml:space="preserve">14.5483436584473</t>
   </si>
   <si>
     <t xml:space="preserve">14.8233594894409</t>
@@ -4133,19 +4133,19 @@
     <t xml:space="preserve">15.5659017562866</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7217454910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9050903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1526031494141</t>
+    <t xml:space="preserve">15.7217445373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9050893783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1526050567627</t>
   </si>
   <si>
     <t xml:space="preserve">16.7026348114014</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2434997558594</t>
+    <t xml:space="preserve">17.2434978485107</t>
   </si>
   <si>
     <t xml:space="preserve">17.509349822998</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">18.2427234649658</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5528583526611</t>
+    <t xml:space="preserve">20.5528564453125</t>
   </si>
   <si>
     <t xml:space="preserve">20.717866897583</t>
@@ -4184,19 +4184,19 @@
     <t xml:space="preserve">19.562801361084</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8928184509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6544742584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8561515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4527969360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5261306762695</t>
+    <t xml:space="preserve">19.8928203582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6544723510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8561496734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4527931213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5261325836182</t>
   </si>
   <si>
     <t xml:space="preserve">19.7278099060059</t>
@@ -4208,7 +4208,7 @@
     <t xml:space="preserve">19.8378162384033</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3244514465332</t>
+    <t xml:space="preserve">19.3244552612305</t>
   </si>
   <si>
     <t xml:space="preserve">18.9760990142822</t>
@@ -4226,31 +4226,31 @@
     <t xml:space="preserve">19.2327823638916</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0578289031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1128311157227</t>
+    <t xml:space="preserve">20.0578269958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1128330230713</t>
   </si>
   <si>
     <t xml:space="preserve">20.2961769104004</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5161895751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8179321289062</t>
+    <t xml:space="preserve">20.5161876678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8179302215576</t>
   </si>
   <si>
     <t xml:space="preserve">21.2495651245117</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9928855895996</t>
+    <t xml:space="preserve">20.992883682251</t>
   </si>
   <si>
     <t xml:space="preserve">20.7728710174561</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8828773498535</t>
+    <t xml:space="preserve">20.8828792572021</t>
   </si>
   <si>
     <t xml:space="preserve">21.0478858947754</t>
@@ -4259,7 +4259,7 @@
     <t xml:space="preserve">20.8095397949219</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7362022399902</t>
+    <t xml:space="preserve">20.7362041473389</t>
   </si>
   <si>
     <t xml:space="preserve">19.7828121185303</t>
@@ -4271,16 +4271,16 @@
     <t xml:space="preserve">19.2511157989502</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8660945892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3977909088135</t>
+    <t xml:space="preserve">18.8660926818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3977928161621</t>
   </si>
   <si>
     <t xml:space="preserve">19.3427886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4894638061523</t>
+    <t xml:space="preserve">19.4894618988037</t>
   </si>
   <si>
     <t xml:space="preserve">19.5994701385498</t>
@@ -4289,19 +4289,19 @@
     <t xml:space="preserve">20.3511810302734</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8744850158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1494998931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0761623382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0394973754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9745483398438</t>
+    <t xml:space="preserve">19.8744869232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1495018005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0761642456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0394954681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9745502471924</t>
   </si>
   <si>
     <t xml:space="preserve">21.2128963470459</t>
@@ -4310,10 +4310,10 @@
     <t xml:space="preserve">21.5795860290527</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6345863342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6529216766357</t>
+    <t xml:space="preserve">21.6345882415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6529235839844</t>
   </si>
   <si>
     <t xml:space="preserve">21.6162509918213</t>
@@ -4322,7 +4322,7 @@
     <t xml:space="preserve">21.5429153442383</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6811981201172</t>
+    <t xml:space="preserve">20.6812000274658</t>
   </si>
   <si>
     <t xml:space="preserve">21.3045673370361</t>
@@ -4334,10 +4334,10 @@
     <t xml:space="preserve">20.4245204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5711936950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.966157913208</t>
+    <t xml:space="preserve">20.5711917877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9661560058594</t>
   </si>
   <si>
     <t xml:space="preserve">19.5077991485596</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">19.9294891357422</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0211601257324</t>
+    <t xml:space="preserve">20.0211620330811</t>
   </si>
   <si>
     <t xml:space="preserve">18.6460819244385</t>
@@ -4364,25 +4364,25 @@
     <t xml:space="preserve">18.481071472168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6094093322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4077339172363</t>
+    <t xml:space="preserve">18.6094131469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.407735824585</t>
   </si>
   <si>
     <t xml:space="preserve">18.3343963623047</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9210948944092</t>
+    <t xml:space="preserve">18.9210968017578</t>
   </si>
   <si>
     <t xml:space="preserve">19.2877864837646</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1961116790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1044425964355</t>
+    <t xml:space="preserve">19.1961135864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1044406890869</t>
   </si>
   <si>
     <t xml:space="preserve">18.7201499938965</t>
@@ -4397,13 +4397,13 @@
     <t xml:space="preserve">17.5378246307373</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7348785400391</t>
+    <t xml:space="preserve">17.7348766326904</t>
   </si>
   <si>
     <t xml:space="preserve">17.6410427093506</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2469329833984</t>
+    <t xml:space="preserve">17.2469348907471</t>
   </si>
   <si>
     <t xml:space="preserve">17.1437168121338</t>
@@ -4421,7 +4421,7 @@
     <t xml:space="preserve">17.0311126708984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9560451507568</t>
+    <t xml:space="preserve">16.9560432434082</t>
   </si>
   <si>
     <t xml:space="preserve">16.89035987854</t>
@@ -4433,19 +4433,19 @@
     <t xml:space="preserve">17.078031539917</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1852855682373</t>
+    <t xml:space="preserve">18.1852874755859</t>
   </si>
   <si>
     <t xml:space="preserve">18.2885055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.565975189209</t>
+    <t xml:space="preserve">17.5659732818604</t>
   </si>
   <si>
     <t xml:space="preserve">18.0069999694824</t>
   </si>
   <si>
-    <t xml:space="preserve">17.922550201416</t>
+    <t xml:space="preserve">17.9225482940674</t>
   </si>
   <si>
     <t xml:space="preserve">17.8662490844727</t>
@@ -4454,28 +4454,28 @@
     <t xml:space="preserve">17.8005619049072</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5753593444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7536468505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9319343566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9882335662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3354263305664</t>
+    <t xml:space="preserve">17.5753574371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7536449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9319324493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9882354736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3354244232178</t>
   </si>
   <si>
     <t xml:space="preserve">18.5137119293213</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7858333587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5230960845947</t>
+    <t xml:space="preserve">18.7858352661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5230941772461</t>
   </si>
   <si>
     <t xml:space="preserve">18.7483005523682</t>
@@ -4502,13 +4502,13 @@
     <t xml:space="preserve">20.3435001373291</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7804870605469</t>
+    <t xml:space="preserve">19.7804889678955</t>
   </si>
   <si>
     <t xml:space="preserve">19.8555564880371</t>
   </si>
   <si>
-    <t xml:space="preserve">19.874324798584</t>
+    <t xml:space="preserve">19.8743228912354</t>
   </si>
   <si>
     <t xml:space="preserve">19.198709487915</t>
@@ -4520,19 +4520,19 @@
     <t xml:space="preserve">19.6678848266602</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2737789154053</t>
+    <t xml:space="preserve">19.2737770080566</t>
   </si>
   <si>
     <t xml:space="preserve">19.4989833831787</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3622665405273</t>
+    <t xml:space="preserve">20.362268447876</t>
   </si>
   <si>
     <t xml:space="preserve">20.7939109802246</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6759643554688</t>
+    <t xml:space="preserve">21.6759624481201</t>
   </si>
   <si>
     <t xml:space="preserve">21.826099395752</t>
@@ -4541,7 +4541,7 @@
     <t xml:space="preserve">22.0325355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1639060974121</t>
+    <t xml:space="preserve">22.1639080047607</t>
   </si>
   <si>
     <t xml:space="preserve">22.0888385772705</t>
@@ -4556,19 +4556,19 @@
     <t xml:space="preserve">22.2389755249023</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2952766418457</t>
+    <t xml:space="preserve">22.2952747344971</t>
   </si>
   <si>
     <t xml:space="preserve">22.482946395874</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9574661254883</t>
+    <t xml:space="preserve">21.9574680328369</t>
   </si>
   <si>
     <t xml:space="preserve">21.8448677062988</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7697982788086</t>
+    <t xml:space="preserve">21.7698001861572</t>
   </si>
   <si>
     <t xml:space="preserve">21.7134971618652</t>
@@ -4577,13 +4577,13 @@
     <t xml:space="preserve">21.995002746582</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5767803192139</t>
+    <t xml:space="preserve">22.5767822265625</t>
   </si>
   <si>
     <t xml:space="preserve">22.670618057251</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9708881378174</t>
+    <t xml:space="preserve">22.970890045166</t>
   </si>
   <si>
     <t xml:space="preserve">22.914587020874</t>
@@ -4592,13 +4592,13 @@
     <t xml:space="preserve">23.158561706543</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2711639404297</t>
+    <t xml:space="preserve">23.2711620330811</t>
   </si>
   <si>
     <t xml:space="preserve">23.1397933959961</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4882926940918</t>
+    <t xml:space="preserve">21.4882907867432</t>
   </si>
   <si>
     <t xml:space="preserve">21.8824005126953</t>
@@ -4607,37 +4607,37 @@
     <t xml:space="preserve">21.8636322021484</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9252796173096</t>
+    <t xml:space="preserve">20.9252777099609</t>
   </si>
   <si>
     <t xml:space="preserve">21.0003471374512</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1692504882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2443180084229</t>
+    <t xml:space="preserve">21.1692523956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2443199157715</t>
   </si>
   <si>
     <t xml:space="preserve">20.8877468109131</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6813106536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1182975769043</t>
+    <t xml:space="preserve">20.6813087463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1182956695557</t>
   </si>
   <si>
     <t xml:space="preserve">20.3998012542725</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8930931091309</t>
+    <t xml:space="preserve">19.8930912017822</t>
   </si>
   <si>
     <t xml:space="preserve">19.2174758911133</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3488483428955</t>
+    <t xml:space="preserve">19.3488464355469</t>
   </si>
   <si>
     <t xml:space="preserve">19.7992553710938</t>
@@ -4661,7 +4661,7 @@
     <t xml:space="preserve">19.4426803588867</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3300800323486</t>
+    <t xml:space="preserve">19.330078125</t>
   </si>
   <si>
     <t xml:space="preserve">18.9359703063965</t>
@@ -4676,7 +4676,7 @@
     <t xml:space="preserve">19.686653137207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1236419677734</t>
+    <t xml:space="preserve">19.1236400604248</t>
   </si>
   <si>
     <t xml:space="preserve">18.9922695159912</t>
@@ -4688,7 +4688,7 @@
     <t xml:space="preserve">19.4051475524902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.818021774292</t>
+    <t xml:space="preserve">19.8180236816406</t>
   </si>
   <si>
     <t xml:space="preserve">19.9681606292725</t>
@@ -4697,13 +4697,13 @@
     <t xml:space="preserve">20.606237411499</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4695243835449</t>
+    <t xml:space="preserve">21.4695224761963</t>
   </si>
   <si>
     <t xml:space="preserve">24.7162265777588</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5848598480225</t>
+    <t xml:space="preserve">24.5848579406738</t>
   </si>
   <si>
     <t xml:space="preserve">24.6974601745605</t>
@@ -4715,13 +4715,13 @@
     <t xml:space="preserve">24.922664642334</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8475971221924</t>
+    <t xml:space="preserve">24.8475952148438</t>
   </si>
   <si>
     <t xml:space="preserve">25.4293766021729</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0486869812012</t>
+    <t xml:space="preserve">26.0486888885498</t>
   </si>
   <si>
     <t xml:space="preserve">25.710880279541</t>
@@ -4730,7 +4730,7 @@
     <t xml:space="preserve">26.2363605499268</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8422527313232</t>
+    <t xml:space="preserve">25.8422508239746</t>
   </si>
   <si>
     <t xml:space="preserve">25.9360847473145</t>
@@ -4742,10 +4742,10 @@
     <t xml:space="preserve">25.7484169006348</t>
   </si>
   <si>
-    <t xml:space="preserve">26.067455291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5741672515869</t>
+    <t xml:space="preserve">26.0674571990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5741653442383</t>
   </si>
   <si>
     <t xml:space="preserve">26.3114280700684</t>
@@ -4757,13 +4757,13 @@
     <t xml:space="preserve">26.7806053161621</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9119758605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0058116912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.231014251709</t>
+    <t xml:space="preserve">26.9119739532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0058097839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2310161590576</t>
   </si>
   <si>
     <t xml:space="preserve">27.1184120178223</t>
@@ -4778,16 +4778,16 @@
     <t xml:space="preserve">27.6814250946045</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7189598083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4749851226807</t>
+    <t xml:space="preserve">27.718957901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4749870300293</t>
   </si>
   <si>
     <t xml:space="preserve">27.7377262115479</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1693687438965</t>
+    <t xml:space="preserve">28.1693668365479</t>
   </si>
   <si>
     <t xml:space="preserve">27.9629287719727</t>
@@ -4796,25 +4796,25 @@
     <t xml:space="preserve">28.6573123931885</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5071754455566</t>
+    <t xml:space="preserve">28.507173538208</t>
   </si>
   <si>
     <t xml:space="preserve">28.6385440826416</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9307422637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.775260925293</t>
+    <t xml:space="preserve">26.9307403564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7752590179443</t>
   </si>
   <si>
     <t xml:space="preserve">27.8878612518311</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4321060180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8074474334717</t>
+    <t xml:space="preserve">28.4321041107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8074493408203</t>
   </si>
   <si>
     <t xml:space="preserve">29.2766265869141</t>
@@ -4829,16 +4829,16 @@
     <t xml:space="preserve">28.1881351470947</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8315601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7940292358398</t>
+    <t xml:space="preserve">27.8315620422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7940273284912</t>
   </si>
   <si>
     <t xml:space="preserve">27.9253959655762</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2819690704346</t>
+    <t xml:space="preserve">28.2819709777832</t>
   </si>
   <si>
     <t xml:space="preserve">29.1640224456787</t>
@@ -4859,13 +4859,13 @@
     <t xml:space="preserve">27.5500545501709</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1934795379639</t>
+    <t xml:space="preserve">27.1934776306152</t>
   </si>
   <si>
     <t xml:space="preserve">26.7243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2175941467285</t>
+    <t xml:space="preserve">26.2175922393799</t>
   </si>
   <si>
     <t xml:space="preserve">26.874439239502</t>
@@ -4892,10 +4892,10 @@
     <t xml:space="preserve">28.206901550293</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9951171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.019229888916</t>
+    <t xml:space="preserve">28.9951190948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0192317962646</t>
   </si>
   <si>
     <t xml:space="preserve">28.4884090423584</t>
@@ -4919,16 +4919,16 @@
     <t xml:space="preserve">30.383882522583</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0460758209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1211414337158</t>
+    <t xml:space="preserve">30.0460739135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1211395263672</t>
   </si>
   <si>
     <t xml:space="preserve">29.6519660949707</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9897708892822</t>
+    <t xml:space="preserve">29.9897727966309</t>
   </si>
   <si>
     <t xml:space="preserve">30.083610534668</t>
@@ -4949,13 +4949,13 @@
     <t xml:space="preserve">29.9334716796875</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5259418487549</t>
+    <t xml:space="preserve">28.5259399414062</t>
   </si>
   <si>
     <t xml:space="preserve">28.3007354736328</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0942993164062</t>
+    <t xml:space="preserve">28.0943012237549</t>
   </si>
   <si>
     <t xml:space="preserve">28.0379962921143</t>
@@ -4970,13 +4970,13 @@
     <t xml:space="preserve">29.5205955505371</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9763507843018</t>
+    <t xml:space="preserve">28.9763488769531</t>
   </si>
   <si>
     <t xml:space="preserve">29.4830627441406</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7645683288574</t>
+    <t xml:space="preserve">29.7645664215088</t>
   </si>
   <si>
     <t xml:space="preserve">28.9575843811035</t>
@@ -4994,7 +4994,7 @@
     <t xml:space="preserve">30.7779903411865</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3973007202148</t>
+    <t xml:space="preserve">31.3973026275635</t>
   </si>
   <si>
     <t xml:space="preserve">29.5581321716309</t>
@@ -5877,6 +5877,9 @@
   </si>
   <si>
     <t xml:space="preserve">30.7600002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8400001525879</t>
   </si>
 </sst>
 </file>
@@ -71293,7 +71296,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6909953704</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>144050</v>
@@ -71314,6 +71317,32 @@
         <v>1954</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6911458333</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>100736</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>31.1200008392334</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>30.3600006103516</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>30.6399993896484</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>30.8400001525879</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1955</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DLG.MI.xlsx
+++ b/data/DLG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="1956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1954" uniqueCount="1954">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,58 +38,58 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7391471862793</t>
+    <t xml:space="preserve">20.7391452789307</t>
   </si>
   <si>
     <t xml:space="preserve">DLG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5564212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6553974151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1757469177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9777965545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7722320556641</t>
+    <t xml:space="preserve">20.5564193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6553955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.175745010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9777984619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7722339630127</t>
   </si>
   <si>
     <t xml:space="preserve">19.4905338287354</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8864345550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5160083770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6328430175781</t>
+    <t xml:space="preserve">19.8864364624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5160064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6328411102295</t>
   </si>
   <si>
     <t xml:space="preserve">17.4348907470703</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5262508392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0542163848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8943347930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0135135650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6354732513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4451351165771</t>
+    <t xml:space="preserve">17.5262546539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0542144775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8943328857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0135154724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6354751586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4451370239258</t>
   </si>
   <si>
     <t xml:space="preserve">16.7116088867188</t>
@@ -98,49 +98,49 @@
     <t xml:space="preserve">16.8029689788818</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6735401153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1329822540283</t>
+    <t xml:space="preserve">16.6735420227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1329860687256</t>
   </si>
   <si>
     <t xml:space="preserve">15.9654846191406</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6533336639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9909601211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7777843475342</t>
+    <t xml:space="preserve">15.6533355712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9909591674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7777853012085</t>
   </si>
   <si>
     <t xml:space="preserve">15.3335666656494</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4123373031616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7397155761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4553804397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2574319839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4097013473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.75230884552</t>
+    <t xml:space="preserve">14.412335395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7397165298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4553861618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2574348449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4097003936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7523097991943</t>
   </si>
   <si>
     <t xml:space="preserve">15.3868618011475</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9121913909912</t>
+    <t xml:space="preserve">15.9121923446655</t>
   </si>
   <si>
     <t xml:space="preserve">15.9578723907471</t>
@@ -155,190 +155,190 @@
     <t xml:space="preserve">16.1938915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5593395233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7496757507324</t>
+    <t xml:space="preserve">16.5593376159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7496776580811</t>
   </si>
   <si>
     <t xml:space="preserve">15.8817405700684</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2193660736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.379246711731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0873031616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.714241027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2878856658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8969650268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3183393478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6076507568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9274196624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9883260726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8893537521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6152658462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3564071655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1356172561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2269792556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3487939834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0442523956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2345895767212</t>
+    <t xml:space="preserve">15.2193670272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3792486190796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0873050689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7142400741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2878866195679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8969640731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3183403015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6076526641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9274206161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9883289337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8893547058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6152677536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3564081192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1356163024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.226978302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3487911224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0442571640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2345914840698</t>
   </si>
   <si>
     <t xml:space="preserve">15.0594816207886</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1432323455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5493793487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7853956222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8234624862671</t>
+    <t xml:space="preserve">15.1432313919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5493803024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7853965759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8234643936157</t>
   </si>
   <si>
     <t xml:space="preserve">14.7831659317017</t>
   </si>
   <si>
-    <t xml:space="preserve">14.977988243103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1572256088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1494340896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.96240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9857797622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9546098709106</t>
+    <t xml:space="preserve">14.9779891967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1572284698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.149432182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9624042510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9857816696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9546117782593</t>
   </si>
   <si>
     <t xml:space="preserve">14.8533020019531</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4689445495605</t>
+    <t xml:space="preserve">15.4689435958862</t>
   </si>
   <si>
     <t xml:space="preserve">15.6715593338013</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2170639038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7572813034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0300312042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2404441833496</t>
+    <t xml:space="preserve">16.21706199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7572803497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0300350189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.240442276001</t>
   </si>
   <si>
     <t xml:space="preserve">16.1469268798828</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3495426177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5054035186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3105792999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7288875579834</t>
+    <t xml:space="preserve">16.3495445251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5054016113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3105773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.728889465332</t>
   </si>
   <si>
     <t xml:space="preserve">16.7937412261963</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0742855072021</t>
+    <t xml:space="preserve">17.0742835998535</t>
   </si>
   <si>
     <t xml:space="preserve">16.7625675201416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7547740936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8482913970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1132469177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3002834320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7678527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9081249237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9470920562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0639820098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4848003387451</t>
+    <t xml:space="preserve">16.7547721862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8482894897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1132488250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3002796173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7678546905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9081287384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9470901489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.063985824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4848022460938</t>
   </si>
   <si>
     <t xml:space="preserve">18.788724899292</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4614238739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3367366790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2743949890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0795726776123</t>
+    <t xml:space="preserve">18.46142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3367385864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2743968963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0795707702637</t>
   </si>
   <si>
     <t xml:space="preserve">18.6484546661377</t>
@@ -347,16 +347,16 @@
     <t xml:space="preserve">18.8276901245117</t>
   </si>
   <si>
-    <t xml:space="preserve">18.453634262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8379878997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3937931060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2535209655762</t>
+    <t xml:space="preserve">18.4536323547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8379917144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3937911987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2535190582275</t>
   </si>
   <si>
     <t xml:space="preserve">17.0820789337158</t>
@@ -365,55 +365,55 @@
     <t xml:space="preserve">17.4951019287109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9237098693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8224048614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7834358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9315052032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6768474578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5234928131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1157531738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3651275634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6612586975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6300868988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8975534439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7806606292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5468711853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7884521484375</t>
+    <t xml:space="preserve">17.923713684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8224067687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7834396362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9315032958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6768455505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.523494720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1157550811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3651294708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6612606048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.630090713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8975553512573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7806596755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5468721389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7884540557861</t>
   </si>
   <si>
     <t xml:space="preserve">16.3729209899902</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1858921051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1625118255615</t>
+    <t xml:space="preserve">16.1858901977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1625137329102</t>
   </si>
   <si>
     <t xml:space="preserve">16.419677734375</t>
@@ -431,58 +431,58 @@
     <t xml:space="preserve">16.9184246063232</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8716659545898</t>
+    <t xml:space="preserve">16.8716697692871</t>
   </si>
   <si>
     <t xml:space="preserve">16.8015308380127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6119937896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2223491668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5964107513428</t>
+    <t xml:space="preserve">17.6119956970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2223510742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5964088439941</t>
   </si>
   <si>
     <t xml:space="preserve">17.4171733856201</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6587524414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3158626556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3236560821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.502893447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0561904907227</t>
+    <t xml:space="preserve">17.6587543487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3158645629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.323657989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5028953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0561923980713</t>
   </si>
   <si>
     <t xml:space="preserve">18.5393543243408</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7030010223389</t>
+    <t xml:space="preserve">18.7030029296875</t>
   </si>
   <si>
     <t xml:space="preserve">18.664041519165</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8121013641357</t>
+    <t xml:space="preserve">18.812105178833</t>
   </si>
   <si>
     <t xml:space="preserve">18.0951557159424</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1497039794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9003314971924</t>
+    <t xml:space="preserve">18.1497077941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9003295898438</t>
   </si>
   <si>
     <t xml:space="preserve">18.1574993133545</t>
@@ -491,52 +491,52 @@
     <t xml:space="preserve">17.8769569396973</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6665458679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9704685211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0328159332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5106868743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5730285644531</t>
+    <t xml:space="preserve">17.6665439605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9704723358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0328121185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5106887817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5730304718018</t>
   </si>
   <si>
     <t xml:space="preserve">17.3626232147217</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4015865325928</t>
+    <t xml:space="preserve">17.4015884399414</t>
   </si>
   <si>
     <t xml:space="preserve">17.2379360198975</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4093799591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1444225311279</t>
+    <t xml:space="preserve">17.4093818664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1444206237793</t>
   </si>
   <si>
     <t xml:space="preserve">16.81711769104</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6145000457764</t>
+    <t xml:space="preserve">16.614501953125</t>
   </si>
   <si>
     <t xml:space="preserve">16.6846370697021</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0197353363037</t>
+    <t xml:space="preserve">17.0197334289551</t>
   </si>
   <si>
     <t xml:space="preserve">17.128833770752</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2691059112549</t>
+    <t xml:space="preserve">17.2691078186035</t>
   </si>
   <si>
     <t xml:space="preserve">16.9963569641113</t>
@@ -545,22 +545,22 @@
     <t xml:space="preserve">17.4405517578125</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4639263153076</t>
+    <t xml:space="preserve">17.4639282226562</t>
   </si>
   <si>
     <t xml:space="preserve">16.8327026367188</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8249092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9028415679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.785945892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7469806671143</t>
+    <t xml:space="preserve">16.8249130249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9028377532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7859477996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7469825744629</t>
   </si>
   <si>
     <t xml:space="preserve">17.2768993377686</t>
@@ -569,58 +569,58 @@
     <t xml:space="preserve">17.2457275390625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0509014129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0976600646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9573879241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2301406860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2067623138428</t>
+    <t xml:space="preserve">17.0509033203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0976638793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9573917388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2301425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.20676612854</t>
   </si>
   <si>
     <t xml:space="preserve">17.4327602386475</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2846965789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0664901733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9521036148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9832744598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2560272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3339576721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9988613128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4065990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.313084602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1182622909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5131912231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0923767089844</t>
+    <t xml:space="preserve">17.2846927642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0664920806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9521026611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9832763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2560291290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3339557647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9988632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4065999984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3130826950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.118260383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5131969451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0923748016357</t>
   </si>
   <si>
     <t xml:space="preserve">15.9131383895874</t>
@@ -629,31 +629,31 @@
     <t xml:space="preserve">16.1780967712402</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7158088684082</t>
+    <t xml:space="preserve">16.7158126831055</t>
   </si>
   <si>
     <t xml:space="preserve">17.0586967468262</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4664363861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.224853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9754838943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7080192565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4976081848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6924285888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5599498748779</t>
+    <t xml:space="preserve">16.466438293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2248592376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9754819869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7080173492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4976100921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6924324035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5599536895752</t>
   </si>
   <si>
     <t xml:space="preserve">16.7703590393066</t>
@@ -662,13 +662,13 @@
     <t xml:space="preserve">16.8638763427734</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0275249481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4561386108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4483432769775</t>
+    <t xml:space="preserve">17.0275268554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4561347961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4483451843262</t>
   </si>
   <si>
     <t xml:space="preserve">17.8847465515137</t>
@@ -677,49 +677,49 @@
     <t xml:space="preserve">18.1185359954834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2354278564453</t>
+    <t xml:space="preserve">18.2354259490967</t>
   </si>
   <si>
     <t xml:space="preserve">18.0172290802002</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8457813262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9626770019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.869161605835</t>
+    <t xml:space="preserve">17.8457832336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9626750946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8691635131836</t>
   </si>
   <si>
     <t xml:space="preserve">17.6353721618652</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7912330627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5808258056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6509590148926</t>
+    <t xml:space="preserve">17.7912311553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5808219909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6509609222412</t>
   </si>
   <si>
     <t xml:space="preserve">18.1107406616211</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9782600402832</t>
+    <t xml:space="preserve">17.9782619476318</t>
   </si>
   <si>
     <t xml:space="preserve">18.3133583068848</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2042541503906</t>
+    <t xml:space="preserve">18.2042579650879</t>
   </si>
   <si>
     <t xml:space="preserve">18.4692153930664</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0848579406738</t>
+    <t xml:space="preserve">19.0848598480225</t>
   </si>
   <si>
     <t xml:space="preserve">19.349817276001</t>
@@ -728,22 +728,22 @@
     <t xml:space="preserve">19.2952671051025</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4667129516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2485065460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3186435699463</t>
+    <t xml:space="preserve">19.4667110443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2485103607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3186454772949</t>
   </si>
   <si>
     <t xml:space="preserve">19.0614795684814</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4199485778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2407131195068</t>
+    <t xml:space="preserve">19.4199504852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2407150268555</t>
   </si>
   <si>
     <t xml:space="preserve">19.0926494598389</t>
@@ -752,76 +752,76 @@
     <t xml:space="preserve">19.4511241912842</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8588619232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6406574249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9056205749512</t>
+    <t xml:space="preserve">18.8588638305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.640661239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9056224822998</t>
   </si>
   <si>
     <t xml:space="preserve">19.2329235076904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4978847503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1914482116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9888381958008</t>
+    <t xml:space="preserve">19.4978809356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1914520263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9888362884521</t>
   </si>
   <si>
     <t xml:space="preserve">20.1213130950928</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9732475280762</t>
+    <t xml:space="preserve">19.9732513427734</t>
   </si>
   <si>
     <t xml:space="preserve">20.9551582336426</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6278495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2201156616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0408802032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7915077209473</t>
+    <t xml:space="preserve">20.6278533935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2201175689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0408782958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7915058135986</t>
   </si>
   <si>
     <t xml:space="preserve">20.7447490692139</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8616466522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2434959411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9006061553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0330848693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.978536605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6721019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4149398803711</t>
+    <t xml:space="preserve">20.8616428375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2434978485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9006080627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.033088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9785346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6721057891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4149417877197</t>
   </si>
   <si>
     <t xml:space="preserve">21.3136310577393</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1967391967773</t>
+    <t xml:space="preserve">21.1967372894287</t>
   </si>
   <si>
     <t xml:space="preserve">21.4227333068848</t>
@@ -830,43 +830,43 @@
     <t xml:space="preserve">21.5785903930664</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1884727478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1002025604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9477291107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0279769897461</t>
+    <t xml:space="preserve">22.1884708404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1002044677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.947732925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0279808044434</t>
   </si>
   <si>
     <t xml:space="preserve">21.9878540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8273582458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.348970413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4693412780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8946514129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3199634552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2878684997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8786010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0310726165771</t>
+    <t xml:space="preserve">21.8273601531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3489685058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4693393707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8946533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3199653625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2878646850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.878604888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0310745239258</t>
   </si>
   <si>
     <t xml:space="preserve">23.4483604431152</t>
@@ -875,31 +875,31 @@
     <t xml:space="preserve">23.0230484008789</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9026756286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6218109130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5014381408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.255765914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8434047698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0600776672363</t>
+    <t xml:space="preserve">22.9026737213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6218090057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5014419555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2557678222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8434104919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0600757598877</t>
   </si>
   <si>
     <t xml:space="preserve">22.6298370361328</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7341575622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9267501831055</t>
+    <t xml:space="preserve">22.7341556549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9267520904541</t>
   </si>
   <si>
     <t xml:space="preserve">23.2316932678223</t>
@@ -908,19 +908,19 @@
     <t xml:space="preserve">23.1434211730957</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1674938201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6570053100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7693557739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6730556488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8495998382568</t>
+    <t xml:space="preserve">23.1674919128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.65700340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7693519592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6730537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8495979309082</t>
   </si>
   <si>
     <t xml:space="preserve">23.7613258361816</t>
@@ -932,10 +932,10 @@
     <t xml:space="preserve">23.2958908081055</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4323120117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7051525115967</t>
+    <t xml:space="preserve">23.4323139190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7051544189453</t>
   </si>
   <si>
     <t xml:space="preserve">23.0069999694824</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">22.8304538726807</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7903308868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0631732940674</t>
+    <t xml:space="preserve">22.7903270721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0631713867188</t>
   </si>
   <si>
     <t xml:space="preserve">23.8255252838135</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">23.3921871185303</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2637901306152</t>
+    <t xml:space="preserve">23.2637939453125</t>
   </si>
   <si>
     <t xml:space="preserve">23.2718162536621</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">23.1915683746338</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9989719390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9076061248779</t>
+    <t xml:space="preserve">22.9989738464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9076080322266</t>
   </si>
   <si>
     <t xml:space="preserve">22.0199546813965</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">21.5545177459717</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4742698669434</t>
+    <t xml:space="preserve">21.4742660522461</t>
   </si>
   <si>
     <t xml:space="preserve">21.6267414093018</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7711849212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7390880584717</t>
+    <t xml:space="preserve">21.771183013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.739086151123</t>
   </si>
   <si>
     <t xml:space="preserve">21.8674831390381</t>
@@ -998,58 +998,58 @@
     <t xml:space="preserve">21.8594589233398</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5255146026611</t>
+    <t xml:space="preserve">22.5255126953125</t>
   </si>
   <si>
     <t xml:space="preserve">22.7421798706055</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3730430603027</t>
+    <t xml:space="preserve">22.3730392456055</t>
   </si>
   <si>
     <t xml:space="preserve">22.7181072235107</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8625526428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7100830078125</t>
+    <t xml:space="preserve">22.8625507354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7100811004639</t>
   </si>
   <si>
     <t xml:space="preserve">22.5335388183594</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6539077758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.292797088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7551364898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.241548538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9927845001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9446334838867</t>
+    <t xml:space="preserve">22.6539096832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2927951812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7551383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2415542602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9927825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9446353912354</t>
   </si>
   <si>
     <t xml:space="preserve">21.0730323791504</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0489559173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6396942138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4310455322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4872207641602</t>
+    <t xml:space="preserve">21.048957824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6396980285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4310474395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4872245788574</t>
   </si>
   <si>
     <t xml:space="preserve">20.8804378509521</t>
@@ -1058,22 +1058,22 @@
     <t xml:space="preserve">20.864387512207</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7119159698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5754928588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5995674133301</t>
+    <t xml:space="preserve">20.7119178771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5754947662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5995693206787</t>
   </si>
   <si>
     <t xml:space="preserve">20.6477184295654</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6156196594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5915431976318</t>
+    <t xml:space="preserve">20.6156177520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5915451049805</t>
   </si>
   <si>
     <t xml:space="preserve">20.3508033752441</t>
@@ -1082,10 +1082,10 @@
     <t xml:space="preserve">20.3427772521973</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2866058349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7440166473389</t>
+    <t xml:space="preserve">20.2866039276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7440147399902</t>
   </si>
   <si>
     <t xml:space="preserve">20.6717910766602</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">20.495246887207</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7359886169434</t>
+    <t xml:space="preserve">20.7359924316406</t>
   </si>
   <si>
     <t xml:space="preserve">21.2174777984619</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">21.3538990020752</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2335243225098</t>
+    <t xml:space="preserve">21.2335262298584</t>
   </si>
   <si>
     <t xml:space="preserve">20.9045104980469</t>
@@ -1115,82 +1115,82 @@
     <t xml:space="preserve">20.5594482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5353736877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4711742401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7520408630371</t>
+    <t xml:space="preserve">20.5353717803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4711761474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7520427703857</t>
   </si>
   <si>
     <t xml:space="preserve">21.3779716491699</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0650043487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2255039215088</t>
+    <t xml:space="preserve">21.0650062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2255001068115</t>
   </si>
   <si>
     <t xml:space="preserve">21.369945526123</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9156303405762</t>
+    <t xml:space="preserve">21.9156322479248</t>
   </si>
   <si>
     <t xml:space="preserve">21.4582195281982</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8032855987549</t>
+    <t xml:space="preserve">21.8032836914062</t>
   </si>
   <si>
     <t xml:space="preserve">21.795259475708</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3088455200195</t>
+    <t xml:space="preserve">22.3088417053223</t>
   </si>
   <si>
     <t xml:space="preserve">22.140323638916</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2285976409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2045230865479</t>
+    <t xml:space="preserve">22.2285957336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2045211791992</t>
   </si>
   <si>
     <t xml:space="preserve">22.1483497619629</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6940364837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0921764373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1082229614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.164400100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7742805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7662582397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5897102355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5415668487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4131660461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5174865722656</t>
+    <t xml:space="preserve">22.694034576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0921783447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.108226776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1644020080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7742824554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7662601470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5897121429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5415630340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4131679534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5174884796143</t>
   </si>
   <si>
     <t xml:space="preserve">22.1563739776611</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">22.5495872497559</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2526702880859</t>
+    <t xml:space="preserve">22.2526721954346</t>
   </si>
   <si>
     <t xml:space="preserve">22.2125492095947</t>
@@ -1223,10 +1223,10 @@
     <t xml:space="preserve">19.6205501556396</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5402984619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4921531677246</t>
+    <t xml:space="preserve">19.54030418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4921550750732</t>
   </si>
   <si>
     <t xml:space="preserve">19.4279537200928</t>
@@ -1235,22 +1235,22 @@
     <t xml:space="preserve">19.7409191131592</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6767196655273</t>
+    <t xml:space="preserve">19.676721572876</t>
   </si>
   <si>
     <t xml:space="preserve">19.8051204681396</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4199333190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7569694519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6606712341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1421604156494</t>
+    <t xml:space="preserve">19.4199314117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7569675445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6606731414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1421585083008</t>
   </si>
   <si>
     <t xml:space="preserve">2